--- a/testdata/PoToGRN-FOC Scenarios.xlsx
+++ b/testdata/PoToGRN-FOC Scenarios.xlsx
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2565" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2693" uniqueCount="154">
   <si>
     <t>Purchase Order &amp; GRN</t>
   </si>
@@ -386,6 +386,135 @@
   </si>
   <si>
     <t>GWL_Item_Dissimilar_Pl_03</t>
+  </si>
+  <si>
+    <t>208</t>
+  </si>
+  <si>
+    <t>2188.81384</t>
+  </si>
+  <si>
+    <t>92</t>
+  </si>
+  <si>
+    <t>540</t>
+  </si>
+  <si>
+    <t>1247.68149</t>
+  </si>
+  <si>
+    <t>230</t>
+  </si>
+  <si>
+    <t>43.3</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>175</t>
+  </si>
+  <si>
+    <t>1011.18714</t>
+  </si>
+  <si>
+    <t>140</t>
+  </si>
+  <si>
+    <t>1955.11257</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>4832.346</t>
+  </si>
+  <si>
+    <t>80</t>
+  </si>
+  <si>
+    <t>124.545</t>
+  </si>
+  <si>
+    <t>84</t>
+  </si>
+  <si>
+    <t>3038.44001</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>27.993</t>
+  </si>
+  <si>
+    <t>8129.88</t>
+  </si>
+  <si>
+    <t>23.994</t>
+  </si>
+  <si>
+    <t>246.36</t>
+  </si>
+  <si>
+    <t>76.661</t>
+  </si>
+  <si>
+    <t>4874.23482</t>
+  </si>
+  <si>
+    <t>59.994</t>
+  </si>
+  <si>
+    <t>129.9</t>
+  </si>
+  <si>
+    <t>69.994</t>
+  </si>
+  <si>
+    <t>12330.23258</t>
+  </si>
+  <si>
+    <t>73.326</t>
+  </si>
+  <si>
+    <t>373.635</t>
+  </si>
+  <si>
+    <t>70.659</t>
+  </si>
+  <si>
+    <t>7860.22599</t>
+  </si>
+  <si>
+    <t>69.993</t>
+  </si>
+  <si>
+    <t>71.661</t>
+  </si>
+  <si>
+    <t>11322.4372</t>
+  </si>
+  <si>
+    <t>86.658</t>
+  </si>
+  <si>
+    <t>112.332</t>
+  </si>
+  <si>
+    <t>6509.78864</t>
+  </si>
+  <si>
+    <t>120</t>
+  </si>
+  <si>
+    <t>93.327</t>
+  </si>
+  <si>
+    <t>4806.50043</t>
+  </si>
+  <si>
+    <t>79.992</t>
   </si>
 </sst>
 </file>
@@ -2090,11 +2219,11 @@
       <c r="AT4" s="29" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" s="30" t="s">
-        <v>78</v>
-      </c>
-      <c r="AV4" s="30" t="s">
-        <v>79</v>
+      <c r="AU4" t="s" s="0">
+        <v>111</v>
+      </c>
+      <c r="AV4" t="s" s="0">
+        <v>112</v>
       </c>
       <c r="AW4" s="29">
         <v>4</v>
@@ -2130,11 +2259,11 @@
       <c r="BL4" s="36" t="s">
         <v>84</v>
       </c>
-      <c r="BM4" s="30" t="s">
+      <c r="BM4" t="s" s="0">
         <v>79</v>
       </c>
-      <c r="BN4" s="30" t="s">
-        <v>85</v>
+      <c r="BN4" t="s" s="0">
+        <v>113</v>
       </c>
       <c r="BO4" s="29">
         <v>82.12</v>
@@ -2294,8 +2423,8 @@
   <dimension ref="A1:BQ5"/>
   <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
   <cols>
-    <col min="2" max="2" width="21.5454545454545" customWidth="1"/>
-    <col min="3" max="3" width="27.8181818181818" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="21.5454545454545"/>
+    <col min="3" max="3" customWidth="true" width="27.8181818181818"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -2812,12 +2941,8 @@
       <c r="AT4" s="29" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" s="30" t="s">
-        <v>78</v>
-      </c>
-      <c r="AV4" s="30" t="s">
-        <v>79</v>
-      </c>
+      <c r="AU4" s="0"/>
+      <c r="AV4" s="0"/>
       <c r="AW4" s="29">
         <v>4</v>
       </c>
@@ -2852,11 +2977,11 @@
       <c r="BL4" s="36" t="s">
         <v>84</v>
       </c>
-      <c r="BM4" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="BN4" s="30" t="s">
-        <v>85</v>
+      <c r="BM4" t="s" s="0">
+        <v>118</v>
+      </c>
+      <c r="BN4" t="s" s="0">
+        <v>118</v>
       </c>
       <c r="BO4" s="29">
         <v>82.12</v>
@@ -3518,11 +3643,11 @@
       <c r="AT4" s="29" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" s="30" t="s">
-        <v>78</v>
-      </c>
-      <c r="AV4" s="30" t="s">
-        <v>79</v>
+      <c r="AU4" t="s" s="0">
+        <v>123</v>
+      </c>
+      <c r="AV4" t="s" s="0">
+        <v>124</v>
       </c>
       <c r="AW4" s="29">
         <v>4</v>
@@ -3558,11 +3683,11 @@
       <c r="BL4" s="36" t="s">
         <v>84</v>
       </c>
-      <c r="BM4" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="BN4" s="30" t="s">
-        <v>85</v>
+      <c r="BM4" t="s" s="0">
+        <v>126</v>
+      </c>
+      <c r="BN4" t="s" s="0">
+        <v>125</v>
       </c>
       <c r="BO4" s="29">
         <v>82.12</v>
@@ -3722,8 +3847,8 @@
   <dimension ref="A1:BQ5"/>
   <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
   <cols>
-    <col min="2" max="2" width="21.5454545454545" customWidth="1"/>
-    <col min="3" max="3" width="27.8181818181818" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="21.5454545454545"/>
+    <col min="3" max="3" customWidth="true" width="27.8181818181818"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -4240,11 +4365,11 @@
       <c r="AT4" s="29" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" s="30" t="s">
-        <v>78</v>
-      </c>
-      <c r="AV4" s="30" t="s">
-        <v>79</v>
+      <c r="AU4" t="s" s="0">
+        <v>127</v>
+      </c>
+      <c r="AV4" t="s" s="0">
+        <v>128</v>
       </c>
       <c r="AW4" s="29">
         <v>4</v>
@@ -4280,11 +4405,11 @@
       <c r="BL4" s="36" t="s">
         <v>84</v>
       </c>
-      <c r="BM4" s="30" t="s">
+      <c r="BM4" t="s" s="0">
         <v>79</v>
       </c>
-      <c r="BN4" s="30" t="s">
-        <v>85</v>
+      <c r="BN4" t="s" s="0">
+        <v>129</v>
       </c>
       <c r="BO4" s="29">
         <v>82.12</v>
@@ -4432,8 +4557,8 @@
   <dimension ref="A1:BQ5"/>
   <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
   <cols>
-    <col min="2" max="2" width="21.5454545454545" customWidth="1"/>
-    <col min="3" max="3" width="27.8181818181818" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="21.5454545454545"/>
+    <col min="3" max="3" customWidth="true" width="27.8181818181818"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -4950,12 +5075,8 @@
       <c r="AT4" s="29" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" s="30" t="s">
-        <v>78</v>
-      </c>
-      <c r="AV4" s="30" t="s">
-        <v>79</v>
-      </c>
+      <c r="AU4" s="0"/>
+      <c r="AV4" s="0"/>
       <c r="AW4" s="29">
         <v>4</v>
       </c>
@@ -4990,12 +5111,8 @@
       <c r="BL4" s="36" t="s">
         <v>84</v>
       </c>
-      <c r="BM4" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="BN4" s="30" t="s">
-        <v>85</v>
-      </c>
+      <c r="BM4" s="0"/>
+      <c r="BN4" s="0"/>
       <c r="BO4" s="29">
         <v>82.12</v>
       </c>
@@ -5142,8 +5259,8 @@
   <dimension ref="A1:BQ5"/>
   <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
   <cols>
-    <col min="2" max="2" width="21.5454545454545" customWidth="1"/>
-    <col min="3" max="3" width="27.8181818181818" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="21.5454545454545"/>
+    <col min="3" max="3" customWidth="true" width="27.8181818181818"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -5660,12 +5777,8 @@
       <c r="AT4" s="29" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" s="30" t="s">
-        <v>78</v>
-      </c>
-      <c r="AV4" s="30" t="s">
-        <v>79</v>
-      </c>
+      <c r="AU4" s="0"/>
+      <c r="AV4" s="0"/>
       <c r="AW4" s="29">
         <v>4</v>
       </c>
@@ -5700,11 +5813,11 @@
       <c r="BL4" s="36" t="s">
         <v>84</v>
       </c>
-      <c r="BM4" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="BN4" s="30" t="s">
-        <v>85</v>
+      <c r="BM4" t="s" s="0">
+        <v>118</v>
+      </c>
+      <c r="BN4" t="s" s="0">
+        <v>118</v>
       </c>
       <c r="BO4" s="29">
         <v>82.12</v>
@@ -5852,8 +5965,8 @@
   <dimension ref="A1:BQ5"/>
   <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
   <cols>
-    <col min="2" max="2" width="21.5454545454545" customWidth="1"/>
-    <col min="3" max="3" width="27.8181818181818" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="21.5454545454545"/>
+    <col min="3" max="3" customWidth="true" width="27.8181818181818"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -6370,12 +6483,8 @@
       <c r="AT4" s="29" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" s="30" t="s">
-        <v>78</v>
-      </c>
-      <c r="AV4" s="30" t="s">
-        <v>79</v>
-      </c>
+      <c r="AU4" s="0"/>
+      <c r="AV4" s="0"/>
       <c r="AW4" s="29">
         <v>4</v>
       </c>
@@ -6410,11 +6519,11 @@
       <c r="BL4" s="36" t="s">
         <v>84</v>
       </c>
-      <c r="BM4" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="BN4" s="30" t="s">
-        <v>85</v>
+      <c r="BM4" t="s" s="0">
+        <v>118</v>
+      </c>
+      <c r="BN4" t="s" s="0">
+        <v>118</v>
       </c>
       <c r="BO4" s="29">
         <v>82.12</v>
@@ -7076,11 +7185,11 @@
       <c r="AT4" s="29" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" s="30" t="s">
-        <v>78</v>
-      </c>
-      <c r="AV4" s="30" t="s">
-        <v>79</v>
+      <c r="AU4" t="s" s="0">
+        <v>130</v>
+      </c>
+      <c r="AV4" t="s" s="0">
+        <v>131</v>
       </c>
       <c r="AW4" s="29">
         <v>4</v>
@@ -7116,11 +7225,11 @@
       <c r="BL4" s="36" t="s">
         <v>84</v>
       </c>
-      <c r="BM4" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="BN4" s="30" t="s">
-        <v>85</v>
+      <c r="BM4" t="s" s="0">
+        <v>133</v>
+      </c>
+      <c r="BN4" t="s" s="0">
+        <v>132</v>
       </c>
       <c r="BO4" s="29">
         <v>82.12</v>
@@ -7794,11 +7903,11 @@
       <c r="AT4" s="29" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" s="30" t="s">
-        <v>78</v>
-      </c>
-      <c r="AV4" s="30" t="s">
-        <v>79</v>
+      <c r="AU4" t="s" s="0">
+        <v>134</v>
+      </c>
+      <c r="AV4" t="s" s="0">
+        <v>135</v>
       </c>
       <c r="AW4" s="29">
         <v>4</v>
@@ -7834,11 +7943,11 @@
       <c r="BL4" s="36" t="s">
         <v>84</v>
       </c>
-      <c r="BM4" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="BN4" s="30" t="s">
-        <v>85</v>
+      <c r="BM4" t="s" s="0">
+        <v>137</v>
+      </c>
+      <c r="BN4" t="s" s="0">
+        <v>136</v>
       </c>
       <c r="BO4" s="29">
         <v>82.12</v>
@@ -7998,8 +8107,8 @@
   <dimension ref="A1:BQ5"/>
   <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
   <cols>
-    <col min="2" max="2" width="21.5454545454545" customWidth="1"/>
-    <col min="3" max="3" width="27.8181818181818" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="21.5454545454545"/>
+    <col min="3" max="3" customWidth="true" width="27.8181818181818"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -8516,12 +8625,8 @@
       <c r="AT4" s="29" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" s="30" t="s">
-        <v>78</v>
-      </c>
-      <c r="AV4" s="30" t="s">
-        <v>79</v>
-      </c>
+      <c r="AU4" s="0"/>
+      <c r="AV4" s="0"/>
       <c r="AW4" s="29">
         <v>4</v>
       </c>
@@ -8556,11 +8661,11 @@
       <c r="BL4" s="36" t="s">
         <v>84</v>
       </c>
-      <c r="BM4" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="BN4" s="30" t="s">
-        <v>85</v>
+      <c r="BM4" t="s" s="0">
+        <v>118</v>
+      </c>
+      <c r="BN4" t="s" s="0">
+        <v>118</v>
       </c>
       <c r="BO4" s="29">
         <v>82.12</v>
@@ -8708,8 +8813,8 @@
   <dimension ref="A1:BQ5"/>
   <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
   <cols>
-    <col min="2" max="2" width="21.5454545454545" customWidth="1"/>
-    <col min="3" max="3" width="27.8181818181818" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="21.5454545454545"/>
+    <col min="3" max="3" customWidth="true" width="27.8181818181818"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -9226,12 +9331,8 @@
       <c r="AT4" s="29" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" s="30" t="s">
-        <v>78</v>
-      </c>
-      <c r="AV4" s="30" t="s">
-        <v>79</v>
-      </c>
+      <c r="AU4" s="0"/>
+      <c r="AV4" s="0"/>
       <c r="AW4" s="29">
         <v>4</v>
       </c>
@@ -9266,11 +9367,11 @@
       <c r="BL4" s="36" t="s">
         <v>84</v>
       </c>
-      <c r="BM4" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="BN4" s="30" t="s">
-        <v>85</v>
+      <c r="BM4" t="s" s="0">
+        <v>118</v>
+      </c>
+      <c r="BN4" t="s" s="0">
+        <v>118</v>
       </c>
       <c r="BO4" s="29">
         <v>82.12</v>
@@ -9418,8 +9519,8 @@
   <dimension ref="A1:BQ5"/>
   <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
   <cols>
-    <col min="2" max="2" width="21.5454545454545" customWidth="1"/>
-    <col min="3" max="3" width="27.8181818181818" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="21.5454545454545"/>
+    <col min="3" max="3" customWidth="true" width="27.8181818181818"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -9936,11 +10037,11 @@
       <c r="AT4" s="29" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" s="30" t="s">
-        <v>78</v>
-      </c>
-      <c r="AV4" s="30" t="s">
-        <v>79</v>
+      <c r="AU4" t="s" s="0">
+        <v>114</v>
+      </c>
+      <c r="AV4" t="s" s="0">
+        <v>115</v>
       </c>
       <c r="AW4" s="29">
         <v>4</v>
@@ -9976,11 +10077,11 @@
       <c r="BL4" s="36" t="s">
         <v>84</v>
       </c>
-      <c r="BM4" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="BN4" s="30" t="s">
-        <v>85</v>
+      <c r="BM4" t="s" s="0">
+        <v>117</v>
+      </c>
+      <c r="BN4" t="s" s="0">
+        <v>116</v>
       </c>
       <c r="BO4" s="29">
         <v>82.12</v>
@@ -10128,8 +10229,8 @@
   <dimension ref="A1:BQ5"/>
   <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
   <cols>
-    <col min="2" max="2" width="28.2727272727273" customWidth="1"/>
-    <col min="3" max="3" width="24.9090909090909" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="28.2727272727273"/>
+    <col min="3" max="3" customWidth="true" width="24.9090909090909"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -10646,11 +10747,11 @@
       <c r="AT4" s="29" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" s="30" t="s">
-        <v>78</v>
-      </c>
-      <c r="AV4" s="30" t="s">
-        <v>79</v>
+      <c r="AU4" t="s" s="0">
+        <v>138</v>
+      </c>
+      <c r="AV4" t="s" s="0">
+        <v>139</v>
       </c>
       <c r="AW4" s="29">
         <v>4</v>
@@ -10686,11 +10787,11 @@
       <c r="BL4" s="36" t="s">
         <v>84</v>
       </c>
-      <c r="BM4" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="BN4" s="30" t="s">
-        <v>85</v>
+      <c r="BM4" t="s" s="0">
+        <v>141</v>
+      </c>
+      <c r="BN4" t="s" s="0">
+        <v>140</v>
       </c>
       <c r="BO4" s="29">
         <v>82.12</v>
@@ -11364,11 +11465,11 @@
       <c r="AT4" s="29" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" s="30" t="s">
-        <v>78</v>
-      </c>
-      <c r="AV4" s="30" t="s">
-        <v>79</v>
+      <c r="AU4" t="s" s="0">
+        <v>142</v>
+      </c>
+      <c r="AV4" t="s" s="0">
+        <v>143</v>
       </c>
       <c r="AW4" s="29">
         <v>4</v>
@@ -11404,11 +11505,11 @@
       <c r="BL4" s="36" t="s">
         <v>84</v>
       </c>
-      <c r="BM4" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="BN4" s="30" t="s">
-        <v>85</v>
+      <c r="BM4" t="s" s="0">
+        <v>133</v>
+      </c>
+      <c r="BN4" t="s" s="0">
+        <v>144</v>
       </c>
       <c r="BO4" s="29">
         <v>82.12</v>
@@ -11568,8 +11669,8 @@
   <dimension ref="A1:BQ5"/>
   <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
   <cols>
-    <col min="2" max="2" width="21.5454545454545" customWidth="1"/>
-    <col min="3" max="3" width="27.8181818181818" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="21.5454545454545"/>
+    <col min="3" max="3" customWidth="true" width="27.8181818181818"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -12086,11 +12187,11 @@
       <c r="AT4" s="29" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" s="30" t="s">
-        <v>78</v>
-      </c>
-      <c r="AV4" s="30" t="s">
-        <v>79</v>
+      <c r="AU4" t="s" s="0">
+        <v>138</v>
+      </c>
+      <c r="AV4" t="s" s="0">
+        <v>139</v>
       </c>
       <c r="AW4" s="29">
         <v>4</v>
@@ -12126,11 +12227,11 @@
       <c r="BL4" s="36" t="s">
         <v>84</v>
       </c>
-      <c r="BM4" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="BN4" s="30" t="s">
-        <v>85</v>
+      <c r="BM4" t="s" s="0">
+        <v>141</v>
+      </c>
+      <c r="BN4" t="s" s="0">
+        <v>140</v>
       </c>
       <c r="BO4" s="29">
         <v>82.12</v>
@@ -12278,8 +12379,8 @@
   <dimension ref="A1:BQ5"/>
   <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
   <cols>
-    <col min="2" max="2" width="21.5454545454545" customWidth="1"/>
-    <col min="3" max="3" width="27.8181818181818" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="21.5454545454545"/>
+    <col min="3" max="3" customWidth="true" width="27.8181818181818"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -12796,11 +12897,11 @@
       <c r="AT4" s="29" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" s="30" t="s">
-        <v>78</v>
-      </c>
-      <c r="AV4" s="30" t="s">
-        <v>79</v>
+      <c r="AU4" t="s" s="0">
+        <v>142</v>
+      </c>
+      <c r="AV4" t="s" s="0">
+        <v>143</v>
       </c>
       <c r="AW4" s="29">
         <v>4</v>
@@ -12836,11 +12937,11 @@
       <c r="BL4" s="36" t="s">
         <v>84</v>
       </c>
-      <c r="BM4" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="BN4" s="30" t="s">
-        <v>85</v>
+      <c r="BM4" t="s" s="0">
+        <v>133</v>
+      </c>
+      <c r="BN4" t="s" s="0">
+        <v>144</v>
       </c>
       <c r="BO4" s="29">
         <v>82.12</v>
@@ -13502,11 +13603,11 @@
       <c r="AT4" s="29" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" s="30" t="s">
-        <v>78</v>
-      </c>
-      <c r="AV4" s="30" t="s">
-        <v>79</v>
+      <c r="AU4" t="s" s="0">
+        <v>145</v>
+      </c>
+      <c r="AV4" t="s" s="0">
+        <v>146</v>
       </c>
       <c r="AW4" s="29">
         <v>4</v>
@@ -13542,11 +13643,11 @@
       <c r="BL4" s="36" t="s">
         <v>84</v>
       </c>
-      <c r="BM4" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="BN4" s="30" t="s">
-        <v>85</v>
+      <c r="BM4" t="s" s="0">
+        <v>141</v>
+      </c>
+      <c r="BN4" t="s" s="0">
+        <v>147</v>
       </c>
       <c r="BO4" s="29">
         <v>82.12</v>
@@ -14220,11 +14321,11 @@
       <c r="AT4" s="29" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" s="30" t="s">
-        <v>78</v>
-      </c>
-      <c r="AV4" s="30" t="s">
-        <v>79</v>
+      <c r="AU4" t="s" s="0">
+        <v>148</v>
+      </c>
+      <c r="AV4" t="s" s="0">
+        <v>149</v>
       </c>
       <c r="AW4" s="29">
         <v>4</v>
@@ -14260,11 +14361,11 @@
       <c r="BL4" s="36" t="s">
         <v>84</v>
       </c>
-      <c r="BM4" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="BN4" s="30" t="s">
-        <v>85</v>
+      <c r="BM4" t="s" s="0">
+        <v>133</v>
+      </c>
+      <c r="BN4" t="s" s="0">
+        <v>150</v>
       </c>
       <c r="BO4" s="29">
         <v>82.12</v>
@@ -14424,8 +14525,8 @@
   <dimension ref="A1:BQ5"/>
   <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
   <cols>
-    <col min="2" max="2" width="21.5454545454545" customWidth="1"/>
-    <col min="3" max="3" width="27.8181818181818" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="21.5454545454545"/>
+    <col min="3" max="3" customWidth="true" width="27.8181818181818"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -14942,11 +15043,11 @@
       <c r="AT4" s="29" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" s="30" t="s">
-        <v>78</v>
-      </c>
-      <c r="AV4" s="30" t="s">
-        <v>79</v>
+      <c r="AU4" t="s" s="0">
+        <v>145</v>
+      </c>
+      <c r="AV4" t="s" s="0">
+        <v>146</v>
       </c>
       <c r="AW4" s="29">
         <v>4</v>
@@ -14982,11 +15083,11 @@
       <c r="BL4" s="36" t="s">
         <v>84</v>
       </c>
-      <c r="BM4" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="BN4" s="30" t="s">
-        <v>85</v>
+      <c r="BM4" t="s" s="0">
+        <v>141</v>
+      </c>
+      <c r="BN4" t="s" s="0">
+        <v>147</v>
       </c>
       <c r="BO4" s="29">
         <v>82.12</v>
@@ -15134,8 +15235,8 @@
   <dimension ref="A1:BQ5"/>
   <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
   <cols>
-    <col min="2" max="2" width="21.5454545454545" customWidth="1"/>
-    <col min="3" max="3" width="27.8181818181818" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="21.5454545454545"/>
+    <col min="3" max="3" customWidth="true" width="27.8181818181818"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -15652,11 +15753,11 @@
       <c r="AT4" s="29" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" s="30" t="s">
-        <v>78</v>
-      </c>
-      <c r="AV4" s="30" t="s">
-        <v>79</v>
+      <c r="AU4" t="s" s="0">
+        <v>151</v>
+      </c>
+      <c r="AV4" t="s" s="0">
+        <v>152</v>
       </c>
       <c r="AW4" s="29">
         <v>4</v>
@@ -15692,11 +15793,11 @@
       <c r="BL4" s="36" t="s">
         <v>84</v>
       </c>
-      <c r="BM4" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="BN4" s="30" t="s">
-        <v>85</v>
+      <c r="BM4" t="s" s="0">
+        <v>137</v>
+      </c>
+      <c r="BN4" t="s" s="0">
+        <v>153</v>
       </c>
       <c r="BO4" s="29">
         <v>82.12</v>
@@ -15844,8 +15945,8 @@
   <dimension ref="A1:BQ5"/>
   <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
   <cols>
-    <col min="2" max="2" width="21.5454545454545" customWidth="1"/>
-    <col min="3" max="3" width="27.8181818181818" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="21.5454545454545"/>
+    <col min="3" max="3" customWidth="true" width="27.8181818181818"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -16362,12 +16463,8 @@
       <c r="AT4" s="29" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" s="30" t="s">
-        <v>78</v>
-      </c>
-      <c r="AV4" s="30" t="s">
-        <v>79</v>
-      </c>
+      <c r="AU4" s="0"/>
+      <c r="AV4" s="0"/>
       <c r="AW4" s="29">
         <v>4</v>
       </c>
@@ -16402,12 +16499,8 @@
       <c r="BL4" s="36" t="s">
         <v>84</v>
       </c>
-      <c r="BM4" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="BN4" s="30" t="s">
-        <v>85</v>
-      </c>
+      <c r="BM4" s="0"/>
+      <c r="BN4" s="0"/>
       <c r="BO4" s="29">
         <v>82.12</v>
       </c>
@@ -16554,8 +16647,8 @@
   <dimension ref="A1:BQ5"/>
   <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
   <cols>
-    <col min="2" max="2" width="21.5454545454545" customWidth="1"/>
-    <col min="3" max="3" width="27.8181818181818" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="21.5454545454545"/>
+    <col min="3" max="3" customWidth="true" width="27.8181818181818"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -17072,12 +17165,8 @@
       <c r="AT4" s="29" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" s="30" t="s">
-        <v>78</v>
-      </c>
-      <c r="AV4" s="30" t="s">
-        <v>79</v>
-      </c>
+      <c r="AU4" s="0"/>
+      <c r="AV4" s="0"/>
       <c r="AW4" s="29">
         <v>4</v>
       </c>
@@ -17112,11 +17201,11 @@
       <c r="BL4" s="36" t="s">
         <v>84</v>
       </c>
-      <c r="BM4" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="BN4" s="30" t="s">
-        <v>85</v>
+      <c r="BM4" t="s" s="0">
+        <v>118</v>
+      </c>
+      <c r="BN4" t="s" s="0">
+        <v>118</v>
       </c>
       <c r="BO4" s="29">
         <v>82.12</v>
@@ -17264,8 +17353,8 @@
   <dimension ref="A1:BQ5"/>
   <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
   <cols>
-    <col min="2" max="2" width="21.5454545454545" customWidth="1"/>
-    <col min="3" max="3" width="27.8181818181818" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="21.5454545454545"/>
+    <col min="3" max="3" customWidth="true" width="27.8181818181818"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -17782,12 +17871,8 @@
       <c r="AT4" s="29" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" s="30" t="s">
-        <v>78</v>
-      </c>
-      <c r="AV4" s="30" t="s">
-        <v>79</v>
-      </c>
+      <c r="AU4" s="0"/>
+      <c r="AV4" s="0"/>
       <c r="AW4" s="29">
         <v>4</v>
       </c>
@@ -17822,11 +17907,11 @@
       <c r="BL4" s="36" t="s">
         <v>84</v>
       </c>
-      <c r="BM4" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="BN4" s="30" t="s">
-        <v>85</v>
+      <c r="BM4" t="s" s="0">
+        <v>118</v>
+      </c>
+      <c r="BN4" t="s" s="0">
+        <v>118</v>
       </c>
       <c r="BO4" s="29">
         <v>82.12</v>
@@ -18488,11 +18573,11 @@
       <c r="AT4" s="29" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" s="30" t="s">
-        <v>78</v>
-      </c>
-      <c r="AV4" s="30" t="s">
-        <v>79</v>
+      <c r="AU4" t="s" s="0">
+        <v>119</v>
+      </c>
+      <c r="AV4" t="s" s="0">
+        <v>120</v>
       </c>
       <c r="AW4" s="29">
         <v>4</v>
@@ -18528,11 +18613,11 @@
       <c r="BL4" s="36" t="s">
         <v>84</v>
       </c>
-      <c r="BM4" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="BN4" s="30" t="s">
-        <v>85</v>
+      <c r="BM4" t="s" s="0">
+        <v>118</v>
+      </c>
+      <c r="BN4" t="s" s="0">
+        <v>118</v>
       </c>
       <c r="BO4" s="29">
         <v>82.12</v>
@@ -18692,8 +18777,8 @@
   <dimension ref="A1:BQ5"/>
   <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
   <cols>
-    <col min="2" max="2" width="21.5454545454545" customWidth="1"/>
-    <col min="3" max="3" width="27.8181818181818" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="21.5454545454545"/>
+    <col min="3" max="3" customWidth="true" width="27.8181818181818"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -19210,11 +19295,11 @@
       <c r="AT4" s="29" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" s="30" t="s">
-        <v>78</v>
-      </c>
-      <c r="AV4" s="30" t="s">
-        <v>79</v>
+      <c r="AU4" t="s" s="0">
+        <v>121</v>
+      </c>
+      <c r="AV4" t="s" s="0">
+        <v>122</v>
       </c>
       <c r="AW4" s="29">
         <v>4</v>
@@ -19250,11 +19335,11 @@
       <c r="BL4" s="36" t="s">
         <v>84</v>
       </c>
-      <c r="BM4" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="BN4" s="30" t="s">
-        <v>85</v>
+      <c r="BM4" t="s" s="0">
+        <v>118</v>
+      </c>
+      <c r="BN4" t="s" s="0">
+        <v>118</v>
       </c>
       <c r="BO4" s="29">
         <v>82.12</v>
@@ -19402,8 +19487,8 @@
   <dimension ref="A1:BQ5"/>
   <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
   <cols>
-    <col min="2" max="2" width="21.5454545454545" customWidth="1"/>
-    <col min="3" max="3" width="27.8181818181818" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="21.5454545454545"/>
+    <col min="3" max="3" customWidth="true" width="27.8181818181818"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -19920,12 +20005,8 @@
       <c r="AT4" s="29" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" s="30" t="s">
-        <v>78</v>
-      </c>
-      <c r="AV4" s="30" t="s">
-        <v>79</v>
-      </c>
+      <c r="AU4" s="0"/>
+      <c r="AV4" s="0"/>
       <c r="AW4" s="29">
         <v>4</v>
       </c>
@@ -19960,12 +20041,8 @@
       <c r="BL4" s="36" t="s">
         <v>84</v>
       </c>
-      <c r="BM4" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="BN4" s="30" t="s">
-        <v>85</v>
-      </c>
+      <c r="BM4" s="0"/>
+      <c r="BN4" s="0"/>
       <c r="BO4" s="29">
         <v>82.12</v>
       </c>
@@ -20112,8 +20189,8 @@
   <dimension ref="A1:BQ5"/>
   <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
   <cols>
-    <col min="2" max="2" width="25.8181818181818" customWidth="1"/>
-    <col min="3" max="3" width="27.8181818181818" customWidth="1"/>
+    <col min="2" max="2" customWidth="true" width="25.8181818181818"/>
+    <col min="3" max="3" customWidth="true" width="27.8181818181818"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -20630,12 +20707,8 @@
       <c r="AT4" s="29" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" s="30" t="s">
-        <v>78</v>
-      </c>
-      <c r="AV4" s="30" t="s">
-        <v>79</v>
-      </c>
+      <c r="AU4" s="0"/>
+      <c r="AV4" s="0"/>
       <c r="AW4" s="29">
         <v>4</v>
       </c>
@@ -20670,11 +20743,11 @@
       <c r="BL4" s="36" t="s">
         <v>84</v>
       </c>
-      <c r="BM4" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="BN4" s="30" t="s">
-        <v>85</v>
+      <c r="BM4" t="s" s="0">
+        <v>118</v>
+      </c>
+      <c r="BN4" t="s" s="0">
+        <v>118</v>
       </c>
       <c r="BO4" s="29">
         <v>82.12</v>

--- a/testdata/PoToGRN-FOC Scenarios.xlsx
+++ b/testdata/PoToGRN-FOC Scenarios.xlsx
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2596" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3145" uniqueCount="348">
   <si>
     <t>Purchase Order &amp; GRN</t>
   </si>
@@ -560,6 +560,543 @@
   </si>
   <si>
     <t>1644.88812</t>
+  </si>
+  <si>
+    <t>1286.60458</t>
+  </si>
+  <si>
+    <t>164</t>
+  </si>
+  <si>
+    <t>1879.90859</t>
+  </si>
+  <si>
+    <t>92</t>
+  </si>
+  <si>
+    <t>2628.66753</t>
+  </si>
+  <si>
+    <t>157.332</t>
+  </si>
+  <si>
+    <t>2856.69921</t>
+  </si>
+  <si>
+    <t>75.999</t>
+  </si>
+  <si>
+    <t>5495.09849</t>
+  </si>
+  <si>
+    <t>118.328</t>
+  </si>
+  <si>
+    <t>4930.82789</t>
+  </si>
+  <si>
+    <t>158.665</t>
+  </si>
+  <si>
+    <t>2875.90422</t>
+  </si>
+  <si>
+    <t>98.997</t>
+  </si>
+  <si>
+    <t>6081.5067</t>
+  </si>
+  <si>
+    <t>90.332</t>
+  </si>
+  <si>
+    <t>9199.00077</t>
+  </si>
+  <si>
+    <t>121.326</t>
+  </si>
+  <si>
+    <t>4053.37644</t>
+  </si>
+  <si>
+    <t>95.33</t>
+  </si>
+  <si>
+    <t>6000.45747</t>
+  </si>
+  <si>
+    <t>126.993</t>
+  </si>
+  <si>
+    <t>2772.09455</t>
+  </si>
+  <si>
+    <t>91.665</t>
+  </si>
+  <si>
+    <t>9069.37612</t>
+  </si>
+  <si>
+    <t>96.663</t>
+  </si>
+  <si>
+    <t>5921.6436</t>
+  </si>
+  <si>
+    <t>9195.74089</t>
+  </si>
+  <si>
+    <t>135.658</t>
+  </si>
+  <si>
+    <t>3491.85112</t>
+  </si>
+  <si>
+    <t>5289.91662</t>
+  </si>
+  <si>
+    <t>174</t>
+  </si>
+  <si>
+    <t>1814.42246</t>
+  </si>
+  <si>
+    <t>95.999</t>
+  </si>
+  <si>
+    <t>8704.42201</t>
+  </si>
+  <si>
+    <t>141.003</t>
+  </si>
+  <si>
+    <t>5063.75805</t>
+  </si>
+  <si>
+    <t>106.327</t>
+  </si>
+  <si>
+    <t>6069.02507</t>
+  </si>
+  <si>
+    <t>158.992</t>
+  </si>
+  <si>
+    <t>2746.54258</t>
+  </si>
+  <si>
+    <t>97.332</t>
+  </si>
+  <si>
+    <t>8589.118</t>
+  </si>
+  <si>
+    <t>450</t>
+  </si>
+  <si>
+    <t>961.01838</t>
+  </si>
+  <si>
+    <t>1255.01708</t>
+  </si>
+  <si>
+    <t>176</t>
+  </si>
+  <si>
+    <t>1754.04016</t>
+  </si>
+  <si>
+    <t>1224.94821</t>
+  </si>
+  <si>
+    <t>129</t>
+  </si>
+  <si>
+    <t>1026.13391</t>
+  </si>
+  <si>
+    <t>172</t>
+  </si>
+  <si>
+    <t>86</t>
+  </si>
+  <si>
+    <t>1623.44968</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>5455.83084</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>2425.46202</t>
+  </si>
+  <si>
+    <t>115</t>
+  </si>
+  <si>
+    <t>5224.03576</t>
+  </si>
+  <si>
+    <t>2335.33338</t>
+  </si>
+  <si>
+    <t>142</t>
+  </si>
+  <si>
+    <t>1411.70395</t>
+  </si>
+  <si>
+    <t>46.66</t>
+  </si>
+  <si>
+    <t>9339.68124</t>
+  </si>
+  <si>
+    <t>123.328</t>
+  </si>
+  <si>
+    <t>4736.18734</t>
+  </si>
+  <si>
+    <t>96.998</t>
+  </si>
+  <si>
+    <t>8590.06502</t>
+  </si>
+  <si>
+    <t>102.996</t>
+  </si>
+  <si>
+    <t>5573.18576</t>
+  </si>
+  <si>
+    <t>102.331</t>
+  </si>
+  <si>
+    <t>8160.7127</t>
+  </si>
+  <si>
+    <t>109.329</t>
+  </si>
+  <si>
+    <t>5265.09751</t>
+  </si>
+  <si>
+    <t>147.336</t>
+  </si>
+  <si>
+    <t>4857.0416</t>
+  </si>
+  <si>
+    <t>98.665</t>
+  </si>
+  <si>
+    <t>8157.01135</t>
+  </si>
+  <si>
+    <t>139.658</t>
+  </si>
+  <si>
+    <t>3628.55556</t>
+  </si>
+  <si>
+    <t>148.669</t>
+  </si>
+  <si>
+    <t>4660.98432</t>
+  </si>
+  <si>
+    <t>179</t>
+  </si>
+  <si>
+    <t>1899.41182</t>
+  </si>
+  <si>
+    <t>109.327</t>
+  </si>
+  <si>
+    <t>5747.55068</t>
+  </si>
+  <si>
+    <t>161.992</t>
+  </si>
+  <si>
+    <t>2805.0549</t>
+  </si>
+  <si>
+    <t>102.665</t>
+  </si>
+  <si>
+    <t>7853.758</t>
+  </si>
+  <si>
+    <t>1195.60215</t>
+  </si>
+  <si>
+    <t>134</t>
+  </si>
+  <si>
+    <t>1032.45735</t>
+  </si>
+  <si>
+    <t>1714.24874</t>
+  </si>
+  <si>
+    <t>90</t>
+  </si>
+  <si>
+    <t>1627.48519</t>
+  </si>
+  <si>
+    <t>1677.44945</t>
+  </si>
+  <si>
+    <t>5002.31873</t>
+  </si>
+  <si>
+    <t>213</t>
+  </si>
+  <si>
+    <t>2856.39276</t>
+  </si>
+  <si>
+    <t>2248.67123</t>
+  </si>
+  <si>
+    <t>146</t>
+  </si>
+  <si>
+    <t>1434.63456</t>
+  </si>
+  <si>
+    <t>114</t>
+  </si>
+  <si>
+    <t>4830.13491</t>
+  </si>
+  <si>
+    <t>104</t>
+  </si>
+  <si>
+    <t>2165.8408</t>
+  </si>
+  <si>
+    <t>8607.54384</t>
+  </si>
+  <si>
+    <t>79.999</t>
+  </si>
+  <si>
+    <t>5659.68251</t>
+  </si>
+  <si>
+    <t>4549.43797</t>
+  </si>
+  <si>
+    <t>168.665</t>
+  </si>
+  <si>
+    <t>2980.66267</t>
+  </si>
+  <si>
+    <t>81.332</t>
+  </si>
+  <si>
+    <t>5707.99682</t>
+  </si>
+  <si>
+    <t>169.998</t>
+  </si>
+  <si>
+    <t>2992.96386</t>
+  </si>
+  <si>
+    <t>103.664</t>
+  </si>
+  <si>
+    <t>8059.44316</t>
+  </si>
+  <si>
+    <t>110.662</t>
+  </si>
+  <si>
+    <t>5205.1117</t>
+  </si>
+  <si>
+    <t>104.997</t>
+  </si>
+  <si>
+    <t>7960.74498</t>
+  </si>
+  <si>
+    <t>111.995</t>
+  </si>
+  <si>
+    <t>5146.55383</t>
+  </si>
+  <si>
+    <t>150.002</t>
+  </si>
+  <si>
+    <t>4622.09906</t>
+  </si>
+  <si>
+    <t>103.998</t>
+  </si>
+  <si>
+    <t>7756.74811</t>
+  </si>
+  <si>
+    <t>151.335</t>
+  </si>
+  <si>
+    <t>4583.89882</t>
+  </si>
+  <si>
+    <t>105.331</t>
+  </si>
+  <si>
+    <t>7662.19361</t>
+  </si>
+  <si>
+    <t>206</t>
+  </si>
+  <si>
+    <t>1687.8734</t>
+  </si>
+  <si>
+    <t>454</t>
+  </si>
+  <si>
+    <t>972.79508</t>
+  </si>
+  <si>
+    <t>210</t>
+  </si>
+  <si>
+    <t>1729.22114</t>
+  </si>
+  <si>
+    <t>458</t>
+  </si>
+  <si>
+    <t>984.36607</t>
+  </si>
+  <si>
+    <t>207</t>
+  </si>
+  <si>
+    <t>1174.33602</t>
+  </si>
+  <si>
+    <t>180</t>
+  </si>
+  <si>
+    <t>1642.28568</t>
+  </si>
+  <si>
+    <t>211</t>
+  </si>
+  <si>
+    <t>1153.87619</t>
+  </si>
+  <si>
+    <t>184</t>
+  </si>
+  <si>
+    <t>1608.65077</t>
+  </si>
+  <si>
+    <t>118</t>
+  </si>
+  <si>
+    <t>4669.62457</t>
+  </si>
+  <si>
+    <t>108</t>
+  </si>
+  <si>
+    <t>2089.14596</t>
+  </si>
+  <si>
+    <t>122</t>
+  </si>
+  <si>
+    <t>4519.6395</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>2017.92932</t>
+  </si>
+  <si>
+    <t>82.665</t>
+  </si>
+  <si>
+    <t>5754.75296</t>
+  </si>
+  <si>
+    <t>171.331</t>
+  </si>
+  <si>
+    <t>3005.07364</t>
+  </si>
+  <si>
+    <t>83.998</t>
+  </si>
+  <si>
+    <t>5800.02511</t>
+  </si>
+  <si>
+    <t>172.664</t>
+  </si>
+  <si>
+    <t>3016.99644</t>
+  </si>
+  <si>
+    <t>106.33</t>
+  </si>
+  <si>
+    <t>7864.52145</t>
+  </si>
+  <si>
+    <t>5089.37351</t>
+  </si>
+  <si>
+    <t>107.663</t>
+  </si>
+  <si>
+    <t>7770.68065</t>
+  </si>
+  <si>
+    <t>114.661</t>
+  </si>
+  <si>
+    <t>5033.5227</t>
+  </si>
+  <si>
+    <t>106.664</t>
+  </si>
+  <si>
+    <t>7570.00244</t>
+  </si>
+  <si>
+    <t>152.668</t>
+  </si>
+  <si>
+    <t>4546.36566</t>
+  </si>
+  <si>
+    <t>107.997</t>
+  </si>
+  <si>
+    <t>7480.08709</t>
   </si>
 </sst>
 </file>
@@ -2355,10 +2892,10 @@
         <v>85</v>
       </c>
       <c r="BM4" t="s" s="0">
-        <v>168</v>
+        <v>308</v>
       </c>
       <c r="BN4" t="s" s="0">
-        <v>167</v>
+        <v>307</v>
       </c>
       <c r="BO4" s="35">
         <f>ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
@@ -3125,6 +3662,8 @@
       <c r="AT4" s="35" t="s">
         <v>76</v>
       </c>
+      <c r="AU4" s="0"/>
+      <c r="AV4" s="0"/>
       <c r="AW4" s="35">
         <f>AM4</f>
         <v>4</v>
@@ -3923,10 +4462,10 @@
         <v>76</v>
       </c>
       <c r="AU4" t="s" s="0">
-        <v>118</v>
+        <v>323</v>
       </c>
       <c r="AV4" t="s" s="0">
-        <v>119</v>
+        <v>324</v>
       </c>
       <c r="AW4" s="35">
         <f>AM4</f>
@@ -3967,10 +4506,10 @@
         <v>85</v>
       </c>
       <c r="BM4" t="s" s="0">
-        <v>120</v>
+        <v>269</v>
       </c>
       <c r="BN4" t="s" s="0">
-        <v>121</v>
+        <v>268</v>
       </c>
       <c r="BO4" s="35">
         <f>ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
@@ -4738,10 +5277,10 @@
         <v>76</v>
       </c>
       <c r="AU4" t="s" s="0">
-        <v>123</v>
+        <v>325</v>
       </c>
       <c r="AV4" t="s" s="0">
-        <v>124</v>
+        <v>326</v>
       </c>
       <c r="AW4" s="35">
         <f>AM4</f>
@@ -4782,10 +5321,10 @@
         <v>85</v>
       </c>
       <c r="BM4" t="s" s="0">
-        <v>125</v>
+        <v>272</v>
       </c>
       <c r="BN4" t="s" s="0">
-        <v>126</v>
+        <v>271</v>
       </c>
       <c r="BO4" s="35">
         <f>ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
@@ -6339,6 +6878,8 @@
       <c r="AT4" s="35" t="s">
         <v>76</v>
       </c>
+      <c r="AU4" s="0"/>
+      <c r="AV4" s="0"/>
       <c r="AW4" s="35">
         <f>AM4</f>
         <v>4</v>
@@ -7136,6 +7677,8 @@
       <c r="AT4" s="35" t="s">
         <v>76</v>
       </c>
+      <c r="AU4" s="0"/>
+      <c r="AV4" s="0"/>
       <c r="AW4" s="35">
         <f>AM4</f>
         <v>4</v>
@@ -7934,10 +8477,10 @@
         <v>76</v>
       </c>
       <c r="AU4" t="s" s="0">
-        <v>131</v>
+        <v>232</v>
       </c>
       <c r="AV4" t="s" s="0">
-        <v>132</v>
+        <v>277</v>
       </c>
       <c r="AW4" s="35">
         <f>AM4</f>
@@ -7952,7 +8495,7 @@
         <v>32.6603333333333</v>
       </c>
       <c r="AZ4" t="s" s="0">
-        <v>132</v>
+        <v>277</v>
       </c>
       <c r="BA4" s="36"/>
       <c r="BB4" s="36" t="s">
@@ -7977,10 +8520,10 @@
         <v>85</v>
       </c>
       <c r="BM4" t="s" s="0">
-        <v>133</v>
+        <v>332</v>
       </c>
       <c r="BN4" t="s" s="0">
-        <v>134</v>
+        <v>331</v>
       </c>
       <c r="BO4" s="35">
         <f>ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
@@ -8748,10 +9291,10 @@
         <v>76</v>
       </c>
       <c r="AU4" t="s" s="0">
-        <v>136</v>
+        <v>178</v>
       </c>
       <c r="AV4" t="s" s="0">
-        <v>137</v>
+        <v>280</v>
       </c>
       <c r="AW4" s="35">
         <f>AM4</f>
@@ -8766,7 +9309,7 @@
         <v>83.3283333333333</v>
       </c>
       <c r="AZ4" t="s" s="0">
-        <v>137</v>
+        <v>280</v>
       </c>
       <c r="BA4" s="36"/>
       <c r="BB4" s="36" t="s">
@@ -8791,10 +9334,10 @@
         <v>85</v>
       </c>
       <c r="BM4" t="s" s="0">
-        <v>138</v>
+        <v>334</v>
       </c>
       <c r="BN4" t="s" s="0">
-        <v>139</v>
+        <v>333</v>
       </c>
       <c r="BO4" s="35">
         <f>ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
@@ -9561,6 +10104,8 @@
       <c r="AT4" s="35" t="s">
         <v>76</v>
       </c>
+      <c r="AU4" s="0"/>
+      <c r="AV4" s="0"/>
       <c r="AW4" s="35">
         <f>AM4</f>
         <v>4</v>
@@ -10358,6 +10903,8 @@
       <c r="AT4" s="35" t="s">
         <v>76</v>
       </c>
+      <c r="AU4" s="0"/>
+      <c r="AV4" s="0"/>
       <c r="AW4" s="35">
         <f>AM4</f>
         <v>4</v>
@@ -11200,10 +11747,10 @@
         <v>85</v>
       </c>
       <c r="BM4" t="s" s="0">
-        <v>93</v>
+        <v>310</v>
       </c>
       <c r="BN4" t="s" s="0">
-        <v>94</v>
+        <v>309</v>
       </c>
       <c r="BO4" s="35">
         <f>ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
@@ -11959,10 +12506,10 @@
         <v>76</v>
       </c>
       <c r="AU4" t="s" s="0">
-        <v>143</v>
+        <v>335</v>
       </c>
       <c r="AV4" t="s" s="0">
-        <v>144</v>
+        <v>336</v>
       </c>
       <c r="AW4" s="35">
         <f>AM4</f>
@@ -12003,10 +12550,10 @@
         <v>85</v>
       </c>
       <c r="BM4" t="s" s="0">
-        <v>145</v>
+        <v>187</v>
       </c>
       <c r="BN4" t="s" s="0">
-        <v>146</v>
+        <v>186</v>
       </c>
       <c r="BO4" s="35">
         <f>ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
@@ -12774,10 +13321,10 @@
         <v>76</v>
       </c>
       <c r="AU4" t="s" s="0">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="AV4" t="s" s="0">
-        <v>149</v>
+        <v>337</v>
       </c>
       <c r="AW4" s="35">
         <f>AM4</f>
@@ -12818,10 +13365,10 @@
         <v>85</v>
       </c>
       <c r="BM4" t="s" s="0">
-        <v>150</v>
+        <v>191</v>
       </c>
       <c r="BN4" t="s" s="0">
-        <v>151</v>
+        <v>190</v>
       </c>
       <c r="BO4" s="35">
         <f>ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
@@ -13589,10 +14136,10 @@
         <v>76</v>
       </c>
       <c r="AU4" t="s" s="0">
-        <v>143</v>
+        <v>338</v>
       </c>
       <c r="AV4" t="s" s="0">
-        <v>144</v>
+        <v>339</v>
       </c>
       <c r="AW4" s="35">
         <f>AM4</f>
@@ -13633,10 +14180,10 @@
         <v>85</v>
       </c>
       <c r="BM4" t="s" s="0">
-        <v>145</v>
+        <v>187</v>
       </c>
       <c r="BN4" t="s" s="0">
-        <v>146</v>
+        <v>186</v>
       </c>
       <c r="BO4" s="35">
         <f>ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
@@ -14392,10 +14939,10 @@
         <v>76</v>
       </c>
       <c r="AU4" t="s" s="0">
-        <v>148</v>
+        <v>340</v>
       </c>
       <c r="AV4" t="s" s="0">
-        <v>149</v>
+        <v>341</v>
       </c>
       <c r="AW4" s="35">
         <f>AM4</f>
@@ -14436,10 +14983,10 @@
         <v>85</v>
       </c>
       <c r="BM4" t="s" s="0">
-        <v>150</v>
+        <v>191</v>
       </c>
       <c r="BN4" t="s" s="0">
-        <v>151</v>
+        <v>190</v>
       </c>
       <c r="BO4" s="35">
         <f>ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
@@ -15195,10 +15742,10 @@
         <v>76</v>
       </c>
       <c r="AU4" t="s" s="0">
-        <v>153</v>
+        <v>342</v>
       </c>
       <c r="AV4" t="s" s="0">
-        <v>154</v>
+        <v>343</v>
       </c>
       <c r="AW4" s="35">
         <f>AM4</f>
@@ -15239,10 +15786,10 @@
         <v>85</v>
       </c>
       <c r="BM4" t="s" s="0">
-        <v>155</v>
+        <v>249</v>
       </c>
       <c r="BN4" t="s" s="0">
-        <v>156</v>
+        <v>248</v>
       </c>
       <c r="BO4" s="35">
         <f>ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
@@ -16010,10 +16557,10 @@
         <v>76</v>
       </c>
       <c r="AU4" t="s" s="0">
-        <v>158</v>
+        <v>344</v>
       </c>
       <c r="AV4" t="s" s="0">
-        <v>159</v>
+        <v>345</v>
       </c>
       <c r="AW4" s="35">
         <f>AM4</f>
@@ -16054,10 +16601,10 @@
         <v>85</v>
       </c>
       <c r="BM4" t="s" s="0">
-        <v>160</v>
+        <v>253</v>
       </c>
       <c r="BN4" t="s" s="0">
-        <v>161</v>
+        <v>252</v>
       </c>
       <c r="BO4" s="35">
         <f>ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
@@ -16825,10 +17372,10 @@
         <v>76</v>
       </c>
       <c r="AU4" t="s" s="0">
-        <v>153</v>
+        <v>346</v>
       </c>
       <c r="AV4" t="s" s="0">
-        <v>154</v>
+        <v>347</v>
       </c>
       <c r="AW4" s="16">
         <f>AM4</f>
@@ -16869,10 +17416,10 @@
         <v>85</v>
       </c>
       <c r="BM4" t="s" s="0">
-        <v>155</v>
+        <v>249</v>
       </c>
       <c r="BN4" t="s" s="0">
-        <v>156</v>
+        <v>248</v>
       </c>
       <c r="BO4" s="16">
         <f>ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
@@ -17628,10 +18175,10 @@
         <v>76</v>
       </c>
       <c r="AU4" t="s" s="0">
-        <v>163</v>
+        <v>254</v>
       </c>
       <c r="AV4" t="s" s="0">
-        <v>164</v>
+        <v>255</v>
       </c>
       <c r="AW4" s="16">
         <f>AM4</f>
@@ -17672,10 +18219,10 @@
         <v>85</v>
       </c>
       <c r="BM4" t="s" s="0">
-        <v>165</v>
+        <v>257</v>
       </c>
       <c r="BN4" t="s" s="0">
-        <v>166</v>
+        <v>256</v>
       </c>
       <c r="BO4" s="16">
         <f>ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
@@ -19229,6 +19776,8 @@
       <c r="AT4" s="35" t="s">
         <v>76</v>
       </c>
+      <c r="AU4" s="0"/>
+      <c r="AV4" s="0"/>
       <c r="AW4" s="35">
         <f>AM4</f>
         <v>4</v>
@@ -20026,6 +20575,8 @@
       <c r="AT4" s="35" t="s">
         <v>76</v>
       </c>
+      <c r="AU4" s="0"/>
+      <c r="AV4" s="0"/>
       <c r="AW4" s="35">
         <f>AM4</f>
         <v>4</v>
@@ -20824,10 +21375,10 @@
         <v>76</v>
       </c>
       <c r="AU4" t="s" s="0">
-        <v>105</v>
+        <v>315</v>
       </c>
       <c r="AV4" t="s" s="0">
-        <v>106</v>
+        <v>316</v>
       </c>
       <c r="AW4" s="35">
         <f>AM4</f>
@@ -20868,10 +21419,10 @@
         <v>85</v>
       </c>
       <c r="BM4" t="s" s="0">
-        <v>107</v>
+        <v>262</v>
       </c>
       <c r="BN4" t="s" s="0">
-        <v>108</v>
+        <v>261</v>
       </c>
       <c r="BO4" s="35">
         <f>ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
@@ -21639,10 +22190,10 @@
         <v>76</v>
       </c>
       <c r="AU4" t="s" s="0">
-        <v>110</v>
+        <v>317</v>
       </c>
       <c r="AV4" t="s" s="0">
-        <v>111</v>
+        <v>318</v>
       </c>
       <c r="AW4" s="35">
         <f>AM4</f>
@@ -21683,10 +22234,10 @@
         <v>85</v>
       </c>
       <c r="BM4" t="s" s="0">
-        <v>112</v>
+        <v>265</v>
       </c>
       <c r="BN4" t="s" s="0">
-        <v>113</v>
+        <v>264</v>
       </c>
       <c r="BO4" s="35">
         <f>ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
@@ -23240,6 +23791,8 @@
       <c r="AT4" s="35" t="s">
         <v>76</v>
       </c>
+      <c r="AU4" s="0"/>
+      <c r="AV4" s="0"/>
       <c r="AW4" s="35">
         <f>AM4</f>
         <v>4</v>

--- a/testdata/PoToGRN-FOC Scenarios.xlsx
+++ b/testdata/PoToGRN-FOC Scenarios.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="7020" firstSheet="5" activeTab="5"/>
+    <workbookView windowWidth="19200" windowHeight="6320"/>
   </bookViews>
   <sheets>
     <sheet name="D-PoToGRNFOCUDGeneralSameUOMWI" sheetId="32" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3145" uniqueCount="348">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2586" uniqueCount="173">
   <si>
     <t>Purchase Order &amp; GRN</t>
   </si>
@@ -313,10 +313,10 @@
     <t>RM WH-49</t>
   </si>
   <si>
-    <t>1600.16606</t>
+    <t>1729.22114</t>
   </si>
   <si>
-    <t>198</t>
+    <t>210</t>
   </si>
   <si>
     <t>Total</t>
@@ -334,10 +334,10 @@
     <t>2297.6737</t>
   </si>
   <si>
-    <t>949.03044</t>
+    <t>984.36607</t>
   </si>
   <si>
-    <t>446</t>
+    <t>458</t>
   </si>
   <si>
     <t>VD Asbl. Val.</t>
@@ -370,31 +370,31 @@
     <t>GWL_Item_Similar_Rc_01</t>
   </si>
   <si>
-    <t>194</t>
+    <t>211</t>
   </si>
   <si>
-    <t>1311.1721</t>
+    <t>1153.87619</t>
   </si>
   <si>
-    <t>1018.1172</t>
+    <t>1032.45735</t>
   </si>
   <si>
-    <t>124</t>
+    <t>134</t>
   </si>
   <si>
     <t>GWL_Item_Similar_Rc_02</t>
   </si>
   <si>
-    <t>160</t>
+    <t>184</t>
   </si>
   <si>
-    <t>1924.5293</t>
+    <t>1608.65077</t>
   </si>
   <si>
-    <t>1617.07941</t>
+    <t>1627.48519</t>
   </si>
   <si>
-    <t>82</t>
+    <t>90</t>
   </si>
   <si>
     <t>GWL_Item_Service_Rc_06</t>
@@ -409,31 +409,31 @@
     <t>GWL_Item_Similar_Pl_01</t>
   </si>
   <si>
-    <t>105</t>
+    <t>122</t>
   </si>
   <si>
-    <t>5709.70164</t>
+    <t>4519.6395</t>
   </si>
   <si>
-    <t>2745.22111</t>
+    <t>2856.39276</t>
   </si>
   <si>
-    <t>203</t>
+    <t>213</t>
   </si>
   <si>
     <t>GWL_Item_Similar_Pl_02</t>
   </si>
   <si>
-    <t>88</t>
+    <t>112</t>
   </si>
   <si>
-    <t>2743.8306</t>
+    <t>2017.92932</t>
   </si>
   <si>
-    <t>1384.93208</t>
+    <t>1434.63456</t>
   </si>
   <si>
-    <t>138</t>
+    <t>146</t>
   </si>
   <si>
     <t>GWL_Item_Service_Pl_03</t>
@@ -448,31 +448,31 @@
     <t>GWL_Item_Dissimilar_04</t>
   </si>
   <si>
-    <t>43.327</t>
+    <t>46.66</t>
   </si>
   <si>
-    <t>9759.43457</t>
+    <t>8607.54384</t>
   </si>
   <si>
-    <t>5418.96799</t>
+    <t>5800.02511</t>
   </si>
   <si>
-    <t>74.666</t>
+    <t>83.998</t>
   </si>
   <si>
     <t>GWL_Item_Dissimilar_05</t>
   </si>
   <si>
-    <t>113.328</t>
+    <t>118.328</t>
   </si>
   <si>
-    <t>5142.64341</t>
+    <t>4549.43797</t>
   </si>
   <si>
-    <t>2837.16598</t>
+    <t>3016.99644</t>
   </si>
   <si>
-    <t>155.999</t>
+    <t>172.664</t>
   </si>
   <si>
     <t>GWL_Dissimilar_St_01</t>
@@ -484,589 +484,31 @@
     <t>GWL_Item_Dissimilar_Rc_01</t>
   </si>
   <si>
-    <t>88.999</t>
-  </si>
-  <si>
-    <t>9729.15848</t>
-  </si>
-  <si>
-    <t>3877.94646</t>
-  </si>
-  <si>
-    <t>117.326</t>
-  </si>
-  <si>
-    <t>GWL_Item_Dissimilar_Rc_02</t>
-  </si>
-  <si>
-    <t>93.997</t>
-  </si>
-  <si>
-    <t>6391.89696</t>
-  </si>
-  <si>
-    <t>2636.45512</t>
-  </si>
-  <si>
-    <t>121.993</t>
-  </si>
-  <si>
-    <t>GWL_Item_Dissimilar_Pl_01</t>
-  </si>
-  <si>
-    <t>90.666</t>
-  </si>
-  <si>
-    <t>9584.95431</t>
-  </si>
-  <si>
-    <t>3318.55699</t>
-  </si>
-  <si>
-    <t>131.658</t>
-  </si>
-  <si>
-    <t>GWL_Item_Dissimilar_Pl_02</t>
-  </si>
-  <si>
-    <t>134.67</t>
-  </si>
-  <si>
-    <t>5477.1729</t>
-  </si>
-  <si>
-    <t>1711.59719</t>
-  </si>
-  <si>
-    <t>169</t>
-  </si>
-  <si>
-    <t>GWL_Item_Dissimilar_Pl_03</t>
-  </si>
-  <si>
-    <t>103.327</t>
-  </si>
-  <si>
-    <t>6418.90517</t>
-  </si>
-  <si>
-    <t>2679.32915</t>
-  </si>
-  <si>
-    <t>155.992</t>
-  </si>
-  <si>
-    <t>202</t>
-  </si>
-  <si>
-    <t>1644.88812</t>
-  </si>
-  <si>
-    <t>1286.60458</t>
-  </si>
-  <si>
-    <t>164</t>
-  </si>
-  <si>
-    <t>1879.90859</t>
-  </si>
-  <si>
-    <t>92</t>
-  </si>
-  <si>
-    <t>2628.66753</t>
-  </si>
-  <si>
-    <t>157.332</t>
-  </si>
-  <si>
-    <t>2856.69921</t>
-  </si>
-  <si>
-    <t>75.999</t>
-  </si>
-  <si>
-    <t>5495.09849</t>
-  </si>
-  <si>
-    <t>118.328</t>
-  </si>
-  <si>
-    <t>4930.82789</t>
-  </si>
-  <si>
-    <t>158.665</t>
-  </si>
-  <si>
-    <t>2875.90422</t>
-  </si>
-  <si>
-    <t>98.997</t>
-  </si>
-  <si>
-    <t>6081.5067</t>
-  </si>
-  <si>
-    <t>90.332</t>
-  </si>
-  <si>
-    <t>9199.00077</t>
-  </si>
-  <si>
-    <t>121.326</t>
-  </si>
-  <si>
-    <t>4053.37644</t>
-  </si>
-  <si>
-    <t>95.33</t>
-  </si>
-  <si>
-    <t>6000.45747</t>
-  </si>
-  <si>
-    <t>126.993</t>
-  </si>
-  <si>
-    <t>2772.09455</t>
-  </si>
-  <si>
-    <t>91.665</t>
-  </si>
-  <si>
-    <t>9069.37612</t>
-  </si>
-  <si>
-    <t>96.663</t>
-  </si>
-  <si>
-    <t>5921.6436</t>
-  </si>
-  <si>
-    <t>9195.74089</t>
-  </si>
-  <si>
-    <t>135.658</t>
-  </si>
-  <si>
-    <t>3491.85112</t>
-  </si>
-  <si>
-    <t>5289.91662</t>
-  </si>
-  <si>
-    <t>174</t>
-  </si>
-  <si>
-    <t>1814.42246</t>
-  </si>
-  <si>
-    <t>95.999</t>
-  </si>
-  <si>
-    <t>8704.42201</t>
-  </si>
-  <si>
-    <t>141.003</t>
-  </si>
-  <si>
-    <t>5063.75805</t>
-  </si>
-  <si>
-    <t>106.327</t>
-  </si>
-  <si>
-    <t>6069.02507</t>
-  </si>
-  <si>
-    <t>158.992</t>
-  </si>
-  <si>
-    <t>2746.54258</t>
-  </si>
-  <si>
-    <t>97.332</t>
-  </si>
-  <si>
-    <t>8589.118</t>
-  </si>
-  <si>
-    <t>450</t>
-  </si>
-  <si>
-    <t>961.01838</t>
-  </si>
-  <si>
-    <t>1255.01708</t>
-  </si>
-  <si>
-    <t>176</t>
-  </si>
-  <si>
-    <t>1754.04016</t>
-  </si>
-  <si>
-    <t>1224.94821</t>
-  </si>
-  <si>
-    <t>129</t>
-  </si>
-  <si>
-    <t>1026.13391</t>
-  </si>
-  <si>
-    <t>172</t>
-  </si>
-  <si>
-    <t>86</t>
-  </si>
-  <si>
-    <t>1623.44968</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>5455.83084</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>2425.46202</t>
-  </si>
-  <si>
-    <t>115</t>
-  </si>
-  <si>
-    <t>5224.03576</t>
-  </si>
-  <si>
-    <t>2335.33338</t>
-  </si>
-  <si>
-    <t>142</t>
-  </si>
-  <si>
-    <t>1411.70395</t>
-  </si>
-  <si>
-    <t>46.66</t>
-  </si>
-  <si>
-    <t>9339.68124</t>
-  </si>
-  <si>
-    <t>123.328</t>
-  </si>
-  <si>
-    <t>4736.18734</t>
-  </si>
-  <si>
-    <t>96.998</t>
-  </si>
-  <si>
-    <t>8590.06502</t>
-  </si>
-  <si>
-    <t>102.996</t>
-  </si>
-  <si>
-    <t>5573.18576</t>
-  </si>
-  <si>
-    <t>102.331</t>
-  </si>
-  <si>
-    <t>8160.7127</t>
-  </si>
-  <si>
-    <t>109.329</t>
-  </si>
-  <si>
-    <t>5265.09751</t>
-  </si>
-  <si>
-    <t>147.336</t>
-  </si>
-  <si>
-    <t>4857.0416</t>
-  </si>
-  <si>
-    <t>98.665</t>
-  </si>
-  <si>
-    <t>8157.01135</t>
-  </si>
-  <si>
-    <t>139.658</t>
-  </si>
-  <si>
-    <t>3628.55556</t>
-  </si>
-  <si>
-    <t>148.669</t>
-  </si>
-  <si>
-    <t>4660.98432</t>
-  </si>
-  <si>
-    <t>179</t>
-  </si>
-  <si>
-    <t>1899.41182</t>
-  </si>
-  <si>
-    <t>109.327</t>
-  </si>
-  <si>
-    <t>5747.55068</t>
-  </si>
-  <si>
-    <t>161.992</t>
-  </si>
-  <si>
-    <t>2805.0549</t>
-  </si>
-  <si>
-    <t>102.665</t>
-  </si>
-  <si>
-    <t>7853.758</t>
-  </si>
-  <si>
-    <t>1195.60215</t>
-  </si>
-  <si>
-    <t>134</t>
-  </si>
-  <si>
-    <t>1032.45735</t>
-  </si>
-  <si>
-    <t>1714.24874</t>
-  </si>
-  <si>
-    <t>90</t>
-  </si>
-  <si>
-    <t>1627.48519</t>
-  </si>
-  <si>
-    <t>1677.44945</t>
-  </si>
-  <si>
-    <t>5002.31873</t>
-  </si>
-  <si>
-    <t>213</t>
-  </si>
-  <si>
-    <t>2856.39276</t>
-  </si>
-  <si>
-    <t>2248.67123</t>
-  </si>
-  <si>
-    <t>146</t>
-  </si>
-  <si>
-    <t>1434.63456</t>
-  </si>
-  <si>
-    <t>114</t>
-  </si>
-  <si>
-    <t>4830.13491</t>
-  </si>
-  <si>
-    <t>104</t>
-  </si>
-  <si>
-    <t>2165.8408</t>
-  </si>
-  <si>
-    <t>8607.54384</t>
-  </si>
-  <si>
-    <t>79.999</t>
-  </si>
-  <si>
-    <t>5659.68251</t>
-  </si>
-  <si>
-    <t>4549.43797</t>
-  </si>
-  <si>
-    <t>168.665</t>
-  </si>
-  <si>
-    <t>2980.66267</t>
-  </si>
-  <si>
-    <t>81.332</t>
-  </si>
-  <si>
-    <t>5707.99682</t>
-  </si>
-  <si>
-    <t>169.998</t>
-  </si>
-  <si>
-    <t>2992.96386</t>
-  </si>
-  <si>
-    <t>103.664</t>
-  </si>
-  <si>
-    <t>8059.44316</t>
-  </si>
-  <si>
-    <t>110.662</t>
-  </si>
-  <si>
-    <t>5205.1117</t>
-  </si>
-  <si>
-    <t>104.997</t>
-  </si>
-  <si>
-    <t>7960.74498</t>
-  </si>
-  <si>
-    <t>111.995</t>
-  </si>
-  <si>
-    <t>5146.55383</t>
-  </si>
-  <si>
-    <t>150.002</t>
-  </si>
-  <si>
-    <t>4622.09906</t>
-  </si>
-  <si>
-    <t>103.998</t>
-  </si>
-  <si>
-    <t>7756.74811</t>
-  </si>
-  <si>
-    <t>151.335</t>
-  </si>
-  <si>
-    <t>4583.89882</t>
-  </si>
-  <si>
-    <t>105.331</t>
-  </si>
-  <si>
-    <t>7662.19361</t>
-  </si>
-  <si>
-    <t>206</t>
-  </si>
-  <si>
-    <t>1687.8734</t>
-  </si>
-  <si>
-    <t>454</t>
-  </si>
-  <si>
-    <t>972.79508</t>
-  </si>
-  <si>
-    <t>210</t>
-  </si>
-  <si>
-    <t>1729.22114</t>
-  </si>
-  <si>
-    <t>458</t>
-  </si>
-  <si>
-    <t>984.36607</t>
-  </si>
-  <si>
-    <t>207</t>
-  </si>
-  <si>
-    <t>1174.33602</t>
-  </si>
-  <si>
-    <t>180</t>
-  </si>
-  <si>
-    <t>1642.28568</t>
-  </si>
-  <si>
-    <t>211</t>
-  </si>
-  <si>
-    <t>1153.87619</t>
-  </si>
-  <si>
-    <t>184</t>
-  </si>
-  <si>
-    <t>1608.65077</t>
-  </si>
-  <si>
-    <t>118</t>
-  </si>
-  <si>
-    <t>4669.62457</t>
-  </si>
-  <si>
-    <t>108</t>
-  </si>
-  <si>
-    <t>2089.14596</t>
-  </si>
-  <si>
-    <t>122</t>
-  </si>
-  <si>
-    <t>4519.6395</t>
-  </si>
-  <si>
-    <t>112</t>
-  </si>
-  <si>
-    <t>2017.92932</t>
-  </si>
-  <si>
-    <t>82.665</t>
-  </si>
-  <si>
-    <t>5754.75296</t>
-  </si>
-  <si>
-    <t>171.331</t>
-  </si>
-  <si>
-    <t>3005.07364</t>
-  </si>
-  <si>
-    <t>83.998</t>
-  </si>
-  <si>
-    <t>5800.02511</t>
-  </si>
-  <si>
-    <t>172.664</t>
-  </si>
-  <si>
-    <t>3016.99644</t>
-  </si>
-  <si>
     <t>106.33</t>
   </si>
   <si>
     <t>7864.52145</t>
   </si>
   <si>
+    <t>4053.37644</t>
+  </si>
+  <si>
+    <t>121.326</t>
+  </si>
+  <si>
+    <t>GWL_Item_Dissimilar_Rc_02</t>
+  </si>
+  <si>
+    <t>113.328</t>
+  </si>
+  <si>
     <t>5089.37351</t>
+  </si>
+  <si>
+    <t>2772.09455</t>
+  </si>
+  <si>
+    <t>126.993</t>
   </si>
   <si>
     <t>107.663</t>
@@ -1081,10 +523,22 @@
     <t>5033.5227</t>
   </si>
   <si>
+    <t>GWL_Item_Dissimilar_Pl_01</t>
+  </si>
+  <si>
     <t>106.664</t>
   </si>
   <si>
     <t>7570.00244</t>
+  </si>
+  <si>
+    <t>3628.55556</t>
+  </si>
+  <si>
+    <t>139.658</t>
+  </si>
+  <si>
+    <t>GWL_Item_Dissimilar_Pl_02</t>
   </si>
   <si>
     <t>152.668</t>
@@ -1093,10 +547,31 @@
     <t>4546.36566</t>
   </si>
   <si>
+    <t>1899.41182</t>
+  </si>
+  <si>
+    <t>179</t>
+  </si>
+  <si>
     <t>107.997</t>
   </si>
   <si>
     <t>7480.08709</t>
+  </si>
+  <si>
+    <t>GWL_Item_Dissimilar_Pl_03</t>
+  </si>
+  <si>
+    <t>109.327</t>
+  </si>
+  <si>
+    <t>5747.55068</t>
+  </si>
+  <si>
+    <t>2805.0549</t>
+  </si>
+  <si>
+    <t>161.992</t>
   </si>
 </sst>
 </file>
@@ -2238,73 +1713,73 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ5"/>
-  <sheetFormatPr defaultColWidth="8.7047619047619" defaultRowHeight="15" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="5.14285714285714"/>
-    <col min="2" max="3" customWidth="true" width="20.5714285714286"/>
-    <col min="4" max="4" customWidth="true" width="79.4285714285714"/>
-    <col min="5" max="5" customWidth="true" width="11.5714285714286"/>
-    <col min="6" max="6" customWidth="true" width="5.14285714285714"/>
-    <col min="7" max="7" customWidth="true" width="11.0"/>
-    <col min="8" max="8" customWidth="true" width="12.7142857142857"/>
-    <col min="9" max="10" customWidth="true" width="5.85714285714286"/>
-    <col min="11" max="11" customWidth="true" width="6.0"/>
-    <col min="12" max="12" customWidth="true" width="14.2857142857143"/>
-    <col min="13" max="13" customWidth="true" width="9.42857142857143"/>
-    <col min="14" max="14" customWidth="true" width="14.2857142857143"/>
-    <col min="15" max="15" customWidth="true" width="15.5714285714286"/>
-    <col min="16" max="16" customWidth="true" width="14.4285714285714"/>
-    <col min="17" max="17" customWidth="true" width="39.4285714285714"/>
-    <col min="18" max="18" customWidth="true" width="11.7142857142857"/>
-    <col min="19" max="19" customWidth="true" width="10.0"/>
-    <col min="20" max="20" customWidth="true" width="6.42857142857143"/>
-    <col min="21" max="21" customWidth="true" width="9.85714285714286"/>
-    <col min="22" max="22" customWidth="true" width="6.57142857142857"/>
-    <col min="23" max="23" customWidth="true" width="37.1428571428571"/>
-    <col min="24" max="25" customWidth="true" width="8.0"/>
-    <col min="26" max="26" customWidth="true" width="7.71428571428571"/>
-    <col min="27" max="27" customWidth="true" width="6.28571428571429"/>
-    <col min="28" max="28" customWidth="true" width="9.28571428571429"/>
-    <col min="29" max="29" customWidth="true" width="9.71428571428571"/>
-    <col min="30" max="30" customWidth="true" width="12.8571428571429"/>
-    <col min="31" max="31" customWidth="true" width="16.1428571428571"/>
-    <col min="32" max="32" customWidth="true" width="15.4285714285714"/>
-    <col min="33" max="33" customWidth="true" width="24.5714285714286"/>
-    <col min="34" max="34" customWidth="true" width="8.57142857142857"/>
-    <col min="35" max="35" customWidth="true" width="14.7142857142857"/>
-    <col min="36" max="36" customWidth="true" width="18.5714285714286"/>
-    <col min="37" max="37" customWidth="true" width="14.1428571428571"/>
-    <col min="38" max="38" customWidth="true" width="14.7142857142857"/>
-    <col min="39" max="39" customWidth="true" width="17.4285714285714"/>
-    <col min="40" max="40" customWidth="true" width="22.0"/>
-    <col min="41" max="41" customWidth="true" width="17.5714285714286"/>
-    <col min="42" max="42" customWidth="true" width="25.2857142857143"/>
-    <col min="43" max="43" customWidth="true" width="13.0"/>
-    <col min="44" max="44" customWidth="true" width="25.7142857142857"/>
-    <col min="45" max="45" customWidth="true" width="10.0"/>
-    <col min="46" max="46" customWidth="true" width="13.0"/>
-    <col min="47" max="47" customWidth="true" width="15.5714285714286"/>
-    <col min="48" max="48" customWidth="true" width="21.1428571428571"/>
-    <col min="49" max="49" customWidth="true" width="11.5714285714286"/>
-    <col min="50" max="50" customWidth="true" width="16.7142857142857"/>
-    <col min="51" max="51" customWidth="true" width="14.0"/>
-    <col min="52" max="52" customWidth="true" width="19.4285714285714"/>
-    <col min="53" max="53" customWidth="true" width="18.8571428571429"/>
-    <col min="54" max="54" customWidth="true" width="23.2857142857143"/>
-    <col min="55" max="55" customWidth="true" width="15.5714285714286"/>
-    <col min="56" max="56" customWidth="true" width="14.2857142857143"/>
-    <col min="57" max="57" customWidth="true" width="17.0"/>
-    <col min="58" max="58" customWidth="true" width="16.2857142857143"/>
-    <col min="59" max="59" customWidth="true" width="13.5714285714286"/>
-    <col min="60" max="61" customWidth="true" width="12.7142857142857"/>
-    <col min="62" max="62" customWidth="true" width="21.8571428571429"/>
-    <col min="63" max="63" customWidth="true" width="30.5714285714286"/>
-    <col min="64" max="64" customWidth="true" width="10.0"/>
-    <col min="65" max="65" customWidth="true" width="42.5714285714286"/>
-    <col min="66" max="66" customWidth="true" width="38.1428571428571"/>
-    <col min="67" max="67" customWidth="true" width="19.4285714285714"/>
-    <col min="68" max="68" customWidth="true" width="35.4285714285714"/>
-    <col min="69" max="69" customWidth="true" width="9.57142857142857"/>
+    <col min="1" max="1" width="5.14545454545455" customWidth="1"/>
+    <col min="2" max="3" width="20.5727272727273" customWidth="1"/>
+    <col min="4" max="4" width="79.4272727272727" customWidth="1"/>
+    <col min="5" max="5" width="11.5727272727273" customWidth="1"/>
+    <col min="6" max="6" width="5.14545454545455" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="12.7181818181818" customWidth="1"/>
+    <col min="9" max="10" width="5.85454545454545" customWidth="1"/>
+    <col min="11" max="11" width="6" customWidth="1"/>
+    <col min="12" max="12" width="14.2818181818182" customWidth="1"/>
+    <col min="13" max="13" width="9.42727272727273" customWidth="1"/>
+    <col min="14" max="14" width="14.2818181818182" customWidth="1"/>
+    <col min="15" max="15" width="15.5727272727273" customWidth="1"/>
+    <col min="16" max="16" width="14.4272727272727" customWidth="1"/>
+    <col min="17" max="17" width="39.4272727272727" customWidth="1"/>
+    <col min="18" max="18" width="11.7181818181818" customWidth="1"/>
+    <col min="19" max="19" width="10" customWidth="1"/>
+    <col min="20" max="20" width="6.42727272727273" customWidth="1"/>
+    <col min="21" max="21" width="9.85454545454546" customWidth="1"/>
+    <col min="22" max="22" width="6.57272727272727" customWidth="1"/>
+    <col min="23" max="23" width="37.1454545454545" customWidth="1"/>
+    <col min="24" max="25" width="8" customWidth="1"/>
+    <col min="26" max="26" width="7.71818181818182" customWidth="1"/>
+    <col min="27" max="27" width="6.28181818181818" customWidth="1"/>
+    <col min="28" max="28" width="9.28181818181818" customWidth="1"/>
+    <col min="29" max="29" width="9.71818181818182" customWidth="1"/>
+    <col min="30" max="30" width="12.8545454545455" customWidth="1"/>
+    <col min="31" max="31" width="16.1454545454545" customWidth="1"/>
+    <col min="32" max="32" width="15.4272727272727" customWidth="1"/>
+    <col min="33" max="33" width="24.5727272727273" customWidth="1"/>
+    <col min="34" max="34" width="8.57272727272727" customWidth="1"/>
+    <col min="35" max="35" width="14.7181818181818" customWidth="1"/>
+    <col min="36" max="36" width="18.5727272727273" customWidth="1"/>
+    <col min="37" max="37" width="14.1454545454545" customWidth="1"/>
+    <col min="38" max="38" width="14.7181818181818" customWidth="1"/>
+    <col min="39" max="39" width="17.4272727272727" customWidth="1"/>
+    <col min="40" max="40" width="22" customWidth="1"/>
+    <col min="41" max="41" width="17.5727272727273" customWidth="1"/>
+    <col min="42" max="42" width="25.2818181818182" customWidth="1"/>
+    <col min="43" max="43" width="13" customWidth="1"/>
+    <col min="44" max="44" width="25.7181818181818" customWidth="1"/>
+    <col min="45" max="45" width="10" customWidth="1"/>
+    <col min="46" max="46" width="13" customWidth="1"/>
+    <col min="47" max="47" width="15.5727272727273" customWidth="1"/>
+    <col min="48" max="48" width="21.1454545454545" customWidth="1"/>
+    <col min="49" max="49" width="11.5727272727273" customWidth="1"/>
+    <col min="50" max="50" width="16.7181818181818" customWidth="1"/>
+    <col min="51" max="51" width="14" customWidth="1"/>
+    <col min="52" max="52" width="19.4272727272727" customWidth="1"/>
+    <col min="53" max="53" width="18.8545454545455" customWidth="1"/>
+    <col min="54" max="54" width="23.2818181818182" customWidth="1"/>
+    <col min="55" max="55" width="15.5727272727273" customWidth="1"/>
+    <col min="56" max="56" width="14.2818181818182" customWidth="1"/>
+    <col min="57" max="57" width="17" customWidth="1"/>
+    <col min="58" max="58" width="16.2818181818182" customWidth="1"/>
+    <col min="59" max="59" width="13.5727272727273" customWidth="1"/>
+    <col min="60" max="61" width="12.7181818181818" customWidth="1"/>
+    <col min="62" max="62" width="21.8545454545455" customWidth="1"/>
+    <col min="63" max="63" width="30.5727272727273" customWidth="1"/>
+    <col min="64" max="64" width="10" customWidth="1"/>
+    <col min="65" max="65" width="42.5727272727273" customWidth="1"/>
+    <col min="66" max="66" width="38.1454545454545" customWidth="1"/>
+    <col min="67" max="67" width="19.4272727272727" customWidth="1"/>
+    <col min="68" max="68" width="35.4272727272727" customWidth="1"/>
+    <col min="69" max="69" width="9.57272727272727" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -2475,7 +1950,7 @@
       <c r="BP2" s="27"/>
       <c r="BQ2" s="27"/>
     </row>
-    <row r="3" ht="15.75" spans="1:69">
+    <row r="3" ht="15.25" spans="1:69">
       <c r="A3" s="28" t="s">
         <v>9</v>
       </c>
@@ -2684,7 +2159,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.75" spans="1:69">
+    <row r="4" ht="15.25" spans="1:69">
       <c r="A4" s="26">
         <v>1</v>
       </c>
@@ -2805,8 +2280,8 @@
         <v>0</v>
       </c>
       <c r="AI4" s="35">
-        <f>S4*$M$21</f>
-        <v>0</v>
+        <f>S4*$M$4</f>
+        <v>1521.28</v>
       </c>
       <c r="AJ4" s="35">
         <f>IF($C$2=3,0,AG4+AH4)</f>
@@ -2825,7 +2300,7 @@
       </c>
       <c r="AN4" s="35">
         <f>AI4/AM4</f>
-        <v>0</v>
+        <v>380.32</v>
       </c>
       <c r="AO4" s="35">
         <f>AJ4/AM4</f>
@@ -2840,7 +2315,7 @@
       </c>
       <c r="AR4" s="35">
         <f>AN4+AO4+AP4</f>
-        <v>0</v>
+        <v>380.32</v>
       </c>
       <c r="AS4" s="35" t="s">
         <v>78</v>
@@ -2848,10 +2323,10 @@
       <c r="AT4" s="35" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" t="s" s="0">
+      <c r="AU4" t="s">
         <v>79</v>
       </c>
-      <c r="AV4" t="s" s="0">
+      <c r="AV4" t="s">
         <v>80</v>
       </c>
       <c r="AW4" s="35">
@@ -2860,13 +2335,13 @@
       </c>
       <c r="AX4" s="35">
         <f>AR4</f>
-        <v>0</v>
+        <v>380.32</v>
       </c>
       <c r="AY4" s="35">
         <f>AU4+AW4</f>
         <v>4</v>
       </c>
-      <c r="AZ4" t="s" s="0">
+      <c r="AZ4" t="s">
         <v>80</v>
       </c>
       <c r="BA4" s="36"/>
@@ -2891,11 +2366,11 @@
       <c r="BL4" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="BM4" t="s" s="0">
-        <v>308</v>
-      </c>
-      <c r="BN4" t="s" s="0">
-        <v>307</v>
+      <c r="BM4" t="s">
+        <v>86</v>
+      </c>
+      <c r="BN4" t="s">
+        <v>87</v>
       </c>
       <c r="BO4" s="35">
         <f>ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
@@ -2996,7 +2471,7 @@
       </c>
       <c r="AI5" s="41">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1521.28</v>
       </c>
       <c r="AJ5" s="41">
         <f t="shared" si="0"/>
@@ -3052,73 +2527,73 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ5"/>
-  <sheetFormatPr defaultColWidth="8.7047619047619" defaultRowHeight="15" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="5.14285714285714"/>
-    <col min="2" max="3" customWidth="true" width="28.2857142857143"/>
-    <col min="4" max="4" customWidth="true" width="79.4285714285714"/>
-    <col min="5" max="5" customWidth="true" width="11.5714285714286"/>
-    <col min="6" max="6" customWidth="true" width="5.14285714285714"/>
-    <col min="7" max="7" customWidth="true" width="11.0"/>
-    <col min="8" max="8" customWidth="true" width="12.7142857142857"/>
-    <col min="9" max="9" customWidth="true" width="5.85714285714286"/>
-    <col min="10" max="10" customWidth="true" width="6.0"/>
-    <col min="11" max="11" customWidth="true" width="5.85714285714286"/>
-    <col min="12" max="12" customWidth="true" width="14.2857142857143"/>
-    <col min="13" max="13" customWidth="true" width="9.42857142857143"/>
-    <col min="14" max="14" customWidth="true" width="14.4285714285714"/>
-    <col min="15" max="15" customWidth="true" width="15.5714285714286"/>
-    <col min="16" max="16" customWidth="true" width="14.4285714285714"/>
-    <col min="17" max="17" customWidth="true" width="39.4285714285714"/>
-    <col min="18" max="18" customWidth="true" width="11.7142857142857"/>
-    <col min="19" max="19" customWidth="true" width="11.8571428571429"/>
-    <col min="20" max="20" customWidth="true" width="6.42857142857143"/>
-    <col min="21" max="22" customWidth="true" width="6.57142857142857"/>
-    <col min="23" max="23" customWidth="true" width="37.1428571428571"/>
-    <col min="24" max="25" customWidth="true" width="8.0"/>
-    <col min="26" max="26" customWidth="true" width="7.71428571428571"/>
-    <col min="27" max="27" customWidth="true" width="6.28571428571429"/>
-    <col min="28" max="28" customWidth="true" width="9.28571428571429"/>
-    <col min="29" max="29" customWidth="true" width="9.71428571428571"/>
-    <col min="30" max="30" customWidth="true" width="12.8571428571429"/>
-    <col min="31" max="31" customWidth="true" width="16.1428571428571"/>
-    <col min="32" max="32" customWidth="true" width="15.4285714285714"/>
-    <col min="33" max="33" customWidth="true" width="24.5714285714286"/>
-    <col min="34" max="34" customWidth="true" width="8.57142857142857"/>
-    <col min="35" max="35" customWidth="true" width="14.7142857142857"/>
-    <col min="36" max="36" customWidth="true" width="18.5714285714286"/>
-    <col min="37" max="37" customWidth="true" width="14.1428571428571"/>
-    <col min="38" max="38" customWidth="true" width="14.7142857142857"/>
-    <col min="39" max="39" customWidth="true" width="17.4285714285714"/>
-    <col min="40" max="40" customWidth="true" width="22.0"/>
-    <col min="41" max="41" customWidth="true" width="17.5714285714286"/>
-    <col min="42" max="42" customWidth="true" width="25.2857142857143"/>
-    <col min="43" max="43" customWidth="true" width="13.0"/>
-    <col min="44" max="44" customWidth="true" width="23.7142857142857"/>
-    <col min="45" max="45" customWidth="true" width="10.0"/>
-    <col min="46" max="46" customWidth="true" width="13.0"/>
-    <col min="47" max="47" customWidth="true" width="15.5714285714286"/>
-    <col min="48" max="48" customWidth="true" width="21.1428571428571"/>
-    <col min="49" max="49" customWidth="true" width="11.5714285714286"/>
-    <col min="50" max="50" customWidth="true" width="16.7142857142857"/>
-    <col min="51" max="51" customWidth="true" width="14.0"/>
-    <col min="52" max="52" customWidth="true" width="19.4285714285714"/>
-    <col min="53" max="53" customWidth="true" width="18.8571428571429"/>
-    <col min="54" max="54" customWidth="true" width="23.2857142857143"/>
-    <col min="55" max="55" customWidth="true" width="15.5714285714286"/>
-    <col min="56" max="56" customWidth="true" width="14.2857142857143"/>
-    <col min="57" max="57" customWidth="true" width="17.0"/>
-    <col min="58" max="58" customWidth="true" width="16.2857142857143"/>
-    <col min="59" max="59" customWidth="true" width="13.5714285714286"/>
-    <col min="60" max="61" customWidth="true" width="12.7142857142857"/>
-    <col min="62" max="62" customWidth="true" width="21.8571428571429"/>
-    <col min="63" max="63" customWidth="true" width="30.5714285714286"/>
-    <col min="64" max="64" customWidth="true" width="10.0"/>
-    <col min="65" max="65" customWidth="true" width="42.5714285714286"/>
-    <col min="66" max="66" customWidth="true" width="38.1428571428571"/>
-    <col min="67" max="67" customWidth="true" width="19.4285714285714"/>
-    <col min="68" max="68" customWidth="true" width="35.4285714285714"/>
-    <col min="69" max="69" customWidth="true" width="9.57142857142857"/>
+    <col min="1" max="1" width="5.14545454545455" customWidth="1"/>
+    <col min="2" max="3" width="28.2818181818182" customWidth="1"/>
+    <col min="4" max="4" width="79.4272727272727" customWidth="1"/>
+    <col min="5" max="5" width="11.5727272727273" customWidth="1"/>
+    <col min="6" max="6" width="5.14545454545455" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="12.7181818181818" customWidth="1"/>
+    <col min="9" max="9" width="5.85454545454545" customWidth="1"/>
+    <col min="10" max="10" width="6" customWidth="1"/>
+    <col min="11" max="11" width="5.85454545454545" customWidth="1"/>
+    <col min="12" max="12" width="14.2818181818182" customWidth="1"/>
+    <col min="13" max="13" width="9.42727272727273" customWidth="1"/>
+    <col min="14" max="14" width="14.4272727272727" customWidth="1"/>
+    <col min="15" max="15" width="15.5727272727273" customWidth="1"/>
+    <col min="16" max="16" width="14.4272727272727" customWidth="1"/>
+    <col min="17" max="17" width="39.4272727272727" customWidth="1"/>
+    <col min="18" max="18" width="11.7181818181818" customWidth="1"/>
+    <col min="19" max="19" width="11.8545454545455" customWidth="1"/>
+    <col min="20" max="20" width="6.42727272727273" customWidth="1"/>
+    <col min="21" max="22" width="6.57272727272727" customWidth="1"/>
+    <col min="23" max="23" width="37.1454545454545" customWidth="1"/>
+    <col min="24" max="25" width="8" customWidth="1"/>
+    <col min="26" max="26" width="7.71818181818182" customWidth="1"/>
+    <col min="27" max="27" width="6.28181818181818" customWidth="1"/>
+    <col min="28" max="28" width="9.28181818181818" customWidth="1"/>
+    <col min="29" max="29" width="9.71818181818182" customWidth="1"/>
+    <col min="30" max="30" width="12.8545454545455" customWidth="1"/>
+    <col min="31" max="31" width="16.1454545454545" customWidth="1"/>
+    <col min="32" max="32" width="15.4272727272727" customWidth="1"/>
+    <col min="33" max="33" width="24.5727272727273" customWidth="1"/>
+    <col min="34" max="34" width="8.57272727272727" customWidth="1"/>
+    <col min="35" max="35" width="14.7181818181818" customWidth="1"/>
+    <col min="36" max="36" width="18.5727272727273" customWidth="1"/>
+    <col min="37" max="37" width="14.1454545454545" customWidth="1"/>
+    <col min="38" max="38" width="14.7181818181818" customWidth="1"/>
+    <col min="39" max="39" width="17.4272727272727" customWidth="1"/>
+    <col min="40" max="40" width="22" customWidth="1"/>
+    <col min="41" max="41" width="17.5727272727273" customWidth="1"/>
+    <col min="42" max="42" width="25.2818181818182" customWidth="1"/>
+    <col min="43" max="43" width="13" customWidth="1"/>
+    <col min="44" max="44" width="23.7181818181818" customWidth="1"/>
+    <col min="45" max="45" width="10" customWidth="1"/>
+    <col min="46" max="46" width="13" customWidth="1"/>
+    <col min="47" max="47" width="15.5727272727273" customWidth="1"/>
+    <col min="48" max="48" width="21.1454545454545" customWidth="1"/>
+    <col min="49" max="49" width="11.5727272727273" customWidth="1"/>
+    <col min="50" max="50" width="16.7181818181818" customWidth="1"/>
+    <col min="51" max="51" width="14" customWidth="1"/>
+    <col min="52" max="52" width="19.4272727272727" customWidth="1"/>
+    <col min="53" max="53" width="18.8545454545455" customWidth="1"/>
+    <col min="54" max="54" width="23.2818181818182" customWidth="1"/>
+    <col min="55" max="55" width="15.5727272727273" customWidth="1"/>
+    <col min="56" max="56" width="14.2818181818182" customWidth="1"/>
+    <col min="57" max="57" width="17" customWidth="1"/>
+    <col min="58" max="58" width="16.2818181818182" customWidth="1"/>
+    <col min="59" max="59" width="13.5727272727273" customWidth="1"/>
+    <col min="60" max="61" width="12.7181818181818" customWidth="1"/>
+    <col min="62" max="62" width="21.8545454545455" customWidth="1"/>
+    <col min="63" max="63" width="30.5727272727273" customWidth="1"/>
+    <col min="64" max="64" width="10" customWidth="1"/>
+    <col min="65" max="65" width="42.5727272727273" customWidth="1"/>
+    <col min="66" max="66" width="38.1454545454545" customWidth="1"/>
+    <col min="67" max="67" width="19.4272727272727" customWidth="1"/>
+    <col min="68" max="68" width="35.4272727272727" customWidth="1"/>
+    <col min="69" max="69" width="9.57272727272727" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -3289,7 +2764,7 @@
       <c r="BP2" s="27"/>
       <c r="BQ2" s="27"/>
     </row>
-    <row r="3" ht="15.75" spans="1:69">
+    <row r="3" ht="15.25" spans="1:69">
       <c r="A3" s="28" t="s">
         <v>9</v>
       </c>
@@ -3498,7 +2973,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.75" spans="1:69">
+    <row r="4" ht="15.25" spans="1:69">
       <c r="A4" s="26">
         <v>1</v>
       </c>
@@ -3662,8 +3137,6 @@
       <c r="AT4" s="35" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" s="0"/>
-      <c r="AV4" s="0"/>
       <c r="AW4" s="35">
         <f>AM4</f>
         <v>4</v>
@@ -3702,10 +3175,10 @@
       <c r="BL4" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="BM4" t="s" s="0">
+      <c r="BM4" t="s">
         <v>100</v>
       </c>
-      <c r="BN4" t="s" s="0">
+      <c r="BN4" t="s">
         <v>100</v>
       </c>
       <c r="BO4" s="35">
@@ -3851,73 +3324,73 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ5"/>
-  <sheetFormatPr defaultColWidth="8.7047619047619" defaultRowHeight="15" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="5.14285714285714"/>
-    <col min="2" max="3" customWidth="true" width="24.7142857142857"/>
-    <col min="4" max="4" customWidth="true" width="79.4285714285714"/>
-    <col min="5" max="5" customWidth="true" width="11.5714285714286"/>
-    <col min="6" max="6" customWidth="true" width="5.14285714285714"/>
-    <col min="7" max="7" customWidth="true" width="11.0"/>
-    <col min="8" max="8" customWidth="true" width="12.7142857142857"/>
-    <col min="9" max="9" customWidth="true" width="5.85714285714286"/>
-    <col min="10" max="10" customWidth="true" width="6.0"/>
-    <col min="11" max="11" customWidth="true" width="5.85714285714286"/>
-    <col min="12" max="12" customWidth="true" width="14.2857142857143"/>
-    <col min="13" max="13" customWidth="true" width="9.42857142857143"/>
-    <col min="14" max="14" customWidth="true" width="14.4285714285714"/>
-    <col min="15" max="15" customWidth="true" width="15.5714285714286"/>
-    <col min="16" max="16" customWidth="true" width="14.4285714285714"/>
-    <col min="17" max="17" customWidth="true" width="39.4285714285714"/>
-    <col min="18" max="18" customWidth="true" width="11.7142857142857"/>
-    <col min="19" max="19" customWidth="true" width="11.8571428571429"/>
-    <col min="20" max="20" customWidth="true" width="6.42857142857143"/>
-    <col min="21" max="22" customWidth="true" width="6.57142857142857"/>
-    <col min="23" max="23" customWidth="true" width="37.1428571428571"/>
-    <col min="24" max="25" customWidth="true" width="8.0"/>
-    <col min="26" max="26" customWidth="true" width="7.71428571428571"/>
-    <col min="27" max="27" customWidth="true" width="6.28571428571429"/>
-    <col min="28" max="28" customWidth="true" width="9.28571428571429"/>
-    <col min="29" max="29" customWidth="true" width="9.71428571428571"/>
-    <col min="30" max="30" customWidth="true" width="12.8571428571429"/>
-    <col min="31" max="31" customWidth="true" width="16.1428571428571"/>
-    <col min="32" max="32" customWidth="true" width="15.4285714285714"/>
-    <col min="33" max="33" customWidth="true" width="24.5714285714286"/>
-    <col min="34" max="34" customWidth="true" width="8.57142857142857"/>
-    <col min="35" max="35" customWidth="true" width="14.7142857142857"/>
-    <col min="36" max="36" customWidth="true" width="18.5714285714286"/>
-    <col min="37" max="37" customWidth="true" width="14.1428571428571"/>
-    <col min="38" max="38" customWidth="true" width="14.7142857142857"/>
-    <col min="39" max="39" customWidth="true" width="17.4285714285714"/>
-    <col min="40" max="40" customWidth="true" width="22.0"/>
-    <col min="41" max="41" customWidth="true" width="17.5714285714286"/>
-    <col min="42" max="42" customWidth="true" width="25.2857142857143"/>
-    <col min="43" max="43" customWidth="true" width="13.0"/>
-    <col min="44" max="44" customWidth="true" width="23.7142857142857"/>
-    <col min="45" max="45" customWidth="true" width="10.0"/>
-    <col min="46" max="46" customWidth="true" width="13.0"/>
-    <col min="47" max="47" customWidth="true" width="15.5714285714286"/>
-    <col min="48" max="48" customWidth="true" width="21.1428571428571"/>
-    <col min="49" max="49" customWidth="true" width="11.5714285714286"/>
-    <col min="50" max="50" customWidth="true" width="16.7142857142857"/>
-    <col min="51" max="51" customWidth="true" width="14.0"/>
-    <col min="52" max="52" customWidth="true" width="19.4285714285714"/>
-    <col min="53" max="53" customWidth="true" width="18.8571428571429"/>
-    <col min="54" max="54" customWidth="true" width="23.2857142857143"/>
-    <col min="55" max="55" customWidth="true" width="15.5714285714286"/>
-    <col min="56" max="56" customWidth="true" width="14.2857142857143"/>
-    <col min="57" max="57" customWidth="true" width="17.0"/>
-    <col min="58" max="58" customWidth="true" width="16.2857142857143"/>
-    <col min="59" max="59" customWidth="true" width="13.5714285714286"/>
-    <col min="60" max="61" customWidth="true" width="12.7142857142857"/>
-    <col min="62" max="62" customWidth="true" width="21.8571428571429"/>
-    <col min="63" max="63" customWidth="true" width="30.5714285714286"/>
-    <col min="64" max="64" customWidth="true" width="10.0"/>
-    <col min="65" max="65" customWidth="true" width="42.5714285714286"/>
-    <col min="66" max="66" customWidth="true" width="38.1428571428571"/>
-    <col min="67" max="67" customWidth="true" width="19.4285714285714"/>
-    <col min="68" max="68" customWidth="true" width="35.4285714285714"/>
-    <col min="69" max="69" customWidth="true" width="9.57142857142857"/>
+    <col min="1" max="1" width="5.14545454545455" customWidth="1"/>
+    <col min="2" max="3" width="24.7181818181818" customWidth="1"/>
+    <col min="4" max="4" width="79.4272727272727" customWidth="1"/>
+    <col min="5" max="5" width="11.5727272727273" customWidth="1"/>
+    <col min="6" max="6" width="5.14545454545455" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="12.7181818181818" customWidth="1"/>
+    <col min="9" max="9" width="5.85454545454545" customWidth="1"/>
+    <col min="10" max="10" width="6" customWidth="1"/>
+    <col min="11" max="11" width="5.85454545454545" customWidth="1"/>
+    <col min="12" max="12" width="14.2818181818182" customWidth="1"/>
+    <col min="13" max="13" width="9.42727272727273" customWidth="1"/>
+    <col min="14" max="14" width="14.4272727272727" customWidth="1"/>
+    <col min="15" max="15" width="15.5727272727273" customWidth="1"/>
+    <col min="16" max="16" width="14.4272727272727" customWidth="1"/>
+    <col min="17" max="17" width="39.4272727272727" customWidth="1"/>
+    <col min="18" max="18" width="11.7181818181818" customWidth="1"/>
+    <col min="19" max="19" width="11.8545454545455" customWidth="1"/>
+    <col min="20" max="20" width="6.42727272727273" customWidth="1"/>
+    <col min="21" max="22" width="6.57272727272727" customWidth="1"/>
+    <col min="23" max="23" width="37.1454545454545" customWidth="1"/>
+    <col min="24" max="25" width="8" customWidth="1"/>
+    <col min="26" max="26" width="7.71818181818182" customWidth="1"/>
+    <col min="27" max="27" width="6.28181818181818" customWidth="1"/>
+    <col min="28" max="28" width="9.28181818181818" customWidth="1"/>
+    <col min="29" max="29" width="9.71818181818182" customWidth="1"/>
+    <col min="30" max="30" width="12.8545454545455" customWidth="1"/>
+    <col min="31" max="31" width="16.1454545454545" customWidth="1"/>
+    <col min="32" max="32" width="15.4272727272727" customWidth="1"/>
+    <col min="33" max="33" width="24.5727272727273" customWidth="1"/>
+    <col min="34" max="34" width="8.57272727272727" customWidth="1"/>
+    <col min="35" max="35" width="14.7181818181818" customWidth="1"/>
+    <col min="36" max="36" width="18.5727272727273" customWidth="1"/>
+    <col min="37" max="37" width="14.1454545454545" customWidth="1"/>
+    <col min="38" max="38" width="14.7181818181818" customWidth="1"/>
+    <col min="39" max="39" width="17.4272727272727" customWidth="1"/>
+    <col min="40" max="40" width="22" customWidth="1"/>
+    <col min="41" max="41" width="17.5727272727273" customWidth="1"/>
+    <col min="42" max="42" width="25.2818181818182" customWidth="1"/>
+    <col min="43" max="43" width="13" customWidth="1"/>
+    <col min="44" max="44" width="23.7181818181818" customWidth="1"/>
+    <col min="45" max="45" width="10" customWidth="1"/>
+    <col min="46" max="46" width="13" customWidth="1"/>
+    <col min="47" max="47" width="15.5727272727273" customWidth="1"/>
+    <col min="48" max="48" width="21.1454545454545" customWidth="1"/>
+    <col min="49" max="49" width="11.5727272727273" customWidth="1"/>
+    <col min="50" max="50" width="16.7181818181818" customWidth="1"/>
+    <col min="51" max="51" width="14" customWidth="1"/>
+    <col min="52" max="52" width="19.4272727272727" customWidth="1"/>
+    <col min="53" max="53" width="18.8545454545455" customWidth="1"/>
+    <col min="54" max="54" width="23.2818181818182" customWidth="1"/>
+    <col min="55" max="55" width="15.5727272727273" customWidth="1"/>
+    <col min="56" max="56" width="14.2818181818182" customWidth="1"/>
+    <col min="57" max="57" width="17" customWidth="1"/>
+    <col min="58" max="58" width="16.2818181818182" customWidth="1"/>
+    <col min="59" max="59" width="13.5727272727273" customWidth="1"/>
+    <col min="60" max="61" width="12.7181818181818" customWidth="1"/>
+    <col min="62" max="62" width="21.8545454545455" customWidth="1"/>
+    <col min="63" max="63" width="30.5727272727273" customWidth="1"/>
+    <col min="64" max="64" width="10" customWidth="1"/>
+    <col min="65" max="65" width="42.5727272727273" customWidth="1"/>
+    <col min="66" max="66" width="38.1454545454545" customWidth="1"/>
+    <col min="67" max="67" width="19.4272727272727" customWidth="1"/>
+    <col min="68" max="68" width="35.4272727272727" customWidth="1"/>
+    <col min="69" max="69" width="9.57272727272727" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -4088,7 +3561,7 @@
       <c r="BP2" s="27"/>
       <c r="BQ2" s="27"/>
     </row>
-    <row r="3" ht="15.75" spans="1:69">
+    <row r="3" ht="15.25" spans="1:69">
       <c r="A3" s="28" t="s">
         <v>9</v>
       </c>
@@ -4297,7 +3770,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.75" spans="1:69">
+    <row r="4" ht="15.25" spans="1:69">
       <c r="A4" s="26">
         <v>1</v>
       </c>
@@ -4461,11 +3934,11 @@
       <c r="AT4" s="35" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" t="s" s="0">
-        <v>323</v>
-      </c>
-      <c r="AV4" t="s" s="0">
-        <v>324</v>
+      <c r="AU4" t="s">
+        <v>118</v>
+      </c>
+      <c r="AV4" t="s">
+        <v>119</v>
       </c>
       <c r="AW4" s="35">
         <f>AM4</f>
@@ -4505,11 +3978,11 @@
       <c r="BL4" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="BM4" t="s" s="0">
-        <v>269</v>
-      </c>
-      <c r="BN4" t="s" s="0">
-        <v>268</v>
+      <c r="BM4" t="s">
+        <v>120</v>
+      </c>
+      <c r="BN4" t="s">
+        <v>121</v>
       </c>
       <c r="BO4" s="35">
         <f>ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
@@ -4666,73 +4139,73 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ5"/>
-  <sheetFormatPr defaultColWidth="8.7047619047619" defaultRowHeight="15" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="5.14285714285714"/>
-    <col min="2" max="3" customWidth="true" width="24.7142857142857"/>
-    <col min="4" max="4" customWidth="true" width="79.4285714285714"/>
-    <col min="5" max="5" customWidth="true" width="11.5714285714286"/>
-    <col min="6" max="6" customWidth="true" width="5.14285714285714"/>
-    <col min="7" max="7" customWidth="true" width="11.0"/>
-    <col min="8" max="8" customWidth="true" width="12.7142857142857"/>
-    <col min="9" max="9" customWidth="true" width="5.85714285714286"/>
-    <col min="10" max="10" customWidth="true" width="6.0"/>
-    <col min="11" max="11" customWidth="true" width="5.85714285714286"/>
-    <col min="12" max="12" customWidth="true" width="14.2857142857143"/>
-    <col min="13" max="13" customWidth="true" width="9.42857142857143"/>
-    <col min="14" max="14" customWidth="true" width="14.4285714285714"/>
-    <col min="15" max="15" customWidth="true" width="15.5714285714286"/>
-    <col min="16" max="16" customWidth="true" width="14.4285714285714"/>
-    <col min="17" max="17" customWidth="true" width="39.4285714285714"/>
-    <col min="18" max="18" customWidth="true" width="11.7142857142857"/>
-    <col min="19" max="19" customWidth="true" width="11.8571428571429"/>
-    <col min="20" max="20" customWidth="true" width="6.42857142857143"/>
-    <col min="21" max="22" customWidth="true" width="6.57142857142857"/>
-    <col min="23" max="23" customWidth="true" width="37.1428571428571"/>
-    <col min="24" max="25" customWidth="true" width="8.0"/>
-    <col min="26" max="26" customWidth="true" width="7.71428571428571"/>
-    <col min="27" max="27" customWidth="true" width="6.28571428571429"/>
-    <col min="28" max="28" customWidth="true" width="9.28571428571429"/>
-    <col min="29" max="29" customWidth="true" width="9.71428571428571"/>
-    <col min="30" max="30" customWidth="true" width="12.8571428571429"/>
-    <col min="31" max="31" customWidth="true" width="16.1428571428571"/>
-    <col min="32" max="32" customWidth="true" width="15.4285714285714"/>
-    <col min="33" max="33" customWidth="true" width="24.5714285714286"/>
-    <col min="34" max="34" customWidth="true" width="8.57142857142857"/>
-    <col min="35" max="35" customWidth="true" width="14.7142857142857"/>
-    <col min="36" max="36" customWidth="true" width="18.5714285714286"/>
-    <col min="37" max="37" customWidth="true" width="14.1428571428571"/>
-    <col min="38" max="38" customWidth="true" width="14.7142857142857"/>
-    <col min="39" max="39" customWidth="true" width="17.4285714285714"/>
-    <col min="40" max="40" customWidth="true" width="22.0"/>
-    <col min="41" max="41" customWidth="true" width="17.5714285714286"/>
-    <col min="42" max="42" customWidth="true" width="25.2857142857143"/>
-    <col min="43" max="43" customWidth="true" width="13.0"/>
-    <col min="44" max="44" customWidth="true" width="23.7142857142857"/>
-    <col min="45" max="45" customWidth="true" width="10.0"/>
-    <col min="46" max="46" customWidth="true" width="13.0"/>
-    <col min="47" max="47" customWidth="true" width="15.5714285714286"/>
-    <col min="48" max="48" customWidth="true" width="21.1428571428571"/>
-    <col min="49" max="49" customWidth="true" width="11.5714285714286"/>
-    <col min="50" max="50" customWidth="true" width="16.7142857142857"/>
-    <col min="51" max="51" customWidth="true" width="14.0"/>
-    <col min="52" max="52" customWidth="true" width="19.4285714285714"/>
-    <col min="53" max="53" customWidth="true" width="18.8571428571429"/>
-    <col min="54" max="54" customWidth="true" width="23.2857142857143"/>
-    <col min="55" max="55" customWidth="true" width="15.5714285714286"/>
-    <col min="56" max="56" customWidth="true" width="14.2857142857143"/>
-    <col min="57" max="57" customWidth="true" width="17.0"/>
-    <col min="58" max="58" customWidth="true" width="16.2857142857143"/>
-    <col min="59" max="59" customWidth="true" width="13.5714285714286"/>
-    <col min="60" max="61" customWidth="true" width="12.7142857142857"/>
-    <col min="62" max="62" customWidth="true" width="21.8571428571429"/>
-    <col min="63" max="63" customWidth="true" width="30.5714285714286"/>
-    <col min="64" max="64" customWidth="true" width="10.0"/>
-    <col min="65" max="65" customWidth="true" width="42.5714285714286"/>
-    <col min="66" max="66" customWidth="true" width="38.1428571428571"/>
-    <col min="67" max="67" customWidth="true" width="19.4285714285714"/>
-    <col min="68" max="68" customWidth="true" width="35.4285714285714"/>
-    <col min="69" max="69" customWidth="true" width="9.57142857142857"/>
+    <col min="1" max="1" width="5.14545454545455" customWidth="1"/>
+    <col min="2" max="3" width="24.7181818181818" customWidth="1"/>
+    <col min="4" max="4" width="79.4272727272727" customWidth="1"/>
+    <col min="5" max="5" width="11.5727272727273" customWidth="1"/>
+    <col min="6" max="6" width="5.14545454545455" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="12.7181818181818" customWidth="1"/>
+    <col min="9" max="9" width="5.85454545454545" customWidth="1"/>
+    <col min="10" max="10" width="6" customWidth="1"/>
+    <col min="11" max="11" width="5.85454545454545" customWidth="1"/>
+    <col min="12" max="12" width="14.2818181818182" customWidth="1"/>
+    <col min="13" max="13" width="9.42727272727273" customWidth="1"/>
+    <col min="14" max="14" width="14.4272727272727" customWidth="1"/>
+    <col min="15" max="15" width="15.5727272727273" customWidth="1"/>
+    <col min="16" max="16" width="14.4272727272727" customWidth="1"/>
+    <col min="17" max="17" width="39.4272727272727" customWidth="1"/>
+    <col min="18" max="18" width="11.7181818181818" customWidth="1"/>
+    <col min="19" max="19" width="11.8545454545455" customWidth="1"/>
+    <col min="20" max="20" width="6.42727272727273" customWidth="1"/>
+    <col min="21" max="22" width="6.57272727272727" customWidth="1"/>
+    <col min="23" max="23" width="37.1454545454545" customWidth="1"/>
+    <col min="24" max="25" width="8" customWidth="1"/>
+    <col min="26" max="26" width="7.71818181818182" customWidth="1"/>
+    <col min="27" max="27" width="6.28181818181818" customWidth="1"/>
+    <col min="28" max="28" width="9.28181818181818" customWidth="1"/>
+    <col min="29" max="29" width="9.71818181818182" customWidth="1"/>
+    <col min="30" max="30" width="12.8545454545455" customWidth="1"/>
+    <col min="31" max="31" width="16.1454545454545" customWidth="1"/>
+    <col min="32" max="32" width="15.4272727272727" customWidth="1"/>
+    <col min="33" max="33" width="24.5727272727273" customWidth="1"/>
+    <col min="34" max="34" width="8.57272727272727" customWidth="1"/>
+    <col min="35" max="35" width="14.7181818181818" customWidth="1"/>
+    <col min="36" max="36" width="18.5727272727273" customWidth="1"/>
+    <col min="37" max="37" width="14.1454545454545" customWidth="1"/>
+    <col min="38" max="38" width="14.7181818181818" customWidth="1"/>
+    <col min="39" max="39" width="17.4272727272727" customWidth="1"/>
+    <col min="40" max="40" width="22" customWidth="1"/>
+    <col min="41" max="41" width="17.5727272727273" customWidth="1"/>
+    <col min="42" max="42" width="25.2818181818182" customWidth="1"/>
+    <col min="43" max="43" width="13" customWidth="1"/>
+    <col min="44" max="44" width="23.7181818181818" customWidth="1"/>
+    <col min="45" max="45" width="10" customWidth="1"/>
+    <col min="46" max="46" width="13" customWidth="1"/>
+    <col min="47" max="47" width="15.5727272727273" customWidth="1"/>
+    <col min="48" max="48" width="21.1454545454545" customWidth="1"/>
+    <col min="49" max="49" width="11.5727272727273" customWidth="1"/>
+    <col min="50" max="50" width="16.7181818181818" customWidth="1"/>
+    <col min="51" max="51" width="14" customWidth="1"/>
+    <col min="52" max="52" width="19.4272727272727" customWidth="1"/>
+    <col min="53" max="53" width="18.8545454545455" customWidth="1"/>
+    <col min="54" max="54" width="23.2818181818182" customWidth="1"/>
+    <col min="55" max="55" width="15.5727272727273" customWidth="1"/>
+    <col min="56" max="56" width="14.2818181818182" customWidth="1"/>
+    <col min="57" max="57" width="17" customWidth="1"/>
+    <col min="58" max="58" width="16.2818181818182" customWidth="1"/>
+    <col min="59" max="59" width="13.5727272727273" customWidth="1"/>
+    <col min="60" max="61" width="12.7181818181818" customWidth="1"/>
+    <col min="62" max="62" width="21.8545454545455" customWidth="1"/>
+    <col min="63" max="63" width="30.5727272727273" customWidth="1"/>
+    <col min="64" max="64" width="10" customWidth="1"/>
+    <col min="65" max="65" width="42.5727272727273" customWidth="1"/>
+    <col min="66" max="66" width="38.1454545454545" customWidth="1"/>
+    <col min="67" max="67" width="19.4272727272727" customWidth="1"/>
+    <col min="68" max="68" width="35.4272727272727" customWidth="1"/>
+    <col min="69" max="69" width="9.57272727272727" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -4903,7 +4376,7 @@
       <c r="BP2" s="27"/>
       <c r="BQ2" s="27"/>
     </row>
-    <row r="3" ht="15.75" spans="1:69">
+    <row r="3" ht="15.25" spans="1:69">
       <c r="A3" s="28" t="s">
         <v>9</v>
       </c>
@@ -5112,7 +4585,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.75" spans="1:69">
+    <row r="4" ht="15.25" spans="1:69">
       <c r="A4" s="26">
         <v>1</v>
       </c>
@@ -5276,11 +4749,11 @@
       <c r="AT4" s="35" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" t="s" s="0">
-        <v>325</v>
-      </c>
-      <c r="AV4" t="s" s="0">
-        <v>326</v>
+      <c r="AU4" t="s">
+        <v>123</v>
+      </c>
+      <c r="AV4" t="s">
+        <v>124</v>
       </c>
       <c r="AW4" s="35">
         <f>AM4</f>
@@ -5320,11 +4793,11 @@
       <c r="BL4" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="BM4" t="s" s="0">
-        <v>272</v>
-      </c>
-      <c r="BN4" t="s" s="0">
-        <v>271</v>
+      <c r="BM4" t="s">
+        <v>125</v>
+      </c>
+      <c r="BN4" t="s">
+        <v>126</v>
       </c>
       <c r="BO4" s="35">
         <f>ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
@@ -5469,73 +4942,73 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ5"/>
-  <sheetFormatPr defaultColWidth="8.7047619047619" defaultRowHeight="15" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="5.14285714285714"/>
-    <col min="2" max="3" customWidth="true" width="25.1428571428571"/>
-    <col min="4" max="4" customWidth="true" width="79.4285714285714"/>
-    <col min="5" max="5" customWidth="true" width="11.5714285714286"/>
-    <col min="6" max="6" customWidth="true" width="5.14285714285714"/>
-    <col min="7" max="7" customWidth="true" width="11.0"/>
-    <col min="8" max="8" customWidth="true" width="12.7142857142857"/>
-    <col min="9" max="9" customWidth="true" width="5.85714285714286"/>
-    <col min="10" max="10" customWidth="true" width="6.0"/>
-    <col min="11" max="11" customWidth="true" width="5.85714285714286"/>
-    <col min="12" max="12" customWidth="true" width="14.2857142857143"/>
-    <col min="13" max="13" customWidth="true" width="9.42857142857143"/>
-    <col min="14" max="14" customWidth="true" width="14.4285714285714"/>
-    <col min="15" max="15" customWidth="true" width="15.5714285714286"/>
-    <col min="16" max="16" customWidth="true" width="14.4285714285714"/>
-    <col min="17" max="17" customWidth="true" width="39.4285714285714"/>
-    <col min="18" max="18" customWidth="true" width="11.7142857142857"/>
-    <col min="19" max="19" customWidth="true" width="11.8571428571429"/>
-    <col min="20" max="20" customWidth="true" width="6.42857142857143"/>
-    <col min="21" max="22" customWidth="true" width="6.57142857142857"/>
-    <col min="23" max="23" customWidth="true" width="37.1428571428571"/>
-    <col min="24" max="25" customWidth="true" width="8.0"/>
-    <col min="26" max="26" customWidth="true" width="7.71428571428571"/>
-    <col min="27" max="27" customWidth="true" width="6.28571428571429"/>
-    <col min="28" max="28" customWidth="true" width="9.28571428571429"/>
-    <col min="29" max="29" customWidth="true" width="9.71428571428571"/>
-    <col min="30" max="30" customWidth="true" width="12.8571428571429"/>
-    <col min="31" max="31" customWidth="true" width="16.1428571428571"/>
-    <col min="32" max="32" customWidth="true" width="15.4285714285714"/>
-    <col min="33" max="33" customWidth="true" width="24.5714285714286"/>
-    <col min="34" max="34" customWidth="true" width="8.57142857142857"/>
-    <col min="35" max="35" customWidth="true" width="14.7142857142857"/>
-    <col min="36" max="36" customWidth="true" width="18.5714285714286"/>
-    <col min="37" max="37" customWidth="true" width="14.1428571428571"/>
-    <col min="38" max="38" customWidth="true" width="14.7142857142857"/>
-    <col min="39" max="39" customWidth="true" width="17.4285714285714"/>
-    <col min="40" max="40" customWidth="true" width="22.0"/>
-    <col min="41" max="41" customWidth="true" width="17.5714285714286"/>
-    <col min="42" max="42" customWidth="true" width="25.2857142857143"/>
-    <col min="43" max="43" customWidth="true" width="13.0"/>
-    <col min="44" max="44" customWidth="true" width="23.7142857142857"/>
-    <col min="45" max="45" customWidth="true" width="10.0"/>
-    <col min="46" max="46" customWidth="true" width="13.0"/>
-    <col min="47" max="47" customWidth="true" width="15.5714285714286"/>
-    <col min="48" max="48" customWidth="true" width="21.1428571428571"/>
-    <col min="49" max="49" customWidth="true" width="11.5714285714286"/>
-    <col min="50" max="50" customWidth="true" width="16.7142857142857"/>
-    <col min="51" max="51" customWidth="true" width="14.0"/>
-    <col min="52" max="52" customWidth="true" width="19.4285714285714"/>
-    <col min="53" max="53" customWidth="true" width="18.8571428571429"/>
-    <col min="54" max="54" customWidth="true" width="23.2857142857143"/>
-    <col min="55" max="55" customWidth="true" width="15.5714285714286"/>
-    <col min="56" max="56" customWidth="true" width="14.2857142857143"/>
-    <col min="57" max="57" customWidth="true" width="17.0"/>
-    <col min="58" max="58" customWidth="true" width="16.2857142857143"/>
-    <col min="59" max="59" customWidth="true" width="13.5714285714286"/>
-    <col min="60" max="61" customWidth="true" width="12.7142857142857"/>
-    <col min="62" max="62" customWidth="true" width="21.8571428571429"/>
-    <col min="63" max="63" customWidth="true" width="30.5714285714286"/>
-    <col min="64" max="64" customWidth="true" width="10.0"/>
-    <col min="65" max="65" customWidth="true" width="42.5714285714286"/>
-    <col min="66" max="66" customWidth="true" width="38.1428571428571"/>
-    <col min="67" max="67" customWidth="true" width="19.4285714285714"/>
-    <col min="68" max="68" customWidth="true" width="35.4285714285714"/>
-    <col min="69" max="69" customWidth="true" width="9.57142857142857"/>
+    <col min="1" max="1" width="5.14545454545455" customWidth="1"/>
+    <col min="2" max="3" width="25.1454545454545" customWidth="1"/>
+    <col min="4" max="4" width="79.4272727272727" customWidth="1"/>
+    <col min="5" max="5" width="11.5727272727273" customWidth="1"/>
+    <col min="6" max="6" width="5.14545454545455" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="12.7181818181818" customWidth="1"/>
+    <col min="9" max="9" width="5.85454545454545" customWidth="1"/>
+    <col min="10" max="10" width="6" customWidth="1"/>
+    <col min="11" max="11" width="5.85454545454545" customWidth="1"/>
+    <col min="12" max="12" width="14.2818181818182" customWidth="1"/>
+    <col min="13" max="13" width="9.42727272727273" customWidth="1"/>
+    <col min="14" max="14" width="14.4272727272727" customWidth="1"/>
+    <col min="15" max="15" width="15.5727272727273" customWidth="1"/>
+    <col min="16" max="16" width="14.4272727272727" customWidth="1"/>
+    <col min="17" max="17" width="39.4272727272727" customWidth="1"/>
+    <col min="18" max="18" width="11.7181818181818" customWidth="1"/>
+    <col min="19" max="19" width="11.8545454545455" customWidth="1"/>
+    <col min="20" max="20" width="6.42727272727273" customWidth="1"/>
+    <col min="21" max="22" width="6.57272727272727" customWidth="1"/>
+    <col min="23" max="23" width="37.1454545454545" customWidth="1"/>
+    <col min="24" max="25" width="8" customWidth="1"/>
+    <col min="26" max="26" width="7.71818181818182" customWidth="1"/>
+    <col min="27" max="27" width="6.28181818181818" customWidth="1"/>
+    <col min="28" max="28" width="9.28181818181818" customWidth="1"/>
+    <col min="29" max="29" width="9.71818181818182" customWidth="1"/>
+    <col min="30" max="30" width="12.8545454545455" customWidth="1"/>
+    <col min="31" max="31" width="16.1454545454545" customWidth="1"/>
+    <col min="32" max="32" width="15.4272727272727" customWidth="1"/>
+    <col min="33" max="33" width="24.5727272727273" customWidth="1"/>
+    <col min="34" max="34" width="8.57272727272727" customWidth="1"/>
+    <col min="35" max="35" width="14.7181818181818" customWidth="1"/>
+    <col min="36" max="36" width="18.5727272727273" customWidth="1"/>
+    <col min="37" max="37" width="14.1454545454545" customWidth="1"/>
+    <col min="38" max="38" width="14.7181818181818" customWidth="1"/>
+    <col min="39" max="39" width="17.4272727272727" customWidth="1"/>
+    <col min="40" max="40" width="22" customWidth="1"/>
+    <col min="41" max="41" width="17.5727272727273" customWidth="1"/>
+    <col min="42" max="42" width="25.2818181818182" customWidth="1"/>
+    <col min="43" max="43" width="13" customWidth="1"/>
+    <col min="44" max="44" width="23.7181818181818" customWidth="1"/>
+    <col min="45" max="45" width="10" customWidth="1"/>
+    <col min="46" max="46" width="13" customWidth="1"/>
+    <col min="47" max="47" width="15.5727272727273" customWidth="1"/>
+    <col min="48" max="48" width="21.1454545454545" customWidth="1"/>
+    <col min="49" max="49" width="11.5727272727273" customWidth="1"/>
+    <col min="50" max="50" width="16.7181818181818" customWidth="1"/>
+    <col min="51" max="51" width="14" customWidth="1"/>
+    <col min="52" max="52" width="19.4272727272727" customWidth="1"/>
+    <col min="53" max="53" width="18.8545454545455" customWidth="1"/>
+    <col min="54" max="54" width="23.2818181818182" customWidth="1"/>
+    <col min="55" max="55" width="15.5727272727273" customWidth="1"/>
+    <col min="56" max="56" width="14.2818181818182" customWidth="1"/>
+    <col min="57" max="57" width="17" customWidth="1"/>
+    <col min="58" max="58" width="16.2818181818182" customWidth="1"/>
+    <col min="59" max="59" width="13.5727272727273" customWidth="1"/>
+    <col min="60" max="61" width="12.7181818181818" customWidth="1"/>
+    <col min="62" max="62" width="21.8545454545455" customWidth="1"/>
+    <col min="63" max="63" width="30.5727272727273" customWidth="1"/>
+    <col min="64" max="64" width="10" customWidth="1"/>
+    <col min="65" max="65" width="42.5727272727273" customWidth="1"/>
+    <col min="66" max="66" width="38.1454545454545" customWidth="1"/>
+    <col min="67" max="67" width="19.4272727272727" customWidth="1"/>
+    <col min="68" max="68" width="35.4272727272727" customWidth="1"/>
+    <col min="69" max="69" width="9.57272727272727" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -5706,7 +5179,7 @@
       <c r="BP2" s="27"/>
       <c r="BQ2" s="27"/>
     </row>
-    <row r="3" ht="15.75" spans="1:69">
+    <row r="3" ht="15.25" spans="1:69">
       <c r="A3" s="28" t="s">
         <v>9</v>
       </c>
@@ -5915,7 +5388,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.75" spans="1:69">
+    <row r="4" ht="15.25" spans="1:69">
       <c r="A4" s="26">
         <v>1</v>
       </c>
@@ -6268,73 +5741,73 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ5"/>
-  <sheetFormatPr defaultColWidth="8.7047619047619" defaultRowHeight="15" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="5.14285714285714"/>
-    <col min="2" max="3" customWidth="true" width="22.0"/>
-    <col min="4" max="4" customWidth="true" width="79.4285714285714"/>
-    <col min="5" max="5" customWidth="true" width="11.5714285714286"/>
-    <col min="6" max="6" customWidth="true" width="5.14285714285714"/>
-    <col min="7" max="7" customWidth="true" width="11.0"/>
-    <col min="8" max="8" customWidth="true" width="12.7142857142857"/>
-    <col min="9" max="9" customWidth="true" width="5.85714285714286"/>
-    <col min="10" max="10" customWidth="true" width="6.0"/>
-    <col min="11" max="11" customWidth="true" width="5.85714285714286"/>
-    <col min="12" max="12" customWidth="true" width="14.2857142857143"/>
-    <col min="13" max="13" customWidth="true" width="9.42857142857143"/>
-    <col min="14" max="14" customWidth="true" width="14.4285714285714"/>
-    <col min="15" max="15" customWidth="true" width="15.5714285714286"/>
-    <col min="16" max="16" customWidth="true" width="14.4285714285714"/>
-    <col min="17" max="17" customWidth="true" width="39.4285714285714"/>
-    <col min="18" max="18" customWidth="true" width="11.7142857142857"/>
-    <col min="19" max="19" customWidth="true" width="11.8571428571429"/>
-    <col min="20" max="20" customWidth="true" width="6.42857142857143"/>
-    <col min="21" max="22" customWidth="true" width="6.57142857142857"/>
-    <col min="23" max="23" customWidth="true" width="37.1428571428571"/>
-    <col min="24" max="25" customWidth="true" width="8.0"/>
-    <col min="26" max="26" customWidth="true" width="7.71428571428571"/>
-    <col min="27" max="27" customWidth="true" width="6.28571428571429"/>
-    <col min="28" max="28" customWidth="true" width="9.28571428571429"/>
-    <col min="29" max="29" customWidth="true" width="9.71428571428571"/>
-    <col min="30" max="30" customWidth="true" width="12.8571428571429"/>
-    <col min="31" max="31" customWidth="true" width="16.1428571428571"/>
-    <col min="32" max="32" customWidth="true" width="15.4285714285714"/>
-    <col min="33" max="33" customWidth="true" width="24.5714285714286"/>
-    <col min="34" max="34" customWidth="true" width="8.57142857142857"/>
-    <col min="35" max="35" customWidth="true" width="14.7142857142857"/>
-    <col min="36" max="36" customWidth="true" width="18.5714285714286"/>
-    <col min="37" max="37" customWidth="true" width="14.1428571428571"/>
-    <col min="38" max="38" customWidth="true" width="14.7142857142857"/>
-    <col min="39" max="39" customWidth="true" width="17.4285714285714"/>
-    <col min="40" max="40" customWidth="true" width="22.0"/>
-    <col min="41" max="41" customWidth="true" width="17.5714285714286"/>
-    <col min="42" max="42" customWidth="true" width="25.2857142857143"/>
-    <col min="43" max="43" customWidth="true" width="13.0"/>
-    <col min="44" max="44" customWidth="true" width="23.7142857142857"/>
-    <col min="45" max="45" customWidth="true" width="10.0"/>
-    <col min="46" max="46" customWidth="true" width="13.0"/>
-    <col min="47" max="47" customWidth="true" width="15.5714285714286"/>
-    <col min="48" max="48" customWidth="true" width="21.1428571428571"/>
-    <col min="49" max="49" customWidth="true" width="11.5714285714286"/>
-    <col min="50" max="50" customWidth="true" width="16.7142857142857"/>
-    <col min="51" max="51" customWidth="true" width="14.0"/>
-    <col min="52" max="52" customWidth="true" width="19.4285714285714"/>
-    <col min="53" max="53" customWidth="true" width="18.8571428571429"/>
-    <col min="54" max="54" customWidth="true" width="23.2857142857143"/>
-    <col min="55" max="55" customWidth="true" width="15.5714285714286"/>
-    <col min="56" max="56" customWidth="true" width="14.2857142857143"/>
-    <col min="57" max="57" customWidth="true" width="17.0"/>
-    <col min="58" max="58" customWidth="true" width="16.2857142857143"/>
-    <col min="59" max="59" customWidth="true" width="13.5714285714286"/>
-    <col min="60" max="61" customWidth="true" width="12.7142857142857"/>
-    <col min="62" max="62" customWidth="true" width="21.8571428571429"/>
-    <col min="63" max="63" customWidth="true" width="30.5714285714286"/>
-    <col min="64" max="64" customWidth="true" width="10.0"/>
-    <col min="65" max="65" customWidth="true" width="42.5714285714286"/>
-    <col min="66" max="66" customWidth="true" width="38.1428571428571"/>
-    <col min="67" max="67" customWidth="true" width="19.4285714285714"/>
-    <col min="68" max="68" customWidth="true" width="35.4285714285714"/>
-    <col min="69" max="69" customWidth="true" width="9.57142857142857"/>
+    <col min="1" max="1" width="5.14545454545455" customWidth="1"/>
+    <col min="2" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="79.4272727272727" customWidth="1"/>
+    <col min="5" max="5" width="11.5727272727273" customWidth="1"/>
+    <col min="6" max="6" width="5.14545454545455" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="12.7181818181818" customWidth="1"/>
+    <col min="9" max="9" width="5.85454545454545" customWidth="1"/>
+    <col min="10" max="10" width="6" customWidth="1"/>
+    <col min="11" max="11" width="5.85454545454545" customWidth="1"/>
+    <col min="12" max="12" width="14.2818181818182" customWidth="1"/>
+    <col min="13" max="13" width="9.42727272727273" customWidth="1"/>
+    <col min="14" max="14" width="14.4272727272727" customWidth="1"/>
+    <col min="15" max="15" width="15.5727272727273" customWidth="1"/>
+    <col min="16" max="16" width="14.4272727272727" customWidth="1"/>
+    <col min="17" max="17" width="39.4272727272727" customWidth="1"/>
+    <col min="18" max="18" width="11.7181818181818" customWidth="1"/>
+    <col min="19" max="19" width="11.8545454545455" customWidth="1"/>
+    <col min="20" max="20" width="6.42727272727273" customWidth="1"/>
+    <col min="21" max="22" width="6.57272727272727" customWidth="1"/>
+    <col min="23" max="23" width="37.1454545454545" customWidth="1"/>
+    <col min="24" max="25" width="8" customWidth="1"/>
+    <col min="26" max="26" width="7.71818181818182" customWidth="1"/>
+    <col min="27" max="27" width="6.28181818181818" customWidth="1"/>
+    <col min="28" max="28" width="9.28181818181818" customWidth="1"/>
+    <col min="29" max="29" width="9.71818181818182" customWidth="1"/>
+    <col min="30" max="30" width="12.8545454545455" customWidth="1"/>
+    <col min="31" max="31" width="16.1454545454545" customWidth="1"/>
+    <col min="32" max="32" width="15.4272727272727" customWidth="1"/>
+    <col min="33" max="33" width="24.5727272727273" customWidth="1"/>
+    <col min="34" max="34" width="8.57272727272727" customWidth="1"/>
+    <col min="35" max="35" width="14.7181818181818" customWidth="1"/>
+    <col min="36" max="36" width="18.5727272727273" customWidth="1"/>
+    <col min="37" max="37" width="14.1454545454545" customWidth="1"/>
+    <col min="38" max="38" width="14.7181818181818" customWidth="1"/>
+    <col min="39" max="39" width="17.4272727272727" customWidth="1"/>
+    <col min="40" max="40" width="22" customWidth="1"/>
+    <col min="41" max="41" width="17.5727272727273" customWidth="1"/>
+    <col min="42" max="42" width="25.2818181818182" customWidth="1"/>
+    <col min="43" max="43" width="13" customWidth="1"/>
+    <col min="44" max="44" width="23.7181818181818" customWidth="1"/>
+    <col min="45" max="45" width="10" customWidth="1"/>
+    <col min="46" max="46" width="13" customWidth="1"/>
+    <col min="47" max="47" width="15.5727272727273" customWidth="1"/>
+    <col min="48" max="48" width="21.1454545454545" customWidth="1"/>
+    <col min="49" max="49" width="11.5727272727273" customWidth="1"/>
+    <col min="50" max="50" width="16.7181818181818" customWidth="1"/>
+    <col min="51" max="51" width="14" customWidth="1"/>
+    <col min="52" max="52" width="19.4272727272727" customWidth="1"/>
+    <col min="53" max="53" width="18.8545454545455" customWidth="1"/>
+    <col min="54" max="54" width="23.2818181818182" customWidth="1"/>
+    <col min="55" max="55" width="15.5727272727273" customWidth="1"/>
+    <col min="56" max="56" width="14.2818181818182" customWidth="1"/>
+    <col min="57" max="57" width="17" customWidth="1"/>
+    <col min="58" max="58" width="16.2818181818182" customWidth="1"/>
+    <col min="59" max="59" width="13.5727272727273" customWidth="1"/>
+    <col min="60" max="61" width="12.7181818181818" customWidth="1"/>
+    <col min="62" max="62" width="21.8545454545455" customWidth="1"/>
+    <col min="63" max="63" width="30.5727272727273" customWidth="1"/>
+    <col min="64" max="64" width="10" customWidth="1"/>
+    <col min="65" max="65" width="42.5727272727273" customWidth="1"/>
+    <col min="66" max="66" width="38.1454545454545" customWidth="1"/>
+    <col min="67" max="67" width="19.4272727272727" customWidth="1"/>
+    <col min="68" max="68" width="35.4272727272727" customWidth="1"/>
+    <col min="69" max="69" width="9.57272727272727" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -6505,7 +5978,7 @@
       <c r="BP2" s="27"/>
       <c r="BQ2" s="27"/>
     </row>
-    <row r="3" ht="15.75" spans="1:69">
+    <row r="3" ht="15.25" spans="1:69">
       <c r="A3" s="28" t="s">
         <v>9</v>
       </c>
@@ -6714,7 +6187,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.75" spans="1:69">
+    <row r="4" ht="15.25" spans="1:69">
       <c r="A4" s="26">
         <v>1</v>
       </c>
@@ -6878,8 +6351,6 @@
       <c r="AT4" s="35" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" s="0"/>
-      <c r="AV4" s="0"/>
       <c r="AW4" s="35">
         <f>AM4</f>
         <v>4</v>
@@ -6918,10 +6389,10 @@
       <c r="BL4" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="BM4" t="s" s="0">
+      <c r="BM4" t="s">
         <v>100</v>
       </c>
-      <c r="BN4" t="s" s="0">
+      <c r="BN4" t="s">
         <v>100</v>
       </c>
       <c r="BO4" s="35">
@@ -7067,73 +6538,73 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ5"/>
-  <sheetFormatPr defaultColWidth="8.7047619047619" defaultRowHeight="15" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="5.14285714285714"/>
-    <col min="2" max="3" customWidth="true" width="22.0"/>
-    <col min="4" max="4" customWidth="true" width="79.4285714285714"/>
-    <col min="5" max="5" customWidth="true" width="11.5714285714286"/>
-    <col min="6" max="6" customWidth="true" width="5.14285714285714"/>
-    <col min="7" max="7" customWidth="true" width="11.0"/>
-    <col min="8" max="8" customWidth="true" width="12.7142857142857"/>
-    <col min="9" max="9" customWidth="true" width="5.85714285714286"/>
-    <col min="10" max="10" customWidth="true" width="6.0"/>
-    <col min="11" max="11" customWidth="true" width="5.85714285714286"/>
-    <col min="12" max="12" customWidth="true" width="14.2857142857143"/>
-    <col min="13" max="13" customWidth="true" width="9.42857142857143"/>
-    <col min="14" max="14" customWidth="true" width="14.4285714285714"/>
-    <col min="15" max="15" customWidth="true" width="15.5714285714286"/>
-    <col min="16" max="16" customWidth="true" width="14.4285714285714"/>
-    <col min="17" max="17" customWidth="true" width="39.4285714285714"/>
-    <col min="18" max="18" customWidth="true" width="11.7142857142857"/>
-    <col min="19" max="19" customWidth="true" width="11.8571428571429"/>
-    <col min="20" max="20" customWidth="true" width="6.42857142857143"/>
-    <col min="21" max="22" customWidth="true" width="6.57142857142857"/>
-    <col min="23" max="23" customWidth="true" width="37.1428571428571"/>
-    <col min="24" max="25" customWidth="true" width="8.0"/>
-    <col min="26" max="26" customWidth="true" width="7.71428571428571"/>
-    <col min="27" max="27" customWidth="true" width="6.28571428571429"/>
-    <col min="28" max="28" customWidth="true" width="9.28571428571429"/>
-    <col min="29" max="29" customWidth="true" width="9.71428571428571"/>
-    <col min="30" max="30" customWidth="true" width="12.8571428571429"/>
-    <col min="31" max="31" customWidth="true" width="16.1428571428571"/>
-    <col min="32" max="32" customWidth="true" width="15.4285714285714"/>
-    <col min="33" max="33" customWidth="true" width="24.5714285714286"/>
-    <col min="34" max="34" customWidth="true" width="8.57142857142857"/>
-    <col min="35" max="35" customWidth="true" width="14.7142857142857"/>
-    <col min="36" max="36" customWidth="true" width="18.5714285714286"/>
-    <col min="37" max="37" customWidth="true" width="14.1428571428571"/>
-    <col min="38" max="38" customWidth="true" width="14.7142857142857"/>
-    <col min="39" max="39" customWidth="true" width="17.4285714285714"/>
-    <col min="40" max="40" customWidth="true" width="22.0"/>
-    <col min="41" max="41" customWidth="true" width="17.5714285714286"/>
-    <col min="42" max="42" customWidth="true" width="25.2857142857143"/>
-    <col min="43" max="43" customWidth="true" width="13.0"/>
-    <col min="44" max="44" customWidth="true" width="23.7142857142857"/>
-    <col min="45" max="45" customWidth="true" width="10.0"/>
-    <col min="46" max="46" customWidth="true" width="13.0"/>
-    <col min="47" max="47" customWidth="true" width="15.5714285714286"/>
-    <col min="48" max="48" customWidth="true" width="21.1428571428571"/>
-    <col min="49" max="49" customWidth="true" width="11.5714285714286"/>
-    <col min="50" max="50" customWidth="true" width="16.7142857142857"/>
-    <col min="51" max="51" customWidth="true" width="14.0"/>
-    <col min="52" max="52" customWidth="true" width="19.4285714285714"/>
-    <col min="53" max="53" customWidth="true" width="18.8571428571429"/>
-    <col min="54" max="54" customWidth="true" width="23.2857142857143"/>
-    <col min="55" max="55" customWidth="true" width="15.5714285714286"/>
-    <col min="56" max="56" customWidth="true" width="14.2857142857143"/>
-    <col min="57" max="57" customWidth="true" width="17.0"/>
-    <col min="58" max="58" customWidth="true" width="16.2857142857143"/>
-    <col min="59" max="59" customWidth="true" width="13.5714285714286"/>
-    <col min="60" max="61" customWidth="true" width="12.7142857142857"/>
-    <col min="62" max="62" customWidth="true" width="21.8571428571429"/>
-    <col min="63" max="63" customWidth="true" width="30.5714285714286"/>
-    <col min="64" max="64" customWidth="true" width="10.0"/>
-    <col min="65" max="65" customWidth="true" width="42.5714285714286"/>
-    <col min="66" max="66" customWidth="true" width="38.1428571428571"/>
-    <col min="67" max="67" customWidth="true" width="19.4285714285714"/>
-    <col min="68" max="68" customWidth="true" width="35.4285714285714"/>
-    <col min="69" max="69" customWidth="true" width="9.57142857142857"/>
+    <col min="1" max="1" width="5.14545454545455" customWidth="1"/>
+    <col min="2" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="79.4272727272727" customWidth="1"/>
+    <col min="5" max="5" width="11.5727272727273" customWidth="1"/>
+    <col min="6" max="6" width="5.14545454545455" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="12.7181818181818" customWidth="1"/>
+    <col min="9" max="9" width="5.85454545454545" customWidth="1"/>
+    <col min="10" max="10" width="6" customWidth="1"/>
+    <col min="11" max="11" width="5.85454545454545" customWidth="1"/>
+    <col min="12" max="12" width="14.2818181818182" customWidth="1"/>
+    <col min="13" max="13" width="9.42727272727273" customWidth="1"/>
+    <col min="14" max="14" width="14.4272727272727" customWidth="1"/>
+    <col min="15" max="15" width="15.5727272727273" customWidth="1"/>
+    <col min="16" max="16" width="14.4272727272727" customWidth="1"/>
+    <col min="17" max="17" width="39.4272727272727" customWidth="1"/>
+    <col min="18" max="18" width="11.7181818181818" customWidth="1"/>
+    <col min="19" max="19" width="11.8545454545455" customWidth="1"/>
+    <col min="20" max="20" width="6.42727272727273" customWidth="1"/>
+    <col min="21" max="22" width="6.57272727272727" customWidth="1"/>
+    <col min="23" max="23" width="37.1454545454545" customWidth="1"/>
+    <col min="24" max="25" width="8" customWidth="1"/>
+    <col min="26" max="26" width="7.71818181818182" customWidth="1"/>
+    <col min="27" max="27" width="6.28181818181818" customWidth="1"/>
+    <col min="28" max="28" width="9.28181818181818" customWidth="1"/>
+    <col min="29" max="29" width="9.71818181818182" customWidth="1"/>
+    <col min="30" max="30" width="12.8545454545455" customWidth="1"/>
+    <col min="31" max="31" width="16.1454545454545" customWidth="1"/>
+    <col min="32" max="32" width="15.4272727272727" customWidth="1"/>
+    <col min="33" max="33" width="24.5727272727273" customWidth="1"/>
+    <col min="34" max="34" width="8.57272727272727" customWidth="1"/>
+    <col min="35" max="35" width="14.7181818181818" customWidth="1"/>
+    <col min="36" max="36" width="18.5727272727273" customWidth="1"/>
+    <col min="37" max="37" width="14.1454545454545" customWidth="1"/>
+    <col min="38" max="38" width="14.7181818181818" customWidth="1"/>
+    <col min="39" max="39" width="17.4272727272727" customWidth="1"/>
+    <col min="40" max="40" width="22" customWidth="1"/>
+    <col min="41" max="41" width="17.5727272727273" customWidth="1"/>
+    <col min="42" max="42" width="25.2818181818182" customWidth="1"/>
+    <col min="43" max="43" width="13" customWidth="1"/>
+    <col min="44" max="44" width="23.7181818181818" customWidth="1"/>
+    <col min="45" max="45" width="10" customWidth="1"/>
+    <col min="46" max="46" width="13" customWidth="1"/>
+    <col min="47" max="47" width="15.5727272727273" customWidth="1"/>
+    <col min="48" max="48" width="21.1454545454545" customWidth="1"/>
+    <col min="49" max="49" width="11.5727272727273" customWidth="1"/>
+    <col min="50" max="50" width="16.7181818181818" customWidth="1"/>
+    <col min="51" max="51" width="14" customWidth="1"/>
+    <col min="52" max="52" width="19.4272727272727" customWidth="1"/>
+    <col min="53" max="53" width="18.8545454545455" customWidth="1"/>
+    <col min="54" max="54" width="23.2818181818182" customWidth="1"/>
+    <col min="55" max="55" width="15.5727272727273" customWidth="1"/>
+    <col min="56" max="56" width="14.2818181818182" customWidth="1"/>
+    <col min="57" max="57" width="17" customWidth="1"/>
+    <col min="58" max="58" width="16.2818181818182" customWidth="1"/>
+    <col min="59" max="59" width="13.5727272727273" customWidth="1"/>
+    <col min="60" max="61" width="12.7181818181818" customWidth="1"/>
+    <col min="62" max="62" width="21.8545454545455" customWidth="1"/>
+    <col min="63" max="63" width="30.5727272727273" customWidth="1"/>
+    <col min="64" max="64" width="10" customWidth="1"/>
+    <col min="65" max="65" width="42.5727272727273" customWidth="1"/>
+    <col min="66" max="66" width="38.1454545454545" customWidth="1"/>
+    <col min="67" max="67" width="19.4272727272727" customWidth="1"/>
+    <col min="68" max="68" width="35.4272727272727" customWidth="1"/>
+    <col min="69" max="69" width="9.57272727272727" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -7304,7 +6775,7 @@
       <c r="BP2" s="27"/>
       <c r="BQ2" s="27"/>
     </row>
-    <row r="3" ht="15.75" spans="1:69">
+    <row r="3" ht="15.25" spans="1:69">
       <c r="A3" s="28" t="s">
         <v>9</v>
       </c>
@@ -7513,7 +6984,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.75" spans="1:69">
+    <row r="4" ht="15.25" spans="1:69">
       <c r="A4" s="26">
         <v>1</v>
       </c>
@@ -7677,8 +7148,6 @@
       <c r="AT4" s="35" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" s="0"/>
-      <c r="AV4" s="0"/>
       <c r="AW4" s="35">
         <f>AM4</f>
         <v>4</v>
@@ -7717,10 +7186,10 @@
       <c r="BL4" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="BM4" t="s" s="0">
+      <c r="BM4" t="s">
         <v>100</v>
       </c>
-      <c r="BN4" t="s" s="0">
+      <c r="BN4" t="s">
         <v>100</v>
       </c>
       <c r="BO4" s="35">
@@ -7866,73 +7335,73 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ5"/>
-  <sheetFormatPr defaultColWidth="8.7047619047619" defaultRowHeight="15" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="5.14285714285714"/>
-    <col min="2" max="3" customWidth="true" width="24.5714285714286"/>
-    <col min="4" max="4" customWidth="true" width="79.4285714285714"/>
-    <col min="5" max="5" customWidth="true" width="11.5714285714286"/>
-    <col min="6" max="6" customWidth="true" width="5.14285714285714"/>
-    <col min="7" max="7" customWidth="true" width="11.0"/>
-    <col min="8" max="8" customWidth="true" width="12.7142857142857"/>
-    <col min="9" max="9" customWidth="true" width="5.85714285714286"/>
-    <col min="10" max="10" customWidth="true" width="6.0"/>
-    <col min="11" max="11" customWidth="true" width="5.85714285714286"/>
-    <col min="12" max="12" customWidth="true" width="14.2857142857143"/>
-    <col min="13" max="13" customWidth="true" width="9.42857142857143"/>
-    <col min="14" max="14" customWidth="true" width="14.4285714285714"/>
-    <col min="15" max="15" customWidth="true" width="15.5714285714286"/>
-    <col min="16" max="16" customWidth="true" width="14.4285714285714"/>
-    <col min="17" max="17" customWidth="true" width="39.4285714285714"/>
-    <col min="18" max="18" customWidth="true" width="11.7142857142857"/>
-    <col min="19" max="19" customWidth="true" width="11.8571428571429"/>
-    <col min="20" max="20" customWidth="true" width="6.42857142857143"/>
-    <col min="21" max="22" customWidth="true" width="6.57142857142857"/>
-    <col min="23" max="23" customWidth="true" width="37.1428571428571"/>
-    <col min="24" max="25" customWidth="true" width="8.0"/>
-    <col min="26" max="26" customWidth="true" width="7.71428571428571"/>
-    <col min="27" max="27" customWidth="true" width="6.28571428571429"/>
-    <col min="28" max="28" customWidth="true" width="9.28571428571429"/>
-    <col min="29" max="29" customWidth="true" width="9.71428571428571"/>
-    <col min="30" max="30" customWidth="true" width="12.8571428571429"/>
-    <col min="31" max="31" customWidth="true" width="16.1428571428571"/>
-    <col min="32" max="32" customWidth="true" width="15.4285714285714"/>
-    <col min="33" max="33" customWidth="true" width="24.5714285714286"/>
-    <col min="34" max="34" customWidth="true" width="8.57142857142857"/>
-    <col min="35" max="35" customWidth="true" width="14.7142857142857"/>
-    <col min="36" max="36" customWidth="true" width="18.5714285714286"/>
-    <col min="37" max="37" customWidth="true" width="14.1428571428571"/>
-    <col min="38" max="38" customWidth="true" width="14.7142857142857"/>
-    <col min="39" max="39" customWidth="true" width="17.4285714285714"/>
-    <col min="40" max="40" customWidth="true" width="22.0"/>
-    <col min="41" max="41" customWidth="true" width="17.5714285714286"/>
-    <col min="42" max="42" customWidth="true" width="25.2857142857143"/>
-    <col min="43" max="43" customWidth="true" width="13.0"/>
-    <col min="44" max="44" customWidth="true" width="23.7142857142857"/>
-    <col min="45" max="45" customWidth="true" width="10.0"/>
-    <col min="46" max="46" customWidth="true" width="13.0"/>
-    <col min="47" max="47" customWidth="true" width="15.5714285714286"/>
-    <col min="48" max="48" customWidth="true" width="21.1428571428571"/>
-    <col min="49" max="49" customWidth="true" width="11.5714285714286"/>
-    <col min="50" max="50" customWidth="true" width="16.7142857142857"/>
-    <col min="51" max="51" customWidth="true" width="14.0"/>
-    <col min="52" max="52" customWidth="true" width="19.4285714285714"/>
-    <col min="53" max="53" customWidth="true" width="18.8571428571429"/>
-    <col min="54" max="54" customWidth="true" width="23.2857142857143"/>
-    <col min="55" max="55" customWidth="true" width="15.5714285714286"/>
-    <col min="56" max="56" customWidth="true" width="14.2857142857143"/>
-    <col min="57" max="57" customWidth="true" width="17.0"/>
-    <col min="58" max="58" customWidth="true" width="16.2857142857143"/>
-    <col min="59" max="59" customWidth="true" width="13.5714285714286"/>
-    <col min="60" max="61" customWidth="true" width="12.7142857142857"/>
-    <col min="62" max="62" customWidth="true" width="21.8571428571429"/>
-    <col min="63" max="63" customWidth="true" width="30.5714285714286"/>
-    <col min="64" max="64" customWidth="true" width="10.0"/>
-    <col min="65" max="65" customWidth="true" width="42.5714285714286"/>
-    <col min="66" max="66" customWidth="true" width="38.1428571428571"/>
-    <col min="67" max="67" customWidth="true" width="19.4285714285714"/>
-    <col min="68" max="68" customWidth="true" width="35.4285714285714"/>
-    <col min="69" max="69" customWidth="true" width="9.57142857142857"/>
+    <col min="1" max="1" width="5.14545454545455" customWidth="1"/>
+    <col min="2" max="3" width="24.5727272727273" customWidth="1"/>
+    <col min="4" max="4" width="79.4272727272727" customWidth="1"/>
+    <col min="5" max="5" width="11.5727272727273" customWidth="1"/>
+    <col min="6" max="6" width="5.14545454545455" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="12.7181818181818" customWidth="1"/>
+    <col min="9" max="9" width="5.85454545454545" customWidth="1"/>
+    <col min="10" max="10" width="6" customWidth="1"/>
+    <col min="11" max="11" width="5.85454545454545" customWidth="1"/>
+    <col min="12" max="12" width="14.2818181818182" customWidth="1"/>
+    <col min="13" max="13" width="9.42727272727273" customWidth="1"/>
+    <col min="14" max="14" width="14.4272727272727" customWidth="1"/>
+    <col min="15" max="15" width="15.5727272727273" customWidth="1"/>
+    <col min="16" max="16" width="14.4272727272727" customWidth="1"/>
+    <col min="17" max="17" width="39.4272727272727" customWidth="1"/>
+    <col min="18" max="18" width="11.7181818181818" customWidth="1"/>
+    <col min="19" max="19" width="11.8545454545455" customWidth="1"/>
+    <col min="20" max="20" width="6.42727272727273" customWidth="1"/>
+    <col min="21" max="22" width="6.57272727272727" customWidth="1"/>
+    <col min="23" max="23" width="37.1454545454545" customWidth="1"/>
+    <col min="24" max="25" width="8" customWidth="1"/>
+    <col min="26" max="26" width="7.71818181818182" customWidth="1"/>
+    <col min="27" max="27" width="6.28181818181818" customWidth="1"/>
+    <col min="28" max="28" width="9.28181818181818" customWidth="1"/>
+    <col min="29" max="29" width="9.71818181818182" customWidth="1"/>
+    <col min="30" max="30" width="12.8545454545455" customWidth="1"/>
+    <col min="31" max="31" width="16.1454545454545" customWidth="1"/>
+    <col min="32" max="32" width="15.4272727272727" customWidth="1"/>
+    <col min="33" max="33" width="24.5727272727273" customWidth="1"/>
+    <col min="34" max="34" width="8.57272727272727" customWidth="1"/>
+    <col min="35" max="35" width="14.7181818181818" customWidth="1"/>
+    <col min="36" max="36" width="18.5727272727273" customWidth="1"/>
+    <col min="37" max="37" width="14.1454545454545" customWidth="1"/>
+    <col min="38" max="38" width="14.7181818181818" customWidth="1"/>
+    <col min="39" max="39" width="17.4272727272727" customWidth="1"/>
+    <col min="40" max="40" width="22" customWidth="1"/>
+    <col min="41" max="41" width="17.5727272727273" customWidth="1"/>
+    <col min="42" max="42" width="25.2818181818182" customWidth="1"/>
+    <col min="43" max="43" width="13" customWidth="1"/>
+    <col min="44" max="44" width="23.7181818181818" customWidth="1"/>
+    <col min="45" max="45" width="10" customWidth="1"/>
+    <col min="46" max="46" width="13" customWidth="1"/>
+    <col min="47" max="47" width="15.5727272727273" customWidth="1"/>
+    <col min="48" max="48" width="21.1454545454545" customWidth="1"/>
+    <col min="49" max="49" width="11.5727272727273" customWidth="1"/>
+    <col min="50" max="50" width="16.7181818181818" customWidth="1"/>
+    <col min="51" max="51" width="14" customWidth="1"/>
+    <col min="52" max="52" width="19.4272727272727" customWidth="1"/>
+    <col min="53" max="53" width="18.8545454545455" customWidth="1"/>
+    <col min="54" max="54" width="23.2818181818182" customWidth="1"/>
+    <col min="55" max="55" width="15.5727272727273" customWidth="1"/>
+    <col min="56" max="56" width="14.2818181818182" customWidth="1"/>
+    <col min="57" max="57" width="17" customWidth="1"/>
+    <col min="58" max="58" width="16.2818181818182" customWidth="1"/>
+    <col min="59" max="59" width="13.5727272727273" customWidth="1"/>
+    <col min="60" max="61" width="12.7181818181818" customWidth="1"/>
+    <col min="62" max="62" width="21.8545454545455" customWidth="1"/>
+    <col min="63" max="63" width="30.5727272727273" customWidth="1"/>
+    <col min="64" max="64" width="10" customWidth="1"/>
+    <col min="65" max="65" width="42.5727272727273" customWidth="1"/>
+    <col min="66" max="66" width="38.1454545454545" customWidth="1"/>
+    <col min="67" max="67" width="19.4272727272727" customWidth="1"/>
+    <col min="68" max="68" width="35.4272727272727" customWidth="1"/>
+    <col min="69" max="69" width="9.57272727272727" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -8103,7 +7572,7 @@
       <c r="BP2" s="27"/>
       <c r="BQ2" s="27"/>
     </row>
-    <row r="3" ht="15.75" spans="1:69">
+    <row r="3" ht="15.25" spans="1:69">
       <c r="A3" s="28" t="s">
         <v>9</v>
       </c>
@@ -8312,7 +7781,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.75" spans="1:69">
+    <row r="4" ht="15.25" spans="1:69">
       <c r="A4" s="26">
         <v>1</v>
       </c>
@@ -8476,11 +7945,11 @@
       <c r="AT4" s="35" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" t="s" s="0">
-        <v>232</v>
-      </c>
-      <c r="AV4" t="s" s="0">
-        <v>277</v>
+      <c r="AU4" t="s">
+        <v>131</v>
+      </c>
+      <c r="AV4" t="s">
+        <v>132</v>
       </c>
       <c r="AW4" s="35">
         <f>AM4</f>
@@ -8494,8 +7963,8 @@
         <f>AU4+AW4</f>
         <v>32.6603333333333</v>
       </c>
-      <c r="AZ4" t="s" s="0">
-        <v>277</v>
+      <c r="AZ4" t="s">
+        <v>132</v>
       </c>
       <c r="BA4" s="36"/>
       <c r="BB4" s="36" t="s">
@@ -8519,11 +7988,11 @@
       <c r="BL4" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="BM4" t="s" s="0">
-        <v>332</v>
-      </c>
-      <c r="BN4" t="s" s="0">
-        <v>331</v>
+      <c r="BM4" t="s">
+        <v>133</v>
+      </c>
+      <c r="BN4" t="s">
+        <v>134</v>
       </c>
       <c r="BO4" s="35">
         <f>ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
@@ -8680,73 +8149,73 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ5"/>
-  <sheetFormatPr defaultColWidth="8.7047619047619" defaultRowHeight="15" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="5.14285714285714"/>
-    <col min="2" max="3" customWidth="true" width="24.5714285714286"/>
-    <col min="4" max="4" customWidth="true" width="79.4285714285714"/>
-    <col min="5" max="5" customWidth="true" width="11.5714285714286"/>
-    <col min="6" max="6" customWidth="true" width="5.14285714285714"/>
-    <col min="7" max="7" customWidth="true" width="11.0"/>
-    <col min="8" max="8" customWidth="true" width="12.7142857142857"/>
-    <col min="9" max="9" customWidth="true" width="5.85714285714286"/>
-    <col min="10" max="10" customWidth="true" width="6.0"/>
-    <col min="11" max="11" customWidth="true" width="5.85714285714286"/>
-    <col min="12" max="12" customWidth="true" width="14.2857142857143"/>
-    <col min="13" max="13" customWidth="true" width="9.42857142857143"/>
-    <col min="14" max="14" customWidth="true" width="14.4285714285714"/>
-    <col min="15" max="15" customWidth="true" width="15.5714285714286"/>
-    <col min="16" max="16" customWidth="true" width="14.4285714285714"/>
-    <col min="17" max="17" customWidth="true" width="39.4285714285714"/>
-    <col min="18" max="18" customWidth="true" width="11.7142857142857"/>
-    <col min="19" max="19" customWidth="true" width="11.8571428571429"/>
-    <col min="20" max="20" customWidth="true" width="6.42857142857143"/>
-    <col min="21" max="22" customWidth="true" width="6.57142857142857"/>
-    <col min="23" max="23" customWidth="true" width="37.1428571428571"/>
-    <col min="24" max="25" customWidth="true" width="8.0"/>
-    <col min="26" max="26" customWidth="true" width="7.71428571428571"/>
-    <col min="27" max="27" customWidth="true" width="6.28571428571429"/>
-    <col min="28" max="28" customWidth="true" width="9.28571428571429"/>
-    <col min="29" max="29" customWidth="true" width="9.71428571428571"/>
-    <col min="30" max="30" customWidth="true" width="12.8571428571429"/>
-    <col min="31" max="31" customWidth="true" width="16.1428571428571"/>
-    <col min="32" max="32" customWidth="true" width="15.4285714285714"/>
-    <col min="33" max="33" customWidth="true" width="24.5714285714286"/>
-    <col min="34" max="34" customWidth="true" width="8.57142857142857"/>
-    <col min="35" max="35" customWidth="true" width="14.7142857142857"/>
-    <col min="36" max="36" customWidth="true" width="18.5714285714286"/>
-    <col min="37" max="37" customWidth="true" width="14.1428571428571"/>
-    <col min="38" max="38" customWidth="true" width="14.7142857142857"/>
-    <col min="39" max="39" customWidth="true" width="17.4285714285714"/>
-    <col min="40" max="40" customWidth="true" width="22.0"/>
-    <col min="41" max="41" customWidth="true" width="17.5714285714286"/>
-    <col min="42" max="42" customWidth="true" width="25.2857142857143"/>
-    <col min="43" max="43" customWidth="true" width="13.0"/>
-    <col min="44" max="44" customWidth="true" width="23.7142857142857"/>
-    <col min="45" max="45" customWidth="true" width="10.0"/>
-    <col min="46" max="46" customWidth="true" width="13.0"/>
-    <col min="47" max="47" customWidth="true" width="15.5714285714286"/>
-    <col min="48" max="48" customWidth="true" width="21.1428571428571"/>
-    <col min="49" max="49" customWidth="true" width="11.5714285714286"/>
-    <col min="50" max="50" customWidth="true" width="16.7142857142857"/>
-    <col min="51" max="51" customWidth="true" width="14.0"/>
-    <col min="52" max="52" customWidth="true" width="19.4285714285714"/>
-    <col min="53" max="53" customWidth="true" width="18.8571428571429"/>
-    <col min="54" max="54" customWidth="true" width="23.2857142857143"/>
-    <col min="55" max="55" customWidth="true" width="15.5714285714286"/>
-    <col min="56" max="56" customWidth="true" width="14.2857142857143"/>
-    <col min="57" max="57" customWidth="true" width="17.0"/>
-    <col min="58" max="58" customWidth="true" width="16.2857142857143"/>
-    <col min="59" max="59" customWidth="true" width="13.5714285714286"/>
-    <col min="60" max="61" customWidth="true" width="12.7142857142857"/>
-    <col min="62" max="62" customWidth="true" width="21.8571428571429"/>
-    <col min="63" max="63" customWidth="true" width="30.5714285714286"/>
-    <col min="64" max="64" customWidth="true" width="10.0"/>
-    <col min="65" max="65" customWidth="true" width="42.5714285714286"/>
-    <col min="66" max="66" customWidth="true" width="38.1428571428571"/>
-    <col min="67" max="67" customWidth="true" width="19.4285714285714"/>
-    <col min="68" max="68" customWidth="true" width="35.4285714285714"/>
-    <col min="69" max="69" customWidth="true" width="9.57142857142857"/>
+    <col min="1" max="1" width="5.14545454545455" customWidth="1"/>
+    <col min="2" max="3" width="24.5727272727273" customWidth="1"/>
+    <col min="4" max="4" width="79.4272727272727" customWidth="1"/>
+    <col min="5" max="5" width="11.5727272727273" customWidth="1"/>
+    <col min="6" max="6" width="5.14545454545455" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="12.7181818181818" customWidth="1"/>
+    <col min="9" max="9" width="5.85454545454545" customWidth="1"/>
+    <col min="10" max="10" width="6" customWidth="1"/>
+    <col min="11" max="11" width="5.85454545454545" customWidth="1"/>
+    <col min="12" max="12" width="14.2818181818182" customWidth="1"/>
+    <col min="13" max="13" width="9.42727272727273" customWidth="1"/>
+    <col min="14" max="14" width="14.4272727272727" customWidth="1"/>
+    <col min="15" max="15" width="15.5727272727273" customWidth="1"/>
+    <col min="16" max="16" width="14.4272727272727" customWidth="1"/>
+    <col min="17" max="17" width="39.4272727272727" customWidth="1"/>
+    <col min="18" max="18" width="11.7181818181818" customWidth="1"/>
+    <col min="19" max="19" width="11.8545454545455" customWidth="1"/>
+    <col min="20" max="20" width="6.42727272727273" customWidth="1"/>
+    <col min="21" max="22" width="6.57272727272727" customWidth="1"/>
+    <col min="23" max="23" width="37.1454545454545" customWidth="1"/>
+    <col min="24" max="25" width="8" customWidth="1"/>
+    <col min="26" max="26" width="7.71818181818182" customWidth="1"/>
+    <col min="27" max="27" width="6.28181818181818" customWidth="1"/>
+    <col min="28" max="28" width="9.28181818181818" customWidth="1"/>
+    <col min="29" max="29" width="9.71818181818182" customWidth="1"/>
+    <col min="30" max="30" width="12.8545454545455" customWidth="1"/>
+    <col min="31" max="31" width="16.1454545454545" customWidth="1"/>
+    <col min="32" max="32" width="15.4272727272727" customWidth="1"/>
+    <col min="33" max="33" width="24.5727272727273" customWidth="1"/>
+    <col min="34" max="34" width="8.57272727272727" customWidth="1"/>
+    <col min="35" max="35" width="14.7181818181818" customWidth="1"/>
+    <col min="36" max="36" width="18.5727272727273" customWidth="1"/>
+    <col min="37" max="37" width="14.1454545454545" customWidth="1"/>
+    <col min="38" max="38" width="14.7181818181818" customWidth="1"/>
+    <col min="39" max="39" width="17.4272727272727" customWidth="1"/>
+    <col min="40" max="40" width="22" customWidth="1"/>
+    <col min="41" max="41" width="17.5727272727273" customWidth="1"/>
+    <col min="42" max="42" width="25.2818181818182" customWidth="1"/>
+    <col min="43" max="43" width="13" customWidth="1"/>
+    <col min="44" max="44" width="23.7181818181818" customWidth="1"/>
+    <col min="45" max="45" width="10" customWidth="1"/>
+    <col min="46" max="46" width="13" customWidth="1"/>
+    <col min="47" max="47" width="15.5727272727273" customWidth="1"/>
+    <col min="48" max="48" width="21.1454545454545" customWidth="1"/>
+    <col min="49" max="49" width="11.5727272727273" customWidth="1"/>
+    <col min="50" max="50" width="16.7181818181818" customWidth="1"/>
+    <col min="51" max="51" width="14" customWidth="1"/>
+    <col min="52" max="52" width="19.4272727272727" customWidth="1"/>
+    <col min="53" max="53" width="18.8545454545455" customWidth="1"/>
+    <col min="54" max="54" width="23.2818181818182" customWidth="1"/>
+    <col min="55" max="55" width="15.5727272727273" customWidth="1"/>
+    <col min="56" max="56" width="14.2818181818182" customWidth="1"/>
+    <col min="57" max="57" width="17" customWidth="1"/>
+    <col min="58" max="58" width="16.2818181818182" customWidth="1"/>
+    <col min="59" max="59" width="13.5727272727273" customWidth="1"/>
+    <col min="60" max="61" width="12.7181818181818" customWidth="1"/>
+    <col min="62" max="62" width="21.8545454545455" customWidth="1"/>
+    <col min="63" max="63" width="30.5727272727273" customWidth="1"/>
+    <col min="64" max="64" width="10" customWidth="1"/>
+    <col min="65" max="65" width="42.5727272727273" customWidth="1"/>
+    <col min="66" max="66" width="38.1454545454545" customWidth="1"/>
+    <col min="67" max="67" width="19.4272727272727" customWidth="1"/>
+    <col min="68" max="68" width="35.4272727272727" customWidth="1"/>
+    <col min="69" max="69" width="9.57272727272727" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -8917,7 +8386,7 @@
       <c r="BP2" s="27"/>
       <c r="BQ2" s="27"/>
     </row>
-    <row r="3" ht="15.75" spans="1:69">
+    <row r="3" ht="15.25" spans="1:69">
       <c r="A3" s="28" t="s">
         <v>9</v>
       </c>
@@ -9126,7 +8595,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.75" spans="1:69">
+    <row r="4" ht="15.25" spans="1:69">
       <c r="A4" s="26">
         <v>1</v>
       </c>
@@ -9290,11 +8759,11 @@
       <c r="AT4" s="35" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" t="s" s="0">
-        <v>178</v>
-      </c>
-      <c r="AV4" t="s" s="0">
-        <v>280</v>
+      <c r="AU4" t="s">
+        <v>136</v>
+      </c>
+      <c r="AV4" t="s">
+        <v>137</v>
       </c>
       <c r="AW4" s="35">
         <f>AM4</f>
@@ -9308,8 +8777,8 @@
         <f>AU4+AW4</f>
         <v>83.3283333333333</v>
       </c>
-      <c r="AZ4" t="s" s="0">
-        <v>280</v>
+      <c r="AZ4" t="s">
+        <v>137</v>
       </c>
       <c r="BA4" s="36"/>
       <c r="BB4" s="36" t="s">
@@ -9333,11 +8802,11 @@
       <c r="BL4" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="BM4" t="s" s="0">
-        <v>334</v>
-      </c>
-      <c r="BN4" t="s" s="0">
-        <v>333</v>
+      <c r="BM4" t="s">
+        <v>138</v>
+      </c>
+      <c r="BN4" t="s">
+        <v>139</v>
       </c>
       <c r="BO4" s="35">
         <f>ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
@@ -9494,73 +8963,73 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ5"/>
-  <sheetFormatPr defaultColWidth="8.7047619047619" defaultRowHeight="15" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="5.14285714285714"/>
-    <col min="2" max="3" customWidth="true" width="22.0"/>
-    <col min="4" max="4" customWidth="true" width="79.4285714285714"/>
-    <col min="5" max="5" customWidth="true" width="11.5714285714286"/>
-    <col min="6" max="6" customWidth="true" width="5.14285714285714"/>
-    <col min="7" max="7" customWidth="true" width="11.0"/>
-    <col min="8" max="8" customWidth="true" width="12.7142857142857"/>
-    <col min="9" max="9" customWidth="true" width="5.85714285714286"/>
-    <col min="10" max="10" customWidth="true" width="6.0"/>
-    <col min="11" max="11" customWidth="true" width="5.85714285714286"/>
-    <col min="12" max="12" customWidth="true" width="14.2857142857143"/>
-    <col min="13" max="13" customWidth="true" width="9.42857142857143"/>
-    <col min="14" max="14" customWidth="true" width="14.4285714285714"/>
-    <col min="15" max="15" customWidth="true" width="15.5714285714286"/>
-    <col min="16" max="16" customWidth="true" width="14.4285714285714"/>
-    <col min="17" max="17" customWidth="true" width="39.4285714285714"/>
-    <col min="18" max="18" customWidth="true" width="11.7142857142857"/>
-    <col min="19" max="19" customWidth="true" width="11.8571428571429"/>
-    <col min="20" max="20" customWidth="true" width="6.42857142857143"/>
-    <col min="21" max="22" customWidth="true" width="6.57142857142857"/>
-    <col min="23" max="23" customWidth="true" width="37.1428571428571"/>
-    <col min="24" max="25" customWidth="true" width="8.0"/>
-    <col min="26" max="26" customWidth="true" width="7.71428571428571"/>
-    <col min="27" max="27" customWidth="true" width="6.28571428571429"/>
-    <col min="28" max="28" customWidth="true" width="9.28571428571429"/>
-    <col min="29" max="29" customWidth="true" width="9.71428571428571"/>
-    <col min="30" max="30" customWidth="true" width="12.8571428571429"/>
-    <col min="31" max="31" customWidth="true" width="16.1428571428571"/>
-    <col min="32" max="32" customWidth="true" width="15.4285714285714"/>
-    <col min="33" max="33" customWidth="true" width="24.5714285714286"/>
-    <col min="34" max="34" customWidth="true" width="8.57142857142857"/>
-    <col min="35" max="35" customWidth="true" width="14.7142857142857"/>
-    <col min="36" max="36" customWidth="true" width="18.5714285714286"/>
-    <col min="37" max="37" customWidth="true" width="14.1428571428571"/>
-    <col min="38" max="38" customWidth="true" width="14.7142857142857"/>
-    <col min="39" max="39" customWidth="true" width="17.4285714285714"/>
-    <col min="40" max="40" customWidth="true" width="22.0"/>
-    <col min="41" max="41" customWidth="true" width="17.5714285714286"/>
-    <col min="42" max="42" customWidth="true" width="25.2857142857143"/>
-    <col min="43" max="43" customWidth="true" width="13.0"/>
-    <col min="44" max="44" customWidth="true" width="23.7142857142857"/>
-    <col min="45" max="45" customWidth="true" width="10.0"/>
-    <col min="46" max="46" customWidth="true" width="13.0"/>
-    <col min="47" max="47" customWidth="true" width="15.5714285714286"/>
-    <col min="48" max="48" customWidth="true" width="21.1428571428571"/>
-    <col min="49" max="49" customWidth="true" width="11.5714285714286"/>
-    <col min="50" max="50" customWidth="true" width="16.7142857142857"/>
-    <col min="51" max="51" customWidth="true" width="14.0"/>
-    <col min="52" max="52" customWidth="true" width="19.4285714285714"/>
-    <col min="53" max="53" customWidth="true" width="18.8571428571429"/>
-    <col min="54" max="54" customWidth="true" width="23.2857142857143"/>
-    <col min="55" max="55" customWidth="true" width="15.5714285714286"/>
-    <col min="56" max="56" customWidth="true" width="14.2857142857143"/>
-    <col min="57" max="57" customWidth="true" width="17.0"/>
-    <col min="58" max="58" customWidth="true" width="16.2857142857143"/>
-    <col min="59" max="59" customWidth="true" width="13.5714285714286"/>
-    <col min="60" max="61" customWidth="true" width="12.7142857142857"/>
-    <col min="62" max="62" customWidth="true" width="21.8571428571429"/>
-    <col min="63" max="63" customWidth="true" width="30.5714285714286"/>
-    <col min="64" max="64" customWidth="true" width="10.0"/>
-    <col min="65" max="65" customWidth="true" width="42.5714285714286"/>
-    <col min="66" max="66" customWidth="true" width="38.1428571428571"/>
-    <col min="67" max="67" customWidth="true" width="19.4285714285714"/>
-    <col min="68" max="68" customWidth="true" width="35.4285714285714"/>
-    <col min="69" max="69" customWidth="true" width="9.57142857142857"/>
+    <col min="1" max="1" width="5.14545454545455" customWidth="1"/>
+    <col min="2" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="79.4272727272727" customWidth="1"/>
+    <col min="5" max="5" width="11.5727272727273" customWidth="1"/>
+    <col min="6" max="6" width="5.14545454545455" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="12.7181818181818" customWidth="1"/>
+    <col min="9" max="9" width="5.85454545454545" customWidth="1"/>
+    <col min="10" max="10" width="6" customWidth="1"/>
+    <col min="11" max="11" width="5.85454545454545" customWidth="1"/>
+    <col min="12" max="12" width="14.2818181818182" customWidth="1"/>
+    <col min="13" max="13" width="9.42727272727273" customWidth="1"/>
+    <col min="14" max="14" width="14.4272727272727" customWidth="1"/>
+    <col min="15" max="15" width="15.5727272727273" customWidth="1"/>
+    <col min="16" max="16" width="14.4272727272727" customWidth="1"/>
+    <col min="17" max="17" width="39.4272727272727" customWidth="1"/>
+    <col min="18" max="18" width="11.7181818181818" customWidth="1"/>
+    <col min="19" max="19" width="11.8545454545455" customWidth="1"/>
+    <col min="20" max="20" width="6.42727272727273" customWidth="1"/>
+    <col min="21" max="22" width="6.57272727272727" customWidth="1"/>
+    <col min="23" max="23" width="37.1454545454545" customWidth="1"/>
+    <col min="24" max="25" width="8" customWidth="1"/>
+    <col min="26" max="26" width="7.71818181818182" customWidth="1"/>
+    <col min="27" max="27" width="6.28181818181818" customWidth="1"/>
+    <col min="28" max="28" width="9.28181818181818" customWidth="1"/>
+    <col min="29" max="29" width="9.71818181818182" customWidth="1"/>
+    <col min="30" max="30" width="12.8545454545455" customWidth="1"/>
+    <col min="31" max="31" width="16.1454545454545" customWidth="1"/>
+    <col min="32" max="32" width="15.4272727272727" customWidth="1"/>
+    <col min="33" max="33" width="24.5727272727273" customWidth="1"/>
+    <col min="34" max="34" width="8.57272727272727" customWidth="1"/>
+    <col min="35" max="35" width="14.7181818181818" customWidth="1"/>
+    <col min="36" max="36" width="18.5727272727273" customWidth="1"/>
+    <col min="37" max="37" width="14.1454545454545" customWidth="1"/>
+    <col min="38" max="38" width="14.7181818181818" customWidth="1"/>
+    <col min="39" max="39" width="17.4272727272727" customWidth="1"/>
+    <col min="40" max="40" width="22" customWidth="1"/>
+    <col min="41" max="41" width="17.5727272727273" customWidth="1"/>
+    <col min="42" max="42" width="25.2818181818182" customWidth="1"/>
+    <col min="43" max="43" width="13" customWidth="1"/>
+    <col min="44" max="44" width="23.7181818181818" customWidth="1"/>
+    <col min="45" max="45" width="10" customWidth="1"/>
+    <col min="46" max="46" width="13" customWidth="1"/>
+    <col min="47" max="47" width="15.5727272727273" customWidth="1"/>
+    <col min="48" max="48" width="21.1454545454545" customWidth="1"/>
+    <col min="49" max="49" width="11.5727272727273" customWidth="1"/>
+    <col min="50" max="50" width="16.7181818181818" customWidth="1"/>
+    <col min="51" max="51" width="14" customWidth="1"/>
+    <col min="52" max="52" width="19.4272727272727" customWidth="1"/>
+    <col min="53" max="53" width="18.8545454545455" customWidth="1"/>
+    <col min="54" max="54" width="23.2818181818182" customWidth="1"/>
+    <col min="55" max="55" width="15.5727272727273" customWidth="1"/>
+    <col min="56" max="56" width="14.2818181818182" customWidth="1"/>
+    <col min="57" max="57" width="17" customWidth="1"/>
+    <col min="58" max="58" width="16.2818181818182" customWidth="1"/>
+    <col min="59" max="59" width="13.5727272727273" customWidth="1"/>
+    <col min="60" max="61" width="12.7181818181818" customWidth="1"/>
+    <col min="62" max="62" width="21.8545454545455" customWidth="1"/>
+    <col min="63" max="63" width="30.5727272727273" customWidth="1"/>
+    <col min="64" max="64" width="10" customWidth="1"/>
+    <col min="65" max="65" width="42.5727272727273" customWidth="1"/>
+    <col min="66" max="66" width="38.1454545454545" customWidth="1"/>
+    <col min="67" max="67" width="19.4272727272727" customWidth="1"/>
+    <col min="68" max="68" width="35.4272727272727" customWidth="1"/>
+    <col min="69" max="69" width="9.57272727272727" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -9731,7 +9200,7 @@
       <c r="BP2" s="27"/>
       <c r="BQ2" s="27"/>
     </row>
-    <row r="3" ht="15.75" spans="1:69">
+    <row r="3" ht="15.25" spans="1:69">
       <c r="A3" s="28" t="s">
         <v>9</v>
       </c>
@@ -9940,7 +9409,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.75" spans="1:69">
+    <row r="4" ht="15.25" spans="1:69">
       <c r="A4" s="26">
         <v>1</v>
       </c>
@@ -10104,8 +9573,6 @@
       <c r="AT4" s="35" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" s="0"/>
-      <c r="AV4" s="0"/>
       <c r="AW4" s="35">
         <f>AM4</f>
         <v>4</v>
@@ -10144,10 +9611,10 @@
       <c r="BL4" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="BM4" t="s" s="0">
+      <c r="BM4" t="s">
         <v>100</v>
       </c>
-      <c r="BN4" t="s" s="0">
+      <c r="BN4" t="s">
         <v>100</v>
       </c>
       <c r="BO4" s="35">
@@ -10293,73 +9760,73 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ5"/>
-  <sheetFormatPr defaultColWidth="8.7047619047619" defaultRowHeight="15" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="5.14285714285714"/>
-    <col min="2" max="3" customWidth="true" width="22.0"/>
-    <col min="4" max="4" customWidth="true" width="79.4285714285714"/>
-    <col min="5" max="5" customWidth="true" width="11.5714285714286"/>
-    <col min="6" max="6" customWidth="true" width="5.14285714285714"/>
-    <col min="7" max="7" customWidth="true" width="11.0"/>
-    <col min="8" max="8" customWidth="true" width="12.7142857142857"/>
-    <col min="9" max="9" customWidth="true" width="5.85714285714286"/>
-    <col min="10" max="10" customWidth="true" width="6.0"/>
-    <col min="11" max="11" customWidth="true" width="5.85714285714286"/>
-    <col min="12" max="12" customWidth="true" width="14.2857142857143"/>
-    <col min="13" max="13" customWidth="true" width="9.42857142857143"/>
-    <col min="14" max="14" customWidth="true" width="14.4285714285714"/>
-    <col min="15" max="15" customWidth="true" width="15.5714285714286"/>
-    <col min="16" max="16" customWidth="true" width="14.4285714285714"/>
-    <col min="17" max="17" customWidth="true" width="39.4285714285714"/>
-    <col min="18" max="18" customWidth="true" width="11.7142857142857"/>
-    <col min="19" max="19" customWidth="true" width="11.8571428571429"/>
-    <col min="20" max="20" customWidth="true" width="6.42857142857143"/>
-    <col min="21" max="22" customWidth="true" width="6.57142857142857"/>
-    <col min="23" max="23" customWidth="true" width="37.1428571428571"/>
-    <col min="24" max="25" customWidth="true" width="8.0"/>
-    <col min="26" max="26" customWidth="true" width="7.71428571428571"/>
-    <col min="27" max="27" customWidth="true" width="6.28571428571429"/>
-    <col min="28" max="28" customWidth="true" width="9.28571428571429"/>
-    <col min="29" max="29" customWidth="true" width="9.71428571428571"/>
-    <col min="30" max="30" customWidth="true" width="12.8571428571429"/>
-    <col min="31" max="31" customWidth="true" width="16.1428571428571"/>
-    <col min="32" max="32" customWidth="true" width="15.4285714285714"/>
-    <col min="33" max="33" customWidth="true" width="24.5714285714286"/>
-    <col min="34" max="34" customWidth="true" width="8.57142857142857"/>
-    <col min="35" max="35" customWidth="true" width="14.7142857142857"/>
-    <col min="36" max="36" customWidth="true" width="18.5714285714286"/>
-    <col min="37" max="37" customWidth="true" width="14.1428571428571"/>
-    <col min="38" max="38" customWidth="true" width="14.7142857142857"/>
-    <col min="39" max="39" customWidth="true" width="17.4285714285714"/>
-    <col min="40" max="40" customWidth="true" width="22.0"/>
-    <col min="41" max="41" customWidth="true" width="17.5714285714286"/>
-    <col min="42" max="42" customWidth="true" width="25.2857142857143"/>
-    <col min="43" max="43" customWidth="true" width="13.0"/>
-    <col min="44" max="44" customWidth="true" width="23.7142857142857"/>
-    <col min="45" max="45" customWidth="true" width="10.0"/>
-    <col min="46" max="46" customWidth="true" width="13.0"/>
-    <col min="47" max="47" customWidth="true" width="15.5714285714286"/>
-    <col min="48" max="48" customWidth="true" width="21.1428571428571"/>
-    <col min="49" max="49" customWidth="true" width="11.5714285714286"/>
-    <col min="50" max="50" customWidth="true" width="16.7142857142857"/>
-    <col min="51" max="51" customWidth="true" width="14.0"/>
-    <col min="52" max="52" customWidth="true" width="19.4285714285714"/>
-    <col min="53" max="53" customWidth="true" width="18.8571428571429"/>
-    <col min="54" max="54" customWidth="true" width="23.2857142857143"/>
-    <col min="55" max="55" customWidth="true" width="15.5714285714286"/>
-    <col min="56" max="56" customWidth="true" width="14.2857142857143"/>
-    <col min="57" max="57" customWidth="true" width="17.0"/>
-    <col min="58" max="58" customWidth="true" width="16.2857142857143"/>
-    <col min="59" max="59" customWidth="true" width="13.5714285714286"/>
-    <col min="60" max="61" customWidth="true" width="12.7142857142857"/>
-    <col min="62" max="62" customWidth="true" width="21.8571428571429"/>
-    <col min="63" max="63" customWidth="true" width="30.5714285714286"/>
-    <col min="64" max="64" customWidth="true" width="10.0"/>
-    <col min="65" max="65" customWidth="true" width="42.5714285714286"/>
-    <col min="66" max="66" customWidth="true" width="38.1428571428571"/>
-    <col min="67" max="67" customWidth="true" width="19.4285714285714"/>
-    <col min="68" max="68" customWidth="true" width="35.4285714285714"/>
-    <col min="69" max="69" customWidth="true" width="9.57142857142857"/>
+    <col min="1" max="1" width="5.14545454545455" customWidth="1"/>
+    <col min="2" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="79.4272727272727" customWidth="1"/>
+    <col min="5" max="5" width="11.5727272727273" customWidth="1"/>
+    <col min="6" max="6" width="5.14545454545455" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="12.7181818181818" customWidth="1"/>
+    <col min="9" max="9" width="5.85454545454545" customWidth="1"/>
+    <col min="10" max="10" width="6" customWidth="1"/>
+    <col min="11" max="11" width="5.85454545454545" customWidth="1"/>
+    <col min="12" max="12" width="14.2818181818182" customWidth="1"/>
+    <col min="13" max="13" width="9.42727272727273" customWidth="1"/>
+    <col min="14" max="14" width="14.4272727272727" customWidth="1"/>
+    <col min="15" max="15" width="15.5727272727273" customWidth="1"/>
+    <col min="16" max="16" width="14.4272727272727" customWidth="1"/>
+    <col min="17" max="17" width="39.4272727272727" customWidth="1"/>
+    <col min="18" max="18" width="11.7181818181818" customWidth="1"/>
+    <col min="19" max="19" width="11.8545454545455" customWidth="1"/>
+    <col min="20" max="20" width="6.42727272727273" customWidth="1"/>
+    <col min="21" max="22" width="6.57272727272727" customWidth="1"/>
+    <col min="23" max="23" width="37.1454545454545" customWidth="1"/>
+    <col min="24" max="25" width="8" customWidth="1"/>
+    <col min="26" max="26" width="7.71818181818182" customWidth="1"/>
+    <col min="27" max="27" width="6.28181818181818" customWidth="1"/>
+    <col min="28" max="28" width="9.28181818181818" customWidth="1"/>
+    <col min="29" max="29" width="9.71818181818182" customWidth="1"/>
+    <col min="30" max="30" width="12.8545454545455" customWidth="1"/>
+    <col min="31" max="31" width="16.1454545454545" customWidth="1"/>
+    <col min="32" max="32" width="15.4272727272727" customWidth="1"/>
+    <col min="33" max="33" width="24.5727272727273" customWidth="1"/>
+    <col min="34" max="34" width="8.57272727272727" customWidth="1"/>
+    <col min="35" max="35" width="14.7181818181818" customWidth="1"/>
+    <col min="36" max="36" width="18.5727272727273" customWidth="1"/>
+    <col min="37" max="37" width="14.1454545454545" customWidth="1"/>
+    <col min="38" max="38" width="14.7181818181818" customWidth="1"/>
+    <col min="39" max="39" width="17.4272727272727" customWidth="1"/>
+    <col min="40" max="40" width="22" customWidth="1"/>
+    <col min="41" max="41" width="17.5727272727273" customWidth="1"/>
+    <col min="42" max="42" width="25.2818181818182" customWidth="1"/>
+    <col min="43" max="43" width="13" customWidth="1"/>
+    <col min="44" max="44" width="23.7181818181818" customWidth="1"/>
+    <col min="45" max="45" width="10" customWidth="1"/>
+    <col min="46" max="46" width="13" customWidth="1"/>
+    <col min="47" max="47" width="15.5727272727273" customWidth="1"/>
+    <col min="48" max="48" width="21.1454545454545" customWidth="1"/>
+    <col min="49" max="49" width="11.5727272727273" customWidth="1"/>
+    <col min="50" max="50" width="16.7181818181818" customWidth="1"/>
+    <col min="51" max="51" width="14" customWidth="1"/>
+    <col min="52" max="52" width="19.4272727272727" customWidth="1"/>
+    <col min="53" max="53" width="18.8545454545455" customWidth="1"/>
+    <col min="54" max="54" width="23.2818181818182" customWidth="1"/>
+    <col min="55" max="55" width="15.5727272727273" customWidth="1"/>
+    <col min="56" max="56" width="14.2818181818182" customWidth="1"/>
+    <col min="57" max="57" width="17" customWidth="1"/>
+    <col min="58" max="58" width="16.2818181818182" customWidth="1"/>
+    <col min="59" max="59" width="13.5727272727273" customWidth="1"/>
+    <col min="60" max="61" width="12.7181818181818" customWidth="1"/>
+    <col min="62" max="62" width="21.8545454545455" customWidth="1"/>
+    <col min="63" max="63" width="30.5727272727273" customWidth="1"/>
+    <col min="64" max="64" width="10" customWidth="1"/>
+    <col min="65" max="65" width="42.5727272727273" customWidth="1"/>
+    <col min="66" max="66" width="38.1454545454545" customWidth="1"/>
+    <col min="67" max="67" width="19.4272727272727" customWidth="1"/>
+    <col min="68" max="68" width="35.4272727272727" customWidth="1"/>
+    <col min="69" max="69" width="9.57272727272727" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -10530,7 +9997,7 @@
       <c r="BP2" s="27"/>
       <c r="BQ2" s="27"/>
     </row>
-    <row r="3" ht="15.75" spans="1:69">
+    <row r="3" ht="15.25" spans="1:69">
       <c r="A3" s="28" t="s">
         <v>9</v>
       </c>
@@ -10739,7 +10206,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.75" spans="1:69">
+    <row r="4" ht="15.25" spans="1:69">
       <c r="A4" s="26">
         <v>1</v>
       </c>
@@ -10903,8 +10370,6 @@
       <c r="AT4" s="35" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" s="0"/>
-      <c r="AV4" s="0"/>
       <c r="AW4" s="35">
         <f>AM4</f>
         <v>4</v>
@@ -10943,10 +10408,10 @@
       <c r="BL4" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="BM4" t="s" s="0">
+      <c r="BM4" t="s">
         <v>100</v>
       </c>
-      <c r="BN4" t="s" s="0">
+      <c r="BN4" t="s">
         <v>100</v>
       </c>
       <c r="BO4" s="35">
@@ -11092,74 +10557,74 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ5"/>
-  <sheetFormatPr defaultColWidth="8.7047619047619" defaultRowHeight="15" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="5.14285714285714"/>
-    <col min="2" max="2" customWidth="true" width="21.8571428571429"/>
-    <col min="3" max="3" customWidth="true" width="27.5714285714286"/>
-    <col min="4" max="4" customWidth="true" width="79.4285714285714"/>
-    <col min="5" max="5" customWidth="true" width="11.5714285714286"/>
-    <col min="6" max="6" customWidth="true" width="5.14285714285714"/>
-    <col min="7" max="7" customWidth="true" width="11.0"/>
-    <col min="8" max="8" customWidth="true" width="12.7142857142857"/>
-    <col min="9" max="10" customWidth="true" width="5.85714285714286"/>
-    <col min="11" max="11" customWidth="true" width="6.0"/>
-    <col min="12" max="12" customWidth="true" width="14.2857142857143"/>
-    <col min="13" max="13" customWidth="true" width="9.42857142857143"/>
-    <col min="14" max="14" customWidth="true" width="14.2857142857143"/>
-    <col min="15" max="15" customWidth="true" width="15.5714285714286"/>
-    <col min="16" max="16" customWidth="true" width="14.4285714285714"/>
-    <col min="17" max="17" customWidth="true" width="39.4285714285714"/>
-    <col min="18" max="18" customWidth="true" width="11.7142857142857"/>
-    <col min="19" max="19" customWidth="true" width="10.0"/>
-    <col min="20" max="20" customWidth="true" width="6.42857142857143"/>
-    <col min="21" max="21" customWidth="true" width="9.85714285714286"/>
-    <col min="22" max="22" customWidth="true" width="6.57142857142857"/>
-    <col min="23" max="23" customWidth="true" width="37.1428571428571"/>
-    <col min="24" max="25" customWidth="true" width="8.0"/>
-    <col min="26" max="26" customWidth="true" width="7.71428571428571"/>
-    <col min="27" max="27" customWidth="true" width="6.28571428571429"/>
-    <col min="28" max="28" customWidth="true" width="9.28571428571429"/>
-    <col min="29" max="29" customWidth="true" width="9.71428571428571"/>
-    <col min="30" max="30" customWidth="true" width="12.8571428571429"/>
-    <col min="31" max="31" customWidth="true" width="16.1428571428571"/>
-    <col min="32" max="32" customWidth="true" width="15.4285714285714"/>
-    <col min="33" max="33" customWidth="true" width="24.5714285714286"/>
-    <col min="34" max="34" customWidth="true" width="8.57142857142857"/>
-    <col min="35" max="35" customWidth="true" width="14.7142857142857"/>
-    <col min="36" max="36" customWidth="true" width="18.5714285714286"/>
-    <col min="37" max="37" customWidth="true" width="14.1428571428571"/>
-    <col min="38" max="38" customWidth="true" width="14.7142857142857"/>
-    <col min="39" max="39" customWidth="true" width="17.4285714285714"/>
-    <col min="40" max="40" customWidth="true" width="22.0"/>
-    <col min="41" max="41" customWidth="true" width="17.5714285714286"/>
-    <col min="42" max="42" customWidth="true" width="25.2857142857143"/>
-    <col min="43" max="43" customWidth="true" width="13.0"/>
-    <col min="44" max="44" customWidth="true" width="25.7142857142857"/>
-    <col min="45" max="45" customWidth="true" width="10.0"/>
-    <col min="46" max="46" customWidth="true" width="13.0"/>
-    <col min="47" max="47" customWidth="true" width="15.5714285714286"/>
-    <col min="48" max="48" customWidth="true" width="21.1428571428571"/>
-    <col min="49" max="49" customWidth="true" width="11.5714285714286"/>
-    <col min="50" max="50" customWidth="true" width="16.7142857142857"/>
-    <col min="51" max="51" customWidth="true" width="14.0"/>
-    <col min="52" max="52" customWidth="true" width="19.4285714285714"/>
-    <col min="53" max="53" customWidth="true" width="18.8571428571429"/>
-    <col min="54" max="54" customWidth="true" width="23.2857142857143"/>
-    <col min="55" max="55" customWidth="true" width="15.5714285714286"/>
-    <col min="56" max="56" customWidth="true" width="14.2857142857143"/>
-    <col min="57" max="57" customWidth="true" width="17.0"/>
-    <col min="58" max="58" customWidth="true" width="16.2857142857143"/>
-    <col min="59" max="59" customWidth="true" width="13.5714285714286"/>
-    <col min="60" max="61" customWidth="true" width="12.7142857142857"/>
-    <col min="62" max="62" customWidth="true" width="21.8571428571429"/>
-    <col min="63" max="63" customWidth="true" width="30.5714285714286"/>
-    <col min="64" max="64" customWidth="true" width="10.0"/>
-    <col min="65" max="65" customWidth="true" width="42.5714285714286"/>
-    <col min="66" max="66" customWidth="true" width="38.1428571428571"/>
-    <col min="67" max="67" customWidth="true" width="19.4285714285714"/>
-    <col min="68" max="68" customWidth="true" width="35.4285714285714"/>
-    <col min="69" max="69" customWidth="true" width="9.57142857142857"/>
+    <col min="1" max="1" width="5.14545454545455" customWidth="1"/>
+    <col min="2" max="2" width="21.8545454545455" customWidth="1"/>
+    <col min="3" max="3" width="27.5727272727273" customWidth="1"/>
+    <col min="4" max="4" width="79.4272727272727" customWidth="1"/>
+    <col min="5" max="5" width="11.5727272727273" customWidth="1"/>
+    <col min="6" max="6" width="5.14545454545455" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="12.7181818181818" customWidth="1"/>
+    <col min="9" max="10" width="5.85454545454545" customWidth="1"/>
+    <col min="11" max="11" width="6" customWidth="1"/>
+    <col min="12" max="12" width="14.2818181818182" customWidth="1"/>
+    <col min="13" max="13" width="9.42727272727273" customWidth="1"/>
+    <col min="14" max="14" width="14.2818181818182" customWidth="1"/>
+    <col min="15" max="15" width="15.5727272727273" customWidth="1"/>
+    <col min="16" max="16" width="14.4272727272727" customWidth="1"/>
+    <col min="17" max="17" width="39.4272727272727" customWidth="1"/>
+    <col min="18" max="18" width="11.7181818181818" customWidth="1"/>
+    <col min="19" max="19" width="10" customWidth="1"/>
+    <col min="20" max="20" width="6.42727272727273" customWidth="1"/>
+    <col min="21" max="21" width="9.85454545454546" customWidth="1"/>
+    <col min="22" max="22" width="6.57272727272727" customWidth="1"/>
+    <col min="23" max="23" width="37.1454545454545" customWidth="1"/>
+    <col min="24" max="25" width="8" customWidth="1"/>
+    <col min="26" max="26" width="7.71818181818182" customWidth="1"/>
+    <col min="27" max="27" width="6.28181818181818" customWidth="1"/>
+    <col min="28" max="28" width="9.28181818181818" customWidth="1"/>
+    <col min="29" max="29" width="9.71818181818182" customWidth="1"/>
+    <col min="30" max="30" width="12.8545454545455" customWidth="1"/>
+    <col min="31" max="31" width="16.1454545454545" customWidth="1"/>
+    <col min="32" max="32" width="15.4272727272727" customWidth="1"/>
+    <col min="33" max="33" width="24.5727272727273" customWidth="1"/>
+    <col min="34" max="34" width="8.57272727272727" customWidth="1"/>
+    <col min="35" max="35" width="14.7181818181818" customWidth="1"/>
+    <col min="36" max="36" width="18.5727272727273" customWidth="1"/>
+    <col min="37" max="37" width="14.1454545454545" customWidth="1"/>
+    <col min="38" max="38" width="14.7181818181818" customWidth="1"/>
+    <col min="39" max="39" width="17.4272727272727" customWidth="1"/>
+    <col min="40" max="40" width="22" customWidth="1"/>
+    <col min="41" max="41" width="17.5727272727273" customWidth="1"/>
+    <col min="42" max="42" width="25.2818181818182" customWidth="1"/>
+    <col min="43" max="43" width="13" customWidth="1"/>
+    <col min="44" max="44" width="25.7181818181818" customWidth="1"/>
+    <col min="45" max="45" width="10" customWidth="1"/>
+    <col min="46" max="46" width="13" customWidth="1"/>
+    <col min="47" max="47" width="15.5727272727273" customWidth="1"/>
+    <col min="48" max="48" width="21.1454545454545" customWidth="1"/>
+    <col min="49" max="49" width="11.5727272727273" customWidth="1"/>
+    <col min="50" max="50" width="16.7181818181818" customWidth="1"/>
+    <col min="51" max="51" width="14" customWidth="1"/>
+    <col min="52" max="52" width="19.4272727272727" customWidth="1"/>
+    <col min="53" max="53" width="18.8545454545455" customWidth="1"/>
+    <col min="54" max="54" width="23.2818181818182" customWidth="1"/>
+    <col min="55" max="55" width="15.5727272727273" customWidth="1"/>
+    <col min="56" max="56" width="14.2818181818182" customWidth="1"/>
+    <col min="57" max="57" width="17" customWidth="1"/>
+    <col min="58" max="58" width="16.2818181818182" customWidth="1"/>
+    <col min="59" max="59" width="13.5727272727273" customWidth="1"/>
+    <col min="60" max="61" width="12.7181818181818" customWidth="1"/>
+    <col min="62" max="62" width="21.8545454545455" customWidth="1"/>
+    <col min="63" max="63" width="30.5727272727273" customWidth="1"/>
+    <col min="64" max="64" width="10" customWidth="1"/>
+    <col min="65" max="65" width="42.5727272727273" customWidth="1"/>
+    <col min="66" max="66" width="38.1454545454545" customWidth="1"/>
+    <col min="67" max="67" width="19.4272727272727" customWidth="1"/>
+    <col min="68" max="68" width="35.4272727272727" customWidth="1"/>
+    <col min="69" max="69" width="9.57272727272727" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -11330,7 +10795,7 @@
       <c r="BP2" s="27"/>
       <c r="BQ2" s="27"/>
     </row>
-    <row r="3" ht="15.75" spans="1:69">
+    <row r="3" ht="15.25" spans="1:69">
       <c r="A3" s="28" t="s">
         <v>9</v>
       </c>
@@ -11539,7 +11004,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.75" spans="1:69">
+    <row r="4" ht="15.25" spans="1:69">
       <c r="A4" s="26">
         <v>1</v>
       </c>
@@ -11703,10 +11168,10 @@
       <c r="AT4" s="35" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" t="s" s="0">
+      <c r="AU4" t="s">
         <v>91</v>
       </c>
-      <c r="AV4" t="s" s="0">
+      <c r="AV4" t="s">
         <v>92</v>
       </c>
       <c r="AW4" s="35">
@@ -11721,7 +11186,7 @@
         <f>AU4+AW4</f>
         <v>4</v>
       </c>
-      <c r="AZ4" t="s" s="0">
+      <c r="AZ4" t="s">
         <v>92</v>
       </c>
       <c r="BA4" s="36"/>
@@ -11746,11 +11211,11 @@
       <c r="BL4" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="BM4" t="s" s="0">
-        <v>310</v>
-      </c>
-      <c r="BN4" t="s" s="0">
-        <v>309</v>
+      <c r="BM4" t="s">
+        <v>93</v>
+      </c>
+      <c r="BN4" t="s">
+        <v>94</v>
       </c>
       <c r="BO4" s="35">
         <f>ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
@@ -11895,73 +11360,73 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ5"/>
-  <sheetFormatPr defaultColWidth="8.7047619047619" defaultRowHeight="15" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="5.14285714285714"/>
-    <col min="2" max="3" customWidth="true" width="28.0"/>
-    <col min="4" max="4" customWidth="true" width="79.4285714285714"/>
-    <col min="5" max="5" customWidth="true" width="11.5714285714286"/>
-    <col min="6" max="6" customWidth="true" width="5.14285714285714"/>
-    <col min="7" max="7" customWidth="true" width="11.0"/>
-    <col min="8" max="8" customWidth="true" width="12.7142857142857"/>
-    <col min="9" max="9" customWidth="true" width="5.85714285714286"/>
-    <col min="10" max="10" customWidth="true" width="6.0"/>
-    <col min="11" max="11" customWidth="true" width="5.85714285714286"/>
-    <col min="12" max="12" customWidth="true" width="14.2857142857143"/>
-    <col min="13" max="13" customWidth="true" width="9.42857142857143"/>
-    <col min="14" max="14" customWidth="true" width="14.4285714285714"/>
-    <col min="15" max="15" customWidth="true" width="15.5714285714286"/>
-    <col min="16" max="16" customWidth="true" width="14.4285714285714"/>
-    <col min="17" max="17" customWidth="true" width="39.4285714285714"/>
-    <col min="18" max="18" customWidth="true" width="11.7142857142857"/>
-    <col min="19" max="19" customWidth="true" width="11.8571428571429"/>
-    <col min="20" max="20" customWidth="true" width="6.42857142857143"/>
-    <col min="21" max="22" customWidth="true" width="6.57142857142857"/>
-    <col min="23" max="23" customWidth="true" width="37.1428571428571"/>
-    <col min="24" max="25" customWidth="true" width="8.0"/>
-    <col min="26" max="26" customWidth="true" width="7.71428571428571"/>
-    <col min="27" max="27" customWidth="true" width="6.28571428571429"/>
-    <col min="28" max="28" customWidth="true" width="9.28571428571429"/>
-    <col min="29" max="29" customWidth="true" width="9.71428571428571"/>
-    <col min="30" max="30" customWidth="true" width="12.8571428571429"/>
-    <col min="31" max="31" customWidth="true" width="16.1428571428571"/>
-    <col min="32" max="32" customWidth="true" width="15.4285714285714"/>
-    <col min="33" max="33" customWidth="true" width="24.5714285714286"/>
-    <col min="34" max="34" customWidth="true" width="8.57142857142857"/>
-    <col min="35" max="35" customWidth="true" width="14.7142857142857"/>
-    <col min="36" max="36" customWidth="true" width="18.5714285714286"/>
-    <col min="37" max="37" customWidth="true" width="14.1428571428571"/>
-    <col min="38" max="38" customWidth="true" width="14.7142857142857"/>
-    <col min="39" max="39" customWidth="true" width="17.4285714285714"/>
-    <col min="40" max="40" customWidth="true" width="22.0"/>
-    <col min="41" max="41" customWidth="true" width="17.5714285714286"/>
-    <col min="42" max="42" customWidth="true" width="25.2857142857143"/>
-    <col min="43" max="43" customWidth="true" width="13.0"/>
-    <col min="44" max="44" customWidth="true" width="23.7142857142857"/>
-    <col min="45" max="45" customWidth="true" width="10.0"/>
-    <col min="46" max="46" customWidth="true" width="13.0"/>
-    <col min="47" max="47" customWidth="true" width="15.5714285714286"/>
-    <col min="48" max="48" customWidth="true" width="21.1428571428571"/>
-    <col min="49" max="49" customWidth="true" width="11.5714285714286"/>
-    <col min="50" max="50" customWidth="true" width="16.7142857142857"/>
-    <col min="51" max="51" customWidth="true" width="14.0"/>
-    <col min="52" max="52" customWidth="true" width="19.4285714285714"/>
-    <col min="53" max="53" customWidth="true" width="18.8571428571429"/>
-    <col min="54" max="54" customWidth="true" width="23.2857142857143"/>
-    <col min="55" max="55" customWidth="true" width="15.5714285714286"/>
-    <col min="56" max="56" customWidth="true" width="14.2857142857143"/>
-    <col min="57" max="57" customWidth="true" width="17.0"/>
-    <col min="58" max="58" customWidth="true" width="16.2857142857143"/>
-    <col min="59" max="59" customWidth="true" width="13.5714285714286"/>
-    <col min="60" max="61" customWidth="true" width="12.7142857142857"/>
-    <col min="62" max="62" customWidth="true" width="21.8571428571429"/>
-    <col min="63" max="63" customWidth="true" width="30.5714285714286"/>
-    <col min="64" max="64" customWidth="true" width="10.0"/>
-    <col min="65" max="65" customWidth="true" width="42.5714285714286"/>
-    <col min="66" max="66" customWidth="true" width="38.1428571428571"/>
-    <col min="67" max="67" customWidth="true" width="19.4285714285714"/>
-    <col min="68" max="68" customWidth="true" width="35.4285714285714"/>
-    <col min="69" max="69" customWidth="true" width="9.57142857142857"/>
+    <col min="1" max="1" width="5.14545454545455" customWidth="1"/>
+    <col min="2" max="3" width="28" customWidth="1"/>
+    <col min="4" max="4" width="79.4272727272727" customWidth="1"/>
+    <col min="5" max="5" width="11.5727272727273" customWidth="1"/>
+    <col min="6" max="6" width="5.14545454545455" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="12.7181818181818" customWidth="1"/>
+    <col min="9" max="9" width="5.85454545454545" customWidth="1"/>
+    <col min="10" max="10" width="6" customWidth="1"/>
+    <col min="11" max="11" width="5.85454545454545" customWidth="1"/>
+    <col min="12" max="12" width="14.2818181818182" customWidth="1"/>
+    <col min="13" max="13" width="9.42727272727273" customWidth="1"/>
+    <col min="14" max="14" width="14.4272727272727" customWidth="1"/>
+    <col min="15" max="15" width="15.5727272727273" customWidth="1"/>
+    <col min="16" max="16" width="14.4272727272727" customWidth="1"/>
+    <col min="17" max="17" width="39.4272727272727" customWidth="1"/>
+    <col min="18" max="18" width="11.7181818181818" customWidth="1"/>
+    <col min="19" max="19" width="11.8545454545455" customWidth="1"/>
+    <col min="20" max="20" width="6.42727272727273" customWidth="1"/>
+    <col min="21" max="22" width="6.57272727272727" customWidth="1"/>
+    <col min="23" max="23" width="37.1454545454545" customWidth="1"/>
+    <col min="24" max="25" width="8" customWidth="1"/>
+    <col min="26" max="26" width="7.71818181818182" customWidth="1"/>
+    <col min="27" max="27" width="6.28181818181818" customWidth="1"/>
+    <col min="28" max="28" width="9.28181818181818" customWidth="1"/>
+    <col min="29" max="29" width="9.71818181818182" customWidth="1"/>
+    <col min="30" max="30" width="12.8545454545455" customWidth="1"/>
+    <col min="31" max="31" width="16.1454545454545" customWidth="1"/>
+    <col min="32" max="32" width="15.4272727272727" customWidth="1"/>
+    <col min="33" max="33" width="24.5727272727273" customWidth="1"/>
+    <col min="34" max="34" width="8.57272727272727" customWidth="1"/>
+    <col min="35" max="35" width="14.7181818181818" customWidth="1"/>
+    <col min="36" max="36" width="18.5727272727273" customWidth="1"/>
+    <col min="37" max="37" width="14.1454545454545" customWidth="1"/>
+    <col min="38" max="38" width="14.7181818181818" customWidth="1"/>
+    <col min="39" max="39" width="17.4272727272727" customWidth="1"/>
+    <col min="40" max="40" width="22" customWidth="1"/>
+    <col min="41" max="41" width="17.5727272727273" customWidth="1"/>
+    <col min="42" max="42" width="25.2818181818182" customWidth="1"/>
+    <col min="43" max="43" width="13" customWidth="1"/>
+    <col min="44" max="44" width="23.7181818181818" customWidth="1"/>
+    <col min="45" max="45" width="10" customWidth="1"/>
+    <col min="46" max="46" width="13" customWidth="1"/>
+    <col min="47" max="47" width="15.5727272727273" customWidth="1"/>
+    <col min="48" max="48" width="21.1454545454545" customWidth="1"/>
+    <col min="49" max="49" width="11.5727272727273" customWidth="1"/>
+    <col min="50" max="50" width="16.7181818181818" customWidth="1"/>
+    <col min="51" max="51" width="14" customWidth="1"/>
+    <col min="52" max="52" width="19.4272727272727" customWidth="1"/>
+    <col min="53" max="53" width="18.8545454545455" customWidth="1"/>
+    <col min="54" max="54" width="23.2818181818182" customWidth="1"/>
+    <col min="55" max="55" width="15.5727272727273" customWidth="1"/>
+    <col min="56" max="56" width="14.2818181818182" customWidth="1"/>
+    <col min="57" max="57" width="17" customWidth="1"/>
+    <col min="58" max="58" width="16.2818181818182" customWidth="1"/>
+    <col min="59" max="59" width="13.5727272727273" customWidth="1"/>
+    <col min="60" max="61" width="12.7181818181818" customWidth="1"/>
+    <col min="62" max="62" width="21.8545454545455" customWidth="1"/>
+    <col min="63" max="63" width="30.5727272727273" customWidth="1"/>
+    <col min="64" max="64" width="10" customWidth="1"/>
+    <col min="65" max="65" width="42.5727272727273" customWidth="1"/>
+    <col min="66" max="66" width="38.1454545454545" customWidth="1"/>
+    <col min="67" max="67" width="19.4272727272727" customWidth="1"/>
+    <col min="68" max="68" width="35.4272727272727" customWidth="1"/>
+    <col min="69" max="69" width="9.57272727272727" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -12132,7 +11597,7 @@
       <c r="BP2" s="27"/>
       <c r="BQ2" s="27"/>
     </row>
-    <row r="3" ht="15.75" spans="1:69">
+    <row r="3" ht="15.25" spans="1:69">
       <c r="A3" s="28" t="s">
         <v>9</v>
       </c>
@@ -12341,7 +11806,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.75" spans="1:69">
+    <row r="4" ht="15.25" spans="1:69">
       <c r="A4" s="26">
         <v>1</v>
       </c>
@@ -12505,11 +11970,11 @@
       <c r="AT4" s="35" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" t="s" s="0">
-        <v>335</v>
-      </c>
-      <c r="AV4" t="s" s="0">
-        <v>336</v>
+      <c r="AU4" t="s">
+        <v>143</v>
+      </c>
+      <c r="AV4" t="s">
+        <v>144</v>
       </c>
       <c r="AW4" s="35">
         <f>AM4</f>
@@ -12549,11 +12014,11 @@
       <c r="BL4" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="BM4" t="s" s="0">
-        <v>187</v>
-      </c>
-      <c r="BN4" t="s" s="0">
-        <v>186</v>
+      <c r="BM4" t="s">
+        <v>145</v>
+      </c>
+      <c r="BN4" t="s">
+        <v>146</v>
       </c>
       <c r="BO4" s="35">
         <f>ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
@@ -12710,73 +12175,73 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ5"/>
-  <sheetFormatPr defaultColWidth="8.7047619047619" defaultRowHeight="15" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="5.14285714285714"/>
-    <col min="2" max="3" customWidth="true" width="28.0"/>
-    <col min="4" max="4" customWidth="true" width="79.4285714285714"/>
-    <col min="5" max="5" customWidth="true" width="11.5714285714286"/>
-    <col min="6" max="6" customWidth="true" width="5.14285714285714"/>
-    <col min="7" max="7" customWidth="true" width="11.0"/>
-    <col min="8" max="8" customWidth="true" width="12.7142857142857"/>
-    <col min="9" max="9" customWidth="true" width="5.85714285714286"/>
-    <col min="10" max="10" customWidth="true" width="6.0"/>
-    <col min="11" max="11" customWidth="true" width="5.85714285714286"/>
-    <col min="12" max="12" customWidth="true" width="14.2857142857143"/>
-    <col min="13" max="13" customWidth="true" width="9.42857142857143"/>
-    <col min="14" max="14" customWidth="true" width="14.4285714285714"/>
-    <col min="15" max="15" customWidth="true" width="15.5714285714286"/>
-    <col min="16" max="16" customWidth="true" width="14.4285714285714"/>
-    <col min="17" max="17" customWidth="true" width="39.4285714285714"/>
-    <col min="18" max="18" customWidth="true" width="11.7142857142857"/>
-    <col min="19" max="19" customWidth="true" width="11.8571428571429"/>
-    <col min="20" max="20" customWidth="true" width="6.42857142857143"/>
-    <col min="21" max="22" customWidth="true" width="6.57142857142857"/>
-    <col min="23" max="23" customWidth="true" width="37.1428571428571"/>
-    <col min="24" max="25" customWidth="true" width="8.0"/>
-    <col min="26" max="26" customWidth="true" width="7.71428571428571"/>
-    <col min="27" max="27" customWidth="true" width="6.28571428571429"/>
-    <col min="28" max="28" customWidth="true" width="9.28571428571429"/>
-    <col min="29" max="29" customWidth="true" width="9.71428571428571"/>
-    <col min="30" max="30" customWidth="true" width="12.8571428571429"/>
-    <col min="31" max="31" customWidth="true" width="16.1428571428571"/>
-    <col min="32" max="32" customWidth="true" width="15.4285714285714"/>
-    <col min="33" max="33" customWidth="true" width="24.5714285714286"/>
-    <col min="34" max="34" customWidth="true" width="8.57142857142857"/>
-    <col min="35" max="35" customWidth="true" width="14.7142857142857"/>
-    <col min="36" max="36" customWidth="true" width="18.5714285714286"/>
-    <col min="37" max="37" customWidth="true" width="14.1428571428571"/>
-    <col min="38" max="38" customWidth="true" width="14.7142857142857"/>
-    <col min="39" max="39" customWidth="true" width="17.4285714285714"/>
-    <col min="40" max="40" customWidth="true" width="22.0"/>
-    <col min="41" max="41" customWidth="true" width="17.5714285714286"/>
-    <col min="42" max="42" customWidth="true" width="25.2857142857143"/>
-    <col min="43" max="43" customWidth="true" width="13.0"/>
-    <col min="44" max="44" customWidth="true" width="23.7142857142857"/>
-    <col min="45" max="45" customWidth="true" width="10.0"/>
-    <col min="46" max="46" customWidth="true" width="13.0"/>
-    <col min="47" max="47" customWidth="true" width="15.5714285714286"/>
-    <col min="48" max="48" customWidth="true" width="21.1428571428571"/>
-    <col min="49" max="49" customWidth="true" width="11.5714285714286"/>
-    <col min="50" max="50" customWidth="true" width="16.7142857142857"/>
-    <col min="51" max="51" customWidth="true" width="14.0"/>
-    <col min="52" max="52" customWidth="true" width="19.4285714285714"/>
-    <col min="53" max="53" customWidth="true" width="18.8571428571429"/>
-    <col min="54" max="54" customWidth="true" width="23.2857142857143"/>
-    <col min="55" max="55" customWidth="true" width="15.5714285714286"/>
-    <col min="56" max="56" customWidth="true" width="14.2857142857143"/>
-    <col min="57" max="57" customWidth="true" width="17.0"/>
-    <col min="58" max="58" customWidth="true" width="16.2857142857143"/>
-    <col min="59" max="59" customWidth="true" width="13.5714285714286"/>
-    <col min="60" max="61" customWidth="true" width="12.7142857142857"/>
-    <col min="62" max="62" customWidth="true" width="21.8571428571429"/>
-    <col min="63" max="63" customWidth="true" width="30.5714285714286"/>
-    <col min="64" max="64" customWidth="true" width="10.0"/>
-    <col min="65" max="65" customWidth="true" width="42.5714285714286"/>
-    <col min="66" max="66" customWidth="true" width="38.1428571428571"/>
-    <col min="67" max="67" customWidth="true" width="19.4285714285714"/>
-    <col min="68" max="68" customWidth="true" width="35.4285714285714"/>
-    <col min="69" max="69" customWidth="true" width="9.57142857142857"/>
+    <col min="1" max="1" width="5.14545454545455" customWidth="1"/>
+    <col min="2" max="3" width="28" customWidth="1"/>
+    <col min="4" max="4" width="79.4272727272727" customWidth="1"/>
+    <col min="5" max="5" width="11.5727272727273" customWidth="1"/>
+    <col min="6" max="6" width="5.14545454545455" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="12.7181818181818" customWidth="1"/>
+    <col min="9" max="9" width="5.85454545454545" customWidth="1"/>
+    <col min="10" max="10" width="6" customWidth="1"/>
+    <col min="11" max="11" width="5.85454545454545" customWidth="1"/>
+    <col min="12" max="12" width="14.2818181818182" customWidth="1"/>
+    <col min="13" max="13" width="9.42727272727273" customWidth="1"/>
+    <col min="14" max="14" width="14.4272727272727" customWidth="1"/>
+    <col min="15" max="15" width="15.5727272727273" customWidth="1"/>
+    <col min="16" max="16" width="14.4272727272727" customWidth="1"/>
+    <col min="17" max="17" width="39.4272727272727" customWidth="1"/>
+    <col min="18" max="18" width="11.7181818181818" customWidth="1"/>
+    <col min="19" max="19" width="11.8545454545455" customWidth="1"/>
+    <col min="20" max="20" width="6.42727272727273" customWidth="1"/>
+    <col min="21" max="22" width="6.57272727272727" customWidth="1"/>
+    <col min="23" max="23" width="37.1454545454545" customWidth="1"/>
+    <col min="24" max="25" width="8" customWidth="1"/>
+    <col min="26" max="26" width="7.71818181818182" customWidth="1"/>
+    <col min="27" max="27" width="6.28181818181818" customWidth="1"/>
+    <col min="28" max="28" width="9.28181818181818" customWidth="1"/>
+    <col min="29" max="29" width="9.71818181818182" customWidth="1"/>
+    <col min="30" max="30" width="12.8545454545455" customWidth="1"/>
+    <col min="31" max="31" width="16.1454545454545" customWidth="1"/>
+    <col min="32" max="32" width="15.4272727272727" customWidth="1"/>
+    <col min="33" max="33" width="24.5727272727273" customWidth="1"/>
+    <col min="34" max="34" width="8.57272727272727" customWidth="1"/>
+    <col min="35" max="35" width="14.7181818181818" customWidth="1"/>
+    <col min="36" max="36" width="18.5727272727273" customWidth="1"/>
+    <col min="37" max="37" width="14.1454545454545" customWidth="1"/>
+    <col min="38" max="38" width="14.7181818181818" customWidth="1"/>
+    <col min="39" max="39" width="17.4272727272727" customWidth="1"/>
+    <col min="40" max="40" width="22" customWidth="1"/>
+    <col min="41" max="41" width="17.5727272727273" customWidth="1"/>
+    <col min="42" max="42" width="25.2818181818182" customWidth="1"/>
+    <col min="43" max="43" width="13" customWidth="1"/>
+    <col min="44" max="44" width="23.7181818181818" customWidth="1"/>
+    <col min="45" max="45" width="10" customWidth="1"/>
+    <col min="46" max="46" width="13" customWidth="1"/>
+    <col min="47" max="47" width="15.5727272727273" customWidth="1"/>
+    <col min="48" max="48" width="21.1454545454545" customWidth="1"/>
+    <col min="49" max="49" width="11.5727272727273" customWidth="1"/>
+    <col min="50" max="50" width="16.7181818181818" customWidth="1"/>
+    <col min="51" max="51" width="14" customWidth="1"/>
+    <col min="52" max="52" width="19.4272727272727" customWidth="1"/>
+    <col min="53" max="53" width="18.8545454545455" customWidth="1"/>
+    <col min="54" max="54" width="23.2818181818182" customWidth="1"/>
+    <col min="55" max="55" width="15.5727272727273" customWidth="1"/>
+    <col min="56" max="56" width="14.2818181818182" customWidth="1"/>
+    <col min="57" max="57" width="17" customWidth="1"/>
+    <col min="58" max="58" width="16.2818181818182" customWidth="1"/>
+    <col min="59" max="59" width="13.5727272727273" customWidth="1"/>
+    <col min="60" max="61" width="12.7181818181818" customWidth="1"/>
+    <col min="62" max="62" width="21.8545454545455" customWidth="1"/>
+    <col min="63" max="63" width="30.5727272727273" customWidth="1"/>
+    <col min="64" max="64" width="10" customWidth="1"/>
+    <col min="65" max="65" width="42.5727272727273" customWidth="1"/>
+    <col min="66" max="66" width="38.1454545454545" customWidth="1"/>
+    <col min="67" max="67" width="19.4272727272727" customWidth="1"/>
+    <col min="68" max="68" width="35.4272727272727" customWidth="1"/>
+    <col min="69" max="69" width="9.57272727272727" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -12947,7 +12412,7 @@
       <c r="BP2" s="27"/>
       <c r="BQ2" s="27"/>
     </row>
-    <row r="3" ht="15.75" spans="1:69">
+    <row r="3" ht="15.25" spans="1:69">
       <c r="A3" s="28" t="s">
         <v>9</v>
       </c>
@@ -13156,7 +12621,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.75" spans="1:69">
+    <row r="4" ht="15.25" spans="1:69">
       <c r="A4" s="26">
         <v>1</v>
       </c>
@@ -13320,11 +12785,11 @@
       <c r="AT4" s="35" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" t="s" s="0">
-        <v>136</v>
-      </c>
-      <c r="AV4" t="s" s="0">
-        <v>337</v>
+      <c r="AU4" t="s">
+        <v>148</v>
+      </c>
+      <c r="AV4" t="s">
+        <v>149</v>
       </c>
       <c r="AW4" s="35">
         <f>AM4</f>
@@ -13364,11 +12829,11 @@
       <c r="BL4" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="BM4" t="s" s="0">
-        <v>191</v>
-      </c>
-      <c r="BN4" t="s" s="0">
-        <v>190</v>
+      <c r="BM4" t="s">
+        <v>150</v>
+      </c>
+      <c r="BN4" t="s">
+        <v>151</v>
       </c>
       <c r="BO4" s="35">
         <f>ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
@@ -13525,73 +12990,73 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ5"/>
-  <sheetFormatPr defaultColWidth="8.7047619047619" defaultRowHeight="15" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="5.14285714285714"/>
-    <col min="2" max="3" customWidth="true" width="28.0"/>
-    <col min="4" max="4" customWidth="true" width="79.4285714285714"/>
-    <col min="5" max="5" customWidth="true" width="11.5714285714286"/>
-    <col min="6" max="6" customWidth="true" width="5.14285714285714"/>
-    <col min="7" max="7" customWidth="true" width="11.0"/>
-    <col min="8" max="8" customWidth="true" width="12.7142857142857"/>
-    <col min="9" max="9" customWidth="true" width="5.85714285714286"/>
-    <col min="10" max="10" customWidth="true" width="6.0"/>
-    <col min="11" max="11" customWidth="true" width="5.85714285714286"/>
-    <col min="12" max="12" customWidth="true" width="14.2857142857143"/>
-    <col min="13" max="13" customWidth="true" width="9.42857142857143"/>
-    <col min="14" max="14" customWidth="true" width="14.4285714285714"/>
-    <col min="15" max="15" customWidth="true" width="15.5714285714286"/>
-    <col min="16" max="16" customWidth="true" width="14.4285714285714"/>
-    <col min="17" max="17" customWidth="true" width="39.4285714285714"/>
-    <col min="18" max="18" customWidth="true" width="11.7142857142857"/>
-    <col min="19" max="19" customWidth="true" width="11.8571428571429"/>
-    <col min="20" max="20" customWidth="true" width="6.42857142857143"/>
-    <col min="21" max="22" customWidth="true" width="6.57142857142857"/>
-    <col min="23" max="23" customWidth="true" width="37.1428571428571"/>
-    <col min="24" max="25" customWidth="true" width="8.0"/>
-    <col min="26" max="26" customWidth="true" width="7.71428571428571"/>
-    <col min="27" max="27" customWidth="true" width="6.28571428571429"/>
-    <col min="28" max="28" customWidth="true" width="9.28571428571429"/>
-    <col min="29" max="29" customWidth="true" width="9.71428571428571"/>
-    <col min="30" max="30" customWidth="true" width="12.8571428571429"/>
-    <col min="31" max="31" customWidth="true" width="16.1428571428571"/>
-    <col min="32" max="32" customWidth="true" width="15.4285714285714"/>
-    <col min="33" max="33" customWidth="true" width="24.5714285714286"/>
-    <col min="34" max="34" customWidth="true" width="8.57142857142857"/>
-    <col min="35" max="35" customWidth="true" width="14.7142857142857"/>
-    <col min="36" max="36" customWidth="true" width="18.5714285714286"/>
-    <col min="37" max="37" customWidth="true" width="14.1428571428571"/>
-    <col min="38" max="38" customWidth="true" width="14.7142857142857"/>
-    <col min="39" max="39" customWidth="true" width="17.4285714285714"/>
-    <col min="40" max="40" customWidth="true" width="22.0"/>
-    <col min="41" max="41" customWidth="true" width="17.5714285714286"/>
-    <col min="42" max="42" customWidth="true" width="25.2857142857143"/>
-    <col min="43" max="43" customWidth="true" width="13.0"/>
-    <col min="44" max="44" customWidth="true" width="23.7142857142857"/>
-    <col min="45" max="45" customWidth="true" width="10.0"/>
-    <col min="46" max="46" customWidth="true" width="13.0"/>
-    <col min="47" max="47" customWidth="true" width="15.5714285714286"/>
-    <col min="48" max="48" customWidth="true" width="21.1428571428571"/>
-    <col min="49" max="49" customWidth="true" width="11.5714285714286"/>
-    <col min="50" max="50" customWidth="true" width="16.7142857142857"/>
-    <col min="51" max="51" customWidth="true" width="14.0"/>
-    <col min="52" max="52" customWidth="true" width="19.4285714285714"/>
-    <col min="53" max="53" customWidth="true" width="18.8571428571429"/>
-    <col min="54" max="54" customWidth="true" width="23.2857142857143"/>
-    <col min="55" max="55" customWidth="true" width="15.5714285714286"/>
-    <col min="56" max="56" customWidth="true" width="14.2857142857143"/>
-    <col min="57" max="57" customWidth="true" width="17.0"/>
-    <col min="58" max="58" customWidth="true" width="16.2857142857143"/>
-    <col min="59" max="59" customWidth="true" width="13.5714285714286"/>
-    <col min="60" max="61" customWidth="true" width="12.7142857142857"/>
-    <col min="62" max="62" customWidth="true" width="21.8571428571429"/>
-    <col min="63" max="63" customWidth="true" width="30.5714285714286"/>
-    <col min="64" max="64" customWidth="true" width="10.0"/>
-    <col min="65" max="65" customWidth="true" width="42.5714285714286"/>
-    <col min="66" max="66" customWidth="true" width="38.1428571428571"/>
-    <col min="67" max="67" customWidth="true" width="19.4285714285714"/>
-    <col min="68" max="68" customWidth="true" width="35.4285714285714"/>
-    <col min="69" max="69" customWidth="true" width="9.57142857142857"/>
+    <col min="1" max="1" width="5.14545454545455" customWidth="1"/>
+    <col min="2" max="3" width="28" customWidth="1"/>
+    <col min="4" max="4" width="79.4272727272727" customWidth="1"/>
+    <col min="5" max="5" width="11.5727272727273" customWidth="1"/>
+    <col min="6" max="6" width="5.14545454545455" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="12.7181818181818" customWidth="1"/>
+    <col min="9" max="9" width="5.85454545454545" customWidth="1"/>
+    <col min="10" max="10" width="6" customWidth="1"/>
+    <col min="11" max="11" width="5.85454545454545" customWidth="1"/>
+    <col min="12" max="12" width="14.2818181818182" customWidth="1"/>
+    <col min="13" max="13" width="9.42727272727273" customWidth="1"/>
+    <col min="14" max="14" width="14.4272727272727" customWidth="1"/>
+    <col min="15" max="15" width="15.5727272727273" customWidth="1"/>
+    <col min="16" max="16" width="14.4272727272727" customWidth="1"/>
+    <col min="17" max="17" width="39.4272727272727" customWidth="1"/>
+    <col min="18" max="18" width="11.7181818181818" customWidth="1"/>
+    <col min="19" max="19" width="11.8545454545455" customWidth="1"/>
+    <col min="20" max="20" width="6.42727272727273" customWidth="1"/>
+    <col min="21" max="22" width="6.57272727272727" customWidth="1"/>
+    <col min="23" max="23" width="37.1454545454545" customWidth="1"/>
+    <col min="24" max="25" width="8" customWidth="1"/>
+    <col min="26" max="26" width="7.71818181818182" customWidth="1"/>
+    <col min="27" max="27" width="6.28181818181818" customWidth="1"/>
+    <col min="28" max="28" width="9.28181818181818" customWidth="1"/>
+    <col min="29" max="29" width="9.71818181818182" customWidth="1"/>
+    <col min="30" max="30" width="12.8545454545455" customWidth="1"/>
+    <col min="31" max="31" width="16.1454545454545" customWidth="1"/>
+    <col min="32" max="32" width="15.4272727272727" customWidth="1"/>
+    <col min="33" max="33" width="24.5727272727273" customWidth="1"/>
+    <col min="34" max="34" width="8.57272727272727" customWidth="1"/>
+    <col min="35" max="35" width="14.7181818181818" customWidth="1"/>
+    <col min="36" max="36" width="18.5727272727273" customWidth="1"/>
+    <col min="37" max="37" width="14.1454545454545" customWidth="1"/>
+    <col min="38" max="38" width="14.7181818181818" customWidth="1"/>
+    <col min="39" max="39" width="17.4272727272727" customWidth="1"/>
+    <col min="40" max="40" width="22" customWidth="1"/>
+    <col min="41" max="41" width="17.5727272727273" customWidth="1"/>
+    <col min="42" max="42" width="25.2818181818182" customWidth="1"/>
+    <col min="43" max="43" width="13" customWidth="1"/>
+    <col min="44" max="44" width="23.7181818181818" customWidth="1"/>
+    <col min="45" max="45" width="10" customWidth="1"/>
+    <col min="46" max="46" width="13" customWidth="1"/>
+    <col min="47" max="47" width="15.5727272727273" customWidth="1"/>
+    <col min="48" max="48" width="21.1454545454545" customWidth="1"/>
+    <col min="49" max="49" width="11.5727272727273" customWidth="1"/>
+    <col min="50" max="50" width="16.7181818181818" customWidth="1"/>
+    <col min="51" max="51" width="14" customWidth="1"/>
+    <col min="52" max="52" width="19.4272727272727" customWidth="1"/>
+    <col min="53" max="53" width="18.8545454545455" customWidth="1"/>
+    <col min="54" max="54" width="23.2818181818182" customWidth="1"/>
+    <col min="55" max="55" width="15.5727272727273" customWidth="1"/>
+    <col min="56" max="56" width="14.2818181818182" customWidth="1"/>
+    <col min="57" max="57" width="17" customWidth="1"/>
+    <col min="58" max="58" width="16.2818181818182" customWidth="1"/>
+    <col min="59" max="59" width="13.5727272727273" customWidth="1"/>
+    <col min="60" max="61" width="12.7181818181818" customWidth="1"/>
+    <col min="62" max="62" width="21.8545454545455" customWidth="1"/>
+    <col min="63" max="63" width="30.5727272727273" customWidth="1"/>
+    <col min="64" max="64" width="10" customWidth="1"/>
+    <col min="65" max="65" width="42.5727272727273" customWidth="1"/>
+    <col min="66" max="66" width="38.1454545454545" customWidth="1"/>
+    <col min="67" max="67" width="19.4272727272727" customWidth="1"/>
+    <col min="68" max="68" width="35.4272727272727" customWidth="1"/>
+    <col min="69" max="69" width="9.57272727272727" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -13762,7 +13227,7 @@
       <c r="BP2" s="27"/>
       <c r="BQ2" s="27"/>
     </row>
-    <row r="3" ht="15.75" spans="1:69">
+    <row r="3" ht="15.25" spans="1:69">
       <c r="A3" s="28" t="s">
         <v>9</v>
       </c>
@@ -13971,7 +13436,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.75" spans="1:69">
+    <row r="4" ht="15.25" spans="1:69">
       <c r="A4" s="26">
         <v>1</v>
       </c>
@@ -14135,11 +13600,11 @@
       <c r="AT4" s="35" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" t="s" s="0">
-        <v>338</v>
-      </c>
-      <c r="AV4" t="s" s="0">
-        <v>339</v>
+      <c r="AU4" t="s">
+        <v>152</v>
+      </c>
+      <c r="AV4" t="s">
+        <v>153</v>
       </c>
       <c r="AW4" s="35">
         <f>AM4</f>
@@ -14179,11 +13644,11 @@
       <c r="BL4" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="BM4" t="s" s="0">
-        <v>187</v>
-      </c>
-      <c r="BN4" t="s" s="0">
-        <v>186</v>
+      <c r="BM4" t="s">
+        <v>145</v>
+      </c>
+      <c r="BN4" t="s">
+        <v>146</v>
       </c>
       <c r="BO4" s="35">
         <f>ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
@@ -14328,73 +13793,73 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ5"/>
-  <sheetFormatPr defaultColWidth="8.7047619047619" defaultRowHeight="15" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="5.14285714285714"/>
-    <col min="2" max="3" customWidth="true" width="28.0"/>
-    <col min="4" max="4" customWidth="true" width="79.4285714285714"/>
-    <col min="5" max="5" customWidth="true" width="11.5714285714286"/>
-    <col min="6" max="6" customWidth="true" width="5.14285714285714"/>
-    <col min="7" max="7" customWidth="true" width="11.0"/>
-    <col min="8" max="8" customWidth="true" width="12.7142857142857"/>
-    <col min="9" max="9" customWidth="true" width="5.85714285714286"/>
-    <col min="10" max="10" customWidth="true" width="6.0"/>
-    <col min="11" max="11" customWidth="true" width="5.85714285714286"/>
-    <col min="12" max="12" customWidth="true" width="14.2857142857143"/>
-    <col min="13" max="13" customWidth="true" width="9.42857142857143"/>
-    <col min="14" max="14" customWidth="true" width="14.4285714285714"/>
-    <col min="15" max="15" customWidth="true" width="15.5714285714286"/>
-    <col min="16" max="16" customWidth="true" width="14.4285714285714"/>
-    <col min="17" max="17" customWidth="true" width="39.4285714285714"/>
-    <col min="18" max="18" customWidth="true" width="11.7142857142857"/>
-    <col min="19" max="19" customWidth="true" width="11.8571428571429"/>
-    <col min="20" max="20" customWidth="true" width="6.42857142857143"/>
-    <col min="21" max="22" customWidth="true" width="6.57142857142857"/>
-    <col min="23" max="23" customWidth="true" width="37.1428571428571"/>
-    <col min="24" max="25" customWidth="true" width="8.0"/>
-    <col min="26" max="26" customWidth="true" width="7.71428571428571"/>
-    <col min="27" max="27" customWidth="true" width="6.28571428571429"/>
-    <col min="28" max="28" customWidth="true" width="9.28571428571429"/>
-    <col min="29" max="29" customWidth="true" width="9.71428571428571"/>
-    <col min="30" max="30" customWidth="true" width="12.8571428571429"/>
-    <col min="31" max="31" customWidth="true" width="16.1428571428571"/>
-    <col min="32" max="32" customWidth="true" width="15.4285714285714"/>
-    <col min="33" max="33" customWidth="true" width="24.5714285714286"/>
-    <col min="34" max="34" customWidth="true" width="8.57142857142857"/>
-    <col min="35" max="35" customWidth="true" width="14.7142857142857"/>
-    <col min="36" max="36" customWidth="true" width="18.5714285714286"/>
-    <col min="37" max="37" customWidth="true" width="14.1428571428571"/>
-    <col min="38" max="38" customWidth="true" width="14.7142857142857"/>
-    <col min="39" max="39" customWidth="true" width="17.4285714285714"/>
-    <col min="40" max="40" customWidth="true" width="22.0"/>
-    <col min="41" max="41" customWidth="true" width="17.5714285714286"/>
-    <col min="42" max="42" customWidth="true" width="25.2857142857143"/>
-    <col min="43" max="43" customWidth="true" width="13.0"/>
-    <col min="44" max="44" customWidth="true" width="23.7142857142857"/>
-    <col min="45" max="45" customWidth="true" width="10.0"/>
-    <col min="46" max="46" customWidth="true" width="13.0"/>
-    <col min="47" max="47" customWidth="true" width="15.5714285714286"/>
-    <col min="48" max="48" customWidth="true" width="21.1428571428571"/>
-    <col min="49" max="49" customWidth="true" width="11.5714285714286"/>
-    <col min="50" max="50" customWidth="true" width="16.7142857142857"/>
-    <col min="51" max="51" customWidth="true" width="14.0"/>
-    <col min="52" max="52" customWidth="true" width="19.4285714285714"/>
-    <col min="53" max="53" customWidth="true" width="18.8571428571429"/>
-    <col min="54" max="54" customWidth="true" width="23.2857142857143"/>
-    <col min="55" max="55" customWidth="true" width="15.5714285714286"/>
-    <col min="56" max="56" customWidth="true" width="14.2857142857143"/>
-    <col min="57" max="57" customWidth="true" width="17.0"/>
-    <col min="58" max="58" customWidth="true" width="16.2857142857143"/>
-    <col min="59" max="59" customWidth="true" width="13.5714285714286"/>
-    <col min="60" max="61" customWidth="true" width="12.7142857142857"/>
-    <col min="62" max="62" customWidth="true" width="21.8571428571429"/>
-    <col min="63" max="63" customWidth="true" width="30.5714285714286"/>
-    <col min="64" max="64" customWidth="true" width="10.0"/>
-    <col min="65" max="65" customWidth="true" width="42.5714285714286"/>
-    <col min="66" max="66" customWidth="true" width="38.1428571428571"/>
-    <col min="67" max="67" customWidth="true" width="19.4285714285714"/>
-    <col min="68" max="68" customWidth="true" width="35.4285714285714"/>
-    <col min="69" max="69" customWidth="true" width="9.57142857142857"/>
+    <col min="1" max="1" width="5.14545454545455" customWidth="1"/>
+    <col min="2" max="3" width="28" customWidth="1"/>
+    <col min="4" max="4" width="79.4272727272727" customWidth="1"/>
+    <col min="5" max="5" width="11.5727272727273" customWidth="1"/>
+    <col min="6" max="6" width="5.14545454545455" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="12.7181818181818" customWidth="1"/>
+    <col min="9" max="9" width="5.85454545454545" customWidth="1"/>
+    <col min="10" max="10" width="6" customWidth="1"/>
+    <col min="11" max="11" width="5.85454545454545" customWidth="1"/>
+    <col min="12" max="12" width="14.2818181818182" customWidth="1"/>
+    <col min="13" max="13" width="9.42727272727273" customWidth="1"/>
+    <col min="14" max="14" width="14.4272727272727" customWidth="1"/>
+    <col min="15" max="15" width="15.5727272727273" customWidth="1"/>
+    <col min="16" max="16" width="14.4272727272727" customWidth="1"/>
+    <col min="17" max="17" width="39.4272727272727" customWidth="1"/>
+    <col min="18" max="18" width="11.7181818181818" customWidth="1"/>
+    <col min="19" max="19" width="11.8545454545455" customWidth="1"/>
+    <col min="20" max="20" width="6.42727272727273" customWidth="1"/>
+    <col min="21" max="22" width="6.57272727272727" customWidth="1"/>
+    <col min="23" max="23" width="37.1454545454545" customWidth="1"/>
+    <col min="24" max="25" width="8" customWidth="1"/>
+    <col min="26" max="26" width="7.71818181818182" customWidth="1"/>
+    <col min="27" max="27" width="6.28181818181818" customWidth="1"/>
+    <col min="28" max="28" width="9.28181818181818" customWidth="1"/>
+    <col min="29" max="29" width="9.71818181818182" customWidth="1"/>
+    <col min="30" max="30" width="12.8545454545455" customWidth="1"/>
+    <col min="31" max="31" width="16.1454545454545" customWidth="1"/>
+    <col min="32" max="32" width="15.4272727272727" customWidth="1"/>
+    <col min="33" max="33" width="24.5727272727273" customWidth="1"/>
+    <col min="34" max="34" width="8.57272727272727" customWidth="1"/>
+    <col min="35" max="35" width="14.7181818181818" customWidth="1"/>
+    <col min="36" max="36" width="18.5727272727273" customWidth="1"/>
+    <col min="37" max="37" width="14.1454545454545" customWidth="1"/>
+    <col min="38" max="38" width="14.7181818181818" customWidth="1"/>
+    <col min="39" max="39" width="17.4272727272727" customWidth="1"/>
+    <col min="40" max="40" width="22" customWidth="1"/>
+    <col min="41" max="41" width="17.5727272727273" customWidth="1"/>
+    <col min="42" max="42" width="25.2818181818182" customWidth="1"/>
+    <col min="43" max="43" width="13" customWidth="1"/>
+    <col min="44" max="44" width="23.7181818181818" customWidth="1"/>
+    <col min="45" max="45" width="10" customWidth="1"/>
+    <col min="46" max="46" width="13" customWidth="1"/>
+    <col min="47" max="47" width="15.5727272727273" customWidth="1"/>
+    <col min="48" max="48" width="21.1454545454545" customWidth="1"/>
+    <col min="49" max="49" width="11.5727272727273" customWidth="1"/>
+    <col min="50" max="50" width="16.7181818181818" customWidth="1"/>
+    <col min="51" max="51" width="14" customWidth="1"/>
+    <col min="52" max="52" width="19.4272727272727" customWidth="1"/>
+    <col min="53" max="53" width="18.8545454545455" customWidth="1"/>
+    <col min="54" max="54" width="23.2818181818182" customWidth="1"/>
+    <col min="55" max="55" width="15.5727272727273" customWidth="1"/>
+    <col min="56" max="56" width="14.2818181818182" customWidth="1"/>
+    <col min="57" max="57" width="17" customWidth="1"/>
+    <col min="58" max="58" width="16.2818181818182" customWidth="1"/>
+    <col min="59" max="59" width="13.5727272727273" customWidth="1"/>
+    <col min="60" max="61" width="12.7181818181818" customWidth="1"/>
+    <col min="62" max="62" width="21.8545454545455" customWidth="1"/>
+    <col min="63" max="63" width="30.5727272727273" customWidth="1"/>
+    <col min="64" max="64" width="10" customWidth="1"/>
+    <col min="65" max="65" width="42.5727272727273" customWidth="1"/>
+    <col min="66" max="66" width="38.1454545454545" customWidth="1"/>
+    <col min="67" max="67" width="19.4272727272727" customWidth="1"/>
+    <col min="68" max="68" width="35.4272727272727" customWidth="1"/>
+    <col min="69" max="69" width="9.57272727272727" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -14565,7 +14030,7 @@
       <c r="BP2" s="27"/>
       <c r="BQ2" s="27"/>
     </row>
-    <row r="3" ht="15.75" spans="1:69">
+    <row r="3" ht="15.25" spans="1:69">
       <c r="A3" s="28" t="s">
         <v>9</v>
       </c>
@@ -14774,7 +14239,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.75" spans="1:69">
+    <row r="4" ht="15.25" spans="1:69">
       <c r="A4" s="26">
         <v>1</v>
       </c>
@@ -14938,11 +14403,11 @@
       <c r="AT4" s="35" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" t="s" s="0">
-        <v>340</v>
-      </c>
-      <c r="AV4" t="s" s="0">
-        <v>341</v>
+      <c r="AU4" t="s">
+        <v>154</v>
+      </c>
+      <c r="AV4" t="s">
+        <v>155</v>
       </c>
       <c r="AW4" s="35">
         <f>AM4</f>
@@ -14982,11 +14447,11 @@
       <c r="BL4" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="BM4" t="s" s="0">
-        <v>191</v>
-      </c>
-      <c r="BN4" t="s" s="0">
-        <v>190</v>
+      <c r="BM4" t="s">
+        <v>150</v>
+      </c>
+      <c r="BN4" t="s">
+        <v>151</v>
       </c>
       <c r="BO4" s="35">
         <f>ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
@@ -15131,73 +14596,73 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ5"/>
-  <sheetFormatPr defaultColWidth="8.7047619047619" defaultRowHeight="15" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="5.14285714285714"/>
-    <col min="2" max="3" customWidth="true" width="27.5714285714286"/>
-    <col min="4" max="4" customWidth="true" width="79.4285714285714"/>
-    <col min="5" max="5" customWidth="true" width="11.5714285714286"/>
-    <col min="6" max="6" customWidth="true" width="5.14285714285714"/>
-    <col min="7" max="7" customWidth="true" width="11.0"/>
-    <col min="8" max="8" customWidth="true" width="12.7142857142857"/>
-    <col min="9" max="9" customWidth="true" width="5.85714285714286"/>
-    <col min="10" max="10" customWidth="true" width="6.0"/>
-    <col min="11" max="11" customWidth="true" width="5.85714285714286"/>
-    <col min="12" max="12" customWidth="true" width="14.2857142857143"/>
-    <col min="13" max="13" customWidth="true" width="9.42857142857143"/>
-    <col min="14" max="14" customWidth="true" width="14.4285714285714"/>
-    <col min="15" max="15" customWidth="true" width="15.5714285714286"/>
-    <col min="16" max="16" customWidth="true" width="14.4285714285714"/>
-    <col min="17" max="17" customWidth="true" width="39.4285714285714"/>
-    <col min="18" max="18" customWidth="true" width="11.7142857142857"/>
-    <col min="19" max="19" customWidth="true" width="11.8571428571429"/>
-    <col min="20" max="20" customWidth="true" width="6.42857142857143"/>
-    <col min="21" max="22" customWidth="true" width="6.57142857142857"/>
-    <col min="23" max="23" customWidth="true" width="37.1428571428571"/>
-    <col min="24" max="25" customWidth="true" width="8.0"/>
-    <col min="26" max="26" customWidth="true" width="7.71428571428571"/>
-    <col min="27" max="27" customWidth="true" width="6.28571428571429"/>
-    <col min="28" max="28" customWidth="true" width="9.28571428571429"/>
-    <col min="29" max="29" customWidth="true" width="9.71428571428571"/>
-    <col min="30" max="30" customWidth="true" width="12.8571428571429"/>
-    <col min="31" max="31" customWidth="true" width="16.1428571428571"/>
-    <col min="32" max="32" customWidth="true" width="15.4285714285714"/>
-    <col min="33" max="33" customWidth="true" width="24.5714285714286"/>
-    <col min="34" max="34" customWidth="true" width="8.57142857142857"/>
-    <col min="35" max="35" customWidth="true" width="14.7142857142857"/>
-    <col min="36" max="36" customWidth="true" width="18.5714285714286"/>
-    <col min="37" max="37" customWidth="true" width="14.1428571428571"/>
-    <col min="38" max="38" customWidth="true" width="14.7142857142857"/>
-    <col min="39" max="39" customWidth="true" width="17.4285714285714"/>
-    <col min="40" max="40" customWidth="true" width="22.0"/>
-    <col min="41" max="41" customWidth="true" width="17.5714285714286"/>
-    <col min="42" max="42" customWidth="true" width="25.2857142857143"/>
-    <col min="43" max="43" customWidth="true" width="13.0"/>
-    <col min="44" max="44" customWidth="true" width="23.7142857142857"/>
-    <col min="45" max="45" customWidth="true" width="10.0"/>
-    <col min="46" max="46" customWidth="true" width="13.0"/>
-    <col min="47" max="47" customWidth="true" width="15.5714285714286"/>
-    <col min="48" max="48" customWidth="true" width="21.1428571428571"/>
-    <col min="49" max="49" customWidth="true" width="11.5714285714286"/>
-    <col min="50" max="50" customWidth="true" width="16.7142857142857"/>
-    <col min="51" max="51" customWidth="true" width="14.0"/>
-    <col min="52" max="52" customWidth="true" width="19.4285714285714"/>
-    <col min="53" max="53" customWidth="true" width="18.8571428571429"/>
-    <col min="54" max="54" customWidth="true" width="23.2857142857143"/>
-    <col min="55" max="55" customWidth="true" width="15.5714285714286"/>
-    <col min="56" max="56" customWidth="true" width="14.2857142857143"/>
-    <col min="57" max="57" customWidth="true" width="17.0"/>
-    <col min="58" max="58" customWidth="true" width="16.2857142857143"/>
-    <col min="59" max="59" customWidth="true" width="13.5714285714286"/>
-    <col min="60" max="61" customWidth="true" width="12.7142857142857"/>
-    <col min="62" max="62" customWidth="true" width="21.8571428571429"/>
-    <col min="63" max="63" customWidth="true" width="30.5714285714286"/>
-    <col min="64" max="64" customWidth="true" width="10.0"/>
-    <col min="65" max="65" customWidth="true" width="42.5714285714286"/>
-    <col min="66" max="66" customWidth="true" width="38.1428571428571"/>
-    <col min="67" max="67" customWidth="true" width="19.4285714285714"/>
-    <col min="68" max="68" customWidth="true" width="35.4285714285714"/>
-    <col min="69" max="69" customWidth="true" width="9.57142857142857"/>
+    <col min="1" max="1" width="5.14545454545455" customWidth="1"/>
+    <col min="2" max="3" width="27.5727272727273" customWidth="1"/>
+    <col min="4" max="4" width="79.4272727272727" customWidth="1"/>
+    <col min="5" max="5" width="11.5727272727273" customWidth="1"/>
+    <col min="6" max="6" width="5.14545454545455" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="12.7181818181818" customWidth="1"/>
+    <col min="9" max="9" width="5.85454545454545" customWidth="1"/>
+    <col min="10" max="10" width="6" customWidth="1"/>
+    <col min="11" max="11" width="5.85454545454545" customWidth="1"/>
+    <col min="12" max="12" width="14.2818181818182" customWidth="1"/>
+    <col min="13" max="13" width="9.42727272727273" customWidth="1"/>
+    <col min="14" max="14" width="14.4272727272727" customWidth="1"/>
+    <col min="15" max="15" width="15.5727272727273" customWidth="1"/>
+    <col min="16" max="16" width="14.4272727272727" customWidth="1"/>
+    <col min="17" max="17" width="39.4272727272727" customWidth="1"/>
+    <col min="18" max="18" width="11.7181818181818" customWidth="1"/>
+    <col min="19" max="19" width="11.8545454545455" customWidth="1"/>
+    <col min="20" max="20" width="6.42727272727273" customWidth="1"/>
+    <col min="21" max="22" width="6.57272727272727" customWidth="1"/>
+    <col min="23" max="23" width="37.1454545454545" customWidth="1"/>
+    <col min="24" max="25" width="8" customWidth="1"/>
+    <col min="26" max="26" width="7.71818181818182" customWidth="1"/>
+    <col min="27" max="27" width="6.28181818181818" customWidth="1"/>
+    <col min="28" max="28" width="9.28181818181818" customWidth="1"/>
+    <col min="29" max="29" width="9.71818181818182" customWidth="1"/>
+    <col min="30" max="30" width="12.8545454545455" customWidth="1"/>
+    <col min="31" max="31" width="16.1454545454545" customWidth="1"/>
+    <col min="32" max="32" width="15.4272727272727" customWidth="1"/>
+    <col min="33" max="33" width="24.5727272727273" customWidth="1"/>
+    <col min="34" max="34" width="8.57272727272727" customWidth="1"/>
+    <col min="35" max="35" width="14.7181818181818" customWidth="1"/>
+    <col min="36" max="36" width="18.5727272727273" customWidth="1"/>
+    <col min="37" max="37" width="14.1454545454545" customWidth="1"/>
+    <col min="38" max="38" width="14.7181818181818" customWidth="1"/>
+    <col min="39" max="39" width="17.4272727272727" customWidth="1"/>
+    <col min="40" max="40" width="22" customWidth="1"/>
+    <col min="41" max="41" width="17.5727272727273" customWidth="1"/>
+    <col min="42" max="42" width="25.2818181818182" customWidth="1"/>
+    <col min="43" max="43" width="13" customWidth="1"/>
+    <col min="44" max="44" width="23.7181818181818" customWidth="1"/>
+    <col min="45" max="45" width="10" customWidth="1"/>
+    <col min="46" max="46" width="13" customWidth="1"/>
+    <col min="47" max="47" width="15.5727272727273" customWidth="1"/>
+    <col min="48" max="48" width="21.1454545454545" customWidth="1"/>
+    <col min="49" max="49" width="11.5727272727273" customWidth="1"/>
+    <col min="50" max="50" width="16.7181818181818" customWidth="1"/>
+    <col min="51" max="51" width="14" customWidth="1"/>
+    <col min="52" max="52" width="19.4272727272727" customWidth="1"/>
+    <col min="53" max="53" width="18.8545454545455" customWidth="1"/>
+    <col min="54" max="54" width="23.2818181818182" customWidth="1"/>
+    <col min="55" max="55" width="15.5727272727273" customWidth="1"/>
+    <col min="56" max="56" width="14.2818181818182" customWidth="1"/>
+    <col min="57" max="57" width="17" customWidth="1"/>
+    <col min="58" max="58" width="16.2818181818182" customWidth="1"/>
+    <col min="59" max="59" width="13.5727272727273" customWidth="1"/>
+    <col min="60" max="61" width="12.7181818181818" customWidth="1"/>
+    <col min="62" max="62" width="21.8545454545455" customWidth="1"/>
+    <col min="63" max="63" width="30.5727272727273" customWidth="1"/>
+    <col min="64" max="64" width="10" customWidth="1"/>
+    <col min="65" max="65" width="42.5727272727273" customWidth="1"/>
+    <col min="66" max="66" width="38.1454545454545" customWidth="1"/>
+    <col min="67" max="67" width="19.4272727272727" customWidth="1"/>
+    <col min="68" max="68" width="35.4272727272727" customWidth="1"/>
+    <col min="69" max="69" width="9.57272727272727" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -15368,7 +14833,7 @@
       <c r="BP2" s="27"/>
       <c r="BQ2" s="27"/>
     </row>
-    <row r="3" ht="15.75" spans="1:69">
+    <row r="3" ht="15.25" spans="1:69">
       <c r="A3" s="28" t="s">
         <v>9</v>
       </c>
@@ -15577,15 +15042,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.75" spans="1:69">
+    <row r="4" ht="15.25" spans="1:69">
       <c r="A4" s="26">
         <v>1</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="C4" s="26" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D4" s="26" t="s">
         <v>76</v>
@@ -15741,11 +15206,11 @@
       <c r="AT4" s="35" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" t="s" s="0">
-        <v>342</v>
-      </c>
-      <c r="AV4" t="s" s="0">
-        <v>343</v>
+      <c r="AU4" t="s">
+        <v>157</v>
+      </c>
+      <c r="AV4" t="s">
+        <v>158</v>
       </c>
       <c r="AW4" s="35">
         <f>AM4</f>
@@ -15785,11 +15250,11 @@
       <c r="BL4" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="BM4" t="s" s="0">
-        <v>249</v>
-      </c>
-      <c r="BN4" t="s" s="0">
-        <v>248</v>
+      <c r="BM4" t="s">
+        <v>159</v>
+      </c>
+      <c r="BN4" t="s">
+        <v>160</v>
       </c>
       <c r="BO4" s="35">
         <f>ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
@@ -15946,73 +15411,73 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ5"/>
-  <sheetFormatPr defaultColWidth="8.7047619047619" defaultRowHeight="15" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="5.14285714285714"/>
-    <col min="2" max="3" customWidth="true" width="27.5714285714286"/>
-    <col min="4" max="4" customWidth="true" width="79.4285714285714"/>
-    <col min="5" max="5" customWidth="true" width="11.5714285714286"/>
-    <col min="6" max="6" customWidth="true" width="5.14285714285714"/>
-    <col min="7" max="7" customWidth="true" width="11.0"/>
-    <col min="8" max="8" customWidth="true" width="12.7142857142857"/>
-    <col min="9" max="9" customWidth="true" width="5.85714285714286"/>
-    <col min="10" max="10" customWidth="true" width="6.0"/>
-    <col min="11" max="11" customWidth="true" width="5.85714285714286"/>
-    <col min="12" max="12" customWidth="true" width="14.2857142857143"/>
-    <col min="13" max="13" customWidth="true" width="9.42857142857143"/>
-    <col min="14" max="14" customWidth="true" width="14.4285714285714"/>
-    <col min="15" max="15" customWidth="true" width="15.5714285714286"/>
-    <col min="16" max="16" customWidth="true" width="14.4285714285714"/>
-    <col min="17" max="17" customWidth="true" width="39.4285714285714"/>
-    <col min="18" max="18" customWidth="true" width="11.7142857142857"/>
-    <col min="19" max="19" customWidth="true" width="11.8571428571429"/>
-    <col min="20" max="20" customWidth="true" width="6.42857142857143"/>
-    <col min="21" max="22" customWidth="true" width="6.57142857142857"/>
-    <col min="23" max="23" customWidth="true" width="37.1428571428571"/>
-    <col min="24" max="25" customWidth="true" width="8.0"/>
-    <col min="26" max="26" customWidth="true" width="7.71428571428571"/>
-    <col min="27" max="27" customWidth="true" width="6.28571428571429"/>
-    <col min="28" max="28" customWidth="true" width="9.28571428571429"/>
-    <col min="29" max="29" customWidth="true" width="9.71428571428571"/>
-    <col min="30" max="30" customWidth="true" width="12.8571428571429"/>
-    <col min="31" max="31" customWidth="true" width="16.1428571428571"/>
-    <col min="32" max="32" customWidth="true" width="15.4285714285714"/>
-    <col min="33" max="33" customWidth="true" width="24.5714285714286"/>
-    <col min="34" max="34" customWidth="true" width="8.57142857142857"/>
-    <col min="35" max="35" customWidth="true" width="14.7142857142857"/>
-    <col min="36" max="36" customWidth="true" width="18.5714285714286"/>
-    <col min="37" max="37" customWidth="true" width="14.1428571428571"/>
-    <col min="38" max="38" customWidth="true" width="14.7142857142857"/>
-    <col min="39" max="39" customWidth="true" width="17.4285714285714"/>
-    <col min="40" max="40" customWidth="true" width="22.0"/>
-    <col min="41" max="41" customWidth="true" width="17.5714285714286"/>
-    <col min="42" max="42" customWidth="true" width="25.2857142857143"/>
-    <col min="43" max="43" customWidth="true" width="13.0"/>
-    <col min="44" max="44" customWidth="true" width="23.7142857142857"/>
-    <col min="45" max="45" customWidth="true" width="10.0"/>
-    <col min="46" max="46" customWidth="true" width="13.0"/>
-    <col min="47" max="47" customWidth="true" width="15.5714285714286"/>
-    <col min="48" max="48" customWidth="true" width="21.1428571428571"/>
-    <col min="49" max="49" customWidth="true" width="11.5714285714286"/>
-    <col min="50" max="50" customWidth="true" width="16.7142857142857"/>
-    <col min="51" max="51" customWidth="true" width="14.0"/>
-    <col min="52" max="52" customWidth="true" width="19.4285714285714"/>
-    <col min="53" max="53" customWidth="true" width="18.8571428571429"/>
-    <col min="54" max="54" customWidth="true" width="23.2857142857143"/>
-    <col min="55" max="55" customWidth="true" width="15.5714285714286"/>
-    <col min="56" max="56" customWidth="true" width="14.2857142857143"/>
-    <col min="57" max="57" customWidth="true" width="17.0"/>
-    <col min="58" max="58" customWidth="true" width="16.2857142857143"/>
-    <col min="59" max="59" customWidth="true" width="13.5714285714286"/>
-    <col min="60" max="61" customWidth="true" width="12.7142857142857"/>
-    <col min="62" max="62" customWidth="true" width="21.8571428571429"/>
-    <col min="63" max="63" customWidth="true" width="30.5714285714286"/>
-    <col min="64" max="64" customWidth="true" width="10.0"/>
-    <col min="65" max="65" customWidth="true" width="42.5714285714286"/>
-    <col min="66" max="66" customWidth="true" width="38.1428571428571"/>
-    <col min="67" max="67" customWidth="true" width="19.4285714285714"/>
-    <col min="68" max="68" customWidth="true" width="35.4285714285714"/>
-    <col min="69" max="69" customWidth="true" width="9.57142857142857"/>
+    <col min="1" max="1" width="5.14545454545455" customWidth="1"/>
+    <col min="2" max="3" width="27.5727272727273" customWidth="1"/>
+    <col min="4" max="4" width="79.4272727272727" customWidth="1"/>
+    <col min="5" max="5" width="11.5727272727273" customWidth="1"/>
+    <col min="6" max="6" width="5.14545454545455" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="12.7181818181818" customWidth="1"/>
+    <col min="9" max="9" width="5.85454545454545" customWidth="1"/>
+    <col min="10" max="10" width="6" customWidth="1"/>
+    <col min="11" max="11" width="5.85454545454545" customWidth="1"/>
+    <col min="12" max="12" width="14.2818181818182" customWidth="1"/>
+    <col min="13" max="13" width="9.42727272727273" customWidth="1"/>
+    <col min="14" max="14" width="14.4272727272727" customWidth="1"/>
+    <col min="15" max="15" width="15.5727272727273" customWidth="1"/>
+    <col min="16" max="16" width="14.4272727272727" customWidth="1"/>
+    <col min="17" max="17" width="39.4272727272727" customWidth="1"/>
+    <col min="18" max="18" width="11.7181818181818" customWidth="1"/>
+    <col min="19" max="19" width="11.8545454545455" customWidth="1"/>
+    <col min="20" max="20" width="6.42727272727273" customWidth="1"/>
+    <col min="21" max="22" width="6.57272727272727" customWidth="1"/>
+    <col min="23" max="23" width="37.1454545454545" customWidth="1"/>
+    <col min="24" max="25" width="8" customWidth="1"/>
+    <col min="26" max="26" width="7.71818181818182" customWidth="1"/>
+    <col min="27" max="27" width="6.28181818181818" customWidth="1"/>
+    <col min="28" max="28" width="9.28181818181818" customWidth="1"/>
+    <col min="29" max="29" width="9.71818181818182" customWidth="1"/>
+    <col min="30" max="30" width="12.8545454545455" customWidth="1"/>
+    <col min="31" max="31" width="16.1454545454545" customWidth="1"/>
+    <col min="32" max="32" width="15.4272727272727" customWidth="1"/>
+    <col min="33" max="33" width="24.5727272727273" customWidth="1"/>
+    <col min="34" max="34" width="8.57272727272727" customWidth="1"/>
+    <col min="35" max="35" width="14.7181818181818" customWidth="1"/>
+    <col min="36" max="36" width="18.5727272727273" customWidth="1"/>
+    <col min="37" max="37" width="14.1454545454545" customWidth="1"/>
+    <col min="38" max="38" width="14.7181818181818" customWidth="1"/>
+    <col min="39" max="39" width="17.4272727272727" customWidth="1"/>
+    <col min="40" max="40" width="22" customWidth="1"/>
+    <col min="41" max="41" width="17.5727272727273" customWidth="1"/>
+    <col min="42" max="42" width="25.2818181818182" customWidth="1"/>
+    <col min="43" max="43" width="13" customWidth="1"/>
+    <col min="44" max="44" width="23.7181818181818" customWidth="1"/>
+    <col min="45" max="45" width="10" customWidth="1"/>
+    <col min="46" max="46" width="13" customWidth="1"/>
+    <col min="47" max="47" width="15.5727272727273" customWidth="1"/>
+    <col min="48" max="48" width="21.1454545454545" customWidth="1"/>
+    <col min="49" max="49" width="11.5727272727273" customWidth="1"/>
+    <col min="50" max="50" width="16.7181818181818" customWidth="1"/>
+    <col min="51" max="51" width="14" customWidth="1"/>
+    <col min="52" max="52" width="19.4272727272727" customWidth="1"/>
+    <col min="53" max="53" width="18.8545454545455" customWidth="1"/>
+    <col min="54" max="54" width="23.2818181818182" customWidth="1"/>
+    <col min="55" max="55" width="15.5727272727273" customWidth="1"/>
+    <col min="56" max="56" width="14.2818181818182" customWidth="1"/>
+    <col min="57" max="57" width="17" customWidth="1"/>
+    <col min="58" max="58" width="16.2818181818182" customWidth="1"/>
+    <col min="59" max="59" width="13.5727272727273" customWidth="1"/>
+    <col min="60" max="61" width="12.7181818181818" customWidth="1"/>
+    <col min="62" max="62" width="21.8545454545455" customWidth="1"/>
+    <col min="63" max="63" width="30.5727272727273" customWidth="1"/>
+    <col min="64" max="64" width="10" customWidth="1"/>
+    <col min="65" max="65" width="42.5727272727273" customWidth="1"/>
+    <col min="66" max="66" width="38.1454545454545" customWidth="1"/>
+    <col min="67" max="67" width="19.4272727272727" customWidth="1"/>
+    <col min="68" max="68" width="35.4272727272727" customWidth="1"/>
+    <col min="69" max="69" width="9.57272727272727" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -16183,7 +15648,7 @@
       <c r="BP2" s="27"/>
       <c r="BQ2" s="27"/>
     </row>
-    <row r="3" ht="15.75" spans="1:69">
+    <row r="3" ht="15.25" spans="1:69">
       <c r="A3" s="28" t="s">
         <v>9</v>
       </c>
@@ -16392,15 +15857,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.75" spans="1:69">
+    <row r="4" ht="15.25" spans="1:69">
       <c r="A4" s="26">
         <v>1</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="C4" s="26" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="D4" s="26" t="s">
         <v>76</v>
@@ -16556,11 +16021,11 @@
       <c r="AT4" s="35" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" t="s" s="0">
-        <v>344</v>
-      </c>
-      <c r="AV4" t="s" s="0">
-        <v>345</v>
+      <c r="AU4" t="s">
+        <v>162</v>
+      </c>
+      <c r="AV4" t="s">
+        <v>163</v>
       </c>
       <c r="AW4" s="35">
         <f>AM4</f>
@@ -16600,11 +16065,11 @@
       <c r="BL4" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="BM4" t="s" s="0">
-        <v>253</v>
-      </c>
-      <c r="BN4" t="s" s="0">
-        <v>252</v>
+      <c r="BM4" t="s">
+        <v>164</v>
+      </c>
+      <c r="BN4" t="s">
+        <v>165</v>
       </c>
       <c r="BO4" s="35">
         <f>ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
@@ -16761,73 +16226,73 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ5"/>
-  <sheetFormatPr defaultColWidth="8.7047619047619" defaultRowHeight="15" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="5.14285714285714"/>
-    <col min="2" max="3" customWidth="true" width="27.5714285714286"/>
-    <col min="4" max="4" customWidth="true" width="79.4285714285714"/>
-    <col min="5" max="5" customWidth="true" width="11.5714285714286"/>
-    <col min="6" max="6" customWidth="true" width="5.14285714285714"/>
-    <col min="7" max="7" customWidth="true" width="11.0"/>
-    <col min="8" max="8" customWidth="true" width="12.7142857142857"/>
-    <col min="9" max="9" customWidth="true" width="5.85714285714286"/>
-    <col min="10" max="10" customWidth="true" width="6.0"/>
-    <col min="11" max="11" customWidth="true" width="5.85714285714286"/>
-    <col min="12" max="12" customWidth="true" width="14.2857142857143"/>
-    <col min="13" max="13" customWidth="true" width="9.42857142857143"/>
-    <col min="14" max="14" customWidth="true" width="14.4285714285714"/>
-    <col min="15" max="15" customWidth="true" width="15.5714285714286"/>
-    <col min="16" max="16" customWidth="true" width="14.4285714285714"/>
-    <col min="17" max="17" customWidth="true" width="39.4285714285714"/>
-    <col min="18" max="18" customWidth="true" width="11.7142857142857"/>
-    <col min="19" max="19" customWidth="true" width="11.8571428571429"/>
-    <col min="20" max="20" customWidth="true" width="6.42857142857143"/>
-    <col min="21" max="22" customWidth="true" width="6.57142857142857"/>
-    <col min="23" max="23" customWidth="true" width="37.1428571428571"/>
-    <col min="24" max="25" customWidth="true" width="8.0"/>
-    <col min="26" max="26" customWidth="true" width="7.71428571428571"/>
-    <col min="27" max="27" customWidth="true" width="6.28571428571429"/>
-    <col min="28" max="28" customWidth="true" width="9.28571428571429"/>
-    <col min="29" max="29" customWidth="true" width="9.71428571428571"/>
-    <col min="30" max="30" customWidth="true" width="12.8571428571429"/>
-    <col min="31" max="31" customWidth="true" width="16.1428571428571"/>
-    <col min="32" max="32" customWidth="true" width="15.4285714285714"/>
-    <col min="33" max="33" customWidth="true" width="24.5714285714286"/>
-    <col min="34" max="34" customWidth="true" width="8.57142857142857"/>
-    <col min="35" max="35" customWidth="true" width="14.7142857142857"/>
-    <col min="36" max="36" customWidth="true" width="18.5714285714286"/>
-    <col min="37" max="37" customWidth="true" width="14.1428571428571"/>
-    <col min="38" max="38" customWidth="true" width="14.7142857142857"/>
-    <col min="39" max="39" customWidth="true" width="17.4285714285714"/>
-    <col min="40" max="40" customWidth="true" width="22.0"/>
-    <col min="41" max="41" customWidth="true" width="17.5714285714286"/>
-    <col min="42" max="42" customWidth="true" width="25.2857142857143"/>
-    <col min="43" max="43" customWidth="true" width="13.0"/>
-    <col min="44" max="44" customWidth="true" width="23.7142857142857"/>
-    <col min="45" max="45" customWidth="true" width="10.0"/>
-    <col min="46" max="46" customWidth="true" width="13.0"/>
-    <col min="47" max="47" customWidth="true" width="15.5714285714286"/>
-    <col min="48" max="48" customWidth="true" width="21.1428571428571"/>
-    <col min="49" max="49" customWidth="true" width="11.5714285714286"/>
-    <col min="50" max="50" customWidth="true" width="16.7142857142857"/>
-    <col min="51" max="51" customWidth="true" width="14.0"/>
-    <col min="52" max="52" customWidth="true" width="19.4285714285714"/>
-    <col min="53" max="53" customWidth="true" width="18.8571428571429"/>
-    <col min="54" max="54" customWidth="true" width="23.2857142857143"/>
-    <col min="55" max="55" customWidth="true" width="15.5714285714286"/>
-    <col min="56" max="56" customWidth="true" width="14.2857142857143"/>
-    <col min="57" max="57" customWidth="true" width="17.0"/>
-    <col min="58" max="58" customWidth="true" width="16.2857142857143"/>
-    <col min="59" max="59" customWidth="true" width="13.5714285714286"/>
-    <col min="60" max="61" customWidth="true" width="12.7142857142857"/>
-    <col min="62" max="62" customWidth="true" width="21.8571428571429"/>
-    <col min="63" max="63" customWidth="true" width="30.5714285714286"/>
-    <col min="64" max="64" customWidth="true" width="10.0"/>
-    <col min="65" max="65" customWidth="true" width="42.5714285714286"/>
-    <col min="66" max="66" customWidth="true" width="38.1428571428571"/>
-    <col min="67" max="67" customWidth="true" width="19.4285714285714"/>
-    <col min="68" max="68" customWidth="true" width="35.4285714285714"/>
-    <col min="69" max="69" customWidth="true" width="9.57142857142857"/>
+    <col min="1" max="1" width="5.14545454545455" customWidth="1"/>
+    <col min="2" max="3" width="27.5727272727273" customWidth="1"/>
+    <col min="4" max="4" width="79.4272727272727" customWidth="1"/>
+    <col min="5" max="5" width="11.5727272727273" customWidth="1"/>
+    <col min="6" max="6" width="5.14545454545455" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="12.7181818181818" customWidth="1"/>
+    <col min="9" max="9" width="5.85454545454545" customWidth="1"/>
+    <col min="10" max="10" width="6" customWidth="1"/>
+    <col min="11" max="11" width="5.85454545454545" customWidth="1"/>
+    <col min="12" max="12" width="14.2818181818182" customWidth="1"/>
+    <col min="13" max="13" width="9.42727272727273" customWidth="1"/>
+    <col min="14" max="14" width="14.4272727272727" customWidth="1"/>
+    <col min="15" max="15" width="15.5727272727273" customWidth="1"/>
+    <col min="16" max="16" width="14.4272727272727" customWidth="1"/>
+    <col min="17" max="17" width="39.4272727272727" customWidth="1"/>
+    <col min="18" max="18" width="11.7181818181818" customWidth="1"/>
+    <col min="19" max="19" width="11.8545454545455" customWidth="1"/>
+    <col min="20" max="20" width="6.42727272727273" customWidth="1"/>
+    <col min="21" max="22" width="6.57272727272727" customWidth="1"/>
+    <col min="23" max="23" width="37.1454545454545" customWidth="1"/>
+    <col min="24" max="25" width="8" customWidth="1"/>
+    <col min="26" max="26" width="7.71818181818182" customWidth="1"/>
+    <col min="27" max="27" width="6.28181818181818" customWidth="1"/>
+    <col min="28" max="28" width="9.28181818181818" customWidth="1"/>
+    <col min="29" max="29" width="9.71818181818182" customWidth="1"/>
+    <col min="30" max="30" width="12.8545454545455" customWidth="1"/>
+    <col min="31" max="31" width="16.1454545454545" customWidth="1"/>
+    <col min="32" max="32" width="15.4272727272727" customWidth="1"/>
+    <col min="33" max="33" width="24.5727272727273" customWidth="1"/>
+    <col min="34" max="34" width="8.57272727272727" customWidth="1"/>
+    <col min="35" max="35" width="14.7181818181818" customWidth="1"/>
+    <col min="36" max="36" width="18.5727272727273" customWidth="1"/>
+    <col min="37" max="37" width="14.1454545454545" customWidth="1"/>
+    <col min="38" max="38" width="14.7181818181818" customWidth="1"/>
+    <col min="39" max="39" width="17.4272727272727" customWidth="1"/>
+    <col min="40" max="40" width="22" customWidth="1"/>
+    <col min="41" max="41" width="17.5727272727273" customWidth="1"/>
+    <col min="42" max="42" width="25.2818181818182" customWidth="1"/>
+    <col min="43" max="43" width="13" customWidth="1"/>
+    <col min="44" max="44" width="23.7181818181818" customWidth="1"/>
+    <col min="45" max="45" width="10" customWidth="1"/>
+    <col min="46" max="46" width="13" customWidth="1"/>
+    <col min="47" max="47" width="15.5727272727273" customWidth="1"/>
+    <col min="48" max="48" width="21.1454545454545" customWidth="1"/>
+    <col min="49" max="49" width="11.5727272727273" customWidth="1"/>
+    <col min="50" max="50" width="16.7181818181818" customWidth="1"/>
+    <col min="51" max="51" width="14" customWidth="1"/>
+    <col min="52" max="52" width="19.4272727272727" customWidth="1"/>
+    <col min="53" max="53" width="18.8545454545455" customWidth="1"/>
+    <col min="54" max="54" width="23.2818181818182" customWidth="1"/>
+    <col min="55" max="55" width="15.5727272727273" customWidth="1"/>
+    <col min="56" max="56" width="14.2818181818182" customWidth="1"/>
+    <col min="57" max="57" width="17" customWidth="1"/>
+    <col min="58" max="58" width="16.2818181818182" customWidth="1"/>
+    <col min="59" max="59" width="13.5727272727273" customWidth="1"/>
+    <col min="60" max="61" width="12.7181818181818" customWidth="1"/>
+    <col min="62" max="62" width="21.8545454545455" customWidth="1"/>
+    <col min="63" max="63" width="30.5727272727273" customWidth="1"/>
+    <col min="64" max="64" width="10" customWidth="1"/>
+    <col min="65" max="65" width="42.5727272727273" customWidth="1"/>
+    <col min="66" max="66" width="38.1454545454545" customWidth="1"/>
+    <col min="67" max="67" width="19.4272727272727" customWidth="1"/>
+    <col min="68" max="68" width="35.4272727272727" customWidth="1"/>
+    <col min="69" max="69" width="9.57272727272727" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -16998,7 +16463,7 @@
       <c r="BP2" s="8"/>
       <c r="BQ2" s="8"/>
     </row>
-    <row r="3" ht="15.75" spans="1:69">
+    <row r="3" ht="15.25" spans="1:69">
       <c r="A3" s="9" t="s">
         <v>9</v>
       </c>
@@ -17207,15 +16672,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.75" spans="1:69">
+    <row r="4" ht="15.25" spans="1:69">
       <c r="A4" s="6">
         <v>1</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>76</v>
@@ -17371,11 +16836,11 @@
       <c r="AT4" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" t="s" s="0">
-        <v>346</v>
-      </c>
-      <c r="AV4" t="s" s="0">
-        <v>347</v>
+      <c r="AU4" t="s">
+        <v>166</v>
+      </c>
+      <c r="AV4" t="s">
+        <v>167</v>
       </c>
       <c r="AW4" s="16">
         <f>AM4</f>
@@ -17415,11 +16880,11 @@
       <c r="BL4" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="BM4" t="s" s="0">
-        <v>249</v>
-      </c>
-      <c r="BN4" t="s" s="0">
-        <v>248</v>
+      <c r="BM4" t="s">
+        <v>159</v>
+      </c>
+      <c r="BN4" t="s">
+        <v>160</v>
       </c>
       <c r="BO4" s="16">
         <f>ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
@@ -17564,73 +17029,73 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ5"/>
-  <sheetFormatPr defaultColWidth="8.7047619047619" defaultRowHeight="15" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="5.14285714285714"/>
-    <col min="2" max="3" customWidth="true" width="27.5714285714286"/>
-    <col min="4" max="4" customWidth="true" width="79.4285714285714"/>
-    <col min="5" max="5" customWidth="true" width="11.5714285714286"/>
-    <col min="6" max="6" customWidth="true" width="5.14285714285714"/>
-    <col min="7" max="7" customWidth="true" width="11.0"/>
-    <col min="8" max="8" customWidth="true" width="12.7142857142857"/>
-    <col min="9" max="9" customWidth="true" width="5.85714285714286"/>
-    <col min="10" max="10" customWidth="true" width="6.0"/>
-    <col min="11" max="11" customWidth="true" width="5.85714285714286"/>
-    <col min="12" max="12" customWidth="true" width="14.2857142857143"/>
-    <col min="13" max="13" customWidth="true" width="9.42857142857143"/>
-    <col min="14" max="14" customWidth="true" width="14.4285714285714"/>
-    <col min="15" max="15" customWidth="true" width="15.5714285714286"/>
-    <col min="16" max="16" customWidth="true" width="14.4285714285714"/>
-    <col min="17" max="17" customWidth="true" width="39.4285714285714"/>
-    <col min="18" max="18" customWidth="true" width="11.7142857142857"/>
-    <col min="19" max="19" customWidth="true" width="11.8571428571429"/>
-    <col min="20" max="20" customWidth="true" width="6.42857142857143"/>
-    <col min="21" max="22" customWidth="true" width="6.57142857142857"/>
-    <col min="23" max="23" customWidth="true" width="37.1428571428571"/>
-    <col min="24" max="25" customWidth="true" width="8.0"/>
-    <col min="26" max="26" customWidth="true" width="7.71428571428571"/>
-    <col min="27" max="27" customWidth="true" width="6.28571428571429"/>
-    <col min="28" max="28" customWidth="true" width="9.28571428571429"/>
-    <col min="29" max="29" customWidth="true" width="9.71428571428571"/>
-    <col min="30" max="30" customWidth="true" width="12.8571428571429"/>
-    <col min="31" max="31" customWidth="true" width="16.1428571428571"/>
-    <col min="32" max="32" customWidth="true" width="15.4285714285714"/>
-    <col min="33" max="33" customWidth="true" width="24.5714285714286"/>
-    <col min="34" max="34" customWidth="true" width="8.57142857142857"/>
-    <col min="35" max="35" customWidth="true" width="14.7142857142857"/>
-    <col min="36" max="36" customWidth="true" width="18.5714285714286"/>
-    <col min="37" max="37" customWidth="true" width="14.1428571428571"/>
-    <col min="38" max="38" customWidth="true" width="14.7142857142857"/>
-    <col min="39" max="39" customWidth="true" width="17.4285714285714"/>
-    <col min="40" max="40" customWidth="true" width="22.0"/>
-    <col min="41" max="41" customWidth="true" width="17.5714285714286"/>
-    <col min="42" max="42" customWidth="true" width="25.2857142857143"/>
-    <col min="43" max="43" customWidth="true" width="13.0"/>
-    <col min="44" max="44" customWidth="true" width="23.7142857142857"/>
-    <col min="45" max="45" customWidth="true" width="10.0"/>
-    <col min="46" max="46" customWidth="true" width="13.0"/>
-    <col min="47" max="47" customWidth="true" width="15.5714285714286"/>
-    <col min="48" max="48" customWidth="true" width="21.1428571428571"/>
-    <col min="49" max="49" customWidth="true" width="11.5714285714286"/>
-    <col min="50" max="50" customWidth="true" width="16.7142857142857"/>
-    <col min="51" max="51" customWidth="true" width="14.0"/>
-    <col min="52" max="52" customWidth="true" width="19.4285714285714"/>
-    <col min="53" max="53" customWidth="true" width="18.8571428571429"/>
-    <col min="54" max="54" customWidth="true" width="23.2857142857143"/>
-    <col min="55" max="55" customWidth="true" width="15.5714285714286"/>
-    <col min="56" max="56" customWidth="true" width="14.2857142857143"/>
-    <col min="57" max="57" customWidth="true" width="17.0"/>
-    <col min="58" max="58" customWidth="true" width="16.2857142857143"/>
-    <col min="59" max="59" customWidth="true" width="13.5714285714286"/>
-    <col min="60" max="61" customWidth="true" width="12.7142857142857"/>
-    <col min="62" max="62" customWidth="true" width="21.8571428571429"/>
-    <col min="63" max="63" customWidth="true" width="30.5714285714286"/>
-    <col min="64" max="64" customWidth="true" width="10.0"/>
-    <col min="65" max="65" customWidth="true" width="42.5714285714286"/>
-    <col min="66" max="66" customWidth="true" width="38.1428571428571"/>
-    <col min="67" max="67" customWidth="true" width="19.4285714285714"/>
-    <col min="68" max="68" customWidth="true" width="35.4285714285714"/>
-    <col min="69" max="69" customWidth="true" width="9.57142857142857"/>
+    <col min="1" max="1" width="5.14545454545455" customWidth="1"/>
+    <col min="2" max="3" width="27.5727272727273" customWidth="1"/>
+    <col min="4" max="4" width="79.4272727272727" customWidth="1"/>
+    <col min="5" max="5" width="11.5727272727273" customWidth="1"/>
+    <col min="6" max="6" width="5.14545454545455" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="12.7181818181818" customWidth="1"/>
+    <col min="9" max="9" width="5.85454545454545" customWidth="1"/>
+    <col min="10" max="10" width="6" customWidth="1"/>
+    <col min="11" max="11" width="5.85454545454545" customWidth="1"/>
+    <col min="12" max="12" width="14.2818181818182" customWidth="1"/>
+    <col min="13" max="13" width="9.42727272727273" customWidth="1"/>
+    <col min="14" max="14" width="14.4272727272727" customWidth="1"/>
+    <col min="15" max="15" width="15.5727272727273" customWidth="1"/>
+    <col min="16" max="16" width="14.4272727272727" customWidth="1"/>
+    <col min="17" max="17" width="39.4272727272727" customWidth="1"/>
+    <col min="18" max="18" width="11.7181818181818" customWidth="1"/>
+    <col min="19" max="19" width="11.8545454545455" customWidth="1"/>
+    <col min="20" max="20" width="6.42727272727273" customWidth="1"/>
+    <col min="21" max="22" width="6.57272727272727" customWidth="1"/>
+    <col min="23" max="23" width="37.1454545454545" customWidth="1"/>
+    <col min="24" max="25" width="8" customWidth="1"/>
+    <col min="26" max="26" width="7.71818181818182" customWidth="1"/>
+    <col min="27" max="27" width="6.28181818181818" customWidth="1"/>
+    <col min="28" max="28" width="9.28181818181818" customWidth="1"/>
+    <col min="29" max="29" width="9.71818181818182" customWidth="1"/>
+    <col min="30" max="30" width="12.8545454545455" customWidth="1"/>
+    <col min="31" max="31" width="16.1454545454545" customWidth="1"/>
+    <col min="32" max="32" width="15.4272727272727" customWidth="1"/>
+    <col min="33" max="33" width="24.5727272727273" customWidth="1"/>
+    <col min="34" max="34" width="8.57272727272727" customWidth="1"/>
+    <col min="35" max="35" width="14.7181818181818" customWidth="1"/>
+    <col min="36" max="36" width="18.5727272727273" customWidth="1"/>
+    <col min="37" max="37" width="14.1454545454545" customWidth="1"/>
+    <col min="38" max="38" width="14.7181818181818" customWidth="1"/>
+    <col min="39" max="39" width="17.4272727272727" customWidth="1"/>
+    <col min="40" max="40" width="22" customWidth="1"/>
+    <col min="41" max="41" width="17.5727272727273" customWidth="1"/>
+    <col min="42" max="42" width="25.2818181818182" customWidth="1"/>
+    <col min="43" max="43" width="13" customWidth="1"/>
+    <col min="44" max="44" width="23.7181818181818" customWidth="1"/>
+    <col min="45" max="45" width="10" customWidth="1"/>
+    <col min="46" max="46" width="13" customWidth="1"/>
+    <col min="47" max="47" width="15.5727272727273" customWidth="1"/>
+    <col min="48" max="48" width="21.1454545454545" customWidth="1"/>
+    <col min="49" max="49" width="11.5727272727273" customWidth="1"/>
+    <col min="50" max="50" width="16.7181818181818" customWidth="1"/>
+    <col min="51" max="51" width="14" customWidth="1"/>
+    <col min="52" max="52" width="19.4272727272727" customWidth="1"/>
+    <col min="53" max="53" width="18.8545454545455" customWidth="1"/>
+    <col min="54" max="54" width="23.2818181818182" customWidth="1"/>
+    <col min="55" max="55" width="15.5727272727273" customWidth="1"/>
+    <col min="56" max="56" width="14.2818181818182" customWidth="1"/>
+    <col min="57" max="57" width="17" customWidth="1"/>
+    <col min="58" max="58" width="16.2818181818182" customWidth="1"/>
+    <col min="59" max="59" width="13.5727272727273" customWidth="1"/>
+    <col min="60" max="61" width="12.7181818181818" customWidth="1"/>
+    <col min="62" max="62" width="21.8545454545455" customWidth="1"/>
+    <col min="63" max="63" width="30.5727272727273" customWidth="1"/>
+    <col min="64" max="64" width="10" customWidth="1"/>
+    <col min="65" max="65" width="42.5727272727273" customWidth="1"/>
+    <col min="66" max="66" width="38.1454545454545" customWidth="1"/>
+    <col min="67" max="67" width="19.4272727272727" customWidth="1"/>
+    <col min="68" max="68" width="35.4272727272727" customWidth="1"/>
+    <col min="69" max="69" width="9.57272727272727" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -17801,7 +17266,7 @@
       <c r="BP2" s="8"/>
       <c r="BQ2" s="8"/>
     </row>
-    <row r="3" ht="15.75" spans="1:69">
+    <row r="3" ht="15.25" spans="1:69">
       <c r="A3" s="9" t="s">
         <v>9</v>
       </c>
@@ -18010,15 +17475,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.75" spans="1:69">
+    <row r="4" ht="15.25" spans="1:69">
       <c r="A4" s="6">
         <v>1</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>76</v>
@@ -18174,11 +17639,11 @@
       <c r="AT4" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" t="s" s="0">
-        <v>254</v>
-      </c>
-      <c r="AV4" t="s" s="0">
-        <v>255</v>
+      <c r="AU4" t="s">
+        <v>169</v>
+      </c>
+      <c r="AV4" t="s">
+        <v>170</v>
       </c>
       <c r="AW4" s="16">
         <f>AM4</f>
@@ -18218,11 +17683,11 @@
       <c r="BL4" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="BM4" t="s" s="0">
-        <v>257</v>
-      </c>
-      <c r="BN4" t="s" s="0">
-        <v>256</v>
+      <c r="BM4" t="s">
+        <v>171</v>
+      </c>
+      <c r="BN4" t="s">
+        <v>172</v>
       </c>
       <c r="BO4" s="16">
         <f>ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
@@ -18367,73 +17832,73 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ5"/>
-  <sheetFormatPr defaultColWidth="8.7047619047619" defaultRowHeight="15" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="5.14285714285714"/>
-    <col min="2" max="3" customWidth="true" width="22.0"/>
-    <col min="4" max="4" customWidth="true" width="79.4285714285714"/>
-    <col min="5" max="5" customWidth="true" width="11.5714285714286"/>
-    <col min="6" max="6" customWidth="true" width="5.14285714285714"/>
-    <col min="7" max="7" customWidth="true" width="11.0"/>
-    <col min="8" max="8" customWidth="true" width="12.7142857142857"/>
-    <col min="9" max="9" customWidth="true" width="5.85714285714286"/>
-    <col min="10" max="10" customWidth="true" width="6.0"/>
-    <col min="11" max="11" customWidth="true" width="5.85714285714286"/>
-    <col min="12" max="12" customWidth="true" width="14.2857142857143"/>
-    <col min="13" max="13" customWidth="true" width="9.42857142857143"/>
-    <col min="14" max="14" customWidth="true" width="14.4285714285714"/>
-    <col min="15" max="15" customWidth="true" width="15.5714285714286"/>
-    <col min="16" max="16" customWidth="true" width="14.4285714285714"/>
-    <col min="17" max="17" customWidth="true" width="39.4285714285714"/>
-    <col min="18" max="18" customWidth="true" width="11.7142857142857"/>
-    <col min="19" max="19" customWidth="true" width="11.8571428571429"/>
-    <col min="20" max="20" customWidth="true" width="6.42857142857143"/>
-    <col min="21" max="22" customWidth="true" width="6.57142857142857"/>
-    <col min="23" max="23" customWidth="true" width="37.1428571428571"/>
-    <col min="24" max="25" customWidth="true" width="8.0"/>
-    <col min="26" max="26" customWidth="true" width="7.71428571428571"/>
-    <col min="27" max="27" customWidth="true" width="6.28571428571429"/>
-    <col min="28" max="28" customWidth="true" width="9.28571428571429"/>
-    <col min="29" max="29" customWidth="true" width="9.71428571428571"/>
-    <col min="30" max="30" customWidth="true" width="12.8571428571429"/>
-    <col min="31" max="31" customWidth="true" width="16.1428571428571"/>
-    <col min="32" max="32" customWidth="true" width="15.4285714285714"/>
-    <col min="33" max="33" customWidth="true" width="24.5714285714286"/>
-    <col min="34" max="34" customWidth="true" width="8.57142857142857"/>
-    <col min="35" max="35" customWidth="true" width="14.7142857142857"/>
-    <col min="36" max="36" customWidth="true" width="18.5714285714286"/>
-    <col min="37" max="37" customWidth="true" width="14.1428571428571"/>
-    <col min="38" max="38" customWidth="true" width="14.7142857142857"/>
-    <col min="39" max="39" customWidth="true" width="17.4285714285714"/>
-    <col min="40" max="40" customWidth="true" width="22.0"/>
-    <col min="41" max="41" customWidth="true" width="17.5714285714286"/>
-    <col min="42" max="42" customWidth="true" width="25.2857142857143"/>
-    <col min="43" max="43" customWidth="true" width="13.0"/>
-    <col min="44" max="44" customWidth="true" width="23.7142857142857"/>
-    <col min="45" max="45" customWidth="true" width="10.0"/>
-    <col min="46" max="46" customWidth="true" width="13.0"/>
-    <col min="47" max="47" customWidth="true" width="15.5714285714286"/>
-    <col min="48" max="48" customWidth="true" width="21.1428571428571"/>
-    <col min="49" max="49" customWidth="true" width="11.5714285714286"/>
-    <col min="50" max="50" customWidth="true" width="16.7142857142857"/>
-    <col min="51" max="51" customWidth="true" width="14.0"/>
-    <col min="52" max="52" customWidth="true" width="19.4285714285714"/>
-    <col min="53" max="53" customWidth="true" width="18.8571428571429"/>
-    <col min="54" max="54" customWidth="true" width="23.2857142857143"/>
-    <col min="55" max="55" customWidth="true" width="15.5714285714286"/>
-    <col min="56" max="56" customWidth="true" width="14.2857142857143"/>
-    <col min="57" max="57" customWidth="true" width="17.0"/>
-    <col min="58" max="58" customWidth="true" width="16.2857142857143"/>
-    <col min="59" max="59" customWidth="true" width="13.5714285714286"/>
-    <col min="60" max="61" customWidth="true" width="12.7142857142857"/>
-    <col min="62" max="62" customWidth="true" width="21.8571428571429"/>
-    <col min="63" max="63" customWidth="true" width="30.5714285714286"/>
-    <col min="64" max="64" customWidth="true" width="10.0"/>
-    <col min="65" max="65" customWidth="true" width="42.5714285714286"/>
-    <col min="66" max="66" customWidth="true" width="38.1428571428571"/>
-    <col min="67" max="67" customWidth="true" width="19.4285714285714"/>
-    <col min="68" max="68" customWidth="true" width="35.4285714285714"/>
-    <col min="69" max="69" customWidth="true" width="9.57142857142857"/>
+    <col min="1" max="1" width="5.14545454545455" customWidth="1"/>
+    <col min="2" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="79.4272727272727" customWidth="1"/>
+    <col min="5" max="5" width="11.5727272727273" customWidth="1"/>
+    <col min="6" max="6" width="5.14545454545455" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="12.7181818181818" customWidth="1"/>
+    <col min="9" max="9" width="5.85454545454545" customWidth="1"/>
+    <col min="10" max="10" width="6" customWidth="1"/>
+    <col min="11" max="11" width="5.85454545454545" customWidth="1"/>
+    <col min="12" max="12" width="14.2818181818182" customWidth="1"/>
+    <col min="13" max="13" width="9.42727272727273" customWidth="1"/>
+    <col min="14" max="14" width="14.4272727272727" customWidth="1"/>
+    <col min="15" max="15" width="15.5727272727273" customWidth="1"/>
+    <col min="16" max="16" width="14.4272727272727" customWidth="1"/>
+    <col min="17" max="17" width="39.4272727272727" customWidth="1"/>
+    <col min="18" max="18" width="11.7181818181818" customWidth="1"/>
+    <col min="19" max="19" width="11.8545454545455" customWidth="1"/>
+    <col min="20" max="20" width="6.42727272727273" customWidth="1"/>
+    <col min="21" max="22" width="6.57272727272727" customWidth="1"/>
+    <col min="23" max="23" width="37.1454545454545" customWidth="1"/>
+    <col min="24" max="25" width="8" customWidth="1"/>
+    <col min="26" max="26" width="7.71818181818182" customWidth="1"/>
+    <col min="27" max="27" width="6.28181818181818" customWidth="1"/>
+    <col min="28" max="28" width="9.28181818181818" customWidth="1"/>
+    <col min="29" max="29" width="9.71818181818182" customWidth="1"/>
+    <col min="30" max="30" width="12.8545454545455" customWidth="1"/>
+    <col min="31" max="31" width="16.1454545454545" customWidth="1"/>
+    <col min="32" max="32" width="15.4272727272727" customWidth="1"/>
+    <col min="33" max="33" width="24.5727272727273" customWidth="1"/>
+    <col min="34" max="34" width="8.57272727272727" customWidth="1"/>
+    <col min="35" max="35" width="14.7181818181818" customWidth="1"/>
+    <col min="36" max="36" width="18.5727272727273" customWidth="1"/>
+    <col min="37" max="37" width="14.1454545454545" customWidth="1"/>
+    <col min="38" max="38" width="14.7181818181818" customWidth="1"/>
+    <col min="39" max="39" width="17.4272727272727" customWidth="1"/>
+    <col min="40" max="40" width="22" customWidth="1"/>
+    <col min="41" max="41" width="17.5727272727273" customWidth="1"/>
+    <col min="42" max="42" width="25.2818181818182" customWidth="1"/>
+    <col min="43" max="43" width="13" customWidth="1"/>
+    <col min="44" max="44" width="23.7181818181818" customWidth="1"/>
+    <col min="45" max="45" width="10" customWidth="1"/>
+    <col min="46" max="46" width="13" customWidth="1"/>
+    <col min="47" max="47" width="15.5727272727273" customWidth="1"/>
+    <col min="48" max="48" width="21.1454545454545" customWidth="1"/>
+    <col min="49" max="49" width="11.5727272727273" customWidth="1"/>
+    <col min="50" max="50" width="16.7181818181818" customWidth="1"/>
+    <col min="51" max="51" width="14" customWidth="1"/>
+    <col min="52" max="52" width="19.4272727272727" customWidth="1"/>
+    <col min="53" max="53" width="18.8545454545455" customWidth="1"/>
+    <col min="54" max="54" width="23.2818181818182" customWidth="1"/>
+    <col min="55" max="55" width="15.5727272727273" customWidth="1"/>
+    <col min="56" max="56" width="14.2818181818182" customWidth="1"/>
+    <col min="57" max="57" width="17" customWidth="1"/>
+    <col min="58" max="58" width="16.2818181818182" customWidth="1"/>
+    <col min="59" max="59" width="13.5727272727273" customWidth="1"/>
+    <col min="60" max="61" width="12.7181818181818" customWidth="1"/>
+    <col min="62" max="62" width="21.8545454545455" customWidth="1"/>
+    <col min="63" max="63" width="30.5727272727273" customWidth="1"/>
+    <col min="64" max="64" width="10" customWidth="1"/>
+    <col min="65" max="65" width="42.5727272727273" customWidth="1"/>
+    <col min="66" max="66" width="38.1454545454545" customWidth="1"/>
+    <col min="67" max="67" width="19.4272727272727" customWidth="1"/>
+    <col min="68" max="68" width="35.4272727272727" customWidth="1"/>
+    <col min="69" max="69" width="9.57272727272727" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -18604,7 +18069,7 @@
       <c r="BP2" s="27"/>
       <c r="BQ2" s="27"/>
     </row>
-    <row r="3" ht="15.75" spans="1:69">
+    <row r="3" ht="15.25" spans="1:69">
       <c r="A3" s="28" t="s">
         <v>9</v>
       </c>
@@ -18813,7 +18278,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.75" spans="1:69">
+    <row r="4" ht="15.25" spans="1:69">
       <c r="A4" s="26">
         <v>1</v>
       </c>
@@ -19166,73 +18631,73 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ5"/>
-  <sheetFormatPr defaultColWidth="8.7047619047619" defaultRowHeight="15" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="5.14285714285714"/>
-    <col min="2" max="3" customWidth="true" width="25.0"/>
-    <col min="4" max="4" customWidth="true" width="79.4285714285714"/>
-    <col min="5" max="5" customWidth="true" width="11.5714285714286"/>
-    <col min="6" max="6" customWidth="true" width="5.14285714285714"/>
-    <col min="7" max="7" customWidth="true" width="11.0"/>
-    <col min="8" max="8" customWidth="true" width="12.7142857142857"/>
-    <col min="9" max="9" customWidth="true" width="5.85714285714286"/>
-    <col min="10" max="10" customWidth="true" width="6.0"/>
-    <col min="11" max="11" customWidth="true" width="5.85714285714286"/>
-    <col min="12" max="12" customWidth="true" width="14.2857142857143"/>
-    <col min="13" max="13" customWidth="true" width="9.42857142857143"/>
-    <col min="14" max="14" customWidth="true" width="14.4285714285714"/>
-    <col min="15" max="15" customWidth="true" width="15.5714285714286"/>
-    <col min="16" max="16" customWidth="true" width="14.4285714285714"/>
-    <col min="17" max="17" customWidth="true" width="39.4285714285714"/>
-    <col min="18" max="18" customWidth="true" width="11.7142857142857"/>
-    <col min="19" max="19" customWidth="true" width="11.8571428571429"/>
-    <col min="20" max="20" customWidth="true" width="6.42857142857143"/>
-    <col min="21" max="22" customWidth="true" width="6.57142857142857"/>
-    <col min="23" max="23" customWidth="true" width="37.1428571428571"/>
-    <col min="24" max="25" customWidth="true" width="8.0"/>
-    <col min="26" max="26" customWidth="true" width="7.71428571428571"/>
-    <col min="27" max="27" customWidth="true" width="6.28571428571429"/>
-    <col min="28" max="28" customWidth="true" width="9.28571428571429"/>
-    <col min="29" max="29" customWidth="true" width="9.71428571428571"/>
-    <col min="30" max="30" customWidth="true" width="12.8571428571429"/>
-    <col min="31" max="31" customWidth="true" width="16.1428571428571"/>
-    <col min="32" max="32" customWidth="true" width="15.4285714285714"/>
-    <col min="33" max="33" customWidth="true" width="24.5714285714286"/>
-    <col min="34" max="34" customWidth="true" width="8.57142857142857"/>
-    <col min="35" max="35" customWidth="true" width="14.7142857142857"/>
-    <col min="36" max="36" customWidth="true" width="18.5714285714286"/>
-    <col min="37" max="37" customWidth="true" width="14.1428571428571"/>
-    <col min="38" max="38" customWidth="true" width="14.7142857142857"/>
-    <col min="39" max="39" customWidth="true" width="17.4285714285714"/>
-    <col min="40" max="40" customWidth="true" width="22.0"/>
-    <col min="41" max="41" customWidth="true" width="17.5714285714286"/>
-    <col min="42" max="42" customWidth="true" width="25.2857142857143"/>
-    <col min="43" max="43" customWidth="true" width="13.0"/>
-    <col min="44" max="44" customWidth="true" width="23.7142857142857"/>
-    <col min="45" max="45" customWidth="true" width="10.0"/>
-    <col min="46" max="46" customWidth="true" width="13.0"/>
-    <col min="47" max="47" customWidth="true" width="15.5714285714286"/>
-    <col min="48" max="48" customWidth="true" width="21.1428571428571"/>
-    <col min="49" max="49" customWidth="true" width="11.5714285714286"/>
-    <col min="50" max="50" customWidth="true" width="16.7142857142857"/>
-    <col min="51" max="51" customWidth="true" width="14.0"/>
-    <col min="52" max="52" customWidth="true" width="19.4285714285714"/>
-    <col min="53" max="53" customWidth="true" width="18.8571428571429"/>
-    <col min="54" max="54" customWidth="true" width="23.2857142857143"/>
-    <col min="55" max="55" customWidth="true" width="15.5714285714286"/>
-    <col min="56" max="56" customWidth="true" width="14.2857142857143"/>
-    <col min="57" max="57" customWidth="true" width="17.0"/>
-    <col min="58" max="58" customWidth="true" width="16.2857142857143"/>
-    <col min="59" max="59" customWidth="true" width="13.5714285714286"/>
-    <col min="60" max="61" customWidth="true" width="12.7142857142857"/>
-    <col min="62" max="62" customWidth="true" width="21.8571428571429"/>
-    <col min="63" max="63" customWidth="true" width="30.5714285714286"/>
-    <col min="64" max="64" customWidth="true" width="10.0"/>
-    <col min="65" max="65" customWidth="true" width="42.5714285714286"/>
-    <col min="66" max="66" customWidth="true" width="38.1428571428571"/>
-    <col min="67" max="67" customWidth="true" width="19.4285714285714"/>
-    <col min="68" max="68" customWidth="true" width="35.4285714285714"/>
-    <col min="69" max="69" customWidth="true" width="9.57142857142857"/>
+    <col min="1" max="1" width="5.14545454545455" customWidth="1"/>
+    <col min="2" max="3" width="25" customWidth="1"/>
+    <col min="4" max="4" width="79.4272727272727" customWidth="1"/>
+    <col min="5" max="5" width="11.5727272727273" customWidth="1"/>
+    <col min="6" max="6" width="5.14545454545455" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="12.7181818181818" customWidth="1"/>
+    <col min="9" max="9" width="5.85454545454545" customWidth="1"/>
+    <col min="10" max="10" width="6" customWidth="1"/>
+    <col min="11" max="11" width="5.85454545454545" customWidth="1"/>
+    <col min="12" max="12" width="14.2818181818182" customWidth="1"/>
+    <col min="13" max="13" width="9.42727272727273" customWidth="1"/>
+    <col min="14" max="14" width="14.4272727272727" customWidth="1"/>
+    <col min="15" max="15" width="15.5727272727273" customWidth="1"/>
+    <col min="16" max="16" width="14.4272727272727" customWidth="1"/>
+    <col min="17" max="17" width="39.4272727272727" customWidth="1"/>
+    <col min="18" max="18" width="11.7181818181818" customWidth="1"/>
+    <col min="19" max="19" width="11.8545454545455" customWidth="1"/>
+    <col min="20" max="20" width="6.42727272727273" customWidth="1"/>
+    <col min="21" max="22" width="6.57272727272727" customWidth="1"/>
+    <col min="23" max="23" width="37.1454545454545" customWidth="1"/>
+    <col min="24" max="25" width="8" customWidth="1"/>
+    <col min="26" max="26" width="7.71818181818182" customWidth="1"/>
+    <col min="27" max="27" width="6.28181818181818" customWidth="1"/>
+    <col min="28" max="28" width="9.28181818181818" customWidth="1"/>
+    <col min="29" max="29" width="9.71818181818182" customWidth="1"/>
+    <col min="30" max="30" width="12.8545454545455" customWidth="1"/>
+    <col min="31" max="31" width="16.1454545454545" customWidth="1"/>
+    <col min="32" max="32" width="15.4272727272727" customWidth="1"/>
+    <col min="33" max="33" width="24.5727272727273" customWidth="1"/>
+    <col min="34" max="34" width="8.57272727272727" customWidth="1"/>
+    <col min="35" max="35" width="14.7181818181818" customWidth="1"/>
+    <col min="36" max="36" width="18.5727272727273" customWidth="1"/>
+    <col min="37" max="37" width="14.1454545454545" customWidth="1"/>
+    <col min="38" max="38" width="14.7181818181818" customWidth="1"/>
+    <col min="39" max="39" width="17.4272727272727" customWidth="1"/>
+    <col min="40" max="40" width="22" customWidth="1"/>
+    <col min="41" max="41" width="17.5727272727273" customWidth="1"/>
+    <col min="42" max="42" width="25.2818181818182" customWidth="1"/>
+    <col min="43" max="43" width="13" customWidth="1"/>
+    <col min="44" max="44" width="23.7181818181818" customWidth="1"/>
+    <col min="45" max="45" width="10" customWidth="1"/>
+    <col min="46" max="46" width="13" customWidth="1"/>
+    <col min="47" max="47" width="15.5727272727273" customWidth="1"/>
+    <col min="48" max="48" width="21.1454545454545" customWidth="1"/>
+    <col min="49" max="49" width="11.5727272727273" customWidth="1"/>
+    <col min="50" max="50" width="16.7181818181818" customWidth="1"/>
+    <col min="51" max="51" width="14" customWidth="1"/>
+    <col min="52" max="52" width="19.4272727272727" customWidth="1"/>
+    <col min="53" max="53" width="18.8545454545455" customWidth="1"/>
+    <col min="54" max="54" width="23.2818181818182" customWidth="1"/>
+    <col min="55" max="55" width="15.5727272727273" customWidth="1"/>
+    <col min="56" max="56" width="14.2818181818182" customWidth="1"/>
+    <col min="57" max="57" width="17" customWidth="1"/>
+    <col min="58" max="58" width="16.2818181818182" customWidth="1"/>
+    <col min="59" max="59" width="13.5727272727273" customWidth="1"/>
+    <col min="60" max="61" width="12.7181818181818" customWidth="1"/>
+    <col min="62" max="62" width="21.8545454545455" customWidth="1"/>
+    <col min="63" max="63" width="30.5727272727273" customWidth="1"/>
+    <col min="64" max="64" width="10" customWidth="1"/>
+    <col min="65" max="65" width="42.5727272727273" customWidth="1"/>
+    <col min="66" max="66" width="38.1454545454545" customWidth="1"/>
+    <col min="67" max="67" width="19.4272727272727" customWidth="1"/>
+    <col min="68" max="68" width="35.4272727272727" customWidth="1"/>
+    <col min="69" max="69" width="9.57272727272727" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -19403,7 +18868,7 @@
       <c r="BP2" s="27"/>
       <c r="BQ2" s="27"/>
     </row>
-    <row r="3" ht="15.75" spans="1:69">
+    <row r="3" ht="15.25" spans="1:69">
       <c r="A3" s="28" t="s">
         <v>9</v>
       </c>
@@ -19612,7 +19077,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.75" spans="1:69">
+    <row r="4" ht="15.25" spans="1:69">
       <c r="A4" s="26">
         <v>1</v>
       </c>
@@ -19776,8 +19241,6 @@
       <c r="AT4" s="35" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" s="0"/>
-      <c r="AV4" s="0"/>
       <c r="AW4" s="35">
         <f>AM4</f>
         <v>4</v>
@@ -19816,10 +19279,10 @@
       <c r="BL4" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="BM4" t="s" s="0">
+      <c r="BM4" t="s">
         <v>100</v>
       </c>
-      <c r="BN4" t="s" s="0">
+      <c r="BN4" t="s">
         <v>100</v>
       </c>
       <c r="BO4" s="35">
@@ -19965,73 +19428,73 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ5"/>
-  <sheetFormatPr defaultColWidth="8.7047619047619" defaultRowHeight="15" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="5.14285714285714"/>
-    <col min="2" max="3" customWidth="true" width="25.0"/>
-    <col min="4" max="4" customWidth="true" width="79.4285714285714"/>
-    <col min="5" max="5" customWidth="true" width="11.5714285714286"/>
-    <col min="6" max="6" customWidth="true" width="5.14285714285714"/>
-    <col min="7" max="7" customWidth="true" width="11.0"/>
-    <col min="8" max="8" customWidth="true" width="12.7142857142857"/>
-    <col min="9" max="9" customWidth="true" width="5.85714285714286"/>
-    <col min="10" max="10" customWidth="true" width="6.0"/>
-    <col min="11" max="11" customWidth="true" width="5.85714285714286"/>
-    <col min="12" max="12" customWidth="true" width="14.2857142857143"/>
-    <col min="13" max="13" customWidth="true" width="9.42857142857143"/>
-    <col min="14" max="14" customWidth="true" width="14.4285714285714"/>
-    <col min="15" max="15" customWidth="true" width="15.5714285714286"/>
-    <col min="16" max="16" customWidth="true" width="14.4285714285714"/>
-    <col min="17" max="17" customWidth="true" width="39.4285714285714"/>
-    <col min="18" max="18" customWidth="true" width="11.7142857142857"/>
-    <col min="19" max="19" customWidth="true" width="11.8571428571429"/>
-    <col min="20" max="20" customWidth="true" width="6.42857142857143"/>
-    <col min="21" max="22" customWidth="true" width="6.57142857142857"/>
-    <col min="23" max="23" customWidth="true" width="37.1428571428571"/>
-    <col min="24" max="25" customWidth="true" width="8.0"/>
-    <col min="26" max="26" customWidth="true" width="7.71428571428571"/>
-    <col min="27" max="27" customWidth="true" width="6.28571428571429"/>
-    <col min="28" max="28" customWidth="true" width="9.28571428571429"/>
-    <col min="29" max="29" customWidth="true" width="9.71428571428571"/>
-    <col min="30" max="30" customWidth="true" width="12.8571428571429"/>
-    <col min="31" max="31" customWidth="true" width="16.1428571428571"/>
-    <col min="32" max="32" customWidth="true" width="15.4285714285714"/>
-    <col min="33" max="33" customWidth="true" width="24.5714285714286"/>
-    <col min="34" max="34" customWidth="true" width="8.57142857142857"/>
-    <col min="35" max="35" customWidth="true" width="14.7142857142857"/>
-    <col min="36" max="36" customWidth="true" width="18.5714285714286"/>
-    <col min="37" max="37" customWidth="true" width="14.1428571428571"/>
-    <col min="38" max="38" customWidth="true" width="14.7142857142857"/>
-    <col min="39" max="39" customWidth="true" width="17.4285714285714"/>
-    <col min="40" max="40" customWidth="true" width="22.0"/>
-    <col min="41" max="41" customWidth="true" width="17.5714285714286"/>
-    <col min="42" max="42" customWidth="true" width="25.2857142857143"/>
-    <col min="43" max="43" customWidth="true" width="13.0"/>
-    <col min="44" max="44" customWidth="true" width="23.7142857142857"/>
-    <col min="45" max="45" customWidth="true" width="10.0"/>
-    <col min="46" max="46" customWidth="true" width="13.0"/>
-    <col min="47" max="47" customWidth="true" width="15.5714285714286"/>
-    <col min="48" max="48" customWidth="true" width="21.1428571428571"/>
-    <col min="49" max="49" customWidth="true" width="11.5714285714286"/>
-    <col min="50" max="50" customWidth="true" width="16.7142857142857"/>
-    <col min="51" max="51" customWidth="true" width="14.0"/>
-    <col min="52" max="52" customWidth="true" width="19.4285714285714"/>
-    <col min="53" max="53" customWidth="true" width="18.8571428571429"/>
-    <col min="54" max="54" customWidth="true" width="23.2857142857143"/>
-    <col min="55" max="55" customWidth="true" width="15.5714285714286"/>
-    <col min="56" max="56" customWidth="true" width="14.2857142857143"/>
-    <col min="57" max="57" customWidth="true" width="17.0"/>
-    <col min="58" max="58" customWidth="true" width="16.2857142857143"/>
-    <col min="59" max="59" customWidth="true" width="13.5714285714286"/>
-    <col min="60" max="61" customWidth="true" width="12.7142857142857"/>
-    <col min="62" max="62" customWidth="true" width="21.8571428571429"/>
-    <col min="63" max="63" customWidth="true" width="30.5714285714286"/>
-    <col min="64" max="64" customWidth="true" width="10.0"/>
-    <col min="65" max="65" customWidth="true" width="42.5714285714286"/>
-    <col min="66" max="66" customWidth="true" width="38.1428571428571"/>
-    <col min="67" max="67" customWidth="true" width="19.4285714285714"/>
-    <col min="68" max="68" customWidth="true" width="35.4285714285714"/>
-    <col min="69" max="69" customWidth="true" width="9.57142857142857"/>
+    <col min="1" max="1" width="5.14545454545455" customWidth="1"/>
+    <col min="2" max="3" width="25" customWidth="1"/>
+    <col min="4" max="4" width="79.4272727272727" customWidth="1"/>
+    <col min="5" max="5" width="11.5727272727273" customWidth="1"/>
+    <col min="6" max="6" width="5.14545454545455" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="12.7181818181818" customWidth="1"/>
+    <col min="9" max="9" width="5.85454545454545" customWidth="1"/>
+    <col min="10" max="10" width="6" customWidth="1"/>
+    <col min="11" max="11" width="5.85454545454545" customWidth="1"/>
+    <col min="12" max="12" width="14.2818181818182" customWidth="1"/>
+    <col min="13" max="13" width="9.42727272727273" customWidth="1"/>
+    <col min="14" max="14" width="14.4272727272727" customWidth="1"/>
+    <col min="15" max="15" width="15.5727272727273" customWidth="1"/>
+    <col min="16" max="16" width="14.4272727272727" customWidth="1"/>
+    <col min="17" max="17" width="39.4272727272727" customWidth="1"/>
+    <col min="18" max="18" width="11.7181818181818" customWidth="1"/>
+    <col min="19" max="19" width="11.8545454545455" customWidth="1"/>
+    <col min="20" max="20" width="6.42727272727273" customWidth="1"/>
+    <col min="21" max="22" width="6.57272727272727" customWidth="1"/>
+    <col min="23" max="23" width="37.1454545454545" customWidth="1"/>
+    <col min="24" max="25" width="8" customWidth="1"/>
+    <col min="26" max="26" width="7.71818181818182" customWidth="1"/>
+    <col min="27" max="27" width="6.28181818181818" customWidth="1"/>
+    <col min="28" max="28" width="9.28181818181818" customWidth="1"/>
+    <col min="29" max="29" width="9.71818181818182" customWidth="1"/>
+    <col min="30" max="30" width="12.8545454545455" customWidth="1"/>
+    <col min="31" max="31" width="16.1454545454545" customWidth="1"/>
+    <col min="32" max="32" width="15.4272727272727" customWidth="1"/>
+    <col min="33" max="33" width="24.5727272727273" customWidth="1"/>
+    <col min="34" max="34" width="8.57272727272727" customWidth="1"/>
+    <col min="35" max="35" width="14.7181818181818" customWidth="1"/>
+    <col min="36" max="36" width="18.5727272727273" customWidth="1"/>
+    <col min="37" max="37" width="14.1454545454545" customWidth="1"/>
+    <col min="38" max="38" width="14.7181818181818" customWidth="1"/>
+    <col min="39" max="39" width="17.4272727272727" customWidth="1"/>
+    <col min="40" max="40" width="22" customWidth="1"/>
+    <col min="41" max="41" width="17.5727272727273" customWidth="1"/>
+    <col min="42" max="42" width="25.2818181818182" customWidth="1"/>
+    <col min="43" max="43" width="13" customWidth="1"/>
+    <col min="44" max="44" width="23.7181818181818" customWidth="1"/>
+    <col min="45" max="45" width="10" customWidth="1"/>
+    <col min="46" max="46" width="13" customWidth="1"/>
+    <col min="47" max="47" width="15.5727272727273" customWidth="1"/>
+    <col min="48" max="48" width="21.1454545454545" customWidth="1"/>
+    <col min="49" max="49" width="11.5727272727273" customWidth="1"/>
+    <col min="50" max="50" width="16.7181818181818" customWidth="1"/>
+    <col min="51" max="51" width="14" customWidth="1"/>
+    <col min="52" max="52" width="19.4272727272727" customWidth="1"/>
+    <col min="53" max="53" width="18.8545454545455" customWidth="1"/>
+    <col min="54" max="54" width="23.2818181818182" customWidth="1"/>
+    <col min="55" max="55" width="15.5727272727273" customWidth="1"/>
+    <col min="56" max="56" width="14.2818181818182" customWidth="1"/>
+    <col min="57" max="57" width="17" customWidth="1"/>
+    <col min="58" max="58" width="16.2818181818182" customWidth="1"/>
+    <col min="59" max="59" width="13.5727272727273" customWidth="1"/>
+    <col min="60" max="61" width="12.7181818181818" customWidth="1"/>
+    <col min="62" max="62" width="21.8545454545455" customWidth="1"/>
+    <col min="63" max="63" width="30.5727272727273" customWidth="1"/>
+    <col min="64" max="64" width="10" customWidth="1"/>
+    <col min="65" max="65" width="42.5727272727273" customWidth="1"/>
+    <col min="66" max="66" width="38.1454545454545" customWidth="1"/>
+    <col min="67" max="67" width="19.4272727272727" customWidth="1"/>
+    <col min="68" max="68" width="35.4272727272727" customWidth="1"/>
+    <col min="69" max="69" width="9.57272727272727" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -20202,7 +19665,7 @@
       <c r="BP2" s="27"/>
       <c r="BQ2" s="27"/>
     </row>
-    <row r="3" ht="15.75" spans="1:69">
+    <row r="3" ht="15.25" spans="1:69">
       <c r="A3" s="28" t="s">
         <v>9</v>
       </c>
@@ -20411,7 +19874,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.75" spans="1:69">
+    <row r="4" ht="15.25" spans="1:69">
       <c r="A4" s="26">
         <v>1</v>
       </c>
@@ -20575,8 +20038,6 @@
       <c r="AT4" s="35" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" s="0"/>
-      <c r="AV4" s="0"/>
       <c r="AW4" s="35">
         <f>AM4</f>
         <v>4</v>
@@ -20615,10 +20076,10 @@
       <c r="BL4" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="BM4" t="s" s="0">
+      <c r="BM4" t="s">
         <v>100</v>
       </c>
-      <c r="BN4" t="s" s="0">
+      <c r="BN4" t="s">
         <v>100</v>
       </c>
       <c r="BO4" s="35">
@@ -20764,73 +20225,73 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ5"/>
-  <sheetFormatPr defaultColWidth="8.7047619047619" defaultRowHeight="15" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="5.14285714285714"/>
-    <col min="2" max="3" customWidth="true" width="25.2857142857143"/>
-    <col min="4" max="4" customWidth="true" width="79.4285714285714"/>
-    <col min="5" max="5" customWidth="true" width="11.5714285714286"/>
-    <col min="6" max="6" customWidth="true" width="5.14285714285714"/>
-    <col min="7" max="7" customWidth="true" width="11.0"/>
-    <col min="8" max="8" customWidth="true" width="12.7142857142857"/>
-    <col min="9" max="9" customWidth="true" width="5.85714285714286"/>
-    <col min="10" max="10" customWidth="true" width="6.0"/>
-    <col min="11" max="11" customWidth="true" width="5.85714285714286"/>
-    <col min="12" max="12" customWidth="true" width="14.2857142857143"/>
-    <col min="13" max="13" customWidth="true" width="9.42857142857143"/>
-    <col min="14" max="14" customWidth="true" width="14.4285714285714"/>
-    <col min="15" max="15" customWidth="true" width="15.5714285714286"/>
-    <col min="16" max="16" customWidth="true" width="14.4285714285714"/>
-    <col min="17" max="17" customWidth="true" width="39.4285714285714"/>
-    <col min="18" max="18" customWidth="true" width="11.7142857142857"/>
-    <col min="19" max="19" customWidth="true" width="11.8571428571429"/>
-    <col min="20" max="20" customWidth="true" width="6.42857142857143"/>
-    <col min="21" max="22" customWidth="true" width="6.57142857142857"/>
-    <col min="23" max="23" customWidth="true" width="37.1428571428571"/>
-    <col min="24" max="25" customWidth="true" width="8.0"/>
-    <col min="26" max="26" customWidth="true" width="7.71428571428571"/>
-    <col min="27" max="27" customWidth="true" width="6.28571428571429"/>
-    <col min="28" max="28" customWidth="true" width="9.28571428571429"/>
-    <col min="29" max="29" customWidth="true" width="9.71428571428571"/>
-    <col min="30" max="30" customWidth="true" width="12.8571428571429"/>
-    <col min="31" max="31" customWidth="true" width="16.1428571428571"/>
-    <col min="32" max="32" customWidth="true" width="15.4285714285714"/>
-    <col min="33" max="33" customWidth="true" width="24.5714285714286"/>
-    <col min="34" max="34" customWidth="true" width="8.57142857142857"/>
-    <col min="35" max="35" customWidth="true" width="14.7142857142857"/>
-    <col min="36" max="36" customWidth="true" width="18.5714285714286"/>
-    <col min="37" max="37" customWidth="true" width="14.1428571428571"/>
-    <col min="38" max="38" customWidth="true" width="14.7142857142857"/>
-    <col min="39" max="39" customWidth="true" width="17.4285714285714"/>
-    <col min="40" max="40" customWidth="true" width="22.0"/>
-    <col min="41" max="41" customWidth="true" width="17.5714285714286"/>
-    <col min="42" max="42" customWidth="true" width="25.2857142857143"/>
-    <col min="43" max="43" customWidth="true" width="13.0"/>
-    <col min="44" max="44" customWidth="true" width="23.7142857142857"/>
-    <col min="45" max="45" customWidth="true" width="10.0"/>
-    <col min="46" max="46" customWidth="true" width="13.0"/>
-    <col min="47" max="47" customWidth="true" width="15.5714285714286"/>
-    <col min="48" max="48" customWidth="true" width="21.1428571428571"/>
-    <col min="49" max="49" customWidth="true" width="11.5714285714286"/>
-    <col min="50" max="50" customWidth="true" width="16.7142857142857"/>
-    <col min="51" max="51" customWidth="true" width="14.0"/>
-    <col min="52" max="52" customWidth="true" width="19.4285714285714"/>
-    <col min="53" max="53" customWidth="true" width="18.8571428571429"/>
-    <col min="54" max="54" customWidth="true" width="23.2857142857143"/>
-    <col min="55" max="55" customWidth="true" width="15.5714285714286"/>
-    <col min="56" max="56" customWidth="true" width="14.2857142857143"/>
-    <col min="57" max="57" customWidth="true" width="17.0"/>
-    <col min="58" max="58" customWidth="true" width="16.2857142857143"/>
-    <col min="59" max="59" customWidth="true" width="13.5714285714286"/>
-    <col min="60" max="61" customWidth="true" width="12.7142857142857"/>
-    <col min="62" max="62" customWidth="true" width="21.8571428571429"/>
-    <col min="63" max="63" customWidth="true" width="30.5714285714286"/>
-    <col min="64" max="64" customWidth="true" width="10.0"/>
-    <col min="65" max="65" customWidth="true" width="42.5714285714286"/>
-    <col min="66" max="66" customWidth="true" width="38.1428571428571"/>
-    <col min="67" max="67" customWidth="true" width="19.4285714285714"/>
-    <col min="68" max="68" customWidth="true" width="35.4285714285714"/>
-    <col min="69" max="69" customWidth="true" width="9.57142857142857"/>
+    <col min="1" max="1" width="5.14545454545455" customWidth="1"/>
+    <col min="2" max="3" width="25.2818181818182" customWidth="1"/>
+    <col min="4" max="4" width="79.4272727272727" customWidth="1"/>
+    <col min="5" max="5" width="11.5727272727273" customWidth="1"/>
+    <col min="6" max="6" width="5.14545454545455" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="12.7181818181818" customWidth="1"/>
+    <col min="9" max="9" width="5.85454545454545" customWidth="1"/>
+    <col min="10" max="10" width="6" customWidth="1"/>
+    <col min="11" max="11" width="5.85454545454545" customWidth="1"/>
+    <col min="12" max="12" width="14.2818181818182" customWidth="1"/>
+    <col min="13" max="13" width="9.42727272727273" customWidth="1"/>
+    <col min="14" max="14" width="14.4272727272727" customWidth="1"/>
+    <col min="15" max="15" width="15.5727272727273" customWidth="1"/>
+    <col min="16" max="16" width="14.4272727272727" customWidth="1"/>
+    <col min="17" max="17" width="39.4272727272727" customWidth="1"/>
+    <col min="18" max="18" width="11.7181818181818" customWidth="1"/>
+    <col min="19" max="19" width="11.8545454545455" customWidth="1"/>
+    <col min="20" max="20" width="6.42727272727273" customWidth="1"/>
+    <col min="21" max="22" width="6.57272727272727" customWidth="1"/>
+    <col min="23" max="23" width="37.1454545454545" customWidth="1"/>
+    <col min="24" max="25" width="8" customWidth="1"/>
+    <col min="26" max="26" width="7.71818181818182" customWidth="1"/>
+    <col min="27" max="27" width="6.28181818181818" customWidth="1"/>
+    <col min="28" max="28" width="9.28181818181818" customWidth="1"/>
+    <col min="29" max="29" width="9.71818181818182" customWidth="1"/>
+    <col min="30" max="30" width="12.8545454545455" customWidth="1"/>
+    <col min="31" max="31" width="16.1454545454545" customWidth="1"/>
+    <col min="32" max="32" width="15.4272727272727" customWidth="1"/>
+    <col min="33" max="33" width="24.5727272727273" customWidth="1"/>
+    <col min="34" max="34" width="8.57272727272727" customWidth="1"/>
+    <col min="35" max="35" width="14.7181818181818" customWidth="1"/>
+    <col min="36" max="36" width="18.5727272727273" customWidth="1"/>
+    <col min="37" max="37" width="14.1454545454545" customWidth="1"/>
+    <col min="38" max="38" width="14.7181818181818" customWidth="1"/>
+    <col min="39" max="39" width="17.4272727272727" customWidth="1"/>
+    <col min="40" max="40" width="22" customWidth="1"/>
+    <col min="41" max="41" width="17.5727272727273" customWidth="1"/>
+    <col min="42" max="42" width="25.2818181818182" customWidth="1"/>
+    <col min="43" max="43" width="13" customWidth="1"/>
+    <col min="44" max="44" width="23.7181818181818" customWidth="1"/>
+    <col min="45" max="45" width="10" customWidth="1"/>
+    <col min="46" max="46" width="13" customWidth="1"/>
+    <col min="47" max="47" width="15.5727272727273" customWidth="1"/>
+    <col min="48" max="48" width="21.1454545454545" customWidth="1"/>
+    <col min="49" max="49" width="11.5727272727273" customWidth="1"/>
+    <col min="50" max="50" width="16.7181818181818" customWidth="1"/>
+    <col min="51" max="51" width="14" customWidth="1"/>
+    <col min="52" max="52" width="19.4272727272727" customWidth="1"/>
+    <col min="53" max="53" width="18.8545454545455" customWidth="1"/>
+    <col min="54" max="54" width="23.2818181818182" customWidth="1"/>
+    <col min="55" max="55" width="15.5727272727273" customWidth="1"/>
+    <col min="56" max="56" width="14.2818181818182" customWidth="1"/>
+    <col min="57" max="57" width="17" customWidth="1"/>
+    <col min="58" max="58" width="16.2818181818182" customWidth="1"/>
+    <col min="59" max="59" width="13.5727272727273" customWidth="1"/>
+    <col min="60" max="61" width="12.7181818181818" customWidth="1"/>
+    <col min="62" max="62" width="21.8545454545455" customWidth="1"/>
+    <col min="63" max="63" width="30.5727272727273" customWidth="1"/>
+    <col min="64" max="64" width="10" customWidth="1"/>
+    <col min="65" max="65" width="42.5727272727273" customWidth="1"/>
+    <col min="66" max="66" width="38.1454545454545" customWidth="1"/>
+    <col min="67" max="67" width="19.4272727272727" customWidth="1"/>
+    <col min="68" max="68" width="35.4272727272727" customWidth="1"/>
+    <col min="69" max="69" width="9.57272727272727" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -21001,7 +20462,7 @@
       <c r="BP2" s="27"/>
       <c r="BQ2" s="27"/>
     </row>
-    <row r="3" spans="1:69">
+    <row r="3" ht="15.25" spans="1:69">
       <c r="A3" s="28" t="s">
         <v>9</v>
       </c>
@@ -21210,7 +20671,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:69">
+    <row r="4" ht="15.25" spans="1:69">
       <c r="A4" s="26">
         <v>1</v>
       </c>
@@ -21374,11 +20835,11 @@
       <c r="AT4" s="35" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" t="s" s="0">
-        <v>315</v>
-      </c>
-      <c r="AV4" t="s" s="0">
-        <v>316</v>
+      <c r="AU4" t="s">
+        <v>105</v>
+      </c>
+      <c r="AV4" t="s">
+        <v>106</v>
       </c>
       <c r="AW4" s="35">
         <f>AM4</f>
@@ -21418,11 +20879,11 @@
       <c r="BL4" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="BM4" t="s" s="0">
-        <v>262</v>
-      </c>
-      <c r="BN4" t="s" s="0">
-        <v>261</v>
+      <c r="BM4" t="s">
+        <v>107</v>
+      </c>
+      <c r="BN4" t="s">
+        <v>108</v>
       </c>
       <c r="BO4" s="35">
         <f>ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
@@ -21579,73 +21040,73 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ5"/>
-  <sheetFormatPr defaultColWidth="8.7047619047619" defaultRowHeight="15" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="5.14285714285714"/>
-    <col min="2" max="3" customWidth="true" width="25.2857142857143"/>
-    <col min="4" max="4" customWidth="true" width="79.4285714285714"/>
-    <col min="5" max="5" customWidth="true" width="11.5714285714286"/>
-    <col min="6" max="6" customWidth="true" width="5.14285714285714"/>
-    <col min="7" max="7" customWidth="true" width="11.0"/>
-    <col min="8" max="8" customWidth="true" width="12.7142857142857"/>
-    <col min="9" max="9" customWidth="true" width="5.85714285714286"/>
-    <col min="10" max="10" customWidth="true" width="6.0"/>
-    <col min="11" max="11" customWidth="true" width="5.85714285714286"/>
-    <col min="12" max="12" customWidth="true" width="14.2857142857143"/>
-    <col min="13" max="13" customWidth="true" width="9.42857142857143"/>
-    <col min="14" max="14" customWidth="true" width="14.4285714285714"/>
-    <col min="15" max="15" customWidth="true" width="15.5714285714286"/>
-    <col min="16" max="16" customWidth="true" width="14.4285714285714"/>
-    <col min="17" max="17" customWidth="true" width="39.4285714285714"/>
-    <col min="18" max="18" customWidth="true" width="11.7142857142857"/>
-    <col min="19" max="19" customWidth="true" width="11.8571428571429"/>
-    <col min="20" max="20" customWidth="true" width="6.42857142857143"/>
-    <col min="21" max="22" customWidth="true" width="6.57142857142857"/>
-    <col min="23" max="23" customWidth="true" width="37.1428571428571"/>
-    <col min="24" max="25" customWidth="true" width="8.0"/>
-    <col min="26" max="26" customWidth="true" width="7.71428571428571"/>
-    <col min="27" max="27" customWidth="true" width="6.28571428571429"/>
-    <col min="28" max="28" customWidth="true" width="9.28571428571429"/>
-    <col min="29" max="29" customWidth="true" width="9.71428571428571"/>
-    <col min="30" max="30" customWidth="true" width="12.8571428571429"/>
-    <col min="31" max="31" customWidth="true" width="16.1428571428571"/>
-    <col min="32" max="32" customWidth="true" width="15.4285714285714"/>
-    <col min="33" max="33" customWidth="true" width="24.5714285714286"/>
-    <col min="34" max="34" customWidth="true" width="8.57142857142857"/>
-    <col min="35" max="35" customWidth="true" width="14.7142857142857"/>
-    <col min="36" max="36" customWidth="true" width="18.5714285714286"/>
-    <col min="37" max="37" customWidth="true" width="14.1428571428571"/>
-    <col min="38" max="38" customWidth="true" width="14.7142857142857"/>
-    <col min="39" max="39" customWidth="true" width="17.4285714285714"/>
-    <col min="40" max="40" customWidth="true" width="22.0"/>
-    <col min="41" max="41" customWidth="true" width="17.5714285714286"/>
-    <col min="42" max="42" customWidth="true" width="25.2857142857143"/>
-    <col min="43" max="43" customWidth="true" width="13.0"/>
-    <col min="44" max="44" customWidth="true" width="23.7142857142857"/>
-    <col min="45" max="45" customWidth="true" width="10.0"/>
-    <col min="46" max="46" customWidth="true" width="13.0"/>
-    <col min="47" max="47" customWidth="true" width="15.5714285714286"/>
-    <col min="48" max="48" customWidth="true" width="21.1428571428571"/>
-    <col min="49" max="49" customWidth="true" width="11.5714285714286"/>
-    <col min="50" max="50" customWidth="true" width="16.7142857142857"/>
-    <col min="51" max="51" customWidth="true" width="14.0"/>
-    <col min="52" max="52" customWidth="true" width="19.4285714285714"/>
-    <col min="53" max="53" customWidth="true" width="18.8571428571429"/>
-    <col min="54" max="54" customWidth="true" width="23.2857142857143"/>
-    <col min="55" max="55" customWidth="true" width="15.5714285714286"/>
-    <col min="56" max="56" customWidth="true" width="14.2857142857143"/>
-    <col min="57" max="57" customWidth="true" width="17.0"/>
-    <col min="58" max="58" customWidth="true" width="16.2857142857143"/>
-    <col min="59" max="59" customWidth="true" width="13.5714285714286"/>
-    <col min="60" max="61" customWidth="true" width="12.7142857142857"/>
-    <col min="62" max="62" customWidth="true" width="21.8571428571429"/>
-    <col min="63" max="63" customWidth="true" width="30.5714285714286"/>
-    <col min="64" max="64" customWidth="true" width="10.0"/>
-    <col min="65" max="65" customWidth="true" width="42.5714285714286"/>
-    <col min="66" max="66" customWidth="true" width="38.1428571428571"/>
-    <col min="67" max="67" customWidth="true" width="19.4285714285714"/>
-    <col min="68" max="68" customWidth="true" width="35.4285714285714"/>
-    <col min="69" max="69" customWidth="true" width="9.57142857142857"/>
+    <col min="1" max="1" width="5.14545454545455" customWidth="1"/>
+    <col min="2" max="3" width="25.2818181818182" customWidth="1"/>
+    <col min="4" max="4" width="79.4272727272727" customWidth="1"/>
+    <col min="5" max="5" width="11.5727272727273" customWidth="1"/>
+    <col min="6" max="6" width="5.14545454545455" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="12.7181818181818" customWidth="1"/>
+    <col min="9" max="9" width="5.85454545454545" customWidth="1"/>
+    <col min="10" max="10" width="6" customWidth="1"/>
+    <col min="11" max="11" width="5.85454545454545" customWidth="1"/>
+    <col min="12" max="12" width="14.2818181818182" customWidth="1"/>
+    <col min="13" max="13" width="9.42727272727273" customWidth="1"/>
+    <col min="14" max="14" width="14.4272727272727" customWidth="1"/>
+    <col min="15" max="15" width="15.5727272727273" customWidth="1"/>
+    <col min="16" max="16" width="14.4272727272727" customWidth="1"/>
+    <col min="17" max="17" width="39.4272727272727" customWidth="1"/>
+    <col min="18" max="18" width="11.7181818181818" customWidth="1"/>
+    <col min="19" max="19" width="11.8545454545455" customWidth="1"/>
+    <col min="20" max="20" width="6.42727272727273" customWidth="1"/>
+    <col min="21" max="22" width="6.57272727272727" customWidth="1"/>
+    <col min="23" max="23" width="37.1454545454545" customWidth="1"/>
+    <col min="24" max="25" width="8" customWidth="1"/>
+    <col min="26" max="26" width="7.71818181818182" customWidth="1"/>
+    <col min="27" max="27" width="6.28181818181818" customWidth="1"/>
+    <col min="28" max="28" width="9.28181818181818" customWidth="1"/>
+    <col min="29" max="29" width="9.71818181818182" customWidth="1"/>
+    <col min="30" max="30" width="12.8545454545455" customWidth="1"/>
+    <col min="31" max="31" width="16.1454545454545" customWidth="1"/>
+    <col min="32" max="32" width="15.4272727272727" customWidth="1"/>
+    <col min="33" max="33" width="24.5727272727273" customWidth="1"/>
+    <col min="34" max="34" width="8.57272727272727" customWidth="1"/>
+    <col min="35" max="35" width="14.7181818181818" customWidth="1"/>
+    <col min="36" max="36" width="18.5727272727273" customWidth="1"/>
+    <col min="37" max="37" width="14.1454545454545" customWidth="1"/>
+    <col min="38" max="38" width="14.7181818181818" customWidth="1"/>
+    <col min="39" max="39" width="17.4272727272727" customWidth="1"/>
+    <col min="40" max="40" width="22" customWidth="1"/>
+    <col min="41" max="41" width="17.5727272727273" customWidth="1"/>
+    <col min="42" max="42" width="25.2818181818182" customWidth="1"/>
+    <col min="43" max="43" width="13" customWidth="1"/>
+    <col min="44" max="44" width="23.7181818181818" customWidth="1"/>
+    <col min="45" max="45" width="10" customWidth="1"/>
+    <col min="46" max="46" width="13" customWidth="1"/>
+    <col min="47" max="47" width="15.5727272727273" customWidth="1"/>
+    <col min="48" max="48" width="21.1454545454545" customWidth="1"/>
+    <col min="49" max="49" width="11.5727272727273" customWidth="1"/>
+    <col min="50" max="50" width="16.7181818181818" customWidth="1"/>
+    <col min="51" max="51" width="14" customWidth="1"/>
+    <col min="52" max="52" width="19.4272727272727" customWidth="1"/>
+    <col min="53" max="53" width="18.8545454545455" customWidth="1"/>
+    <col min="54" max="54" width="23.2818181818182" customWidth="1"/>
+    <col min="55" max="55" width="15.5727272727273" customWidth="1"/>
+    <col min="56" max="56" width="14.2818181818182" customWidth="1"/>
+    <col min="57" max="57" width="17" customWidth="1"/>
+    <col min="58" max="58" width="16.2818181818182" customWidth="1"/>
+    <col min="59" max="59" width="13.5727272727273" customWidth="1"/>
+    <col min="60" max="61" width="12.7181818181818" customWidth="1"/>
+    <col min="62" max="62" width="21.8545454545455" customWidth="1"/>
+    <col min="63" max="63" width="30.5727272727273" customWidth="1"/>
+    <col min="64" max="64" width="10" customWidth="1"/>
+    <col min="65" max="65" width="42.5727272727273" customWidth="1"/>
+    <col min="66" max="66" width="38.1454545454545" customWidth="1"/>
+    <col min="67" max="67" width="19.4272727272727" customWidth="1"/>
+    <col min="68" max="68" width="35.4272727272727" customWidth="1"/>
+    <col min="69" max="69" width="9.57272727272727" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -21816,7 +21277,7 @@
       <c r="BP2" s="27"/>
       <c r="BQ2" s="27"/>
     </row>
-    <row r="3" ht="15.75" spans="1:69">
+    <row r="3" ht="15.25" spans="1:69">
       <c r="A3" s="28" t="s">
         <v>9</v>
       </c>
@@ -22025,7 +21486,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.75" spans="1:69">
+    <row r="4" ht="15.25" spans="1:69">
       <c r="A4" s="26">
         <v>1</v>
       </c>
@@ -22189,11 +21650,11 @@
       <c r="AT4" s="35" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" t="s" s="0">
-        <v>317</v>
-      </c>
-      <c r="AV4" t="s" s="0">
-        <v>318</v>
+      <c r="AU4" t="s">
+        <v>110</v>
+      </c>
+      <c r="AV4" t="s">
+        <v>111</v>
       </c>
       <c r="AW4" s="35">
         <f>AM4</f>
@@ -22233,11 +21694,11 @@
       <c r="BL4" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="BM4" t="s" s="0">
-        <v>265</v>
-      </c>
-      <c r="BN4" t="s" s="0">
-        <v>264</v>
+      <c r="BM4" t="s">
+        <v>112</v>
+      </c>
+      <c r="BN4" t="s">
+        <v>113</v>
       </c>
       <c r="BO4" s="35">
         <f>ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
@@ -22382,73 +21843,73 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ5"/>
-  <sheetFormatPr defaultColWidth="8.7047619047619" defaultRowHeight="15" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="5.14285714285714"/>
-    <col min="2" max="3" customWidth="true" width="25.5714285714286"/>
-    <col min="4" max="4" customWidth="true" width="79.4285714285714"/>
-    <col min="5" max="5" customWidth="true" width="11.5714285714286"/>
-    <col min="6" max="6" customWidth="true" width="5.14285714285714"/>
-    <col min="7" max="7" customWidth="true" width="11.0"/>
-    <col min="8" max="8" customWidth="true" width="12.7142857142857"/>
-    <col min="9" max="9" customWidth="true" width="5.85714285714286"/>
-    <col min="10" max="10" customWidth="true" width="6.0"/>
-    <col min="11" max="11" customWidth="true" width="5.85714285714286"/>
-    <col min="12" max="12" customWidth="true" width="14.2857142857143"/>
-    <col min="13" max="13" customWidth="true" width="9.42857142857143"/>
-    <col min="14" max="14" customWidth="true" width="14.4285714285714"/>
-    <col min="15" max="15" customWidth="true" width="15.5714285714286"/>
-    <col min="16" max="16" customWidth="true" width="14.4285714285714"/>
-    <col min="17" max="17" customWidth="true" width="39.4285714285714"/>
-    <col min="18" max="18" customWidth="true" width="11.7142857142857"/>
-    <col min="19" max="19" customWidth="true" width="11.8571428571429"/>
-    <col min="20" max="20" customWidth="true" width="6.42857142857143"/>
-    <col min="21" max="22" customWidth="true" width="6.57142857142857"/>
-    <col min="23" max="23" customWidth="true" width="37.1428571428571"/>
-    <col min="24" max="25" customWidth="true" width="8.0"/>
-    <col min="26" max="26" customWidth="true" width="7.71428571428571"/>
-    <col min="27" max="27" customWidth="true" width="6.28571428571429"/>
-    <col min="28" max="28" customWidth="true" width="9.28571428571429"/>
-    <col min="29" max="29" customWidth="true" width="9.71428571428571"/>
-    <col min="30" max="30" customWidth="true" width="12.8571428571429"/>
-    <col min="31" max="31" customWidth="true" width="16.1428571428571"/>
-    <col min="32" max="32" customWidth="true" width="15.4285714285714"/>
-    <col min="33" max="33" customWidth="true" width="24.5714285714286"/>
-    <col min="34" max="34" customWidth="true" width="8.57142857142857"/>
-    <col min="35" max="35" customWidth="true" width="14.7142857142857"/>
-    <col min="36" max="36" customWidth="true" width="18.5714285714286"/>
-    <col min="37" max="37" customWidth="true" width="14.1428571428571"/>
-    <col min="38" max="38" customWidth="true" width="14.7142857142857"/>
-    <col min="39" max="39" customWidth="true" width="17.4285714285714"/>
-    <col min="40" max="40" customWidth="true" width="22.0"/>
-    <col min="41" max="41" customWidth="true" width="17.5714285714286"/>
-    <col min="42" max="42" customWidth="true" width="25.2857142857143"/>
-    <col min="43" max="43" customWidth="true" width="13.0"/>
-    <col min="44" max="44" customWidth="true" width="23.7142857142857"/>
-    <col min="45" max="45" customWidth="true" width="10.0"/>
-    <col min="46" max="46" customWidth="true" width="13.0"/>
-    <col min="47" max="47" customWidth="true" width="15.5714285714286"/>
-    <col min="48" max="48" customWidth="true" width="21.1428571428571"/>
-    <col min="49" max="49" customWidth="true" width="11.5714285714286"/>
-    <col min="50" max="50" customWidth="true" width="16.7142857142857"/>
-    <col min="51" max="51" customWidth="true" width="14.0"/>
-    <col min="52" max="52" customWidth="true" width="19.4285714285714"/>
-    <col min="53" max="53" customWidth="true" width="18.8571428571429"/>
-    <col min="54" max="54" customWidth="true" width="23.2857142857143"/>
-    <col min="55" max="55" customWidth="true" width="15.5714285714286"/>
-    <col min="56" max="56" customWidth="true" width="14.2857142857143"/>
-    <col min="57" max="57" customWidth="true" width="17.0"/>
-    <col min="58" max="58" customWidth="true" width="16.2857142857143"/>
-    <col min="59" max="59" customWidth="true" width="13.5714285714286"/>
-    <col min="60" max="61" customWidth="true" width="12.7142857142857"/>
-    <col min="62" max="62" customWidth="true" width="21.8571428571429"/>
-    <col min="63" max="63" customWidth="true" width="30.5714285714286"/>
-    <col min="64" max="64" customWidth="true" width="10.0"/>
-    <col min="65" max="65" customWidth="true" width="42.5714285714286"/>
-    <col min="66" max="66" customWidth="true" width="38.1428571428571"/>
-    <col min="67" max="67" customWidth="true" width="19.4285714285714"/>
-    <col min="68" max="68" customWidth="true" width="35.4285714285714"/>
-    <col min="69" max="69" customWidth="true" width="9.57142857142857"/>
+    <col min="1" max="1" width="5.14545454545455" customWidth="1"/>
+    <col min="2" max="3" width="25.5727272727273" customWidth="1"/>
+    <col min="4" max="4" width="79.4272727272727" customWidth="1"/>
+    <col min="5" max="5" width="11.5727272727273" customWidth="1"/>
+    <col min="6" max="6" width="5.14545454545455" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="12.7181818181818" customWidth="1"/>
+    <col min="9" max="9" width="5.85454545454545" customWidth="1"/>
+    <col min="10" max="10" width="6" customWidth="1"/>
+    <col min="11" max="11" width="5.85454545454545" customWidth="1"/>
+    <col min="12" max="12" width="14.2818181818182" customWidth="1"/>
+    <col min="13" max="13" width="9.42727272727273" customWidth="1"/>
+    <col min="14" max="14" width="14.4272727272727" customWidth="1"/>
+    <col min="15" max="15" width="15.5727272727273" customWidth="1"/>
+    <col min="16" max="16" width="14.4272727272727" customWidth="1"/>
+    <col min="17" max="17" width="39.4272727272727" customWidth="1"/>
+    <col min="18" max="18" width="11.7181818181818" customWidth="1"/>
+    <col min="19" max="19" width="11.8545454545455" customWidth="1"/>
+    <col min="20" max="20" width="6.42727272727273" customWidth="1"/>
+    <col min="21" max="22" width="6.57272727272727" customWidth="1"/>
+    <col min="23" max="23" width="37.1454545454545" customWidth="1"/>
+    <col min="24" max="25" width="8" customWidth="1"/>
+    <col min="26" max="26" width="7.71818181818182" customWidth="1"/>
+    <col min="27" max="27" width="6.28181818181818" customWidth="1"/>
+    <col min="28" max="28" width="9.28181818181818" customWidth="1"/>
+    <col min="29" max="29" width="9.71818181818182" customWidth="1"/>
+    <col min="30" max="30" width="12.8545454545455" customWidth="1"/>
+    <col min="31" max="31" width="16.1454545454545" customWidth="1"/>
+    <col min="32" max="32" width="15.4272727272727" customWidth="1"/>
+    <col min="33" max="33" width="24.5727272727273" customWidth="1"/>
+    <col min="34" max="34" width="8.57272727272727" customWidth="1"/>
+    <col min="35" max="35" width="14.7181818181818" customWidth="1"/>
+    <col min="36" max="36" width="18.5727272727273" customWidth="1"/>
+    <col min="37" max="37" width="14.1454545454545" customWidth="1"/>
+    <col min="38" max="38" width="14.7181818181818" customWidth="1"/>
+    <col min="39" max="39" width="17.4272727272727" customWidth="1"/>
+    <col min="40" max="40" width="22" customWidth="1"/>
+    <col min="41" max="41" width="17.5727272727273" customWidth="1"/>
+    <col min="42" max="42" width="25.2818181818182" customWidth="1"/>
+    <col min="43" max="43" width="13" customWidth="1"/>
+    <col min="44" max="44" width="23.7181818181818" customWidth="1"/>
+    <col min="45" max="45" width="10" customWidth="1"/>
+    <col min="46" max="46" width="13" customWidth="1"/>
+    <col min="47" max="47" width="15.5727272727273" customWidth="1"/>
+    <col min="48" max="48" width="21.1454545454545" customWidth="1"/>
+    <col min="49" max="49" width="11.5727272727273" customWidth="1"/>
+    <col min="50" max="50" width="16.7181818181818" customWidth="1"/>
+    <col min="51" max="51" width="14" customWidth="1"/>
+    <col min="52" max="52" width="19.4272727272727" customWidth="1"/>
+    <col min="53" max="53" width="18.8545454545455" customWidth="1"/>
+    <col min="54" max="54" width="23.2818181818182" customWidth="1"/>
+    <col min="55" max="55" width="15.5727272727273" customWidth="1"/>
+    <col min="56" max="56" width="14.2818181818182" customWidth="1"/>
+    <col min="57" max="57" width="17" customWidth="1"/>
+    <col min="58" max="58" width="16.2818181818182" customWidth="1"/>
+    <col min="59" max="59" width="13.5727272727273" customWidth="1"/>
+    <col min="60" max="61" width="12.7181818181818" customWidth="1"/>
+    <col min="62" max="62" width="21.8545454545455" customWidth="1"/>
+    <col min="63" max="63" width="30.5727272727273" customWidth="1"/>
+    <col min="64" max="64" width="10" customWidth="1"/>
+    <col min="65" max="65" width="42.5727272727273" customWidth="1"/>
+    <col min="66" max="66" width="38.1454545454545" customWidth="1"/>
+    <col min="67" max="67" width="19.4272727272727" customWidth="1"/>
+    <col min="68" max="68" width="35.4272727272727" customWidth="1"/>
+    <col min="69" max="69" width="9.57272727272727" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -22619,7 +22080,7 @@
       <c r="BP2" s="27"/>
       <c r="BQ2" s="27"/>
     </row>
-    <row r="3" ht="15.75" spans="1:69">
+    <row r="3" ht="15.25" spans="1:69">
       <c r="A3" s="28" t="s">
         <v>9</v>
       </c>
@@ -22828,7 +22289,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.75" spans="1:69">
+    <row r="4" ht="15.25" spans="1:69">
       <c r="A4" s="26">
         <v>1</v>
       </c>
@@ -23181,73 +22642,73 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ5"/>
-  <sheetFormatPr defaultColWidth="8.7047619047619" defaultRowHeight="15" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="5.14285714285714"/>
-    <col min="2" max="3" customWidth="true" width="28.2857142857143"/>
-    <col min="4" max="4" customWidth="true" width="79.4285714285714"/>
-    <col min="5" max="5" customWidth="true" width="11.5714285714286"/>
-    <col min="6" max="6" customWidth="true" width="5.14285714285714"/>
-    <col min="7" max="7" customWidth="true" width="11.0"/>
-    <col min="8" max="8" customWidth="true" width="12.7142857142857"/>
-    <col min="9" max="9" customWidth="true" width="5.85714285714286"/>
-    <col min="10" max="10" customWidth="true" width="6.0"/>
-    <col min="11" max="11" customWidth="true" width="5.85714285714286"/>
-    <col min="12" max="12" customWidth="true" width="14.2857142857143"/>
-    <col min="13" max="13" customWidth="true" width="9.42857142857143"/>
-    <col min="14" max="14" customWidth="true" width="14.4285714285714"/>
-    <col min="15" max="15" customWidth="true" width="15.5714285714286"/>
-    <col min="16" max="16" customWidth="true" width="14.4285714285714"/>
-    <col min="17" max="17" customWidth="true" width="39.4285714285714"/>
-    <col min="18" max="18" customWidth="true" width="11.7142857142857"/>
-    <col min="19" max="19" customWidth="true" width="11.8571428571429"/>
-    <col min="20" max="20" customWidth="true" width="6.42857142857143"/>
-    <col min="21" max="22" customWidth="true" width="6.57142857142857"/>
-    <col min="23" max="23" customWidth="true" width="37.1428571428571"/>
-    <col min="24" max="25" customWidth="true" width="8.0"/>
-    <col min="26" max="26" customWidth="true" width="7.71428571428571"/>
-    <col min="27" max="27" customWidth="true" width="6.28571428571429"/>
-    <col min="28" max="28" customWidth="true" width="9.28571428571429"/>
-    <col min="29" max="29" customWidth="true" width="9.71428571428571"/>
-    <col min="30" max="30" customWidth="true" width="12.8571428571429"/>
-    <col min="31" max="31" customWidth="true" width="16.1428571428571"/>
-    <col min="32" max="32" customWidth="true" width="15.4285714285714"/>
-    <col min="33" max="33" customWidth="true" width="24.5714285714286"/>
-    <col min="34" max="34" customWidth="true" width="8.57142857142857"/>
-    <col min="35" max="35" customWidth="true" width="14.7142857142857"/>
-    <col min="36" max="36" customWidth="true" width="18.5714285714286"/>
-    <col min="37" max="37" customWidth="true" width="14.1428571428571"/>
-    <col min="38" max="38" customWidth="true" width="14.7142857142857"/>
-    <col min="39" max="39" customWidth="true" width="17.4285714285714"/>
-    <col min="40" max="40" customWidth="true" width="22.0"/>
-    <col min="41" max="41" customWidth="true" width="17.5714285714286"/>
-    <col min="42" max="42" customWidth="true" width="25.2857142857143"/>
-    <col min="43" max="43" customWidth="true" width="13.0"/>
-    <col min="44" max="44" customWidth="true" width="23.7142857142857"/>
-    <col min="45" max="45" customWidth="true" width="10.0"/>
-    <col min="46" max="46" customWidth="true" width="13.0"/>
-    <col min="47" max="47" customWidth="true" width="15.5714285714286"/>
-    <col min="48" max="48" customWidth="true" width="21.1428571428571"/>
-    <col min="49" max="49" customWidth="true" width="11.5714285714286"/>
-    <col min="50" max="50" customWidth="true" width="16.7142857142857"/>
-    <col min="51" max="51" customWidth="true" width="14.0"/>
-    <col min="52" max="52" customWidth="true" width="19.4285714285714"/>
-    <col min="53" max="53" customWidth="true" width="18.8571428571429"/>
-    <col min="54" max="54" customWidth="true" width="23.2857142857143"/>
-    <col min="55" max="55" customWidth="true" width="15.5714285714286"/>
-    <col min="56" max="56" customWidth="true" width="14.2857142857143"/>
-    <col min="57" max="57" customWidth="true" width="17.0"/>
-    <col min="58" max="58" customWidth="true" width="16.2857142857143"/>
-    <col min="59" max="59" customWidth="true" width="13.5714285714286"/>
-    <col min="60" max="61" customWidth="true" width="12.7142857142857"/>
-    <col min="62" max="62" customWidth="true" width="21.8571428571429"/>
-    <col min="63" max="63" customWidth="true" width="30.5714285714286"/>
-    <col min="64" max="64" customWidth="true" width="10.0"/>
-    <col min="65" max="65" customWidth="true" width="42.5714285714286"/>
-    <col min="66" max="66" customWidth="true" width="38.1428571428571"/>
-    <col min="67" max="67" customWidth="true" width="19.4285714285714"/>
-    <col min="68" max="68" customWidth="true" width="35.4285714285714"/>
-    <col min="69" max="69" customWidth="true" width="9.57142857142857"/>
+    <col min="1" max="1" width="5.14545454545455" customWidth="1"/>
+    <col min="2" max="3" width="28.2818181818182" customWidth="1"/>
+    <col min="4" max="4" width="79.4272727272727" customWidth="1"/>
+    <col min="5" max="5" width="11.5727272727273" customWidth="1"/>
+    <col min="6" max="6" width="5.14545454545455" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="12.7181818181818" customWidth="1"/>
+    <col min="9" max="9" width="5.85454545454545" customWidth="1"/>
+    <col min="10" max="10" width="6" customWidth="1"/>
+    <col min="11" max="11" width="5.85454545454545" customWidth="1"/>
+    <col min="12" max="12" width="14.2818181818182" customWidth="1"/>
+    <col min="13" max="13" width="9.42727272727273" customWidth="1"/>
+    <col min="14" max="14" width="14.4272727272727" customWidth="1"/>
+    <col min="15" max="15" width="15.5727272727273" customWidth="1"/>
+    <col min="16" max="16" width="14.4272727272727" customWidth="1"/>
+    <col min="17" max="17" width="39.4272727272727" customWidth="1"/>
+    <col min="18" max="18" width="11.7181818181818" customWidth="1"/>
+    <col min="19" max="19" width="11.8545454545455" customWidth="1"/>
+    <col min="20" max="20" width="6.42727272727273" customWidth="1"/>
+    <col min="21" max="22" width="6.57272727272727" customWidth="1"/>
+    <col min="23" max="23" width="37.1454545454545" customWidth="1"/>
+    <col min="24" max="25" width="8" customWidth="1"/>
+    <col min="26" max="26" width="7.71818181818182" customWidth="1"/>
+    <col min="27" max="27" width="6.28181818181818" customWidth="1"/>
+    <col min="28" max="28" width="9.28181818181818" customWidth="1"/>
+    <col min="29" max="29" width="9.71818181818182" customWidth="1"/>
+    <col min="30" max="30" width="12.8545454545455" customWidth="1"/>
+    <col min="31" max="31" width="16.1454545454545" customWidth="1"/>
+    <col min="32" max="32" width="15.4272727272727" customWidth="1"/>
+    <col min="33" max="33" width="24.5727272727273" customWidth="1"/>
+    <col min="34" max="34" width="8.57272727272727" customWidth="1"/>
+    <col min="35" max="35" width="14.7181818181818" customWidth="1"/>
+    <col min="36" max="36" width="18.5727272727273" customWidth="1"/>
+    <col min="37" max="37" width="14.1454545454545" customWidth="1"/>
+    <col min="38" max="38" width="14.7181818181818" customWidth="1"/>
+    <col min="39" max="39" width="17.4272727272727" customWidth="1"/>
+    <col min="40" max="40" width="22" customWidth="1"/>
+    <col min="41" max="41" width="17.5727272727273" customWidth="1"/>
+    <col min="42" max="42" width="25.2818181818182" customWidth="1"/>
+    <col min="43" max="43" width="13" customWidth="1"/>
+    <col min="44" max="44" width="23.7181818181818" customWidth="1"/>
+    <col min="45" max="45" width="10" customWidth="1"/>
+    <col min="46" max="46" width="13" customWidth="1"/>
+    <col min="47" max="47" width="15.5727272727273" customWidth="1"/>
+    <col min="48" max="48" width="21.1454545454545" customWidth="1"/>
+    <col min="49" max="49" width="11.5727272727273" customWidth="1"/>
+    <col min="50" max="50" width="16.7181818181818" customWidth="1"/>
+    <col min="51" max="51" width="14" customWidth="1"/>
+    <col min="52" max="52" width="19.4272727272727" customWidth="1"/>
+    <col min="53" max="53" width="18.8545454545455" customWidth="1"/>
+    <col min="54" max="54" width="23.2818181818182" customWidth="1"/>
+    <col min="55" max="55" width="15.5727272727273" customWidth="1"/>
+    <col min="56" max="56" width="14.2818181818182" customWidth="1"/>
+    <col min="57" max="57" width="17" customWidth="1"/>
+    <col min="58" max="58" width="16.2818181818182" customWidth="1"/>
+    <col min="59" max="59" width="13.5727272727273" customWidth="1"/>
+    <col min="60" max="61" width="12.7181818181818" customWidth="1"/>
+    <col min="62" max="62" width="21.8545454545455" customWidth="1"/>
+    <col min="63" max="63" width="30.5727272727273" customWidth="1"/>
+    <col min="64" max="64" width="10" customWidth="1"/>
+    <col min="65" max="65" width="42.5727272727273" customWidth="1"/>
+    <col min="66" max="66" width="38.1454545454545" customWidth="1"/>
+    <col min="67" max="67" width="19.4272727272727" customWidth="1"/>
+    <col min="68" max="68" width="35.4272727272727" customWidth="1"/>
+    <col min="69" max="69" width="9.57272727272727" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -23418,7 +22879,7 @@
       <c r="BP2" s="27"/>
       <c r="BQ2" s="27"/>
     </row>
-    <row r="3" ht="15.75" spans="1:69">
+    <row r="3" ht="15.25" spans="1:69">
       <c r="A3" s="28" t="s">
         <v>9</v>
       </c>
@@ -23627,7 +23088,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.75" spans="1:69">
+    <row r="4" ht="15.25" spans="1:69">
       <c r="A4" s="26">
         <v>1</v>
       </c>
@@ -23791,8 +23252,6 @@
       <c r="AT4" s="35" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" s="0"/>
-      <c r="AV4" s="0"/>
       <c r="AW4" s="35">
         <f>AM4</f>
         <v>4</v>
@@ -23831,10 +23290,10 @@
       <c r="BL4" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="BM4" t="s" s="0">
+      <c r="BM4" t="s">
         <v>100</v>
       </c>
-      <c r="BN4" t="s" s="0">
+      <c r="BN4" t="s">
         <v>100</v>
       </c>
       <c r="BO4" s="35">

--- a/testdata/PoToGRN-FOC Scenarios.xlsx
+++ b/testdata/PoToGRN-FOC Scenarios.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="6320"/>
+    <workbookView windowWidth="19200" windowHeight="6920" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="D-PoToGRNFOCUDGeneralSameUOMWI" sheetId="32" r:id="rId1"/>
@@ -11004,7 +11004,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.25" spans="1:69">
+    <row r="4" spans="1:69">
       <c r="A4" s="26">
         <v>1</v>
       </c>

--- a/testdata/PoToGRN-FOC Scenarios.xlsx
+++ b/testdata/PoToGRN-FOC Scenarios.xlsx
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2586" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2742" uniqueCount="224">
   <si>
     <t>Purchase Order &amp; GRN</t>
   </si>
@@ -572,6 +572,159 @@
   </si>
   <si>
     <t>161.992</t>
+  </si>
+  <si>
+    <t>630</t>
+  </si>
+  <si>
+    <t>6859.72364</t>
+  </si>
+  <si>
+    <t>1118</t>
+  </si>
+  <si>
+    <t>5018.61692</t>
+  </si>
+  <si>
+    <t>2082</t>
+  </si>
+  <si>
+    <t>3679.49017</t>
+  </si>
+  <si>
+    <t>3718</t>
+  </si>
+  <si>
+    <t>2982.50151</t>
+  </si>
+  <si>
+    <t>544</t>
+  </si>
+  <si>
+    <t>2121.79328</t>
+  </si>
+  <si>
+    <t>1783</t>
+  </si>
+  <si>
+    <t>1781.28226</t>
+  </si>
+  <si>
+    <t>4476.1466</t>
+  </si>
+  <si>
+    <t>1272</t>
+  </si>
+  <si>
+    <t>3083.62724</t>
+  </si>
+  <si>
+    <t>545</t>
+  </si>
+  <si>
+    <t>8188.3901</t>
+  </si>
+  <si>
+    <t>1788</t>
+  </si>
+  <si>
+    <t>5322.85475</t>
+  </si>
+  <si>
+    <t>699</t>
+  </si>
+  <si>
+    <t>4538.80752</t>
+  </si>
+  <si>
+    <t>1258</t>
+  </si>
+  <si>
+    <t>3167.55516</t>
+  </si>
+  <si>
+    <t>211.656</t>
+  </si>
+  <si>
+    <t>13748.09797</t>
+  </si>
+  <si>
+    <t>678.991</t>
+  </si>
+  <si>
+    <t>10681.35923</t>
+  </si>
+  <si>
+    <t>533.322</t>
+  </si>
+  <si>
+    <t>7162.62564</t>
+  </si>
+  <si>
+    <t>1540.992</t>
+  </si>
+  <si>
+    <t>5550.52354</t>
+  </si>
+  <si>
+    <t>303.985</t>
+  </si>
+  <si>
+    <t>11450.08032</t>
+  </si>
+  <si>
+    <t>833.326</t>
+  </si>
+  <si>
+    <t>8534.62923</t>
+  </si>
+  <si>
+    <t>475.65</t>
+  </si>
+  <si>
+    <t>11276.18743</t>
+  </si>
+  <si>
+    <t>1146.993</t>
+  </si>
+  <si>
+    <t>7581.88817</t>
+  </si>
+  <si>
+    <t>270.987</t>
+  </si>
+  <si>
+    <t>12627.95556</t>
+  </si>
+  <si>
+    <t>906.658</t>
+  </si>
+  <si>
+    <t>10072.50148</t>
+  </si>
+  <si>
+    <t>467.991</t>
+  </si>
+  <si>
+    <t>9750.1385</t>
+  </si>
+  <si>
+    <t>1086</t>
+  </si>
+  <si>
+    <t>6642.66948</t>
+  </si>
+  <si>
+    <t>463.327</t>
+  </si>
+  <si>
+    <t>8765.64227</t>
+  </si>
+  <si>
+    <t>1599.992</t>
+  </si>
+  <si>
+    <t>7754.44104</t>
   </si>
 </sst>
 </file>
@@ -1715,71 +1868,71 @@
   <dimension ref="A1:BQ5"/>
   <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" width="5.14545454545455" customWidth="1"/>
-    <col min="2" max="3" width="20.5727272727273" customWidth="1"/>
-    <col min="4" max="4" width="79.4272727272727" customWidth="1"/>
-    <col min="5" max="5" width="11.5727272727273" customWidth="1"/>
-    <col min="6" max="6" width="5.14545454545455" customWidth="1"/>
-    <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="12.7181818181818" customWidth="1"/>
-    <col min="9" max="10" width="5.85454545454545" customWidth="1"/>
-    <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="14.2818181818182" customWidth="1"/>
-    <col min="13" max="13" width="9.42727272727273" customWidth="1"/>
-    <col min="14" max="14" width="14.2818181818182" customWidth="1"/>
-    <col min="15" max="15" width="15.5727272727273" customWidth="1"/>
-    <col min="16" max="16" width="14.4272727272727" customWidth="1"/>
-    <col min="17" max="17" width="39.4272727272727" customWidth="1"/>
-    <col min="18" max="18" width="11.7181818181818" customWidth="1"/>
-    <col min="19" max="19" width="10" customWidth="1"/>
-    <col min="20" max="20" width="6.42727272727273" customWidth="1"/>
-    <col min="21" max="21" width="9.85454545454546" customWidth="1"/>
-    <col min="22" max="22" width="6.57272727272727" customWidth="1"/>
-    <col min="23" max="23" width="37.1454545454545" customWidth="1"/>
-    <col min="24" max="25" width="8" customWidth="1"/>
-    <col min="26" max="26" width="7.71818181818182" customWidth="1"/>
-    <col min="27" max="27" width="6.28181818181818" customWidth="1"/>
-    <col min="28" max="28" width="9.28181818181818" customWidth="1"/>
-    <col min="29" max="29" width="9.71818181818182" customWidth="1"/>
-    <col min="30" max="30" width="12.8545454545455" customWidth="1"/>
-    <col min="31" max="31" width="16.1454545454545" customWidth="1"/>
-    <col min="32" max="32" width="15.4272727272727" customWidth="1"/>
-    <col min="33" max="33" width="24.5727272727273" customWidth="1"/>
-    <col min="34" max="34" width="8.57272727272727" customWidth="1"/>
-    <col min="35" max="35" width="14.7181818181818" customWidth="1"/>
-    <col min="36" max="36" width="18.5727272727273" customWidth="1"/>
-    <col min="37" max="37" width="14.1454545454545" customWidth="1"/>
-    <col min="38" max="38" width="14.7181818181818" customWidth="1"/>
-    <col min="39" max="39" width="17.4272727272727" customWidth="1"/>
-    <col min="40" max="40" width="22" customWidth="1"/>
-    <col min="41" max="41" width="17.5727272727273" customWidth="1"/>
-    <col min="42" max="42" width="25.2818181818182" customWidth="1"/>
-    <col min="43" max="43" width="13" customWidth="1"/>
-    <col min="44" max="44" width="25.7181818181818" customWidth="1"/>
-    <col min="45" max="45" width="10" customWidth="1"/>
-    <col min="46" max="46" width="13" customWidth="1"/>
-    <col min="47" max="47" width="15.5727272727273" customWidth="1"/>
-    <col min="48" max="48" width="21.1454545454545" customWidth="1"/>
-    <col min="49" max="49" width="11.5727272727273" customWidth="1"/>
-    <col min="50" max="50" width="16.7181818181818" customWidth="1"/>
-    <col min="51" max="51" width="14" customWidth="1"/>
-    <col min="52" max="52" width="19.4272727272727" customWidth="1"/>
-    <col min="53" max="53" width="18.8545454545455" customWidth="1"/>
-    <col min="54" max="54" width="23.2818181818182" customWidth="1"/>
-    <col min="55" max="55" width="15.5727272727273" customWidth="1"/>
-    <col min="56" max="56" width="14.2818181818182" customWidth="1"/>
-    <col min="57" max="57" width="17" customWidth="1"/>
-    <col min="58" max="58" width="16.2818181818182" customWidth="1"/>
-    <col min="59" max="59" width="13.5727272727273" customWidth="1"/>
-    <col min="60" max="61" width="12.7181818181818" customWidth="1"/>
-    <col min="62" max="62" width="21.8545454545455" customWidth="1"/>
-    <col min="63" max="63" width="30.5727272727273" customWidth="1"/>
-    <col min="64" max="64" width="10" customWidth="1"/>
-    <col min="65" max="65" width="42.5727272727273" customWidth="1"/>
-    <col min="66" max="66" width="38.1454545454545" customWidth="1"/>
-    <col min="67" max="67" width="19.4272727272727" customWidth="1"/>
-    <col min="68" max="68" width="35.4272727272727" customWidth="1"/>
-    <col min="69" max="69" width="9.57272727272727" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="5.14545454545455"/>
+    <col min="2" max="3" customWidth="true" width="20.5727272727273"/>
+    <col min="4" max="4" customWidth="true" width="79.4272727272727"/>
+    <col min="5" max="5" customWidth="true" width="11.5727272727273"/>
+    <col min="6" max="6" customWidth="true" width="5.14545454545455"/>
+    <col min="7" max="7" customWidth="true" width="11.0"/>
+    <col min="8" max="8" customWidth="true" width="12.7181818181818"/>
+    <col min="9" max="10" customWidth="true" width="5.85454545454545"/>
+    <col min="11" max="11" customWidth="true" width="6.0"/>
+    <col min="12" max="12" customWidth="true" width="14.2818181818182"/>
+    <col min="13" max="13" customWidth="true" width="9.42727272727273"/>
+    <col min="14" max="14" customWidth="true" width="14.2818181818182"/>
+    <col min="15" max="15" customWidth="true" width="15.5727272727273"/>
+    <col min="16" max="16" customWidth="true" width="14.4272727272727"/>
+    <col min="17" max="17" customWidth="true" width="39.4272727272727"/>
+    <col min="18" max="18" customWidth="true" width="11.7181818181818"/>
+    <col min="19" max="19" customWidth="true" width="10.0"/>
+    <col min="20" max="20" customWidth="true" width="6.42727272727273"/>
+    <col min="21" max="21" customWidth="true" width="9.85454545454546"/>
+    <col min="22" max="22" customWidth="true" width="6.57272727272727"/>
+    <col min="23" max="23" customWidth="true" width="37.1454545454545"/>
+    <col min="24" max="25" customWidth="true" width="8.0"/>
+    <col min="26" max="26" customWidth="true" width="7.71818181818182"/>
+    <col min="27" max="27" customWidth="true" width="6.28181818181818"/>
+    <col min="28" max="28" customWidth="true" width="9.28181818181818"/>
+    <col min="29" max="29" customWidth="true" width="9.71818181818182"/>
+    <col min="30" max="30" customWidth="true" width="12.8545454545455"/>
+    <col min="31" max="31" customWidth="true" width="16.1454545454545"/>
+    <col min="32" max="32" customWidth="true" width="15.4272727272727"/>
+    <col min="33" max="33" customWidth="true" width="24.5727272727273"/>
+    <col min="34" max="34" customWidth="true" width="8.57272727272727"/>
+    <col min="35" max="35" customWidth="true" width="14.7181818181818"/>
+    <col min="36" max="36" customWidth="true" width="18.5727272727273"/>
+    <col min="37" max="37" customWidth="true" width="14.1454545454545"/>
+    <col min="38" max="38" customWidth="true" width="14.7181818181818"/>
+    <col min="39" max="39" customWidth="true" width="17.4272727272727"/>
+    <col min="40" max="40" customWidth="true" width="22.0"/>
+    <col min="41" max="41" customWidth="true" width="17.5727272727273"/>
+    <col min="42" max="42" customWidth="true" width="25.2818181818182"/>
+    <col min="43" max="43" customWidth="true" width="13.0"/>
+    <col min="44" max="44" customWidth="true" width="25.7181818181818"/>
+    <col min="45" max="45" customWidth="true" width="10.0"/>
+    <col min="46" max="46" customWidth="true" width="13.0"/>
+    <col min="47" max="47" customWidth="true" width="15.5727272727273"/>
+    <col min="48" max="48" customWidth="true" width="21.1454545454545"/>
+    <col min="49" max="49" customWidth="true" width="11.5727272727273"/>
+    <col min="50" max="50" customWidth="true" width="16.7181818181818"/>
+    <col min="51" max="51" customWidth="true" width="14.0"/>
+    <col min="52" max="52" customWidth="true" width="19.4272727272727"/>
+    <col min="53" max="53" customWidth="true" width="18.8545454545455"/>
+    <col min="54" max="54" customWidth="true" width="23.2818181818182"/>
+    <col min="55" max="55" customWidth="true" width="15.5727272727273"/>
+    <col min="56" max="56" customWidth="true" width="14.2818181818182"/>
+    <col min="57" max="57" customWidth="true" width="17.0"/>
+    <col min="58" max="58" customWidth="true" width="16.2818181818182"/>
+    <col min="59" max="59" customWidth="true" width="13.5727272727273"/>
+    <col min="60" max="61" customWidth="true" width="12.7181818181818"/>
+    <col min="62" max="62" customWidth="true" width="21.8545454545455"/>
+    <col min="63" max="63" customWidth="true" width="30.5727272727273"/>
+    <col min="64" max="64" customWidth="true" width="10.0"/>
+    <col min="65" max="65" customWidth="true" width="42.5727272727273"/>
+    <col min="66" max="66" customWidth="true" width="38.1454545454545"/>
+    <col min="67" max="67" customWidth="true" width="19.4272727272727"/>
+    <col min="68" max="68" customWidth="true" width="35.4272727272727"/>
+    <col min="69" max="69" customWidth="true" width="9.57272727272727"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -2323,11 +2476,11 @@
       <c r="AT4" s="35" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" t="s">
-        <v>79</v>
-      </c>
-      <c r="AV4" t="s">
-        <v>80</v>
+      <c r="AU4" t="s" s="0">
+        <v>173</v>
+      </c>
+      <c r="AV4" t="s" s="0">
+        <v>174</v>
       </c>
       <c r="AW4" s="35">
         <f>AM4</f>
@@ -2341,7 +2494,7 @@
         <f>AU4+AW4</f>
         <v>4</v>
       </c>
-      <c r="AZ4" t="s">
+      <c r="AZ4" t="s" s="0">
         <v>80</v>
       </c>
       <c r="BA4" s="36"/>
@@ -2366,11 +2519,11 @@
       <c r="BL4" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="BM4" t="s">
-        <v>86</v>
-      </c>
-      <c r="BN4" t="s">
-        <v>87</v>
+      <c r="BM4" t="s" s="0">
+        <v>176</v>
+      </c>
+      <c r="BN4" t="s" s="0">
+        <v>175</v>
       </c>
       <c r="BO4" s="35">
         <f>ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
@@ -2529,71 +2682,71 @@
   <dimension ref="A1:BQ5"/>
   <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" width="5.14545454545455" customWidth="1"/>
-    <col min="2" max="3" width="28.2818181818182" customWidth="1"/>
-    <col min="4" max="4" width="79.4272727272727" customWidth="1"/>
-    <col min="5" max="5" width="11.5727272727273" customWidth="1"/>
-    <col min="6" max="6" width="5.14545454545455" customWidth="1"/>
-    <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="12.7181818181818" customWidth="1"/>
-    <col min="9" max="9" width="5.85454545454545" customWidth="1"/>
-    <col min="10" max="10" width="6" customWidth="1"/>
-    <col min="11" max="11" width="5.85454545454545" customWidth="1"/>
-    <col min="12" max="12" width="14.2818181818182" customWidth="1"/>
-    <col min="13" max="13" width="9.42727272727273" customWidth="1"/>
-    <col min="14" max="14" width="14.4272727272727" customWidth="1"/>
-    <col min="15" max="15" width="15.5727272727273" customWidth="1"/>
-    <col min="16" max="16" width="14.4272727272727" customWidth="1"/>
-    <col min="17" max="17" width="39.4272727272727" customWidth="1"/>
-    <col min="18" max="18" width="11.7181818181818" customWidth="1"/>
-    <col min="19" max="19" width="11.8545454545455" customWidth="1"/>
-    <col min="20" max="20" width="6.42727272727273" customWidth="1"/>
-    <col min="21" max="22" width="6.57272727272727" customWidth="1"/>
-    <col min="23" max="23" width="37.1454545454545" customWidth="1"/>
-    <col min="24" max="25" width="8" customWidth="1"/>
-    <col min="26" max="26" width="7.71818181818182" customWidth="1"/>
-    <col min="27" max="27" width="6.28181818181818" customWidth="1"/>
-    <col min="28" max="28" width="9.28181818181818" customWidth="1"/>
-    <col min="29" max="29" width="9.71818181818182" customWidth="1"/>
-    <col min="30" max="30" width="12.8545454545455" customWidth="1"/>
-    <col min="31" max="31" width="16.1454545454545" customWidth="1"/>
-    <col min="32" max="32" width="15.4272727272727" customWidth="1"/>
-    <col min="33" max="33" width="24.5727272727273" customWidth="1"/>
-    <col min="34" max="34" width="8.57272727272727" customWidth="1"/>
-    <col min="35" max="35" width="14.7181818181818" customWidth="1"/>
-    <col min="36" max="36" width="18.5727272727273" customWidth="1"/>
-    <col min="37" max="37" width="14.1454545454545" customWidth="1"/>
-    <col min="38" max="38" width="14.7181818181818" customWidth="1"/>
-    <col min="39" max="39" width="17.4272727272727" customWidth="1"/>
-    <col min="40" max="40" width="22" customWidth="1"/>
-    <col min="41" max="41" width="17.5727272727273" customWidth="1"/>
-    <col min="42" max="42" width="25.2818181818182" customWidth="1"/>
-    <col min="43" max="43" width="13" customWidth="1"/>
-    <col min="44" max="44" width="23.7181818181818" customWidth="1"/>
-    <col min="45" max="45" width="10" customWidth="1"/>
-    <col min="46" max="46" width="13" customWidth="1"/>
-    <col min="47" max="47" width="15.5727272727273" customWidth="1"/>
-    <col min="48" max="48" width="21.1454545454545" customWidth="1"/>
-    <col min="49" max="49" width="11.5727272727273" customWidth="1"/>
-    <col min="50" max="50" width="16.7181818181818" customWidth="1"/>
-    <col min="51" max="51" width="14" customWidth="1"/>
-    <col min="52" max="52" width="19.4272727272727" customWidth="1"/>
-    <col min="53" max="53" width="18.8545454545455" customWidth="1"/>
-    <col min="54" max="54" width="23.2818181818182" customWidth="1"/>
-    <col min="55" max="55" width="15.5727272727273" customWidth="1"/>
-    <col min="56" max="56" width="14.2818181818182" customWidth="1"/>
-    <col min="57" max="57" width="17" customWidth="1"/>
-    <col min="58" max="58" width="16.2818181818182" customWidth="1"/>
-    <col min="59" max="59" width="13.5727272727273" customWidth="1"/>
-    <col min="60" max="61" width="12.7181818181818" customWidth="1"/>
-    <col min="62" max="62" width="21.8545454545455" customWidth="1"/>
-    <col min="63" max="63" width="30.5727272727273" customWidth="1"/>
-    <col min="64" max="64" width="10" customWidth="1"/>
-    <col min="65" max="65" width="42.5727272727273" customWidth="1"/>
-    <col min="66" max="66" width="38.1454545454545" customWidth="1"/>
-    <col min="67" max="67" width="19.4272727272727" customWidth="1"/>
-    <col min="68" max="68" width="35.4272727272727" customWidth="1"/>
-    <col min="69" max="69" width="9.57272727272727" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="5.14545454545455"/>
+    <col min="2" max="3" customWidth="true" width="28.2818181818182"/>
+    <col min="4" max="4" customWidth="true" width="79.4272727272727"/>
+    <col min="5" max="5" customWidth="true" width="11.5727272727273"/>
+    <col min="6" max="6" customWidth="true" width="5.14545454545455"/>
+    <col min="7" max="7" customWidth="true" width="11.0"/>
+    <col min="8" max="8" customWidth="true" width="12.7181818181818"/>
+    <col min="9" max="9" customWidth="true" width="5.85454545454545"/>
+    <col min="10" max="10" customWidth="true" width="6.0"/>
+    <col min="11" max="11" customWidth="true" width="5.85454545454545"/>
+    <col min="12" max="12" customWidth="true" width="14.2818181818182"/>
+    <col min="13" max="13" customWidth="true" width="9.42727272727273"/>
+    <col min="14" max="14" customWidth="true" width="14.4272727272727"/>
+    <col min="15" max="15" customWidth="true" width="15.5727272727273"/>
+    <col min="16" max="16" customWidth="true" width="14.4272727272727"/>
+    <col min="17" max="17" customWidth="true" width="39.4272727272727"/>
+    <col min="18" max="18" customWidth="true" width="11.7181818181818"/>
+    <col min="19" max="19" customWidth="true" width="11.8545454545455"/>
+    <col min="20" max="20" customWidth="true" width="6.42727272727273"/>
+    <col min="21" max="22" customWidth="true" width="6.57272727272727"/>
+    <col min="23" max="23" customWidth="true" width="37.1454545454545"/>
+    <col min="24" max="25" customWidth="true" width="8.0"/>
+    <col min="26" max="26" customWidth="true" width="7.71818181818182"/>
+    <col min="27" max="27" customWidth="true" width="6.28181818181818"/>
+    <col min="28" max="28" customWidth="true" width="9.28181818181818"/>
+    <col min="29" max="29" customWidth="true" width="9.71818181818182"/>
+    <col min="30" max="30" customWidth="true" width="12.8545454545455"/>
+    <col min="31" max="31" customWidth="true" width="16.1454545454545"/>
+    <col min="32" max="32" customWidth="true" width="15.4272727272727"/>
+    <col min="33" max="33" customWidth="true" width="24.5727272727273"/>
+    <col min="34" max="34" customWidth="true" width="8.57272727272727"/>
+    <col min="35" max="35" customWidth="true" width="14.7181818181818"/>
+    <col min="36" max="36" customWidth="true" width="18.5727272727273"/>
+    <col min="37" max="37" customWidth="true" width="14.1454545454545"/>
+    <col min="38" max="38" customWidth="true" width="14.7181818181818"/>
+    <col min="39" max="39" customWidth="true" width="17.4272727272727"/>
+    <col min="40" max="40" customWidth="true" width="22.0"/>
+    <col min="41" max="41" customWidth="true" width="17.5727272727273"/>
+    <col min="42" max="42" customWidth="true" width="25.2818181818182"/>
+    <col min="43" max="43" customWidth="true" width="13.0"/>
+    <col min="44" max="44" customWidth="true" width="23.7181818181818"/>
+    <col min="45" max="45" customWidth="true" width="10.0"/>
+    <col min="46" max="46" customWidth="true" width="13.0"/>
+    <col min="47" max="47" customWidth="true" width="15.5727272727273"/>
+    <col min="48" max="48" customWidth="true" width="21.1454545454545"/>
+    <col min="49" max="49" customWidth="true" width="11.5727272727273"/>
+    <col min="50" max="50" customWidth="true" width="16.7181818181818"/>
+    <col min="51" max="51" customWidth="true" width="14.0"/>
+    <col min="52" max="52" customWidth="true" width="19.4272727272727"/>
+    <col min="53" max="53" customWidth="true" width="18.8545454545455"/>
+    <col min="54" max="54" customWidth="true" width="23.2818181818182"/>
+    <col min="55" max="55" customWidth="true" width="15.5727272727273"/>
+    <col min="56" max="56" customWidth="true" width="14.2818181818182"/>
+    <col min="57" max="57" customWidth="true" width="17.0"/>
+    <col min="58" max="58" customWidth="true" width="16.2818181818182"/>
+    <col min="59" max="59" customWidth="true" width="13.5727272727273"/>
+    <col min="60" max="61" customWidth="true" width="12.7181818181818"/>
+    <col min="62" max="62" customWidth="true" width="21.8545454545455"/>
+    <col min="63" max="63" customWidth="true" width="30.5727272727273"/>
+    <col min="64" max="64" customWidth="true" width="10.0"/>
+    <col min="65" max="65" customWidth="true" width="42.5727272727273"/>
+    <col min="66" max="66" customWidth="true" width="38.1454545454545"/>
+    <col min="67" max="67" customWidth="true" width="19.4272727272727"/>
+    <col min="68" max="68" customWidth="true" width="35.4272727272727"/>
+    <col min="69" max="69" customWidth="true" width="9.57272727272727"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -3137,6 +3290,8 @@
       <c r="AT4" s="35" t="s">
         <v>76</v>
       </c>
+      <c r="AU4" s="0"/>
+      <c r="AV4" s="0"/>
       <c r="AW4" s="35">
         <f>AM4</f>
         <v>4</v>
@@ -3175,10 +3330,10 @@
       <c r="BL4" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="BM4" t="s">
+      <c r="BM4" t="s" s="0">
         <v>100</v>
       </c>
-      <c r="BN4" t="s">
+      <c r="BN4" t="s" s="0">
         <v>100</v>
       </c>
       <c r="BO4" s="35">
@@ -3326,71 +3481,71 @@
   <dimension ref="A1:BQ5"/>
   <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" width="5.14545454545455" customWidth="1"/>
-    <col min="2" max="3" width="24.7181818181818" customWidth="1"/>
-    <col min="4" max="4" width="79.4272727272727" customWidth="1"/>
-    <col min="5" max="5" width="11.5727272727273" customWidth="1"/>
-    <col min="6" max="6" width="5.14545454545455" customWidth="1"/>
-    <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="12.7181818181818" customWidth="1"/>
-    <col min="9" max="9" width="5.85454545454545" customWidth="1"/>
-    <col min="10" max="10" width="6" customWidth="1"/>
-    <col min="11" max="11" width="5.85454545454545" customWidth="1"/>
-    <col min="12" max="12" width="14.2818181818182" customWidth="1"/>
-    <col min="13" max="13" width="9.42727272727273" customWidth="1"/>
-    <col min="14" max="14" width="14.4272727272727" customWidth="1"/>
-    <col min="15" max="15" width="15.5727272727273" customWidth="1"/>
-    <col min="16" max="16" width="14.4272727272727" customWidth="1"/>
-    <col min="17" max="17" width="39.4272727272727" customWidth="1"/>
-    <col min="18" max="18" width="11.7181818181818" customWidth="1"/>
-    <col min="19" max="19" width="11.8545454545455" customWidth="1"/>
-    <col min="20" max="20" width="6.42727272727273" customWidth="1"/>
-    <col min="21" max="22" width="6.57272727272727" customWidth="1"/>
-    <col min="23" max="23" width="37.1454545454545" customWidth="1"/>
-    <col min="24" max="25" width="8" customWidth="1"/>
-    <col min="26" max="26" width="7.71818181818182" customWidth="1"/>
-    <col min="27" max="27" width="6.28181818181818" customWidth="1"/>
-    <col min="28" max="28" width="9.28181818181818" customWidth="1"/>
-    <col min="29" max="29" width="9.71818181818182" customWidth="1"/>
-    <col min="30" max="30" width="12.8545454545455" customWidth="1"/>
-    <col min="31" max="31" width="16.1454545454545" customWidth="1"/>
-    <col min="32" max="32" width="15.4272727272727" customWidth="1"/>
-    <col min="33" max="33" width="24.5727272727273" customWidth="1"/>
-    <col min="34" max="34" width="8.57272727272727" customWidth="1"/>
-    <col min="35" max="35" width="14.7181818181818" customWidth="1"/>
-    <col min="36" max="36" width="18.5727272727273" customWidth="1"/>
-    <col min="37" max="37" width="14.1454545454545" customWidth="1"/>
-    <col min="38" max="38" width="14.7181818181818" customWidth="1"/>
-    <col min="39" max="39" width="17.4272727272727" customWidth="1"/>
-    <col min="40" max="40" width="22" customWidth="1"/>
-    <col min="41" max="41" width="17.5727272727273" customWidth="1"/>
-    <col min="42" max="42" width="25.2818181818182" customWidth="1"/>
-    <col min="43" max="43" width="13" customWidth="1"/>
-    <col min="44" max="44" width="23.7181818181818" customWidth="1"/>
-    <col min="45" max="45" width="10" customWidth="1"/>
-    <col min="46" max="46" width="13" customWidth="1"/>
-    <col min="47" max="47" width="15.5727272727273" customWidth="1"/>
-    <col min="48" max="48" width="21.1454545454545" customWidth="1"/>
-    <col min="49" max="49" width="11.5727272727273" customWidth="1"/>
-    <col min="50" max="50" width="16.7181818181818" customWidth="1"/>
-    <col min="51" max="51" width="14" customWidth="1"/>
-    <col min="52" max="52" width="19.4272727272727" customWidth="1"/>
-    <col min="53" max="53" width="18.8545454545455" customWidth="1"/>
-    <col min="54" max="54" width="23.2818181818182" customWidth="1"/>
-    <col min="55" max="55" width="15.5727272727273" customWidth="1"/>
-    <col min="56" max="56" width="14.2818181818182" customWidth="1"/>
-    <col min="57" max="57" width="17" customWidth="1"/>
-    <col min="58" max="58" width="16.2818181818182" customWidth="1"/>
-    <col min="59" max="59" width="13.5727272727273" customWidth="1"/>
-    <col min="60" max="61" width="12.7181818181818" customWidth="1"/>
-    <col min="62" max="62" width="21.8545454545455" customWidth="1"/>
-    <col min="63" max="63" width="30.5727272727273" customWidth="1"/>
-    <col min="64" max="64" width="10" customWidth="1"/>
-    <col min="65" max="65" width="42.5727272727273" customWidth="1"/>
-    <col min="66" max="66" width="38.1454545454545" customWidth="1"/>
-    <col min="67" max="67" width="19.4272727272727" customWidth="1"/>
-    <col min="68" max="68" width="35.4272727272727" customWidth="1"/>
-    <col min="69" max="69" width="9.57272727272727" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="5.14545454545455"/>
+    <col min="2" max="3" customWidth="true" width="24.7181818181818"/>
+    <col min="4" max="4" customWidth="true" width="79.4272727272727"/>
+    <col min="5" max="5" customWidth="true" width="11.5727272727273"/>
+    <col min="6" max="6" customWidth="true" width="5.14545454545455"/>
+    <col min="7" max="7" customWidth="true" width="11.0"/>
+    <col min="8" max="8" customWidth="true" width="12.7181818181818"/>
+    <col min="9" max="9" customWidth="true" width="5.85454545454545"/>
+    <col min="10" max="10" customWidth="true" width="6.0"/>
+    <col min="11" max="11" customWidth="true" width="5.85454545454545"/>
+    <col min="12" max="12" customWidth="true" width="14.2818181818182"/>
+    <col min="13" max="13" customWidth="true" width="9.42727272727273"/>
+    <col min="14" max="14" customWidth="true" width="14.4272727272727"/>
+    <col min="15" max="15" customWidth="true" width="15.5727272727273"/>
+    <col min="16" max="16" customWidth="true" width="14.4272727272727"/>
+    <col min="17" max="17" customWidth="true" width="39.4272727272727"/>
+    <col min="18" max="18" customWidth="true" width="11.7181818181818"/>
+    <col min="19" max="19" customWidth="true" width="11.8545454545455"/>
+    <col min="20" max="20" customWidth="true" width="6.42727272727273"/>
+    <col min="21" max="22" customWidth="true" width="6.57272727272727"/>
+    <col min="23" max="23" customWidth="true" width="37.1454545454545"/>
+    <col min="24" max="25" customWidth="true" width="8.0"/>
+    <col min="26" max="26" customWidth="true" width="7.71818181818182"/>
+    <col min="27" max="27" customWidth="true" width="6.28181818181818"/>
+    <col min="28" max="28" customWidth="true" width="9.28181818181818"/>
+    <col min="29" max="29" customWidth="true" width="9.71818181818182"/>
+    <col min="30" max="30" customWidth="true" width="12.8545454545455"/>
+    <col min="31" max="31" customWidth="true" width="16.1454545454545"/>
+    <col min="32" max="32" customWidth="true" width="15.4272727272727"/>
+    <col min="33" max="33" customWidth="true" width="24.5727272727273"/>
+    <col min="34" max="34" customWidth="true" width="8.57272727272727"/>
+    <col min="35" max="35" customWidth="true" width="14.7181818181818"/>
+    <col min="36" max="36" customWidth="true" width="18.5727272727273"/>
+    <col min="37" max="37" customWidth="true" width="14.1454545454545"/>
+    <col min="38" max="38" customWidth="true" width="14.7181818181818"/>
+    <col min="39" max="39" customWidth="true" width="17.4272727272727"/>
+    <col min="40" max="40" customWidth="true" width="22.0"/>
+    <col min="41" max="41" customWidth="true" width="17.5727272727273"/>
+    <col min="42" max="42" customWidth="true" width="25.2818181818182"/>
+    <col min="43" max="43" customWidth="true" width="13.0"/>
+    <col min="44" max="44" customWidth="true" width="23.7181818181818"/>
+    <col min="45" max="45" customWidth="true" width="10.0"/>
+    <col min="46" max="46" customWidth="true" width="13.0"/>
+    <col min="47" max="47" customWidth="true" width="15.5727272727273"/>
+    <col min="48" max="48" customWidth="true" width="21.1454545454545"/>
+    <col min="49" max="49" customWidth="true" width="11.5727272727273"/>
+    <col min="50" max="50" customWidth="true" width="16.7181818181818"/>
+    <col min="51" max="51" customWidth="true" width="14.0"/>
+    <col min="52" max="52" customWidth="true" width="19.4272727272727"/>
+    <col min="53" max="53" customWidth="true" width="18.8545454545455"/>
+    <col min="54" max="54" customWidth="true" width="23.2818181818182"/>
+    <col min="55" max="55" customWidth="true" width="15.5727272727273"/>
+    <col min="56" max="56" customWidth="true" width="14.2818181818182"/>
+    <col min="57" max="57" customWidth="true" width="17.0"/>
+    <col min="58" max="58" customWidth="true" width="16.2818181818182"/>
+    <col min="59" max="59" customWidth="true" width="13.5727272727273"/>
+    <col min="60" max="61" customWidth="true" width="12.7181818181818"/>
+    <col min="62" max="62" customWidth="true" width="21.8545454545455"/>
+    <col min="63" max="63" customWidth="true" width="30.5727272727273"/>
+    <col min="64" max="64" customWidth="true" width="10.0"/>
+    <col min="65" max="65" customWidth="true" width="42.5727272727273"/>
+    <col min="66" max="66" customWidth="true" width="38.1454545454545"/>
+    <col min="67" max="67" customWidth="true" width="19.4272727272727"/>
+    <col min="68" max="68" customWidth="true" width="35.4272727272727"/>
+    <col min="69" max="69" customWidth="true" width="9.57272727272727"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -3934,11 +4089,11 @@
       <c r="AT4" s="35" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" t="s">
-        <v>118</v>
-      </c>
-      <c r="AV4" t="s">
-        <v>119</v>
+      <c r="AU4" t="s" s="0">
+        <v>188</v>
+      </c>
+      <c r="AV4" t="s" s="0">
+        <v>189</v>
       </c>
       <c r="AW4" s="35">
         <f>AM4</f>
@@ -3978,11 +4133,11 @@
       <c r="BL4" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="BM4" t="s">
-        <v>120</v>
-      </c>
-      <c r="BN4" t="s">
-        <v>121</v>
+      <c r="BM4" t="s" s="0">
+        <v>191</v>
+      </c>
+      <c r="BN4" t="s" s="0">
+        <v>190</v>
       </c>
       <c r="BO4" s="35">
         <f>ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
@@ -4141,71 +4296,71 @@
   <dimension ref="A1:BQ5"/>
   <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" width="5.14545454545455" customWidth="1"/>
-    <col min="2" max="3" width="24.7181818181818" customWidth="1"/>
-    <col min="4" max="4" width="79.4272727272727" customWidth="1"/>
-    <col min="5" max="5" width="11.5727272727273" customWidth="1"/>
-    <col min="6" max="6" width="5.14545454545455" customWidth="1"/>
-    <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="12.7181818181818" customWidth="1"/>
-    <col min="9" max="9" width="5.85454545454545" customWidth="1"/>
-    <col min="10" max="10" width="6" customWidth="1"/>
-    <col min="11" max="11" width="5.85454545454545" customWidth="1"/>
-    <col min="12" max="12" width="14.2818181818182" customWidth="1"/>
-    <col min="13" max="13" width="9.42727272727273" customWidth="1"/>
-    <col min="14" max="14" width="14.4272727272727" customWidth="1"/>
-    <col min="15" max="15" width="15.5727272727273" customWidth="1"/>
-    <col min="16" max="16" width="14.4272727272727" customWidth="1"/>
-    <col min="17" max="17" width="39.4272727272727" customWidth="1"/>
-    <col min="18" max="18" width="11.7181818181818" customWidth="1"/>
-    <col min="19" max="19" width="11.8545454545455" customWidth="1"/>
-    <col min="20" max="20" width="6.42727272727273" customWidth="1"/>
-    <col min="21" max="22" width="6.57272727272727" customWidth="1"/>
-    <col min="23" max="23" width="37.1454545454545" customWidth="1"/>
-    <col min="24" max="25" width="8" customWidth="1"/>
-    <col min="26" max="26" width="7.71818181818182" customWidth="1"/>
-    <col min="27" max="27" width="6.28181818181818" customWidth="1"/>
-    <col min="28" max="28" width="9.28181818181818" customWidth="1"/>
-    <col min="29" max="29" width="9.71818181818182" customWidth="1"/>
-    <col min="30" max="30" width="12.8545454545455" customWidth="1"/>
-    <col min="31" max="31" width="16.1454545454545" customWidth="1"/>
-    <col min="32" max="32" width="15.4272727272727" customWidth="1"/>
-    <col min="33" max="33" width="24.5727272727273" customWidth="1"/>
-    <col min="34" max="34" width="8.57272727272727" customWidth="1"/>
-    <col min="35" max="35" width="14.7181818181818" customWidth="1"/>
-    <col min="36" max="36" width="18.5727272727273" customWidth="1"/>
-    <col min="37" max="37" width="14.1454545454545" customWidth="1"/>
-    <col min="38" max="38" width="14.7181818181818" customWidth="1"/>
-    <col min="39" max="39" width="17.4272727272727" customWidth="1"/>
-    <col min="40" max="40" width="22" customWidth="1"/>
-    <col min="41" max="41" width="17.5727272727273" customWidth="1"/>
-    <col min="42" max="42" width="25.2818181818182" customWidth="1"/>
-    <col min="43" max="43" width="13" customWidth="1"/>
-    <col min="44" max="44" width="23.7181818181818" customWidth="1"/>
-    <col min="45" max="45" width="10" customWidth="1"/>
-    <col min="46" max="46" width="13" customWidth="1"/>
-    <col min="47" max="47" width="15.5727272727273" customWidth="1"/>
-    <col min="48" max="48" width="21.1454545454545" customWidth="1"/>
-    <col min="49" max="49" width="11.5727272727273" customWidth="1"/>
-    <col min="50" max="50" width="16.7181818181818" customWidth="1"/>
-    <col min="51" max="51" width="14" customWidth="1"/>
-    <col min="52" max="52" width="19.4272727272727" customWidth="1"/>
-    <col min="53" max="53" width="18.8545454545455" customWidth="1"/>
-    <col min="54" max="54" width="23.2818181818182" customWidth="1"/>
-    <col min="55" max="55" width="15.5727272727273" customWidth="1"/>
-    <col min="56" max="56" width="14.2818181818182" customWidth="1"/>
-    <col min="57" max="57" width="17" customWidth="1"/>
-    <col min="58" max="58" width="16.2818181818182" customWidth="1"/>
-    <col min="59" max="59" width="13.5727272727273" customWidth="1"/>
-    <col min="60" max="61" width="12.7181818181818" customWidth="1"/>
-    <col min="62" max="62" width="21.8545454545455" customWidth="1"/>
-    <col min="63" max="63" width="30.5727272727273" customWidth="1"/>
-    <col min="64" max="64" width="10" customWidth="1"/>
-    <col min="65" max="65" width="42.5727272727273" customWidth="1"/>
-    <col min="66" max="66" width="38.1454545454545" customWidth="1"/>
-    <col min="67" max="67" width="19.4272727272727" customWidth="1"/>
-    <col min="68" max="68" width="35.4272727272727" customWidth="1"/>
-    <col min="69" max="69" width="9.57272727272727" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="5.14545454545455"/>
+    <col min="2" max="3" customWidth="true" width="24.7181818181818"/>
+    <col min="4" max="4" customWidth="true" width="79.4272727272727"/>
+    <col min="5" max="5" customWidth="true" width="11.5727272727273"/>
+    <col min="6" max="6" customWidth="true" width="5.14545454545455"/>
+    <col min="7" max="7" customWidth="true" width="11.0"/>
+    <col min="8" max="8" customWidth="true" width="12.7181818181818"/>
+    <col min="9" max="9" customWidth="true" width="5.85454545454545"/>
+    <col min="10" max="10" customWidth="true" width="6.0"/>
+    <col min="11" max="11" customWidth="true" width="5.85454545454545"/>
+    <col min="12" max="12" customWidth="true" width="14.2818181818182"/>
+    <col min="13" max="13" customWidth="true" width="9.42727272727273"/>
+    <col min="14" max="14" customWidth="true" width="14.4272727272727"/>
+    <col min="15" max="15" customWidth="true" width="15.5727272727273"/>
+    <col min="16" max="16" customWidth="true" width="14.4272727272727"/>
+    <col min="17" max="17" customWidth="true" width="39.4272727272727"/>
+    <col min="18" max="18" customWidth="true" width="11.7181818181818"/>
+    <col min="19" max="19" customWidth="true" width="11.8545454545455"/>
+    <col min="20" max="20" customWidth="true" width="6.42727272727273"/>
+    <col min="21" max="22" customWidth="true" width="6.57272727272727"/>
+    <col min="23" max="23" customWidth="true" width="37.1454545454545"/>
+    <col min="24" max="25" customWidth="true" width="8.0"/>
+    <col min="26" max="26" customWidth="true" width="7.71818181818182"/>
+    <col min="27" max="27" customWidth="true" width="6.28181818181818"/>
+    <col min="28" max="28" customWidth="true" width="9.28181818181818"/>
+    <col min="29" max="29" customWidth="true" width="9.71818181818182"/>
+    <col min="30" max="30" customWidth="true" width="12.8545454545455"/>
+    <col min="31" max="31" customWidth="true" width="16.1454545454545"/>
+    <col min="32" max="32" customWidth="true" width="15.4272727272727"/>
+    <col min="33" max="33" customWidth="true" width="24.5727272727273"/>
+    <col min="34" max="34" customWidth="true" width="8.57272727272727"/>
+    <col min="35" max="35" customWidth="true" width="14.7181818181818"/>
+    <col min="36" max="36" customWidth="true" width="18.5727272727273"/>
+    <col min="37" max="37" customWidth="true" width="14.1454545454545"/>
+    <col min="38" max="38" customWidth="true" width="14.7181818181818"/>
+    <col min="39" max="39" customWidth="true" width="17.4272727272727"/>
+    <col min="40" max="40" customWidth="true" width="22.0"/>
+    <col min="41" max="41" customWidth="true" width="17.5727272727273"/>
+    <col min="42" max="42" customWidth="true" width="25.2818181818182"/>
+    <col min="43" max="43" customWidth="true" width="13.0"/>
+    <col min="44" max="44" customWidth="true" width="23.7181818181818"/>
+    <col min="45" max="45" customWidth="true" width="10.0"/>
+    <col min="46" max="46" customWidth="true" width="13.0"/>
+    <col min="47" max="47" customWidth="true" width="15.5727272727273"/>
+    <col min="48" max="48" customWidth="true" width="21.1454545454545"/>
+    <col min="49" max="49" customWidth="true" width="11.5727272727273"/>
+    <col min="50" max="50" customWidth="true" width="16.7181818181818"/>
+    <col min="51" max="51" customWidth="true" width="14.0"/>
+    <col min="52" max="52" customWidth="true" width="19.4272727272727"/>
+    <col min="53" max="53" customWidth="true" width="18.8545454545455"/>
+    <col min="54" max="54" customWidth="true" width="23.2818181818182"/>
+    <col min="55" max="55" customWidth="true" width="15.5727272727273"/>
+    <col min="56" max="56" customWidth="true" width="14.2818181818182"/>
+    <col min="57" max="57" customWidth="true" width="17.0"/>
+    <col min="58" max="58" customWidth="true" width="16.2818181818182"/>
+    <col min="59" max="59" customWidth="true" width="13.5727272727273"/>
+    <col min="60" max="61" customWidth="true" width="12.7181818181818"/>
+    <col min="62" max="62" customWidth="true" width="21.8545454545455"/>
+    <col min="63" max="63" customWidth="true" width="30.5727272727273"/>
+    <col min="64" max="64" customWidth="true" width="10.0"/>
+    <col min="65" max="65" customWidth="true" width="42.5727272727273"/>
+    <col min="66" max="66" customWidth="true" width="38.1454545454545"/>
+    <col min="67" max="67" customWidth="true" width="19.4272727272727"/>
+    <col min="68" max="68" customWidth="true" width="35.4272727272727"/>
+    <col min="69" max="69" customWidth="true" width="9.57272727272727"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -4749,11 +4904,11 @@
       <c r="AT4" s="35" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" t="s">
-        <v>123</v>
-      </c>
-      <c r="AV4" t="s">
-        <v>124</v>
+      <c r="AU4" t="s" s="0">
+        <v>192</v>
+      </c>
+      <c r="AV4" t="s" s="0">
+        <v>193</v>
       </c>
       <c r="AW4" s="35">
         <f>AM4</f>
@@ -4793,11 +4948,11 @@
       <c r="BL4" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="BM4" t="s">
-        <v>125</v>
-      </c>
-      <c r="BN4" t="s">
-        <v>126</v>
+      <c r="BM4" t="s" s="0">
+        <v>195</v>
+      </c>
+      <c r="BN4" t="s" s="0">
+        <v>194</v>
       </c>
       <c r="BO4" s="35">
         <f>ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
@@ -4944,71 +5099,71 @@
   <dimension ref="A1:BQ5"/>
   <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" width="5.14545454545455" customWidth="1"/>
-    <col min="2" max="3" width="25.1454545454545" customWidth="1"/>
-    <col min="4" max="4" width="79.4272727272727" customWidth="1"/>
-    <col min="5" max="5" width="11.5727272727273" customWidth="1"/>
-    <col min="6" max="6" width="5.14545454545455" customWidth="1"/>
-    <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="12.7181818181818" customWidth="1"/>
-    <col min="9" max="9" width="5.85454545454545" customWidth="1"/>
-    <col min="10" max="10" width="6" customWidth="1"/>
-    <col min="11" max="11" width="5.85454545454545" customWidth="1"/>
-    <col min="12" max="12" width="14.2818181818182" customWidth="1"/>
-    <col min="13" max="13" width="9.42727272727273" customWidth="1"/>
-    <col min="14" max="14" width="14.4272727272727" customWidth="1"/>
-    <col min="15" max="15" width="15.5727272727273" customWidth="1"/>
-    <col min="16" max="16" width="14.4272727272727" customWidth="1"/>
-    <col min="17" max="17" width="39.4272727272727" customWidth="1"/>
-    <col min="18" max="18" width="11.7181818181818" customWidth="1"/>
-    <col min="19" max="19" width="11.8545454545455" customWidth="1"/>
-    <col min="20" max="20" width="6.42727272727273" customWidth="1"/>
-    <col min="21" max="22" width="6.57272727272727" customWidth="1"/>
-    <col min="23" max="23" width="37.1454545454545" customWidth="1"/>
-    <col min="24" max="25" width="8" customWidth="1"/>
-    <col min="26" max="26" width="7.71818181818182" customWidth="1"/>
-    <col min="27" max="27" width="6.28181818181818" customWidth="1"/>
-    <col min="28" max="28" width="9.28181818181818" customWidth="1"/>
-    <col min="29" max="29" width="9.71818181818182" customWidth="1"/>
-    <col min="30" max="30" width="12.8545454545455" customWidth="1"/>
-    <col min="31" max="31" width="16.1454545454545" customWidth="1"/>
-    <col min="32" max="32" width="15.4272727272727" customWidth="1"/>
-    <col min="33" max="33" width="24.5727272727273" customWidth="1"/>
-    <col min="34" max="34" width="8.57272727272727" customWidth="1"/>
-    <col min="35" max="35" width="14.7181818181818" customWidth="1"/>
-    <col min="36" max="36" width="18.5727272727273" customWidth="1"/>
-    <col min="37" max="37" width="14.1454545454545" customWidth="1"/>
-    <col min="38" max="38" width="14.7181818181818" customWidth="1"/>
-    <col min="39" max="39" width="17.4272727272727" customWidth="1"/>
-    <col min="40" max="40" width="22" customWidth="1"/>
-    <col min="41" max="41" width="17.5727272727273" customWidth="1"/>
-    <col min="42" max="42" width="25.2818181818182" customWidth="1"/>
-    <col min="43" max="43" width="13" customWidth="1"/>
-    <col min="44" max="44" width="23.7181818181818" customWidth="1"/>
-    <col min="45" max="45" width="10" customWidth="1"/>
-    <col min="46" max="46" width="13" customWidth="1"/>
-    <col min="47" max="47" width="15.5727272727273" customWidth="1"/>
-    <col min="48" max="48" width="21.1454545454545" customWidth="1"/>
-    <col min="49" max="49" width="11.5727272727273" customWidth="1"/>
-    <col min="50" max="50" width="16.7181818181818" customWidth="1"/>
-    <col min="51" max="51" width="14" customWidth="1"/>
-    <col min="52" max="52" width="19.4272727272727" customWidth="1"/>
-    <col min="53" max="53" width="18.8545454545455" customWidth="1"/>
-    <col min="54" max="54" width="23.2818181818182" customWidth="1"/>
-    <col min="55" max="55" width="15.5727272727273" customWidth="1"/>
-    <col min="56" max="56" width="14.2818181818182" customWidth="1"/>
-    <col min="57" max="57" width="17" customWidth="1"/>
-    <col min="58" max="58" width="16.2818181818182" customWidth="1"/>
-    <col min="59" max="59" width="13.5727272727273" customWidth="1"/>
-    <col min="60" max="61" width="12.7181818181818" customWidth="1"/>
-    <col min="62" max="62" width="21.8545454545455" customWidth="1"/>
-    <col min="63" max="63" width="30.5727272727273" customWidth="1"/>
-    <col min="64" max="64" width="10" customWidth="1"/>
-    <col min="65" max="65" width="42.5727272727273" customWidth="1"/>
-    <col min="66" max="66" width="38.1454545454545" customWidth="1"/>
-    <col min="67" max="67" width="19.4272727272727" customWidth="1"/>
-    <col min="68" max="68" width="35.4272727272727" customWidth="1"/>
-    <col min="69" max="69" width="9.57272727272727" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="5.14545454545455"/>
+    <col min="2" max="3" customWidth="true" width="25.1454545454545"/>
+    <col min="4" max="4" customWidth="true" width="79.4272727272727"/>
+    <col min="5" max="5" customWidth="true" width="11.5727272727273"/>
+    <col min="6" max="6" customWidth="true" width="5.14545454545455"/>
+    <col min="7" max="7" customWidth="true" width="11.0"/>
+    <col min="8" max="8" customWidth="true" width="12.7181818181818"/>
+    <col min="9" max="9" customWidth="true" width="5.85454545454545"/>
+    <col min="10" max="10" customWidth="true" width="6.0"/>
+    <col min="11" max="11" customWidth="true" width="5.85454545454545"/>
+    <col min="12" max="12" customWidth="true" width="14.2818181818182"/>
+    <col min="13" max="13" customWidth="true" width="9.42727272727273"/>
+    <col min="14" max="14" customWidth="true" width="14.4272727272727"/>
+    <col min="15" max="15" customWidth="true" width="15.5727272727273"/>
+    <col min="16" max="16" customWidth="true" width="14.4272727272727"/>
+    <col min="17" max="17" customWidth="true" width="39.4272727272727"/>
+    <col min="18" max="18" customWidth="true" width="11.7181818181818"/>
+    <col min="19" max="19" customWidth="true" width="11.8545454545455"/>
+    <col min="20" max="20" customWidth="true" width="6.42727272727273"/>
+    <col min="21" max="22" customWidth="true" width="6.57272727272727"/>
+    <col min="23" max="23" customWidth="true" width="37.1454545454545"/>
+    <col min="24" max="25" customWidth="true" width="8.0"/>
+    <col min="26" max="26" customWidth="true" width="7.71818181818182"/>
+    <col min="27" max="27" customWidth="true" width="6.28181818181818"/>
+    <col min="28" max="28" customWidth="true" width="9.28181818181818"/>
+    <col min="29" max="29" customWidth="true" width="9.71818181818182"/>
+    <col min="30" max="30" customWidth="true" width="12.8545454545455"/>
+    <col min="31" max="31" customWidth="true" width="16.1454545454545"/>
+    <col min="32" max="32" customWidth="true" width="15.4272727272727"/>
+    <col min="33" max="33" customWidth="true" width="24.5727272727273"/>
+    <col min="34" max="34" customWidth="true" width="8.57272727272727"/>
+    <col min="35" max="35" customWidth="true" width="14.7181818181818"/>
+    <col min="36" max="36" customWidth="true" width="18.5727272727273"/>
+    <col min="37" max="37" customWidth="true" width="14.1454545454545"/>
+    <col min="38" max="38" customWidth="true" width="14.7181818181818"/>
+    <col min="39" max="39" customWidth="true" width="17.4272727272727"/>
+    <col min="40" max="40" customWidth="true" width="22.0"/>
+    <col min="41" max="41" customWidth="true" width="17.5727272727273"/>
+    <col min="42" max="42" customWidth="true" width="25.2818181818182"/>
+    <col min="43" max="43" customWidth="true" width="13.0"/>
+    <col min="44" max="44" customWidth="true" width="23.7181818181818"/>
+    <col min="45" max="45" customWidth="true" width="10.0"/>
+    <col min="46" max="46" customWidth="true" width="13.0"/>
+    <col min="47" max="47" customWidth="true" width="15.5727272727273"/>
+    <col min="48" max="48" customWidth="true" width="21.1454545454545"/>
+    <col min="49" max="49" customWidth="true" width="11.5727272727273"/>
+    <col min="50" max="50" customWidth="true" width="16.7181818181818"/>
+    <col min="51" max="51" customWidth="true" width="14.0"/>
+    <col min="52" max="52" customWidth="true" width="19.4272727272727"/>
+    <col min="53" max="53" customWidth="true" width="18.8545454545455"/>
+    <col min="54" max="54" customWidth="true" width="23.2818181818182"/>
+    <col min="55" max="55" customWidth="true" width="15.5727272727273"/>
+    <col min="56" max="56" customWidth="true" width="14.2818181818182"/>
+    <col min="57" max="57" customWidth="true" width="17.0"/>
+    <col min="58" max="58" customWidth="true" width="16.2818181818182"/>
+    <col min="59" max="59" customWidth="true" width="13.5727272727273"/>
+    <col min="60" max="61" customWidth="true" width="12.7181818181818"/>
+    <col min="62" max="62" customWidth="true" width="21.8545454545455"/>
+    <col min="63" max="63" customWidth="true" width="30.5727272727273"/>
+    <col min="64" max="64" customWidth="true" width="10.0"/>
+    <col min="65" max="65" customWidth="true" width="42.5727272727273"/>
+    <col min="66" max="66" customWidth="true" width="38.1454545454545"/>
+    <col min="67" max="67" customWidth="true" width="19.4272727272727"/>
+    <col min="68" max="68" customWidth="true" width="35.4272727272727"/>
+    <col min="69" max="69" customWidth="true" width="9.57272727272727"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -5743,71 +5898,71 @@
   <dimension ref="A1:BQ5"/>
   <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" width="5.14545454545455" customWidth="1"/>
-    <col min="2" max="3" width="22" customWidth="1"/>
-    <col min="4" max="4" width="79.4272727272727" customWidth="1"/>
-    <col min="5" max="5" width="11.5727272727273" customWidth="1"/>
-    <col min="6" max="6" width="5.14545454545455" customWidth="1"/>
-    <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="12.7181818181818" customWidth="1"/>
-    <col min="9" max="9" width="5.85454545454545" customWidth="1"/>
-    <col min="10" max="10" width="6" customWidth="1"/>
-    <col min="11" max="11" width="5.85454545454545" customWidth="1"/>
-    <col min="12" max="12" width="14.2818181818182" customWidth="1"/>
-    <col min="13" max="13" width="9.42727272727273" customWidth="1"/>
-    <col min="14" max="14" width="14.4272727272727" customWidth="1"/>
-    <col min="15" max="15" width="15.5727272727273" customWidth="1"/>
-    <col min="16" max="16" width="14.4272727272727" customWidth="1"/>
-    <col min="17" max="17" width="39.4272727272727" customWidth="1"/>
-    <col min="18" max="18" width="11.7181818181818" customWidth="1"/>
-    <col min="19" max="19" width="11.8545454545455" customWidth="1"/>
-    <col min="20" max="20" width="6.42727272727273" customWidth="1"/>
-    <col min="21" max="22" width="6.57272727272727" customWidth="1"/>
-    <col min="23" max="23" width="37.1454545454545" customWidth="1"/>
-    <col min="24" max="25" width="8" customWidth="1"/>
-    <col min="26" max="26" width="7.71818181818182" customWidth="1"/>
-    <col min="27" max="27" width="6.28181818181818" customWidth="1"/>
-    <col min="28" max="28" width="9.28181818181818" customWidth="1"/>
-    <col min="29" max="29" width="9.71818181818182" customWidth="1"/>
-    <col min="30" max="30" width="12.8545454545455" customWidth="1"/>
-    <col min="31" max="31" width="16.1454545454545" customWidth="1"/>
-    <col min="32" max="32" width="15.4272727272727" customWidth="1"/>
-    <col min="33" max="33" width="24.5727272727273" customWidth="1"/>
-    <col min="34" max="34" width="8.57272727272727" customWidth="1"/>
-    <col min="35" max="35" width="14.7181818181818" customWidth="1"/>
-    <col min="36" max="36" width="18.5727272727273" customWidth="1"/>
-    <col min="37" max="37" width="14.1454545454545" customWidth="1"/>
-    <col min="38" max="38" width="14.7181818181818" customWidth="1"/>
-    <col min="39" max="39" width="17.4272727272727" customWidth="1"/>
-    <col min="40" max="40" width="22" customWidth="1"/>
-    <col min="41" max="41" width="17.5727272727273" customWidth="1"/>
-    <col min="42" max="42" width="25.2818181818182" customWidth="1"/>
-    <col min="43" max="43" width="13" customWidth="1"/>
-    <col min="44" max="44" width="23.7181818181818" customWidth="1"/>
-    <col min="45" max="45" width="10" customWidth="1"/>
-    <col min="46" max="46" width="13" customWidth="1"/>
-    <col min="47" max="47" width="15.5727272727273" customWidth="1"/>
-    <col min="48" max="48" width="21.1454545454545" customWidth="1"/>
-    <col min="49" max="49" width="11.5727272727273" customWidth="1"/>
-    <col min="50" max="50" width="16.7181818181818" customWidth="1"/>
-    <col min="51" max="51" width="14" customWidth="1"/>
-    <col min="52" max="52" width="19.4272727272727" customWidth="1"/>
-    <col min="53" max="53" width="18.8545454545455" customWidth="1"/>
-    <col min="54" max="54" width="23.2818181818182" customWidth="1"/>
-    <col min="55" max="55" width="15.5727272727273" customWidth="1"/>
-    <col min="56" max="56" width="14.2818181818182" customWidth="1"/>
-    <col min="57" max="57" width="17" customWidth="1"/>
-    <col min="58" max="58" width="16.2818181818182" customWidth="1"/>
-    <col min="59" max="59" width="13.5727272727273" customWidth="1"/>
-    <col min="60" max="61" width="12.7181818181818" customWidth="1"/>
-    <col min="62" max="62" width="21.8545454545455" customWidth="1"/>
-    <col min="63" max="63" width="30.5727272727273" customWidth="1"/>
-    <col min="64" max="64" width="10" customWidth="1"/>
-    <col min="65" max="65" width="42.5727272727273" customWidth="1"/>
-    <col min="66" max="66" width="38.1454545454545" customWidth="1"/>
-    <col min="67" max="67" width="19.4272727272727" customWidth="1"/>
-    <col min="68" max="68" width="35.4272727272727" customWidth="1"/>
-    <col min="69" max="69" width="9.57272727272727" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="5.14545454545455"/>
+    <col min="2" max="3" customWidth="true" width="22.0"/>
+    <col min="4" max="4" customWidth="true" width="79.4272727272727"/>
+    <col min="5" max="5" customWidth="true" width="11.5727272727273"/>
+    <col min="6" max="6" customWidth="true" width="5.14545454545455"/>
+    <col min="7" max="7" customWidth="true" width="11.0"/>
+    <col min="8" max="8" customWidth="true" width="12.7181818181818"/>
+    <col min="9" max="9" customWidth="true" width="5.85454545454545"/>
+    <col min="10" max="10" customWidth="true" width="6.0"/>
+    <col min="11" max="11" customWidth="true" width="5.85454545454545"/>
+    <col min="12" max="12" customWidth="true" width="14.2818181818182"/>
+    <col min="13" max="13" customWidth="true" width="9.42727272727273"/>
+    <col min="14" max="14" customWidth="true" width="14.4272727272727"/>
+    <col min="15" max="15" customWidth="true" width="15.5727272727273"/>
+    <col min="16" max="16" customWidth="true" width="14.4272727272727"/>
+    <col min="17" max="17" customWidth="true" width="39.4272727272727"/>
+    <col min="18" max="18" customWidth="true" width="11.7181818181818"/>
+    <col min="19" max="19" customWidth="true" width="11.8545454545455"/>
+    <col min="20" max="20" customWidth="true" width="6.42727272727273"/>
+    <col min="21" max="22" customWidth="true" width="6.57272727272727"/>
+    <col min="23" max="23" customWidth="true" width="37.1454545454545"/>
+    <col min="24" max="25" customWidth="true" width="8.0"/>
+    <col min="26" max="26" customWidth="true" width="7.71818181818182"/>
+    <col min="27" max="27" customWidth="true" width="6.28181818181818"/>
+    <col min="28" max="28" customWidth="true" width="9.28181818181818"/>
+    <col min="29" max="29" customWidth="true" width="9.71818181818182"/>
+    <col min="30" max="30" customWidth="true" width="12.8545454545455"/>
+    <col min="31" max="31" customWidth="true" width="16.1454545454545"/>
+    <col min="32" max="32" customWidth="true" width="15.4272727272727"/>
+    <col min="33" max="33" customWidth="true" width="24.5727272727273"/>
+    <col min="34" max="34" customWidth="true" width="8.57272727272727"/>
+    <col min="35" max="35" customWidth="true" width="14.7181818181818"/>
+    <col min="36" max="36" customWidth="true" width="18.5727272727273"/>
+    <col min="37" max="37" customWidth="true" width="14.1454545454545"/>
+    <col min="38" max="38" customWidth="true" width="14.7181818181818"/>
+    <col min="39" max="39" customWidth="true" width="17.4272727272727"/>
+    <col min="40" max="40" customWidth="true" width="22.0"/>
+    <col min="41" max="41" customWidth="true" width="17.5727272727273"/>
+    <col min="42" max="42" customWidth="true" width="25.2818181818182"/>
+    <col min="43" max="43" customWidth="true" width="13.0"/>
+    <col min="44" max="44" customWidth="true" width="23.7181818181818"/>
+    <col min="45" max="45" customWidth="true" width="10.0"/>
+    <col min="46" max="46" customWidth="true" width="13.0"/>
+    <col min="47" max="47" customWidth="true" width="15.5727272727273"/>
+    <col min="48" max="48" customWidth="true" width="21.1454545454545"/>
+    <col min="49" max="49" customWidth="true" width="11.5727272727273"/>
+    <col min="50" max="50" customWidth="true" width="16.7181818181818"/>
+    <col min="51" max="51" customWidth="true" width="14.0"/>
+    <col min="52" max="52" customWidth="true" width="19.4272727272727"/>
+    <col min="53" max="53" customWidth="true" width="18.8545454545455"/>
+    <col min="54" max="54" customWidth="true" width="23.2818181818182"/>
+    <col min="55" max="55" customWidth="true" width="15.5727272727273"/>
+    <col min="56" max="56" customWidth="true" width="14.2818181818182"/>
+    <col min="57" max="57" customWidth="true" width="17.0"/>
+    <col min="58" max="58" customWidth="true" width="16.2818181818182"/>
+    <col min="59" max="59" customWidth="true" width="13.5727272727273"/>
+    <col min="60" max="61" customWidth="true" width="12.7181818181818"/>
+    <col min="62" max="62" customWidth="true" width="21.8545454545455"/>
+    <col min="63" max="63" customWidth="true" width="30.5727272727273"/>
+    <col min="64" max="64" customWidth="true" width="10.0"/>
+    <col min="65" max="65" customWidth="true" width="42.5727272727273"/>
+    <col min="66" max="66" customWidth="true" width="38.1454545454545"/>
+    <col min="67" max="67" customWidth="true" width="19.4272727272727"/>
+    <col min="68" max="68" customWidth="true" width="35.4272727272727"/>
+    <col min="69" max="69" customWidth="true" width="9.57272727272727"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -6351,6 +6506,8 @@
       <c r="AT4" s="35" t="s">
         <v>76</v>
       </c>
+      <c r="AU4" s="0"/>
+      <c r="AV4" s="0"/>
       <c r="AW4" s="35">
         <f>AM4</f>
         <v>4</v>
@@ -6389,10 +6546,10 @@
       <c r="BL4" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="BM4" t="s">
+      <c r="BM4" t="s" s="0">
         <v>100</v>
       </c>
-      <c r="BN4" t="s">
+      <c r="BN4" t="s" s="0">
         <v>100</v>
       </c>
       <c r="BO4" s="35">
@@ -6540,71 +6697,71 @@
   <dimension ref="A1:BQ5"/>
   <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" width="5.14545454545455" customWidth="1"/>
-    <col min="2" max="3" width="22" customWidth="1"/>
-    <col min="4" max="4" width="79.4272727272727" customWidth="1"/>
-    <col min="5" max="5" width="11.5727272727273" customWidth="1"/>
-    <col min="6" max="6" width="5.14545454545455" customWidth="1"/>
-    <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="12.7181818181818" customWidth="1"/>
-    <col min="9" max="9" width="5.85454545454545" customWidth="1"/>
-    <col min="10" max="10" width="6" customWidth="1"/>
-    <col min="11" max="11" width="5.85454545454545" customWidth="1"/>
-    <col min="12" max="12" width="14.2818181818182" customWidth="1"/>
-    <col min="13" max="13" width="9.42727272727273" customWidth="1"/>
-    <col min="14" max="14" width="14.4272727272727" customWidth="1"/>
-    <col min="15" max="15" width="15.5727272727273" customWidth="1"/>
-    <col min="16" max="16" width="14.4272727272727" customWidth="1"/>
-    <col min="17" max="17" width="39.4272727272727" customWidth="1"/>
-    <col min="18" max="18" width="11.7181818181818" customWidth="1"/>
-    <col min="19" max="19" width="11.8545454545455" customWidth="1"/>
-    <col min="20" max="20" width="6.42727272727273" customWidth="1"/>
-    <col min="21" max="22" width="6.57272727272727" customWidth="1"/>
-    <col min="23" max="23" width="37.1454545454545" customWidth="1"/>
-    <col min="24" max="25" width="8" customWidth="1"/>
-    <col min="26" max="26" width="7.71818181818182" customWidth="1"/>
-    <col min="27" max="27" width="6.28181818181818" customWidth="1"/>
-    <col min="28" max="28" width="9.28181818181818" customWidth="1"/>
-    <col min="29" max="29" width="9.71818181818182" customWidth="1"/>
-    <col min="30" max="30" width="12.8545454545455" customWidth="1"/>
-    <col min="31" max="31" width="16.1454545454545" customWidth="1"/>
-    <col min="32" max="32" width="15.4272727272727" customWidth="1"/>
-    <col min="33" max="33" width="24.5727272727273" customWidth="1"/>
-    <col min="34" max="34" width="8.57272727272727" customWidth="1"/>
-    <col min="35" max="35" width="14.7181818181818" customWidth="1"/>
-    <col min="36" max="36" width="18.5727272727273" customWidth="1"/>
-    <col min="37" max="37" width="14.1454545454545" customWidth="1"/>
-    <col min="38" max="38" width="14.7181818181818" customWidth="1"/>
-    <col min="39" max="39" width="17.4272727272727" customWidth="1"/>
-    <col min="40" max="40" width="22" customWidth="1"/>
-    <col min="41" max="41" width="17.5727272727273" customWidth="1"/>
-    <col min="42" max="42" width="25.2818181818182" customWidth="1"/>
-    <col min="43" max="43" width="13" customWidth="1"/>
-    <col min="44" max="44" width="23.7181818181818" customWidth="1"/>
-    <col min="45" max="45" width="10" customWidth="1"/>
-    <col min="46" max="46" width="13" customWidth="1"/>
-    <col min="47" max="47" width="15.5727272727273" customWidth="1"/>
-    <col min="48" max="48" width="21.1454545454545" customWidth="1"/>
-    <col min="49" max="49" width="11.5727272727273" customWidth="1"/>
-    <col min="50" max="50" width="16.7181818181818" customWidth="1"/>
-    <col min="51" max="51" width="14" customWidth="1"/>
-    <col min="52" max="52" width="19.4272727272727" customWidth="1"/>
-    <col min="53" max="53" width="18.8545454545455" customWidth="1"/>
-    <col min="54" max="54" width="23.2818181818182" customWidth="1"/>
-    <col min="55" max="55" width="15.5727272727273" customWidth="1"/>
-    <col min="56" max="56" width="14.2818181818182" customWidth="1"/>
-    <col min="57" max="57" width="17" customWidth="1"/>
-    <col min="58" max="58" width="16.2818181818182" customWidth="1"/>
-    <col min="59" max="59" width="13.5727272727273" customWidth="1"/>
-    <col min="60" max="61" width="12.7181818181818" customWidth="1"/>
-    <col min="62" max="62" width="21.8545454545455" customWidth="1"/>
-    <col min="63" max="63" width="30.5727272727273" customWidth="1"/>
-    <col min="64" max="64" width="10" customWidth="1"/>
-    <col min="65" max="65" width="42.5727272727273" customWidth="1"/>
-    <col min="66" max="66" width="38.1454545454545" customWidth="1"/>
-    <col min="67" max="67" width="19.4272727272727" customWidth="1"/>
-    <col min="68" max="68" width="35.4272727272727" customWidth="1"/>
-    <col min="69" max="69" width="9.57272727272727" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="5.14545454545455"/>
+    <col min="2" max="3" customWidth="true" width="22.0"/>
+    <col min="4" max="4" customWidth="true" width="79.4272727272727"/>
+    <col min="5" max="5" customWidth="true" width="11.5727272727273"/>
+    <col min="6" max="6" customWidth="true" width="5.14545454545455"/>
+    <col min="7" max="7" customWidth="true" width="11.0"/>
+    <col min="8" max="8" customWidth="true" width="12.7181818181818"/>
+    <col min="9" max="9" customWidth="true" width="5.85454545454545"/>
+    <col min="10" max="10" customWidth="true" width="6.0"/>
+    <col min="11" max="11" customWidth="true" width="5.85454545454545"/>
+    <col min="12" max="12" customWidth="true" width="14.2818181818182"/>
+    <col min="13" max="13" customWidth="true" width="9.42727272727273"/>
+    <col min="14" max="14" customWidth="true" width="14.4272727272727"/>
+    <col min="15" max="15" customWidth="true" width="15.5727272727273"/>
+    <col min="16" max="16" customWidth="true" width="14.4272727272727"/>
+    <col min="17" max="17" customWidth="true" width="39.4272727272727"/>
+    <col min="18" max="18" customWidth="true" width="11.7181818181818"/>
+    <col min="19" max="19" customWidth="true" width="11.8545454545455"/>
+    <col min="20" max="20" customWidth="true" width="6.42727272727273"/>
+    <col min="21" max="22" customWidth="true" width="6.57272727272727"/>
+    <col min="23" max="23" customWidth="true" width="37.1454545454545"/>
+    <col min="24" max="25" customWidth="true" width="8.0"/>
+    <col min="26" max="26" customWidth="true" width="7.71818181818182"/>
+    <col min="27" max="27" customWidth="true" width="6.28181818181818"/>
+    <col min="28" max="28" customWidth="true" width="9.28181818181818"/>
+    <col min="29" max="29" customWidth="true" width="9.71818181818182"/>
+    <col min="30" max="30" customWidth="true" width="12.8545454545455"/>
+    <col min="31" max="31" customWidth="true" width="16.1454545454545"/>
+    <col min="32" max="32" customWidth="true" width="15.4272727272727"/>
+    <col min="33" max="33" customWidth="true" width="24.5727272727273"/>
+    <col min="34" max="34" customWidth="true" width="8.57272727272727"/>
+    <col min="35" max="35" customWidth="true" width="14.7181818181818"/>
+    <col min="36" max="36" customWidth="true" width="18.5727272727273"/>
+    <col min="37" max="37" customWidth="true" width="14.1454545454545"/>
+    <col min="38" max="38" customWidth="true" width="14.7181818181818"/>
+    <col min="39" max="39" customWidth="true" width="17.4272727272727"/>
+    <col min="40" max="40" customWidth="true" width="22.0"/>
+    <col min="41" max="41" customWidth="true" width="17.5727272727273"/>
+    <col min="42" max="42" customWidth="true" width="25.2818181818182"/>
+    <col min="43" max="43" customWidth="true" width="13.0"/>
+    <col min="44" max="44" customWidth="true" width="23.7181818181818"/>
+    <col min="45" max="45" customWidth="true" width="10.0"/>
+    <col min="46" max="46" customWidth="true" width="13.0"/>
+    <col min="47" max="47" customWidth="true" width="15.5727272727273"/>
+    <col min="48" max="48" customWidth="true" width="21.1454545454545"/>
+    <col min="49" max="49" customWidth="true" width="11.5727272727273"/>
+    <col min="50" max="50" customWidth="true" width="16.7181818181818"/>
+    <col min="51" max="51" customWidth="true" width="14.0"/>
+    <col min="52" max="52" customWidth="true" width="19.4272727272727"/>
+    <col min="53" max="53" customWidth="true" width="18.8545454545455"/>
+    <col min="54" max="54" customWidth="true" width="23.2818181818182"/>
+    <col min="55" max="55" customWidth="true" width="15.5727272727273"/>
+    <col min="56" max="56" customWidth="true" width="14.2818181818182"/>
+    <col min="57" max="57" customWidth="true" width="17.0"/>
+    <col min="58" max="58" customWidth="true" width="16.2818181818182"/>
+    <col min="59" max="59" customWidth="true" width="13.5727272727273"/>
+    <col min="60" max="61" customWidth="true" width="12.7181818181818"/>
+    <col min="62" max="62" customWidth="true" width="21.8545454545455"/>
+    <col min="63" max="63" customWidth="true" width="30.5727272727273"/>
+    <col min="64" max="64" customWidth="true" width="10.0"/>
+    <col min="65" max="65" customWidth="true" width="42.5727272727273"/>
+    <col min="66" max="66" customWidth="true" width="38.1454545454545"/>
+    <col min="67" max="67" customWidth="true" width="19.4272727272727"/>
+    <col min="68" max="68" customWidth="true" width="35.4272727272727"/>
+    <col min="69" max="69" customWidth="true" width="9.57272727272727"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -7148,6 +7305,8 @@
       <c r="AT4" s="35" t="s">
         <v>76</v>
       </c>
+      <c r="AU4" s="0"/>
+      <c r="AV4" s="0"/>
       <c r="AW4" s="35">
         <f>AM4</f>
         <v>4</v>
@@ -7186,10 +7345,10 @@
       <c r="BL4" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="BM4" t="s">
+      <c r="BM4" t="s" s="0">
         <v>100</v>
       </c>
-      <c r="BN4" t="s">
+      <c r="BN4" t="s" s="0">
         <v>100</v>
       </c>
       <c r="BO4" s="35">
@@ -7337,71 +7496,71 @@
   <dimension ref="A1:BQ5"/>
   <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" width="5.14545454545455" customWidth="1"/>
-    <col min="2" max="3" width="24.5727272727273" customWidth="1"/>
-    <col min="4" max="4" width="79.4272727272727" customWidth="1"/>
-    <col min="5" max="5" width="11.5727272727273" customWidth="1"/>
-    <col min="6" max="6" width="5.14545454545455" customWidth="1"/>
-    <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="12.7181818181818" customWidth="1"/>
-    <col min="9" max="9" width="5.85454545454545" customWidth="1"/>
-    <col min="10" max="10" width="6" customWidth="1"/>
-    <col min="11" max="11" width="5.85454545454545" customWidth="1"/>
-    <col min="12" max="12" width="14.2818181818182" customWidth="1"/>
-    <col min="13" max="13" width="9.42727272727273" customWidth="1"/>
-    <col min="14" max="14" width="14.4272727272727" customWidth="1"/>
-    <col min="15" max="15" width="15.5727272727273" customWidth="1"/>
-    <col min="16" max="16" width="14.4272727272727" customWidth="1"/>
-    <col min="17" max="17" width="39.4272727272727" customWidth="1"/>
-    <col min="18" max="18" width="11.7181818181818" customWidth="1"/>
-    <col min="19" max="19" width="11.8545454545455" customWidth="1"/>
-    <col min="20" max="20" width="6.42727272727273" customWidth="1"/>
-    <col min="21" max="22" width="6.57272727272727" customWidth="1"/>
-    <col min="23" max="23" width="37.1454545454545" customWidth="1"/>
-    <col min="24" max="25" width="8" customWidth="1"/>
-    <col min="26" max="26" width="7.71818181818182" customWidth="1"/>
-    <col min="27" max="27" width="6.28181818181818" customWidth="1"/>
-    <col min="28" max="28" width="9.28181818181818" customWidth="1"/>
-    <col min="29" max="29" width="9.71818181818182" customWidth="1"/>
-    <col min="30" max="30" width="12.8545454545455" customWidth="1"/>
-    <col min="31" max="31" width="16.1454545454545" customWidth="1"/>
-    <col min="32" max="32" width="15.4272727272727" customWidth="1"/>
-    <col min="33" max="33" width="24.5727272727273" customWidth="1"/>
-    <col min="34" max="34" width="8.57272727272727" customWidth="1"/>
-    <col min="35" max="35" width="14.7181818181818" customWidth="1"/>
-    <col min="36" max="36" width="18.5727272727273" customWidth="1"/>
-    <col min="37" max="37" width="14.1454545454545" customWidth="1"/>
-    <col min="38" max="38" width="14.7181818181818" customWidth="1"/>
-    <col min="39" max="39" width="17.4272727272727" customWidth="1"/>
-    <col min="40" max="40" width="22" customWidth="1"/>
-    <col min="41" max="41" width="17.5727272727273" customWidth="1"/>
-    <col min="42" max="42" width="25.2818181818182" customWidth="1"/>
-    <col min="43" max="43" width="13" customWidth="1"/>
-    <col min="44" max="44" width="23.7181818181818" customWidth="1"/>
-    <col min="45" max="45" width="10" customWidth="1"/>
-    <col min="46" max="46" width="13" customWidth="1"/>
-    <col min="47" max="47" width="15.5727272727273" customWidth="1"/>
-    <col min="48" max="48" width="21.1454545454545" customWidth="1"/>
-    <col min="49" max="49" width="11.5727272727273" customWidth="1"/>
-    <col min="50" max="50" width="16.7181818181818" customWidth="1"/>
-    <col min="51" max="51" width="14" customWidth="1"/>
-    <col min="52" max="52" width="19.4272727272727" customWidth="1"/>
-    <col min="53" max="53" width="18.8545454545455" customWidth="1"/>
-    <col min="54" max="54" width="23.2818181818182" customWidth="1"/>
-    <col min="55" max="55" width="15.5727272727273" customWidth="1"/>
-    <col min="56" max="56" width="14.2818181818182" customWidth="1"/>
-    <col min="57" max="57" width="17" customWidth="1"/>
-    <col min="58" max="58" width="16.2818181818182" customWidth="1"/>
-    <col min="59" max="59" width="13.5727272727273" customWidth="1"/>
-    <col min="60" max="61" width="12.7181818181818" customWidth="1"/>
-    <col min="62" max="62" width="21.8545454545455" customWidth="1"/>
-    <col min="63" max="63" width="30.5727272727273" customWidth="1"/>
-    <col min="64" max="64" width="10" customWidth="1"/>
-    <col min="65" max="65" width="42.5727272727273" customWidth="1"/>
-    <col min="66" max="66" width="38.1454545454545" customWidth="1"/>
-    <col min="67" max="67" width="19.4272727272727" customWidth="1"/>
-    <col min="68" max="68" width="35.4272727272727" customWidth="1"/>
-    <col min="69" max="69" width="9.57272727272727" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="5.14545454545455"/>
+    <col min="2" max="3" customWidth="true" width="24.5727272727273"/>
+    <col min="4" max="4" customWidth="true" width="79.4272727272727"/>
+    <col min="5" max="5" customWidth="true" width="11.5727272727273"/>
+    <col min="6" max="6" customWidth="true" width="5.14545454545455"/>
+    <col min="7" max="7" customWidth="true" width="11.0"/>
+    <col min="8" max="8" customWidth="true" width="12.7181818181818"/>
+    <col min="9" max="9" customWidth="true" width="5.85454545454545"/>
+    <col min="10" max="10" customWidth="true" width="6.0"/>
+    <col min="11" max="11" customWidth="true" width="5.85454545454545"/>
+    <col min="12" max="12" customWidth="true" width="14.2818181818182"/>
+    <col min="13" max="13" customWidth="true" width="9.42727272727273"/>
+    <col min="14" max="14" customWidth="true" width="14.4272727272727"/>
+    <col min="15" max="15" customWidth="true" width="15.5727272727273"/>
+    <col min="16" max="16" customWidth="true" width="14.4272727272727"/>
+    <col min="17" max="17" customWidth="true" width="39.4272727272727"/>
+    <col min="18" max="18" customWidth="true" width="11.7181818181818"/>
+    <col min="19" max="19" customWidth="true" width="11.8545454545455"/>
+    <col min="20" max="20" customWidth="true" width="6.42727272727273"/>
+    <col min="21" max="22" customWidth="true" width="6.57272727272727"/>
+    <col min="23" max="23" customWidth="true" width="37.1454545454545"/>
+    <col min="24" max="25" customWidth="true" width="8.0"/>
+    <col min="26" max="26" customWidth="true" width="7.71818181818182"/>
+    <col min="27" max="27" customWidth="true" width="6.28181818181818"/>
+    <col min="28" max="28" customWidth="true" width="9.28181818181818"/>
+    <col min="29" max="29" customWidth="true" width="9.71818181818182"/>
+    <col min="30" max="30" customWidth="true" width="12.8545454545455"/>
+    <col min="31" max="31" customWidth="true" width="16.1454545454545"/>
+    <col min="32" max="32" customWidth="true" width="15.4272727272727"/>
+    <col min="33" max="33" customWidth="true" width="24.5727272727273"/>
+    <col min="34" max="34" customWidth="true" width="8.57272727272727"/>
+    <col min="35" max="35" customWidth="true" width="14.7181818181818"/>
+    <col min="36" max="36" customWidth="true" width="18.5727272727273"/>
+    <col min="37" max="37" customWidth="true" width="14.1454545454545"/>
+    <col min="38" max="38" customWidth="true" width="14.7181818181818"/>
+    <col min="39" max="39" customWidth="true" width="17.4272727272727"/>
+    <col min="40" max="40" customWidth="true" width="22.0"/>
+    <col min="41" max="41" customWidth="true" width="17.5727272727273"/>
+    <col min="42" max="42" customWidth="true" width="25.2818181818182"/>
+    <col min="43" max="43" customWidth="true" width="13.0"/>
+    <col min="44" max="44" customWidth="true" width="23.7181818181818"/>
+    <col min="45" max="45" customWidth="true" width="10.0"/>
+    <col min="46" max="46" customWidth="true" width="13.0"/>
+    <col min="47" max="47" customWidth="true" width="15.5727272727273"/>
+    <col min="48" max="48" customWidth="true" width="21.1454545454545"/>
+    <col min="49" max="49" customWidth="true" width="11.5727272727273"/>
+    <col min="50" max="50" customWidth="true" width="16.7181818181818"/>
+    <col min="51" max="51" customWidth="true" width="14.0"/>
+    <col min="52" max="52" customWidth="true" width="19.4272727272727"/>
+    <col min="53" max="53" customWidth="true" width="18.8545454545455"/>
+    <col min="54" max="54" customWidth="true" width="23.2818181818182"/>
+    <col min="55" max="55" customWidth="true" width="15.5727272727273"/>
+    <col min="56" max="56" customWidth="true" width="14.2818181818182"/>
+    <col min="57" max="57" customWidth="true" width="17.0"/>
+    <col min="58" max="58" customWidth="true" width="16.2818181818182"/>
+    <col min="59" max="59" customWidth="true" width="13.5727272727273"/>
+    <col min="60" max="61" customWidth="true" width="12.7181818181818"/>
+    <col min="62" max="62" customWidth="true" width="21.8545454545455"/>
+    <col min="63" max="63" customWidth="true" width="30.5727272727273"/>
+    <col min="64" max="64" customWidth="true" width="10.0"/>
+    <col min="65" max="65" customWidth="true" width="42.5727272727273"/>
+    <col min="66" max="66" customWidth="true" width="38.1454545454545"/>
+    <col min="67" max="67" customWidth="true" width="19.4272727272727"/>
+    <col min="68" max="68" customWidth="true" width="35.4272727272727"/>
+    <col min="69" max="69" customWidth="true" width="9.57272727272727"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -7945,11 +8104,11 @@
       <c r="AT4" s="35" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" t="s">
-        <v>131</v>
-      </c>
-      <c r="AV4" t="s">
-        <v>132</v>
+      <c r="AU4" t="s" s="0">
+        <v>196</v>
+      </c>
+      <c r="AV4" t="s" s="0">
+        <v>197</v>
       </c>
       <c r="AW4" s="35">
         <f>AM4</f>
@@ -7963,7 +8122,7 @@
         <f>AU4+AW4</f>
         <v>32.6603333333333</v>
       </c>
-      <c r="AZ4" t="s">
+      <c r="AZ4" t="s" s="0">
         <v>132</v>
       </c>
       <c r="BA4" s="36"/>
@@ -7988,11 +8147,11 @@
       <c r="BL4" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="BM4" t="s">
-        <v>133</v>
-      </c>
-      <c r="BN4" t="s">
-        <v>134</v>
+      <c r="BM4" t="s" s="0">
+        <v>199</v>
+      </c>
+      <c r="BN4" t="s" s="0">
+        <v>198</v>
       </c>
       <c r="BO4" s="35">
         <f>ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
@@ -8151,71 +8310,71 @@
   <dimension ref="A1:BQ5"/>
   <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" width="5.14545454545455" customWidth="1"/>
-    <col min="2" max="3" width="24.5727272727273" customWidth="1"/>
-    <col min="4" max="4" width="79.4272727272727" customWidth="1"/>
-    <col min="5" max="5" width="11.5727272727273" customWidth="1"/>
-    <col min="6" max="6" width="5.14545454545455" customWidth="1"/>
-    <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="12.7181818181818" customWidth="1"/>
-    <col min="9" max="9" width="5.85454545454545" customWidth="1"/>
-    <col min="10" max="10" width="6" customWidth="1"/>
-    <col min="11" max="11" width="5.85454545454545" customWidth="1"/>
-    <col min="12" max="12" width="14.2818181818182" customWidth="1"/>
-    <col min="13" max="13" width="9.42727272727273" customWidth="1"/>
-    <col min="14" max="14" width="14.4272727272727" customWidth="1"/>
-    <col min="15" max="15" width="15.5727272727273" customWidth="1"/>
-    <col min="16" max="16" width="14.4272727272727" customWidth="1"/>
-    <col min="17" max="17" width="39.4272727272727" customWidth="1"/>
-    <col min="18" max="18" width="11.7181818181818" customWidth="1"/>
-    <col min="19" max="19" width="11.8545454545455" customWidth="1"/>
-    <col min="20" max="20" width="6.42727272727273" customWidth="1"/>
-    <col min="21" max="22" width="6.57272727272727" customWidth="1"/>
-    <col min="23" max="23" width="37.1454545454545" customWidth="1"/>
-    <col min="24" max="25" width="8" customWidth="1"/>
-    <col min="26" max="26" width="7.71818181818182" customWidth="1"/>
-    <col min="27" max="27" width="6.28181818181818" customWidth="1"/>
-    <col min="28" max="28" width="9.28181818181818" customWidth="1"/>
-    <col min="29" max="29" width="9.71818181818182" customWidth="1"/>
-    <col min="30" max="30" width="12.8545454545455" customWidth="1"/>
-    <col min="31" max="31" width="16.1454545454545" customWidth="1"/>
-    <col min="32" max="32" width="15.4272727272727" customWidth="1"/>
-    <col min="33" max="33" width="24.5727272727273" customWidth="1"/>
-    <col min="34" max="34" width="8.57272727272727" customWidth="1"/>
-    <col min="35" max="35" width="14.7181818181818" customWidth="1"/>
-    <col min="36" max="36" width="18.5727272727273" customWidth="1"/>
-    <col min="37" max="37" width="14.1454545454545" customWidth="1"/>
-    <col min="38" max="38" width="14.7181818181818" customWidth="1"/>
-    <col min="39" max="39" width="17.4272727272727" customWidth="1"/>
-    <col min="40" max="40" width="22" customWidth="1"/>
-    <col min="41" max="41" width="17.5727272727273" customWidth="1"/>
-    <col min="42" max="42" width="25.2818181818182" customWidth="1"/>
-    <col min="43" max="43" width="13" customWidth="1"/>
-    <col min="44" max="44" width="23.7181818181818" customWidth="1"/>
-    <col min="45" max="45" width="10" customWidth="1"/>
-    <col min="46" max="46" width="13" customWidth="1"/>
-    <col min="47" max="47" width="15.5727272727273" customWidth="1"/>
-    <col min="48" max="48" width="21.1454545454545" customWidth="1"/>
-    <col min="49" max="49" width="11.5727272727273" customWidth="1"/>
-    <col min="50" max="50" width="16.7181818181818" customWidth="1"/>
-    <col min="51" max="51" width="14" customWidth="1"/>
-    <col min="52" max="52" width="19.4272727272727" customWidth="1"/>
-    <col min="53" max="53" width="18.8545454545455" customWidth="1"/>
-    <col min="54" max="54" width="23.2818181818182" customWidth="1"/>
-    <col min="55" max="55" width="15.5727272727273" customWidth="1"/>
-    <col min="56" max="56" width="14.2818181818182" customWidth="1"/>
-    <col min="57" max="57" width="17" customWidth="1"/>
-    <col min="58" max="58" width="16.2818181818182" customWidth="1"/>
-    <col min="59" max="59" width="13.5727272727273" customWidth="1"/>
-    <col min="60" max="61" width="12.7181818181818" customWidth="1"/>
-    <col min="62" max="62" width="21.8545454545455" customWidth="1"/>
-    <col min="63" max="63" width="30.5727272727273" customWidth="1"/>
-    <col min="64" max="64" width="10" customWidth="1"/>
-    <col min="65" max="65" width="42.5727272727273" customWidth="1"/>
-    <col min="66" max="66" width="38.1454545454545" customWidth="1"/>
-    <col min="67" max="67" width="19.4272727272727" customWidth="1"/>
-    <col min="68" max="68" width="35.4272727272727" customWidth="1"/>
-    <col min="69" max="69" width="9.57272727272727" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="5.14545454545455"/>
+    <col min="2" max="3" customWidth="true" width="24.5727272727273"/>
+    <col min="4" max="4" customWidth="true" width="79.4272727272727"/>
+    <col min="5" max="5" customWidth="true" width="11.5727272727273"/>
+    <col min="6" max="6" customWidth="true" width="5.14545454545455"/>
+    <col min="7" max="7" customWidth="true" width="11.0"/>
+    <col min="8" max="8" customWidth="true" width="12.7181818181818"/>
+    <col min="9" max="9" customWidth="true" width="5.85454545454545"/>
+    <col min="10" max="10" customWidth="true" width="6.0"/>
+    <col min="11" max="11" customWidth="true" width="5.85454545454545"/>
+    <col min="12" max="12" customWidth="true" width="14.2818181818182"/>
+    <col min="13" max="13" customWidth="true" width="9.42727272727273"/>
+    <col min="14" max="14" customWidth="true" width="14.4272727272727"/>
+    <col min="15" max="15" customWidth="true" width="15.5727272727273"/>
+    <col min="16" max="16" customWidth="true" width="14.4272727272727"/>
+    <col min="17" max="17" customWidth="true" width="39.4272727272727"/>
+    <col min="18" max="18" customWidth="true" width="11.7181818181818"/>
+    <col min="19" max="19" customWidth="true" width="11.8545454545455"/>
+    <col min="20" max="20" customWidth="true" width="6.42727272727273"/>
+    <col min="21" max="22" customWidth="true" width="6.57272727272727"/>
+    <col min="23" max="23" customWidth="true" width="37.1454545454545"/>
+    <col min="24" max="25" customWidth="true" width="8.0"/>
+    <col min="26" max="26" customWidth="true" width="7.71818181818182"/>
+    <col min="27" max="27" customWidth="true" width="6.28181818181818"/>
+    <col min="28" max="28" customWidth="true" width="9.28181818181818"/>
+    <col min="29" max="29" customWidth="true" width="9.71818181818182"/>
+    <col min="30" max="30" customWidth="true" width="12.8545454545455"/>
+    <col min="31" max="31" customWidth="true" width="16.1454545454545"/>
+    <col min="32" max="32" customWidth="true" width="15.4272727272727"/>
+    <col min="33" max="33" customWidth="true" width="24.5727272727273"/>
+    <col min="34" max="34" customWidth="true" width="8.57272727272727"/>
+    <col min="35" max="35" customWidth="true" width="14.7181818181818"/>
+    <col min="36" max="36" customWidth="true" width="18.5727272727273"/>
+    <col min="37" max="37" customWidth="true" width="14.1454545454545"/>
+    <col min="38" max="38" customWidth="true" width="14.7181818181818"/>
+    <col min="39" max="39" customWidth="true" width="17.4272727272727"/>
+    <col min="40" max="40" customWidth="true" width="22.0"/>
+    <col min="41" max="41" customWidth="true" width="17.5727272727273"/>
+    <col min="42" max="42" customWidth="true" width="25.2818181818182"/>
+    <col min="43" max="43" customWidth="true" width="13.0"/>
+    <col min="44" max="44" customWidth="true" width="23.7181818181818"/>
+    <col min="45" max="45" customWidth="true" width="10.0"/>
+    <col min="46" max="46" customWidth="true" width="13.0"/>
+    <col min="47" max="47" customWidth="true" width="15.5727272727273"/>
+    <col min="48" max="48" customWidth="true" width="21.1454545454545"/>
+    <col min="49" max="49" customWidth="true" width="11.5727272727273"/>
+    <col min="50" max="50" customWidth="true" width="16.7181818181818"/>
+    <col min="51" max="51" customWidth="true" width="14.0"/>
+    <col min="52" max="52" customWidth="true" width="19.4272727272727"/>
+    <col min="53" max="53" customWidth="true" width="18.8545454545455"/>
+    <col min="54" max="54" customWidth="true" width="23.2818181818182"/>
+    <col min="55" max="55" customWidth="true" width="15.5727272727273"/>
+    <col min="56" max="56" customWidth="true" width="14.2818181818182"/>
+    <col min="57" max="57" customWidth="true" width="17.0"/>
+    <col min="58" max="58" customWidth="true" width="16.2818181818182"/>
+    <col min="59" max="59" customWidth="true" width="13.5727272727273"/>
+    <col min="60" max="61" customWidth="true" width="12.7181818181818"/>
+    <col min="62" max="62" customWidth="true" width="21.8545454545455"/>
+    <col min="63" max="63" customWidth="true" width="30.5727272727273"/>
+    <col min="64" max="64" customWidth="true" width="10.0"/>
+    <col min="65" max="65" customWidth="true" width="42.5727272727273"/>
+    <col min="66" max="66" customWidth="true" width="38.1454545454545"/>
+    <col min="67" max="67" customWidth="true" width="19.4272727272727"/>
+    <col min="68" max="68" customWidth="true" width="35.4272727272727"/>
+    <col min="69" max="69" customWidth="true" width="9.57272727272727"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -8759,11 +8918,11 @@
       <c r="AT4" s="35" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" t="s">
-        <v>136</v>
-      </c>
-      <c r="AV4" t="s">
-        <v>137</v>
+      <c r="AU4" t="s" s="0">
+        <v>200</v>
+      </c>
+      <c r="AV4" t="s" s="0">
+        <v>201</v>
       </c>
       <c r="AW4" s="35">
         <f>AM4</f>
@@ -8777,7 +8936,7 @@
         <f>AU4+AW4</f>
         <v>83.3283333333333</v>
       </c>
-      <c r="AZ4" t="s">
+      <c r="AZ4" t="s" s="0">
         <v>137</v>
       </c>
       <c r="BA4" s="36"/>
@@ -8802,11 +8961,11 @@
       <c r="BL4" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="BM4" t="s">
-        <v>138</v>
-      </c>
-      <c r="BN4" t="s">
-        <v>139</v>
+      <c r="BM4" t="s" s="0">
+        <v>203</v>
+      </c>
+      <c r="BN4" t="s" s="0">
+        <v>202</v>
       </c>
       <c r="BO4" s="35">
         <f>ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
@@ -8965,71 +9124,71 @@
   <dimension ref="A1:BQ5"/>
   <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" width="5.14545454545455" customWidth="1"/>
-    <col min="2" max="3" width="22" customWidth="1"/>
-    <col min="4" max="4" width="79.4272727272727" customWidth="1"/>
-    <col min="5" max="5" width="11.5727272727273" customWidth="1"/>
-    <col min="6" max="6" width="5.14545454545455" customWidth="1"/>
-    <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="12.7181818181818" customWidth="1"/>
-    <col min="9" max="9" width="5.85454545454545" customWidth="1"/>
-    <col min="10" max="10" width="6" customWidth="1"/>
-    <col min="11" max="11" width="5.85454545454545" customWidth="1"/>
-    <col min="12" max="12" width="14.2818181818182" customWidth="1"/>
-    <col min="13" max="13" width="9.42727272727273" customWidth="1"/>
-    <col min="14" max="14" width="14.4272727272727" customWidth="1"/>
-    <col min="15" max="15" width="15.5727272727273" customWidth="1"/>
-    <col min="16" max="16" width="14.4272727272727" customWidth="1"/>
-    <col min="17" max="17" width="39.4272727272727" customWidth="1"/>
-    <col min="18" max="18" width="11.7181818181818" customWidth="1"/>
-    <col min="19" max="19" width="11.8545454545455" customWidth="1"/>
-    <col min="20" max="20" width="6.42727272727273" customWidth="1"/>
-    <col min="21" max="22" width="6.57272727272727" customWidth="1"/>
-    <col min="23" max="23" width="37.1454545454545" customWidth="1"/>
-    <col min="24" max="25" width="8" customWidth="1"/>
-    <col min="26" max="26" width="7.71818181818182" customWidth="1"/>
-    <col min="27" max="27" width="6.28181818181818" customWidth="1"/>
-    <col min="28" max="28" width="9.28181818181818" customWidth="1"/>
-    <col min="29" max="29" width="9.71818181818182" customWidth="1"/>
-    <col min="30" max="30" width="12.8545454545455" customWidth="1"/>
-    <col min="31" max="31" width="16.1454545454545" customWidth="1"/>
-    <col min="32" max="32" width="15.4272727272727" customWidth="1"/>
-    <col min="33" max="33" width="24.5727272727273" customWidth="1"/>
-    <col min="34" max="34" width="8.57272727272727" customWidth="1"/>
-    <col min="35" max="35" width="14.7181818181818" customWidth="1"/>
-    <col min="36" max="36" width="18.5727272727273" customWidth="1"/>
-    <col min="37" max="37" width="14.1454545454545" customWidth="1"/>
-    <col min="38" max="38" width="14.7181818181818" customWidth="1"/>
-    <col min="39" max="39" width="17.4272727272727" customWidth="1"/>
-    <col min="40" max="40" width="22" customWidth="1"/>
-    <col min="41" max="41" width="17.5727272727273" customWidth="1"/>
-    <col min="42" max="42" width="25.2818181818182" customWidth="1"/>
-    <col min="43" max="43" width="13" customWidth="1"/>
-    <col min="44" max="44" width="23.7181818181818" customWidth="1"/>
-    <col min="45" max="45" width="10" customWidth="1"/>
-    <col min="46" max="46" width="13" customWidth="1"/>
-    <col min="47" max="47" width="15.5727272727273" customWidth="1"/>
-    <col min="48" max="48" width="21.1454545454545" customWidth="1"/>
-    <col min="49" max="49" width="11.5727272727273" customWidth="1"/>
-    <col min="50" max="50" width="16.7181818181818" customWidth="1"/>
-    <col min="51" max="51" width="14" customWidth="1"/>
-    <col min="52" max="52" width="19.4272727272727" customWidth="1"/>
-    <col min="53" max="53" width="18.8545454545455" customWidth="1"/>
-    <col min="54" max="54" width="23.2818181818182" customWidth="1"/>
-    <col min="55" max="55" width="15.5727272727273" customWidth="1"/>
-    <col min="56" max="56" width="14.2818181818182" customWidth="1"/>
-    <col min="57" max="57" width="17" customWidth="1"/>
-    <col min="58" max="58" width="16.2818181818182" customWidth="1"/>
-    <col min="59" max="59" width="13.5727272727273" customWidth="1"/>
-    <col min="60" max="61" width="12.7181818181818" customWidth="1"/>
-    <col min="62" max="62" width="21.8545454545455" customWidth="1"/>
-    <col min="63" max="63" width="30.5727272727273" customWidth="1"/>
-    <col min="64" max="64" width="10" customWidth="1"/>
-    <col min="65" max="65" width="42.5727272727273" customWidth="1"/>
-    <col min="66" max="66" width="38.1454545454545" customWidth="1"/>
-    <col min="67" max="67" width="19.4272727272727" customWidth="1"/>
-    <col min="68" max="68" width="35.4272727272727" customWidth="1"/>
-    <col min="69" max="69" width="9.57272727272727" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="5.14545454545455"/>
+    <col min="2" max="3" customWidth="true" width="22.0"/>
+    <col min="4" max="4" customWidth="true" width="79.4272727272727"/>
+    <col min="5" max="5" customWidth="true" width="11.5727272727273"/>
+    <col min="6" max="6" customWidth="true" width="5.14545454545455"/>
+    <col min="7" max="7" customWidth="true" width="11.0"/>
+    <col min="8" max="8" customWidth="true" width="12.7181818181818"/>
+    <col min="9" max="9" customWidth="true" width="5.85454545454545"/>
+    <col min="10" max="10" customWidth="true" width="6.0"/>
+    <col min="11" max="11" customWidth="true" width="5.85454545454545"/>
+    <col min="12" max="12" customWidth="true" width="14.2818181818182"/>
+    <col min="13" max="13" customWidth="true" width="9.42727272727273"/>
+    <col min="14" max="14" customWidth="true" width="14.4272727272727"/>
+    <col min="15" max="15" customWidth="true" width="15.5727272727273"/>
+    <col min="16" max="16" customWidth="true" width="14.4272727272727"/>
+    <col min="17" max="17" customWidth="true" width="39.4272727272727"/>
+    <col min="18" max="18" customWidth="true" width="11.7181818181818"/>
+    <col min="19" max="19" customWidth="true" width="11.8545454545455"/>
+    <col min="20" max="20" customWidth="true" width="6.42727272727273"/>
+    <col min="21" max="22" customWidth="true" width="6.57272727272727"/>
+    <col min="23" max="23" customWidth="true" width="37.1454545454545"/>
+    <col min="24" max="25" customWidth="true" width="8.0"/>
+    <col min="26" max="26" customWidth="true" width="7.71818181818182"/>
+    <col min="27" max="27" customWidth="true" width="6.28181818181818"/>
+    <col min="28" max="28" customWidth="true" width="9.28181818181818"/>
+    <col min="29" max="29" customWidth="true" width="9.71818181818182"/>
+    <col min="30" max="30" customWidth="true" width="12.8545454545455"/>
+    <col min="31" max="31" customWidth="true" width="16.1454545454545"/>
+    <col min="32" max="32" customWidth="true" width="15.4272727272727"/>
+    <col min="33" max="33" customWidth="true" width="24.5727272727273"/>
+    <col min="34" max="34" customWidth="true" width="8.57272727272727"/>
+    <col min="35" max="35" customWidth="true" width="14.7181818181818"/>
+    <col min="36" max="36" customWidth="true" width="18.5727272727273"/>
+    <col min="37" max="37" customWidth="true" width="14.1454545454545"/>
+    <col min="38" max="38" customWidth="true" width="14.7181818181818"/>
+    <col min="39" max="39" customWidth="true" width="17.4272727272727"/>
+    <col min="40" max="40" customWidth="true" width="22.0"/>
+    <col min="41" max="41" customWidth="true" width="17.5727272727273"/>
+    <col min="42" max="42" customWidth="true" width="25.2818181818182"/>
+    <col min="43" max="43" customWidth="true" width="13.0"/>
+    <col min="44" max="44" customWidth="true" width="23.7181818181818"/>
+    <col min="45" max="45" customWidth="true" width="10.0"/>
+    <col min="46" max="46" customWidth="true" width="13.0"/>
+    <col min="47" max="47" customWidth="true" width="15.5727272727273"/>
+    <col min="48" max="48" customWidth="true" width="21.1454545454545"/>
+    <col min="49" max="49" customWidth="true" width="11.5727272727273"/>
+    <col min="50" max="50" customWidth="true" width="16.7181818181818"/>
+    <col min="51" max="51" customWidth="true" width="14.0"/>
+    <col min="52" max="52" customWidth="true" width="19.4272727272727"/>
+    <col min="53" max="53" customWidth="true" width="18.8545454545455"/>
+    <col min="54" max="54" customWidth="true" width="23.2818181818182"/>
+    <col min="55" max="55" customWidth="true" width="15.5727272727273"/>
+    <col min="56" max="56" customWidth="true" width="14.2818181818182"/>
+    <col min="57" max="57" customWidth="true" width="17.0"/>
+    <col min="58" max="58" customWidth="true" width="16.2818181818182"/>
+    <col min="59" max="59" customWidth="true" width="13.5727272727273"/>
+    <col min="60" max="61" customWidth="true" width="12.7181818181818"/>
+    <col min="62" max="62" customWidth="true" width="21.8545454545455"/>
+    <col min="63" max="63" customWidth="true" width="30.5727272727273"/>
+    <col min="64" max="64" customWidth="true" width="10.0"/>
+    <col min="65" max="65" customWidth="true" width="42.5727272727273"/>
+    <col min="66" max="66" customWidth="true" width="38.1454545454545"/>
+    <col min="67" max="67" customWidth="true" width="19.4272727272727"/>
+    <col min="68" max="68" customWidth="true" width="35.4272727272727"/>
+    <col min="69" max="69" customWidth="true" width="9.57272727272727"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -9573,6 +9732,8 @@
       <c r="AT4" s="35" t="s">
         <v>76</v>
       </c>
+      <c r="AU4" s="0"/>
+      <c r="AV4" s="0"/>
       <c r="AW4" s="35">
         <f>AM4</f>
         <v>4</v>
@@ -9611,10 +9772,10 @@
       <c r="BL4" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="BM4" t="s">
+      <c r="BM4" t="s" s="0">
         <v>100</v>
       </c>
-      <c r="BN4" t="s">
+      <c r="BN4" t="s" s="0">
         <v>100</v>
       </c>
       <c r="BO4" s="35">
@@ -9762,71 +9923,71 @@
   <dimension ref="A1:BQ5"/>
   <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" width="5.14545454545455" customWidth="1"/>
-    <col min="2" max="3" width="22" customWidth="1"/>
-    <col min="4" max="4" width="79.4272727272727" customWidth="1"/>
-    <col min="5" max="5" width="11.5727272727273" customWidth="1"/>
-    <col min="6" max="6" width="5.14545454545455" customWidth="1"/>
-    <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="12.7181818181818" customWidth="1"/>
-    <col min="9" max="9" width="5.85454545454545" customWidth="1"/>
-    <col min="10" max="10" width="6" customWidth="1"/>
-    <col min="11" max="11" width="5.85454545454545" customWidth="1"/>
-    <col min="12" max="12" width="14.2818181818182" customWidth="1"/>
-    <col min="13" max="13" width="9.42727272727273" customWidth="1"/>
-    <col min="14" max="14" width="14.4272727272727" customWidth="1"/>
-    <col min="15" max="15" width="15.5727272727273" customWidth="1"/>
-    <col min="16" max="16" width="14.4272727272727" customWidth="1"/>
-    <col min="17" max="17" width="39.4272727272727" customWidth="1"/>
-    <col min="18" max="18" width="11.7181818181818" customWidth="1"/>
-    <col min="19" max="19" width="11.8545454545455" customWidth="1"/>
-    <col min="20" max="20" width="6.42727272727273" customWidth="1"/>
-    <col min="21" max="22" width="6.57272727272727" customWidth="1"/>
-    <col min="23" max="23" width="37.1454545454545" customWidth="1"/>
-    <col min="24" max="25" width="8" customWidth="1"/>
-    <col min="26" max="26" width="7.71818181818182" customWidth="1"/>
-    <col min="27" max="27" width="6.28181818181818" customWidth="1"/>
-    <col min="28" max="28" width="9.28181818181818" customWidth="1"/>
-    <col min="29" max="29" width="9.71818181818182" customWidth="1"/>
-    <col min="30" max="30" width="12.8545454545455" customWidth="1"/>
-    <col min="31" max="31" width="16.1454545454545" customWidth="1"/>
-    <col min="32" max="32" width="15.4272727272727" customWidth="1"/>
-    <col min="33" max="33" width="24.5727272727273" customWidth="1"/>
-    <col min="34" max="34" width="8.57272727272727" customWidth="1"/>
-    <col min="35" max="35" width="14.7181818181818" customWidth="1"/>
-    <col min="36" max="36" width="18.5727272727273" customWidth="1"/>
-    <col min="37" max="37" width="14.1454545454545" customWidth="1"/>
-    <col min="38" max="38" width="14.7181818181818" customWidth="1"/>
-    <col min="39" max="39" width="17.4272727272727" customWidth="1"/>
-    <col min="40" max="40" width="22" customWidth="1"/>
-    <col min="41" max="41" width="17.5727272727273" customWidth="1"/>
-    <col min="42" max="42" width="25.2818181818182" customWidth="1"/>
-    <col min="43" max="43" width="13" customWidth="1"/>
-    <col min="44" max="44" width="23.7181818181818" customWidth="1"/>
-    <col min="45" max="45" width="10" customWidth="1"/>
-    <col min="46" max="46" width="13" customWidth="1"/>
-    <col min="47" max="47" width="15.5727272727273" customWidth="1"/>
-    <col min="48" max="48" width="21.1454545454545" customWidth="1"/>
-    <col min="49" max="49" width="11.5727272727273" customWidth="1"/>
-    <col min="50" max="50" width="16.7181818181818" customWidth="1"/>
-    <col min="51" max="51" width="14" customWidth="1"/>
-    <col min="52" max="52" width="19.4272727272727" customWidth="1"/>
-    <col min="53" max="53" width="18.8545454545455" customWidth="1"/>
-    <col min="54" max="54" width="23.2818181818182" customWidth="1"/>
-    <col min="55" max="55" width="15.5727272727273" customWidth="1"/>
-    <col min="56" max="56" width="14.2818181818182" customWidth="1"/>
-    <col min="57" max="57" width="17" customWidth="1"/>
-    <col min="58" max="58" width="16.2818181818182" customWidth="1"/>
-    <col min="59" max="59" width="13.5727272727273" customWidth="1"/>
-    <col min="60" max="61" width="12.7181818181818" customWidth="1"/>
-    <col min="62" max="62" width="21.8545454545455" customWidth="1"/>
-    <col min="63" max="63" width="30.5727272727273" customWidth="1"/>
-    <col min="64" max="64" width="10" customWidth="1"/>
-    <col min="65" max="65" width="42.5727272727273" customWidth="1"/>
-    <col min="66" max="66" width="38.1454545454545" customWidth="1"/>
-    <col min="67" max="67" width="19.4272727272727" customWidth="1"/>
-    <col min="68" max="68" width="35.4272727272727" customWidth="1"/>
-    <col min="69" max="69" width="9.57272727272727" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="5.14545454545455"/>
+    <col min="2" max="3" customWidth="true" width="22.0"/>
+    <col min="4" max="4" customWidth="true" width="79.4272727272727"/>
+    <col min="5" max="5" customWidth="true" width="11.5727272727273"/>
+    <col min="6" max="6" customWidth="true" width="5.14545454545455"/>
+    <col min="7" max="7" customWidth="true" width="11.0"/>
+    <col min="8" max="8" customWidth="true" width="12.7181818181818"/>
+    <col min="9" max="9" customWidth="true" width="5.85454545454545"/>
+    <col min="10" max="10" customWidth="true" width="6.0"/>
+    <col min="11" max="11" customWidth="true" width="5.85454545454545"/>
+    <col min="12" max="12" customWidth="true" width="14.2818181818182"/>
+    <col min="13" max="13" customWidth="true" width="9.42727272727273"/>
+    <col min="14" max="14" customWidth="true" width="14.4272727272727"/>
+    <col min="15" max="15" customWidth="true" width="15.5727272727273"/>
+    <col min="16" max="16" customWidth="true" width="14.4272727272727"/>
+    <col min="17" max="17" customWidth="true" width="39.4272727272727"/>
+    <col min="18" max="18" customWidth="true" width="11.7181818181818"/>
+    <col min="19" max="19" customWidth="true" width="11.8545454545455"/>
+    <col min="20" max="20" customWidth="true" width="6.42727272727273"/>
+    <col min="21" max="22" customWidth="true" width="6.57272727272727"/>
+    <col min="23" max="23" customWidth="true" width="37.1454545454545"/>
+    <col min="24" max="25" customWidth="true" width="8.0"/>
+    <col min="26" max="26" customWidth="true" width="7.71818181818182"/>
+    <col min="27" max="27" customWidth="true" width="6.28181818181818"/>
+    <col min="28" max="28" customWidth="true" width="9.28181818181818"/>
+    <col min="29" max="29" customWidth="true" width="9.71818181818182"/>
+    <col min="30" max="30" customWidth="true" width="12.8545454545455"/>
+    <col min="31" max="31" customWidth="true" width="16.1454545454545"/>
+    <col min="32" max="32" customWidth="true" width="15.4272727272727"/>
+    <col min="33" max="33" customWidth="true" width="24.5727272727273"/>
+    <col min="34" max="34" customWidth="true" width="8.57272727272727"/>
+    <col min="35" max="35" customWidth="true" width="14.7181818181818"/>
+    <col min="36" max="36" customWidth="true" width="18.5727272727273"/>
+    <col min="37" max="37" customWidth="true" width="14.1454545454545"/>
+    <col min="38" max="38" customWidth="true" width="14.7181818181818"/>
+    <col min="39" max="39" customWidth="true" width="17.4272727272727"/>
+    <col min="40" max="40" customWidth="true" width="22.0"/>
+    <col min="41" max="41" customWidth="true" width="17.5727272727273"/>
+    <col min="42" max="42" customWidth="true" width="25.2818181818182"/>
+    <col min="43" max="43" customWidth="true" width="13.0"/>
+    <col min="44" max="44" customWidth="true" width="23.7181818181818"/>
+    <col min="45" max="45" customWidth="true" width="10.0"/>
+    <col min="46" max="46" customWidth="true" width="13.0"/>
+    <col min="47" max="47" customWidth="true" width="15.5727272727273"/>
+    <col min="48" max="48" customWidth="true" width="21.1454545454545"/>
+    <col min="49" max="49" customWidth="true" width="11.5727272727273"/>
+    <col min="50" max="50" customWidth="true" width="16.7181818181818"/>
+    <col min="51" max="51" customWidth="true" width="14.0"/>
+    <col min="52" max="52" customWidth="true" width="19.4272727272727"/>
+    <col min="53" max="53" customWidth="true" width="18.8545454545455"/>
+    <col min="54" max="54" customWidth="true" width="23.2818181818182"/>
+    <col min="55" max="55" customWidth="true" width="15.5727272727273"/>
+    <col min="56" max="56" customWidth="true" width="14.2818181818182"/>
+    <col min="57" max="57" customWidth="true" width="17.0"/>
+    <col min="58" max="58" customWidth="true" width="16.2818181818182"/>
+    <col min="59" max="59" customWidth="true" width="13.5727272727273"/>
+    <col min="60" max="61" customWidth="true" width="12.7181818181818"/>
+    <col min="62" max="62" customWidth="true" width="21.8545454545455"/>
+    <col min="63" max="63" customWidth="true" width="30.5727272727273"/>
+    <col min="64" max="64" customWidth="true" width="10.0"/>
+    <col min="65" max="65" customWidth="true" width="42.5727272727273"/>
+    <col min="66" max="66" customWidth="true" width="38.1454545454545"/>
+    <col min="67" max="67" customWidth="true" width="19.4272727272727"/>
+    <col min="68" max="68" customWidth="true" width="35.4272727272727"/>
+    <col min="69" max="69" customWidth="true" width="9.57272727272727"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -10370,6 +10531,8 @@
       <c r="AT4" s="35" t="s">
         <v>76</v>
       </c>
+      <c r="AU4" s="0"/>
+      <c r="AV4" s="0"/>
       <c r="AW4" s="35">
         <f>AM4</f>
         <v>4</v>
@@ -10408,10 +10571,10 @@
       <c r="BL4" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="BM4" t="s">
+      <c r="BM4" t="s" s="0">
         <v>100</v>
       </c>
-      <c r="BN4" t="s">
+      <c r="BN4" t="s" s="0">
         <v>100</v>
       </c>
       <c r="BO4" s="35">
@@ -10559,72 +10722,72 @@
   <dimension ref="A1:BQ5"/>
   <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" width="5.14545454545455" customWidth="1"/>
-    <col min="2" max="2" width="21.8545454545455" customWidth="1"/>
-    <col min="3" max="3" width="27.5727272727273" customWidth="1"/>
-    <col min="4" max="4" width="79.4272727272727" customWidth="1"/>
-    <col min="5" max="5" width="11.5727272727273" customWidth="1"/>
-    <col min="6" max="6" width="5.14545454545455" customWidth="1"/>
-    <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="12.7181818181818" customWidth="1"/>
-    <col min="9" max="10" width="5.85454545454545" customWidth="1"/>
-    <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="14.2818181818182" customWidth="1"/>
-    <col min="13" max="13" width="9.42727272727273" customWidth="1"/>
-    <col min="14" max="14" width="14.2818181818182" customWidth="1"/>
-    <col min="15" max="15" width="15.5727272727273" customWidth="1"/>
-    <col min="16" max="16" width="14.4272727272727" customWidth="1"/>
-    <col min="17" max="17" width="39.4272727272727" customWidth="1"/>
-    <col min="18" max="18" width="11.7181818181818" customWidth="1"/>
-    <col min="19" max="19" width="10" customWidth="1"/>
-    <col min="20" max="20" width="6.42727272727273" customWidth="1"/>
-    <col min="21" max="21" width="9.85454545454546" customWidth="1"/>
-    <col min="22" max="22" width="6.57272727272727" customWidth="1"/>
-    <col min="23" max="23" width="37.1454545454545" customWidth="1"/>
-    <col min="24" max="25" width="8" customWidth="1"/>
-    <col min="26" max="26" width="7.71818181818182" customWidth="1"/>
-    <col min="27" max="27" width="6.28181818181818" customWidth="1"/>
-    <col min="28" max="28" width="9.28181818181818" customWidth="1"/>
-    <col min="29" max="29" width="9.71818181818182" customWidth="1"/>
-    <col min="30" max="30" width="12.8545454545455" customWidth="1"/>
-    <col min="31" max="31" width="16.1454545454545" customWidth="1"/>
-    <col min="32" max="32" width="15.4272727272727" customWidth="1"/>
-    <col min="33" max="33" width="24.5727272727273" customWidth="1"/>
-    <col min="34" max="34" width="8.57272727272727" customWidth="1"/>
-    <col min="35" max="35" width="14.7181818181818" customWidth="1"/>
-    <col min="36" max="36" width="18.5727272727273" customWidth="1"/>
-    <col min="37" max="37" width="14.1454545454545" customWidth="1"/>
-    <col min="38" max="38" width="14.7181818181818" customWidth="1"/>
-    <col min="39" max="39" width="17.4272727272727" customWidth="1"/>
-    <col min="40" max="40" width="22" customWidth="1"/>
-    <col min="41" max="41" width="17.5727272727273" customWidth="1"/>
-    <col min="42" max="42" width="25.2818181818182" customWidth="1"/>
-    <col min="43" max="43" width="13" customWidth="1"/>
-    <col min="44" max="44" width="25.7181818181818" customWidth="1"/>
-    <col min="45" max="45" width="10" customWidth="1"/>
-    <col min="46" max="46" width="13" customWidth="1"/>
-    <col min="47" max="47" width="15.5727272727273" customWidth="1"/>
-    <col min="48" max="48" width="21.1454545454545" customWidth="1"/>
-    <col min="49" max="49" width="11.5727272727273" customWidth="1"/>
-    <col min="50" max="50" width="16.7181818181818" customWidth="1"/>
-    <col min="51" max="51" width="14" customWidth="1"/>
-    <col min="52" max="52" width="19.4272727272727" customWidth="1"/>
-    <col min="53" max="53" width="18.8545454545455" customWidth="1"/>
-    <col min="54" max="54" width="23.2818181818182" customWidth="1"/>
-    <col min="55" max="55" width="15.5727272727273" customWidth="1"/>
-    <col min="56" max="56" width="14.2818181818182" customWidth="1"/>
-    <col min="57" max="57" width="17" customWidth="1"/>
-    <col min="58" max="58" width="16.2818181818182" customWidth="1"/>
-    <col min="59" max="59" width="13.5727272727273" customWidth="1"/>
-    <col min="60" max="61" width="12.7181818181818" customWidth="1"/>
-    <col min="62" max="62" width="21.8545454545455" customWidth="1"/>
-    <col min="63" max="63" width="30.5727272727273" customWidth="1"/>
-    <col min="64" max="64" width="10" customWidth="1"/>
-    <col min="65" max="65" width="42.5727272727273" customWidth="1"/>
-    <col min="66" max="66" width="38.1454545454545" customWidth="1"/>
-    <col min="67" max="67" width="19.4272727272727" customWidth="1"/>
-    <col min="68" max="68" width="35.4272727272727" customWidth="1"/>
-    <col min="69" max="69" width="9.57272727272727" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="5.14545454545455"/>
+    <col min="2" max="2" customWidth="true" width="21.8545454545455"/>
+    <col min="3" max="3" customWidth="true" width="27.5727272727273"/>
+    <col min="4" max="4" customWidth="true" width="79.4272727272727"/>
+    <col min="5" max="5" customWidth="true" width="11.5727272727273"/>
+    <col min="6" max="6" customWidth="true" width="5.14545454545455"/>
+    <col min="7" max="7" customWidth="true" width="11.0"/>
+    <col min="8" max="8" customWidth="true" width="12.7181818181818"/>
+    <col min="9" max="10" customWidth="true" width="5.85454545454545"/>
+    <col min="11" max="11" customWidth="true" width="6.0"/>
+    <col min="12" max="12" customWidth="true" width="14.2818181818182"/>
+    <col min="13" max="13" customWidth="true" width="9.42727272727273"/>
+    <col min="14" max="14" customWidth="true" width="14.2818181818182"/>
+    <col min="15" max="15" customWidth="true" width="15.5727272727273"/>
+    <col min="16" max="16" customWidth="true" width="14.4272727272727"/>
+    <col min="17" max="17" customWidth="true" width="39.4272727272727"/>
+    <col min="18" max="18" customWidth="true" width="11.7181818181818"/>
+    <col min="19" max="19" customWidth="true" width="10.0"/>
+    <col min="20" max="20" customWidth="true" width="6.42727272727273"/>
+    <col min="21" max="21" customWidth="true" width="9.85454545454546"/>
+    <col min="22" max="22" customWidth="true" width="6.57272727272727"/>
+    <col min="23" max="23" customWidth="true" width="37.1454545454545"/>
+    <col min="24" max="25" customWidth="true" width="8.0"/>
+    <col min="26" max="26" customWidth="true" width="7.71818181818182"/>
+    <col min="27" max="27" customWidth="true" width="6.28181818181818"/>
+    <col min="28" max="28" customWidth="true" width="9.28181818181818"/>
+    <col min="29" max="29" customWidth="true" width="9.71818181818182"/>
+    <col min="30" max="30" customWidth="true" width="12.8545454545455"/>
+    <col min="31" max="31" customWidth="true" width="16.1454545454545"/>
+    <col min="32" max="32" customWidth="true" width="15.4272727272727"/>
+    <col min="33" max="33" customWidth="true" width="24.5727272727273"/>
+    <col min="34" max="34" customWidth="true" width="8.57272727272727"/>
+    <col min="35" max="35" customWidth="true" width="14.7181818181818"/>
+    <col min="36" max="36" customWidth="true" width="18.5727272727273"/>
+    <col min="37" max="37" customWidth="true" width="14.1454545454545"/>
+    <col min="38" max="38" customWidth="true" width="14.7181818181818"/>
+    <col min="39" max="39" customWidth="true" width="17.4272727272727"/>
+    <col min="40" max="40" customWidth="true" width="22.0"/>
+    <col min="41" max="41" customWidth="true" width="17.5727272727273"/>
+    <col min="42" max="42" customWidth="true" width="25.2818181818182"/>
+    <col min="43" max="43" customWidth="true" width="13.0"/>
+    <col min="44" max="44" customWidth="true" width="25.7181818181818"/>
+    <col min="45" max="45" customWidth="true" width="10.0"/>
+    <col min="46" max="46" customWidth="true" width="13.0"/>
+    <col min="47" max="47" customWidth="true" width="15.5727272727273"/>
+    <col min="48" max="48" customWidth="true" width="21.1454545454545"/>
+    <col min="49" max="49" customWidth="true" width="11.5727272727273"/>
+    <col min="50" max="50" customWidth="true" width="16.7181818181818"/>
+    <col min="51" max="51" customWidth="true" width="14.0"/>
+    <col min="52" max="52" customWidth="true" width="19.4272727272727"/>
+    <col min="53" max="53" customWidth="true" width="18.8545454545455"/>
+    <col min="54" max="54" customWidth="true" width="23.2818181818182"/>
+    <col min="55" max="55" customWidth="true" width="15.5727272727273"/>
+    <col min="56" max="56" customWidth="true" width="14.2818181818182"/>
+    <col min="57" max="57" customWidth="true" width="17.0"/>
+    <col min="58" max="58" customWidth="true" width="16.2818181818182"/>
+    <col min="59" max="59" customWidth="true" width="13.5727272727273"/>
+    <col min="60" max="61" customWidth="true" width="12.7181818181818"/>
+    <col min="62" max="62" customWidth="true" width="21.8545454545455"/>
+    <col min="63" max="63" customWidth="true" width="30.5727272727273"/>
+    <col min="64" max="64" customWidth="true" width="10.0"/>
+    <col min="65" max="65" customWidth="true" width="42.5727272727273"/>
+    <col min="66" max="66" customWidth="true" width="38.1454545454545"/>
+    <col min="67" max="67" customWidth="true" width="19.4272727272727"/>
+    <col min="68" max="68" customWidth="true" width="35.4272727272727"/>
+    <col min="69" max="69" customWidth="true" width="9.57272727272727"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -11168,11 +11331,11 @@
       <c r="AT4" s="35" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" t="s">
-        <v>91</v>
-      </c>
-      <c r="AV4" t="s">
-        <v>92</v>
+      <c r="AU4" t="s" s="0">
+        <v>177</v>
+      </c>
+      <c r="AV4" t="s" s="0">
+        <v>178</v>
       </c>
       <c r="AW4" s="35">
         <f>AM4</f>
@@ -11186,7 +11349,7 @@
         <f>AU4+AW4</f>
         <v>4</v>
       </c>
-      <c r="AZ4" t="s">
+      <c r="AZ4" t="s" s="0">
         <v>92</v>
       </c>
       <c r="BA4" s="36"/>
@@ -11211,11 +11374,11 @@
       <c r="BL4" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="BM4" t="s">
-        <v>93</v>
-      </c>
-      <c r="BN4" t="s">
-        <v>94</v>
+      <c r="BM4" t="s" s="0">
+        <v>180</v>
+      </c>
+      <c r="BN4" t="s" s="0">
+        <v>179</v>
       </c>
       <c r="BO4" s="35">
         <f>ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
@@ -11362,71 +11525,71 @@
   <dimension ref="A1:BQ5"/>
   <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" width="5.14545454545455" customWidth="1"/>
-    <col min="2" max="3" width="28" customWidth="1"/>
-    <col min="4" max="4" width="79.4272727272727" customWidth="1"/>
-    <col min="5" max="5" width="11.5727272727273" customWidth="1"/>
-    <col min="6" max="6" width="5.14545454545455" customWidth="1"/>
-    <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="12.7181818181818" customWidth="1"/>
-    <col min="9" max="9" width="5.85454545454545" customWidth="1"/>
-    <col min="10" max="10" width="6" customWidth="1"/>
-    <col min="11" max="11" width="5.85454545454545" customWidth="1"/>
-    <col min="12" max="12" width="14.2818181818182" customWidth="1"/>
-    <col min="13" max="13" width="9.42727272727273" customWidth="1"/>
-    <col min="14" max="14" width="14.4272727272727" customWidth="1"/>
-    <col min="15" max="15" width="15.5727272727273" customWidth="1"/>
-    <col min="16" max="16" width="14.4272727272727" customWidth="1"/>
-    <col min="17" max="17" width="39.4272727272727" customWidth="1"/>
-    <col min="18" max="18" width="11.7181818181818" customWidth="1"/>
-    <col min="19" max="19" width="11.8545454545455" customWidth="1"/>
-    <col min="20" max="20" width="6.42727272727273" customWidth="1"/>
-    <col min="21" max="22" width="6.57272727272727" customWidth="1"/>
-    <col min="23" max="23" width="37.1454545454545" customWidth="1"/>
-    <col min="24" max="25" width="8" customWidth="1"/>
-    <col min="26" max="26" width="7.71818181818182" customWidth="1"/>
-    <col min="27" max="27" width="6.28181818181818" customWidth="1"/>
-    <col min="28" max="28" width="9.28181818181818" customWidth="1"/>
-    <col min="29" max="29" width="9.71818181818182" customWidth="1"/>
-    <col min="30" max="30" width="12.8545454545455" customWidth="1"/>
-    <col min="31" max="31" width="16.1454545454545" customWidth="1"/>
-    <col min="32" max="32" width="15.4272727272727" customWidth="1"/>
-    <col min="33" max="33" width="24.5727272727273" customWidth="1"/>
-    <col min="34" max="34" width="8.57272727272727" customWidth="1"/>
-    <col min="35" max="35" width="14.7181818181818" customWidth="1"/>
-    <col min="36" max="36" width="18.5727272727273" customWidth="1"/>
-    <col min="37" max="37" width="14.1454545454545" customWidth="1"/>
-    <col min="38" max="38" width="14.7181818181818" customWidth="1"/>
-    <col min="39" max="39" width="17.4272727272727" customWidth="1"/>
-    <col min="40" max="40" width="22" customWidth="1"/>
-    <col min="41" max="41" width="17.5727272727273" customWidth="1"/>
-    <col min="42" max="42" width="25.2818181818182" customWidth="1"/>
-    <col min="43" max="43" width="13" customWidth="1"/>
-    <col min="44" max="44" width="23.7181818181818" customWidth="1"/>
-    <col min="45" max="45" width="10" customWidth="1"/>
-    <col min="46" max="46" width="13" customWidth="1"/>
-    <col min="47" max="47" width="15.5727272727273" customWidth="1"/>
-    <col min="48" max="48" width="21.1454545454545" customWidth="1"/>
-    <col min="49" max="49" width="11.5727272727273" customWidth="1"/>
-    <col min="50" max="50" width="16.7181818181818" customWidth="1"/>
-    <col min="51" max="51" width="14" customWidth="1"/>
-    <col min="52" max="52" width="19.4272727272727" customWidth="1"/>
-    <col min="53" max="53" width="18.8545454545455" customWidth="1"/>
-    <col min="54" max="54" width="23.2818181818182" customWidth="1"/>
-    <col min="55" max="55" width="15.5727272727273" customWidth="1"/>
-    <col min="56" max="56" width="14.2818181818182" customWidth="1"/>
-    <col min="57" max="57" width="17" customWidth="1"/>
-    <col min="58" max="58" width="16.2818181818182" customWidth="1"/>
-    <col min="59" max="59" width="13.5727272727273" customWidth="1"/>
-    <col min="60" max="61" width="12.7181818181818" customWidth="1"/>
-    <col min="62" max="62" width="21.8545454545455" customWidth="1"/>
-    <col min="63" max="63" width="30.5727272727273" customWidth="1"/>
-    <col min="64" max="64" width="10" customWidth="1"/>
-    <col min="65" max="65" width="42.5727272727273" customWidth="1"/>
-    <col min="66" max="66" width="38.1454545454545" customWidth="1"/>
-    <col min="67" max="67" width="19.4272727272727" customWidth="1"/>
-    <col min="68" max="68" width="35.4272727272727" customWidth="1"/>
-    <col min="69" max="69" width="9.57272727272727" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="5.14545454545455"/>
+    <col min="2" max="3" customWidth="true" width="28.0"/>
+    <col min="4" max="4" customWidth="true" width="79.4272727272727"/>
+    <col min="5" max="5" customWidth="true" width="11.5727272727273"/>
+    <col min="6" max="6" customWidth="true" width="5.14545454545455"/>
+    <col min="7" max="7" customWidth="true" width="11.0"/>
+    <col min="8" max="8" customWidth="true" width="12.7181818181818"/>
+    <col min="9" max="9" customWidth="true" width="5.85454545454545"/>
+    <col min="10" max="10" customWidth="true" width="6.0"/>
+    <col min="11" max="11" customWidth="true" width="5.85454545454545"/>
+    <col min="12" max="12" customWidth="true" width="14.2818181818182"/>
+    <col min="13" max="13" customWidth="true" width="9.42727272727273"/>
+    <col min="14" max="14" customWidth="true" width="14.4272727272727"/>
+    <col min="15" max="15" customWidth="true" width="15.5727272727273"/>
+    <col min="16" max="16" customWidth="true" width="14.4272727272727"/>
+    <col min="17" max="17" customWidth="true" width="39.4272727272727"/>
+    <col min="18" max="18" customWidth="true" width="11.7181818181818"/>
+    <col min="19" max="19" customWidth="true" width="11.8545454545455"/>
+    <col min="20" max="20" customWidth="true" width="6.42727272727273"/>
+    <col min="21" max="22" customWidth="true" width="6.57272727272727"/>
+    <col min="23" max="23" customWidth="true" width="37.1454545454545"/>
+    <col min="24" max="25" customWidth="true" width="8.0"/>
+    <col min="26" max="26" customWidth="true" width="7.71818181818182"/>
+    <col min="27" max="27" customWidth="true" width="6.28181818181818"/>
+    <col min="28" max="28" customWidth="true" width="9.28181818181818"/>
+    <col min="29" max="29" customWidth="true" width="9.71818181818182"/>
+    <col min="30" max="30" customWidth="true" width="12.8545454545455"/>
+    <col min="31" max="31" customWidth="true" width="16.1454545454545"/>
+    <col min="32" max="32" customWidth="true" width="15.4272727272727"/>
+    <col min="33" max="33" customWidth="true" width="24.5727272727273"/>
+    <col min="34" max="34" customWidth="true" width="8.57272727272727"/>
+    <col min="35" max="35" customWidth="true" width="14.7181818181818"/>
+    <col min="36" max="36" customWidth="true" width="18.5727272727273"/>
+    <col min="37" max="37" customWidth="true" width="14.1454545454545"/>
+    <col min="38" max="38" customWidth="true" width="14.7181818181818"/>
+    <col min="39" max="39" customWidth="true" width="17.4272727272727"/>
+    <col min="40" max="40" customWidth="true" width="22.0"/>
+    <col min="41" max="41" customWidth="true" width="17.5727272727273"/>
+    <col min="42" max="42" customWidth="true" width="25.2818181818182"/>
+    <col min="43" max="43" customWidth="true" width="13.0"/>
+    <col min="44" max="44" customWidth="true" width="23.7181818181818"/>
+    <col min="45" max="45" customWidth="true" width="10.0"/>
+    <col min="46" max="46" customWidth="true" width="13.0"/>
+    <col min="47" max="47" customWidth="true" width="15.5727272727273"/>
+    <col min="48" max="48" customWidth="true" width="21.1454545454545"/>
+    <col min="49" max="49" customWidth="true" width="11.5727272727273"/>
+    <col min="50" max="50" customWidth="true" width="16.7181818181818"/>
+    <col min="51" max="51" customWidth="true" width="14.0"/>
+    <col min="52" max="52" customWidth="true" width="19.4272727272727"/>
+    <col min="53" max="53" customWidth="true" width="18.8545454545455"/>
+    <col min="54" max="54" customWidth="true" width="23.2818181818182"/>
+    <col min="55" max="55" customWidth="true" width="15.5727272727273"/>
+    <col min="56" max="56" customWidth="true" width="14.2818181818182"/>
+    <col min="57" max="57" customWidth="true" width="17.0"/>
+    <col min="58" max="58" customWidth="true" width="16.2818181818182"/>
+    <col min="59" max="59" customWidth="true" width="13.5727272727273"/>
+    <col min="60" max="61" customWidth="true" width="12.7181818181818"/>
+    <col min="62" max="62" customWidth="true" width="21.8545454545455"/>
+    <col min="63" max="63" customWidth="true" width="30.5727272727273"/>
+    <col min="64" max="64" customWidth="true" width="10.0"/>
+    <col min="65" max="65" customWidth="true" width="42.5727272727273"/>
+    <col min="66" max="66" customWidth="true" width="38.1454545454545"/>
+    <col min="67" max="67" customWidth="true" width="19.4272727272727"/>
+    <col min="68" max="68" customWidth="true" width="35.4272727272727"/>
+    <col min="69" max="69" customWidth="true" width="9.57272727272727"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -11970,11 +12133,11 @@
       <c r="AT4" s="35" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" t="s">
-        <v>143</v>
-      </c>
-      <c r="AV4" t="s">
-        <v>144</v>
+      <c r="AU4" t="s" s="0">
+        <v>204</v>
+      </c>
+      <c r="AV4" t="s" s="0">
+        <v>205</v>
       </c>
       <c r="AW4" s="35">
         <f>AM4</f>
@@ -12014,11 +12177,11 @@
       <c r="BL4" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="BM4" t="s">
-        <v>145</v>
-      </c>
-      <c r="BN4" t="s">
-        <v>146</v>
+      <c r="BM4" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="BN4" t="s" s="0">
+        <v>206</v>
       </c>
       <c r="BO4" s="35">
         <f>ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
@@ -12177,71 +12340,71 @@
   <dimension ref="A1:BQ5"/>
   <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" width="5.14545454545455" customWidth="1"/>
-    <col min="2" max="3" width="28" customWidth="1"/>
-    <col min="4" max="4" width="79.4272727272727" customWidth="1"/>
-    <col min="5" max="5" width="11.5727272727273" customWidth="1"/>
-    <col min="6" max="6" width="5.14545454545455" customWidth="1"/>
-    <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="12.7181818181818" customWidth="1"/>
-    <col min="9" max="9" width="5.85454545454545" customWidth="1"/>
-    <col min="10" max="10" width="6" customWidth="1"/>
-    <col min="11" max="11" width="5.85454545454545" customWidth="1"/>
-    <col min="12" max="12" width="14.2818181818182" customWidth="1"/>
-    <col min="13" max="13" width="9.42727272727273" customWidth="1"/>
-    <col min="14" max="14" width="14.4272727272727" customWidth="1"/>
-    <col min="15" max="15" width="15.5727272727273" customWidth="1"/>
-    <col min="16" max="16" width="14.4272727272727" customWidth="1"/>
-    <col min="17" max="17" width="39.4272727272727" customWidth="1"/>
-    <col min="18" max="18" width="11.7181818181818" customWidth="1"/>
-    <col min="19" max="19" width="11.8545454545455" customWidth="1"/>
-    <col min="20" max="20" width="6.42727272727273" customWidth="1"/>
-    <col min="21" max="22" width="6.57272727272727" customWidth="1"/>
-    <col min="23" max="23" width="37.1454545454545" customWidth="1"/>
-    <col min="24" max="25" width="8" customWidth="1"/>
-    <col min="26" max="26" width="7.71818181818182" customWidth="1"/>
-    <col min="27" max="27" width="6.28181818181818" customWidth="1"/>
-    <col min="28" max="28" width="9.28181818181818" customWidth="1"/>
-    <col min="29" max="29" width="9.71818181818182" customWidth="1"/>
-    <col min="30" max="30" width="12.8545454545455" customWidth="1"/>
-    <col min="31" max="31" width="16.1454545454545" customWidth="1"/>
-    <col min="32" max="32" width="15.4272727272727" customWidth="1"/>
-    <col min="33" max="33" width="24.5727272727273" customWidth="1"/>
-    <col min="34" max="34" width="8.57272727272727" customWidth="1"/>
-    <col min="35" max="35" width="14.7181818181818" customWidth="1"/>
-    <col min="36" max="36" width="18.5727272727273" customWidth="1"/>
-    <col min="37" max="37" width="14.1454545454545" customWidth="1"/>
-    <col min="38" max="38" width="14.7181818181818" customWidth="1"/>
-    <col min="39" max="39" width="17.4272727272727" customWidth="1"/>
-    <col min="40" max="40" width="22" customWidth="1"/>
-    <col min="41" max="41" width="17.5727272727273" customWidth="1"/>
-    <col min="42" max="42" width="25.2818181818182" customWidth="1"/>
-    <col min="43" max="43" width="13" customWidth="1"/>
-    <col min="44" max="44" width="23.7181818181818" customWidth="1"/>
-    <col min="45" max="45" width="10" customWidth="1"/>
-    <col min="46" max="46" width="13" customWidth="1"/>
-    <col min="47" max="47" width="15.5727272727273" customWidth="1"/>
-    <col min="48" max="48" width="21.1454545454545" customWidth="1"/>
-    <col min="49" max="49" width="11.5727272727273" customWidth="1"/>
-    <col min="50" max="50" width="16.7181818181818" customWidth="1"/>
-    <col min="51" max="51" width="14" customWidth="1"/>
-    <col min="52" max="52" width="19.4272727272727" customWidth="1"/>
-    <col min="53" max="53" width="18.8545454545455" customWidth="1"/>
-    <col min="54" max="54" width="23.2818181818182" customWidth="1"/>
-    <col min="55" max="55" width="15.5727272727273" customWidth="1"/>
-    <col min="56" max="56" width="14.2818181818182" customWidth="1"/>
-    <col min="57" max="57" width="17" customWidth="1"/>
-    <col min="58" max="58" width="16.2818181818182" customWidth="1"/>
-    <col min="59" max="59" width="13.5727272727273" customWidth="1"/>
-    <col min="60" max="61" width="12.7181818181818" customWidth="1"/>
-    <col min="62" max="62" width="21.8545454545455" customWidth="1"/>
-    <col min="63" max="63" width="30.5727272727273" customWidth="1"/>
-    <col min="64" max="64" width="10" customWidth="1"/>
-    <col min="65" max="65" width="42.5727272727273" customWidth="1"/>
-    <col min="66" max="66" width="38.1454545454545" customWidth="1"/>
-    <col min="67" max="67" width="19.4272727272727" customWidth="1"/>
-    <col min="68" max="68" width="35.4272727272727" customWidth="1"/>
-    <col min="69" max="69" width="9.57272727272727" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="5.14545454545455"/>
+    <col min="2" max="3" customWidth="true" width="28.0"/>
+    <col min="4" max="4" customWidth="true" width="79.4272727272727"/>
+    <col min="5" max="5" customWidth="true" width="11.5727272727273"/>
+    <col min="6" max="6" customWidth="true" width="5.14545454545455"/>
+    <col min="7" max="7" customWidth="true" width="11.0"/>
+    <col min="8" max="8" customWidth="true" width="12.7181818181818"/>
+    <col min="9" max="9" customWidth="true" width="5.85454545454545"/>
+    <col min="10" max="10" customWidth="true" width="6.0"/>
+    <col min="11" max="11" customWidth="true" width="5.85454545454545"/>
+    <col min="12" max="12" customWidth="true" width="14.2818181818182"/>
+    <col min="13" max="13" customWidth="true" width="9.42727272727273"/>
+    <col min="14" max="14" customWidth="true" width="14.4272727272727"/>
+    <col min="15" max="15" customWidth="true" width="15.5727272727273"/>
+    <col min="16" max="16" customWidth="true" width="14.4272727272727"/>
+    <col min="17" max="17" customWidth="true" width="39.4272727272727"/>
+    <col min="18" max="18" customWidth="true" width="11.7181818181818"/>
+    <col min="19" max="19" customWidth="true" width="11.8545454545455"/>
+    <col min="20" max="20" customWidth="true" width="6.42727272727273"/>
+    <col min="21" max="22" customWidth="true" width="6.57272727272727"/>
+    <col min="23" max="23" customWidth="true" width="37.1454545454545"/>
+    <col min="24" max="25" customWidth="true" width="8.0"/>
+    <col min="26" max="26" customWidth="true" width="7.71818181818182"/>
+    <col min="27" max="27" customWidth="true" width="6.28181818181818"/>
+    <col min="28" max="28" customWidth="true" width="9.28181818181818"/>
+    <col min="29" max="29" customWidth="true" width="9.71818181818182"/>
+    <col min="30" max="30" customWidth="true" width="12.8545454545455"/>
+    <col min="31" max="31" customWidth="true" width="16.1454545454545"/>
+    <col min="32" max="32" customWidth="true" width="15.4272727272727"/>
+    <col min="33" max="33" customWidth="true" width="24.5727272727273"/>
+    <col min="34" max="34" customWidth="true" width="8.57272727272727"/>
+    <col min="35" max="35" customWidth="true" width="14.7181818181818"/>
+    <col min="36" max="36" customWidth="true" width="18.5727272727273"/>
+    <col min="37" max="37" customWidth="true" width="14.1454545454545"/>
+    <col min="38" max="38" customWidth="true" width="14.7181818181818"/>
+    <col min="39" max="39" customWidth="true" width="17.4272727272727"/>
+    <col min="40" max="40" customWidth="true" width="22.0"/>
+    <col min="41" max="41" customWidth="true" width="17.5727272727273"/>
+    <col min="42" max="42" customWidth="true" width="25.2818181818182"/>
+    <col min="43" max="43" customWidth="true" width="13.0"/>
+    <col min="44" max="44" customWidth="true" width="23.7181818181818"/>
+    <col min="45" max="45" customWidth="true" width="10.0"/>
+    <col min="46" max="46" customWidth="true" width="13.0"/>
+    <col min="47" max="47" customWidth="true" width="15.5727272727273"/>
+    <col min="48" max="48" customWidth="true" width="21.1454545454545"/>
+    <col min="49" max="49" customWidth="true" width="11.5727272727273"/>
+    <col min="50" max="50" customWidth="true" width="16.7181818181818"/>
+    <col min="51" max="51" customWidth="true" width="14.0"/>
+    <col min="52" max="52" customWidth="true" width="19.4272727272727"/>
+    <col min="53" max="53" customWidth="true" width="18.8545454545455"/>
+    <col min="54" max="54" customWidth="true" width="23.2818181818182"/>
+    <col min="55" max="55" customWidth="true" width="15.5727272727273"/>
+    <col min="56" max="56" customWidth="true" width="14.2818181818182"/>
+    <col min="57" max="57" customWidth="true" width="17.0"/>
+    <col min="58" max="58" customWidth="true" width="16.2818181818182"/>
+    <col min="59" max="59" customWidth="true" width="13.5727272727273"/>
+    <col min="60" max="61" customWidth="true" width="12.7181818181818"/>
+    <col min="62" max="62" customWidth="true" width="21.8545454545455"/>
+    <col min="63" max="63" customWidth="true" width="30.5727272727273"/>
+    <col min="64" max="64" customWidth="true" width="10.0"/>
+    <col min="65" max="65" customWidth="true" width="42.5727272727273"/>
+    <col min="66" max="66" customWidth="true" width="38.1454545454545"/>
+    <col min="67" max="67" customWidth="true" width="19.4272727272727"/>
+    <col min="68" max="68" customWidth="true" width="35.4272727272727"/>
+    <col min="69" max="69" customWidth="true" width="9.57272727272727"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -12785,11 +12948,11 @@
       <c r="AT4" s="35" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" t="s">
-        <v>148</v>
-      </c>
-      <c r="AV4" t="s">
-        <v>149</v>
+      <c r="AU4" t="s" s="0">
+        <v>208</v>
+      </c>
+      <c r="AV4" t="s" s="0">
+        <v>209</v>
       </c>
       <c r="AW4" s="35">
         <f>AM4</f>
@@ -12829,11 +12992,11 @@
       <c r="BL4" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="BM4" t="s">
-        <v>150</v>
-      </c>
-      <c r="BN4" t="s">
-        <v>151</v>
+      <c r="BM4" t="s" s="0">
+        <v>211</v>
+      </c>
+      <c r="BN4" t="s" s="0">
+        <v>210</v>
       </c>
       <c r="BO4" s="35">
         <f>ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
@@ -12992,71 +13155,71 @@
   <dimension ref="A1:BQ5"/>
   <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" width="5.14545454545455" customWidth="1"/>
-    <col min="2" max="3" width="28" customWidth="1"/>
-    <col min="4" max="4" width="79.4272727272727" customWidth="1"/>
-    <col min="5" max="5" width="11.5727272727273" customWidth="1"/>
-    <col min="6" max="6" width="5.14545454545455" customWidth="1"/>
-    <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="12.7181818181818" customWidth="1"/>
-    <col min="9" max="9" width="5.85454545454545" customWidth="1"/>
-    <col min="10" max="10" width="6" customWidth="1"/>
-    <col min="11" max="11" width="5.85454545454545" customWidth="1"/>
-    <col min="12" max="12" width="14.2818181818182" customWidth="1"/>
-    <col min="13" max="13" width="9.42727272727273" customWidth="1"/>
-    <col min="14" max="14" width="14.4272727272727" customWidth="1"/>
-    <col min="15" max="15" width="15.5727272727273" customWidth="1"/>
-    <col min="16" max="16" width="14.4272727272727" customWidth="1"/>
-    <col min="17" max="17" width="39.4272727272727" customWidth="1"/>
-    <col min="18" max="18" width="11.7181818181818" customWidth="1"/>
-    <col min="19" max="19" width="11.8545454545455" customWidth="1"/>
-    <col min="20" max="20" width="6.42727272727273" customWidth="1"/>
-    <col min="21" max="22" width="6.57272727272727" customWidth="1"/>
-    <col min="23" max="23" width="37.1454545454545" customWidth="1"/>
-    <col min="24" max="25" width="8" customWidth="1"/>
-    <col min="26" max="26" width="7.71818181818182" customWidth="1"/>
-    <col min="27" max="27" width="6.28181818181818" customWidth="1"/>
-    <col min="28" max="28" width="9.28181818181818" customWidth="1"/>
-    <col min="29" max="29" width="9.71818181818182" customWidth="1"/>
-    <col min="30" max="30" width="12.8545454545455" customWidth="1"/>
-    <col min="31" max="31" width="16.1454545454545" customWidth="1"/>
-    <col min="32" max="32" width="15.4272727272727" customWidth="1"/>
-    <col min="33" max="33" width="24.5727272727273" customWidth="1"/>
-    <col min="34" max="34" width="8.57272727272727" customWidth="1"/>
-    <col min="35" max="35" width="14.7181818181818" customWidth="1"/>
-    <col min="36" max="36" width="18.5727272727273" customWidth="1"/>
-    <col min="37" max="37" width="14.1454545454545" customWidth="1"/>
-    <col min="38" max="38" width="14.7181818181818" customWidth="1"/>
-    <col min="39" max="39" width="17.4272727272727" customWidth="1"/>
-    <col min="40" max="40" width="22" customWidth="1"/>
-    <col min="41" max="41" width="17.5727272727273" customWidth="1"/>
-    <col min="42" max="42" width="25.2818181818182" customWidth="1"/>
-    <col min="43" max="43" width="13" customWidth="1"/>
-    <col min="44" max="44" width="23.7181818181818" customWidth="1"/>
-    <col min="45" max="45" width="10" customWidth="1"/>
-    <col min="46" max="46" width="13" customWidth="1"/>
-    <col min="47" max="47" width="15.5727272727273" customWidth="1"/>
-    <col min="48" max="48" width="21.1454545454545" customWidth="1"/>
-    <col min="49" max="49" width="11.5727272727273" customWidth="1"/>
-    <col min="50" max="50" width="16.7181818181818" customWidth="1"/>
-    <col min="51" max="51" width="14" customWidth="1"/>
-    <col min="52" max="52" width="19.4272727272727" customWidth="1"/>
-    <col min="53" max="53" width="18.8545454545455" customWidth="1"/>
-    <col min="54" max="54" width="23.2818181818182" customWidth="1"/>
-    <col min="55" max="55" width="15.5727272727273" customWidth="1"/>
-    <col min="56" max="56" width="14.2818181818182" customWidth="1"/>
-    <col min="57" max="57" width="17" customWidth="1"/>
-    <col min="58" max="58" width="16.2818181818182" customWidth="1"/>
-    <col min="59" max="59" width="13.5727272727273" customWidth="1"/>
-    <col min="60" max="61" width="12.7181818181818" customWidth="1"/>
-    <col min="62" max="62" width="21.8545454545455" customWidth="1"/>
-    <col min="63" max="63" width="30.5727272727273" customWidth="1"/>
-    <col min="64" max="64" width="10" customWidth="1"/>
-    <col min="65" max="65" width="42.5727272727273" customWidth="1"/>
-    <col min="66" max="66" width="38.1454545454545" customWidth="1"/>
-    <col min="67" max="67" width="19.4272727272727" customWidth="1"/>
-    <col min="68" max="68" width="35.4272727272727" customWidth="1"/>
-    <col min="69" max="69" width="9.57272727272727" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="5.14545454545455"/>
+    <col min="2" max="3" customWidth="true" width="28.0"/>
+    <col min="4" max="4" customWidth="true" width="79.4272727272727"/>
+    <col min="5" max="5" customWidth="true" width="11.5727272727273"/>
+    <col min="6" max="6" customWidth="true" width="5.14545454545455"/>
+    <col min="7" max="7" customWidth="true" width="11.0"/>
+    <col min="8" max="8" customWidth="true" width="12.7181818181818"/>
+    <col min="9" max="9" customWidth="true" width="5.85454545454545"/>
+    <col min="10" max="10" customWidth="true" width="6.0"/>
+    <col min="11" max="11" customWidth="true" width="5.85454545454545"/>
+    <col min="12" max="12" customWidth="true" width="14.2818181818182"/>
+    <col min="13" max="13" customWidth="true" width="9.42727272727273"/>
+    <col min="14" max="14" customWidth="true" width="14.4272727272727"/>
+    <col min="15" max="15" customWidth="true" width="15.5727272727273"/>
+    <col min="16" max="16" customWidth="true" width="14.4272727272727"/>
+    <col min="17" max="17" customWidth="true" width="39.4272727272727"/>
+    <col min="18" max="18" customWidth="true" width="11.7181818181818"/>
+    <col min="19" max="19" customWidth="true" width="11.8545454545455"/>
+    <col min="20" max="20" customWidth="true" width="6.42727272727273"/>
+    <col min="21" max="22" customWidth="true" width="6.57272727272727"/>
+    <col min="23" max="23" customWidth="true" width="37.1454545454545"/>
+    <col min="24" max="25" customWidth="true" width="8.0"/>
+    <col min="26" max="26" customWidth="true" width="7.71818181818182"/>
+    <col min="27" max="27" customWidth="true" width="6.28181818181818"/>
+    <col min="28" max="28" customWidth="true" width="9.28181818181818"/>
+    <col min="29" max="29" customWidth="true" width="9.71818181818182"/>
+    <col min="30" max="30" customWidth="true" width="12.8545454545455"/>
+    <col min="31" max="31" customWidth="true" width="16.1454545454545"/>
+    <col min="32" max="32" customWidth="true" width="15.4272727272727"/>
+    <col min="33" max="33" customWidth="true" width="24.5727272727273"/>
+    <col min="34" max="34" customWidth="true" width="8.57272727272727"/>
+    <col min="35" max="35" customWidth="true" width="14.7181818181818"/>
+    <col min="36" max="36" customWidth="true" width="18.5727272727273"/>
+    <col min="37" max="37" customWidth="true" width="14.1454545454545"/>
+    <col min="38" max="38" customWidth="true" width="14.7181818181818"/>
+    <col min="39" max="39" customWidth="true" width="17.4272727272727"/>
+    <col min="40" max="40" customWidth="true" width="22.0"/>
+    <col min="41" max="41" customWidth="true" width="17.5727272727273"/>
+    <col min="42" max="42" customWidth="true" width="25.2818181818182"/>
+    <col min="43" max="43" customWidth="true" width="13.0"/>
+    <col min="44" max="44" customWidth="true" width="23.7181818181818"/>
+    <col min="45" max="45" customWidth="true" width="10.0"/>
+    <col min="46" max="46" customWidth="true" width="13.0"/>
+    <col min="47" max="47" customWidth="true" width="15.5727272727273"/>
+    <col min="48" max="48" customWidth="true" width="21.1454545454545"/>
+    <col min="49" max="49" customWidth="true" width="11.5727272727273"/>
+    <col min="50" max="50" customWidth="true" width="16.7181818181818"/>
+    <col min="51" max="51" customWidth="true" width="14.0"/>
+    <col min="52" max="52" customWidth="true" width="19.4272727272727"/>
+    <col min="53" max="53" customWidth="true" width="18.8545454545455"/>
+    <col min="54" max="54" customWidth="true" width="23.2818181818182"/>
+    <col min="55" max="55" customWidth="true" width="15.5727272727273"/>
+    <col min="56" max="56" customWidth="true" width="14.2818181818182"/>
+    <col min="57" max="57" customWidth="true" width="17.0"/>
+    <col min="58" max="58" customWidth="true" width="16.2818181818182"/>
+    <col min="59" max="59" customWidth="true" width="13.5727272727273"/>
+    <col min="60" max="61" customWidth="true" width="12.7181818181818"/>
+    <col min="62" max="62" customWidth="true" width="21.8545454545455"/>
+    <col min="63" max="63" customWidth="true" width="30.5727272727273"/>
+    <col min="64" max="64" customWidth="true" width="10.0"/>
+    <col min="65" max="65" customWidth="true" width="42.5727272727273"/>
+    <col min="66" max="66" customWidth="true" width="38.1454545454545"/>
+    <col min="67" max="67" customWidth="true" width="19.4272727272727"/>
+    <col min="68" max="68" customWidth="true" width="35.4272727272727"/>
+    <col min="69" max="69" customWidth="true" width="9.57272727272727"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -13600,11 +13763,11 @@
       <c r="AT4" s="35" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" t="s">
-        <v>152</v>
-      </c>
-      <c r="AV4" t="s">
-        <v>153</v>
+      <c r="AU4" t="s" s="0">
+        <v>204</v>
+      </c>
+      <c r="AV4" t="s" s="0">
+        <v>205</v>
       </c>
       <c r="AW4" s="35">
         <f>AM4</f>
@@ -13644,11 +13807,11 @@
       <c r="BL4" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="BM4" t="s">
-        <v>145</v>
-      </c>
-      <c r="BN4" t="s">
-        <v>146</v>
+      <c r="BM4" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="BN4" t="s" s="0">
+        <v>206</v>
       </c>
       <c r="BO4" s="35">
         <f>ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
@@ -13795,71 +13958,71 @@
   <dimension ref="A1:BQ5"/>
   <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" width="5.14545454545455" customWidth="1"/>
-    <col min="2" max="3" width="28" customWidth="1"/>
-    <col min="4" max="4" width="79.4272727272727" customWidth="1"/>
-    <col min="5" max="5" width="11.5727272727273" customWidth="1"/>
-    <col min="6" max="6" width="5.14545454545455" customWidth="1"/>
-    <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="12.7181818181818" customWidth="1"/>
-    <col min="9" max="9" width="5.85454545454545" customWidth="1"/>
-    <col min="10" max="10" width="6" customWidth="1"/>
-    <col min="11" max="11" width="5.85454545454545" customWidth="1"/>
-    <col min="12" max="12" width="14.2818181818182" customWidth="1"/>
-    <col min="13" max="13" width="9.42727272727273" customWidth="1"/>
-    <col min="14" max="14" width="14.4272727272727" customWidth="1"/>
-    <col min="15" max="15" width="15.5727272727273" customWidth="1"/>
-    <col min="16" max="16" width="14.4272727272727" customWidth="1"/>
-    <col min="17" max="17" width="39.4272727272727" customWidth="1"/>
-    <col min="18" max="18" width="11.7181818181818" customWidth="1"/>
-    <col min="19" max="19" width="11.8545454545455" customWidth="1"/>
-    <col min="20" max="20" width="6.42727272727273" customWidth="1"/>
-    <col min="21" max="22" width="6.57272727272727" customWidth="1"/>
-    <col min="23" max="23" width="37.1454545454545" customWidth="1"/>
-    <col min="24" max="25" width="8" customWidth="1"/>
-    <col min="26" max="26" width="7.71818181818182" customWidth="1"/>
-    <col min="27" max="27" width="6.28181818181818" customWidth="1"/>
-    <col min="28" max="28" width="9.28181818181818" customWidth="1"/>
-    <col min="29" max="29" width="9.71818181818182" customWidth="1"/>
-    <col min="30" max="30" width="12.8545454545455" customWidth="1"/>
-    <col min="31" max="31" width="16.1454545454545" customWidth="1"/>
-    <col min="32" max="32" width="15.4272727272727" customWidth="1"/>
-    <col min="33" max="33" width="24.5727272727273" customWidth="1"/>
-    <col min="34" max="34" width="8.57272727272727" customWidth="1"/>
-    <col min="35" max="35" width="14.7181818181818" customWidth="1"/>
-    <col min="36" max="36" width="18.5727272727273" customWidth="1"/>
-    <col min="37" max="37" width="14.1454545454545" customWidth="1"/>
-    <col min="38" max="38" width="14.7181818181818" customWidth="1"/>
-    <col min="39" max="39" width="17.4272727272727" customWidth="1"/>
-    <col min="40" max="40" width="22" customWidth="1"/>
-    <col min="41" max="41" width="17.5727272727273" customWidth="1"/>
-    <col min="42" max="42" width="25.2818181818182" customWidth="1"/>
-    <col min="43" max="43" width="13" customWidth="1"/>
-    <col min="44" max="44" width="23.7181818181818" customWidth="1"/>
-    <col min="45" max="45" width="10" customWidth="1"/>
-    <col min="46" max="46" width="13" customWidth="1"/>
-    <col min="47" max="47" width="15.5727272727273" customWidth="1"/>
-    <col min="48" max="48" width="21.1454545454545" customWidth="1"/>
-    <col min="49" max="49" width="11.5727272727273" customWidth="1"/>
-    <col min="50" max="50" width="16.7181818181818" customWidth="1"/>
-    <col min="51" max="51" width="14" customWidth="1"/>
-    <col min="52" max="52" width="19.4272727272727" customWidth="1"/>
-    <col min="53" max="53" width="18.8545454545455" customWidth="1"/>
-    <col min="54" max="54" width="23.2818181818182" customWidth="1"/>
-    <col min="55" max="55" width="15.5727272727273" customWidth="1"/>
-    <col min="56" max="56" width="14.2818181818182" customWidth="1"/>
-    <col min="57" max="57" width="17" customWidth="1"/>
-    <col min="58" max="58" width="16.2818181818182" customWidth="1"/>
-    <col min="59" max="59" width="13.5727272727273" customWidth="1"/>
-    <col min="60" max="61" width="12.7181818181818" customWidth="1"/>
-    <col min="62" max="62" width="21.8545454545455" customWidth="1"/>
-    <col min="63" max="63" width="30.5727272727273" customWidth="1"/>
-    <col min="64" max="64" width="10" customWidth="1"/>
-    <col min="65" max="65" width="42.5727272727273" customWidth="1"/>
-    <col min="66" max="66" width="38.1454545454545" customWidth="1"/>
-    <col min="67" max="67" width="19.4272727272727" customWidth="1"/>
-    <col min="68" max="68" width="35.4272727272727" customWidth="1"/>
-    <col min="69" max="69" width="9.57272727272727" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="5.14545454545455"/>
+    <col min="2" max="3" customWidth="true" width="28.0"/>
+    <col min="4" max="4" customWidth="true" width="79.4272727272727"/>
+    <col min="5" max="5" customWidth="true" width="11.5727272727273"/>
+    <col min="6" max="6" customWidth="true" width="5.14545454545455"/>
+    <col min="7" max="7" customWidth="true" width="11.0"/>
+    <col min="8" max="8" customWidth="true" width="12.7181818181818"/>
+    <col min="9" max="9" customWidth="true" width="5.85454545454545"/>
+    <col min="10" max="10" customWidth="true" width="6.0"/>
+    <col min="11" max="11" customWidth="true" width="5.85454545454545"/>
+    <col min="12" max="12" customWidth="true" width="14.2818181818182"/>
+    <col min="13" max="13" customWidth="true" width="9.42727272727273"/>
+    <col min="14" max="14" customWidth="true" width="14.4272727272727"/>
+    <col min="15" max="15" customWidth="true" width="15.5727272727273"/>
+    <col min="16" max="16" customWidth="true" width="14.4272727272727"/>
+    <col min="17" max="17" customWidth="true" width="39.4272727272727"/>
+    <col min="18" max="18" customWidth="true" width="11.7181818181818"/>
+    <col min="19" max="19" customWidth="true" width="11.8545454545455"/>
+    <col min="20" max="20" customWidth="true" width="6.42727272727273"/>
+    <col min="21" max="22" customWidth="true" width="6.57272727272727"/>
+    <col min="23" max="23" customWidth="true" width="37.1454545454545"/>
+    <col min="24" max="25" customWidth="true" width="8.0"/>
+    <col min="26" max="26" customWidth="true" width="7.71818181818182"/>
+    <col min="27" max="27" customWidth="true" width="6.28181818181818"/>
+    <col min="28" max="28" customWidth="true" width="9.28181818181818"/>
+    <col min="29" max="29" customWidth="true" width="9.71818181818182"/>
+    <col min="30" max="30" customWidth="true" width="12.8545454545455"/>
+    <col min="31" max="31" customWidth="true" width="16.1454545454545"/>
+    <col min="32" max="32" customWidth="true" width="15.4272727272727"/>
+    <col min="33" max="33" customWidth="true" width="24.5727272727273"/>
+    <col min="34" max="34" customWidth="true" width="8.57272727272727"/>
+    <col min="35" max="35" customWidth="true" width="14.7181818181818"/>
+    <col min="36" max="36" customWidth="true" width="18.5727272727273"/>
+    <col min="37" max="37" customWidth="true" width="14.1454545454545"/>
+    <col min="38" max="38" customWidth="true" width="14.7181818181818"/>
+    <col min="39" max="39" customWidth="true" width="17.4272727272727"/>
+    <col min="40" max="40" customWidth="true" width="22.0"/>
+    <col min="41" max="41" customWidth="true" width="17.5727272727273"/>
+    <col min="42" max="42" customWidth="true" width="25.2818181818182"/>
+    <col min="43" max="43" customWidth="true" width="13.0"/>
+    <col min="44" max="44" customWidth="true" width="23.7181818181818"/>
+    <col min="45" max="45" customWidth="true" width="10.0"/>
+    <col min="46" max="46" customWidth="true" width="13.0"/>
+    <col min="47" max="47" customWidth="true" width="15.5727272727273"/>
+    <col min="48" max="48" customWidth="true" width="21.1454545454545"/>
+    <col min="49" max="49" customWidth="true" width="11.5727272727273"/>
+    <col min="50" max="50" customWidth="true" width="16.7181818181818"/>
+    <col min="51" max="51" customWidth="true" width="14.0"/>
+    <col min="52" max="52" customWidth="true" width="19.4272727272727"/>
+    <col min="53" max="53" customWidth="true" width="18.8545454545455"/>
+    <col min="54" max="54" customWidth="true" width="23.2818181818182"/>
+    <col min="55" max="55" customWidth="true" width="15.5727272727273"/>
+    <col min="56" max="56" customWidth="true" width="14.2818181818182"/>
+    <col min="57" max="57" customWidth="true" width="17.0"/>
+    <col min="58" max="58" customWidth="true" width="16.2818181818182"/>
+    <col min="59" max="59" customWidth="true" width="13.5727272727273"/>
+    <col min="60" max="61" customWidth="true" width="12.7181818181818"/>
+    <col min="62" max="62" customWidth="true" width="21.8545454545455"/>
+    <col min="63" max="63" customWidth="true" width="30.5727272727273"/>
+    <col min="64" max="64" customWidth="true" width="10.0"/>
+    <col min="65" max="65" customWidth="true" width="42.5727272727273"/>
+    <col min="66" max="66" customWidth="true" width="38.1454545454545"/>
+    <col min="67" max="67" customWidth="true" width="19.4272727272727"/>
+    <col min="68" max="68" customWidth="true" width="35.4272727272727"/>
+    <col min="69" max="69" customWidth="true" width="9.57272727272727"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -14403,11 +14566,11 @@
       <c r="AT4" s="35" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" t="s">
-        <v>154</v>
-      </c>
-      <c r="AV4" t="s">
-        <v>155</v>
+      <c r="AU4" t="s" s="0">
+        <v>208</v>
+      </c>
+      <c r="AV4" t="s" s="0">
+        <v>209</v>
       </c>
       <c r="AW4" s="35">
         <f>AM4</f>
@@ -14447,11 +14610,11 @@
       <c r="BL4" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="BM4" t="s">
-        <v>150</v>
-      </c>
-      <c r="BN4" t="s">
-        <v>151</v>
+      <c r="BM4" t="s" s="0">
+        <v>211</v>
+      </c>
+      <c r="BN4" t="s" s="0">
+        <v>210</v>
       </c>
       <c r="BO4" s="35">
         <f>ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
@@ -14598,71 +14761,71 @@
   <dimension ref="A1:BQ5"/>
   <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" width="5.14545454545455" customWidth="1"/>
-    <col min="2" max="3" width="27.5727272727273" customWidth="1"/>
-    <col min="4" max="4" width="79.4272727272727" customWidth="1"/>
-    <col min="5" max="5" width="11.5727272727273" customWidth="1"/>
-    <col min="6" max="6" width="5.14545454545455" customWidth="1"/>
-    <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="12.7181818181818" customWidth="1"/>
-    <col min="9" max="9" width="5.85454545454545" customWidth="1"/>
-    <col min="10" max="10" width="6" customWidth="1"/>
-    <col min="11" max="11" width="5.85454545454545" customWidth="1"/>
-    <col min="12" max="12" width="14.2818181818182" customWidth="1"/>
-    <col min="13" max="13" width="9.42727272727273" customWidth="1"/>
-    <col min="14" max="14" width="14.4272727272727" customWidth="1"/>
-    <col min="15" max="15" width="15.5727272727273" customWidth="1"/>
-    <col min="16" max="16" width="14.4272727272727" customWidth="1"/>
-    <col min="17" max="17" width="39.4272727272727" customWidth="1"/>
-    <col min="18" max="18" width="11.7181818181818" customWidth="1"/>
-    <col min="19" max="19" width="11.8545454545455" customWidth="1"/>
-    <col min="20" max="20" width="6.42727272727273" customWidth="1"/>
-    <col min="21" max="22" width="6.57272727272727" customWidth="1"/>
-    <col min="23" max="23" width="37.1454545454545" customWidth="1"/>
-    <col min="24" max="25" width="8" customWidth="1"/>
-    <col min="26" max="26" width="7.71818181818182" customWidth="1"/>
-    <col min="27" max="27" width="6.28181818181818" customWidth="1"/>
-    <col min="28" max="28" width="9.28181818181818" customWidth="1"/>
-    <col min="29" max="29" width="9.71818181818182" customWidth="1"/>
-    <col min="30" max="30" width="12.8545454545455" customWidth="1"/>
-    <col min="31" max="31" width="16.1454545454545" customWidth="1"/>
-    <col min="32" max="32" width="15.4272727272727" customWidth="1"/>
-    <col min="33" max="33" width="24.5727272727273" customWidth="1"/>
-    <col min="34" max="34" width="8.57272727272727" customWidth="1"/>
-    <col min="35" max="35" width="14.7181818181818" customWidth="1"/>
-    <col min="36" max="36" width="18.5727272727273" customWidth="1"/>
-    <col min="37" max="37" width="14.1454545454545" customWidth="1"/>
-    <col min="38" max="38" width="14.7181818181818" customWidth="1"/>
-    <col min="39" max="39" width="17.4272727272727" customWidth="1"/>
-    <col min="40" max="40" width="22" customWidth="1"/>
-    <col min="41" max="41" width="17.5727272727273" customWidth="1"/>
-    <col min="42" max="42" width="25.2818181818182" customWidth="1"/>
-    <col min="43" max="43" width="13" customWidth="1"/>
-    <col min="44" max="44" width="23.7181818181818" customWidth="1"/>
-    <col min="45" max="45" width="10" customWidth="1"/>
-    <col min="46" max="46" width="13" customWidth="1"/>
-    <col min="47" max="47" width="15.5727272727273" customWidth="1"/>
-    <col min="48" max="48" width="21.1454545454545" customWidth="1"/>
-    <col min="49" max="49" width="11.5727272727273" customWidth="1"/>
-    <col min="50" max="50" width="16.7181818181818" customWidth="1"/>
-    <col min="51" max="51" width="14" customWidth="1"/>
-    <col min="52" max="52" width="19.4272727272727" customWidth="1"/>
-    <col min="53" max="53" width="18.8545454545455" customWidth="1"/>
-    <col min="54" max="54" width="23.2818181818182" customWidth="1"/>
-    <col min="55" max="55" width="15.5727272727273" customWidth="1"/>
-    <col min="56" max="56" width="14.2818181818182" customWidth="1"/>
-    <col min="57" max="57" width="17" customWidth="1"/>
-    <col min="58" max="58" width="16.2818181818182" customWidth="1"/>
-    <col min="59" max="59" width="13.5727272727273" customWidth="1"/>
-    <col min="60" max="61" width="12.7181818181818" customWidth="1"/>
-    <col min="62" max="62" width="21.8545454545455" customWidth="1"/>
-    <col min="63" max="63" width="30.5727272727273" customWidth="1"/>
-    <col min="64" max="64" width="10" customWidth="1"/>
-    <col min="65" max="65" width="42.5727272727273" customWidth="1"/>
-    <col min="66" max="66" width="38.1454545454545" customWidth="1"/>
-    <col min="67" max="67" width="19.4272727272727" customWidth="1"/>
-    <col min="68" max="68" width="35.4272727272727" customWidth="1"/>
-    <col min="69" max="69" width="9.57272727272727" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="5.14545454545455"/>
+    <col min="2" max="3" customWidth="true" width="27.5727272727273"/>
+    <col min="4" max="4" customWidth="true" width="79.4272727272727"/>
+    <col min="5" max="5" customWidth="true" width="11.5727272727273"/>
+    <col min="6" max="6" customWidth="true" width="5.14545454545455"/>
+    <col min="7" max="7" customWidth="true" width="11.0"/>
+    <col min="8" max="8" customWidth="true" width="12.7181818181818"/>
+    <col min="9" max="9" customWidth="true" width="5.85454545454545"/>
+    <col min="10" max="10" customWidth="true" width="6.0"/>
+    <col min="11" max="11" customWidth="true" width="5.85454545454545"/>
+    <col min="12" max="12" customWidth="true" width="14.2818181818182"/>
+    <col min="13" max="13" customWidth="true" width="9.42727272727273"/>
+    <col min="14" max="14" customWidth="true" width="14.4272727272727"/>
+    <col min="15" max="15" customWidth="true" width="15.5727272727273"/>
+    <col min="16" max="16" customWidth="true" width="14.4272727272727"/>
+    <col min="17" max="17" customWidth="true" width="39.4272727272727"/>
+    <col min="18" max="18" customWidth="true" width="11.7181818181818"/>
+    <col min="19" max="19" customWidth="true" width="11.8545454545455"/>
+    <col min="20" max="20" customWidth="true" width="6.42727272727273"/>
+    <col min="21" max="22" customWidth="true" width="6.57272727272727"/>
+    <col min="23" max="23" customWidth="true" width="37.1454545454545"/>
+    <col min="24" max="25" customWidth="true" width="8.0"/>
+    <col min="26" max="26" customWidth="true" width="7.71818181818182"/>
+    <col min="27" max="27" customWidth="true" width="6.28181818181818"/>
+    <col min="28" max="28" customWidth="true" width="9.28181818181818"/>
+    <col min="29" max="29" customWidth="true" width="9.71818181818182"/>
+    <col min="30" max="30" customWidth="true" width="12.8545454545455"/>
+    <col min="31" max="31" customWidth="true" width="16.1454545454545"/>
+    <col min="32" max="32" customWidth="true" width="15.4272727272727"/>
+    <col min="33" max="33" customWidth="true" width="24.5727272727273"/>
+    <col min="34" max="34" customWidth="true" width="8.57272727272727"/>
+    <col min="35" max="35" customWidth="true" width="14.7181818181818"/>
+    <col min="36" max="36" customWidth="true" width="18.5727272727273"/>
+    <col min="37" max="37" customWidth="true" width="14.1454545454545"/>
+    <col min="38" max="38" customWidth="true" width="14.7181818181818"/>
+    <col min="39" max="39" customWidth="true" width="17.4272727272727"/>
+    <col min="40" max="40" customWidth="true" width="22.0"/>
+    <col min="41" max="41" customWidth="true" width="17.5727272727273"/>
+    <col min="42" max="42" customWidth="true" width="25.2818181818182"/>
+    <col min="43" max="43" customWidth="true" width="13.0"/>
+    <col min="44" max="44" customWidth="true" width="23.7181818181818"/>
+    <col min="45" max="45" customWidth="true" width="10.0"/>
+    <col min="46" max="46" customWidth="true" width="13.0"/>
+    <col min="47" max="47" customWidth="true" width="15.5727272727273"/>
+    <col min="48" max="48" customWidth="true" width="21.1454545454545"/>
+    <col min="49" max="49" customWidth="true" width="11.5727272727273"/>
+    <col min="50" max="50" customWidth="true" width="16.7181818181818"/>
+    <col min="51" max="51" customWidth="true" width="14.0"/>
+    <col min="52" max="52" customWidth="true" width="19.4272727272727"/>
+    <col min="53" max="53" customWidth="true" width="18.8545454545455"/>
+    <col min="54" max="54" customWidth="true" width="23.2818181818182"/>
+    <col min="55" max="55" customWidth="true" width="15.5727272727273"/>
+    <col min="56" max="56" customWidth="true" width="14.2818181818182"/>
+    <col min="57" max="57" customWidth="true" width="17.0"/>
+    <col min="58" max="58" customWidth="true" width="16.2818181818182"/>
+    <col min="59" max="59" customWidth="true" width="13.5727272727273"/>
+    <col min="60" max="61" customWidth="true" width="12.7181818181818"/>
+    <col min="62" max="62" customWidth="true" width="21.8545454545455"/>
+    <col min="63" max="63" customWidth="true" width="30.5727272727273"/>
+    <col min="64" max="64" customWidth="true" width="10.0"/>
+    <col min="65" max="65" customWidth="true" width="42.5727272727273"/>
+    <col min="66" max="66" customWidth="true" width="38.1454545454545"/>
+    <col min="67" max="67" customWidth="true" width="19.4272727272727"/>
+    <col min="68" max="68" customWidth="true" width="35.4272727272727"/>
+    <col min="69" max="69" customWidth="true" width="9.57272727272727"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -15206,11 +15369,11 @@
       <c r="AT4" s="35" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" t="s">
-        <v>157</v>
-      </c>
-      <c r="AV4" t="s">
-        <v>158</v>
+      <c r="AU4" t="s" s="0">
+        <v>212</v>
+      </c>
+      <c r="AV4" t="s" s="0">
+        <v>213</v>
       </c>
       <c r="AW4" s="35">
         <f>AM4</f>
@@ -15250,11 +15413,11 @@
       <c r="BL4" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="BM4" t="s">
-        <v>159</v>
-      </c>
-      <c r="BN4" t="s">
-        <v>160</v>
+      <c r="BM4" t="s" s="0">
+        <v>215</v>
+      </c>
+      <c r="BN4" t="s" s="0">
+        <v>214</v>
       </c>
       <c r="BO4" s="35">
         <f>ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
@@ -15413,71 +15576,71 @@
   <dimension ref="A1:BQ5"/>
   <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" width="5.14545454545455" customWidth="1"/>
-    <col min="2" max="3" width="27.5727272727273" customWidth="1"/>
-    <col min="4" max="4" width="79.4272727272727" customWidth="1"/>
-    <col min="5" max="5" width="11.5727272727273" customWidth="1"/>
-    <col min="6" max="6" width="5.14545454545455" customWidth="1"/>
-    <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="12.7181818181818" customWidth="1"/>
-    <col min="9" max="9" width="5.85454545454545" customWidth="1"/>
-    <col min="10" max="10" width="6" customWidth="1"/>
-    <col min="11" max="11" width="5.85454545454545" customWidth="1"/>
-    <col min="12" max="12" width="14.2818181818182" customWidth="1"/>
-    <col min="13" max="13" width="9.42727272727273" customWidth="1"/>
-    <col min="14" max="14" width="14.4272727272727" customWidth="1"/>
-    <col min="15" max="15" width="15.5727272727273" customWidth="1"/>
-    <col min="16" max="16" width="14.4272727272727" customWidth="1"/>
-    <col min="17" max="17" width="39.4272727272727" customWidth="1"/>
-    <col min="18" max="18" width="11.7181818181818" customWidth="1"/>
-    <col min="19" max="19" width="11.8545454545455" customWidth="1"/>
-    <col min="20" max="20" width="6.42727272727273" customWidth="1"/>
-    <col min="21" max="22" width="6.57272727272727" customWidth="1"/>
-    <col min="23" max="23" width="37.1454545454545" customWidth="1"/>
-    <col min="24" max="25" width="8" customWidth="1"/>
-    <col min="26" max="26" width="7.71818181818182" customWidth="1"/>
-    <col min="27" max="27" width="6.28181818181818" customWidth="1"/>
-    <col min="28" max="28" width="9.28181818181818" customWidth="1"/>
-    <col min="29" max="29" width="9.71818181818182" customWidth="1"/>
-    <col min="30" max="30" width="12.8545454545455" customWidth="1"/>
-    <col min="31" max="31" width="16.1454545454545" customWidth="1"/>
-    <col min="32" max="32" width="15.4272727272727" customWidth="1"/>
-    <col min="33" max="33" width="24.5727272727273" customWidth="1"/>
-    <col min="34" max="34" width="8.57272727272727" customWidth="1"/>
-    <col min="35" max="35" width="14.7181818181818" customWidth="1"/>
-    <col min="36" max="36" width="18.5727272727273" customWidth="1"/>
-    <col min="37" max="37" width="14.1454545454545" customWidth="1"/>
-    <col min="38" max="38" width="14.7181818181818" customWidth="1"/>
-    <col min="39" max="39" width="17.4272727272727" customWidth="1"/>
-    <col min="40" max="40" width="22" customWidth="1"/>
-    <col min="41" max="41" width="17.5727272727273" customWidth="1"/>
-    <col min="42" max="42" width="25.2818181818182" customWidth="1"/>
-    <col min="43" max="43" width="13" customWidth="1"/>
-    <col min="44" max="44" width="23.7181818181818" customWidth="1"/>
-    <col min="45" max="45" width="10" customWidth="1"/>
-    <col min="46" max="46" width="13" customWidth="1"/>
-    <col min="47" max="47" width="15.5727272727273" customWidth="1"/>
-    <col min="48" max="48" width="21.1454545454545" customWidth="1"/>
-    <col min="49" max="49" width="11.5727272727273" customWidth="1"/>
-    <col min="50" max="50" width="16.7181818181818" customWidth="1"/>
-    <col min="51" max="51" width="14" customWidth="1"/>
-    <col min="52" max="52" width="19.4272727272727" customWidth="1"/>
-    <col min="53" max="53" width="18.8545454545455" customWidth="1"/>
-    <col min="54" max="54" width="23.2818181818182" customWidth="1"/>
-    <col min="55" max="55" width="15.5727272727273" customWidth="1"/>
-    <col min="56" max="56" width="14.2818181818182" customWidth="1"/>
-    <col min="57" max="57" width="17" customWidth="1"/>
-    <col min="58" max="58" width="16.2818181818182" customWidth="1"/>
-    <col min="59" max="59" width="13.5727272727273" customWidth="1"/>
-    <col min="60" max="61" width="12.7181818181818" customWidth="1"/>
-    <col min="62" max="62" width="21.8545454545455" customWidth="1"/>
-    <col min="63" max="63" width="30.5727272727273" customWidth="1"/>
-    <col min="64" max="64" width="10" customWidth="1"/>
-    <col min="65" max="65" width="42.5727272727273" customWidth="1"/>
-    <col min="66" max="66" width="38.1454545454545" customWidth="1"/>
-    <col min="67" max="67" width="19.4272727272727" customWidth="1"/>
-    <col min="68" max="68" width="35.4272727272727" customWidth="1"/>
-    <col min="69" max="69" width="9.57272727272727" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="5.14545454545455"/>
+    <col min="2" max="3" customWidth="true" width="27.5727272727273"/>
+    <col min="4" max="4" customWidth="true" width="79.4272727272727"/>
+    <col min="5" max="5" customWidth="true" width="11.5727272727273"/>
+    <col min="6" max="6" customWidth="true" width="5.14545454545455"/>
+    <col min="7" max="7" customWidth="true" width="11.0"/>
+    <col min="8" max="8" customWidth="true" width="12.7181818181818"/>
+    <col min="9" max="9" customWidth="true" width="5.85454545454545"/>
+    <col min="10" max="10" customWidth="true" width="6.0"/>
+    <col min="11" max="11" customWidth="true" width="5.85454545454545"/>
+    <col min="12" max="12" customWidth="true" width="14.2818181818182"/>
+    <col min="13" max="13" customWidth="true" width="9.42727272727273"/>
+    <col min="14" max="14" customWidth="true" width="14.4272727272727"/>
+    <col min="15" max="15" customWidth="true" width="15.5727272727273"/>
+    <col min="16" max="16" customWidth="true" width="14.4272727272727"/>
+    <col min="17" max="17" customWidth="true" width="39.4272727272727"/>
+    <col min="18" max="18" customWidth="true" width="11.7181818181818"/>
+    <col min="19" max="19" customWidth="true" width="11.8545454545455"/>
+    <col min="20" max="20" customWidth="true" width="6.42727272727273"/>
+    <col min="21" max="22" customWidth="true" width="6.57272727272727"/>
+    <col min="23" max="23" customWidth="true" width="37.1454545454545"/>
+    <col min="24" max="25" customWidth="true" width="8.0"/>
+    <col min="26" max="26" customWidth="true" width="7.71818181818182"/>
+    <col min="27" max="27" customWidth="true" width="6.28181818181818"/>
+    <col min="28" max="28" customWidth="true" width="9.28181818181818"/>
+    <col min="29" max="29" customWidth="true" width="9.71818181818182"/>
+    <col min="30" max="30" customWidth="true" width="12.8545454545455"/>
+    <col min="31" max="31" customWidth="true" width="16.1454545454545"/>
+    <col min="32" max="32" customWidth="true" width="15.4272727272727"/>
+    <col min="33" max="33" customWidth="true" width="24.5727272727273"/>
+    <col min="34" max="34" customWidth="true" width="8.57272727272727"/>
+    <col min="35" max="35" customWidth="true" width="14.7181818181818"/>
+    <col min="36" max="36" customWidth="true" width="18.5727272727273"/>
+    <col min="37" max="37" customWidth="true" width="14.1454545454545"/>
+    <col min="38" max="38" customWidth="true" width="14.7181818181818"/>
+    <col min="39" max="39" customWidth="true" width="17.4272727272727"/>
+    <col min="40" max="40" customWidth="true" width="22.0"/>
+    <col min="41" max="41" customWidth="true" width="17.5727272727273"/>
+    <col min="42" max="42" customWidth="true" width="25.2818181818182"/>
+    <col min="43" max="43" customWidth="true" width="13.0"/>
+    <col min="44" max="44" customWidth="true" width="23.7181818181818"/>
+    <col min="45" max="45" customWidth="true" width="10.0"/>
+    <col min="46" max="46" customWidth="true" width="13.0"/>
+    <col min="47" max="47" customWidth="true" width="15.5727272727273"/>
+    <col min="48" max="48" customWidth="true" width="21.1454545454545"/>
+    <col min="49" max="49" customWidth="true" width="11.5727272727273"/>
+    <col min="50" max="50" customWidth="true" width="16.7181818181818"/>
+    <col min="51" max="51" customWidth="true" width="14.0"/>
+    <col min="52" max="52" customWidth="true" width="19.4272727272727"/>
+    <col min="53" max="53" customWidth="true" width="18.8545454545455"/>
+    <col min="54" max="54" customWidth="true" width="23.2818181818182"/>
+    <col min="55" max="55" customWidth="true" width="15.5727272727273"/>
+    <col min="56" max="56" customWidth="true" width="14.2818181818182"/>
+    <col min="57" max="57" customWidth="true" width="17.0"/>
+    <col min="58" max="58" customWidth="true" width="16.2818181818182"/>
+    <col min="59" max="59" customWidth="true" width="13.5727272727273"/>
+    <col min="60" max="61" customWidth="true" width="12.7181818181818"/>
+    <col min="62" max="62" customWidth="true" width="21.8545454545455"/>
+    <col min="63" max="63" customWidth="true" width="30.5727272727273"/>
+    <col min="64" max="64" customWidth="true" width="10.0"/>
+    <col min="65" max="65" customWidth="true" width="42.5727272727273"/>
+    <col min="66" max="66" customWidth="true" width="38.1454545454545"/>
+    <col min="67" max="67" customWidth="true" width="19.4272727272727"/>
+    <col min="68" max="68" customWidth="true" width="35.4272727272727"/>
+    <col min="69" max="69" customWidth="true" width="9.57272727272727"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -16021,11 +16184,11 @@
       <c r="AT4" s="35" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" t="s">
-        <v>162</v>
-      </c>
-      <c r="AV4" t="s">
-        <v>163</v>
+      <c r="AU4" t="s" s="0">
+        <v>216</v>
+      </c>
+      <c r="AV4" t="s" s="0">
+        <v>217</v>
       </c>
       <c r="AW4" s="35">
         <f>AM4</f>
@@ -16065,11 +16228,11 @@
       <c r="BL4" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="BM4" t="s">
-        <v>164</v>
-      </c>
-      <c r="BN4" t="s">
-        <v>165</v>
+      <c r="BM4" t="s" s="0">
+        <v>219</v>
+      </c>
+      <c r="BN4" t="s" s="0">
+        <v>218</v>
       </c>
       <c r="BO4" s="35">
         <f>ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
@@ -16228,71 +16391,71 @@
   <dimension ref="A1:BQ5"/>
   <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" width="5.14545454545455" customWidth="1"/>
-    <col min="2" max="3" width="27.5727272727273" customWidth="1"/>
-    <col min="4" max="4" width="79.4272727272727" customWidth="1"/>
-    <col min="5" max="5" width="11.5727272727273" customWidth="1"/>
-    <col min="6" max="6" width="5.14545454545455" customWidth="1"/>
-    <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="12.7181818181818" customWidth="1"/>
-    <col min="9" max="9" width="5.85454545454545" customWidth="1"/>
-    <col min="10" max="10" width="6" customWidth="1"/>
-    <col min="11" max="11" width="5.85454545454545" customWidth="1"/>
-    <col min="12" max="12" width="14.2818181818182" customWidth="1"/>
-    <col min="13" max="13" width="9.42727272727273" customWidth="1"/>
-    <col min="14" max="14" width="14.4272727272727" customWidth="1"/>
-    <col min="15" max="15" width="15.5727272727273" customWidth="1"/>
-    <col min="16" max="16" width="14.4272727272727" customWidth="1"/>
-    <col min="17" max="17" width="39.4272727272727" customWidth="1"/>
-    <col min="18" max="18" width="11.7181818181818" customWidth="1"/>
-    <col min="19" max="19" width="11.8545454545455" customWidth="1"/>
-    <col min="20" max="20" width="6.42727272727273" customWidth="1"/>
-    <col min="21" max="22" width="6.57272727272727" customWidth="1"/>
-    <col min="23" max="23" width="37.1454545454545" customWidth="1"/>
-    <col min="24" max="25" width="8" customWidth="1"/>
-    <col min="26" max="26" width="7.71818181818182" customWidth="1"/>
-    <col min="27" max="27" width="6.28181818181818" customWidth="1"/>
-    <col min="28" max="28" width="9.28181818181818" customWidth="1"/>
-    <col min="29" max="29" width="9.71818181818182" customWidth="1"/>
-    <col min="30" max="30" width="12.8545454545455" customWidth="1"/>
-    <col min="31" max="31" width="16.1454545454545" customWidth="1"/>
-    <col min="32" max="32" width="15.4272727272727" customWidth="1"/>
-    <col min="33" max="33" width="24.5727272727273" customWidth="1"/>
-    <col min="34" max="34" width="8.57272727272727" customWidth="1"/>
-    <col min="35" max="35" width="14.7181818181818" customWidth="1"/>
-    <col min="36" max="36" width="18.5727272727273" customWidth="1"/>
-    <col min="37" max="37" width="14.1454545454545" customWidth="1"/>
-    <col min="38" max="38" width="14.7181818181818" customWidth="1"/>
-    <col min="39" max="39" width="17.4272727272727" customWidth="1"/>
-    <col min="40" max="40" width="22" customWidth="1"/>
-    <col min="41" max="41" width="17.5727272727273" customWidth="1"/>
-    <col min="42" max="42" width="25.2818181818182" customWidth="1"/>
-    <col min="43" max="43" width="13" customWidth="1"/>
-    <col min="44" max="44" width="23.7181818181818" customWidth="1"/>
-    <col min="45" max="45" width="10" customWidth="1"/>
-    <col min="46" max="46" width="13" customWidth="1"/>
-    <col min="47" max="47" width="15.5727272727273" customWidth="1"/>
-    <col min="48" max="48" width="21.1454545454545" customWidth="1"/>
-    <col min="49" max="49" width="11.5727272727273" customWidth="1"/>
-    <col min="50" max="50" width="16.7181818181818" customWidth="1"/>
-    <col min="51" max="51" width="14" customWidth="1"/>
-    <col min="52" max="52" width="19.4272727272727" customWidth="1"/>
-    <col min="53" max="53" width="18.8545454545455" customWidth="1"/>
-    <col min="54" max="54" width="23.2818181818182" customWidth="1"/>
-    <col min="55" max="55" width="15.5727272727273" customWidth="1"/>
-    <col min="56" max="56" width="14.2818181818182" customWidth="1"/>
-    <col min="57" max="57" width="17" customWidth="1"/>
-    <col min="58" max="58" width="16.2818181818182" customWidth="1"/>
-    <col min="59" max="59" width="13.5727272727273" customWidth="1"/>
-    <col min="60" max="61" width="12.7181818181818" customWidth="1"/>
-    <col min="62" max="62" width="21.8545454545455" customWidth="1"/>
-    <col min="63" max="63" width="30.5727272727273" customWidth="1"/>
-    <col min="64" max="64" width="10" customWidth="1"/>
-    <col min="65" max="65" width="42.5727272727273" customWidth="1"/>
-    <col min="66" max="66" width="38.1454545454545" customWidth="1"/>
-    <col min="67" max="67" width="19.4272727272727" customWidth="1"/>
-    <col min="68" max="68" width="35.4272727272727" customWidth="1"/>
-    <col min="69" max="69" width="9.57272727272727" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="5.14545454545455"/>
+    <col min="2" max="3" customWidth="true" width="27.5727272727273"/>
+    <col min="4" max="4" customWidth="true" width="79.4272727272727"/>
+    <col min="5" max="5" customWidth="true" width="11.5727272727273"/>
+    <col min="6" max="6" customWidth="true" width="5.14545454545455"/>
+    <col min="7" max="7" customWidth="true" width="11.0"/>
+    <col min="8" max="8" customWidth="true" width="12.7181818181818"/>
+    <col min="9" max="9" customWidth="true" width="5.85454545454545"/>
+    <col min="10" max="10" customWidth="true" width="6.0"/>
+    <col min="11" max="11" customWidth="true" width="5.85454545454545"/>
+    <col min="12" max="12" customWidth="true" width="14.2818181818182"/>
+    <col min="13" max="13" customWidth="true" width="9.42727272727273"/>
+    <col min="14" max="14" customWidth="true" width="14.4272727272727"/>
+    <col min="15" max="15" customWidth="true" width="15.5727272727273"/>
+    <col min="16" max="16" customWidth="true" width="14.4272727272727"/>
+    <col min="17" max="17" customWidth="true" width="39.4272727272727"/>
+    <col min="18" max="18" customWidth="true" width="11.7181818181818"/>
+    <col min="19" max="19" customWidth="true" width="11.8545454545455"/>
+    <col min="20" max="20" customWidth="true" width="6.42727272727273"/>
+    <col min="21" max="22" customWidth="true" width="6.57272727272727"/>
+    <col min="23" max="23" customWidth="true" width="37.1454545454545"/>
+    <col min="24" max="25" customWidth="true" width="8.0"/>
+    <col min="26" max="26" customWidth="true" width="7.71818181818182"/>
+    <col min="27" max="27" customWidth="true" width="6.28181818181818"/>
+    <col min="28" max="28" customWidth="true" width="9.28181818181818"/>
+    <col min="29" max="29" customWidth="true" width="9.71818181818182"/>
+    <col min="30" max="30" customWidth="true" width="12.8545454545455"/>
+    <col min="31" max="31" customWidth="true" width="16.1454545454545"/>
+    <col min="32" max="32" customWidth="true" width="15.4272727272727"/>
+    <col min="33" max="33" customWidth="true" width="24.5727272727273"/>
+    <col min="34" max="34" customWidth="true" width="8.57272727272727"/>
+    <col min="35" max="35" customWidth="true" width="14.7181818181818"/>
+    <col min="36" max="36" customWidth="true" width="18.5727272727273"/>
+    <col min="37" max="37" customWidth="true" width="14.1454545454545"/>
+    <col min="38" max="38" customWidth="true" width="14.7181818181818"/>
+    <col min="39" max="39" customWidth="true" width="17.4272727272727"/>
+    <col min="40" max="40" customWidth="true" width="22.0"/>
+    <col min="41" max="41" customWidth="true" width="17.5727272727273"/>
+    <col min="42" max="42" customWidth="true" width="25.2818181818182"/>
+    <col min="43" max="43" customWidth="true" width="13.0"/>
+    <col min="44" max="44" customWidth="true" width="23.7181818181818"/>
+    <col min="45" max="45" customWidth="true" width="10.0"/>
+    <col min="46" max="46" customWidth="true" width="13.0"/>
+    <col min="47" max="47" customWidth="true" width="15.5727272727273"/>
+    <col min="48" max="48" customWidth="true" width="21.1454545454545"/>
+    <col min="49" max="49" customWidth="true" width="11.5727272727273"/>
+    <col min="50" max="50" customWidth="true" width="16.7181818181818"/>
+    <col min="51" max="51" customWidth="true" width="14.0"/>
+    <col min="52" max="52" customWidth="true" width="19.4272727272727"/>
+    <col min="53" max="53" customWidth="true" width="18.8545454545455"/>
+    <col min="54" max="54" customWidth="true" width="23.2818181818182"/>
+    <col min="55" max="55" customWidth="true" width="15.5727272727273"/>
+    <col min="56" max="56" customWidth="true" width="14.2818181818182"/>
+    <col min="57" max="57" customWidth="true" width="17.0"/>
+    <col min="58" max="58" customWidth="true" width="16.2818181818182"/>
+    <col min="59" max="59" customWidth="true" width="13.5727272727273"/>
+    <col min="60" max="61" customWidth="true" width="12.7181818181818"/>
+    <col min="62" max="62" customWidth="true" width="21.8545454545455"/>
+    <col min="63" max="63" customWidth="true" width="30.5727272727273"/>
+    <col min="64" max="64" customWidth="true" width="10.0"/>
+    <col min="65" max="65" customWidth="true" width="42.5727272727273"/>
+    <col min="66" max="66" customWidth="true" width="38.1454545454545"/>
+    <col min="67" max="67" customWidth="true" width="19.4272727272727"/>
+    <col min="68" max="68" customWidth="true" width="35.4272727272727"/>
+    <col min="69" max="69" customWidth="true" width="9.57272727272727"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -16836,11 +16999,11 @@
       <c r="AT4" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" t="s">
-        <v>166</v>
-      </c>
-      <c r="AV4" t="s">
-        <v>167</v>
+      <c r="AU4" t="s" s="0">
+        <v>212</v>
+      </c>
+      <c r="AV4" t="s" s="0">
+        <v>213</v>
       </c>
       <c r="AW4" s="16">
         <f>AM4</f>
@@ -16880,11 +17043,11 @@
       <c r="BL4" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="BM4" t="s">
-        <v>159</v>
-      </c>
-      <c r="BN4" t="s">
-        <v>160</v>
+      <c r="BM4" t="s" s="0">
+        <v>215</v>
+      </c>
+      <c r="BN4" t="s" s="0">
+        <v>214</v>
       </c>
       <c r="BO4" s="16">
         <f>ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
@@ -17031,71 +17194,71 @@
   <dimension ref="A1:BQ5"/>
   <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" width="5.14545454545455" customWidth="1"/>
-    <col min="2" max="3" width="27.5727272727273" customWidth="1"/>
-    <col min="4" max="4" width="79.4272727272727" customWidth="1"/>
-    <col min="5" max="5" width="11.5727272727273" customWidth="1"/>
-    <col min="6" max="6" width="5.14545454545455" customWidth="1"/>
-    <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="12.7181818181818" customWidth="1"/>
-    <col min="9" max="9" width="5.85454545454545" customWidth="1"/>
-    <col min="10" max="10" width="6" customWidth="1"/>
-    <col min="11" max="11" width="5.85454545454545" customWidth="1"/>
-    <col min="12" max="12" width="14.2818181818182" customWidth="1"/>
-    <col min="13" max="13" width="9.42727272727273" customWidth="1"/>
-    <col min="14" max="14" width="14.4272727272727" customWidth="1"/>
-    <col min="15" max="15" width="15.5727272727273" customWidth="1"/>
-    <col min="16" max="16" width="14.4272727272727" customWidth="1"/>
-    <col min="17" max="17" width="39.4272727272727" customWidth="1"/>
-    <col min="18" max="18" width="11.7181818181818" customWidth="1"/>
-    <col min="19" max="19" width="11.8545454545455" customWidth="1"/>
-    <col min="20" max="20" width="6.42727272727273" customWidth="1"/>
-    <col min="21" max="22" width="6.57272727272727" customWidth="1"/>
-    <col min="23" max="23" width="37.1454545454545" customWidth="1"/>
-    <col min="24" max="25" width="8" customWidth="1"/>
-    <col min="26" max="26" width="7.71818181818182" customWidth="1"/>
-    <col min="27" max="27" width="6.28181818181818" customWidth="1"/>
-    <col min="28" max="28" width="9.28181818181818" customWidth="1"/>
-    <col min="29" max="29" width="9.71818181818182" customWidth="1"/>
-    <col min="30" max="30" width="12.8545454545455" customWidth="1"/>
-    <col min="31" max="31" width="16.1454545454545" customWidth="1"/>
-    <col min="32" max="32" width="15.4272727272727" customWidth="1"/>
-    <col min="33" max="33" width="24.5727272727273" customWidth="1"/>
-    <col min="34" max="34" width="8.57272727272727" customWidth="1"/>
-    <col min="35" max="35" width="14.7181818181818" customWidth="1"/>
-    <col min="36" max="36" width="18.5727272727273" customWidth="1"/>
-    <col min="37" max="37" width="14.1454545454545" customWidth="1"/>
-    <col min="38" max="38" width="14.7181818181818" customWidth="1"/>
-    <col min="39" max="39" width="17.4272727272727" customWidth="1"/>
-    <col min="40" max="40" width="22" customWidth="1"/>
-    <col min="41" max="41" width="17.5727272727273" customWidth="1"/>
-    <col min="42" max="42" width="25.2818181818182" customWidth="1"/>
-    <col min="43" max="43" width="13" customWidth="1"/>
-    <col min="44" max="44" width="23.7181818181818" customWidth="1"/>
-    <col min="45" max="45" width="10" customWidth="1"/>
-    <col min="46" max="46" width="13" customWidth="1"/>
-    <col min="47" max="47" width="15.5727272727273" customWidth="1"/>
-    <col min="48" max="48" width="21.1454545454545" customWidth="1"/>
-    <col min="49" max="49" width="11.5727272727273" customWidth="1"/>
-    <col min="50" max="50" width="16.7181818181818" customWidth="1"/>
-    <col min="51" max="51" width="14" customWidth="1"/>
-    <col min="52" max="52" width="19.4272727272727" customWidth="1"/>
-    <col min="53" max="53" width="18.8545454545455" customWidth="1"/>
-    <col min="54" max="54" width="23.2818181818182" customWidth="1"/>
-    <col min="55" max="55" width="15.5727272727273" customWidth="1"/>
-    <col min="56" max="56" width="14.2818181818182" customWidth="1"/>
-    <col min="57" max="57" width="17" customWidth="1"/>
-    <col min="58" max="58" width="16.2818181818182" customWidth="1"/>
-    <col min="59" max="59" width="13.5727272727273" customWidth="1"/>
-    <col min="60" max="61" width="12.7181818181818" customWidth="1"/>
-    <col min="62" max="62" width="21.8545454545455" customWidth="1"/>
-    <col min="63" max="63" width="30.5727272727273" customWidth="1"/>
-    <col min="64" max="64" width="10" customWidth="1"/>
-    <col min="65" max="65" width="42.5727272727273" customWidth="1"/>
-    <col min="66" max="66" width="38.1454545454545" customWidth="1"/>
-    <col min="67" max="67" width="19.4272727272727" customWidth="1"/>
-    <col min="68" max="68" width="35.4272727272727" customWidth="1"/>
-    <col min="69" max="69" width="9.57272727272727" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="5.14545454545455"/>
+    <col min="2" max="3" customWidth="true" width="27.5727272727273"/>
+    <col min="4" max="4" customWidth="true" width="79.4272727272727"/>
+    <col min="5" max="5" customWidth="true" width="11.5727272727273"/>
+    <col min="6" max="6" customWidth="true" width="5.14545454545455"/>
+    <col min="7" max="7" customWidth="true" width="11.0"/>
+    <col min="8" max="8" customWidth="true" width="12.7181818181818"/>
+    <col min="9" max="9" customWidth="true" width="5.85454545454545"/>
+    <col min="10" max="10" customWidth="true" width="6.0"/>
+    <col min="11" max="11" customWidth="true" width="5.85454545454545"/>
+    <col min="12" max="12" customWidth="true" width="14.2818181818182"/>
+    <col min="13" max="13" customWidth="true" width="9.42727272727273"/>
+    <col min="14" max="14" customWidth="true" width="14.4272727272727"/>
+    <col min="15" max="15" customWidth="true" width="15.5727272727273"/>
+    <col min="16" max="16" customWidth="true" width="14.4272727272727"/>
+    <col min="17" max="17" customWidth="true" width="39.4272727272727"/>
+    <col min="18" max="18" customWidth="true" width="11.7181818181818"/>
+    <col min="19" max="19" customWidth="true" width="11.8545454545455"/>
+    <col min="20" max="20" customWidth="true" width="6.42727272727273"/>
+    <col min="21" max="22" customWidth="true" width="6.57272727272727"/>
+    <col min="23" max="23" customWidth="true" width="37.1454545454545"/>
+    <col min="24" max="25" customWidth="true" width="8.0"/>
+    <col min="26" max="26" customWidth="true" width="7.71818181818182"/>
+    <col min="27" max="27" customWidth="true" width="6.28181818181818"/>
+    <col min="28" max="28" customWidth="true" width="9.28181818181818"/>
+    <col min="29" max="29" customWidth="true" width="9.71818181818182"/>
+    <col min="30" max="30" customWidth="true" width="12.8545454545455"/>
+    <col min="31" max="31" customWidth="true" width="16.1454545454545"/>
+    <col min="32" max="32" customWidth="true" width="15.4272727272727"/>
+    <col min="33" max="33" customWidth="true" width="24.5727272727273"/>
+    <col min="34" max="34" customWidth="true" width="8.57272727272727"/>
+    <col min="35" max="35" customWidth="true" width="14.7181818181818"/>
+    <col min="36" max="36" customWidth="true" width="18.5727272727273"/>
+    <col min="37" max="37" customWidth="true" width="14.1454545454545"/>
+    <col min="38" max="38" customWidth="true" width="14.7181818181818"/>
+    <col min="39" max="39" customWidth="true" width="17.4272727272727"/>
+    <col min="40" max="40" customWidth="true" width="22.0"/>
+    <col min="41" max="41" customWidth="true" width="17.5727272727273"/>
+    <col min="42" max="42" customWidth="true" width="25.2818181818182"/>
+    <col min="43" max="43" customWidth="true" width="13.0"/>
+    <col min="44" max="44" customWidth="true" width="23.7181818181818"/>
+    <col min="45" max="45" customWidth="true" width="10.0"/>
+    <col min="46" max="46" customWidth="true" width="13.0"/>
+    <col min="47" max="47" customWidth="true" width="15.5727272727273"/>
+    <col min="48" max="48" customWidth="true" width="21.1454545454545"/>
+    <col min="49" max="49" customWidth="true" width="11.5727272727273"/>
+    <col min="50" max="50" customWidth="true" width="16.7181818181818"/>
+    <col min="51" max="51" customWidth="true" width="14.0"/>
+    <col min="52" max="52" customWidth="true" width="19.4272727272727"/>
+    <col min="53" max="53" customWidth="true" width="18.8545454545455"/>
+    <col min="54" max="54" customWidth="true" width="23.2818181818182"/>
+    <col min="55" max="55" customWidth="true" width="15.5727272727273"/>
+    <col min="56" max="56" customWidth="true" width="14.2818181818182"/>
+    <col min="57" max="57" customWidth="true" width="17.0"/>
+    <col min="58" max="58" customWidth="true" width="16.2818181818182"/>
+    <col min="59" max="59" customWidth="true" width="13.5727272727273"/>
+    <col min="60" max="61" customWidth="true" width="12.7181818181818"/>
+    <col min="62" max="62" customWidth="true" width="21.8545454545455"/>
+    <col min="63" max="63" customWidth="true" width="30.5727272727273"/>
+    <col min="64" max="64" customWidth="true" width="10.0"/>
+    <col min="65" max="65" customWidth="true" width="42.5727272727273"/>
+    <col min="66" max="66" customWidth="true" width="38.1454545454545"/>
+    <col min="67" max="67" customWidth="true" width="19.4272727272727"/>
+    <col min="68" max="68" customWidth="true" width="35.4272727272727"/>
+    <col min="69" max="69" customWidth="true" width="9.57272727272727"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -17639,11 +17802,11 @@
       <c r="AT4" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" t="s">
-        <v>169</v>
-      </c>
-      <c r="AV4" t="s">
-        <v>170</v>
+      <c r="AU4" t="s" s="0">
+        <v>220</v>
+      </c>
+      <c r="AV4" t="s" s="0">
+        <v>221</v>
       </c>
       <c r="AW4" s="16">
         <f>AM4</f>
@@ -17683,11 +17846,11 @@
       <c r="BL4" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="BM4" t="s">
-        <v>171</v>
-      </c>
-      <c r="BN4" t="s">
-        <v>172</v>
+      <c r="BM4" t="s" s="0">
+        <v>223</v>
+      </c>
+      <c r="BN4" t="s" s="0">
+        <v>222</v>
       </c>
       <c r="BO4" s="16">
         <f>ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
@@ -17834,71 +17997,71 @@
   <dimension ref="A1:BQ5"/>
   <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" width="5.14545454545455" customWidth="1"/>
-    <col min="2" max="3" width="22" customWidth="1"/>
-    <col min="4" max="4" width="79.4272727272727" customWidth="1"/>
-    <col min="5" max="5" width="11.5727272727273" customWidth="1"/>
-    <col min="6" max="6" width="5.14545454545455" customWidth="1"/>
-    <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="12.7181818181818" customWidth="1"/>
-    <col min="9" max="9" width="5.85454545454545" customWidth="1"/>
-    <col min="10" max="10" width="6" customWidth="1"/>
-    <col min="11" max="11" width="5.85454545454545" customWidth="1"/>
-    <col min="12" max="12" width="14.2818181818182" customWidth="1"/>
-    <col min="13" max="13" width="9.42727272727273" customWidth="1"/>
-    <col min="14" max="14" width="14.4272727272727" customWidth="1"/>
-    <col min="15" max="15" width="15.5727272727273" customWidth="1"/>
-    <col min="16" max="16" width="14.4272727272727" customWidth="1"/>
-    <col min="17" max="17" width="39.4272727272727" customWidth="1"/>
-    <col min="18" max="18" width="11.7181818181818" customWidth="1"/>
-    <col min="19" max="19" width="11.8545454545455" customWidth="1"/>
-    <col min="20" max="20" width="6.42727272727273" customWidth="1"/>
-    <col min="21" max="22" width="6.57272727272727" customWidth="1"/>
-    <col min="23" max="23" width="37.1454545454545" customWidth="1"/>
-    <col min="24" max="25" width="8" customWidth="1"/>
-    <col min="26" max="26" width="7.71818181818182" customWidth="1"/>
-    <col min="27" max="27" width="6.28181818181818" customWidth="1"/>
-    <col min="28" max="28" width="9.28181818181818" customWidth="1"/>
-    <col min="29" max="29" width="9.71818181818182" customWidth="1"/>
-    <col min="30" max="30" width="12.8545454545455" customWidth="1"/>
-    <col min="31" max="31" width="16.1454545454545" customWidth="1"/>
-    <col min="32" max="32" width="15.4272727272727" customWidth="1"/>
-    <col min="33" max="33" width="24.5727272727273" customWidth="1"/>
-    <col min="34" max="34" width="8.57272727272727" customWidth="1"/>
-    <col min="35" max="35" width="14.7181818181818" customWidth="1"/>
-    <col min="36" max="36" width="18.5727272727273" customWidth="1"/>
-    <col min="37" max="37" width="14.1454545454545" customWidth="1"/>
-    <col min="38" max="38" width="14.7181818181818" customWidth="1"/>
-    <col min="39" max="39" width="17.4272727272727" customWidth="1"/>
-    <col min="40" max="40" width="22" customWidth="1"/>
-    <col min="41" max="41" width="17.5727272727273" customWidth="1"/>
-    <col min="42" max="42" width="25.2818181818182" customWidth="1"/>
-    <col min="43" max="43" width="13" customWidth="1"/>
-    <col min="44" max="44" width="23.7181818181818" customWidth="1"/>
-    <col min="45" max="45" width="10" customWidth="1"/>
-    <col min="46" max="46" width="13" customWidth="1"/>
-    <col min="47" max="47" width="15.5727272727273" customWidth="1"/>
-    <col min="48" max="48" width="21.1454545454545" customWidth="1"/>
-    <col min="49" max="49" width="11.5727272727273" customWidth="1"/>
-    <col min="50" max="50" width="16.7181818181818" customWidth="1"/>
-    <col min="51" max="51" width="14" customWidth="1"/>
-    <col min="52" max="52" width="19.4272727272727" customWidth="1"/>
-    <col min="53" max="53" width="18.8545454545455" customWidth="1"/>
-    <col min="54" max="54" width="23.2818181818182" customWidth="1"/>
-    <col min="55" max="55" width="15.5727272727273" customWidth="1"/>
-    <col min="56" max="56" width="14.2818181818182" customWidth="1"/>
-    <col min="57" max="57" width="17" customWidth="1"/>
-    <col min="58" max="58" width="16.2818181818182" customWidth="1"/>
-    <col min="59" max="59" width="13.5727272727273" customWidth="1"/>
-    <col min="60" max="61" width="12.7181818181818" customWidth="1"/>
-    <col min="62" max="62" width="21.8545454545455" customWidth="1"/>
-    <col min="63" max="63" width="30.5727272727273" customWidth="1"/>
-    <col min="64" max="64" width="10" customWidth="1"/>
-    <col min="65" max="65" width="42.5727272727273" customWidth="1"/>
-    <col min="66" max="66" width="38.1454545454545" customWidth="1"/>
-    <col min="67" max="67" width="19.4272727272727" customWidth="1"/>
-    <col min="68" max="68" width="35.4272727272727" customWidth="1"/>
-    <col min="69" max="69" width="9.57272727272727" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="5.14545454545455"/>
+    <col min="2" max="3" customWidth="true" width="22.0"/>
+    <col min="4" max="4" customWidth="true" width="79.4272727272727"/>
+    <col min="5" max="5" customWidth="true" width="11.5727272727273"/>
+    <col min="6" max="6" customWidth="true" width="5.14545454545455"/>
+    <col min="7" max="7" customWidth="true" width="11.0"/>
+    <col min="8" max="8" customWidth="true" width="12.7181818181818"/>
+    <col min="9" max="9" customWidth="true" width="5.85454545454545"/>
+    <col min="10" max="10" customWidth="true" width="6.0"/>
+    <col min="11" max="11" customWidth="true" width="5.85454545454545"/>
+    <col min="12" max="12" customWidth="true" width="14.2818181818182"/>
+    <col min="13" max="13" customWidth="true" width="9.42727272727273"/>
+    <col min="14" max="14" customWidth="true" width="14.4272727272727"/>
+    <col min="15" max="15" customWidth="true" width="15.5727272727273"/>
+    <col min="16" max="16" customWidth="true" width="14.4272727272727"/>
+    <col min="17" max="17" customWidth="true" width="39.4272727272727"/>
+    <col min="18" max="18" customWidth="true" width="11.7181818181818"/>
+    <col min="19" max="19" customWidth="true" width="11.8545454545455"/>
+    <col min="20" max="20" customWidth="true" width="6.42727272727273"/>
+    <col min="21" max="22" customWidth="true" width="6.57272727272727"/>
+    <col min="23" max="23" customWidth="true" width="37.1454545454545"/>
+    <col min="24" max="25" customWidth="true" width="8.0"/>
+    <col min="26" max="26" customWidth="true" width="7.71818181818182"/>
+    <col min="27" max="27" customWidth="true" width="6.28181818181818"/>
+    <col min="28" max="28" customWidth="true" width="9.28181818181818"/>
+    <col min="29" max="29" customWidth="true" width="9.71818181818182"/>
+    <col min="30" max="30" customWidth="true" width="12.8545454545455"/>
+    <col min="31" max="31" customWidth="true" width="16.1454545454545"/>
+    <col min="32" max="32" customWidth="true" width="15.4272727272727"/>
+    <col min="33" max="33" customWidth="true" width="24.5727272727273"/>
+    <col min="34" max="34" customWidth="true" width="8.57272727272727"/>
+    <col min="35" max="35" customWidth="true" width="14.7181818181818"/>
+    <col min="36" max="36" customWidth="true" width="18.5727272727273"/>
+    <col min="37" max="37" customWidth="true" width="14.1454545454545"/>
+    <col min="38" max="38" customWidth="true" width="14.7181818181818"/>
+    <col min="39" max="39" customWidth="true" width="17.4272727272727"/>
+    <col min="40" max="40" customWidth="true" width="22.0"/>
+    <col min="41" max="41" customWidth="true" width="17.5727272727273"/>
+    <col min="42" max="42" customWidth="true" width="25.2818181818182"/>
+    <col min="43" max="43" customWidth="true" width="13.0"/>
+    <col min="44" max="44" customWidth="true" width="23.7181818181818"/>
+    <col min="45" max="45" customWidth="true" width="10.0"/>
+    <col min="46" max="46" customWidth="true" width="13.0"/>
+    <col min="47" max="47" customWidth="true" width="15.5727272727273"/>
+    <col min="48" max="48" customWidth="true" width="21.1454545454545"/>
+    <col min="49" max="49" customWidth="true" width="11.5727272727273"/>
+    <col min="50" max="50" customWidth="true" width="16.7181818181818"/>
+    <col min="51" max="51" customWidth="true" width="14.0"/>
+    <col min="52" max="52" customWidth="true" width="19.4272727272727"/>
+    <col min="53" max="53" customWidth="true" width="18.8545454545455"/>
+    <col min="54" max="54" customWidth="true" width="23.2818181818182"/>
+    <col min="55" max="55" customWidth="true" width="15.5727272727273"/>
+    <col min="56" max="56" customWidth="true" width="14.2818181818182"/>
+    <col min="57" max="57" customWidth="true" width="17.0"/>
+    <col min="58" max="58" customWidth="true" width="16.2818181818182"/>
+    <col min="59" max="59" customWidth="true" width="13.5727272727273"/>
+    <col min="60" max="61" customWidth="true" width="12.7181818181818"/>
+    <col min="62" max="62" customWidth="true" width="21.8545454545455"/>
+    <col min="63" max="63" customWidth="true" width="30.5727272727273"/>
+    <col min="64" max="64" customWidth="true" width="10.0"/>
+    <col min="65" max="65" customWidth="true" width="42.5727272727273"/>
+    <col min="66" max="66" customWidth="true" width="38.1454545454545"/>
+    <col min="67" max="67" customWidth="true" width="19.4272727272727"/>
+    <col min="68" max="68" customWidth="true" width="35.4272727272727"/>
+    <col min="69" max="69" customWidth="true" width="9.57272727272727"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -18633,71 +18796,71 @@
   <dimension ref="A1:BQ5"/>
   <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" width="5.14545454545455" customWidth="1"/>
-    <col min="2" max="3" width="25" customWidth="1"/>
-    <col min="4" max="4" width="79.4272727272727" customWidth="1"/>
-    <col min="5" max="5" width="11.5727272727273" customWidth="1"/>
-    <col min="6" max="6" width="5.14545454545455" customWidth="1"/>
-    <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="12.7181818181818" customWidth="1"/>
-    <col min="9" max="9" width="5.85454545454545" customWidth="1"/>
-    <col min="10" max="10" width="6" customWidth="1"/>
-    <col min="11" max="11" width="5.85454545454545" customWidth="1"/>
-    <col min="12" max="12" width="14.2818181818182" customWidth="1"/>
-    <col min="13" max="13" width="9.42727272727273" customWidth="1"/>
-    <col min="14" max="14" width="14.4272727272727" customWidth="1"/>
-    <col min="15" max="15" width="15.5727272727273" customWidth="1"/>
-    <col min="16" max="16" width="14.4272727272727" customWidth="1"/>
-    <col min="17" max="17" width="39.4272727272727" customWidth="1"/>
-    <col min="18" max="18" width="11.7181818181818" customWidth="1"/>
-    <col min="19" max="19" width="11.8545454545455" customWidth="1"/>
-    <col min="20" max="20" width="6.42727272727273" customWidth="1"/>
-    <col min="21" max="22" width="6.57272727272727" customWidth="1"/>
-    <col min="23" max="23" width="37.1454545454545" customWidth="1"/>
-    <col min="24" max="25" width="8" customWidth="1"/>
-    <col min="26" max="26" width="7.71818181818182" customWidth="1"/>
-    <col min="27" max="27" width="6.28181818181818" customWidth="1"/>
-    <col min="28" max="28" width="9.28181818181818" customWidth="1"/>
-    <col min="29" max="29" width="9.71818181818182" customWidth="1"/>
-    <col min="30" max="30" width="12.8545454545455" customWidth="1"/>
-    <col min="31" max="31" width="16.1454545454545" customWidth="1"/>
-    <col min="32" max="32" width="15.4272727272727" customWidth="1"/>
-    <col min="33" max="33" width="24.5727272727273" customWidth="1"/>
-    <col min="34" max="34" width="8.57272727272727" customWidth="1"/>
-    <col min="35" max="35" width="14.7181818181818" customWidth="1"/>
-    <col min="36" max="36" width="18.5727272727273" customWidth="1"/>
-    <col min="37" max="37" width="14.1454545454545" customWidth="1"/>
-    <col min="38" max="38" width="14.7181818181818" customWidth="1"/>
-    <col min="39" max="39" width="17.4272727272727" customWidth="1"/>
-    <col min="40" max="40" width="22" customWidth="1"/>
-    <col min="41" max="41" width="17.5727272727273" customWidth="1"/>
-    <col min="42" max="42" width="25.2818181818182" customWidth="1"/>
-    <col min="43" max="43" width="13" customWidth="1"/>
-    <col min="44" max="44" width="23.7181818181818" customWidth="1"/>
-    <col min="45" max="45" width="10" customWidth="1"/>
-    <col min="46" max="46" width="13" customWidth="1"/>
-    <col min="47" max="47" width="15.5727272727273" customWidth="1"/>
-    <col min="48" max="48" width="21.1454545454545" customWidth="1"/>
-    <col min="49" max="49" width="11.5727272727273" customWidth="1"/>
-    <col min="50" max="50" width="16.7181818181818" customWidth="1"/>
-    <col min="51" max="51" width="14" customWidth="1"/>
-    <col min="52" max="52" width="19.4272727272727" customWidth="1"/>
-    <col min="53" max="53" width="18.8545454545455" customWidth="1"/>
-    <col min="54" max="54" width="23.2818181818182" customWidth="1"/>
-    <col min="55" max="55" width="15.5727272727273" customWidth="1"/>
-    <col min="56" max="56" width="14.2818181818182" customWidth="1"/>
-    <col min="57" max="57" width="17" customWidth="1"/>
-    <col min="58" max="58" width="16.2818181818182" customWidth="1"/>
-    <col min="59" max="59" width="13.5727272727273" customWidth="1"/>
-    <col min="60" max="61" width="12.7181818181818" customWidth="1"/>
-    <col min="62" max="62" width="21.8545454545455" customWidth="1"/>
-    <col min="63" max="63" width="30.5727272727273" customWidth="1"/>
-    <col min="64" max="64" width="10" customWidth="1"/>
-    <col min="65" max="65" width="42.5727272727273" customWidth="1"/>
-    <col min="66" max="66" width="38.1454545454545" customWidth="1"/>
-    <col min="67" max="67" width="19.4272727272727" customWidth="1"/>
-    <col min="68" max="68" width="35.4272727272727" customWidth="1"/>
-    <col min="69" max="69" width="9.57272727272727" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="5.14545454545455"/>
+    <col min="2" max="3" customWidth="true" width="25.0"/>
+    <col min="4" max="4" customWidth="true" width="79.4272727272727"/>
+    <col min="5" max="5" customWidth="true" width="11.5727272727273"/>
+    <col min="6" max="6" customWidth="true" width="5.14545454545455"/>
+    <col min="7" max="7" customWidth="true" width="11.0"/>
+    <col min="8" max="8" customWidth="true" width="12.7181818181818"/>
+    <col min="9" max="9" customWidth="true" width="5.85454545454545"/>
+    <col min="10" max="10" customWidth="true" width="6.0"/>
+    <col min="11" max="11" customWidth="true" width="5.85454545454545"/>
+    <col min="12" max="12" customWidth="true" width="14.2818181818182"/>
+    <col min="13" max="13" customWidth="true" width="9.42727272727273"/>
+    <col min="14" max="14" customWidth="true" width="14.4272727272727"/>
+    <col min="15" max="15" customWidth="true" width="15.5727272727273"/>
+    <col min="16" max="16" customWidth="true" width="14.4272727272727"/>
+    <col min="17" max="17" customWidth="true" width="39.4272727272727"/>
+    <col min="18" max="18" customWidth="true" width="11.7181818181818"/>
+    <col min="19" max="19" customWidth="true" width="11.8545454545455"/>
+    <col min="20" max="20" customWidth="true" width="6.42727272727273"/>
+    <col min="21" max="22" customWidth="true" width="6.57272727272727"/>
+    <col min="23" max="23" customWidth="true" width="37.1454545454545"/>
+    <col min="24" max="25" customWidth="true" width="8.0"/>
+    <col min="26" max="26" customWidth="true" width="7.71818181818182"/>
+    <col min="27" max="27" customWidth="true" width="6.28181818181818"/>
+    <col min="28" max="28" customWidth="true" width="9.28181818181818"/>
+    <col min="29" max="29" customWidth="true" width="9.71818181818182"/>
+    <col min="30" max="30" customWidth="true" width="12.8545454545455"/>
+    <col min="31" max="31" customWidth="true" width="16.1454545454545"/>
+    <col min="32" max="32" customWidth="true" width="15.4272727272727"/>
+    <col min="33" max="33" customWidth="true" width="24.5727272727273"/>
+    <col min="34" max="34" customWidth="true" width="8.57272727272727"/>
+    <col min="35" max="35" customWidth="true" width="14.7181818181818"/>
+    <col min="36" max="36" customWidth="true" width="18.5727272727273"/>
+    <col min="37" max="37" customWidth="true" width="14.1454545454545"/>
+    <col min="38" max="38" customWidth="true" width="14.7181818181818"/>
+    <col min="39" max="39" customWidth="true" width="17.4272727272727"/>
+    <col min="40" max="40" customWidth="true" width="22.0"/>
+    <col min="41" max="41" customWidth="true" width="17.5727272727273"/>
+    <col min="42" max="42" customWidth="true" width="25.2818181818182"/>
+    <col min="43" max="43" customWidth="true" width="13.0"/>
+    <col min="44" max="44" customWidth="true" width="23.7181818181818"/>
+    <col min="45" max="45" customWidth="true" width="10.0"/>
+    <col min="46" max="46" customWidth="true" width="13.0"/>
+    <col min="47" max="47" customWidth="true" width="15.5727272727273"/>
+    <col min="48" max="48" customWidth="true" width="21.1454545454545"/>
+    <col min="49" max="49" customWidth="true" width="11.5727272727273"/>
+    <col min="50" max="50" customWidth="true" width="16.7181818181818"/>
+    <col min="51" max="51" customWidth="true" width="14.0"/>
+    <col min="52" max="52" customWidth="true" width="19.4272727272727"/>
+    <col min="53" max="53" customWidth="true" width="18.8545454545455"/>
+    <col min="54" max="54" customWidth="true" width="23.2818181818182"/>
+    <col min="55" max="55" customWidth="true" width="15.5727272727273"/>
+    <col min="56" max="56" customWidth="true" width="14.2818181818182"/>
+    <col min="57" max="57" customWidth="true" width="17.0"/>
+    <col min="58" max="58" customWidth="true" width="16.2818181818182"/>
+    <col min="59" max="59" customWidth="true" width="13.5727272727273"/>
+    <col min="60" max="61" customWidth="true" width="12.7181818181818"/>
+    <col min="62" max="62" customWidth="true" width="21.8545454545455"/>
+    <col min="63" max="63" customWidth="true" width="30.5727272727273"/>
+    <col min="64" max="64" customWidth="true" width="10.0"/>
+    <col min="65" max="65" customWidth="true" width="42.5727272727273"/>
+    <col min="66" max="66" customWidth="true" width="38.1454545454545"/>
+    <col min="67" max="67" customWidth="true" width="19.4272727272727"/>
+    <col min="68" max="68" customWidth="true" width="35.4272727272727"/>
+    <col min="69" max="69" customWidth="true" width="9.57272727272727"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -19241,6 +19404,8 @@
       <c r="AT4" s="35" t="s">
         <v>76</v>
       </c>
+      <c r="AU4" s="0"/>
+      <c r="AV4" s="0"/>
       <c r="AW4" s="35">
         <f>AM4</f>
         <v>4</v>
@@ -19279,10 +19444,10 @@
       <c r="BL4" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="BM4" t="s">
+      <c r="BM4" t="s" s="0">
         <v>100</v>
       </c>
-      <c r="BN4" t="s">
+      <c r="BN4" t="s" s="0">
         <v>100</v>
       </c>
       <c r="BO4" s="35">
@@ -19430,71 +19595,71 @@
   <dimension ref="A1:BQ5"/>
   <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" width="5.14545454545455" customWidth="1"/>
-    <col min="2" max="3" width="25" customWidth="1"/>
-    <col min="4" max="4" width="79.4272727272727" customWidth="1"/>
-    <col min="5" max="5" width="11.5727272727273" customWidth="1"/>
-    <col min="6" max="6" width="5.14545454545455" customWidth="1"/>
-    <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="12.7181818181818" customWidth="1"/>
-    <col min="9" max="9" width="5.85454545454545" customWidth="1"/>
-    <col min="10" max="10" width="6" customWidth="1"/>
-    <col min="11" max="11" width="5.85454545454545" customWidth="1"/>
-    <col min="12" max="12" width="14.2818181818182" customWidth="1"/>
-    <col min="13" max="13" width="9.42727272727273" customWidth="1"/>
-    <col min="14" max="14" width="14.4272727272727" customWidth="1"/>
-    <col min="15" max="15" width="15.5727272727273" customWidth="1"/>
-    <col min="16" max="16" width="14.4272727272727" customWidth="1"/>
-    <col min="17" max="17" width="39.4272727272727" customWidth="1"/>
-    <col min="18" max="18" width="11.7181818181818" customWidth="1"/>
-    <col min="19" max="19" width="11.8545454545455" customWidth="1"/>
-    <col min="20" max="20" width="6.42727272727273" customWidth="1"/>
-    <col min="21" max="22" width="6.57272727272727" customWidth="1"/>
-    <col min="23" max="23" width="37.1454545454545" customWidth="1"/>
-    <col min="24" max="25" width="8" customWidth="1"/>
-    <col min="26" max="26" width="7.71818181818182" customWidth="1"/>
-    <col min="27" max="27" width="6.28181818181818" customWidth="1"/>
-    <col min="28" max="28" width="9.28181818181818" customWidth="1"/>
-    <col min="29" max="29" width="9.71818181818182" customWidth="1"/>
-    <col min="30" max="30" width="12.8545454545455" customWidth="1"/>
-    <col min="31" max="31" width="16.1454545454545" customWidth="1"/>
-    <col min="32" max="32" width="15.4272727272727" customWidth="1"/>
-    <col min="33" max="33" width="24.5727272727273" customWidth="1"/>
-    <col min="34" max="34" width="8.57272727272727" customWidth="1"/>
-    <col min="35" max="35" width="14.7181818181818" customWidth="1"/>
-    <col min="36" max="36" width="18.5727272727273" customWidth="1"/>
-    <col min="37" max="37" width="14.1454545454545" customWidth="1"/>
-    <col min="38" max="38" width="14.7181818181818" customWidth="1"/>
-    <col min="39" max="39" width="17.4272727272727" customWidth="1"/>
-    <col min="40" max="40" width="22" customWidth="1"/>
-    <col min="41" max="41" width="17.5727272727273" customWidth="1"/>
-    <col min="42" max="42" width="25.2818181818182" customWidth="1"/>
-    <col min="43" max="43" width="13" customWidth="1"/>
-    <col min="44" max="44" width="23.7181818181818" customWidth="1"/>
-    <col min="45" max="45" width="10" customWidth="1"/>
-    <col min="46" max="46" width="13" customWidth="1"/>
-    <col min="47" max="47" width="15.5727272727273" customWidth="1"/>
-    <col min="48" max="48" width="21.1454545454545" customWidth="1"/>
-    <col min="49" max="49" width="11.5727272727273" customWidth="1"/>
-    <col min="50" max="50" width="16.7181818181818" customWidth="1"/>
-    <col min="51" max="51" width="14" customWidth="1"/>
-    <col min="52" max="52" width="19.4272727272727" customWidth="1"/>
-    <col min="53" max="53" width="18.8545454545455" customWidth="1"/>
-    <col min="54" max="54" width="23.2818181818182" customWidth="1"/>
-    <col min="55" max="55" width="15.5727272727273" customWidth="1"/>
-    <col min="56" max="56" width="14.2818181818182" customWidth="1"/>
-    <col min="57" max="57" width="17" customWidth="1"/>
-    <col min="58" max="58" width="16.2818181818182" customWidth="1"/>
-    <col min="59" max="59" width="13.5727272727273" customWidth="1"/>
-    <col min="60" max="61" width="12.7181818181818" customWidth="1"/>
-    <col min="62" max="62" width="21.8545454545455" customWidth="1"/>
-    <col min="63" max="63" width="30.5727272727273" customWidth="1"/>
-    <col min="64" max="64" width="10" customWidth="1"/>
-    <col min="65" max="65" width="42.5727272727273" customWidth="1"/>
-    <col min="66" max="66" width="38.1454545454545" customWidth="1"/>
-    <col min="67" max="67" width="19.4272727272727" customWidth="1"/>
-    <col min="68" max="68" width="35.4272727272727" customWidth="1"/>
-    <col min="69" max="69" width="9.57272727272727" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="5.14545454545455"/>
+    <col min="2" max="3" customWidth="true" width="25.0"/>
+    <col min="4" max="4" customWidth="true" width="79.4272727272727"/>
+    <col min="5" max="5" customWidth="true" width="11.5727272727273"/>
+    <col min="6" max="6" customWidth="true" width="5.14545454545455"/>
+    <col min="7" max="7" customWidth="true" width="11.0"/>
+    <col min="8" max="8" customWidth="true" width="12.7181818181818"/>
+    <col min="9" max="9" customWidth="true" width="5.85454545454545"/>
+    <col min="10" max="10" customWidth="true" width="6.0"/>
+    <col min="11" max="11" customWidth="true" width="5.85454545454545"/>
+    <col min="12" max="12" customWidth="true" width="14.2818181818182"/>
+    <col min="13" max="13" customWidth="true" width="9.42727272727273"/>
+    <col min="14" max="14" customWidth="true" width="14.4272727272727"/>
+    <col min="15" max="15" customWidth="true" width="15.5727272727273"/>
+    <col min="16" max="16" customWidth="true" width="14.4272727272727"/>
+    <col min="17" max="17" customWidth="true" width="39.4272727272727"/>
+    <col min="18" max="18" customWidth="true" width="11.7181818181818"/>
+    <col min="19" max="19" customWidth="true" width="11.8545454545455"/>
+    <col min="20" max="20" customWidth="true" width="6.42727272727273"/>
+    <col min="21" max="22" customWidth="true" width="6.57272727272727"/>
+    <col min="23" max="23" customWidth="true" width="37.1454545454545"/>
+    <col min="24" max="25" customWidth="true" width="8.0"/>
+    <col min="26" max="26" customWidth="true" width="7.71818181818182"/>
+    <col min="27" max="27" customWidth="true" width="6.28181818181818"/>
+    <col min="28" max="28" customWidth="true" width="9.28181818181818"/>
+    <col min="29" max="29" customWidth="true" width="9.71818181818182"/>
+    <col min="30" max="30" customWidth="true" width="12.8545454545455"/>
+    <col min="31" max="31" customWidth="true" width="16.1454545454545"/>
+    <col min="32" max="32" customWidth="true" width="15.4272727272727"/>
+    <col min="33" max="33" customWidth="true" width="24.5727272727273"/>
+    <col min="34" max="34" customWidth="true" width="8.57272727272727"/>
+    <col min="35" max="35" customWidth="true" width="14.7181818181818"/>
+    <col min="36" max="36" customWidth="true" width="18.5727272727273"/>
+    <col min="37" max="37" customWidth="true" width="14.1454545454545"/>
+    <col min="38" max="38" customWidth="true" width="14.7181818181818"/>
+    <col min="39" max="39" customWidth="true" width="17.4272727272727"/>
+    <col min="40" max="40" customWidth="true" width="22.0"/>
+    <col min="41" max="41" customWidth="true" width="17.5727272727273"/>
+    <col min="42" max="42" customWidth="true" width="25.2818181818182"/>
+    <col min="43" max="43" customWidth="true" width="13.0"/>
+    <col min="44" max="44" customWidth="true" width="23.7181818181818"/>
+    <col min="45" max="45" customWidth="true" width="10.0"/>
+    <col min="46" max="46" customWidth="true" width="13.0"/>
+    <col min="47" max="47" customWidth="true" width="15.5727272727273"/>
+    <col min="48" max="48" customWidth="true" width="21.1454545454545"/>
+    <col min="49" max="49" customWidth="true" width="11.5727272727273"/>
+    <col min="50" max="50" customWidth="true" width="16.7181818181818"/>
+    <col min="51" max="51" customWidth="true" width="14.0"/>
+    <col min="52" max="52" customWidth="true" width="19.4272727272727"/>
+    <col min="53" max="53" customWidth="true" width="18.8545454545455"/>
+    <col min="54" max="54" customWidth="true" width="23.2818181818182"/>
+    <col min="55" max="55" customWidth="true" width="15.5727272727273"/>
+    <col min="56" max="56" customWidth="true" width="14.2818181818182"/>
+    <col min="57" max="57" customWidth="true" width="17.0"/>
+    <col min="58" max="58" customWidth="true" width="16.2818181818182"/>
+    <col min="59" max="59" customWidth="true" width="13.5727272727273"/>
+    <col min="60" max="61" customWidth="true" width="12.7181818181818"/>
+    <col min="62" max="62" customWidth="true" width="21.8545454545455"/>
+    <col min="63" max="63" customWidth="true" width="30.5727272727273"/>
+    <col min="64" max="64" customWidth="true" width="10.0"/>
+    <col min="65" max="65" customWidth="true" width="42.5727272727273"/>
+    <col min="66" max="66" customWidth="true" width="38.1454545454545"/>
+    <col min="67" max="67" customWidth="true" width="19.4272727272727"/>
+    <col min="68" max="68" customWidth="true" width="35.4272727272727"/>
+    <col min="69" max="69" customWidth="true" width="9.57272727272727"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -20038,6 +20203,8 @@
       <c r="AT4" s="35" t="s">
         <v>76</v>
       </c>
+      <c r="AU4" s="0"/>
+      <c r="AV4" s="0"/>
       <c r="AW4" s="35">
         <f>AM4</f>
         <v>4</v>
@@ -20076,10 +20243,10 @@
       <c r="BL4" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="BM4" t="s">
+      <c r="BM4" t="s" s="0">
         <v>100</v>
       </c>
-      <c r="BN4" t="s">
+      <c r="BN4" t="s" s="0">
         <v>100</v>
       </c>
       <c r="BO4" s="35">
@@ -20227,71 +20394,71 @@
   <dimension ref="A1:BQ5"/>
   <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" width="5.14545454545455" customWidth="1"/>
-    <col min="2" max="3" width="25.2818181818182" customWidth="1"/>
-    <col min="4" max="4" width="79.4272727272727" customWidth="1"/>
-    <col min="5" max="5" width="11.5727272727273" customWidth="1"/>
-    <col min="6" max="6" width="5.14545454545455" customWidth="1"/>
-    <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="12.7181818181818" customWidth="1"/>
-    <col min="9" max="9" width="5.85454545454545" customWidth="1"/>
-    <col min="10" max="10" width="6" customWidth="1"/>
-    <col min="11" max="11" width="5.85454545454545" customWidth="1"/>
-    <col min="12" max="12" width="14.2818181818182" customWidth="1"/>
-    <col min="13" max="13" width="9.42727272727273" customWidth="1"/>
-    <col min="14" max="14" width="14.4272727272727" customWidth="1"/>
-    <col min="15" max="15" width="15.5727272727273" customWidth="1"/>
-    <col min="16" max="16" width="14.4272727272727" customWidth="1"/>
-    <col min="17" max="17" width="39.4272727272727" customWidth="1"/>
-    <col min="18" max="18" width="11.7181818181818" customWidth="1"/>
-    <col min="19" max="19" width="11.8545454545455" customWidth="1"/>
-    <col min="20" max="20" width="6.42727272727273" customWidth="1"/>
-    <col min="21" max="22" width="6.57272727272727" customWidth="1"/>
-    <col min="23" max="23" width="37.1454545454545" customWidth="1"/>
-    <col min="24" max="25" width="8" customWidth="1"/>
-    <col min="26" max="26" width="7.71818181818182" customWidth="1"/>
-    <col min="27" max="27" width="6.28181818181818" customWidth="1"/>
-    <col min="28" max="28" width="9.28181818181818" customWidth="1"/>
-    <col min="29" max="29" width="9.71818181818182" customWidth="1"/>
-    <col min="30" max="30" width="12.8545454545455" customWidth="1"/>
-    <col min="31" max="31" width="16.1454545454545" customWidth="1"/>
-    <col min="32" max="32" width="15.4272727272727" customWidth="1"/>
-    <col min="33" max="33" width="24.5727272727273" customWidth="1"/>
-    <col min="34" max="34" width="8.57272727272727" customWidth="1"/>
-    <col min="35" max="35" width="14.7181818181818" customWidth="1"/>
-    <col min="36" max="36" width="18.5727272727273" customWidth="1"/>
-    <col min="37" max="37" width="14.1454545454545" customWidth="1"/>
-    <col min="38" max="38" width="14.7181818181818" customWidth="1"/>
-    <col min="39" max="39" width="17.4272727272727" customWidth="1"/>
-    <col min="40" max="40" width="22" customWidth="1"/>
-    <col min="41" max="41" width="17.5727272727273" customWidth="1"/>
-    <col min="42" max="42" width="25.2818181818182" customWidth="1"/>
-    <col min="43" max="43" width="13" customWidth="1"/>
-    <col min="44" max="44" width="23.7181818181818" customWidth="1"/>
-    <col min="45" max="45" width="10" customWidth="1"/>
-    <col min="46" max="46" width="13" customWidth="1"/>
-    <col min="47" max="47" width="15.5727272727273" customWidth="1"/>
-    <col min="48" max="48" width="21.1454545454545" customWidth="1"/>
-    <col min="49" max="49" width="11.5727272727273" customWidth="1"/>
-    <col min="50" max="50" width="16.7181818181818" customWidth="1"/>
-    <col min="51" max="51" width="14" customWidth="1"/>
-    <col min="52" max="52" width="19.4272727272727" customWidth="1"/>
-    <col min="53" max="53" width="18.8545454545455" customWidth="1"/>
-    <col min="54" max="54" width="23.2818181818182" customWidth="1"/>
-    <col min="55" max="55" width="15.5727272727273" customWidth="1"/>
-    <col min="56" max="56" width="14.2818181818182" customWidth="1"/>
-    <col min="57" max="57" width="17" customWidth="1"/>
-    <col min="58" max="58" width="16.2818181818182" customWidth="1"/>
-    <col min="59" max="59" width="13.5727272727273" customWidth="1"/>
-    <col min="60" max="61" width="12.7181818181818" customWidth="1"/>
-    <col min="62" max="62" width="21.8545454545455" customWidth="1"/>
-    <col min="63" max="63" width="30.5727272727273" customWidth="1"/>
-    <col min="64" max="64" width="10" customWidth="1"/>
-    <col min="65" max="65" width="42.5727272727273" customWidth="1"/>
-    <col min="66" max="66" width="38.1454545454545" customWidth="1"/>
-    <col min="67" max="67" width="19.4272727272727" customWidth="1"/>
-    <col min="68" max="68" width="35.4272727272727" customWidth="1"/>
-    <col min="69" max="69" width="9.57272727272727" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="5.14545454545455"/>
+    <col min="2" max="3" customWidth="true" width="25.2818181818182"/>
+    <col min="4" max="4" customWidth="true" width="79.4272727272727"/>
+    <col min="5" max="5" customWidth="true" width="11.5727272727273"/>
+    <col min="6" max="6" customWidth="true" width="5.14545454545455"/>
+    <col min="7" max="7" customWidth="true" width="11.0"/>
+    <col min="8" max="8" customWidth="true" width="12.7181818181818"/>
+    <col min="9" max="9" customWidth="true" width="5.85454545454545"/>
+    <col min="10" max="10" customWidth="true" width="6.0"/>
+    <col min="11" max="11" customWidth="true" width="5.85454545454545"/>
+    <col min="12" max="12" customWidth="true" width="14.2818181818182"/>
+    <col min="13" max="13" customWidth="true" width="9.42727272727273"/>
+    <col min="14" max="14" customWidth="true" width="14.4272727272727"/>
+    <col min="15" max="15" customWidth="true" width="15.5727272727273"/>
+    <col min="16" max="16" customWidth="true" width="14.4272727272727"/>
+    <col min="17" max="17" customWidth="true" width="39.4272727272727"/>
+    <col min="18" max="18" customWidth="true" width="11.7181818181818"/>
+    <col min="19" max="19" customWidth="true" width="11.8545454545455"/>
+    <col min="20" max="20" customWidth="true" width="6.42727272727273"/>
+    <col min="21" max="22" customWidth="true" width="6.57272727272727"/>
+    <col min="23" max="23" customWidth="true" width="37.1454545454545"/>
+    <col min="24" max="25" customWidth="true" width="8.0"/>
+    <col min="26" max="26" customWidth="true" width="7.71818181818182"/>
+    <col min="27" max="27" customWidth="true" width="6.28181818181818"/>
+    <col min="28" max="28" customWidth="true" width="9.28181818181818"/>
+    <col min="29" max="29" customWidth="true" width="9.71818181818182"/>
+    <col min="30" max="30" customWidth="true" width="12.8545454545455"/>
+    <col min="31" max="31" customWidth="true" width="16.1454545454545"/>
+    <col min="32" max="32" customWidth="true" width="15.4272727272727"/>
+    <col min="33" max="33" customWidth="true" width="24.5727272727273"/>
+    <col min="34" max="34" customWidth="true" width="8.57272727272727"/>
+    <col min="35" max="35" customWidth="true" width="14.7181818181818"/>
+    <col min="36" max="36" customWidth="true" width="18.5727272727273"/>
+    <col min="37" max="37" customWidth="true" width="14.1454545454545"/>
+    <col min="38" max="38" customWidth="true" width="14.7181818181818"/>
+    <col min="39" max="39" customWidth="true" width="17.4272727272727"/>
+    <col min="40" max="40" customWidth="true" width="22.0"/>
+    <col min="41" max="41" customWidth="true" width="17.5727272727273"/>
+    <col min="42" max="42" customWidth="true" width="25.2818181818182"/>
+    <col min="43" max="43" customWidth="true" width="13.0"/>
+    <col min="44" max="44" customWidth="true" width="23.7181818181818"/>
+    <col min="45" max="45" customWidth="true" width="10.0"/>
+    <col min="46" max="46" customWidth="true" width="13.0"/>
+    <col min="47" max="47" customWidth="true" width="15.5727272727273"/>
+    <col min="48" max="48" customWidth="true" width="21.1454545454545"/>
+    <col min="49" max="49" customWidth="true" width="11.5727272727273"/>
+    <col min="50" max="50" customWidth="true" width="16.7181818181818"/>
+    <col min="51" max="51" customWidth="true" width="14.0"/>
+    <col min="52" max="52" customWidth="true" width="19.4272727272727"/>
+    <col min="53" max="53" customWidth="true" width="18.8545454545455"/>
+    <col min="54" max="54" customWidth="true" width="23.2818181818182"/>
+    <col min="55" max="55" customWidth="true" width="15.5727272727273"/>
+    <col min="56" max="56" customWidth="true" width="14.2818181818182"/>
+    <col min="57" max="57" customWidth="true" width="17.0"/>
+    <col min="58" max="58" customWidth="true" width="16.2818181818182"/>
+    <col min="59" max="59" customWidth="true" width="13.5727272727273"/>
+    <col min="60" max="61" customWidth="true" width="12.7181818181818"/>
+    <col min="62" max="62" customWidth="true" width="21.8545454545455"/>
+    <col min="63" max="63" customWidth="true" width="30.5727272727273"/>
+    <col min="64" max="64" customWidth="true" width="10.0"/>
+    <col min="65" max="65" customWidth="true" width="42.5727272727273"/>
+    <col min="66" max="66" customWidth="true" width="38.1454545454545"/>
+    <col min="67" max="67" customWidth="true" width="19.4272727272727"/>
+    <col min="68" max="68" customWidth="true" width="35.4272727272727"/>
+    <col min="69" max="69" customWidth="true" width="9.57272727272727"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -20835,11 +21002,11 @@
       <c r="AT4" s="35" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" t="s">
-        <v>105</v>
-      </c>
-      <c r="AV4" t="s">
-        <v>106</v>
+      <c r="AU4" t="s" s="0">
+        <v>181</v>
+      </c>
+      <c r="AV4" t="s" s="0">
+        <v>182</v>
       </c>
       <c r="AW4" s="35">
         <f>AM4</f>
@@ -20879,11 +21046,11 @@
       <c r="BL4" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="BM4" t="s">
-        <v>107</v>
-      </c>
-      <c r="BN4" t="s">
-        <v>108</v>
+      <c r="BM4" t="s" s="0">
+        <v>184</v>
+      </c>
+      <c r="BN4" t="s" s="0">
+        <v>183</v>
       </c>
       <c r="BO4" s="35">
         <f>ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
@@ -21042,71 +21209,71 @@
   <dimension ref="A1:BQ5"/>
   <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" width="5.14545454545455" customWidth="1"/>
-    <col min="2" max="3" width="25.2818181818182" customWidth="1"/>
-    <col min="4" max="4" width="79.4272727272727" customWidth="1"/>
-    <col min="5" max="5" width="11.5727272727273" customWidth="1"/>
-    <col min="6" max="6" width="5.14545454545455" customWidth="1"/>
-    <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="12.7181818181818" customWidth="1"/>
-    <col min="9" max="9" width="5.85454545454545" customWidth="1"/>
-    <col min="10" max="10" width="6" customWidth="1"/>
-    <col min="11" max="11" width="5.85454545454545" customWidth="1"/>
-    <col min="12" max="12" width="14.2818181818182" customWidth="1"/>
-    <col min="13" max="13" width="9.42727272727273" customWidth="1"/>
-    <col min="14" max="14" width="14.4272727272727" customWidth="1"/>
-    <col min="15" max="15" width="15.5727272727273" customWidth="1"/>
-    <col min="16" max="16" width="14.4272727272727" customWidth="1"/>
-    <col min="17" max="17" width="39.4272727272727" customWidth="1"/>
-    <col min="18" max="18" width="11.7181818181818" customWidth="1"/>
-    <col min="19" max="19" width="11.8545454545455" customWidth="1"/>
-    <col min="20" max="20" width="6.42727272727273" customWidth="1"/>
-    <col min="21" max="22" width="6.57272727272727" customWidth="1"/>
-    <col min="23" max="23" width="37.1454545454545" customWidth="1"/>
-    <col min="24" max="25" width="8" customWidth="1"/>
-    <col min="26" max="26" width="7.71818181818182" customWidth="1"/>
-    <col min="27" max="27" width="6.28181818181818" customWidth="1"/>
-    <col min="28" max="28" width="9.28181818181818" customWidth="1"/>
-    <col min="29" max="29" width="9.71818181818182" customWidth="1"/>
-    <col min="30" max="30" width="12.8545454545455" customWidth="1"/>
-    <col min="31" max="31" width="16.1454545454545" customWidth="1"/>
-    <col min="32" max="32" width="15.4272727272727" customWidth="1"/>
-    <col min="33" max="33" width="24.5727272727273" customWidth="1"/>
-    <col min="34" max="34" width="8.57272727272727" customWidth="1"/>
-    <col min="35" max="35" width="14.7181818181818" customWidth="1"/>
-    <col min="36" max="36" width="18.5727272727273" customWidth="1"/>
-    <col min="37" max="37" width="14.1454545454545" customWidth="1"/>
-    <col min="38" max="38" width="14.7181818181818" customWidth="1"/>
-    <col min="39" max="39" width="17.4272727272727" customWidth="1"/>
-    <col min="40" max="40" width="22" customWidth="1"/>
-    <col min="41" max="41" width="17.5727272727273" customWidth="1"/>
-    <col min="42" max="42" width="25.2818181818182" customWidth="1"/>
-    <col min="43" max="43" width="13" customWidth="1"/>
-    <col min="44" max="44" width="23.7181818181818" customWidth="1"/>
-    <col min="45" max="45" width="10" customWidth="1"/>
-    <col min="46" max="46" width="13" customWidth="1"/>
-    <col min="47" max="47" width="15.5727272727273" customWidth="1"/>
-    <col min="48" max="48" width="21.1454545454545" customWidth="1"/>
-    <col min="49" max="49" width="11.5727272727273" customWidth="1"/>
-    <col min="50" max="50" width="16.7181818181818" customWidth="1"/>
-    <col min="51" max="51" width="14" customWidth="1"/>
-    <col min="52" max="52" width="19.4272727272727" customWidth="1"/>
-    <col min="53" max="53" width="18.8545454545455" customWidth="1"/>
-    <col min="54" max="54" width="23.2818181818182" customWidth="1"/>
-    <col min="55" max="55" width="15.5727272727273" customWidth="1"/>
-    <col min="56" max="56" width="14.2818181818182" customWidth="1"/>
-    <col min="57" max="57" width="17" customWidth="1"/>
-    <col min="58" max="58" width="16.2818181818182" customWidth="1"/>
-    <col min="59" max="59" width="13.5727272727273" customWidth="1"/>
-    <col min="60" max="61" width="12.7181818181818" customWidth="1"/>
-    <col min="62" max="62" width="21.8545454545455" customWidth="1"/>
-    <col min="63" max="63" width="30.5727272727273" customWidth="1"/>
-    <col min="64" max="64" width="10" customWidth="1"/>
-    <col min="65" max="65" width="42.5727272727273" customWidth="1"/>
-    <col min="66" max="66" width="38.1454545454545" customWidth="1"/>
-    <col min="67" max="67" width="19.4272727272727" customWidth="1"/>
-    <col min="68" max="68" width="35.4272727272727" customWidth="1"/>
-    <col min="69" max="69" width="9.57272727272727" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="5.14545454545455"/>
+    <col min="2" max="3" customWidth="true" width="25.2818181818182"/>
+    <col min="4" max="4" customWidth="true" width="79.4272727272727"/>
+    <col min="5" max="5" customWidth="true" width="11.5727272727273"/>
+    <col min="6" max="6" customWidth="true" width="5.14545454545455"/>
+    <col min="7" max="7" customWidth="true" width="11.0"/>
+    <col min="8" max="8" customWidth="true" width="12.7181818181818"/>
+    <col min="9" max="9" customWidth="true" width="5.85454545454545"/>
+    <col min="10" max="10" customWidth="true" width="6.0"/>
+    <col min="11" max="11" customWidth="true" width="5.85454545454545"/>
+    <col min="12" max="12" customWidth="true" width="14.2818181818182"/>
+    <col min="13" max="13" customWidth="true" width="9.42727272727273"/>
+    <col min="14" max="14" customWidth="true" width="14.4272727272727"/>
+    <col min="15" max="15" customWidth="true" width="15.5727272727273"/>
+    <col min="16" max="16" customWidth="true" width="14.4272727272727"/>
+    <col min="17" max="17" customWidth="true" width="39.4272727272727"/>
+    <col min="18" max="18" customWidth="true" width="11.7181818181818"/>
+    <col min="19" max="19" customWidth="true" width="11.8545454545455"/>
+    <col min="20" max="20" customWidth="true" width="6.42727272727273"/>
+    <col min="21" max="22" customWidth="true" width="6.57272727272727"/>
+    <col min="23" max="23" customWidth="true" width="37.1454545454545"/>
+    <col min="24" max="25" customWidth="true" width="8.0"/>
+    <col min="26" max="26" customWidth="true" width="7.71818181818182"/>
+    <col min="27" max="27" customWidth="true" width="6.28181818181818"/>
+    <col min="28" max="28" customWidth="true" width="9.28181818181818"/>
+    <col min="29" max="29" customWidth="true" width="9.71818181818182"/>
+    <col min="30" max="30" customWidth="true" width="12.8545454545455"/>
+    <col min="31" max="31" customWidth="true" width="16.1454545454545"/>
+    <col min="32" max="32" customWidth="true" width="15.4272727272727"/>
+    <col min="33" max="33" customWidth="true" width="24.5727272727273"/>
+    <col min="34" max="34" customWidth="true" width="8.57272727272727"/>
+    <col min="35" max="35" customWidth="true" width="14.7181818181818"/>
+    <col min="36" max="36" customWidth="true" width="18.5727272727273"/>
+    <col min="37" max="37" customWidth="true" width="14.1454545454545"/>
+    <col min="38" max="38" customWidth="true" width="14.7181818181818"/>
+    <col min="39" max="39" customWidth="true" width="17.4272727272727"/>
+    <col min="40" max="40" customWidth="true" width="22.0"/>
+    <col min="41" max="41" customWidth="true" width="17.5727272727273"/>
+    <col min="42" max="42" customWidth="true" width="25.2818181818182"/>
+    <col min="43" max="43" customWidth="true" width="13.0"/>
+    <col min="44" max="44" customWidth="true" width="23.7181818181818"/>
+    <col min="45" max="45" customWidth="true" width="10.0"/>
+    <col min="46" max="46" customWidth="true" width="13.0"/>
+    <col min="47" max="47" customWidth="true" width="15.5727272727273"/>
+    <col min="48" max="48" customWidth="true" width="21.1454545454545"/>
+    <col min="49" max="49" customWidth="true" width="11.5727272727273"/>
+    <col min="50" max="50" customWidth="true" width="16.7181818181818"/>
+    <col min="51" max="51" customWidth="true" width="14.0"/>
+    <col min="52" max="52" customWidth="true" width="19.4272727272727"/>
+    <col min="53" max="53" customWidth="true" width="18.8545454545455"/>
+    <col min="54" max="54" customWidth="true" width="23.2818181818182"/>
+    <col min="55" max="55" customWidth="true" width="15.5727272727273"/>
+    <col min="56" max="56" customWidth="true" width="14.2818181818182"/>
+    <col min="57" max="57" customWidth="true" width="17.0"/>
+    <col min="58" max="58" customWidth="true" width="16.2818181818182"/>
+    <col min="59" max="59" customWidth="true" width="13.5727272727273"/>
+    <col min="60" max="61" customWidth="true" width="12.7181818181818"/>
+    <col min="62" max="62" customWidth="true" width="21.8545454545455"/>
+    <col min="63" max="63" customWidth="true" width="30.5727272727273"/>
+    <col min="64" max="64" customWidth="true" width="10.0"/>
+    <col min="65" max="65" customWidth="true" width="42.5727272727273"/>
+    <col min="66" max="66" customWidth="true" width="38.1454545454545"/>
+    <col min="67" max="67" customWidth="true" width="19.4272727272727"/>
+    <col min="68" max="68" customWidth="true" width="35.4272727272727"/>
+    <col min="69" max="69" customWidth="true" width="9.57272727272727"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -21650,11 +21817,11 @@
       <c r="AT4" s="35" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" t="s">
-        <v>110</v>
-      </c>
-      <c r="AV4" t="s">
-        <v>111</v>
+      <c r="AU4" t="s" s="0">
+        <v>173</v>
+      </c>
+      <c r="AV4" t="s" s="0">
+        <v>185</v>
       </c>
       <c r="AW4" s="35">
         <f>AM4</f>
@@ -21694,11 +21861,11 @@
       <c r="BL4" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="BM4" t="s">
-        <v>112</v>
-      </c>
-      <c r="BN4" t="s">
-        <v>113</v>
+      <c r="BM4" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="BN4" t="s" s="0">
+        <v>186</v>
       </c>
       <c r="BO4" s="35">
         <f>ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
@@ -21845,71 +22012,71 @@
   <dimension ref="A1:BQ5"/>
   <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" width="5.14545454545455" customWidth="1"/>
-    <col min="2" max="3" width="25.5727272727273" customWidth="1"/>
-    <col min="4" max="4" width="79.4272727272727" customWidth="1"/>
-    <col min="5" max="5" width="11.5727272727273" customWidth="1"/>
-    <col min="6" max="6" width="5.14545454545455" customWidth="1"/>
-    <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="12.7181818181818" customWidth="1"/>
-    <col min="9" max="9" width="5.85454545454545" customWidth="1"/>
-    <col min="10" max="10" width="6" customWidth="1"/>
-    <col min="11" max="11" width="5.85454545454545" customWidth="1"/>
-    <col min="12" max="12" width="14.2818181818182" customWidth="1"/>
-    <col min="13" max="13" width="9.42727272727273" customWidth="1"/>
-    <col min="14" max="14" width="14.4272727272727" customWidth="1"/>
-    <col min="15" max="15" width="15.5727272727273" customWidth="1"/>
-    <col min="16" max="16" width="14.4272727272727" customWidth="1"/>
-    <col min="17" max="17" width="39.4272727272727" customWidth="1"/>
-    <col min="18" max="18" width="11.7181818181818" customWidth="1"/>
-    <col min="19" max="19" width="11.8545454545455" customWidth="1"/>
-    <col min="20" max="20" width="6.42727272727273" customWidth="1"/>
-    <col min="21" max="22" width="6.57272727272727" customWidth="1"/>
-    <col min="23" max="23" width="37.1454545454545" customWidth="1"/>
-    <col min="24" max="25" width="8" customWidth="1"/>
-    <col min="26" max="26" width="7.71818181818182" customWidth="1"/>
-    <col min="27" max="27" width="6.28181818181818" customWidth="1"/>
-    <col min="28" max="28" width="9.28181818181818" customWidth="1"/>
-    <col min="29" max="29" width="9.71818181818182" customWidth="1"/>
-    <col min="30" max="30" width="12.8545454545455" customWidth="1"/>
-    <col min="31" max="31" width="16.1454545454545" customWidth="1"/>
-    <col min="32" max="32" width="15.4272727272727" customWidth="1"/>
-    <col min="33" max="33" width="24.5727272727273" customWidth="1"/>
-    <col min="34" max="34" width="8.57272727272727" customWidth="1"/>
-    <col min="35" max="35" width="14.7181818181818" customWidth="1"/>
-    <col min="36" max="36" width="18.5727272727273" customWidth="1"/>
-    <col min="37" max="37" width="14.1454545454545" customWidth="1"/>
-    <col min="38" max="38" width="14.7181818181818" customWidth="1"/>
-    <col min="39" max="39" width="17.4272727272727" customWidth="1"/>
-    <col min="40" max="40" width="22" customWidth="1"/>
-    <col min="41" max="41" width="17.5727272727273" customWidth="1"/>
-    <col min="42" max="42" width="25.2818181818182" customWidth="1"/>
-    <col min="43" max="43" width="13" customWidth="1"/>
-    <col min="44" max="44" width="23.7181818181818" customWidth="1"/>
-    <col min="45" max="45" width="10" customWidth="1"/>
-    <col min="46" max="46" width="13" customWidth="1"/>
-    <col min="47" max="47" width="15.5727272727273" customWidth="1"/>
-    <col min="48" max="48" width="21.1454545454545" customWidth="1"/>
-    <col min="49" max="49" width="11.5727272727273" customWidth="1"/>
-    <col min="50" max="50" width="16.7181818181818" customWidth="1"/>
-    <col min="51" max="51" width="14" customWidth="1"/>
-    <col min="52" max="52" width="19.4272727272727" customWidth="1"/>
-    <col min="53" max="53" width="18.8545454545455" customWidth="1"/>
-    <col min="54" max="54" width="23.2818181818182" customWidth="1"/>
-    <col min="55" max="55" width="15.5727272727273" customWidth="1"/>
-    <col min="56" max="56" width="14.2818181818182" customWidth="1"/>
-    <col min="57" max="57" width="17" customWidth="1"/>
-    <col min="58" max="58" width="16.2818181818182" customWidth="1"/>
-    <col min="59" max="59" width="13.5727272727273" customWidth="1"/>
-    <col min="60" max="61" width="12.7181818181818" customWidth="1"/>
-    <col min="62" max="62" width="21.8545454545455" customWidth="1"/>
-    <col min="63" max="63" width="30.5727272727273" customWidth="1"/>
-    <col min="64" max="64" width="10" customWidth="1"/>
-    <col min="65" max="65" width="42.5727272727273" customWidth="1"/>
-    <col min="66" max="66" width="38.1454545454545" customWidth="1"/>
-    <col min="67" max="67" width="19.4272727272727" customWidth="1"/>
-    <col min="68" max="68" width="35.4272727272727" customWidth="1"/>
-    <col min="69" max="69" width="9.57272727272727" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="5.14545454545455"/>
+    <col min="2" max="3" customWidth="true" width="25.5727272727273"/>
+    <col min="4" max="4" customWidth="true" width="79.4272727272727"/>
+    <col min="5" max="5" customWidth="true" width="11.5727272727273"/>
+    <col min="6" max="6" customWidth="true" width="5.14545454545455"/>
+    <col min="7" max="7" customWidth="true" width="11.0"/>
+    <col min="8" max="8" customWidth="true" width="12.7181818181818"/>
+    <col min="9" max="9" customWidth="true" width="5.85454545454545"/>
+    <col min="10" max="10" customWidth="true" width="6.0"/>
+    <col min="11" max="11" customWidth="true" width="5.85454545454545"/>
+    <col min="12" max="12" customWidth="true" width="14.2818181818182"/>
+    <col min="13" max="13" customWidth="true" width="9.42727272727273"/>
+    <col min="14" max="14" customWidth="true" width="14.4272727272727"/>
+    <col min="15" max="15" customWidth="true" width="15.5727272727273"/>
+    <col min="16" max="16" customWidth="true" width="14.4272727272727"/>
+    <col min="17" max="17" customWidth="true" width="39.4272727272727"/>
+    <col min="18" max="18" customWidth="true" width="11.7181818181818"/>
+    <col min="19" max="19" customWidth="true" width="11.8545454545455"/>
+    <col min="20" max="20" customWidth="true" width="6.42727272727273"/>
+    <col min="21" max="22" customWidth="true" width="6.57272727272727"/>
+    <col min="23" max="23" customWidth="true" width="37.1454545454545"/>
+    <col min="24" max="25" customWidth="true" width="8.0"/>
+    <col min="26" max="26" customWidth="true" width="7.71818181818182"/>
+    <col min="27" max="27" customWidth="true" width="6.28181818181818"/>
+    <col min="28" max="28" customWidth="true" width="9.28181818181818"/>
+    <col min="29" max="29" customWidth="true" width="9.71818181818182"/>
+    <col min="30" max="30" customWidth="true" width="12.8545454545455"/>
+    <col min="31" max="31" customWidth="true" width="16.1454545454545"/>
+    <col min="32" max="32" customWidth="true" width="15.4272727272727"/>
+    <col min="33" max="33" customWidth="true" width="24.5727272727273"/>
+    <col min="34" max="34" customWidth="true" width="8.57272727272727"/>
+    <col min="35" max="35" customWidth="true" width="14.7181818181818"/>
+    <col min="36" max="36" customWidth="true" width="18.5727272727273"/>
+    <col min="37" max="37" customWidth="true" width="14.1454545454545"/>
+    <col min="38" max="38" customWidth="true" width="14.7181818181818"/>
+    <col min="39" max="39" customWidth="true" width="17.4272727272727"/>
+    <col min="40" max="40" customWidth="true" width="22.0"/>
+    <col min="41" max="41" customWidth="true" width="17.5727272727273"/>
+    <col min="42" max="42" customWidth="true" width="25.2818181818182"/>
+    <col min="43" max="43" customWidth="true" width="13.0"/>
+    <col min="44" max="44" customWidth="true" width="23.7181818181818"/>
+    <col min="45" max="45" customWidth="true" width="10.0"/>
+    <col min="46" max="46" customWidth="true" width="13.0"/>
+    <col min="47" max="47" customWidth="true" width="15.5727272727273"/>
+    <col min="48" max="48" customWidth="true" width="21.1454545454545"/>
+    <col min="49" max="49" customWidth="true" width="11.5727272727273"/>
+    <col min="50" max="50" customWidth="true" width="16.7181818181818"/>
+    <col min="51" max="51" customWidth="true" width="14.0"/>
+    <col min="52" max="52" customWidth="true" width="19.4272727272727"/>
+    <col min="53" max="53" customWidth="true" width="18.8545454545455"/>
+    <col min="54" max="54" customWidth="true" width="23.2818181818182"/>
+    <col min="55" max="55" customWidth="true" width="15.5727272727273"/>
+    <col min="56" max="56" customWidth="true" width="14.2818181818182"/>
+    <col min="57" max="57" customWidth="true" width="17.0"/>
+    <col min="58" max="58" customWidth="true" width="16.2818181818182"/>
+    <col min="59" max="59" customWidth="true" width="13.5727272727273"/>
+    <col min="60" max="61" customWidth="true" width="12.7181818181818"/>
+    <col min="62" max="62" customWidth="true" width="21.8545454545455"/>
+    <col min="63" max="63" customWidth="true" width="30.5727272727273"/>
+    <col min="64" max="64" customWidth="true" width="10.0"/>
+    <col min="65" max="65" customWidth="true" width="42.5727272727273"/>
+    <col min="66" max="66" customWidth="true" width="38.1454545454545"/>
+    <col min="67" max="67" customWidth="true" width="19.4272727272727"/>
+    <col min="68" max="68" customWidth="true" width="35.4272727272727"/>
+    <col min="69" max="69" customWidth="true" width="9.57272727272727"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -22644,71 +22811,71 @@
   <dimension ref="A1:BQ5"/>
   <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" width="5.14545454545455" customWidth="1"/>
-    <col min="2" max="3" width="28.2818181818182" customWidth="1"/>
-    <col min="4" max="4" width="79.4272727272727" customWidth="1"/>
-    <col min="5" max="5" width="11.5727272727273" customWidth="1"/>
-    <col min="6" max="6" width="5.14545454545455" customWidth="1"/>
-    <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="12.7181818181818" customWidth="1"/>
-    <col min="9" max="9" width="5.85454545454545" customWidth="1"/>
-    <col min="10" max="10" width="6" customWidth="1"/>
-    <col min="11" max="11" width="5.85454545454545" customWidth="1"/>
-    <col min="12" max="12" width="14.2818181818182" customWidth="1"/>
-    <col min="13" max="13" width="9.42727272727273" customWidth="1"/>
-    <col min="14" max="14" width="14.4272727272727" customWidth="1"/>
-    <col min="15" max="15" width="15.5727272727273" customWidth="1"/>
-    <col min="16" max="16" width="14.4272727272727" customWidth="1"/>
-    <col min="17" max="17" width="39.4272727272727" customWidth="1"/>
-    <col min="18" max="18" width="11.7181818181818" customWidth="1"/>
-    <col min="19" max="19" width="11.8545454545455" customWidth="1"/>
-    <col min="20" max="20" width="6.42727272727273" customWidth="1"/>
-    <col min="21" max="22" width="6.57272727272727" customWidth="1"/>
-    <col min="23" max="23" width="37.1454545454545" customWidth="1"/>
-    <col min="24" max="25" width="8" customWidth="1"/>
-    <col min="26" max="26" width="7.71818181818182" customWidth="1"/>
-    <col min="27" max="27" width="6.28181818181818" customWidth="1"/>
-    <col min="28" max="28" width="9.28181818181818" customWidth="1"/>
-    <col min="29" max="29" width="9.71818181818182" customWidth="1"/>
-    <col min="30" max="30" width="12.8545454545455" customWidth="1"/>
-    <col min="31" max="31" width="16.1454545454545" customWidth="1"/>
-    <col min="32" max="32" width="15.4272727272727" customWidth="1"/>
-    <col min="33" max="33" width="24.5727272727273" customWidth="1"/>
-    <col min="34" max="34" width="8.57272727272727" customWidth="1"/>
-    <col min="35" max="35" width="14.7181818181818" customWidth="1"/>
-    <col min="36" max="36" width="18.5727272727273" customWidth="1"/>
-    <col min="37" max="37" width="14.1454545454545" customWidth="1"/>
-    <col min="38" max="38" width="14.7181818181818" customWidth="1"/>
-    <col min="39" max="39" width="17.4272727272727" customWidth="1"/>
-    <col min="40" max="40" width="22" customWidth="1"/>
-    <col min="41" max="41" width="17.5727272727273" customWidth="1"/>
-    <col min="42" max="42" width="25.2818181818182" customWidth="1"/>
-    <col min="43" max="43" width="13" customWidth="1"/>
-    <col min="44" max="44" width="23.7181818181818" customWidth="1"/>
-    <col min="45" max="45" width="10" customWidth="1"/>
-    <col min="46" max="46" width="13" customWidth="1"/>
-    <col min="47" max="47" width="15.5727272727273" customWidth="1"/>
-    <col min="48" max="48" width="21.1454545454545" customWidth="1"/>
-    <col min="49" max="49" width="11.5727272727273" customWidth="1"/>
-    <col min="50" max="50" width="16.7181818181818" customWidth="1"/>
-    <col min="51" max="51" width="14" customWidth="1"/>
-    <col min="52" max="52" width="19.4272727272727" customWidth="1"/>
-    <col min="53" max="53" width="18.8545454545455" customWidth="1"/>
-    <col min="54" max="54" width="23.2818181818182" customWidth="1"/>
-    <col min="55" max="55" width="15.5727272727273" customWidth="1"/>
-    <col min="56" max="56" width="14.2818181818182" customWidth="1"/>
-    <col min="57" max="57" width="17" customWidth="1"/>
-    <col min="58" max="58" width="16.2818181818182" customWidth="1"/>
-    <col min="59" max="59" width="13.5727272727273" customWidth="1"/>
-    <col min="60" max="61" width="12.7181818181818" customWidth="1"/>
-    <col min="62" max="62" width="21.8545454545455" customWidth="1"/>
-    <col min="63" max="63" width="30.5727272727273" customWidth="1"/>
-    <col min="64" max="64" width="10" customWidth="1"/>
-    <col min="65" max="65" width="42.5727272727273" customWidth="1"/>
-    <col min="66" max="66" width="38.1454545454545" customWidth="1"/>
-    <col min="67" max="67" width="19.4272727272727" customWidth="1"/>
-    <col min="68" max="68" width="35.4272727272727" customWidth="1"/>
-    <col min="69" max="69" width="9.57272727272727" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="5.14545454545455"/>
+    <col min="2" max="3" customWidth="true" width="28.2818181818182"/>
+    <col min="4" max="4" customWidth="true" width="79.4272727272727"/>
+    <col min="5" max="5" customWidth="true" width="11.5727272727273"/>
+    <col min="6" max="6" customWidth="true" width="5.14545454545455"/>
+    <col min="7" max="7" customWidth="true" width="11.0"/>
+    <col min="8" max="8" customWidth="true" width="12.7181818181818"/>
+    <col min="9" max="9" customWidth="true" width="5.85454545454545"/>
+    <col min="10" max="10" customWidth="true" width="6.0"/>
+    <col min="11" max="11" customWidth="true" width="5.85454545454545"/>
+    <col min="12" max="12" customWidth="true" width="14.2818181818182"/>
+    <col min="13" max="13" customWidth="true" width="9.42727272727273"/>
+    <col min="14" max="14" customWidth="true" width="14.4272727272727"/>
+    <col min="15" max="15" customWidth="true" width="15.5727272727273"/>
+    <col min="16" max="16" customWidth="true" width="14.4272727272727"/>
+    <col min="17" max="17" customWidth="true" width="39.4272727272727"/>
+    <col min="18" max="18" customWidth="true" width="11.7181818181818"/>
+    <col min="19" max="19" customWidth="true" width="11.8545454545455"/>
+    <col min="20" max="20" customWidth="true" width="6.42727272727273"/>
+    <col min="21" max="22" customWidth="true" width="6.57272727272727"/>
+    <col min="23" max="23" customWidth="true" width="37.1454545454545"/>
+    <col min="24" max="25" customWidth="true" width="8.0"/>
+    <col min="26" max="26" customWidth="true" width="7.71818181818182"/>
+    <col min="27" max="27" customWidth="true" width="6.28181818181818"/>
+    <col min="28" max="28" customWidth="true" width="9.28181818181818"/>
+    <col min="29" max="29" customWidth="true" width="9.71818181818182"/>
+    <col min="30" max="30" customWidth="true" width="12.8545454545455"/>
+    <col min="31" max="31" customWidth="true" width="16.1454545454545"/>
+    <col min="32" max="32" customWidth="true" width="15.4272727272727"/>
+    <col min="33" max="33" customWidth="true" width="24.5727272727273"/>
+    <col min="34" max="34" customWidth="true" width="8.57272727272727"/>
+    <col min="35" max="35" customWidth="true" width="14.7181818181818"/>
+    <col min="36" max="36" customWidth="true" width="18.5727272727273"/>
+    <col min="37" max="37" customWidth="true" width="14.1454545454545"/>
+    <col min="38" max="38" customWidth="true" width="14.7181818181818"/>
+    <col min="39" max="39" customWidth="true" width="17.4272727272727"/>
+    <col min="40" max="40" customWidth="true" width="22.0"/>
+    <col min="41" max="41" customWidth="true" width="17.5727272727273"/>
+    <col min="42" max="42" customWidth="true" width="25.2818181818182"/>
+    <col min="43" max="43" customWidth="true" width="13.0"/>
+    <col min="44" max="44" customWidth="true" width="23.7181818181818"/>
+    <col min="45" max="45" customWidth="true" width="10.0"/>
+    <col min="46" max="46" customWidth="true" width="13.0"/>
+    <col min="47" max="47" customWidth="true" width="15.5727272727273"/>
+    <col min="48" max="48" customWidth="true" width="21.1454545454545"/>
+    <col min="49" max="49" customWidth="true" width="11.5727272727273"/>
+    <col min="50" max="50" customWidth="true" width="16.7181818181818"/>
+    <col min="51" max="51" customWidth="true" width="14.0"/>
+    <col min="52" max="52" customWidth="true" width="19.4272727272727"/>
+    <col min="53" max="53" customWidth="true" width="18.8545454545455"/>
+    <col min="54" max="54" customWidth="true" width="23.2818181818182"/>
+    <col min="55" max="55" customWidth="true" width="15.5727272727273"/>
+    <col min="56" max="56" customWidth="true" width="14.2818181818182"/>
+    <col min="57" max="57" customWidth="true" width="17.0"/>
+    <col min="58" max="58" customWidth="true" width="16.2818181818182"/>
+    <col min="59" max="59" customWidth="true" width="13.5727272727273"/>
+    <col min="60" max="61" customWidth="true" width="12.7181818181818"/>
+    <col min="62" max="62" customWidth="true" width="21.8545454545455"/>
+    <col min="63" max="63" customWidth="true" width="30.5727272727273"/>
+    <col min="64" max="64" customWidth="true" width="10.0"/>
+    <col min="65" max="65" customWidth="true" width="42.5727272727273"/>
+    <col min="66" max="66" customWidth="true" width="38.1454545454545"/>
+    <col min="67" max="67" customWidth="true" width="19.4272727272727"/>
+    <col min="68" max="68" customWidth="true" width="35.4272727272727"/>
+    <col min="69" max="69" customWidth="true" width="9.57272727272727"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -23252,6 +23419,8 @@
       <c r="AT4" s="35" t="s">
         <v>76</v>
       </c>
+      <c r="AU4" s="0"/>
+      <c r="AV4" s="0"/>
       <c r="AW4" s="35">
         <f>AM4</f>
         <v>4</v>
@@ -23290,10 +23459,10 @@
       <c r="BL4" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="BM4" t="s">
+      <c r="BM4" t="s" s="0">
         <v>100</v>
       </c>
-      <c r="BN4" t="s">
+      <c r="BN4" t="s" s="0">
         <v>100</v>
       </c>
       <c r="BO4" s="35">

--- a/testdata/PoToGRN-FOC Scenarios.xlsx
+++ b/testdata/PoToGRN-FOC Scenarios.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="6920" activeTab="1"/>
+    <workbookView windowWidth="20490" windowHeight="7020" firstSheet="11" activeTab="12"/>
   </bookViews>
   <sheets>
     <sheet name="D-PoToGRNFOCUDGeneralSameUOMWI" sheetId="32" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2742" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2584" uniqueCount="167">
   <si>
     <t>Purchase Order &amp; GRN</t>
   </si>
@@ -292,10 +292,10 @@
     <t>INS WH-1</t>
   </si>
   <si>
-    <t>326</t>
+    <t>630</t>
   </si>
   <si>
-    <t>3858.62995</t>
+    <t>3679.49017</t>
   </si>
   <si>
     <t>Receipt Qty &amp; Unit cost</t>
@@ -313,10 +313,10 @@
     <t>RM WH-49</t>
   </si>
   <si>
-    <t>1729.22114</t>
+    <t>5018.61692</t>
   </si>
   <si>
-    <t>210</t>
+    <t>1118</t>
   </si>
   <si>
     <t>Total</t>
@@ -328,16 +328,13 @@
     <t>GWL_Item_Similar_05_Desc</t>
   </si>
   <si>
-    <t>990</t>
+    <t>2082</t>
   </si>
   <si>
-    <t>2297.6737</t>
+    <t>2982.50151</t>
   </si>
   <si>
-    <t>984.36607</t>
-  </si>
-  <si>
-    <t>458</t>
+    <t>3718</t>
   </si>
   <si>
     <t>VD Asbl. Val.</t>
@@ -370,31 +367,28 @@
     <t>GWL_Item_Similar_Rc_01</t>
   </si>
   <si>
-    <t>211</t>
+    <t>544</t>
   </si>
   <si>
-    <t>1153.87619</t>
+    <t>2121.79328</t>
   </si>
   <si>
-    <t>1032.45735</t>
+    <t>1781.28226</t>
   </si>
   <si>
-    <t>134</t>
+    <t>1783</t>
   </si>
   <si>
     <t>GWL_Item_Similar_Rc_02</t>
   </si>
   <si>
-    <t>184</t>
+    <t>4476.1466</t>
   </si>
   <si>
-    <t>1608.65077</t>
+    <t>3083.62724</t>
   </si>
   <si>
-    <t>1627.48519</t>
-  </si>
-  <si>
-    <t>90</t>
+    <t>1272</t>
   </si>
   <si>
     <t>GWL_Item_Service_Rc_06</t>
@@ -409,31 +403,31 @@
     <t>GWL_Item_Similar_Pl_01</t>
   </si>
   <si>
-    <t>122</t>
+    <t>545</t>
   </si>
   <si>
-    <t>4519.6395</t>
+    <t>8188.3901</t>
   </si>
   <si>
-    <t>2856.39276</t>
+    <t>5322.85475</t>
   </si>
   <si>
-    <t>213</t>
+    <t>1788</t>
   </si>
   <si>
     <t>GWL_Item_Similar_Pl_02</t>
   </si>
   <si>
-    <t>112</t>
+    <t>699</t>
   </si>
   <si>
-    <t>2017.92932</t>
+    <t>4538.80752</t>
   </si>
   <si>
-    <t>1434.63456</t>
+    <t>3167.55516</t>
   </si>
   <si>
-    <t>146</t>
+    <t>1258</t>
   </si>
   <si>
     <t>GWL_Item_Service_Pl_03</t>
@@ -448,31 +442,37 @@
     <t>GWL_Item_Dissimilar_04</t>
   </si>
   <si>
-    <t>46.66</t>
+    <t>211.656</t>
+  </si>
+  <si>
+    <t>13748.09797</t>
   </si>
   <si>
     <t>8607.54384</t>
   </si>
   <si>
-    <t>5800.02511</t>
+    <t>10681.35923</t>
   </si>
   <si>
-    <t>83.998</t>
+    <t>678.991</t>
   </si>
   <si>
     <t>GWL_Item_Dissimilar_05</t>
   </si>
   <si>
-    <t>118.328</t>
+    <t>533.322</t>
+  </si>
+  <si>
+    <t>7162.62564</t>
   </si>
   <si>
     <t>4549.43797</t>
   </si>
   <si>
-    <t>3016.99644</t>
+    <t>5550.52354</t>
   </si>
   <si>
-    <t>172.664</t>
+    <t>1540.992</t>
   </si>
   <si>
     <t>GWL_Dissimilar_St_01</t>
@@ -484,199 +484,19 @@
     <t>GWL_Item_Dissimilar_Rc_01</t>
   </si>
   <si>
-    <t>106.33</t>
-  </si>
-  <si>
-    <t>7864.52145</t>
-  </si>
-  <si>
-    <t>4053.37644</t>
-  </si>
-  <si>
-    <t>121.326</t>
-  </si>
-  <si>
-    <t>GWL_Item_Dissimilar_Rc_02</t>
-  </si>
-  <si>
-    <t>113.328</t>
-  </si>
-  <si>
-    <t>5089.37351</t>
-  </si>
-  <si>
-    <t>2772.09455</t>
-  </si>
-  <si>
-    <t>126.993</t>
-  </si>
-  <si>
-    <t>107.663</t>
-  </si>
-  <si>
-    <t>7770.68065</t>
-  </si>
-  <si>
-    <t>114.661</t>
-  </si>
-  <si>
-    <t>5033.5227</t>
-  </si>
-  <si>
-    <t>GWL_Item_Dissimilar_Pl_01</t>
-  </si>
-  <si>
-    <t>106.664</t>
-  </si>
-  <si>
-    <t>7570.00244</t>
-  </si>
-  <si>
-    <t>3628.55556</t>
-  </si>
-  <si>
-    <t>139.658</t>
-  </si>
-  <si>
-    <t>GWL_Item_Dissimilar_Pl_02</t>
-  </si>
-  <si>
-    <t>152.668</t>
-  </si>
-  <si>
-    <t>4546.36566</t>
-  </si>
-  <si>
-    <t>1899.41182</t>
-  </si>
-  <si>
-    <t>179</t>
-  </si>
-  <si>
-    <t>107.997</t>
-  </si>
-  <si>
-    <t>7480.08709</t>
-  </si>
-  <si>
-    <t>GWL_Item_Dissimilar_Pl_03</t>
-  </si>
-  <si>
-    <t>109.327</t>
-  </si>
-  <si>
-    <t>5747.55068</t>
-  </si>
-  <si>
-    <t>2805.0549</t>
-  </si>
-  <si>
-    <t>161.992</t>
-  </si>
-  <si>
-    <t>630</t>
-  </si>
-  <si>
-    <t>6859.72364</t>
-  </si>
-  <si>
-    <t>1118</t>
-  </si>
-  <si>
-    <t>5018.61692</t>
-  </si>
-  <si>
-    <t>2082</t>
-  </si>
-  <si>
-    <t>3679.49017</t>
-  </si>
-  <si>
-    <t>3718</t>
-  </si>
-  <si>
-    <t>2982.50151</t>
-  </si>
-  <si>
-    <t>544</t>
-  </si>
-  <si>
-    <t>2121.79328</t>
-  </si>
-  <si>
-    <t>1783</t>
-  </si>
-  <si>
-    <t>1781.28226</t>
-  </si>
-  <si>
-    <t>4476.1466</t>
-  </si>
-  <si>
-    <t>1272</t>
-  </si>
-  <si>
-    <t>3083.62724</t>
-  </si>
-  <si>
-    <t>545</t>
-  </si>
-  <si>
-    <t>8188.3901</t>
-  </si>
-  <si>
-    <t>1788</t>
-  </si>
-  <si>
-    <t>5322.85475</t>
-  </si>
-  <si>
-    <t>699</t>
-  </si>
-  <si>
-    <t>4538.80752</t>
-  </si>
-  <si>
-    <t>1258</t>
-  </si>
-  <si>
-    <t>3167.55516</t>
-  </si>
-  <si>
-    <t>211.656</t>
-  </si>
-  <si>
-    <t>13748.09797</t>
-  </si>
-  <si>
-    <t>678.991</t>
-  </si>
-  <si>
-    <t>10681.35923</t>
-  </si>
-  <si>
-    <t>533.322</t>
-  </si>
-  <si>
-    <t>7162.62564</t>
-  </si>
-  <si>
-    <t>1540.992</t>
-  </si>
-  <si>
-    <t>5550.52354</t>
-  </si>
-  <si>
     <t>303.985</t>
   </si>
   <si>
     <t>11450.08032</t>
   </si>
   <si>
+    <t>8534.62923</t>
+  </si>
+  <si>
     <t>833.326</t>
   </si>
   <si>
-    <t>8534.62923</t>
+    <t>GWL_Item_Dissimilar_Rc_02</t>
   </si>
   <si>
     <t>475.65</t>
@@ -685,10 +505,13 @@
     <t>11276.18743</t>
   </si>
   <si>
+    <t>7581.88817</t>
+  </si>
+  <si>
     <t>1146.993</t>
   </si>
   <si>
-    <t>7581.88817</t>
+    <t>GWL_Item_Dissimilar_Pl_01</t>
   </si>
   <si>
     <t>270.987</t>
@@ -697,10 +520,13 @@
     <t>12627.95556</t>
   </si>
   <si>
+    <t>10072.50148</t>
+  </si>
+  <si>
     <t>906.658</t>
   </si>
   <si>
-    <t>10072.50148</t>
+    <t>GWL_Item_Dissimilar_Pl_02</t>
   </si>
   <si>
     <t>467.991</t>
@@ -709,10 +535,13 @@
     <t>9750.1385</t>
   </si>
   <si>
+    <t>6642.66948</t>
+  </si>
+  <si>
     <t>1086</t>
   </si>
   <si>
-    <t>6642.66948</t>
+    <t>GWL_Item_Dissimilar_Pl_03</t>
   </si>
   <si>
     <t>463.327</t>
@@ -721,10 +550,10 @@
     <t>8765.64227</t>
   </si>
   <si>
-    <t>1599.992</t>
+    <t>7754.44104</t>
   </si>
   <si>
-    <t>7754.44104</t>
+    <t>1599.992</t>
   </si>
 </sst>
 </file>
@@ -1866,73 +1695,73 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ5"/>
-  <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="8.7047619047619" defaultRowHeight="15" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="5.14545454545455"/>
-    <col min="2" max="3" customWidth="true" width="20.5727272727273"/>
-    <col min="4" max="4" customWidth="true" width="79.4272727272727"/>
-    <col min="5" max="5" customWidth="true" width="11.5727272727273"/>
-    <col min="6" max="6" customWidth="true" width="5.14545454545455"/>
-    <col min="7" max="7" customWidth="true" width="11.0"/>
-    <col min="8" max="8" customWidth="true" width="12.7181818181818"/>
-    <col min="9" max="10" customWidth="true" width="5.85454545454545"/>
-    <col min="11" max="11" customWidth="true" width="6.0"/>
-    <col min="12" max="12" customWidth="true" width="14.2818181818182"/>
-    <col min="13" max="13" customWidth="true" width="9.42727272727273"/>
-    <col min="14" max="14" customWidth="true" width="14.2818181818182"/>
-    <col min="15" max="15" customWidth="true" width="15.5727272727273"/>
-    <col min="16" max="16" customWidth="true" width="14.4272727272727"/>
-    <col min="17" max="17" customWidth="true" width="39.4272727272727"/>
-    <col min="18" max="18" customWidth="true" width="11.7181818181818"/>
-    <col min="19" max="19" customWidth="true" width="10.0"/>
-    <col min="20" max="20" customWidth="true" width="6.42727272727273"/>
-    <col min="21" max="21" customWidth="true" width="9.85454545454546"/>
-    <col min="22" max="22" customWidth="true" width="6.57272727272727"/>
-    <col min="23" max="23" customWidth="true" width="37.1454545454545"/>
-    <col min="24" max="25" customWidth="true" width="8.0"/>
-    <col min="26" max="26" customWidth="true" width="7.71818181818182"/>
-    <col min="27" max="27" customWidth="true" width="6.28181818181818"/>
-    <col min="28" max="28" customWidth="true" width="9.28181818181818"/>
-    <col min="29" max="29" customWidth="true" width="9.71818181818182"/>
-    <col min="30" max="30" customWidth="true" width="12.8545454545455"/>
-    <col min="31" max="31" customWidth="true" width="16.1454545454545"/>
-    <col min="32" max="32" customWidth="true" width="15.4272727272727"/>
-    <col min="33" max="33" customWidth="true" width="24.5727272727273"/>
-    <col min="34" max="34" customWidth="true" width="8.57272727272727"/>
-    <col min="35" max="35" customWidth="true" width="14.7181818181818"/>
-    <col min="36" max="36" customWidth="true" width="18.5727272727273"/>
-    <col min="37" max="37" customWidth="true" width="14.1454545454545"/>
-    <col min="38" max="38" customWidth="true" width="14.7181818181818"/>
-    <col min="39" max="39" customWidth="true" width="17.4272727272727"/>
-    <col min="40" max="40" customWidth="true" width="22.0"/>
-    <col min="41" max="41" customWidth="true" width="17.5727272727273"/>
-    <col min="42" max="42" customWidth="true" width="25.2818181818182"/>
-    <col min="43" max="43" customWidth="true" width="13.0"/>
-    <col min="44" max="44" customWidth="true" width="25.7181818181818"/>
-    <col min="45" max="45" customWidth="true" width="10.0"/>
-    <col min="46" max="46" customWidth="true" width="13.0"/>
-    <col min="47" max="47" customWidth="true" width="15.5727272727273"/>
-    <col min="48" max="48" customWidth="true" width="21.1454545454545"/>
-    <col min="49" max="49" customWidth="true" width="11.5727272727273"/>
-    <col min="50" max="50" customWidth="true" width="16.7181818181818"/>
-    <col min="51" max="51" customWidth="true" width="14.0"/>
-    <col min="52" max="52" customWidth="true" width="19.4272727272727"/>
-    <col min="53" max="53" customWidth="true" width="18.8545454545455"/>
-    <col min="54" max="54" customWidth="true" width="23.2818181818182"/>
-    <col min="55" max="55" customWidth="true" width="15.5727272727273"/>
-    <col min="56" max="56" customWidth="true" width="14.2818181818182"/>
-    <col min="57" max="57" customWidth="true" width="17.0"/>
-    <col min="58" max="58" customWidth="true" width="16.2818181818182"/>
-    <col min="59" max="59" customWidth="true" width="13.5727272727273"/>
-    <col min="60" max="61" customWidth="true" width="12.7181818181818"/>
-    <col min="62" max="62" customWidth="true" width="21.8545454545455"/>
-    <col min="63" max="63" customWidth="true" width="30.5727272727273"/>
-    <col min="64" max="64" customWidth="true" width="10.0"/>
-    <col min="65" max="65" customWidth="true" width="42.5727272727273"/>
-    <col min="66" max="66" customWidth="true" width="38.1454545454545"/>
-    <col min="67" max="67" customWidth="true" width="19.4272727272727"/>
-    <col min="68" max="68" customWidth="true" width="35.4272727272727"/>
-    <col min="69" max="69" customWidth="true" width="9.57272727272727"/>
+    <col min="1" max="1" width="5.14285714285714" customWidth="1"/>
+    <col min="2" max="3" width="20.5714285714286" customWidth="1"/>
+    <col min="4" max="4" width="79.4285714285714" customWidth="1"/>
+    <col min="5" max="5" width="11.5714285714286" customWidth="1"/>
+    <col min="6" max="6" width="5.14285714285714" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="12.7142857142857" customWidth="1"/>
+    <col min="9" max="10" width="5.85714285714286" customWidth="1"/>
+    <col min="11" max="11" width="6" customWidth="1"/>
+    <col min="12" max="12" width="14.2857142857143" customWidth="1"/>
+    <col min="13" max="13" width="9.42857142857143" customWidth="1"/>
+    <col min="14" max="14" width="14.2857142857143" customWidth="1"/>
+    <col min="15" max="15" width="15.5714285714286" customWidth="1"/>
+    <col min="16" max="16" width="14.4285714285714" customWidth="1"/>
+    <col min="17" max="17" width="39.4285714285714" customWidth="1"/>
+    <col min="18" max="18" width="11.7142857142857" customWidth="1"/>
+    <col min="19" max="19" width="10" customWidth="1"/>
+    <col min="20" max="20" width="6.42857142857143" customWidth="1"/>
+    <col min="21" max="21" width="9.85714285714286" customWidth="1"/>
+    <col min="22" max="22" width="6.57142857142857" customWidth="1"/>
+    <col min="23" max="23" width="37.1428571428571" customWidth="1"/>
+    <col min="24" max="25" width="8" customWidth="1"/>
+    <col min="26" max="26" width="7.71428571428571" customWidth="1"/>
+    <col min="27" max="27" width="6.28571428571429" customWidth="1"/>
+    <col min="28" max="28" width="9.28571428571429" customWidth="1"/>
+    <col min="29" max="29" width="9.71428571428571" customWidth="1"/>
+    <col min="30" max="30" width="12.8571428571429" customWidth="1"/>
+    <col min="31" max="31" width="16.1428571428571" customWidth="1"/>
+    <col min="32" max="32" width="15.4285714285714" customWidth="1"/>
+    <col min="33" max="33" width="24.5714285714286" customWidth="1"/>
+    <col min="34" max="34" width="8.57142857142857" customWidth="1"/>
+    <col min="35" max="35" width="14.7142857142857" customWidth="1"/>
+    <col min="36" max="36" width="18.5714285714286" customWidth="1"/>
+    <col min="37" max="37" width="14.1428571428571" customWidth="1"/>
+    <col min="38" max="38" width="14.7142857142857" customWidth="1"/>
+    <col min="39" max="39" width="17.4285714285714" customWidth="1"/>
+    <col min="40" max="40" width="22" customWidth="1"/>
+    <col min="41" max="41" width="17.5714285714286" customWidth="1"/>
+    <col min="42" max="42" width="25.2857142857143" customWidth="1"/>
+    <col min="43" max="43" width="13" customWidth="1"/>
+    <col min="44" max="44" width="25.7142857142857" customWidth="1"/>
+    <col min="45" max="45" width="10" customWidth="1"/>
+    <col min="46" max="46" width="13" customWidth="1"/>
+    <col min="47" max="47" width="15.5714285714286" customWidth="1"/>
+    <col min="48" max="48" width="21.1428571428571" customWidth="1"/>
+    <col min="49" max="49" width="11.5714285714286" customWidth="1"/>
+    <col min="50" max="50" width="16.7142857142857" customWidth="1"/>
+    <col min="51" max="51" width="14" customWidth="1"/>
+    <col min="52" max="52" width="19.4285714285714" customWidth="1"/>
+    <col min="53" max="53" width="18.8571428571429" customWidth="1"/>
+    <col min="54" max="54" width="23.2857142857143" customWidth="1"/>
+    <col min="55" max="55" width="15.5714285714286" customWidth="1"/>
+    <col min="56" max="56" width="14.2857142857143" customWidth="1"/>
+    <col min="57" max="57" width="17" customWidth="1"/>
+    <col min="58" max="58" width="16.2857142857143" customWidth="1"/>
+    <col min="59" max="59" width="13.5714285714286" customWidth="1"/>
+    <col min="60" max="61" width="12.7142857142857" customWidth="1"/>
+    <col min="62" max="62" width="21.8571428571429" customWidth="1"/>
+    <col min="63" max="63" width="30.5714285714286" customWidth="1"/>
+    <col min="64" max="64" width="10" customWidth="1"/>
+    <col min="65" max="65" width="42.5714285714286" customWidth="1"/>
+    <col min="66" max="66" width="38.1428571428571" customWidth="1"/>
+    <col min="67" max="67" width="19.4285714285714" customWidth="1"/>
+    <col min="68" max="68" width="35.4285714285714" customWidth="1"/>
+    <col min="69" max="69" width="9.57142857142857" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -2103,7 +1932,7 @@
       <c r="BP2" s="27"/>
       <c r="BQ2" s="27"/>
     </row>
-    <row r="3" ht="15.25" spans="1:69">
+    <row r="3" ht="15.75" spans="1:69">
       <c r="A3" s="28" t="s">
         <v>9</v>
       </c>
@@ -2312,7 +2141,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.25" spans="1:69">
+    <row r="4" ht="15.75" spans="1:69">
       <c r="A4" s="26">
         <v>1</v>
       </c>
@@ -2476,11 +2305,11 @@
       <c r="AT4" s="35" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" t="s" s="0">
-        <v>173</v>
-      </c>
-      <c r="AV4" t="s" s="0">
-        <v>174</v>
+      <c r="AU4" t="s">
+        <v>79</v>
+      </c>
+      <c r="AV4" t="s">
+        <v>80</v>
       </c>
       <c r="AW4" s="35">
         <f>AM4</f>
@@ -2494,8 +2323,9 @@
         <f>AU4+AW4</f>
         <v>4</v>
       </c>
-      <c r="AZ4" t="s" s="0">
-        <v>80</v>
+      <c r="AZ4">
+        <f>ROUND(((AU4*AV4)+(AW4*AX4))/(AU4+AW4),5)</f>
+        <v>3658.67522</v>
       </c>
       <c r="BA4" s="36"/>
       <c r="BB4" s="36" t="s">
@@ -2519,15 +2349,15 @@
       <c r="BL4" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="BM4" t="s" s="0">
-        <v>176</v>
-      </c>
-      <c r="BN4" t="s" s="0">
-        <v>175</v>
+      <c r="BM4" t="s">
+        <v>86</v>
+      </c>
+      <c r="BN4" t="s">
+        <v>87</v>
       </c>
       <c r="BO4" s="35">
         <f>ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
-        <v>0</v>
+        <v>5013.76864</v>
       </c>
       <c r="BP4" s="36">
         <f>BN4+AW4</f>
@@ -2680,73 +2510,73 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ5"/>
-  <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="8.7047619047619" defaultRowHeight="15" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="5.14545454545455"/>
-    <col min="2" max="3" customWidth="true" width="28.2818181818182"/>
-    <col min="4" max="4" customWidth="true" width="79.4272727272727"/>
-    <col min="5" max="5" customWidth="true" width="11.5727272727273"/>
-    <col min="6" max="6" customWidth="true" width="5.14545454545455"/>
-    <col min="7" max="7" customWidth="true" width="11.0"/>
-    <col min="8" max="8" customWidth="true" width="12.7181818181818"/>
-    <col min="9" max="9" customWidth="true" width="5.85454545454545"/>
-    <col min="10" max="10" customWidth="true" width="6.0"/>
-    <col min="11" max="11" customWidth="true" width="5.85454545454545"/>
-    <col min="12" max="12" customWidth="true" width="14.2818181818182"/>
-    <col min="13" max="13" customWidth="true" width="9.42727272727273"/>
-    <col min="14" max="14" customWidth="true" width="14.4272727272727"/>
-    <col min="15" max="15" customWidth="true" width="15.5727272727273"/>
-    <col min="16" max="16" customWidth="true" width="14.4272727272727"/>
-    <col min="17" max="17" customWidth="true" width="39.4272727272727"/>
-    <col min="18" max="18" customWidth="true" width="11.7181818181818"/>
-    <col min="19" max="19" customWidth="true" width="11.8545454545455"/>
-    <col min="20" max="20" customWidth="true" width="6.42727272727273"/>
-    <col min="21" max="22" customWidth="true" width="6.57272727272727"/>
-    <col min="23" max="23" customWidth="true" width="37.1454545454545"/>
-    <col min="24" max="25" customWidth="true" width="8.0"/>
-    <col min="26" max="26" customWidth="true" width="7.71818181818182"/>
-    <col min="27" max="27" customWidth="true" width="6.28181818181818"/>
-    <col min="28" max="28" customWidth="true" width="9.28181818181818"/>
-    <col min="29" max="29" customWidth="true" width="9.71818181818182"/>
-    <col min="30" max="30" customWidth="true" width="12.8545454545455"/>
-    <col min="31" max="31" customWidth="true" width="16.1454545454545"/>
-    <col min="32" max="32" customWidth="true" width="15.4272727272727"/>
-    <col min="33" max="33" customWidth="true" width="24.5727272727273"/>
-    <col min="34" max="34" customWidth="true" width="8.57272727272727"/>
-    <col min="35" max="35" customWidth="true" width="14.7181818181818"/>
-    <col min="36" max="36" customWidth="true" width="18.5727272727273"/>
-    <col min="37" max="37" customWidth="true" width="14.1454545454545"/>
-    <col min="38" max="38" customWidth="true" width="14.7181818181818"/>
-    <col min="39" max="39" customWidth="true" width="17.4272727272727"/>
-    <col min="40" max="40" customWidth="true" width="22.0"/>
-    <col min="41" max="41" customWidth="true" width="17.5727272727273"/>
-    <col min="42" max="42" customWidth="true" width="25.2818181818182"/>
-    <col min="43" max="43" customWidth="true" width="13.0"/>
-    <col min="44" max="44" customWidth="true" width="23.7181818181818"/>
-    <col min="45" max="45" customWidth="true" width="10.0"/>
-    <col min="46" max="46" customWidth="true" width="13.0"/>
-    <col min="47" max="47" customWidth="true" width="15.5727272727273"/>
-    <col min="48" max="48" customWidth="true" width="21.1454545454545"/>
-    <col min="49" max="49" customWidth="true" width="11.5727272727273"/>
-    <col min="50" max="50" customWidth="true" width="16.7181818181818"/>
-    <col min="51" max="51" customWidth="true" width="14.0"/>
-    <col min="52" max="52" customWidth="true" width="19.4272727272727"/>
-    <col min="53" max="53" customWidth="true" width="18.8545454545455"/>
-    <col min="54" max="54" customWidth="true" width="23.2818181818182"/>
-    <col min="55" max="55" customWidth="true" width="15.5727272727273"/>
-    <col min="56" max="56" customWidth="true" width="14.2818181818182"/>
-    <col min="57" max="57" customWidth="true" width="17.0"/>
-    <col min="58" max="58" customWidth="true" width="16.2818181818182"/>
-    <col min="59" max="59" customWidth="true" width="13.5727272727273"/>
-    <col min="60" max="61" customWidth="true" width="12.7181818181818"/>
-    <col min="62" max="62" customWidth="true" width="21.8545454545455"/>
-    <col min="63" max="63" customWidth="true" width="30.5727272727273"/>
-    <col min="64" max="64" customWidth="true" width="10.0"/>
-    <col min="65" max="65" customWidth="true" width="42.5727272727273"/>
-    <col min="66" max="66" customWidth="true" width="38.1454545454545"/>
-    <col min="67" max="67" customWidth="true" width="19.4272727272727"/>
-    <col min="68" max="68" customWidth="true" width="35.4272727272727"/>
-    <col min="69" max="69" customWidth="true" width="9.57272727272727"/>
+    <col min="1" max="1" width="5.14285714285714" customWidth="1"/>
+    <col min="2" max="3" width="28.2857142857143" customWidth="1"/>
+    <col min="4" max="4" width="79.4285714285714" customWidth="1"/>
+    <col min="5" max="5" width="11.5714285714286" customWidth="1"/>
+    <col min="6" max="6" width="5.14285714285714" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="12.7142857142857" customWidth="1"/>
+    <col min="9" max="9" width="5.85714285714286" customWidth="1"/>
+    <col min="10" max="10" width="6" customWidth="1"/>
+    <col min="11" max="11" width="5.85714285714286" customWidth="1"/>
+    <col min="12" max="12" width="14.2857142857143" customWidth="1"/>
+    <col min="13" max="13" width="9.42857142857143" customWidth="1"/>
+    <col min="14" max="14" width="14.4285714285714" customWidth="1"/>
+    <col min="15" max="15" width="15.5714285714286" customWidth="1"/>
+    <col min="16" max="16" width="14.4285714285714" customWidth="1"/>
+    <col min="17" max="17" width="39.4285714285714" customWidth="1"/>
+    <col min="18" max="18" width="11.7142857142857" customWidth="1"/>
+    <col min="19" max="19" width="11.8571428571429" customWidth="1"/>
+    <col min="20" max="20" width="6.42857142857143" customWidth="1"/>
+    <col min="21" max="22" width="6.57142857142857" customWidth="1"/>
+    <col min="23" max="23" width="37.1428571428571" customWidth="1"/>
+    <col min="24" max="25" width="8" customWidth="1"/>
+    <col min="26" max="26" width="7.71428571428571" customWidth="1"/>
+    <col min="27" max="27" width="6.28571428571429" customWidth="1"/>
+    <col min="28" max="28" width="9.28571428571429" customWidth="1"/>
+    <col min="29" max="29" width="9.71428571428571" customWidth="1"/>
+    <col min="30" max="30" width="12.8571428571429" customWidth="1"/>
+    <col min="31" max="31" width="16.1428571428571" customWidth="1"/>
+    <col min="32" max="32" width="15.4285714285714" customWidth="1"/>
+    <col min="33" max="33" width="24.5714285714286" customWidth="1"/>
+    <col min="34" max="34" width="8.57142857142857" customWidth="1"/>
+    <col min="35" max="35" width="14.7142857142857" customWidth="1"/>
+    <col min="36" max="36" width="18.5714285714286" customWidth="1"/>
+    <col min="37" max="37" width="14.1428571428571" customWidth="1"/>
+    <col min="38" max="38" width="14.7142857142857" customWidth="1"/>
+    <col min="39" max="39" width="17.4285714285714" customWidth="1"/>
+    <col min="40" max="40" width="22" customWidth="1"/>
+    <col min="41" max="41" width="17.5714285714286" customWidth="1"/>
+    <col min="42" max="42" width="25.2857142857143" customWidth="1"/>
+    <col min="43" max="43" width="13" customWidth="1"/>
+    <col min="44" max="44" width="23.7142857142857" customWidth="1"/>
+    <col min="45" max="45" width="10" customWidth="1"/>
+    <col min="46" max="46" width="13" customWidth="1"/>
+    <col min="47" max="47" width="15.5714285714286" customWidth="1"/>
+    <col min="48" max="48" width="21.1428571428571" customWidth="1"/>
+    <col min="49" max="49" width="11.5714285714286" customWidth="1"/>
+    <col min="50" max="50" width="16.7142857142857" customWidth="1"/>
+    <col min="51" max="51" width="14" customWidth="1"/>
+    <col min="52" max="52" width="19.4285714285714" customWidth="1"/>
+    <col min="53" max="53" width="18.8571428571429" customWidth="1"/>
+    <col min="54" max="54" width="23.2857142857143" customWidth="1"/>
+    <col min="55" max="55" width="15.5714285714286" customWidth="1"/>
+    <col min="56" max="56" width="14.2857142857143" customWidth="1"/>
+    <col min="57" max="57" width="17" customWidth="1"/>
+    <col min="58" max="58" width="16.2857142857143" customWidth="1"/>
+    <col min="59" max="59" width="13.5714285714286" customWidth="1"/>
+    <col min="60" max="61" width="12.7142857142857" customWidth="1"/>
+    <col min="62" max="62" width="21.8571428571429" customWidth="1"/>
+    <col min="63" max="63" width="30.5714285714286" customWidth="1"/>
+    <col min="64" max="64" width="10" customWidth="1"/>
+    <col min="65" max="65" width="42.5714285714286" customWidth="1"/>
+    <col min="66" max="66" width="38.1428571428571" customWidth="1"/>
+    <col min="67" max="67" width="19.4285714285714" customWidth="1"/>
+    <col min="68" max="68" width="35.4285714285714" customWidth="1"/>
+    <col min="69" max="69" width="9.57142857142857" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -2917,7 +2747,7 @@
       <c r="BP2" s="27"/>
       <c r="BQ2" s="27"/>
     </row>
-    <row r="3" ht="15.25" spans="1:69">
+    <row r="3" ht="15.75" spans="1:69">
       <c r="A3" s="28" t="s">
         <v>9</v>
       </c>
@@ -2964,7 +2794,7 @@
         <v>25</v>
       </c>
       <c r="P3" s="30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="Q3" s="30" t="s">
         <v>23</v>
@@ -2973,13 +2803,13 @@
         <v>26</v>
       </c>
       <c r="S3" s="28" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="T3" s="28" t="s">
         <v>28</v>
       </c>
       <c r="U3" s="31" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="V3" s="31" t="s">
         <v>30</v>
@@ -3048,7 +2878,7 @@
         <v>51</v>
       </c>
       <c r="AR3" s="33" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AS3" s="28" t="s">
         <v>53</v>
@@ -3126,15 +2956,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.25" spans="1:69">
+    <row r="4" ht="15.75" spans="1:69">
       <c r="A4" s="26">
         <v>1</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C4" s="26" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D4" s="26" t="s">
         <v>76</v>
@@ -3153,7 +2983,7 @@
         <v>400</v>
       </c>
       <c r="I4" s="27" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J4" s="35">
         <v>2</v>
@@ -3290,8 +3120,6 @@
       <c r="AT4" s="35" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" s="0"/>
-      <c r="AV4" s="0"/>
       <c r="AW4" s="35">
         <f>AM4</f>
         <v>4</v>
@@ -3330,11 +3158,11 @@
       <c r="BL4" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="BM4" t="s" s="0">
-        <v>100</v>
-      </c>
-      <c r="BN4" t="s" s="0">
-        <v>100</v>
+      <c r="BM4" t="s">
+        <v>99</v>
+      </c>
+      <c r="BN4" t="s">
+        <v>99</v>
       </c>
       <c r="BO4" s="35">
         <f>ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
@@ -3479,73 +3307,73 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ5"/>
-  <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="8.7047619047619" defaultRowHeight="15" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="5.14545454545455"/>
-    <col min="2" max="3" customWidth="true" width="24.7181818181818"/>
-    <col min="4" max="4" customWidth="true" width="79.4272727272727"/>
-    <col min="5" max="5" customWidth="true" width="11.5727272727273"/>
-    <col min="6" max="6" customWidth="true" width="5.14545454545455"/>
-    <col min="7" max="7" customWidth="true" width="11.0"/>
-    <col min="8" max="8" customWidth="true" width="12.7181818181818"/>
-    <col min="9" max="9" customWidth="true" width="5.85454545454545"/>
-    <col min="10" max="10" customWidth="true" width="6.0"/>
-    <col min="11" max="11" customWidth="true" width="5.85454545454545"/>
-    <col min="12" max="12" customWidth="true" width="14.2818181818182"/>
-    <col min="13" max="13" customWidth="true" width="9.42727272727273"/>
-    <col min="14" max="14" customWidth="true" width="14.4272727272727"/>
-    <col min="15" max="15" customWidth="true" width="15.5727272727273"/>
-    <col min="16" max="16" customWidth="true" width="14.4272727272727"/>
-    <col min="17" max="17" customWidth="true" width="39.4272727272727"/>
-    <col min="18" max="18" customWidth="true" width="11.7181818181818"/>
-    <col min="19" max="19" customWidth="true" width="11.8545454545455"/>
-    <col min="20" max="20" customWidth="true" width="6.42727272727273"/>
-    <col min="21" max="22" customWidth="true" width="6.57272727272727"/>
-    <col min="23" max="23" customWidth="true" width="37.1454545454545"/>
-    <col min="24" max="25" customWidth="true" width="8.0"/>
-    <col min="26" max="26" customWidth="true" width="7.71818181818182"/>
-    <col min="27" max="27" customWidth="true" width="6.28181818181818"/>
-    <col min="28" max="28" customWidth="true" width="9.28181818181818"/>
-    <col min="29" max="29" customWidth="true" width="9.71818181818182"/>
-    <col min="30" max="30" customWidth="true" width="12.8545454545455"/>
-    <col min="31" max="31" customWidth="true" width="16.1454545454545"/>
-    <col min="32" max="32" customWidth="true" width="15.4272727272727"/>
-    <col min="33" max="33" customWidth="true" width="24.5727272727273"/>
-    <col min="34" max="34" customWidth="true" width="8.57272727272727"/>
-    <col min="35" max="35" customWidth="true" width="14.7181818181818"/>
-    <col min="36" max="36" customWidth="true" width="18.5727272727273"/>
-    <col min="37" max="37" customWidth="true" width="14.1454545454545"/>
-    <col min="38" max="38" customWidth="true" width="14.7181818181818"/>
-    <col min="39" max="39" customWidth="true" width="17.4272727272727"/>
-    <col min="40" max="40" customWidth="true" width="22.0"/>
-    <col min="41" max="41" customWidth="true" width="17.5727272727273"/>
-    <col min="42" max="42" customWidth="true" width="25.2818181818182"/>
-    <col min="43" max="43" customWidth="true" width="13.0"/>
-    <col min="44" max="44" customWidth="true" width="23.7181818181818"/>
-    <col min="45" max="45" customWidth="true" width="10.0"/>
-    <col min="46" max="46" customWidth="true" width="13.0"/>
-    <col min="47" max="47" customWidth="true" width="15.5727272727273"/>
-    <col min="48" max="48" customWidth="true" width="21.1454545454545"/>
-    <col min="49" max="49" customWidth="true" width="11.5727272727273"/>
-    <col min="50" max="50" customWidth="true" width="16.7181818181818"/>
-    <col min="51" max="51" customWidth="true" width="14.0"/>
-    <col min="52" max="52" customWidth="true" width="19.4272727272727"/>
-    <col min="53" max="53" customWidth="true" width="18.8545454545455"/>
-    <col min="54" max="54" customWidth="true" width="23.2818181818182"/>
-    <col min="55" max="55" customWidth="true" width="15.5727272727273"/>
-    <col min="56" max="56" customWidth="true" width="14.2818181818182"/>
-    <col min="57" max="57" customWidth="true" width="17.0"/>
-    <col min="58" max="58" customWidth="true" width="16.2818181818182"/>
-    <col min="59" max="59" customWidth="true" width="13.5727272727273"/>
-    <col min="60" max="61" customWidth="true" width="12.7181818181818"/>
-    <col min="62" max="62" customWidth="true" width="21.8545454545455"/>
-    <col min="63" max="63" customWidth="true" width="30.5727272727273"/>
-    <col min="64" max="64" customWidth="true" width="10.0"/>
-    <col min="65" max="65" customWidth="true" width="42.5727272727273"/>
-    <col min="66" max="66" customWidth="true" width="38.1454545454545"/>
-    <col min="67" max="67" customWidth="true" width="19.4272727272727"/>
-    <col min="68" max="68" customWidth="true" width="35.4272727272727"/>
-    <col min="69" max="69" customWidth="true" width="9.57272727272727"/>
+    <col min="1" max="1" width="5.14285714285714" customWidth="1"/>
+    <col min="2" max="3" width="24.7142857142857" customWidth="1"/>
+    <col min="4" max="4" width="79.4285714285714" customWidth="1"/>
+    <col min="5" max="5" width="11.5714285714286" customWidth="1"/>
+    <col min="6" max="6" width="5.14285714285714" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="12.7142857142857" customWidth="1"/>
+    <col min="9" max="9" width="5.85714285714286" customWidth="1"/>
+    <col min="10" max="10" width="6" customWidth="1"/>
+    <col min="11" max="11" width="5.85714285714286" customWidth="1"/>
+    <col min="12" max="12" width="14.2857142857143" customWidth="1"/>
+    <col min="13" max="13" width="9.42857142857143" customWidth="1"/>
+    <col min="14" max="14" width="14.4285714285714" customWidth="1"/>
+    <col min="15" max="15" width="15.5714285714286" customWidth="1"/>
+    <col min="16" max="16" width="14.4285714285714" customWidth="1"/>
+    <col min="17" max="17" width="39.4285714285714" customWidth="1"/>
+    <col min="18" max="18" width="11.7142857142857" customWidth="1"/>
+    <col min="19" max="19" width="11.8571428571429" customWidth="1"/>
+    <col min="20" max="20" width="6.42857142857143" customWidth="1"/>
+    <col min="21" max="22" width="6.57142857142857" customWidth="1"/>
+    <col min="23" max="23" width="37.1428571428571" customWidth="1"/>
+    <col min="24" max="25" width="8" customWidth="1"/>
+    <col min="26" max="26" width="7.71428571428571" customWidth="1"/>
+    <col min="27" max="27" width="6.28571428571429" customWidth="1"/>
+    <col min="28" max="28" width="9.28571428571429" customWidth="1"/>
+    <col min="29" max="29" width="9.71428571428571" customWidth="1"/>
+    <col min="30" max="30" width="12.8571428571429" customWidth="1"/>
+    <col min="31" max="31" width="16.1428571428571" customWidth="1"/>
+    <col min="32" max="32" width="15.4285714285714" customWidth="1"/>
+    <col min="33" max="33" width="24.5714285714286" customWidth="1"/>
+    <col min="34" max="34" width="8.57142857142857" customWidth="1"/>
+    <col min="35" max="35" width="14.7142857142857" customWidth="1"/>
+    <col min="36" max="36" width="18.5714285714286" customWidth="1"/>
+    <col min="37" max="37" width="14.1428571428571" customWidth="1"/>
+    <col min="38" max="38" width="14.7142857142857" customWidth="1"/>
+    <col min="39" max="39" width="17.4285714285714" customWidth="1"/>
+    <col min="40" max="40" width="22" customWidth="1"/>
+    <col min="41" max="41" width="17.5714285714286" customWidth="1"/>
+    <col min="42" max="42" width="25.2857142857143" customWidth="1"/>
+    <col min="43" max="43" width="13" customWidth="1"/>
+    <col min="44" max="44" width="23.7142857142857" customWidth="1"/>
+    <col min="45" max="45" width="10" customWidth="1"/>
+    <col min="46" max="46" width="13" customWidth="1"/>
+    <col min="47" max="47" width="15.5714285714286" customWidth="1"/>
+    <col min="48" max="48" width="21.1428571428571" customWidth="1"/>
+    <col min="49" max="49" width="11.5714285714286" customWidth="1"/>
+    <col min="50" max="50" width="16.7142857142857" customWidth="1"/>
+    <col min="51" max="51" width="14" customWidth="1"/>
+    <col min="52" max="52" width="19.4285714285714" customWidth="1"/>
+    <col min="53" max="53" width="18.8571428571429" customWidth="1"/>
+    <col min="54" max="54" width="23.2857142857143" customWidth="1"/>
+    <col min="55" max="55" width="15.5714285714286" customWidth="1"/>
+    <col min="56" max="56" width="14.2857142857143" customWidth="1"/>
+    <col min="57" max="57" width="17" customWidth="1"/>
+    <col min="58" max="58" width="16.2857142857143" customWidth="1"/>
+    <col min="59" max="59" width="13.5714285714286" customWidth="1"/>
+    <col min="60" max="61" width="12.7142857142857" customWidth="1"/>
+    <col min="62" max="62" width="21.8571428571429" customWidth="1"/>
+    <col min="63" max="63" width="30.5714285714286" customWidth="1"/>
+    <col min="64" max="64" width="10" customWidth="1"/>
+    <col min="65" max="65" width="42.5714285714286" customWidth="1"/>
+    <col min="66" max="66" width="38.1428571428571" customWidth="1"/>
+    <col min="67" max="67" width="19.4285714285714" customWidth="1"/>
+    <col min="68" max="68" width="35.4285714285714" customWidth="1"/>
+    <col min="69" max="69" width="9.57142857142857" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -3716,7 +3544,7 @@
       <c r="BP2" s="27"/>
       <c r="BQ2" s="27"/>
     </row>
-    <row r="3" ht="15.25" spans="1:69">
+    <row r="3" ht="15.75" spans="1:69">
       <c r="A3" s="28" t="s">
         <v>9</v>
       </c>
@@ -3763,7 +3591,7 @@
         <v>25</v>
       </c>
       <c r="P3" s="30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="Q3" s="30" t="s">
         <v>23</v>
@@ -3772,13 +3600,13 @@
         <v>26</v>
       </c>
       <c r="S3" s="28" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="T3" s="28" t="s">
         <v>28</v>
       </c>
       <c r="U3" s="31" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="V3" s="31" t="s">
         <v>30</v>
@@ -3847,7 +3675,7 @@
         <v>51</v>
       </c>
       <c r="AR3" s="33" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AS3" s="28" t="s">
         <v>53</v>
@@ -3925,15 +3753,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.25" spans="1:69">
+    <row r="4" ht="15.75" spans="1:69">
       <c r="A4" s="26">
         <v>1</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C4" s="26" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D4" s="26" t="s">
         <v>76</v>
@@ -4089,11 +3917,11 @@
       <c r="AT4" s="35" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" t="s" s="0">
-        <v>188</v>
-      </c>
-      <c r="AV4" t="s" s="0">
-        <v>189</v>
+      <c r="AU4" t="s">
+        <v>116</v>
+      </c>
+      <c r="AV4" t="s">
+        <v>117</v>
       </c>
       <c r="AW4" s="35">
         <f>AM4</f>
@@ -4133,11 +3961,11 @@
       <c r="BL4" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="BM4" t="s" s="0">
-        <v>191</v>
-      </c>
-      <c r="BN4" t="s" s="0">
-        <v>190</v>
+      <c r="BM4" t="s">
+        <v>118</v>
+      </c>
+      <c r="BN4" t="s">
+        <v>119</v>
       </c>
       <c r="BO4" s="35">
         <f>ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
@@ -4294,73 +4122,73 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ5"/>
-  <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="8.7047619047619" defaultRowHeight="15" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="5.14545454545455"/>
-    <col min="2" max="3" customWidth="true" width="24.7181818181818"/>
-    <col min="4" max="4" customWidth="true" width="79.4272727272727"/>
-    <col min="5" max="5" customWidth="true" width="11.5727272727273"/>
-    <col min="6" max="6" customWidth="true" width="5.14545454545455"/>
-    <col min="7" max="7" customWidth="true" width="11.0"/>
-    <col min="8" max="8" customWidth="true" width="12.7181818181818"/>
-    <col min="9" max="9" customWidth="true" width="5.85454545454545"/>
-    <col min="10" max="10" customWidth="true" width="6.0"/>
-    <col min="11" max="11" customWidth="true" width="5.85454545454545"/>
-    <col min="12" max="12" customWidth="true" width="14.2818181818182"/>
-    <col min="13" max="13" customWidth="true" width="9.42727272727273"/>
-    <col min="14" max="14" customWidth="true" width="14.4272727272727"/>
-    <col min="15" max="15" customWidth="true" width="15.5727272727273"/>
-    <col min="16" max="16" customWidth="true" width="14.4272727272727"/>
-    <col min="17" max="17" customWidth="true" width="39.4272727272727"/>
-    <col min="18" max="18" customWidth="true" width="11.7181818181818"/>
-    <col min="19" max="19" customWidth="true" width="11.8545454545455"/>
-    <col min="20" max="20" customWidth="true" width="6.42727272727273"/>
-    <col min="21" max="22" customWidth="true" width="6.57272727272727"/>
-    <col min="23" max="23" customWidth="true" width="37.1454545454545"/>
-    <col min="24" max="25" customWidth="true" width="8.0"/>
-    <col min="26" max="26" customWidth="true" width="7.71818181818182"/>
-    <col min="27" max="27" customWidth="true" width="6.28181818181818"/>
-    <col min="28" max="28" customWidth="true" width="9.28181818181818"/>
-    <col min="29" max="29" customWidth="true" width="9.71818181818182"/>
-    <col min="30" max="30" customWidth="true" width="12.8545454545455"/>
-    <col min="31" max="31" customWidth="true" width="16.1454545454545"/>
-    <col min="32" max="32" customWidth="true" width="15.4272727272727"/>
-    <col min="33" max="33" customWidth="true" width="24.5727272727273"/>
-    <col min="34" max="34" customWidth="true" width="8.57272727272727"/>
-    <col min="35" max="35" customWidth="true" width="14.7181818181818"/>
-    <col min="36" max="36" customWidth="true" width="18.5727272727273"/>
-    <col min="37" max="37" customWidth="true" width="14.1454545454545"/>
-    <col min="38" max="38" customWidth="true" width="14.7181818181818"/>
-    <col min="39" max="39" customWidth="true" width="17.4272727272727"/>
-    <col min="40" max="40" customWidth="true" width="22.0"/>
-    <col min="41" max="41" customWidth="true" width="17.5727272727273"/>
-    <col min="42" max="42" customWidth="true" width="25.2818181818182"/>
-    <col min="43" max="43" customWidth="true" width="13.0"/>
-    <col min="44" max="44" customWidth="true" width="23.7181818181818"/>
-    <col min="45" max="45" customWidth="true" width="10.0"/>
-    <col min="46" max="46" customWidth="true" width="13.0"/>
-    <col min="47" max="47" customWidth="true" width="15.5727272727273"/>
-    <col min="48" max="48" customWidth="true" width="21.1454545454545"/>
-    <col min="49" max="49" customWidth="true" width="11.5727272727273"/>
-    <col min="50" max="50" customWidth="true" width="16.7181818181818"/>
-    <col min="51" max="51" customWidth="true" width="14.0"/>
-    <col min="52" max="52" customWidth="true" width="19.4272727272727"/>
-    <col min="53" max="53" customWidth="true" width="18.8545454545455"/>
-    <col min="54" max="54" customWidth="true" width="23.2818181818182"/>
-    <col min="55" max="55" customWidth="true" width="15.5727272727273"/>
-    <col min="56" max="56" customWidth="true" width="14.2818181818182"/>
-    <col min="57" max="57" customWidth="true" width="17.0"/>
-    <col min="58" max="58" customWidth="true" width="16.2818181818182"/>
-    <col min="59" max="59" customWidth="true" width="13.5727272727273"/>
-    <col min="60" max="61" customWidth="true" width="12.7181818181818"/>
-    <col min="62" max="62" customWidth="true" width="21.8545454545455"/>
-    <col min="63" max="63" customWidth="true" width="30.5727272727273"/>
-    <col min="64" max="64" customWidth="true" width="10.0"/>
-    <col min="65" max="65" customWidth="true" width="42.5727272727273"/>
-    <col min="66" max="66" customWidth="true" width="38.1454545454545"/>
-    <col min="67" max="67" customWidth="true" width="19.4272727272727"/>
-    <col min="68" max="68" customWidth="true" width="35.4272727272727"/>
-    <col min="69" max="69" customWidth="true" width="9.57272727272727"/>
+    <col min="1" max="1" width="5.14285714285714" customWidth="1"/>
+    <col min="2" max="3" width="24.7142857142857" customWidth="1"/>
+    <col min="4" max="4" width="79.4285714285714" customWidth="1"/>
+    <col min="5" max="5" width="11.5714285714286" customWidth="1"/>
+    <col min="6" max="6" width="5.14285714285714" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="12.7142857142857" customWidth="1"/>
+    <col min="9" max="9" width="5.85714285714286" customWidth="1"/>
+    <col min="10" max="10" width="6" customWidth="1"/>
+    <col min="11" max="11" width="5.85714285714286" customWidth="1"/>
+    <col min="12" max="12" width="14.2857142857143" customWidth="1"/>
+    <col min="13" max="13" width="9.42857142857143" customWidth="1"/>
+    <col min="14" max="14" width="14.4285714285714" customWidth="1"/>
+    <col min="15" max="15" width="15.5714285714286" customWidth="1"/>
+    <col min="16" max="16" width="14.4285714285714" customWidth="1"/>
+    <col min="17" max="17" width="39.4285714285714" customWidth="1"/>
+    <col min="18" max="18" width="11.7142857142857" customWidth="1"/>
+    <col min="19" max="19" width="11.8571428571429" customWidth="1"/>
+    <col min="20" max="20" width="6.42857142857143" customWidth="1"/>
+    <col min="21" max="22" width="6.57142857142857" customWidth="1"/>
+    <col min="23" max="23" width="37.1428571428571" customWidth="1"/>
+    <col min="24" max="25" width="8" customWidth="1"/>
+    <col min="26" max="26" width="7.71428571428571" customWidth="1"/>
+    <col min="27" max="27" width="6.28571428571429" customWidth="1"/>
+    <col min="28" max="28" width="9.28571428571429" customWidth="1"/>
+    <col min="29" max="29" width="9.71428571428571" customWidth="1"/>
+    <col min="30" max="30" width="12.8571428571429" customWidth="1"/>
+    <col min="31" max="31" width="16.1428571428571" customWidth="1"/>
+    <col min="32" max="32" width="15.4285714285714" customWidth="1"/>
+    <col min="33" max="33" width="24.5714285714286" customWidth="1"/>
+    <col min="34" max="34" width="8.57142857142857" customWidth="1"/>
+    <col min="35" max="35" width="14.7142857142857" customWidth="1"/>
+    <col min="36" max="36" width="18.5714285714286" customWidth="1"/>
+    <col min="37" max="37" width="14.1428571428571" customWidth="1"/>
+    <col min="38" max="38" width="14.7142857142857" customWidth="1"/>
+    <col min="39" max="39" width="17.4285714285714" customWidth="1"/>
+    <col min="40" max="40" width="22" customWidth="1"/>
+    <col min="41" max="41" width="17.5714285714286" customWidth="1"/>
+    <col min="42" max="42" width="25.2857142857143" customWidth="1"/>
+    <col min="43" max="43" width="13" customWidth="1"/>
+    <col min="44" max="44" width="23.7142857142857" customWidth="1"/>
+    <col min="45" max="45" width="10" customWidth="1"/>
+    <col min="46" max="46" width="13" customWidth="1"/>
+    <col min="47" max="47" width="15.5714285714286" customWidth="1"/>
+    <col min="48" max="48" width="21.1428571428571" customWidth="1"/>
+    <col min="49" max="49" width="11.5714285714286" customWidth="1"/>
+    <col min="50" max="50" width="16.7142857142857" customWidth="1"/>
+    <col min="51" max="51" width="14" customWidth="1"/>
+    <col min="52" max="52" width="19.4285714285714" customWidth="1"/>
+    <col min="53" max="53" width="18.8571428571429" customWidth="1"/>
+    <col min="54" max="54" width="23.2857142857143" customWidth="1"/>
+    <col min="55" max="55" width="15.5714285714286" customWidth="1"/>
+    <col min="56" max="56" width="14.2857142857143" customWidth="1"/>
+    <col min="57" max="57" width="17" customWidth="1"/>
+    <col min="58" max="58" width="16.2857142857143" customWidth="1"/>
+    <col min="59" max="59" width="13.5714285714286" customWidth="1"/>
+    <col min="60" max="61" width="12.7142857142857" customWidth="1"/>
+    <col min="62" max="62" width="21.8571428571429" customWidth="1"/>
+    <col min="63" max="63" width="30.5714285714286" customWidth="1"/>
+    <col min="64" max="64" width="10" customWidth="1"/>
+    <col min="65" max="65" width="42.5714285714286" customWidth="1"/>
+    <col min="66" max="66" width="38.1428571428571" customWidth="1"/>
+    <col min="67" max="67" width="19.4285714285714" customWidth="1"/>
+    <col min="68" max="68" width="35.4285714285714" customWidth="1"/>
+    <col min="69" max="69" width="9.57142857142857" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -4531,7 +4359,7 @@
       <c r="BP2" s="27"/>
       <c r="BQ2" s="27"/>
     </row>
-    <row r="3" ht="15.25" spans="1:69">
+    <row r="3" ht="15.75" spans="1:69">
       <c r="A3" s="28" t="s">
         <v>9</v>
       </c>
@@ -4578,7 +4406,7 @@
         <v>25</v>
       </c>
       <c r="P3" s="30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="Q3" s="30" t="s">
         <v>23</v>
@@ -4587,13 +4415,13 @@
         <v>26</v>
       </c>
       <c r="S3" s="28" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="T3" s="28" t="s">
         <v>28</v>
       </c>
       <c r="U3" s="31" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="V3" s="31" t="s">
         <v>30</v>
@@ -4662,7 +4490,7 @@
         <v>51</v>
       </c>
       <c r="AR3" s="33" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AS3" s="28" t="s">
         <v>53</v>
@@ -4740,15 +4568,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.25" spans="1:69">
+    <row r="4" ht="15.75" spans="1:69">
       <c r="A4" s="26">
         <v>1</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C4" s="26" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D4" s="26" t="s">
         <v>76</v>
@@ -4904,11 +4732,11 @@
       <c r="AT4" s="35" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" t="s" s="0">
-        <v>192</v>
-      </c>
-      <c r="AV4" t="s" s="0">
-        <v>193</v>
+      <c r="AU4" t="s">
+        <v>121</v>
+      </c>
+      <c r="AV4" t="s">
+        <v>122</v>
       </c>
       <c r="AW4" s="35">
         <f>AM4</f>
@@ -4948,11 +4776,11 @@
       <c r="BL4" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="BM4" t="s" s="0">
-        <v>195</v>
-      </c>
-      <c r="BN4" t="s" s="0">
-        <v>194</v>
+      <c r="BM4" t="s">
+        <v>123</v>
+      </c>
+      <c r="BN4" t="s">
+        <v>124</v>
       </c>
       <c r="BO4" s="35">
         <f>ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
@@ -5097,73 +4925,73 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ5"/>
-  <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="8.7047619047619" defaultRowHeight="15" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="5.14545454545455"/>
-    <col min="2" max="3" customWidth="true" width="25.1454545454545"/>
-    <col min="4" max="4" customWidth="true" width="79.4272727272727"/>
-    <col min="5" max="5" customWidth="true" width="11.5727272727273"/>
-    <col min="6" max="6" customWidth="true" width="5.14545454545455"/>
-    <col min="7" max="7" customWidth="true" width="11.0"/>
-    <col min="8" max="8" customWidth="true" width="12.7181818181818"/>
-    <col min="9" max="9" customWidth="true" width="5.85454545454545"/>
-    <col min="10" max="10" customWidth="true" width="6.0"/>
-    <col min="11" max="11" customWidth="true" width="5.85454545454545"/>
-    <col min="12" max="12" customWidth="true" width="14.2818181818182"/>
-    <col min="13" max="13" customWidth="true" width="9.42727272727273"/>
-    <col min="14" max="14" customWidth="true" width="14.4272727272727"/>
-    <col min="15" max="15" customWidth="true" width="15.5727272727273"/>
-    <col min="16" max="16" customWidth="true" width="14.4272727272727"/>
-    <col min="17" max="17" customWidth="true" width="39.4272727272727"/>
-    <col min="18" max="18" customWidth="true" width="11.7181818181818"/>
-    <col min="19" max="19" customWidth="true" width="11.8545454545455"/>
-    <col min="20" max="20" customWidth="true" width="6.42727272727273"/>
-    <col min="21" max="22" customWidth="true" width="6.57272727272727"/>
-    <col min="23" max="23" customWidth="true" width="37.1454545454545"/>
-    <col min="24" max="25" customWidth="true" width="8.0"/>
-    <col min="26" max="26" customWidth="true" width="7.71818181818182"/>
-    <col min="27" max="27" customWidth="true" width="6.28181818181818"/>
-    <col min="28" max="28" customWidth="true" width="9.28181818181818"/>
-    <col min="29" max="29" customWidth="true" width="9.71818181818182"/>
-    <col min="30" max="30" customWidth="true" width="12.8545454545455"/>
-    <col min="31" max="31" customWidth="true" width="16.1454545454545"/>
-    <col min="32" max="32" customWidth="true" width="15.4272727272727"/>
-    <col min="33" max="33" customWidth="true" width="24.5727272727273"/>
-    <col min="34" max="34" customWidth="true" width="8.57272727272727"/>
-    <col min="35" max="35" customWidth="true" width="14.7181818181818"/>
-    <col min="36" max="36" customWidth="true" width="18.5727272727273"/>
-    <col min="37" max="37" customWidth="true" width="14.1454545454545"/>
-    <col min="38" max="38" customWidth="true" width="14.7181818181818"/>
-    <col min="39" max="39" customWidth="true" width="17.4272727272727"/>
-    <col min="40" max="40" customWidth="true" width="22.0"/>
-    <col min="41" max="41" customWidth="true" width="17.5727272727273"/>
-    <col min="42" max="42" customWidth="true" width="25.2818181818182"/>
-    <col min="43" max="43" customWidth="true" width="13.0"/>
-    <col min="44" max="44" customWidth="true" width="23.7181818181818"/>
-    <col min="45" max="45" customWidth="true" width="10.0"/>
-    <col min="46" max="46" customWidth="true" width="13.0"/>
-    <col min="47" max="47" customWidth="true" width="15.5727272727273"/>
-    <col min="48" max="48" customWidth="true" width="21.1454545454545"/>
-    <col min="49" max="49" customWidth="true" width="11.5727272727273"/>
-    <col min="50" max="50" customWidth="true" width="16.7181818181818"/>
-    <col min="51" max="51" customWidth="true" width="14.0"/>
-    <col min="52" max="52" customWidth="true" width="19.4272727272727"/>
-    <col min="53" max="53" customWidth="true" width="18.8545454545455"/>
-    <col min="54" max="54" customWidth="true" width="23.2818181818182"/>
-    <col min="55" max="55" customWidth="true" width="15.5727272727273"/>
-    <col min="56" max="56" customWidth="true" width="14.2818181818182"/>
-    <col min="57" max="57" customWidth="true" width="17.0"/>
-    <col min="58" max="58" customWidth="true" width="16.2818181818182"/>
-    <col min="59" max="59" customWidth="true" width="13.5727272727273"/>
-    <col min="60" max="61" customWidth="true" width="12.7181818181818"/>
-    <col min="62" max="62" customWidth="true" width="21.8545454545455"/>
-    <col min="63" max="63" customWidth="true" width="30.5727272727273"/>
-    <col min="64" max="64" customWidth="true" width="10.0"/>
-    <col min="65" max="65" customWidth="true" width="42.5727272727273"/>
-    <col min="66" max="66" customWidth="true" width="38.1454545454545"/>
-    <col min="67" max="67" customWidth="true" width="19.4272727272727"/>
-    <col min="68" max="68" customWidth="true" width="35.4272727272727"/>
-    <col min="69" max="69" customWidth="true" width="9.57272727272727"/>
+    <col min="1" max="1" width="5.14285714285714" customWidth="1"/>
+    <col min="2" max="3" width="25.1428571428571" customWidth="1"/>
+    <col min="4" max="4" width="79.4285714285714" customWidth="1"/>
+    <col min="5" max="5" width="11.5714285714286" customWidth="1"/>
+    <col min="6" max="6" width="5.14285714285714" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="12.7142857142857" customWidth="1"/>
+    <col min="9" max="9" width="5.85714285714286" customWidth="1"/>
+    <col min="10" max="10" width="6" customWidth="1"/>
+    <col min="11" max="11" width="5.85714285714286" customWidth="1"/>
+    <col min="12" max="12" width="14.2857142857143" customWidth="1"/>
+    <col min="13" max="13" width="9.42857142857143" customWidth="1"/>
+    <col min="14" max="14" width="14.4285714285714" customWidth="1"/>
+    <col min="15" max="15" width="15.5714285714286" customWidth="1"/>
+    <col min="16" max="16" width="14.4285714285714" customWidth="1"/>
+    <col min="17" max="17" width="39.4285714285714" customWidth="1"/>
+    <col min="18" max="18" width="11.7142857142857" customWidth="1"/>
+    <col min="19" max="19" width="11.8571428571429" customWidth="1"/>
+    <col min="20" max="20" width="6.42857142857143" customWidth="1"/>
+    <col min="21" max="22" width="6.57142857142857" customWidth="1"/>
+    <col min="23" max="23" width="37.1428571428571" customWidth="1"/>
+    <col min="24" max="25" width="8" customWidth="1"/>
+    <col min="26" max="26" width="7.71428571428571" customWidth="1"/>
+    <col min="27" max="27" width="6.28571428571429" customWidth="1"/>
+    <col min="28" max="28" width="9.28571428571429" customWidth="1"/>
+    <col min="29" max="29" width="9.71428571428571" customWidth="1"/>
+    <col min="30" max="30" width="12.8571428571429" customWidth="1"/>
+    <col min="31" max="31" width="16.1428571428571" customWidth="1"/>
+    <col min="32" max="32" width="15.4285714285714" customWidth="1"/>
+    <col min="33" max="33" width="24.5714285714286" customWidth="1"/>
+    <col min="34" max="34" width="8.57142857142857" customWidth="1"/>
+    <col min="35" max="35" width="14.7142857142857" customWidth="1"/>
+    <col min="36" max="36" width="18.5714285714286" customWidth="1"/>
+    <col min="37" max="37" width="14.1428571428571" customWidth="1"/>
+    <col min="38" max="38" width="14.7142857142857" customWidth="1"/>
+    <col min="39" max="39" width="17.4285714285714" customWidth="1"/>
+    <col min="40" max="40" width="22" customWidth="1"/>
+    <col min="41" max="41" width="17.5714285714286" customWidth="1"/>
+    <col min="42" max="42" width="25.2857142857143" customWidth="1"/>
+    <col min="43" max="43" width="13" customWidth="1"/>
+    <col min="44" max="44" width="23.7142857142857" customWidth="1"/>
+    <col min="45" max="45" width="10" customWidth="1"/>
+    <col min="46" max="46" width="13" customWidth="1"/>
+    <col min="47" max="47" width="15.5714285714286" customWidth="1"/>
+    <col min="48" max="48" width="21.1428571428571" customWidth="1"/>
+    <col min="49" max="49" width="11.5714285714286" customWidth="1"/>
+    <col min="50" max="50" width="16.7142857142857" customWidth="1"/>
+    <col min="51" max="51" width="14" customWidth="1"/>
+    <col min="52" max="52" width="19.4285714285714" customWidth="1"/>
+    <col min="53" max="53" width="18.8571428571429" customWidth="1"/>
+    <col min="54" max="54" width="23.2857142857143" customWidth="1"/>
+    <col min="55" max="55" width="15.5714285714286" customWidth="1"/>
+    <col min="56" max="56" width="14.2857142857143" customWidth="1"/>
+    <col min="57" max="57" width="17" customWidth="1"/>
+    <col min="58" max="58" width="16.2857142857143" customWidth="1"/>
+    <col min="59" max="59" width="13.5714285714286" customWidth="1"/>
+    <col min="60" max="61" width="12.7142857142857" customWidth="1"/>
+    <col min="62" max="62" width="21.8571428571429" customWidth="1"/>
+    <col min="63" max="63" width="30.5714285714286" customWidth="1"/>
+    <col min="64" max="64" width="10" customWidth="1"/>
+    <col min="65" max="65" width="42.5714285714286" customWidth="1"/>
+    <col min="66" max="66" width="38.1428571428571" customWidth="1"/>
+    <col min="67" max="67" width="19.4285714285714" customWidth="1"/>
+    <col min="68" max="68" width="35.4285714285714" customWidth="1"/>
+    <col min="69" max="69" width="9.57142857142857" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -5334,7 +5162,7 @@
       <c r="BP2" s="27"/>
       <c r="BQ2" s="27"/>
     </row>
-    <row r="3" ht="15.25" spans="1:69">
+    <row r="3" ht="15.75" spans="1:69">
       <c r="A3" s="28" t="s">
         <v>9</v>
       </c>
@@ -5381,7 +5209,7 @@
         <v>25</v>
       </c>
       <c r="P3" s="30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="Q3" s="30" t="s">
         <v>23</v>
@@ -5390,13 +5218,13 @@
         <v>26</v>
       </c>
       <c r="S3" s="28" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="T3" s="28" t="s">
         <v>28</v>
       </c>
       <c r="U3" s="31" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="V3" s="31" t="s">
         <v>30</v>
@@ -5465,7 +5293,7 @@
         <v>51</v>
       </c>
       <c r="AR3" s="33" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AS3" s="28" t="s">
         <v>53</v>
@@ -5543,15 +5371,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.25" spans="1:69">
+    <row r="4" ht="15.75" spans="1:69">
       <c r="A4" s="26">
         <v>1</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C4" s="26" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D4" s="26" t="s">
         <v>76</v>
@@ -5748,10 +5576,10 @@
         <v>85</v>
       </c>
       <c r="BM4" s="27" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="BN4" s="27" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="BO4" s="35">
         <f>ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
@@ -5896,73 +5724,73 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ5"/>
-  <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="8.7047619047619" defaultRowHeight="15" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="5.14545454545455"/>
-    <col min="2" max="3" customWidth="true" width="22.0"/>
-    <col min="4" max="4" customWidth="true" width="79.4272727272727"/>
-    <col min="5" max="5" customWidth="true" width="11.5727272727273"/>
-    <col min="6" max="6" customWidth="true" width="5.14545454545455"/>
-    <col min="7" max="7" customWidth="true" width="11.0"/>
-    <col min="8" max="8" customWidth="true" width="12.7181818181818"/>
-    <col min="9" max="9" customWidth="true" width="5.85454545454545"/>
-    <col min="10" max="10" customWidth="true" width="6.0"/>
-    <col min="11" max="11" customWidth="true" width="5.85454545454545"/>
-    <col min="12" max="12" customWidth="true" width="14.2818181818182"/>
-    <col min="13" max="13" customWidth="true" width="9.42727272727273"/>
-    <col min="14" max="14" customWidth="true" width="14.4272727272727"/>
-    <col min="15" max="15" customWidth="true" width="15.5727272727273"/>
-    <col min="16" max="16" customWidth="true" width="14.4272727272727"/>
-    <col min="17" max="17" customWidth="true" width="39.4272727272727"/>
-    <col min="18" max="18" customWidth="true" width="11.7181818181818"/>
-    <col min="19" max="19" customWidth="true" width="11.8545454545455"/>
-    <col min="20" max="20" customWidth="true" width="6.42727272727273"/>
-    <col min="21" max="22" customWidth="true" width="6.57272727272727"/>
-    <col min="23" max="23" customWidth="true" width="37.1454545454545"/>
-    <col min="24" max="25" customWidth="true" width="8.0"/>
-    <col min="26" max="26" customWidth="true" width="7.71818181818182"/>
-    <col min="27" max="27" customWidth="true" width="6.28181818181818"/>
-    <col min="28" max="28" customWidth="true" width="9.28181818181818"/>
-    <col min="29" max="29" customWidth="true" width="9.71818181818182"/>
-    <col min="30" max="30" customWidth="true" width="12.8545454545455"/>
-    <col min="31" max="31" customWidth="true" width="16.1454545454545"/>
-    <col min="32" max="32" customWidth="true" width="15.4272727272727"/>
-    <col min="33" max="33" customWidth="true" width="24.5727272727273"/>
-    <col min="34" max="34" customWidth="true" width="8.57272727272727"/>
-    <col min="35" max="35" customWidth="true" width="14.7181818181818"/>
-    <col min="36" max="36" customWidth="true" width="18.5727272727273"/>
-    <col min="37" max="37" customWidth="true" width="14.1454545454545"/>
-    <col min="38" max="38" customWidth="true" width="14.7181818181818"/>
-    <col min="39" max="39" customWidth="true" width="17.4272727272727"/>
-    <col min="40" max="40" customWidth="true" width="22.0"/>
-    <col min="41" max="41" customWidth="true" width="17.5727272727273"/>
-    <col min="42" max="42" customWidth="true" width="25.2818181818182"/>
-    <col min="43" max="43" customWidth="true" width="13.0"/>
-    <col min="44" max="44" customWidth="true" width="23.7181818181818"/>
-    <col min="45" max="45" customWidth="true" width="10.0"/>
-    <col min="46" max="46" customWidth="true" width="13.0"/>
-    <col min="47" max="47" customWidth="true" width="15.5727272727273"/>
-    <col min="48" max="48" customWidth="true" width="21.1454545454545"/>
-    <col min="49" max="49" customWidth="true" width="11.5727272727273"/>
-    <col min="50" max="50" customWidth="true" width="16.7181818181818"/>
-    <col min="51" max="51" customWidth="true" width="14.0"/>
-    <col min="52" max="52" customWidth="true" width="19.4272727272727"/>
-    <col min="53" max="53" customWidth="true" width="18.8545454545455"/>
-    <col min="54" max="54" customWidth="true" width="23.2818181818182"/>
-    <col min="55" max="55" customWidth="true" width="15.5727272727273"/>
-    <col min="56" max="56" customWidth="true" width="14.2818181818182"/>
-    <col min="57" max="57" customWidth="true" width="17.0"/>
-    <col min="58" max="58" customWidth="true" width="16.2818181818182"/>
-    <col min="59" max="59" customWidth="true" width="13.5727272727273"/>
-    <col min="60" max="61" customWidth="true" width="12.7181818181818"/>
-    <col min="62" max="62" customWidth="true" width="21.8545454545455"/>
-    <col min="63" max="63" customWidth="true" width="30.5727272727273"/>
-    <col min="64" max="64" customWidth="true" width="10.0"/>
-    <col min="65" max="65" customWidth="true" width="42.5727272727273"/>
-    <col min="66" max="66" customWidth="true" width="38.1454545454545"/>
-    <col min="67" max="67" customWidth="true" width="19.4272727272727"/>
-    <col min="68" max="68" customWidth="true" width="35.4272727272727"/>
-    <col min="69" max="69" customWidth="true" width="9.57272727272727"/>
+    <col min="1" max="1" width="5.14285714285714" customWidth="1"/>
+    <col min="2" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="79.4285714285714" customWidth="1"/>
+    <col min="5" max="5" width="11.5714285714286" customWidth="1"/>
+    <col min="6" max="6" width="5.14285714285714" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="12.7142857142857" customWidth="1"/>
+    <col min="9" max="9" width="5.85714285714286" customWidth="1"/>
+    <col min="10" max="10" width="6" customWidth="1"/>
+    <col min="11" max="11" width="5.85714285714286" customWidth="1"/>
+    <col min="12" max="12" width="14.2857142857143" customWidth="1"/>
+    <col min="13" max="13" width="9.42857142857143" customWidth="1"/>
+    <col min="14" max="14" width="14.4285714285714" customWidth="1"/>
+    <col min="15" max="15" width="15.5714285714286" customWidth="1"/>
+    <col min="16" max="16" width="14.4285714285714" customWidth="1"/>
+    <col min="17" max="17" width="39.4285714285714" customWidth="1"/>
+    <col min="18" max="18" width="11.7142857142857" customWidth="1"/>
+    <col min="19" max="19" width="11.8571428571429" customWidth="1"/>
+    <col min="20" max="20" width="6.42857142857143" customWidth="1"/>
+    <col min="21" max="22" width="6.57142857142857" customWidth="1"/>
+    <col min="23" max="23" width="37.1428571428571" customWidth="1"/>
+    <col min="24" max="25" width="8" customWidth="1"/>
+    <col min="26" max="26" width="7.71428571428571" customWidth="1"/>
+    <col min="27" max="27" width="6.28571428571429" customWidth="1"/>
+    <col min="28" max="28" width="9.28571428571429" customWidth="1"/>
+    <col min="29" max="29" width="9.71428571428571" customWidth="1"/>
+    <col min="30" max="30" width="12.8571428571429" customWidth="1"/>
+    <col min="31" max="31" width="16.1428571428571" customWidth="1"/>
+    <col min="32" max="32" width="15.4285714285714" customWidth="1"/>
+    <col min="33" max="33" width="24.5714285714286" customWidth="1"/>
+    <col min="34" max="34" width="8.57142857142857" customWidth="1"/>
+    <col min="35" max="35" width="14.7142857142857" customWidth="1"/>
+    <col min="36" max="36" width="18.5714285714286" customWidth="1"/>
+    <col min="37" max="37" width="14.1428571428571" customWidth="1"/>
+    <col min="38" max="38" width="14.7142857142857" customWidth="1"/>
+    <col min="39" max="39" width="17.4285714285714" customWidth="1"/>
+    <col min="40" max="40" width="22" customWidth="1"/>
+    <col min="41" max="41" width="17.5714285714286" customWidth="1"/>
+    <col min="42" max="42" width="25.2857142857143" customWidth="1"/>
+    <col min="43" max="43" width="13" customWidth="1"/>
+    <col min="44" max="44" width="23.7142857142857" customWidth="1"/>
+    <col min="45" max="45" width="10" customWidth="1"/>
+    <col min="46" max="46" width="13" customWidth="1"/>
+    <col min="47" max="47" width="15.5714285714286" customWidth="1"/>
+    <col min="48" max="48" width="21.1428571428571" customWidth="1"/>
+    <col min="49" max="49" width="11.5714285714286" customWidth="1"/>
+    <col min="50" max="50" width="16.7142857142857" customWidth="1"/>
+    <col min="51" max="51" width="14" customWidth="1"/>
+    <col min="52" max="52" width="19.4285714285714" customWidth="1"/>
+    <col min="53" max="53" width="18.8571428571429" customWidth="1"/>
+    <col min="54" max="54" width="23.2857142857143" customWidth="1"/>
+    <col min="55" max="55" width="15.5714285714286" customWidth="1"/>
+    <col min="56" max="56" width="14.2857142857143" customWidth="1"/>
+    <col min="57" max="57" width="17" customWidth="1"/>
+    <col min="58" max="58" width="16.2857142857143" customWidth="1"/>
+    <col min="59" max="59" width="13.5714285714286" customWidth="1"/>
+    <col min="60" max="61" width="12.7142857142857" customWidth="1"/>
+    <col min="62" max="62" width="21.8571428571429" customWidth="1"/>
+    <col min="63" max="63" width="30.5714285714286" customWidth="1"/>
+    <col min="64" max="64" width="10" customWidth="1"/>
+    <col min="65" max="65" width="42.5714285714286" customWidth="1"/>
+    <col min="66" max="66" width="38.1428571428571" customWidth="1"/>
+    <col min="67" max="67" width="19.4285714285714" customWidth="1"/>
+    <col min="68" max="68" width="35.4285714285714" customWidth="1"/>
+    <col min="69" max="69" width="9.57142857142857" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -6133,7 +5961,7 @@
       <c r="BP2" s="27"/>
       <c r="BQ2" s="27"/>
     </row>
-    <row r="3" ht="15.25" spans="1:69">
+    <row r="3" ht="15.75" spans="1:69">
       <c r="A3" s="28" t="s">
         <v>9</v>
       </c>
@@ -6180,7 +6008,7 @@
         <v>25</v>
       </c>
       <c r="P3" s="30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="Q3" s="30" t="s">
         <v>23</v>
@@ -6189,13 +6017,13 @@
         <v>26</v>
       </c>
       <c r="S3" s="28" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="T3" s="28" t="s">
         <v>28</v>
       </c>
       <c r="U3" s="31" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="V3" s="31" t="s">
         <v>30</v>
@@ -6264,7 +6092,7 @@
         <v>51</v>
       </c>
       <c r="AR3" s="33" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AS3" s="28" t="s">
         <v>53</v>
@@ -6342,15 +6170,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.25" spans="1:69">
+    <row r="4" ht="15.75" spans="1:69">
       <c r="A4" s="26">
         <v>1</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C4" s="26" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D4" s="26" t="s">
         <v>76</v>
@@ -6369,7 +6197,7 @@
         <v>400</v>
       </c>
       <c r="I4" s="27" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J4" s="35">
         <v>2</v>
@@ -6506,8 +6334,6 @@
       <c r="AT4" s="35" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" s="0"/>
-      <c r="AV4" s="0"/>
       <c r="AW4" s="35">
         <f>AM4</f>
         <v>4</v>
@@ -6546,11 +6372,11 @@
       <c r="BL4" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="BM4" t="s" s="0">
-        <v>100</v>
-      </c>
-      <c r="BN4" t="s" s="0">
-        <v>100</v>
+      <c r="BM4" t="s">
+        <v>99</v>
+      </c>
+      <c r="BN4" t="s">
+        <v>99</v>
       </c>
       <c r="BO4" s="35">
         <f>ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
@@ -6695,73 +6521,73 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ5"/>
-  <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="8.7047619047619" defaultRowHeight="15" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="5.14545454545455"/>
-    <col min="2" max="3" customWidth="true" width="22.0"/>
-    <col min="4" max="4" customWidth="true" width="79.4272727272727"/>
-    <col min="5" max="5" customWidth="true" width="11.5727272727273"/>
-    <col min="6" max="6" customWidth="true" width="5.14545454545455"/>
-    <col min="7" max="7" customWidth="true" width="11.0"/>
-    <col min="8" max="8" customWidth="true" width="12.7181818181818"/>
-    <col min="9" max="9" customWidth="true" width="5.85454545454545"/>
-    <col min="10" max="10" customWidth="true" width="6.0"/>
-    <col min="11" max="11" customWidth="true" width="5.85454545454545"/>
-    <col min="12" max="12" customWidth="true" width="14.2818181818182"/>
-    <col min="13" max="13" customWidth="true" width="9.42727272727273"/>
-    <col min="14" max="14" customWidth="true" width="14.4272727272727"/>
-    <col min="15" max="15" customWidth="true" width="15.5727272727273"/>
-    <col min="16" max="16" customWidth="true" width="14.4272727272727"/>
-    <col min="17" max="17" customWidth="true" width="39.4272727272727"/>
-    <col min="18" max="18" customWidth="true" width="11.7181818181818"/>
-    <col min="19" max="19" customWidth="true" width="11.8545454545455"/>
-    <col min="20" max="20" customWidth="true" width="6.42727272727273"/>
-    <col min="21" max="22" customWidth="true" width="6.57272727272727"/>
-    <col min="23" max="23" customWidth="true" width="37.1454545454545"/>
-    <col min="24" max="25" customWidth="true" width="8.0"/>
-    <col min="26" max="26" customWidth="true" width="7.71818181818182"/>
-    <col min="27" max="27" customWidth="true" width="6.28181818181818"/>
-    <col min="28" max="28" customWidth="true" width="9.28181818181818"/>
-    <col min="29" max="29" customWidth="true" width="9.71818181818182"/>
-    <col min="30" max="30" customWidth="true" width="12.8545454545455"/>
-    <col min="31" max="31" customWidth="true" width="16.1454545454545"/>
-    <col min="32" max="32" customWidth="true" width="15.4272727272727"/>
-    <col min="33" max="33" customWidth="true" width="24.5727272727273"/>
-    <col min="34" max="34" customWidth="true" width="8.57272727272727"/>
-    <col min="35" max="35" customWidth="true" width="14.7181818181818"/>
-    <col min="36" max="36" customWidth="true" width="18.5727272727273"/>
-    <col min="37" max="37" customWidth="true" width="14.1454545454545"/>
-    <col min="38" max="38" customWidth="true" width="14.7181818181818"/>
-    <col min="39" max="39" customWidth="true" width="17.4272727272727"/>
-    <col min="40" max="40" customWidth="true" width="22.0"/>
-    <col min="41" max="41" customWidth="true" width="17.5727272727273"/>
-    <col min="42" max="42" customWidth="true" width="25.2818181818182"/>
-    <col min="43" max="43" customWidth="true" width="13.0"/>
-    <col min="44" max="44" customWidth="true" width="23.7181818181818"/>
-    <col min="45" max="45" customWidth="true" width="10.0"/>
-    <col min="46" max="46" customWidth="true" width="13.0"/>
-    <col min="47" max="47" customWidth="true" width="15.5727272727273"/>
-    <col min="48" max="48" customWidth="true" width="21.1454545454545"/>
-    <col min="49" max="49" customWidth="true" width="11.5727272727273"/>
-    <col min="50" max="50" customWidth="true" width="16.7181818181818"/>
-    <col min="51" max="51" customWidth="true" width="14.0"/>
-    <col min="52" max="52" customWidth="true" width="19.4272727272727"/>
-    <col min="53" max="53" customWidth="true" width="18.8545454545455"/>
-    <col min="54" max="54" customWidth="true" width="23.2818181818182"/>
-    <col min="55" max="55" customWidth="true" width="15.5727272727273"/>
-    <col min="56" max="56" customWidth="true" width="14.2818181818182"/>
-    <col min="57" max="57" customWidth="true" width="17.0"/>
-    <col min="58" max="58" customWidth="true" width="16.2818181818182"/>
-    <col min="59" max="59" customWidth="true" width="13.5727272727273"/>
-    <col min="60" max="61" customWidth="true" width="12.7181818181818"/>
-    <col min="62" max="62" customWidth="true" width="21.8545454545455"/>
-    <col min="63" max="63" customWidth="true" width="30.5727272727273"/>
-    <col min="64" max="64" customWidth="true" width="10.0"/>
-    <col min="65" max="65" customWidth="true" width="42.5727272727273"/>
-    <col min="66" max="66" customWidth="true" width="38.1454545454545"/>
-    <col min="67" max="67" customWidth="true" width="19.4272727272727"/>
-    <col min="68" max="68" customWidth="true" width="35.4272727272727"/>
-    <col min="69" max="69" customWidth="true" width="9.57272727272727"/>
+    <col min="1" max="1" width="5.14285714285714" customWidth="1"/>
+    <col min="2" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="79.4285714285714" customWidth="1"/>
+    <col min="5" max="5" width="11.5714285714286" customWidth="1"/>
+    <col min="6" max="6" width="5.14285714285714" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="12.7142857142857" customWidth="1"/>
+    <col min="9" max="9" width="5.85714285714286" customWidth="1"/>
+    <col min="10" max="10" width="6" customWidth="1"/>
+    <col min="11" max="11" width="5.85714285714286" customWidth="1"/>
+    <col min="12" max="12" width="14.2857142857143" customWidth="1"/>
+    <col min="13" max="13" width="9.42857142857143" customWidth="1"/>
+    <col min="14" max="14" width="14.4285714285714" customWidth="1"/>
+    <col min="15" max="15" width="15.5714285714286" customWidth="1"/>
+    <col min="16" max="16" width="14.4285714285714" customWidth="1"/>
+    <col min="17" max="17" width="39.4285714285714" customWidth="1"/>
+    <col min="18" max="18" width="11.7142857142857" customWidth="1"/>
+    <col min="19" max="19" width="11.8571428571429" customWidth="1"/>
+    <col min="20" max="20" width="6.42857142857143" customWidth="1"/>
+    <col min="21" max="22" width="6.57142857142857" customWidth="1"/>
+    <col min="23" max="23" width="37.1428571428571" customWidth="1"/>
+    <col min="24" max="25" width="8" customWidth="1"/>
+    <col min="26" max="26" width="7.71428571428571" customWidth="1"/>
+    <col min="27" max="27" width="6.28571428571429" customWidth="1"/>
+    <col min="28" max="28" width="9.28571428571429" customWidth="1"/>
+    <col min="29" max="29" width="9.71428571428571" customWidth="1"/>
+    <col min="30" max="30" width="12.8571428571429" customWidth="1"/>
+    <col min="31" max="31" width="16.1428571428571" customWidth="1"/>
+    <col min="32" max="32" width="15.4285714285714" customWidth="1"/>
+    <col min="33" max="33" width="24.5714285714286" customWidth="1"/>
+    <col min="34" max="34" width="8.57142857142857" customWidth="1"/>
+    <col min="35" max="35" width="14.7142857142857" customWidth="1"/>
+    <col min="36" max="36" width="18.5714285714286" customWidth="1"/>
+    <col min="37" max="37" width="14.1428571428571" customWidth="1"/>
+    <col min="38" max="38" width="14.7142857142857" customWidth="1"/>
+    <col min="39" max="39" width="17.4285714285714" customWidth="1"/>
+    <col min="40" max="40" width="22" customWidth="1"/>
+    <col min="41" max="41" width="17.5714285714286" customWidth="1"/>
+    <col min="42" max="42" width="25.2857142857143" customWidth="1"/>
+    <col min="43" max="43" width="13" customWidth="1"/>
+    <col min="44" max="44" width="23.7142857142857" customWidth="1"/>
+    <col min="45" max="45" width="10" customWidth="1"/>
+    <col min="46" max="46" width="13" customWidth="1"/>
+    <col min="47" max="47" width="15.5714285714286" customWidth="1"/>
+    <col min="48" max="48" width="21.1428571428571" customWidth="1"/>
+    <col min="49" max="49" width="11.5714285714286" customWidth="1"/>
+    <col min="50" max="50" width="16.7142857142857" customWidth="1"/>
+    <col min="51" max="51" width="14" customWidth="1"/>
+    <col min="52" max="52" width="19.4285714285714" customWidth="1"/>
+    <col min="53" max="53" width="18.8571428571429" customWidth="1"/>
+    <col min="54" max="54" width="23.2857142857143" customWidth="1"/>
+    <col min="55" max="55" width="15.5714285714286" customWidth="1"/>
+    <col min="56" max="56" width="14.2857142857143" customWidth="1"/>
+    <col min="57" max="57" width="17" customWidth="1"/>
+    <col min="58" max="58" width="16.2857142857143" customWidth="1"/>
+    <col min="59" max="59" width="13.5714285714286" customWidth="1"/>
+    <col min="60" max="61" width="12.7142857142857" customWidth="1"/>
+    <col min="62" max="62" width="21.8571428571429" customWidth="1"/>
+    <col min="63" max="63" width="30.5714285714286" customWidth="1"/>
+    <col min="64" max="64" width="10" customWidth="1"/>
+    <col min="65" max="65" width="42.5714285714286" customWidth="1"/>
+    <col min="66" max="66" width="38.1428571428571" customWidth="1"/>
+    <col min="67" max="67" width="19.4285714285714" customWidth="1"/>
+    <col min="68" max="68" width="35.4285714285714" customWidth="1"/>
+    <col min="69" max="69" width="9.57142857142857" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -6932,7 +6758,7 @@
       <c r="BP2" s="27"/>
       <c r="BQ2" s="27"/>
     </row>
-    <row r="3" ht="15.25" spans="1:69">
+    <row r="3" ht="15.75" spans="1:69">
       <c r="A3" s="28" t="s">
         <v>9</v>
       </c>
@@ -6979,7 +6805,7 @@
         <v>25</v>
       </c>
       <c r="P3" s="30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="Q3" s="30" t="s">
         <v>23</v>
@@ -6988,13 +6814,13 @@
         <v>26</v>
       </c>
       <c r="S3" s="28" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="T3" s="28" t="s">
         <v>28</v>
       </c>
       <c r="U3" s="31" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="V3" s="31" t="s">
         <v>30</v>
@@ -7063,7 +6889,7 @@
         <v>51</v>
       </c>
       <c r="AR3" s="33" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AS3" s="28" t="s">
         <v>53</v>
@@ -7141,15 +6967,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.25" spans="1:69">
+    <row r="4" ht="15.75" spans="1:69">
       <c r="A4" s="26">
         <v>1</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C4" s="26" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D4" s="26" t="s">
         <v>76</v>
@@ -7168,7 +6994,7 @@
         <v>400</v>
       </c>
       <c r="I4" s="27" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J4" s="35">
         <v>2</v>
@@ -7305,8 +7131,6 @@
       <c r="AT4" s="35" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" s="0"/>
-      <c r="AV4" s="0"/>
       <c r="AW4" s="35">
         <f>AM4</f>
         <v>4</v>
@@ -7345,11 +7169,11 @@
       <c r="BL4" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="BM4" t="s" s="0">
-        <v>100</v>
-      </c>
-      <c r="BN4" t="s" s="0">
-        <v>100</v>
+      <c r="BM4" t="s">
+        <v>99</v>
+      </c>
+      <c r="BN4" t="s">
+        <v>99</v>
       </c>
       <c r="BO4" s="35">
         <f>ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
@@ -7494,73 +7318,73 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ5"/>
-  <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="8.7047619047619" defaultRowHeight="15" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="5.14545454545455"/>
-    <col min="2" max="3" customWidth="true" width="24.5727272727273"/>
-    <col min="4" max="4" customWidth="true" width="79.4272727272727"/>
-    <col min="5" max="5" customWidth="true" width="11.5727272727273"/>
-    <col min="6" max="6" customWidth="true" width="5.14545454545455"/>
-    <col min="7" max="7" customWidth="true" width="11.0"/>
-    <col min="8" max="8" customWidth="true" width="12.7181818181818"/>
-    <col min="9" max="9" customWidth="true" width="5.85454545454545"/>
-    <col min="10" max="10" customWidth="true" width="6.0"/>
-    <col min="11" max="11" customWidth="true" width="5.85454545454545"/>
-    <col min="12" max="12" customWidth="true" width="14.2818181818182"/>
-    <col min="13" max="13" customWidth="true" width="9.42727272727273"/>
-    <col min="14" max="14" customWidth="true" width="14.4272727272727"/>
-    <col min="15" max="15" customWidth="true" width="15.5727272727273"/>
-    <col min="16" max="16" customWidth="true" width="14.4272727272727"/>
-    <col min="17" max="17" customWidth="true" width="39.4272727272727"/>
-    <col min="18" max="18" customWidth="true" width="11.7181818181818"/>
-    <col min="19" max="19" customWidth="true" width="11.8545454545455"/>
-    <col min="20" max="20" customWidth="true" width="6.42727272727273"/>
-    <col min="21" max="22" customWidth="true" width="6.57272727272727"/>
-    <col min="23" max="23" customWidth="true" width="37.1454545454545"/>
-    <col min="24" max="25" customWidth="true" width="8.0"/>
-    <col min="26" max="26" customWidth="true" width="7.71818181818182"/>
-    <col min="27" max="27" customWidth="true" width="6.28181818181818"/>
-    <col min="28" max="28" customWidth="true" width="9.28181818181818"/>
-    <col min="29" max="29" customWidth="true" width="9.71818181818182"/>
-    <col min="30" max="30" customWidth="true" width="12.8545454545455"/>
-    <col min="31" max="31" customWidth="true" width="16.1454545454545"/>
-    <col min="32" max="32" customWidth="true" width="15.4272727272727"/>
-    <col min="33" max="33" customWidth="true" width="24.5727272727273"/>
-    <col min="34" max="34" customWidth="true" width="8.57272727272727"/>
-    <col min="35" max="35" customWidth="true" width="14.7181818181818"/>
-    <col min="36" max="36" customWidth="true" width="18.5727272727273"/>
-    <col min="37" max="37" customWidth="true" width="14.1454545454545"/>
-    <col min="38" max="38" customWidth="true" width="14.7181818181818"/>
-    <col min="39" max="39" customWidth="true" width="17.4272727272727"/>
-    <col min="40" max="40" customWidth="true" width="22.0"/>
-    <col min="41" max="41" customWidth="true" width="17.5727272727273"/>
-    <col min="42" max="42" customWidth="true" width="25.2818181818182"/>
-    <col min="43" max="43" customWidth="true" width="13.0"/>
-    <col min="44" max="44" customWidth="true" width="23.7181818181818"/>
-    <col min="45" max="45" customWidth="true" width="10.0"/>
-    <col min="46" max="46" customWidth="true" width="13.0"/>
-    <col min="47" max="47" customWidth="true" width="15.5727272727273"/>
-    <col min="48" max="48" customWidth="true" width="21.1454545454545"/>
-    <col min="49" max="49" customWidth="true" width="11.5727272727273"/>
-    <col min="50" max="50" customWidth="true" width="16.7181818181818"/>
-    <col min="51" max="51" customWidth="true" width="14.0"/>
-    <col min="52" max="52" customWidth="true" width="19.4272727272727"/>
-    <col min="53" max="53" customWidth="true" width="18.8545454545455"/>
-    <col min="54" max="54" customWidth="true" width="23.2818181818182"/>
-    <col min="55" max="55" customWidth="true" width="15.5727272727273"/>
-    <col min="56" max="56" customWidth="true" width="14.2818181818182"/>
-    <col min="57" max="57" customWidth="true" width="17.0"/>
-    <col min="58" max="58" customWidth="true" width="16.2818181818182"/>
-    <col min="59" max="59" customWidth="true" width="13.5727272727273"/>
-    <col min="60" max="61" customWidth="true" width="12.7181818181818"/>
-    <col min="62" max="62" customWidth="true" width="21.8545454545455"/>
-    <col min="63" max="63" customWidth="true" width="30.5727272727273"/>
-    <col min="64" max="64" customWidth="true" width="10.0"/>
-    <col min="65" max="65" customWidth="true" width="42.5727272727273"/>
-    <col min="66" max="66" customWidth="true" width="38.1454545454545"/>
-    <col min="67" max="67" customWidth="true" width="19.4272727272727"/>
-    <col min="68" max="68" customWidth="true" width="35.4272727272727"/>
-    <col min="69" max="69" customWidth="true" width="9.57272727272727"/>
+    <col min="1" max="1" width="5.14285714285714" customWidth="1"/>
+    <col min="2" max="3" width="24.5714285714286" customWidth="1"/>
+    <col min="4" max="4" width="79.4285714285714" customWidth="1"/>
+    <col min="5" max="5" width="11.5714285714286" customWidth="1"/>
+    <col min="6" max="6" width="5.14285714285714" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="12.7142857142857" customWidth="1"/>
+    <col min="9" max="9" width="5.85714285714286" customWidth="1"/>
+    <col min="10" max="10" width="6" customWidth="1"/>
+    <col min="11" max="11" width="5.85714285714286" customWidth="1"/>
+    <col min="12" max="12" width="14.2857142857143" customWidth="1"/>
+    <col min="13" max="13" width="9.42857142857143" customWidth="1"/>
+    <col min="14" max="14" width="14.4285714285714" customWidth="1"/>
+    <col min="15" max="15" width="15.5714285714286" customWidth="1"/>
+    <col min="16" max="16" width="14.4285714285714" customWidth="1"/>
+    <col min="17" max="17" width="39.4285714285714" customWidth="1"/>
+    <col min="18" max="18" width="11.7142857142857" customWidth="1"/>
+    <col min="19" max="19" width="11.8571428571429" customWidth="1"/>
+    <col min="20" max="20" width="6.42857142857143" customWidth="1"/>
+    <col min="21" max="22" width="6.57142857142857" customWidth="1"/>
+    <col min="23" max="23" width="37.1428571428571" customWidth="1"/>
+    <col min="24" max="25" width="8" customWidth="1"/>
+    <col min="26" max="26" width="7.71428571428571" customWidth="1"/>
+    <col min="27" max="27" width="6.28571428571429" customWidth="1"/>
+    <col min="28" max="28" width="9.28571428571429" customWidth="1"/>
+    <col min="29" max="29" width="9.71428571428571" customWidth="1"/>
+    <col min="30" max="30" width="12.8571428571429" customWidth="1"/>
+    <col min="31" max="31" width="16.1428571428571" customWidth="1"/>
+    <col min="32" max="32" width="15.4285714285714" customWidth="1"/>
+    <col min="33" max="33" width="24.5714285714286" customWidth="1"/>
+    <col min="34" max="34" width="8.57142857142857" customWidth="1"/>
+    <col min="35" max="35" width="14.7142857142857" customWidth="1"/>
+    <col min="36" max="36" width="18.5714285714286" customWidth="1"/>
+    <col min="37" max="37" width="14.1428571428571" customWidth="1"/>
+    <col min="38" max="38" width="14.7142857142857" customWidth="1"/>
+    <col min="39" max="39" width="17.4285714285714" customWidth="1"/>
+    <col min="40" max="40" width="22" customWidth="1"/>
+    <col min="41" max="41" width="17.5714285714286" customWidth="1"/>
+    <col min="42" max="42" width="25.2857142857143" customWidth="1"/>
+    <col min="43" max="43" width="13" customWidth="1"/>
+    <col min="44" max="44" width="23.7142857142857" customWidth="1"/>
+    <col min="45" max="45" width="10" customWidth="1"/>
+    <col min="46" max="46" width="13" customWidth="1"/>
+    <col min="47" max="47" width="15.5714285714286" customWidth="1"/>
+    <col min="48" max="48" width="21.1428571428571" customWidth="1"/>
+    <col min="49" max="49" width="11.5714285714286" customWidth="1"/>
+    <col min="50" max="50" width="16.7142857142857" customWidth="1"/>
+    <col min="51" max="51" width="14" customWidth="1"/>
+    <col min="52" max="52" width="19.4285714285714" customWidth="1"/>
+    <col min="53" max="53" width="18.8571428571429" customWidth="1"/>
+    <col min="54" max="54" width="23.2857142857143" customWidth="1"/>
+    <col min="55" max="55" width="15.5714285714286" customWidth="1"/>
+    <col min="56" max="56" width="14.2857142857143" customWidth="1"/>
+    <col min="57" max="57" width="17" customWidth="1"/>
+    <col min="58" max="58" width="16.2857142857143" customWidth="1"/>
+    <col min="59" max="59" width="13.5714285714286" customWidth="1"/>
+    <col min="60" max="61" width="12.7142857142857" customWidth="1"/>
+    <col min="62" max="62" width="21.8571428571429" customWidth="1"/>
+    <col min="63" max="63" width="30.5714285714286" customWidth="1"/>
+    <col min="64" max="64" width="10" customWidth="1"/>
+    <col min="65" max="65" width="42.5714285714286" customWidth="1"/>
+    <col min="66" max="66" width="38.1428571428571" customWidth="1"/>
+    <col min="67" max="67" width="19.4285714285714" customWidth="1"/>
+    <col min="68" max="68" width="35.4285714285714" customWidth="1"/>
+    <col min="69" max="69" width="9.57142857142857" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -7731,7 +7555,7 @@
       <c r="BP2" s="27"/>
       <c r="BQ2" s="27"/>
     </row>
-    <row r="3" ht="15.25" spans="1:69">
+    <row r="3" ht="15.75" spans="1:69">
       <c r="A3" s="28" t="s">
         <v>9</v>
       </c>
@@ -7778,7 +7602,7 @@
         <v>25</v>
       </c>
       <c r="P3" s="30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="Q3" s="30" t="s">
         <v>23</v>
@@ -7787,13 +7611,13 @@
         <v>26</v>
       </c>
       <c r="S3" s="28" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="T3" s="28" t="s">
         <v>28</v>
       </c>
       <c r="U3" s="31" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="V3" s="31" t="s">
         <v>30</v>
@@ -7862,7 +7686,7 @@
         <v>51</v>
       </c>
       <c r="AR3" s="33" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AS3" s="28" t="s">
         <v>53</v>
@@ -7940,15 +7764,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.25" spans="1:69">
+    <row r="4" ht="15.75" spans="1:69">
       <c r="A4" s="26">
         <v>1</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C4" s="26" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D4" s="26" t="s">
         <v>76</v>
@@ -8104,11 +7928,11 @@
       <c r="AT4" s="35" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" t="s" s="0">
-        <v>196</v>
-      </c>
-      <c r="AV4" t="s" s="0">
-        <v>197</v>
+      <c r="AU4" t="s">
+        <v>129</v>
+      </c>
+      <c r="AV4" t="s">
+        <v>130</v>
       </c>
       <c r="AW4" s="35">
         <f>AM4</f>
@@ -8122,8 +7946,8 @@
         <f>AU4+AW4</f>
         <v>32.6603333333333</v>
       </c>
-      <c r="AZ4" t="s" s="0">
-        <v>132</v>
+      <c r="AZ4" t="s">
+        <v>131</v>
       </c>
       <c r="BA4" s="36"/>
       <c r="BB4" s="36" t="s">
@@ -8147,11 +7971,11 @@
       <c r="BL4" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="BM4" t="s" s="0">
-        <v>199</v>
-      </c>
-      <c r="BN4" t="s" s="0">
-        <v>198</v>
+      <c r="BM4" t="s">
+        <v>132</v>
+      </c>
+      <c r="BN4" t="s">
+        <v>133</v>
       </c>
       <c r="BO4" s="35">
         <f>ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
@@ -8308,73 +8132,73 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ5"/>
-  <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="8.7047619047619" defaultRowHeight="15" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="5.14545454545455"/>
-    <col min="2" max="3" customWidth="true" width="24.5727272727273"/>
-    <col min="4" max="4" customWidth="true" width="79.4272727272727"/>
-    <col min="5" max="5" customWidth="true" width="11.5727272727273"/>
-    <col min="6" max="6" customWidth="true" width="5.14545454545455"/>
-    <col min="7" max="7" customWidth="true" width="11.0"/>
-    <col min="8" max="8" customWidth="true" width="12.7181818181818"/>
-    <col min="9" max="9" customWidth="true" width="5.85454545454545"/>
-    <col min="10" max="10" customWidth="true" width="6.0"/>
-    <col min="11" max="11" customWidth="true" width="5.85454545454545"/>
-    <col min="12" max="12" customWidth="true" width="14.2818181818182"/>
-    <col min="13" max="13" customWidth="true" width="9.42727272727273"/>
-    <col min="14" max="14" customWidth="true" width="14.4272727272727"/>
-    <col min="15" max="15" customWidth="true" width="15.5727272727273"/>
-    <col min="16" max="16" customWidth="true" width="14.4272727272727"/>
-    <col min="17" max="17" customWidth="true" width="39.4272727272727"/>
-    <col min="18" max="18" customWidth="true" width="11.7181818181818"/>
-    <col min="19" max="19" customWidth="true" width="11.8545454545455"/>
-    <col min="20" max="20" customWidth="true" width="6.42727272727273"/>
-    <col min="21" max="22" customWidth="true" width="6.57272727272727"/>
-    <col min="23" max="23" customWidth="true" width="37.1454545454545"/>
-    <col min="24" max="25" customWidth="true" width="8.0"/>
-    <col min="26" max="26" customWidth="true" width="7.71818181818182"/>
-    <col min="27" max="27" customWidth="true" width="6.28181818181818"/>
-    <col min="28" max="28" customWidth="true" width="9.28181818181818"/>
-    <col min="29" max="29" customWidth="true" width="9.71818181818182"/>
-    <col min="30" max="30" customWidth="true" width="12.8545454545455"/>
-    <col min="31" max="31" customWidth="true" width="16.1454545454545"/>
-    <col min="32" max="32" customWidth="true" width="15.4272727272727"/>
-    <col min="33" max="33" customWidth="true" width="24.5727272727273"/>
-    <col min="34" max="34" customWidth="true" width="8.57272727272727"/>
-    <col min="35" max="35" customWidth="true" width="14.7181818181818"/>
-    <col min="36" max="36" customWidth="true" width="18.5727272727273"/>
-    <col min="37" max="37" customWidth="true" width="14.1454545454545"/>
-    <col min="38" max="38" customWidth="true" width="14.7181818181818"/>
-    <col min="39" max="39" customWidth="true" width="17.4272727272727"/>
-    <col min="40" max="40" customWidth="true" width="22.0"/>
-    <col min="41" max="41" customWidth="true" width="17.5727272727273"/>
-    <col min="42" max="42" customWidth="true" width="25.2818181818182"/>
-    <col min="43" max="43" customWidth="true" width="13.0"/>
-    <col min="44" max="44" customWidth="true" width="23.7181818181818"/>
-    <col min="45" max="45" customWidth="true" width="10.0"/>
-    <col min="46" max="46" customWidth="true" width="13.0"/>
-    <col min="47" max="47" customWidth="true" width="15.5727272727273"/>
-    <col min="48" max="48" customWidth="true" width="21.1454545454545"/>
-    <col min="49" max="49" customWidth="true" width="11.5727272727273"/>
-    <col min="50" max="50" customWidth="true" width="16.7181818181818"/>
-    <col min="51" max="51" customWidth="true" width="14.0"/>
-    <col min="52" max="52" customWidth="true" width="19.4272727272727"/>
-    <col min="53" max="53" customWidth="true" width="18.8545454545455"/>
-    <col min="54" max="54" customWidth="true" width="23.2818181818182"/>
-    <col min="55" max="55" customWidth="true" width="15.5727272727273"/>
-    <col min="56" max="56" customWidth="true" width="14.2818181818182"/>
-    <col min="57" max="57" customWidth="true" width="17.0"/>
-    <col min="58" max="58" customWidth="true" width="16.2818181818182"/>
-    <col min="59" max="59" customWidth="true" width="13.5727272727273"/>
-    <col min="60" max="61" customWidth="true" width="12.7181818181818"/>
-    <col min="62" max="62" customWidth="true" width="21.8545454545455"/>
-    <col min="63" max="63" customWidth="true" width="30.5727272727273"/>
-    <col min="64" max="64" customWidth="true" width="10.0"/>
-    <col min="65" max="65" customWidth="true" width="42.5727272727273"/>
-    <col min="66" max="66" customWidth="true" width="38.1454545454545"/>
-    <col min="67" max="67" customWidth="true" width="19.4272727272727"/>
-    <col min="68" max="68" customWidth="true" width="35.4272727272727"/>
-    <col min="69" max="69" customWidth="true" width="9.57272727272727"/>
+    <col min="1" max="1" width="5.14285714285714" customWidth="1"/>
+    <col min="2" max="3" width="24.5714285714286" customWidth="1"/>
+    <col min="4" max="4" width="79.4285714285714" customWidth="1"/>
+    <col min="5" max="5" width="11.5714285714286" customWidth="1"/>
+    <col min="6" max="6" width="5.14285714285714" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="12.7142857142857" customWidth="1"/>
+    <col min="9" max="9" width="5.85714285714286" customWidth="1"/>
+    <col min="10" max="10" width="6" customWidth="1"/>
+    <col min="11" max="11" width="5.85714285714286" customWidth="1"/>
+    <col min="12" max="12" width="14.2857142857143" customWidth="1"/>
+    <col min="13" max="13" width="9.42857142857143" customWidth="1"/>
+    <col min="14" max="14" width="14.4285714285714" customWidth="1"/>
+    <col min="15" max="15" width="15.5714285714286" customWidth="1"/>
+    <col min="16" max="16" width="14.4285714285714" customWidth="1"/>
+    <col min="17" max="17" width="39.4285714285714" customWidth="1"/>
+    <col min="18" max="18" width="11.7142857142857" customWidth="1"/>
+    <col min="19" max="19" width="11.8571428571429" customWidth="1"/>
+    <col min="20" max="20" width="6.42857142857143" customWidth="1"/>
+    <col min="21" max="22" width="6.57142857142857" customWidth="1"/>
+    <col min="23" max="23" width="37.1428571428571" customWidth="1"/>
+    <col min="24" max="25" width="8" customWidth="1"/>
+    <col min="26" max="26" width="7.71428571428571" customWidth="1"/>
+    <col min="27" max="27" width="6.28571428571429" customWidth="1"/>
+    <col min="28" max="28" width="9.28571428571429" customWidth="1"/>
+    <col min="29" max="29" width="9.71428571428571" customWidth="1"/>
+    <col min="30" max="30" width="12.8571428571429" customWidth="1"/>
+    <col min="31" max="31" width="16.1428571428571" customWidth="1"/>
+    <col min="32" max="32" width="15.4285714285714" customWidth="1"/>
+    <col min="33" max="33" width="24.5714285714286" customWidth="1"/>
+    <col min="34" max="34" width="8.57142857142857" customWidth="1"/>
+    <col min="35" max="35" width="14.7142857142857" customWidth="1"/>
+    <col min="36" max="36" width="18.5714285714286" customWidth="1"/>
+    <col min="37" max="37" width="14.1428571428571" customWidth="1"/>
+    <col min="38" max="38" width="14.7142857142857" customWidth="1"/>
+    <col min="39" max="39" width="17.4285714285714" customWidth="1"/>
+    <col min="40" max="40" width="22" customWidth="1"/>
+    <col min="41" max="41" width="17.5714285714286" customWidth="1"/>
+    <col min="42" max="42" width="25.2857142857143" customWidth="1"/>
+    <col min="43" max="43" width="13" customWidth="1"/>
+    <col min="44" max="44" width="23.7142857142857" customWidth="1"/>
+    <col min="45" max="45" width="10" customWidth="1"/>
+    <col min="46" max="46" width="13" customWidth="1"/>
+    <col min="47" max="47" width="15.5714285714286" customWidth="1"/>
+    <col min="48" max="48" width="21.1428571428571" customWidth="1"/>
+    <col min="49" max="49" width="11.5714285714286" customWidth="1"/>
+    <col min="50" max="50" width="16.7142857142857" customWidth="1"/>
+    <col min="51" max="51" width="14" customWidth="1"/>
+    <col min="52" max="52" width="19.4285714285714" customWidth="1"/>
+    <col min="53" max="53" width="18.8571428571429" customWidth="1"/>
+    <col min="54" max="54" width="23.2857142857143" customWidth="1"/>
+    <col min="55" max="55" width="15.5714285714286" customWidth="1"/>
+    <col min="56" max="56" width="14.2857142857143" customWidth="1"/>
+    <col min="57" max="57" width="17" customWidth="1"/>
+    <col min="58" max="58" width="16.2857142857143" customWidth="1"/>
+    <col min="59" max="59" width="13.5714285714286" customWidth="1"/>
+    <col min="60" max="61" width="12.7142857142857" customWidth="1"/>
+    <col min="62" max="62" width="21.8571428571429" customWidth="1"/>
+    <col min="63" max="63" width="30.5714285714286" customWidth="1"/>
+    <col min="64" max="64" width="10" customWidth="1"/>
+    <col min="65" max="65" width="42.5714285714286" customWidth="1"/>
+    <col min="66" max="66" width="38.1428571428571" customWidth="1"/>
+    <col min="67" max="67" width="19.4285714285714" customWidth="1"/>
+    <col min="68" max="68" width="35.4285714285714" customWidth="1"/>
+    <col min="69" max="69" width="9.57142857142857" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -8545,7 +8369,7 @@
       <c r="BP2" s="27"/>
       <c r="BQ2" s="27"/>
     </row>
-    <row r="3" ht="15.25" spans="1:69">
+    <row r="3" ht="15.75" spans="1:69">
       <c r="A3" s="28" t="s">
         <v>9</v>
       </c>
@@ -8592,7 +8416,7 @@
         <v>25</v>
       </c>
       <c r="P3" s="30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="Q3" s="30" t="s">
         <v>23</v>
@@ -8601,13 +8425,13 @@
         <v>26</v>
       </c>
       <c r="S3" s="28" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="T3" s="28" t="s">
         <v>28</v>
       </c>
       <c r="U3" s="31" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="V3" s="31" t="s">
         <v>30</v>
@@ -8676,7 +8500,7 @@
         <v>51</v>
       </c>
       <c r="AR3" s="33" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AS3" s="28" t="s">
         <v>53</v>
@@ -8754,15 +8578,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.25" spans="1:69">
+    <row r="4" ht="15.75" spans="1:69">
       <c r="A4" s="26">
         <v>1</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C4" s="26" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D4" s="26" t="s">
         <v>76</v>
@@ -8918,11 +8742,11 @@
       <c r="AT4" s="35" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" t="s" s="0">
-        <v>200</v>
-      </c>
-      <c r="AV4" t="s" s="0">
-        <v>201</v>
+      <c r="AU4" t="s">
+        <v>135</v>
+      </c>
+      <c r="AV4" t="s">
+        <v>136</v>
       </c>
       <c r="AW4" s="35">
         <f>AM4</f>
@@ -8936,7 +8760,7 @@
         <f>AU4+AW4</f>
         <v>83.3283333333333</v>
       </c>
-      <c r="AZ4" t="s" s="0">
+      <c r="AZ4" t="s">
         <v>137</v>
       </c>
       <c r="BA4" s="36"/>
@@ -8961,11 +8785,11 @@
       <c r="BL4" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="BM4" t="s" s="0">
-        <v>203</v>
-      </c>
-      <c r="BN4" t="s" s="0">
-        <v>202</v>
+      <c r="BM4" t="s">
+        <v>138</v>
+      </c>
+      <c r="BN4" t="s">
+        <v>139</v>
       </c>
       <c r="BO4" s="35">
         <f>ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
@@ -9122,73 +8946,73 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ5"/>
-  <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="8.7047619047619" defaultRowHeight="15" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="5.14545454545455"/>
-    <col min="2" max="3" customWidth="true" width="22.0"/>
-    <col min="4" max="4" customWidth="true" width="79.4272727272727"/>
-    <col min="5" max="5" customWidth="true" width="11.5727272727273"/>
-    <col min="6" max="6" customWidth="true" width="5.14545454545455"/>
-    <col min="7" max="7" customWidth="true" width="11.0"/>
-    <col min="8" max="8" customWidth="true" width="12.7181818181818"/>
-    <col min="9" max="9" customWidth="true" width="5.85454545454545"/>
-    <col min="10" max="10" customWidth="true" width="6.0"/>
-    <col min="11" max="11" customWidth="true" width="5.85454545454545"/>
-    <col min="12" max="12" customWidth="true" width="14.2818181818182"/>
-    <col min="13" max="13" customWidth="true" width="9.42727272727273"/>
-    <col min="14" max="14" customWidth="true" width="14.4272727272727"/>
-    <col min="15" max="15" customWidth="true" width="15.5727272727273"/>
-    <col min="16" max="16" customWidth="true" width="14.4272727272727"/>
-    <col min="17" max="17" customWidth="true" width="39.4272727272727"/>
-    <col min="18" max="18" customWidth="true" width="11.7181818181818"/>
-    <col min="19" max="19" customWidth="true" width="11.8545454545455"/>
-    <col min="20" max="20" customWidth="true" width="6.42727272727273"/>
-    <col min="21" max="22" customWidth="true" width="6.57272727272727"/>
-    <col min="23" max="23" customWidth="true" width="37.1454545454545"/>
-    <col min="24" max="25" customWidth="true" width="8.0"/>
-    <col min="26" max="26" customWidth="true" width="7.71818181818182"/>
-    <col min="27" max="27" customWidth="true" width="6.28181818181818"/>
-    <col min="28" max="28" customWidth="true" width="9.28181818181818"/>
-    <col min="29" max="29" customWidth="true" width="9.71818181818182"/>
-    <col min="30" max="30" customWidth="true" width="12.8545454545455"/>
-    <col min="31" max="31" customWidth="true" width="16.1454545454545"/>
-    <col min="32" max="32" customWidth="true" width="15.4272727272727"/>
-    <col min="33" max="33" customWidth="true" width="24.5727272727273"/>
-    <col min="34" max="34" customWidth="true" width="8.57272727272727"/>
-    <col min="35" max="35" customWidth="true" width="14.7181818181818"/>
-    <col min="36" max="36" customWidth="true" width="18.5727272727273"/>
-    <col min="37" max="37" customWidth="true" width="14.1454545454545"/>
-    <col min="38" max="38" customWidth="true" width="14.7181818181818"/>
-    <col min="39" max="39" customWidth="true" width="17.4272727272727"/>
-    <col min="40" max="40" customWidth="true" width="22.0"/>
-    <col min="41" max="41" customWidth="true" width="17.5727272727273"/>
-    <col min="42" max="42" customWidth="true" width="25.2818181818182"/>
-    <col min="43" max="43" customWidth="true" width="13.0"/>
-    <col min="44" max="44" customWidth="true" width="23.7181818181818"/>
-    <col min="45" max="45" customWidth="true" width="10.0"/>
-    <col min="46" max="46" customWidth="true" width="13.0"/>
-    <col min="47" max="47" customWidth="true" width="15.5727272727273"/>
-    <col min="48" max="48" customWidth="true" width="21.1454545454545"/>
-    <col min="49" max="49" customWidth="true" width="11.5727272727273"/>
-    <col min="50" max="50" customWidth="true" width="16.7181818181818"/>
-    <col min="51" max="51" customWidth="true" width="14.0"/>
-    <col min="52" max="52" customWidth="true" width="19.4272727272727"/>
-    <col min="53" max="53" customWidth="true" width="18.8545454545455"/>
-    <col min="54" max="54" customWidth="true" width="23.2818181818182"/>
-    <col min="55" max="55" customWidth="true" width="15.5727272727273"/>
-    <col min="56" max="56" customWidth="true" width="14.2818181818182"/>
-    <col min="57" max="57" customWidth="true" width="17.0"/>
-    <col min="58" max="58" customWidth="true" width="16.2818181818182"/>
-    <col min="59" max="59" customWidth="true" width="13.5727272727273"/>
-    <col min="60" max="61" customWidth="true" width="12.7181818181818"/>
-    <col min="62" max="62" customWidth="true" width="21.8545454545455"/>
-    <col min="63" max="63" customWidth="true" width="30.5727272727273"/>
-    <col min="64" max="64" customWidth="true" width="10.0"/>
-    <col min="65" max="65" customWidth="true" width="42.5727272727273"/>
-    <col min="66" max="66" customWidth="true" width="38.1454545454545"/>
-    <col min="67" max="67" customWidth="true" width="19.4272727272727"/>
-    <col min="68" max="68" customWidth="true" width="35.4272727272727"/>
-    <col min="69" max="69" customWidth="true" width="9.57272727272727"/>
+    <col min="1" max="1" width="5.14285714285714" customWidth="1"/>
+    <col min="2" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="79.4285714285714" customWidth="1"/>
+    <col min="5" max="5" width="11.5714285714286" customWidth="1"/>
+    <col min="6" max="6" width="5.14285714285714" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="12.7142857142857" customWidth="1"/>
+    <col min="9" max="9" width="5.85714285714286" customWidth="1"/>
+    <col min="10" max="10" width="6" customWidth="1"/>
+    <col min="11" max="11" width="5.85714285714286" customWidth="1"/>
+    <col min="12" max="12" width="14.2857142857143" customWidth="1"/>
+    <col min="13" max="13" width="9.42857142857143" customWidth="1"/>
+    <col min="14" max="14" width="14.4285714285714" customWidth="1"/>
+    <col min="15" max="15" width="15.5714285714286" customWidth="1"/>
+    <col min="16" max="16" width="14.4285714285714" customWidth="1"/>
+    <col min="17" max="17" width="39.4285714285714" customWidth="1"/>
+    <col min="18" max="18" width="11.7142857142857" customWidth="1"/>
+    <col min="19" max="19" width="11.8571428571429" customWidth="1"/>
+    <col min="20" max="20" width="6.42857142857143" customWidth="1"/>
+    <col min="21" max="22" width="6.57142857142857" customWidth="1"/>
+    <col min="23" max="23" width="37.1428571428571" customWidth="1"/>
+    <col min="24" max="25" width="8" customWidth="1"/>
+    <col min="26" max="26" width="7.71428571428571" customWidth="1"/>
+    <col min="27" max="27" width="6.28571428571429" customWidth="1"/>
+    <col min="28" max="28" width="9.28571428571429" customWidth="1"/>
+    <col min="29" max="29" width="9.71428571428571" customWidth="1"/>
+    <col min="30" max="30" width="12.8571428571429" customWidth="1"/>
+    <col min="31" max="31" width="16.1428571428571" customWidth="1"/>
+    <col min="32" max="32" width="15.4285714285714" customWidth="1"/>
+    <col min="33" max="33" width="24.5714285714286" customWidth="1"/>
+    <col min="34" max="34" width="8.57142857142857" customWidth="1"/>
+    <col min="35" max="35" width="14.7142857142857" customWidth="1"/>
+    <col min="36" max="36" width="18.5714285714286" customWidth="1"/>
+    <col min="37" max="37" width="14.1428571428571" customWidth="1"/>
+    <col min="38" max="38" width="14.7142857142857" customWidth="1"/>
+    <col min="39" max="39" width="17.4285714285714" customWidth="1"/>
+    <col min="40" max="40" width="22" customWidth="1"/>
+    <col min="41" max="41" width="17.5714285714286" customWidth="1"/>
+    <col min="42" max="42" width="25.2857142857143" customWidth="1"/>
+    <col min="43" max="43" width="13" customWidth="1"/>
+    <col min="44" max="44" width="23.7142857142857" customWidth="1"/>
+    <col min="45" max="45" width="10" customWidth="1"/>
+    <col min="46" max="46" width="13" customWidth="1"/>
+    <col min="47" max="47" width="15.5714285714286" customWidth="1"/>
+    <col min="48" max="48" width="21.1428571428571" customWidth="1"/>
+    <col min="49" max="49" width="11.5714285714286" customWidth="1"/>
+    <col min="50" max="50" width="16.7142857142857" customWidth="1"/>
+    <col min="51" max="51" width="14" customWidth="1"/>
+    <col min="52" max="52" width="19.4285714285714" customWidth="1"/>
+    <col min="53" max="53" width="18.8571428571429" customWidth="1"/>
+    <col min="54" max="54" width="23.2857142857143" customWidth="1"/>
+    <col min="55" max="55" width="15.5714285714286" customWidth="1"/>
+    <col min="56" max="56" width="14.2857142857143" customWidth="1"/>
+    <col min="57" max="57" width="17" customWidth="1"/>
+    <col min="58" max="58" width="16.2857142857143" customWidth="1"/>
+    <col min="59" max="59" width="13.5714285714286" customWidth="1"/>
+    <col min="60" max="61" width="12.7142857142857" customWidth="1"/>
+    <col min="62" max="62" width="21.8571428571429" customWidth="1"/>
+    <col min="63" max="63" width="30.5714285714286" customWidth="1"/>
+    <col min="64" max="64" width="10" customWidth="1"/>
+    <col min="65" max="65" width="42.5714285714286" customWidth="1"/>
+    <col min="66" max="66" width="38.1428571428571" customWidth="1"/>
+    <col min="67" max="67" width="19.4285714285714" customWidth="1"/>
+    <col min="68" max="68" width="35.4285714285714" customWidth="1"/>
+    <col min="69" max="69" width="9.57142857142857" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -9359,7 +9183,7 @@
       <c r="BP2" s="27"/>
       <c r="BQ2" s="27"/>
     </row>
-    <row r="3" ht="15.25" spans="1:69">
+    <row r="3" ht="15.75" spans="1:69">
       <c r="A3" s="28" t="s">
         <v>9</v>
       </c>
@@ -9406,7 +9230,7 @@
         <v>25</v>
       </c>
       <c r="P3" s="30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="Q3" s="30" t="s">
         <v>23</v>
@@ -9415,13 +9239,13 @@
         <v>26</v>
       </c>
       <c r="S3" s="28" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="T3" s="28" t="s">
         <v>28</v>
       </c>
       <c r="U3" s="31" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="V3" s="31" t="s">
         <v>30</v>
@@ -9490,7 +9314,7 @@
         <v>51</v>
       </c>
       <c r="AR3" s="33" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AS3" s="28" t="s">
         <v>53</v>
@@ -9568,7 +9392,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.25" spans="1:69">
+    <row r="4" ht="15.75" spans="1:69">
       <c r="A4" s="26">
         <v>1</v>
       </c>
@@ -9595,7 +9419,7 @@
         <v>400</v>
       </c>
       <c r="I4" s="27" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J4" s="35">
         <v>2</v>
@@ -9732,8 +9556,6 @@
       <c r="AT4" s="35" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" s="0"/>
-      <c r="AV4" s="0"/>
       <c r="AW4" s="35">
         <f>AM4</f>
         <v>4</v>
@@ -9772,11 +9594,11 @@
       <c r="BL4" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="BM4" t="s" s="0">
-        <v>100</v>
-      </c>
-      <c r="BN4" t="s" s="0">
-        <v>100</v>
+      <c r="BM4" t="s">
+        <v>99</v>
+      </c>
+      <c r="BN4" t="s">
+        <v>99</v>
       </c>
       <c r="BO4" s="35">
         <f>ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
@@ -9921,73 +9743,73 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ5"/>
-  <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="8.7047619047619" defaultRowHeight="15" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="5.14545454545455"/>
-    <col min="2" max="3" customWidth="true" width="22.0"/>
-    <col min="4" max="4" customWidth="true" width="79.4272727272727"/>
-    <col min="5" max="5" customWidth="true" width="11.5727272727273"/>
-    <col min="6" max="6" customWidth="true" width="5.14545454545455"/>
-    <col min="7" max="7" customWidth="true" width="11.0"/>
-    <col min="8" max="8" customWidth="true" width="12.7181818181818"/>
-    <col min="9" max="9" customWidth="true" width="5.85454545454545"/>
-    <col min="10" max="10" customWidth="true" width="6.0"/>
-    <col min="11" max="11" customWidth="true" width="5.85454545454545"/>
-    <col min="12" max="12" customWidth="true" width="14.2818181818182"/>
-    <col min="13" max="13" customWidth="true" width="9.42727272727273"/>
-    <col min="14" max="14" customWidth="true" width="14.4272727272727"/>
-    <col min="15" max="15" customWidth="true" width="15.5727272727273"/>
-    <col min="16" max="16" customWidth="true" width="14.4272727272727"/>
-    <col min="17" max="17" customWidth="true" width="39.4272727272727"/>
-    <col min="18" max="18" customWidth="true" width="11.7181818181818"/>
-    <col min="19" max="19" customWidth="true" width="11.8545454545455"/>
-    <col min="20" max="20" customWidth="true" width="6.42727272727273"/>
-    <col min="21" max="22" customWidth="true" width="6.57272727272727"/>
-    <col min="23" max="23" customWidth="true" width="37.1454545454545"/>
-    <col min="24" max="25" customWidth="true" width="8.0"/>
-    <col min="26" max="26" customWidth="true" width="7.71818181818182"/>
-    <col min="27" max="27" customWidth="true" width="6.28181818181818"/>
-    <col min="28" max="28" customWidth="true" width="9.28181818181818"/>
-    <col min="29" max="29" customWidth="true" width="9.71818181818182"/>
-    <col min="30" max="30" customWidth="true" width="12.8545454545455"/>
-    <col min="31" max="31" customWidth="true" width="16.1454545454545"/>
-    <col min="32" max="32" customWidth="true" width="15.4272727272727"/>
-    <col min="33" max="33" customWidth="true" width="24.5727272727273"/>
-    <col min="34" max="34" customWidth="true" width="8.57272727272727"/>
-    <col min="35" max="35" customWidth="true" width="14.7181818181818"/>
-    <col min="36" max="36" customWidth="true" width="18.5727272727273"/>
-    <col min="37" max="37" customWidth="true" width="14.1454545454545"/>
-    <col min="38" max="38" customWidth="true" width="14.7181818181818"/>
-    <col min="39" max="39" customWidth="true" width="17.4272727272727"/>
-    <col min="40" max="40" customWidth="true" width="22.0"/>
-    <col min="41" max="41" customWidth="true" width="17.5727272727273"/>
-    <col min="42" max="42" customWidth="true" width="25.2818181818182"/>
-    <col min="43" max="43" customWidth="true" width="13.0"/>
-    <col min="44" max="44" customWidth="true" width="23.7181818181818"/>
-    <col min="45" max="45" customWidth="true" width="10.0"/>
-    <col min="46" max="46" customWidth="true" width="13.0"/>
-    <col min="47" max="47" customWidth="true" width="15.5727272727273"/>
-    <col min="48" max="48" customWidth="true" width="21.1454545454545"/>
-    <col min="49" max="49" customWidth="true" width="11.5727272727273"/>
-    <col min="50" max="50" customWidth="true" width="16.7181818181818"/>
-    <col min="51" max="51" customWidth="true" width="14.0"/>
-    <col min="52" max="52" customWidth="true" width="19.4272727272727"/>
-    <col min="53" max="53" customWidth="true" width="18.8545454545455"/>
-    <col min="54" max="54" customWidth="true" width="23.2818181818182"/>
-    <col min="55" max="55" customWidth="true" width="15.5727272727273"/>
-    <col min="56" max="56" customWidth="true" width="14.2818181818182"/>
-    <col min="57" max="57" customWidth="true" width="17.0"/>
-    <col min="58" max="58" customWidth="true" width="16.2818181818182"/>
-    <col min="59" max="59" customWidth="true" width="13.5727272727273"/>
-    <col min="60" max="61" customWidth="true" width="12.7181818181818"/>
-    <col min="62" max="62" customWidth="true" width="21.8545454545455"/>
-    <col min="63" max="63" customWidth="true" width="30.5727272727273"/>
-    <col min="64" max="64" customWidth="true" width="10.0"/>
-    <col min="65" max="65" customWidth="true" width="42.5727272727273"/>
-    <col min="66" max="66" customWidth="true" width="38.1454545454545"/>
-    <col min="67" max="67" customWidth="true" width="19.4272727272727"/>
-    <col min="68" max="68" customWidth="true" width="35.4272727272727"/>
-    <col min="69" max="69" customWidth="true" width="9.57272727272727"/>
+    <col min="1" max="1" width="5.14285714285714" customWidth="1"/>
+    <col min="2" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="79.4285714285714" customWidth="1"/>
+    <col min="5" max="5" width="11.5714285714286" customWidth="1"/>
+    <col min="6" max="6" width="5.14285714285714" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="12.7142857142857" customWidth="1"/>
+    <col min="9" max="9" width="5.85714285714286" customWidth="1"/>
+    <col min="10" max="10" width="6" customWidth="1"/>
+    <col min="11" max="11" width="5.85714285714286" customWidth="1"/>
+    <col min="12" max="12" width="14.2857142857143" customWidth="1"/>
+    <col min="13" max="13" width="9.42857142857143" customWidth="1"/>
+    <col min="14" max="14" width="14.4285714285714" customWidth="1"/>
+    <col min="15" max="15" width="15.5714285714286" customWidth="1"/>
+    <col min="16" max="16" width="14.4285714285714" customWidth="1"/>
+    <col min="17" max="17" width="39.4285714285714" customWidth="1"/>
+    <col min="18" max="18" width="11.7142857142857" customWidth="1"/>
+    <col min="19" max="19" width="11.8571428571429" customWidth="1"/>
+    <col min="20" max="20" width="6.42857142857143" customWidth="1"/>
+    <col min="21" max="22" width="6.57142857142857" customWidth="1"/>
+    <col min="23" max="23" width="37.1428571428571" customWidth="1"/>
+    <col min="24" max="25" width="8" customWidth="1"/>
+    <col min="26" max="26" width="7.71428571428571" customWidth="1"/>
+    <col min="27" max="27" width="6.28571428571429" customWidth="1"/>
+    <col min="28" max="28" width="9.28571428571429" customWidth="1"/>
+    <col min="29" max="29" width="9.71428571428571" customWidth="1"/>
+    <col min="30" max="30" width="12.8571428571429" customWidth="1"/>
+    <col min="31" max="31" width="16.1428571428571" customWidth="1"/>
+    <col min="32" max="32" width="15.4285714285714" customWidth="1"/>
+    <col min="33" max="33" width="24.5714285714286" customWidth="1"/>
+    <col min="34" max="34" width="8.57142857142857" customWidth="1"/>
+    <col min="35" max="35" width="14.7142857142857" customWidth="1"/>
+    <col min="36" max="36" width="18.5714285714286" customWidth="1"/>
+    <col min="37" max="37" width="14.1428571428571" customWidth="1"/>
+    <col min="38" max="38" width="14.7142857142857" customWidth="1"/>
+    <col min="39" max="39" width="17.4285714285714" customWidth="1"/>
+    <col min="40" max="40" width="22" customWidth="1"/>
+    <col min="41" max="41" width="17.5714285714286" customWidth="1"/>
+    <col min="42" max="42" width="25.2857142857143" customWidth="1"/>
+    <col min="43" max="43" width="13" customWidth="1"/>
+    <col min="44" max="44" width="23.7142857142857" customWidth="1"/>
+    <col min="45" max="45" width="10" customWidth="1"/>
+    <col min="46" max="46" width="13" customWidth="1"/>
+    <col min="47" max="47" width="15.5714285714286" customWidth="1"/>
+    <col min="48" max="48" width="21.1428571428571" customWidth="1"/>
+    <col min="49" max="49" width="11.5714285714286" customWidth="1"/>
+    <col min="50" max="50" width="16.7142857142857" customWidth="1"/>
+    <col min="51" max="51" width="14" customWidth="1"/>
+    <col min="52" max="52" width="19.4285714285714" customWidth="1"/>
+    <col min="53" max="53" width="18.8571428571429" customWidth="1"/>
+    <col min="54" max="54" width="23.2857142857143" customWidth="1"/>
+    <col min="55" max="55" width="15.5714285714286" customWidth="1"/>
+    <col min="56" max="56" width="14.2857142857143" customWidth="1"/>
+    <col min="57" max="57" width="17" customWidth="1"/>
+    <col min="58" max="58" width="16.2857142857143" customWidth="1"/>
+    <col min="59" max="59" width="13.5714285714286" customWidth="1"/>
+    <col min="60" max="61" width="12.7142857142857" customWidth="1"/>
+    <col min="62" max="62" width="21.8571428571429" customWidth="1"/>
+    <col min="63" max="63" width="30.5714285714286" customWidth="1"/>
+    <col min="64" max="64" width="10" customWidth="1"/>
+    <col min="65" max="65" width="42.5714285714286" customWidth="1"/>
+    <col min="66" max="66" width="38.1428571428571" customWidth="1"/>
+    <col min="67" max="67" width="19.4285714285714" customWidth="1"/>
+    <col min="68" max="68" width="35.4285714285714" customWidth="1"/>
+    <col min="69" max="69" width="9.57142857142857" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -10158,7 +9980,7 @@
       <c r="BP2" s="27"/>
       <c r="BQ2" s="27"/>
     </row>
-    <row r="3" ht="15.25" spans="1:69">
+    <row r="3" ht="15.75" spans="1:69">
       <c r="A3" s="28" t="s">
         <v>9</v>
       </c>
@@ -10205,7 +10027,7 @@
         <v>25</v>
       </c>
       <c r="P3" s="30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="Q3" s="30" t="s">
         <v>23</v>
@@ -10214,13 +10036,13 @@
         <v>26</v>
       </c>
       <c r="S3" s="28" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="T3" s="28" t="s">
         <v>28</v>
       </c>
       <c r="U3" s="31" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="V3" s="31" t="s">
         <v>30</v>
@@ -10289,7 +10111,7 @@
         <v>51</v>
       </c>
       <c r="AR3" s="33" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AS3" s="28" t="s">
         <v>53</v>
@@ -10367,7 +10189,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.25" spans="1:69">
+    <row r="4" ht="15.75" spans="1:69">
       <c r="A4" s="26">
         <v>1</v>
       </c>
@@ -10394,7 +10216,7 @@
         <v>400</v>
       </c>
       <c r="I4" s="27" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J4" s="35">
         <v>2</v>
@@ -10531,8 +10353,6 @@
       <c r="AT4" s="35" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" s="0"/>
-      <c r="AV4" s="0"/>
       <c r="AW4" s="35">
         <f>AM4</f>
         <v>4</v>
@@ -10571,11 +10391,11 @@
       <c r="BL4" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="BM4" t="s" s="0">
-        <v>100</v>
-      </c>
-      <c r="BN4" t="s" s="0">
-        <v>100</v>
+      <c r="BM4" t="s">
+        <v>99</v>
+      </c>
+      <c r="BN4" t="s">
+        <v>99</v>
       </c>
       <c r="BO4" s="35">
         <f>ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
@@ -10720,74 +10540,74 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ5"/>
-  <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="8.7047619047619" defaultRowHeight="15" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="5.14545454545455"/>
-    <col min="2" max="2" customWidth="true" width="21.8545454545455"/>
-    <col min="3" max="3" customWidth="true" width="27.5727272727273"/>
-    <col min="4" max="4" customWidth="true" width="79.4272727272727"/>
-    <col min="5" max="5" customWidth="true" width="11.5727272727273"/>
-    <col min="6" max="6" customWidth="true" width="5.14545454545455"/>
-    <col min="7" max="7" customWidth="true" width="11.0"/>
-    <col min="8" max="8" customWidth="true" width="12.7181818181818"/>
-    <col min="9" max="10" customWidth="true" width="5.85454545454545"/>
-    <col min="11" max="11" customWidth="true" width="6.0"/>
-    <col min="12" max="12" customWidth="true" width="14.2818181818182"/>
-    <col min="13" max="13" customWidth="true" width="9.42727272727273"/>
-    <col min="14" max="14" customWidth="true" width="14.2818181818182"/>
-    <col min="15" max="15" customWidth="true" width="15.5727272727273"/>
-    <col min="16" max="16" customWidth="true" width="14.4272727272727"/>
-    <col min="17" max="17" customWidth="true" width="39.4272727272727"/>
-    <col min="18" max="18" customWidth="true" width="11.7181818181818"/>
-    <col min="19" max="19" customWidth="true" width="10.0"/>
-    <col min="20" max="20" customWidth="true" width="6.42727272727273"/>
-    <col min="21" max="21" customWidth="true" width="9.85454545454546"/>
-    <col min="22" max="22" customWidth="true" width="6.57272727272727"/>
-    <col min="23" max="23" customWidth="true" width="37.1454545454545"/>
-    <col min="24" max="25" customWidth="true" width="8.0"/>
-    <col min="26" max="26" customWidth="true" width="7.71818181818182"/>
-    <col min="27" max="27" customWidth="true" width="6.28181818181818"/>
-    <col min="28" max="28" customWidth="true" width="9.28181818181818"/>
-    <col min="29" max="29" customWidth="true" width="9.71818181818182"/>
-    <col min="30" max="30" customWidth="true" width="12.8545454545455"/>
-    <col min="31" max="31" customWidth="true" width="16.1454545454545"/>
-    <col min="32" max="32" customWidth="true" width="15.4272727272727"/>
-    <col min="33" max="33" customWidth="true" width="24.5727272727273"/>
-    <col min="34" max="34" customWidth="true" width="8.57272727272727"/>
-    <col min="35" max="35" customWidth="true" width="14.7181818181818"/>
-    <col min="36" max="36" customWidth="true" width="18.5727272727273"/>
-    <col min="37" max="37" customWidth="true" width="14.1454545454545"/>
-    <col min="38" max="38" customWidth="true" width="14.7181818181818"/>
-    <col min="39" max="39" customWidth="true" width="17.4272727272727"/>
-    <col min="40" max="40" customWidth="true" width="22.0"/>
-    <col min="41" max="41" customWidth="true" width="17.5727272727273"/>
-    <col min="42" max="42" customWidth="true" width="25.2818181818182"/>
-    <col min="43" max="43" customWidth="true" width="13.0"/>
-    <col min="44" max="44" customWidth="true" width="25.7181818181818"/>
-    <col min="45" max="45" customWidth="true" width="10.0"/>
-    <col min="46" max="46" customWidth="true" width="13.0"/>
-    <col min="47" max="47" customWidth="true" width="15.5727272727273"/>
-    <col min="48" max="48" customWidth="true" width="21.1454545454545"/>
-    <col min="49" max="49" customWidth="true" width="11.5727272727273"/>
-    <col min="50" max="50" customWidth="true" width="16.7181818181818"/>
-    <col min="51" max="51" customWidth="true" width="14.0"/>
-    <col min="52" max="52" customWidth="true" width="19.4272727272727"/>
-    <col min="53" max="53" customWidth="true" width="18.8545454545455"/>
-    <col min="54" max="54" customWidth="true" width="23.2818181818182"/>
-    <col min="55" max="55" customWidth="true" width="15.5727272727273"/>
-    <col min="56" max="56" customWidth="true" width="14.2818181818182"/>
-    <col min="57" max="57" customWidth="true" width="17.0"/>
-    <col min="58" max="58" customWidth="true" width="16.2818181818182"/>
-    <col min="59" max="59" customWidth="true" width="13.5727272727273"/>
-    <col min="60" max="61" customWidth="true" width="12.7181818181818"/>
-    <col min="62" max="62" customWidth="true" width="21.8545454545455"/>
-    <col min="63" max="63" customWidth="true" width="30.5727272727273"/>
-    <col min="64" max="64" customWidth="true" width="10.0"/>
-    <col min="65" max="65" customWidth="true" width="42.5727272727273"/>
-    <col min="66" max="66" customWidth="true" width="38.1454545454545"/>
-    <col min="67" max="67" customWidth="true" width="19.4272727272727"/>
-    <col min="68" max="68" customWidth="true" width="35.4272727272727"/>
-    <col min="69" max="69" customWidth="true" width="9.57272727272727"/>
+    <col min="1" max="1" width="5.14285714285714" customWidth="1"/>
+    <col min="2" max="2" width="21.8571428571429" customWidth="1"/>
+    <col min="3" max="3" width="27.5714285714286" customWidth="1"/>
+    <col min="4" max="4" width="79.4285714285714" customWidth="1"/>
+    <col min="5" max="5" width="11.5714285714286" customWidth="1"/>
+    <col min="6" max="6" width="5.14285714285714" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="12.7142857142857" customWidth="1"/>
+    <col min="9" max="10" width="5.85714285714286" customWidth="1"/>
+    <col min="11" max="11" width="6" customWidth="1"/>
+    <col min="12" max="12" width="14.2857142857143" customWidth="1"/>
+    <col min="13" max="13" width="9.42857142857143" customWidth="1"/>
+    <col min="14" max="14" width="14.2857142857143" customWidth="1"/>
+    <col min="15" max="15" width="15.5714285714286" customWidth="1"/>
+    <col min="16" max="16" width="14.4285714285714" customWidth="1"/>
+    <col min="17" max="17" width="39.4285714285714" customWidth="1"/>
+    <col min="18" max="18" width="11.7142857142857" customWidth="1"/>
+    <col min="19" max="19" width="10" customWidth="1"/>
+    <col min="20" max="20" width="6.42857142857143" customWidth="1"/>
+    <col min="21" max="21" width="9.85714285714286" customWidth="1"/>
+    <col min="22" max="22" width="6.57142857142857" customWidth="1"/>
+    <col min="23" max="23" width="37.1428571428571" customWidth="1"/>
+    <col min="24" max="25" width="8" customWidth="1"/>
+    <col min="26" max="26" width="7.71428571428571" customWidth="1"/>
+    <col min="27" max="27" width="6.28571428571429" customWidth="1"/>
+    <col min="28" max="28" width="9.28571428571429" customWidth="1"/>
+    <col min="29" max="29" width="9.71428571428571" customWidth="1"/>
+    <col min="30" max="30" width="12.8571428571429" customWidth="1"/>
+    <col min="31" max="31" width="16.1428571428571" customWidth="1"/>
+    <col min="32" max="32" width="15.4285714285714" customWidth="1"/>
+    <col min="33" max="33" width="24.5714285714286" customWidth="1"/>
+    <col min="34" max="34" width="8.57142857142857" customWidth="1"/>
+    <col min="35" max="35" width="14.7142857142857" customWidth="1"/>
+    <col min="36" max="36" width="18.5714285714286" customWidth="1"/>
+    <col min="37" max="37" width="14.1428571428571" customWidth="1"/>
+    <col min="38" max="38" width="14.7142857142857" customWidth="1"/>
+    <col min="39" max="39" width="17.4285714285714" customWidth="1"/>
+    <col min="40" max="40" width="22" customWidth="1"/>
+    <col min="41" max="41" width="17.5714285714286" customWidth="1"/>
+    <col min="42" max="42" width="25.2857142857143" customWidth="1"/>
+    <col min="43" max="43" width="13" customWidth="1"/>
+    <col min="44" max="44" width="25.7142857142857" customWidth="1"/>
+    <col min="45" max="45" width="10" customWidth="1"/>
+    <col min="46" max="46" width="13" customWidth="1"/>
+    <col min="47" max="47" width="15.5714285714286" customWidth="1"/>
+    <col min="48" max="48" width="21.1428571428571" customWidth="1"/>
+    <col min="49" max="49" width="11.5714285714286" customWidth="1"/>
+    <col min="50" max="50" width="16.7142857142857" customWidth="1"/>
+    <col min="51" max="51" width="14" customWidth="1"/>
+    <col min="52" max="52" width="19.4285714285714" customWidth="1"/>
+    <col min="53" max="53" width="18.8571428571429" customWidth="1"/>
+    <col min="54" max="54" width="23.2857142857143" customWidth="1"/>
+    <col min="55" max="55" width="15.5714285714286" customWidth="1"/>
+    <col min="56" max="56" width="14.2857142857143" customWidth="1"/>
+    <col min="57" max="57" width="17" customWidth="1"/>
+    <col min="58" max="58" width="16.2857142857143" customWidth="1"/>
+    <col min="59" max="59" width="13.5714285714286" customWidth="1"/>
+    <col min="60" max="61" width="12.7142857142857" customWidth="1"/>
+    <col min="62" max="62" width="21.8571428571429" customWidth="1"/>
+    <col min="63" max="63" width="30.5714285714286" customWidth="1"/>
+    <col min="64" max="64" width="10" customWidth="1"/>
+    <col min="65" max="65" width="42.5714285714286" customWidth="1"/>
+    <col min="66" max="66" width="38.1428571428571" customWidth="1"/>
+    <col min="67" max="67" width="19.4285714285714" customWidth="1"/>
+    <col min="68" max="68" width="35.4285714285714" customWidth="1"/>
+    <col min="69" max="69" width="9.57142857142857" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -10958,7 +10778,7 @@
       <c r="BP2" s="27"/>
       <c r="BQ2" s="27"/>
     </row>
-    <row r="3" ht="15.25" spans="1:69">
+    <row r="3" ht="15.75" spans="1:69">
       <c r="A3" s="28" t="s">
         <v>9</v>
       </c>
@@ -11167,7 +10987,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:69">
+    <row r="4" ht="15.75" spans="1:69">
       <c r="A4" s="26">
         <v>1</v>
       </c>
@@ -11331,11 +11151,11 @@
       <c r="AT4" s="35" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" t="s" s="0">
-        <v>177</v>
-      </c>
-      <c r="AV4" t="s" s="0">
-        <v>178</v>
+      <c r="AU4" t="s">
+        <v>91</v>
+      </c>
+      <c r="AV4" t="s">
+        <v>80</v>
       </c>
       <c r="AW4" s="35">
         <f>AM4</f>
@@ -11349,8 +11169,9 @@
         <f>AU4+AW4</f>
         <v>4</v>
       </c>
-      <c r="AZ4" t="s" s="0">
-        <v>92</v>
+      <c r="AZ4">
+        <f>ROUND(((AU4*AV4)+(AW4*AX4))/(AU4+AW4),5)</f>
+        <v>3672.43458</v>
       </c>
       <c r="BA4" s="36"/>
       <c r="BB4" s="36" t="s">
@@ -11374,15 +11195,15 @@
       <c r="BL4" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="BM4" t="s" s="0">
-        <v>180</v>
-      </c>
-      <c r="BN4" t="s" s="0">
-        <v>179</v>
+      <c r="BM4" t="s">
+        <v>92</v>
+      </c>
+      <c r="BN4" t="s">
+        <v>93</v>
       </c>
       <c r="BO4" s="35">
         <f>ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
-        <v>0</v>
+        <v>2983.24297</v>
       </c>
       <c r="BP4" s="36">
         <f>BN4+AW4</f>
@@ -11523,73 +11344,73 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ5"/>
-  <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="8.7047619047619" defaultRowHeight="15" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="5.14545454545455"/>
-    <col min="2" max="3" customWidth="true" width="28.0"/>
-    <col min="4" max="4" customWidth="true" width="79.4272727272727"/>
-    <col min="5" max="5" customWidth="true" width="11.5727272727273"/>
-    <col min="6" max="6" customWidth="true" width="5.14545454545455"/>
-    <col min="7" max="7" customWidth="true" width="11.0"/>
-    <col min="8" max="8" customWidth="true" width="12.7181818181818"/>
-    <col min="9" max="9" customWidth="true" width="5.85454545454545"/>
-    <col min="10" max="10" customWidth="true" width="6.0"/>
-    <col min="11" max="11" customWidth="true" width="5.85454545454545"/>
-    <col min="12" max="12" customWidth="true" width="14.2818181818182"/>
-    <col min="13" max="13" customWidth="true" width="9.42727272727273"/>
-    <col min="14" max="14" customWidth="true" width="14.4272727272727"/>
-    <col min="15" max="15" customWidth="true" width="15.5727272727273"/>
-    <col min="16" max="16" customWidth="true" width="14.4272727272727"/>
-    <col min="17" max="17" customWidth="true" width="39.4272727272727"/>
-    <col min="18" max="18" customWidth="true" width="11.7181818181818"/>
-    <col min="19" max="19" customWidth="true" width="11.8545454545455"/>
-    <col min="20" max="20" customWidth="true" width="6.42727272727273"/>
-    <col min="21" max="22" customWidth="true" width="6.57272727272727"/>
-    <col min="23" max="23" customWidth="true" width="37.1454545454545"/>
-    <col min="24" max="25" customWidth="true" width="8.0"/>
-    <col min="26" max="26" customWidth="true" width="7.71818181818182"/>
-    <col min="27" max="27" customWidth="true" width="6.28181818181818"/>
-    <col min="28" max="28" customWidth="true" width="9.28181818181818"/>
-    <col min="29" max="29" customWidth="true" width="9.71818181818182"/>
-    <col min="30" max="30" customWidth="true" width="12.8545454545455"/>
-    <col min="31" max="31" customWidth="true" width="16.1454545454545"/>
-    <col min="32" max="32" customWidth="true" width="15.4272727272727"/>
-    <col min="33" max="33" customWidth="true" width="24.5727272727273"/>
-    <col min="34" max="34" customWidth="true" width="8.57272727272727"/>
-    <col min="35" max="35" customWidth="true" width="14.7181818181818"/>
-    <col min="36" max="36" customWidth="true" width="18.5727272727273"/>
-    <col min="37" max="37" customWidth="true" width="14.1454545454545"/>
-    <col min="38" max="38" customWidth="true" width="14.7181818181818"/>
-    <col min="39" max="39" customWidth="true" width="17.4272727272727"/>
-    <col min="40" max="40" customWidth="true" width="22.0"/>
-    <col min="41" max="41" customWidth="true" width="17.5727272727273"/>
-    <col min="42" max="42" customWidth="true" width="25.2818181818182"/>
-    <col min="43" max="43" customWidth="true" width="13.0"/>
-    <col min="44" max="44" customWidth="true" width="23.7181818181818"/>
-    <col min="45" max="45" customWidth="true" width="10.0"/>
-    <col min="46" max="46" customWidth="true" width="13.0"/>
-    <col min="47" max="47" customWidth="true" width="15.5727272727273"/>
-    <col min="48" max="48" customWidth="true" width="21.1454545454545"/>
-    <col min="49" max="49" customWidth="true" width="11.5727272727273"/>
-    <col min="50" max="50" customWidth="true" width="16.7181818181818"/>
-    <col min="51" max="51" customWidth="true" width="14.0"/>
-    <col min="52" max="52" customWidth="true" width="19.4272727272727"/>
-    <col min="53" max="53" customWidth="true" width="18.8545454545455"/>
-    <col min="54" max="54" customWidth="true" width="23.2818181818182"/>
-    <col min="55" max="55" customWidth="true" width="15.5727272727273"/>
-    <col min="56" max="56" customWidth="true" width="14.2818181818182"/>
-    <col min="57" max="57" customWidth="true" width="17.0"/>
-    <col min="58" max="58" customWidth="true" width="16.2818181818182"/>
-    <col min="59" max="59" customWidth="true" width="13.5727272727273"/>
-    <col min="60" max="61" customWidth="true" width="12.7181818181818"/>
-    <col min="62" max="62" customWidth="true" width="21.8545454545455"/>
-    <col min="63" max="63" customWidth="true" width="30.5727272727273"/>
-    <col min="64" max="64" customWidth="true" width="10.0"/>
-    <col min="65" max="65" customWidth="true" width="42.5727272727273"/>
-    <col min="66" max="66" customWidth="true" width="38.1454545454545"/>
-    <col min="67" max="67" customWidth="true" width="19.4272727272727"/>
-    <col min="68" max="68" customWidth="true" width="35.4272727272727"/>
-    <col min="69" max="69" customWidth="true" width="9.57272727272727"/>
+    <col min="1" max="1" width="5.14285714285714" customWidth="1"/>
+    <col min="2" max="3" width="28" customWidth="1"/>
+    <col min="4" max="4" width="79.4285714285714" customWidth="1"/>
+    <col min="5" max="5" width="11.5714285714286" customWidth="1"/>
+    <col min="6" max="6" width="5.14285714285714" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="12.7142857142857" customWidth="1"/>
+    <col min="9" max="9" width="5.85714285714286" customWidth="1"/>
+    <col min="10" max="10" width="6" customWidth="1"/>
+    <col min="11" max="11" width="5.85714285714286" customWidth="1"/>
+    <col min="12" max="12" width="14.2857142857143" customWidth="1"/>
+    <col min="13" max="13" width="9.42857142857143" customWidth="1"/>
+    <col min="14" max="14" width="14.4285714285714" customWidth="1"/>
+    <col min="15" max="15" width="15.5714285714286" customWidth="1"/>
+    <col min="16" max="16" width="14.4285714285714" customWidth="1"/>
+    <col min="17" max="17" width="39.4285714285714" customWidth="1"/>
+    <col min="18" max="18" width="11.7142857142857" customWidth="1"/>
+    <col min="19" max="19" width="11.8571428571429" customWidth="1"/>
+    <col min="20" max="20" width="6.42857142857143" customWidth="1"/>
+    <col min="21" max="22" width="6.57142857142857" customWidth="1"/>
+    <col min="23" max="23" width="37.1428571428571" customWidth="1"/>
+    <col min="24" max="25" width="8" customWidth="1"/>
+    <col min="26" max="26" width="7.71428571428571" customWidth="1"/>
+    <col min="27" max="27" width="6.28571428571429" customWidth="1"/>
+    <col min="28" max="28" width="9.28571428571429" customWidth="1"/>
+    <col min="29" max="29" width="9.71428571428571" customWidth="1"/>
+    <col min="30" max="30" width="12.8571428571429" customWidth="1"/>
+    <col min="31" max="31" width="16.1428571428571" customWidth="1"/>
+    <col min="32" max="32" width="15.4285714285714" customWidth="1"/>
+    <col min="33" max="33" width="24.5714285714286" customWidth="1"/>
+    <col min="34" max="34" width="8.57142857142857" customWidth="1"/>
+    <col min="35" max="35" width="14.7142857142857" customWidth="1"/>
+    <col min="36" max="36" width="18.5714285714286" customWidth="1"/>
+    <col min="37" max="37" width="14.1428571428571" customWidth="1"/>
+    <col min="38" max="38" width="14.7142857142857" customWidth="1"/>
+    <col min="39" max="39" width="17.4285714285714" customWidth="1"/>
+    <col min="40" max="40" width="22" customWidth="1"/>
+    <col min="41" max="41" width="17.5714285714286" customWidth="1"/>
+    <col min="42" max="42" width="25.2857142857143" customWidth="1"/>
+    <col min="43" max="43" width="13" customWidth="1"/>
+    <col min="44" max="44" width="23.7142857142857" customWidth="1"/>
+    <col min="45" max="45" width="10" customWidth="1"/>
+    <col min="46" max="46" width="13" customWidth="1"/>
+    <col min="47" max="47" width="15.5714285714286" customWidth="1"/>
+    <col min="48" max="48" width="21.1428571428571" customWidth="1"/>
+    <col min="49" max="49" width="11.5714285714286" customWidth="1"/>
+    <col min="50" max="50" width="16.7142857142857" customWidth="1"/>
+    <col min="51" max="51" width="14" customWidth="1"/>
+    <col min="52" max="52" width="19.4285714285714" customWidth="1"/>
+    <col min="53" max="53" width="18.8571428571429" customWidth="1"/>
+    <col min="54" max="54" width="23.2857142857143" customWidth="1"/>
+    <col min="55" max="55" width="15.5714285714286" customWidth="1"/>
+    <col min="56" max="56" width="14.2857142857143" customWidth="1"/>
+    <col min="57" max="57" width="17" customWidth="1"/>
+    <col min="58" max="58" width="16.2857142857143" customWidth="1"/>
+    <col min="59" max="59" width="13.5714285714286" customWidth="1"/>
+    <col min="60" max="61" width="12.7142857142857" customWidth="1"/>
+    <col min="62" max="62" width="21.8571428571429" customWidth="1"/>
+    <col min="63" max="63" width="30.5714285714286" customWidth="1"/>
+    <col min="64" max="64" width="10" customWidth="1"/>
+    <col min="65" max="65" width="42.5714285714286" customWidth="1"/>
+    <col min="66" max="66" width="38.1428571428571" customWidth="1"/>
+    <col min="67" max="67" width="19.4285714285714" customWidth="1"/>
+    <col min="68" max="68" width="35.4285714285714" customWidth="1"/>
+    <col min="69" max="69" width="9.57142857142857" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -11760,7 +11581,7 @@
       <c r="BP2" s="27"/>
       <c r="BQ2" s="27"/>
     </row>
-    <row r="3" ht="15.25" spans="1:69">
+    <row r="3" ht="15.75" spans="1:69">
       <c r="A3" s="28" t="s">
         <v>9</v>
       </c>
@@ -11807,7 +11628,7 @@
         <v>25</v>
       </c>
       <c r="P3" s="30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="Q3" s="30" t="s">
         <v>23</v>
@@ -11816,13 +11637,13 @@
         <v>26</v>
       </c>
       <c r="S3" s="28" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="T3" s="28" t="s">
         <v>28</v>
       </c>
       <c r="U3" s="31" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="V3" s="31" t="s">
         <v>30</v>
@@ -11891,7 +11712,7 @@
         <v>51</v>
       </c>
       <c r="AR3" s="33" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AS3" s="28" t="s">
         <v>53</v>
@@ -11969,7 +11790,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.25" spans="1:69">
+    <row r="4" ht="15.75" spans="1:69">
       <c r="A4" s="26">
         <v>1</v>
       </c>
@@ -12133,11 +11954,11 @@
       <c r="AT4" s="35" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" t="s" s="0">
-        <v>204</v>
-      </c>
-      <c r="AV4" t="s" s="0">
-        <v>205</v>
+      <c r="AU4" t="s">
+        <v>143</v>
+      </c>
+      <c r="AV4" t="s">
+        <v>144</v>
       </c>
       <c r="AW4" s="35">
         <f>AM4</f>
@@ -12177,11 +11998,11 @@
       <c r="BL4" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="BM4" t="s" s="0">
-        <v>207</v>
-      </c>
-      <c r="BN4" t="s" s="0">
-        <v>206</v>
+      <c r="BM4" t="s">
+        <v>145</v>
+      </c>
+      <c r="BN4" t="s">
+        <v>146</v>
       </c>
       <c r="BO4" s="35">
         <f>ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
@@ -12338,73 +12159,73 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ5"/>
-  <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="8.7047619047619" defaultRowHeight="15" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="5.14545454545455"/>
-    <col min="2" max="3" customWidth="true" width="28.0"/>
-    <col min="4" max="4" customWidth="true" width="79.4272727272727"/>
-    <col min="5" max="5" customWidth="true" width="11.5727272727273"/>
-    <col min="6" max="6" customWidth="true" width="5.14545454545455"/>
-    <col min="7" max="7" customWidth="true" width="11.0"/>
-    <col min="8" max="8" customWidth="true" width="12.7181818181818"/>
-    <col min="9" max="9" customWidth="true" width="5.85454545454545"/>
-    <col min="10" max="10" customWidth="true" width="6.0"/>
-    <col min="11" max="11" customWidth="true" width="5.85454545454545"/>
-    <col min="12" max="12" customWidth="true" width="14.2818181818182"/>
-    <col min="13" max="13" customWidth="true" width="9.42727272727273"/>
-    <col min="14" max="14" customWidth="true" width="14.4272727272727"/>
-    <col min="15" max="15" customWidth="true" width="15.5727272727273"/>
-    <col min="16" max="16" customWidth="true" width="14.4272727272727"/>
-    <col min="17" max="17" customWidth="true" width="39.4272727272727"/>
-    <col min="18" max="18" customWidth="true" width="11.7181818181818"/>
-    <col min="19" max="19" customWidth="true" width="11.8545454545455"/>
-    <col min="20" max="20" customWidth="true" width="6.42727272727273"/>
-    <col min="21" max="22" customWidth="true" width="6.57272727272727"/>
-    <col min="23" max="23" customWidth="true" width="37.1454545454545"/>
-    <col min="24" max="25" customWidth="true" width="8.0"/>
-    <col min="26" max="26" customWidth="true" width="7.71818181818182"/>
-    <col min="27" max="27" customWidth="true" width="6.28181818181818"/>
-    <col min="28" max="28" customWidth="true" width="9.28181818181818"/>
-    <col min="29" max="29" customWidth="true" width="9.71818181818182"/>
-    <col min="30" max="30" customWidth="true" width="12.8545454545455"/>
-    <col min="31" max="31" customWidth="true" width="16.1454545454545"/>
-    <col min="32" max="32" customWidth="true" width="15.4272727272727"/>
-    <col min="33" max="33" customWidth="true" width="24.5727272727273"/>
-    <col min="34" max="34" customWidth="true" width="8.57272727272727"/>
-    <col min="35" max="35" customWidth="true" width="14.7181818181818"/>
-    <col min="36" max="36" customWidth="true" width="18.5727272727273"/>
-    <col min="37" max="37" customWidth="true" width="14.1454545454545"/>
-    <col min="38" max="38" customWidth="true" width="14.7181818181818"/>
-    <col min="39" max="39" customWidth="true" width="17.4272727272727"/>
-    <col min="40" max="40" customWidth="true" width="22.0"/>
-    <col min="41" max="41" customWidth="true" width="17.5727272727273"/>
-    <col min="42" max="42" customWidth="true" width="25.2818181818182"/>
-    <col min="43" max="43" customWidth="true" width="13.0"/>
-    <col min="44" max="44" customWidth="true" width="23.7181818181818"/>
-    <col min="45" max="45" customWidth="true" width="10.0"/>
-    <col min="46" max="46" customWidth="true" width="13.0"/>
-    <col min="47" max="47" customWidth="true" width="15.5727272727273"/>
-    <col min="48" max="48" customWidth="true" width="21.1454545454545"/>
-    <col min="49" max="49" customWidth="true" width="11.5727272727273"/>
-    <col min="50" max="50" customWidth="true" width="16.7181818181818"/>
-    <col min="51" max="51" customWidth="true" width="14.0"/>
-    <col min="52" max="52" customWidth="true" width="19.4272727272727"/>
-    <col min="53" max="53" customWidth="true" width="18.8545454545455"/>
-    <col min="54" max="54" customWidth="true" width="23.2818181818182"/>
-    <col min="55" max="55" customWidth="true" width="15.5727272727273"/>
-    <col min="56" max="56" customWidth="true" width="14.2818181818182"/>
-    <col min="57" max="57" customWidth="true" width="17.0"/>
-    <col min="58" max="58" customWidth="true" width="16.2818181818182"/>
-    <col min="59" max="59" customWidth="true" width="13.5727272727273"/>
-    <col min="60" max="61" customWidth="true" width="12.7181818181818"/>
-    <col min="62" max="62" customWidth="true" width="21.8545454545455"/>
-    <col min="63" max="63" customWidth="true" width="30.5727272727273"/>
-    <col min="64" max="64" customWidth="true" width="10.0"/>
-    <col min="65" max="65" customWidth="true" width="42.5727272727273"/>
-    <col min="66" max="66" customWidth="true" width="38.1454545454545"/>
-    <col min="67" max="67" customWidth="true" width="19.4272727272727"/>
-    <col min="68" max="68" customWidth="true" width="35.4272727272727"/>
-    <col min="69" max="69" customWidth="true" width="9.57272727272727"/>
+    <col min="1" max="1" width="5.14285714285714" customWidth="1"/>
+    <col min="2" max="3" width="28" customWidth="1"/>
+    <col min="4" max="4" width="79.4285714285714" customWidth="1"/>
+    <col min="5" max="5" width="11.5714285714286" customWidth="1"/>
+    <col min="6" max="6" width="5.14285714285714" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="12.7142857142857" customWidth="1"/>
+    <col min="9" max="9" width="5.85714285714286" customWidth="1"/>
+    <col min="10" max="10" width="6" customWidth="1"/>
+    <col min="11" max="11" width="5.85714285714286" customWidth="1"/>
+    <col min="12" max="12" width="14.2857142857143" customWidth="1"/>
+    <col min="13" max="13" width="9.42857142857143" customWidth="1"/>
+    <col min="14" max="14" width="14.4285714285714" customWidth="1"/>
+    <col min="15" max="15" width="15.5714285714286" customWidth="1"/>
+    <col min="16" max="16" width="14.4285714285714" customWidth="1"/>
+    <col min="17" max="17" width="39.4285714285714" customWidth="1"/>
+    <col min="18" max="18" width="11.7142857142857" customWidth="1"/>
+    <col min="19" max="19" width="11.8571428571429" customWidth="1"/>
+    <col min="20" max="20" width="6.42857142857143" customWidth="1"/>
+    <col min="21" max="22" width="6.57142857142857" customWidth="1"/>
+    <col min="23" max="23" width="37.1428571428571" customWidth="1"/>
+    <col min="24" max="25" width="8" customWidth="1"/>
+    <col min="26" max="26" width="7.71428571428571" customWidth="1"/>
+    <col min="27" max="27" width="6.28571428571429" customWidth="1"/>
+    <col min="28" max="28" width="9.28571428571429" customWidth="1"/>
+    <col min="29" max="29" width="9.71428571428571" customWidth="1"/>
+    <col min="30" max="30" width="12.8571428571429" customWidth="1"/>
+    <col min="31" max="31" width="16.1428571428571" customWidth="1"/>
+    <col min="32" max="32" width="15.4285714285714" customWidth="1"/>
+    <col min="33" max="33" width="24.5714285714286" customWidth="1"/>
+    <col min="34" max="34" width="8.57142857142857" customWidth="1"/>
+    <col min="35" max="35" width="14.7142857142857" customWidth="1"/>
+    <col min="36" max="36" width="18.5714285714286" customWidth="1"/>
+    <col min="37" max="37" width="14.1428571428571" customWidth="1"/>
+    <col min="38" max="38" width="14.7142857142857" customWidth="1"/>
+    <col min="39" max="39" width="17.4285714285714" customWidth="1"/>
+    <col min="40" max="40" width="22" customWidth="1"/>
+    <col min="41" max="41" width="17.5714285714286" customWidth="1"/>
+    <col min="42" max="42" width="25.2857142857143" customWidth="1"/>
+    <col min="43" max="43" width="13" customWidth="1"/>
+    <col min="44" max="44" width="23.7142857142857" customWidth="1"/>
+    <col min="45" max="45" width="10" customWidth="1"/>
+    <col min="46" max="46" width="13" customWidth="1"/>
+    <col min="47" max="47" width="15.5714285714286" customWidth="1"/>
+    <col min="48" max="48" width="21.1428571428571" customWidth="1"/>
+    <col min="49" max="49" width="11.5714285714286" customWidth="1"/>
+    <col min="50" max="50" width="16.7142857142857" customWidth="1"/>
+    <col min="51" max="51" width="14" customWidth="1"/>
+    <col min="52" max="52" width="19.4285714285714" customWidth="1"/>
+    <col min="53" max="53" width="18.8571428571429" customWidth="1"/>
+    <col min="54" max="54" width="23.2857142857143" customWidth="1"/>
+    <col min="55" max="55" width="15.5714285714286" customWidth="1"/>
+    <col min="56" max="56" width="14.2857142857143" customWidth="1"/>
+    <col min="57" max="57" width="17" customWidth="1"/>
+    <col min="58" max="58" width="16.2857142857143" customWidth="1"/>
+    <col min="59" max="59" width="13.5714285714286" customWidth="1"/>
+    <col min="60" max="61" width="12.7142857142857" customWidth="1"/>
+    <col min="62" max="62" width="21.8571428571429" customWidth="1"/>
+    <col min="63" max="63" width="30.5714285714286" customWidth="1"/>
+    <col min="64" max="64" width="10" customWidth="1"/>
+    <col min="65" max="65" width="42.5714285714286" customWidth="1"/>
+    <col min="66" max="66" width="38.1428571428571" customWidth="1"/>
+    <col min="67" max="67" width="19.4285714285714" customWidth="1"/>
+    <col min="68" max="68" width="35.4285714285714" customWidth="1"/>
+    <col min="69" max="69" width="9.57142857142857" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -12575,7 +12396,7 @@
       <c r="BP2" s="27"/>
       <c r="BQ2" s="27"/>
     </row>
-    <row r="3" ht="15.25" spans="1:69">
+    <row r="3" ht="15.75" spans="1:69">
       <c r="A3" s="28" t="s">
         <v>9</v>
       </c>
@@ -12622,7 +12443,7 @@
         <v>25</v>
       </c>
       <c r="P3" s="30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="Q3" s="30" t="s">
         <v>23</v>
@@ -12631,13 +12452,13 @@
         <v>26</v>
       </c>
       <c r="S3" s="28" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="T3" s="28" t="s">
         <v>28</v>
       </c>
       <c r="U3" s="31" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="V3" s="31" t="s">
         <v>30</v>
@@ -12706,7 +12527,7 @@
         <v>51</v>
       </c>
       <c r="AR3" s="33" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AS3" s="28" t="s">
         <v>53</v>
@@ -12784,7 +12605,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.25" spans="1:69">
+    <row r="4" ht="15.75" spans="1:69">
       <c r="A4" s="26">
         <v>1</v>
       </c>
@@ -12948,11 +12769,11 @@
       <c r="AT4" s="35" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" t="s" s="0">
-        <v>208</v>
-      </c>
-      <c r="AV4" t="s" s="0">
-        <v>209</v>
+      <c r="AU4" t="s">
+        <v>148</v>
+      </c>
+      <c r="AV4" t="s">
+        <v>149</v>
       </c>
       <c r="AW4" s="35">
         <f>AM4</f>
@@ -12992,11 +12813,11 @@
       <c r="BL4" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="BM4" t="s" s="0">
-        <v>211</v>
-      </c>
-      <c r="BN4" t="s" s="0">
-        <v>210</v>
+      <c r="BM4" t="s">
+        <v>150</v>
+      </c>
+      <c r="BN4" t="s">
+        <v>151</v>
       </c>
       <c r="BO4" s="35">
         <f>ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
@@ -13153,73 +12974,73 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ5"/>
-  <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="8.7047619047619" defaultRowHeight="15" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="5.14545454545455"/>
-    <col min="2" max="3" customWidth="true" width="28.0"/>
-    <col min="4" max="4" customWidth="true" width="79.4272727272727"/>
-    <col min="5" max="5" customWidth="true" width="11.5727272727273"/>
-    <col min="6" max="6" customWidth="true" width="5.14545454545455"/>
-    <col min="7" max="7" customWidth="true" width="11.0"/>
-    <col min="8" max="8" customWidth="true" width="12.7181818181818"/>
-    <col min="9" max="9" customWidth="true" width="5.85454545454545"/>
-    <col min="10" max="10" customWidth="true" width="6.0"/>
-    <col min="11" max="11" customWidth="true" width="5.85454545454545"/>
-    <col min="12" max="12" customWidth="true" width="14.2818181818182"/>
-    <col min="13" max="13" customWidth="true" width="9.42727272727273"/>
-    <col min="14" max="14" customWidth="true" width="14.4272727272727"/>
-    <col min="15" max="15" customWidth="true" width="15.5727272727273"/>
-    <col min="16" max="16" customWidth="true" width="14.4272727272727"/>
-    <col min="17" max="17" customWidth="true" width="39.4272727272727"/>
-    <col min="18" max="18" customWidth="true" width="11.7181818181818"/>
-    <col min="19" max="19" customWidth="true" width="11.8545454545455"/>
-    <col min="20" max="20" customWidth="true" width="6.42727272727273"/>
-    <col min="21" max="22" customWidth="true" width="6.57272727272727"/>
-    <col min="23" max="23" customWidth="true" width="37.1454545454545"/>
-    <col min="24" max="25" customWidth="true" width="8.0"/>
-    <col min="26" max="26" customWidth="true" width="7.71818181818182"/>
-    <col min="27" max="27" customWidth="true" width="6.28181818181818"/>
-    <col min="28" max="28" customWidth="true" width="9.28181818181818"/>
-    <col min="29" max="29" customWidth="true" width="9.71818181818182"/>
-    <col min="30" max="30" customWidth="true" width="12.8545454545455"/>
-    <col min="31" max="31" customWidth="true" width="16.1454545454545"/>
-    <col min="32" max="32" customWidth="true" width="15.4272727272727"/>
-    <col min="33" max="33" customWidth="true" width="24.5727272727273"/>
-    <col min="34" max="34" customWidth="true" width="8.57272727272727"/>
-    <col min="35" max="35" customWidth="true" width="14.7181818181818"/>
-    <col min="36" max="36" customWidth="true" width="18.5727272727273"/>
-    <col min="37" max="37" customWidth="true" width="14.1454545454545"/>
-    <col min="38" max="38" customWidth="true" width="14.7181818181818"/>
-    <col min="39" max="39" customWidth="true" width="17.4272727272727"/>
-    <col min="40" max="40" customWidth="true" width="22.0"/>
-    <col min="41" max="41" customWidth="true" width="17.5727272727273"/>
-    <col min="42" max="42" customWidth="true" width="25.2818181818182"/>
-    <col min="43" max="43" customWidth="true" width="13.0"/>
-    <col min="44" max="44" customWidth="true" width="23.7181818181818"/>
-    <col min="45" max="45" customWidth="true" width="10.0"/>
-    <col min="46" max="46" customWidth="true" width="13.0"/>
-    <col min="47" max="47" customWidth="true" width="15.5727272727273"/>
-    <col min="48" max="48" customWidth="true" width="21.1454545454545"/>
-    <col min="49" max="49" customWidth="true" width="11.5727272727273"/>
-    <col min="50" max="50" customWidth="true" width="16.7181818181818"/>
-    <col min="51" max="51" customWidth="true" width="14.0"/>
-    <col min="52" max="52" customWidth="true" width="19.4272727272727"/>
-    <col min="53" max="53" customWidth="true" width="18.8545454545455"/>
-    <col min="54" max="54" customWidth="true" width="23.2818181818182"/>
-    <col min="55" max="55" customWidth="true" width="15.5727272727273"/>
-    <col min="56" max="56" customWidth="true" width="14.2818181818182"/>
-    <col min="57" max="57" customWidth="true" width="17.0"/>
-    <col min="58" max="58" customWidth="true" width="16.2818181818182"/>
-    <col min="59" max="59" customWidth="true" width="13.5727272727273"/>
-    <col min="60" max="61" customWidth="true" width="12.7181818181818"/>
-    <col min="62" max="62" customWidth="true" width="21.8545454545455"/>
-    <col min="63" max="63" customWidth="true" width="30.5727272727273"/>
-    <col min="64" max="64" customWidth="true" width="10.0"/>
-    <col min="65" max="65" customWidth="true" width="42.5727272727273"/>
-    <col min="66" max="66" customWidth="true" width="38.1454545454545"/>
-    <col min="67" max="67" customWidth="true" width="19.4272727272727"/>
-    <col min="68" max="68" customWidth="true" width="35.4272727272727"/>
-    <col min="69" max="69" customWidth="true" width="9.57272727272727"/>
+    <col min="1" max="1" width="5.14285714285714" customWidth="1"/>
+    <col min="2" max="3" width="28" customWidth="1"/>
+    <col min="4" max="4" width="79.4285714285714" customWidth="1"/>
+    <col min="5" max="5" width="11.5714285714286" customWidth="1"/>
+    <col min="6" max="6" width="5.14285714285714" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="12.7142857142857" customWidth="1"/>
+    <col min="9" max="9" width="5.85714285714286" customWidth="1"/>
+    <col min="10" max="10" width="6" customWidth="1"/>
+    <col min="11" max="11" width="5.85714285714286" customWidth="1"/>
+    <col min="12" max="12" width="14.2857142857143" customWidth="1"/>
+    <col min="13" max="13" width="9.42857142857143" customWidth="1"/>
+    <col min="14" max="14" width="14.4285714285714" customWidth="1"/>
+    <col min="15" max="15" width="15.5714285714286" customWidth="1"/>
+    <col min="16" max="16" width="14.4285714285714" customWidth="1"/>
+    <col min="17" max="17" width="39.4285714285714" customWidth="1"/>
+    <col min="18" max="18" width="11.7142857142857" customWidth="1"/>
+    <col min="19" max="19" width="11.8571428571429" customWidth="1"/>
+    <col min="20" max="20" width="6.42857142857143" customWidth="1"/>
+    <col min="21" max="22" width="6.57142857142857" customWidth="1"/>
+    <col min="23" max="23" width="37.1428571428571" customWidth="1"/>
+    <col min="24" max="25" width="8" customWidth="1"/>
+    <col min="26" max="26" width="7.71428571428571" customWidth="1"/>
+    <col min="27" max="27" width="6.28571428571429" customWidth="1"/>
+    <col min="28" max="28" width="9.28571428571429" customWidth="1"/>
+    <col min="29" max="29" width="9.71428571428571" customWidth="1"/>
+    <col min="30" max="30" width="12.8571428571429" customWidth="1"/>
+    <col min="31" max="31" width="16.1428571428571" customWidth="1"/>
+    <col min="32" max="32" width="15.4285714285714" customWidth="1"/>
+    <col min="33" max="33" width="24.5714285714286" customWidth="1"/>
+    <col min="34" max="34" width="8.57142857142857" customWidth="1"/>
+    <col min="35" max="35" width="14.7142857142857" customWidth="1"/>
+    <col min="36" max="36" width="18.5714285714286" customWidth="1"/>
+    <col min="37" max="37" width="14.1428571428571" customWidth="1"/>
+    <col min="38" max="38" width="14.7142857142857" customWidth="1"/>
+    <col min="39" max="39" width="17.4285714285714" customWidth="1"/>
+    <col min="40" max="40" width="22" customWidth="1"/>
+    <col min="41" max="41" width="17.5714285714286" customWidth="1"/>
+    <col min="42" max="42" width="25.2857142857143" customWidth="1"/>
+    <col min="43" max="43" width="13" customWidth="1"/>
+    <col min="44" max="44" width="23.7142857142857" customWidth="1"/>
+    <col min="45" max="45" width="10" customWidth="1"/>
+    <col min="46" max="46" width="13" customWidth="1"/>
+    <col min="47" max="47" width="15.5714285714286" customWidth="1"/>
+    <col min="48" max="48" width="21.1428571428571" customWidth="1"/>
+    <col min="49" max="49" width="11.5714285714286" customWidth="1"/>
+    <col min="50" max="50" width="16.7142857142857" customWidth="1"/>
+    <col min="51" max="51" width="14" customWidth="1"/>
+    <col min="52" max="52" width="19.4285714285714" customWidth="1"/>
+    <col min="53" max="53" width="18.8571428571429" customWidth="1"/>
+    <col min="54" max="54" width="23.2857142857143" customWidth="1"/>
+    <col min="55" max="55" width="15.5714285714286" customWidth="1"/>
+    <col min="56" max="56" width="14.2857142857143" customWidth="1"/>
+    <col min="57" max="57" width="17" customWidth="1"/>
+    <col min="58" max="58" width="16.2857142857143" customWidth="1"/>
+    <col min="59" max="59" width="13.5714285714286" customWidth="1"/>
+    <col min="60" max="61" width="12.7142857142857" customWidth="1"/>
+    <col min="62" max="62" width="21.8571428571429" customWidth="1"/>
+    <col min="63" max="63" width="30.5714285714286" customWidth="1"/>
+    <col min="64" max="64" width="10" customWidth="1"/>
+    <col min="65" max="65" width="42.5714285714286" customWidth="1"/>
+    <col min="66" max="66" width="38.1428571428571" customWidth="1"/>
+    <col min="67" max="67" width="19.4285714285714" customWidth="1"/>
+    <col min="68" max="68" width="35.4285714285714" customWidth="1"/>
+    <col min="69" max="69" width="9.57142857142857" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -13390,7 +13211,7 @@
       <c r="BP2" s="27"/>
       <c r="BQ2" s="27"/>
     </row>
-    <row r="3" ht="15.25" spans="1:69">
+    <row r="3" ht="15.75" spans="1:69">
       <c r="A3" s="28" t="s">
         <v>9</v>
       </c>
@@ -13437,7 +13258,7 @@
         <v>25</v>
       </c>
       <c r="P3" s="30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="Q3" s="30" t="s">
         <v>23</v>
@@ -13446,13 +13267,13 @@
         <v>26</v>
       </c>
       <c r="S3" s="28" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="T3" s="28" t="s">
         <v>28</v>
       </c>
       <c r="U3" s="31" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="V3" s="31" t="s">
         <v>30</v>
@@ -13521,7 +13342,7 @@
         <v>51</v>
       </c>
       <c r="AR3" s="33" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AS3" s="28" t="s">
         <v>53</v>
@@ -13599,7 +13420,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.25" spans="1:69">
+    <row r="4" ht="15.75" spans="1:69">
       <c r="A4" s="26">
         <v>1</v>
       </c>
@@ -13626,7 +13447,7 @@
         <v>400</v>
       </c>
       <c r="I4" s="27" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J4" s="35">
         <v>2</v>
@@ -13763,11 +13584,11 @@
       <c r="AT4" s="35" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" t="s" s="0">
-        <v>204</v>
-      </c>
-      <c r="AV4" t="s" s="0">
-        <v>205</v>
+      <c r="AU4" t="s">
+        <v>143</v>
+      </c>
+      <c r="AV4" t="s">
+        <v>144</v>
       </c>
       <c r="AW4" s="35">
         <f>AM4</f>
@@ -13807,11 +13628,11 @@
       <c r="BL4" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="BM4" t="s" s="0">
-        <v>207</v>
-      </c>
-      <c r="BN4" t="s" s="0">
-        <v>206</v>
+      <c r="BM4" t="s">
+        <v>145</v>
+      </c>
+      <c r="BN4" t="s">
+        <v>146</v>
       </c>
       <c r="BO4" s="35">
         <f>ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
@@ -13956,73 +13777,73 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ5"/>
-  <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="8.7047619047619" defaultRowHeight="15" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="5.14545454545455"/>
-    <col min="2" max="3" customWidth="true" width="28.0"/>
-    <col min="4" max="4" customWidth="true" width="79.4272727272727"/>
-    <col min="5" max="5" customWidth="true" width="11.5727272727273"/>
-    <col min="6" max="6" customWidth="true" width="5.14545454545455"/>
-    <col min="7" max="7" customWidth="true" width="11.0"/>
-    <col min="8" max="8" customWidth="true" width="12.7181818181818"/>
-    <col min="9" max="9" customWidth="true" width="5.85454545454545"/>
-    <col min="10" max="10" customWidth="true" width="6.0"/>
-    <col min="11" max="11" customWidth="true" width="5.85454545454545"/>
-    <col min="12" max="12" customWidth="true" width="14.2818181818182"/>
-    <col min="13" max="13" customWidth="true" width="9.42727272727273"/>
-    <col min="14" max="14" customWidth="true" width="14.4272727272727"/>
-    <col min="15" max="15" customWidth="true" width="15.5727272727273"/>
-    <col min="16" max="16" customWidth="true" width="14.4272727272727"/>
-    <col min="17" max="17" customWidth="true" width="39.4272727272727"/>
-    <col min="18" max="18" customWidth="true" width="11.7181818181818"/>
-    <col min="19" max="19" customWidth="true" width="11.8545454545455"/>
-    <col min="20" max="20" customWidth="true" width="6.42727272727273"/>
-    <col min="21" max="22" customWidth="true" width="6.57272727272727"/>
-    <col min="23" max="23" customWidth="true" width="37.1454545454545"/>
-    <col min="24" max="25" customWidth="true" width="8.0"/>
-    <col min="26" max="26" customWidth="true" width="7.71818181818182"/>
-    <col min="27" max="27" customWidth="true" width="6.28181818181818"/>
-    <col min="28" max="28" customWidth="true" width="9.28181818181818"/>
-    <col min="29" max="29" customWidth="true" width="9.71818181818182"/>
-    <col min="30" max="30" customWidth="true" width="12.8545454545455"/>
-    <col min="31" max="31" customWidth="true" width="16.1454545454545"/>
-    <col min="32" max="32" customWidth="true" width="15.4272727272727"/>
-    <col min="33" max="33" customWidth="true" width="24.5727272727273"/>
-    <col min="34" max="34" customWidth="true" width="8.57272727272727"/>
-    <col min="35" max="35" customWidth="true" width="14.7181818181818"/>
-    <col min="36" max="36" customWidth="true" width="18.5727272727273"/>
-    <col min="37" max="37" customWidth="true" width="14.1454545454545"/>
-    <col min="38" max="38" customWidth="true" width="14.7181818181818"/>
-    <col min="39" max="39" customWidth="true" width="17.4272727272727"/>
-    <col min="40" max="40" customWidth="true" width="22.0"/>
-    <col min="41" max="41" customWidth="true" width="17.5727272727273"/>
-    <col min="42" max="42" customWidth="true" width="25.2818181818182"/>
-    <col min="43" max="43" customWidth="true" width="13.0"/>
-    <col min="44" max="44" customWidth="true" width="23.7181818181818"/>
-    <col min="45" max="45" customWidth="true" width="10.0"/>
-    <col min="46" max="46" customWidth="true" width="13.0"/>
-    <col min="47" max="47" customWidth="true" width="15.5727272727273"/>
-    <col min="48" max="48" customWidth="true" width="21.1454545454545"/>
-    <col min="49" max="49" customWidth="true" width="11.5727272727273"/>
-    <col min="50" max="50" customWidth="true" width="16.7181818181818"/>
-    <col min="51" max="51" customWidth="true" width="14.0"/>
-    <col min="52" max="52" customWidth="true" width="19.4272727272727"/>
-    <col min="53" max="53" customWidth="true" width="18.8545454545455"/>
-    <col min="54" max="54" customWidth="true" width="23.2818181818182"/>
-    <col min="55" max="55" customWidth="true" width="15.5727272727273"/>
-    <col min="56" max="56" customWidth="true" width="14.2818181818182"/>
-    <col min="57" max="57" customWidth="true" width="17.0"/>
-    <col min="58" max="58" customWidth="true" width="16.2818181818182"/>
-    <col min="59" max="59" customWidth="true" width="13.5727272727273"/>
-    <col min="60" max="61" customWidth="true" width="12.7181818181818"/>
-    <col min="62" max="62" customWidth="true" width="21.8545454545455"/>
-    <col min="63" max="63" customWidth="true" width="30.5727272727273"/>
-    <col min="64" max="64" customWidth="true" width="10.0"/>
-    <col min="65" max="65" customWidth="true" width="42.5727272727273"/>
-    <col min="66" max="66" customWidth="true" width="38.1454545454545"/>
-    <col min="67" max="67" customWidth="true" width="19.4272727272727"/>
-    <col min="68" max="68" customWidth="true" width="35.4272727272727"/>
-    <col min="69" max="69" customWidth="true" width="9.57272727272727"/>
+    <col min="1" max="1" width="5.14285714285714" customWidth="1"/>
+    <col min="2" max="3" width="28" customWidth="1"/>
+    <col min="4" max="4" width="79.4285714285714" customWidth="1"/>
+    <col min="5" max="5" width="11.5714285714286" customWidth="1"/>
+    <col min="6" max="6" width="5.14285714285714" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="12.7142857142857" customWidth="1"/>
+    <col min="9" max="9" width="5.85714285714286" customWidth="1"/>
+    <col min="10" max="10" width="6" customWidth="1"/>
+    <col min="11" max="11" width="5.85714285714286" customWidth="1"/>
+    <col min="12" max="12" width="14.2857142857143" customWidth="1"/>
+    <col min="13" max="13" width="9.42857142857143" customWidth="1"/>
+    <col min="14" max="14" width="14.4285714285714" customWidth="1"/>
+    <col min="15" max="15" width="15.5714285714286" customWidth="1"/>
+    <col min="16" max="16" width="14.4285714285714" customWidth="1"/>
+    <col min="17" max="17" width="39.4285714285714" customWidth="1"/>
+    <col min="18" max="18" width="11.7142857142857" customWidth="1"/>
+    <col min="19" max="19" width="11.8571428571429" customWidth="1"/>
+    <col min="20" max="20" width="6.42857142857143" customWidth="1"/>
+    <col min="21" max="22" width="6.57142857142857" customWidth="1"/>
+    <col min="23" max="23" width="37.1428571428571" customWidth="1"/>
+    <col min="24" max="25" width="8" customWidth="1"/>
+    <col min="26" max="26" width="7.71428571428571" customWidth="1"/>
+    <col min="27" max="27" width="6.28571428571429" customWidth="1"/>
+    <col min="28" max="28" width="9.28571428571429" customWidth="1"/>
+    <col min="29" max="29" width="9.71428571428571" customWidth="1"/>
+    <col min="30" max="30" width="12.8571428571429" customWidth="1"/>
+    <col min="31" max="31" width="16.1428571428571" customWidth="1"/>
+    <col min="32" max="32" width="15.4285714285714" customWidth="1"/>
+    <col min="33" max="33" width="24.5714285714286" customWidth="1"/>
+    <col min="34" max="34" width="8.57142857142857" customWidth="1"/>
+    <col min="35" max="35" width="14.7142857142857" customWidth="1"/>
+    <col min="36" max="36" width="18.5714285714286" customWidth="1"/>
+    <col min="37" max="37" width="14.1428571428571" customWidth="1"/>
+    <col min="38" max="38" width="14.7142857142857" customWidth="1"/>
+    <col min="39" max="39" width="17.4285714285714" customWidth="1"/>
+    <col min="40" max="40" width="22" customWidth="1"/>
+    <col min="41" max="41" width="17.5714285714286" customWidth="1"/>
+    <col min="42" max="42" width="25.2857142857143" customWidth="1"/>
+    <col min="43" max="43" width="13" customWidth="1"/>
+    <col min="44" max="44" width="23.7142857142857" customWidth="1"/>
+    <col min="45" max="45" width="10" customWidth="1"/>
+    <col min="46" max="46" width="13" customWidth="1"/>
+    <col min="47" max="47" width="15.5714285714286" customWidth="1"/>
+    <col min="48" max="48" width="21.1428571428571" customWidth="1"/>
+    <col min="49" max="49" width="11.5714285714286" customWidth="1"/>
+    <col min="50" max="50" width="16.7142857142857" customWidth="1"/>
+    <col min="51" max="51" width="14" customWidth="1"/>
+    <col min="52" max="52" width="19.4285714285714" customWidth="1"/>
+    <col min="53" max="53" width="18.8571428571429" customWidth="1"/>
+    <col min="54" max="54" width="23.2857142857143" customWidth="1"/>
+    <col min="55" max="55" width="15.5714285714286" customWidth="1"/>
+    <col min="56" max="56" width="14.2857142857143" customWidth="1"/>
+    <col min="57" max="57" width="17" customWidth="1"/>
+    <col min="58" max="58" width="16.2857142857143" customWidth="1"/>
+    <col min="59" max="59" width="13.5714285714286" customWidth="1"/>
+    <col min="60" max="61" width="12.7142857142857" customWidth="1"/>
+    <col min="62" max="62" width="21.8571428571429" customWidth="1"/>
+    <col min="63" max="63" width="30.5714285714286" customWidth="1"/>
+    <col min="64" max="64" width="10" customWidth="1"/>
+    <col min="65" max="65" width="42.5714285714286" customWidth="1"/>
+    <col min="66" max="66" width="38.1428571428571" customWidth="1"/>
+    <col min="67" max="67" width="19.4285714285714" customWidth="1"/>
+    <col min="68" max="68" width="35.4285714285714" customWidth="1"/>
+    <col min="69" max="69" width="9.57142857142857" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -14193,7 +14014,7 @@
       <c r="BP2" s="27"/>
       <c r="BQ2" s="27"/>
     </row>
-    <row r="3" ht="15.25" spans="1:69">
+    <row r="3" ht="15.75" spans="1:69">
       <c r="A3" s="28" t="s">
         <v>9</v>
       </c>
@@ -14240,7 +14061,7 @@
         <v>25</v>
       </c>
       <c r="P3" s="30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="Q3" s="30" t="s">
         <v>23</v>
@@ -14249,13 +14070,13 @@
         <v>26</v>
       </c>
       <c r="S3" s="28" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="T3" s="28" t="s">
         <v>28</v>
       </c>
       <c r="U3" s="31" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="V3" s="31" t="s">
         <v>30</v>
@@ -14324,7 +14145,7 @@
         <v>51</v>
       </c>
       <c r="AR3" s="33" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AS3" s="28" t="s">
         <v>53</v>
@@ -14402,7 +14223,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.25" spans="1:69">
+    <row r="4" ht="15.75" spans="1:69">
       <c r="A4" s="26">
         <v>1</v>
       </c>
@@ -14429,7 +14250,7 @@
         <v>400</v>
       </c>
       <c r="I4" s="27" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J4" s="35">
         <v>2</v>
@@ -14566,11 +14387,11 @@
       <c r="AT4" s="35" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" t="s" s="0">
-        <v>208</v>
-      </c>
-      <c r="AV4" t="s" s="0">
-        <v>209</v>
+      <c r="AU4" t="s">
+        <v>148</v>
+      </c>
+      <c r="AV4" t="s">
+        <v>149</v>
       </c>
       <c r="AW4" s="35">
         <f>AM4</f>
@@ -14610,11 +14431,11 @@
       <c r="BL4" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="BM4" t="s" s="0">
-        <v>211</v>
-      </c>
-      <c r="BN4" t="s" s="0">
-        <v>210</v>
+      <c r="BM4" t="s">
+        <v>150</v>
+      </c>
+      <c r="BN4" t="s">
+        <v>151</v>
       </c>
       <c r="BO4" s="35">
         <f>ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
@@ -14759,73 +14580,73 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ5"/>
-  <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="8.7047619047619" defaultRowHeight="15" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="5.14545454545455"/>
-    <col min="2" max="3" customWidth="true" width="27.5727272727273"/>
-    <col min="4" max="4" customWidth="true" width="79.4272727272727"/>
-    <col min="5" max="5" customWidth="true" width="11.5727272727273"/>
-    <col min="6" max="6" customWidth="true" width="5.14545454545455"/>
-    <col min="7" max="7" customWidth="true" width="11.0"/>
-    <col min="8" max="8" customWidth="true" width="12.7181818181818"/>
-    <col min="9" max="9" customWidth="true" width="5.85454545454545"/>
-    <col min="10" max="10" customWidth="true" width="6.0"/>
-    <col min="11" max="11" customWidth="true" width="5.85454545454545"/>
-    <col min="12" max="12" customWidth="true" width="14.2818181818182"/>
-    <col min="13" max="13" customWidth="true" width="9.42727272727273"/>
-    <col min="14" max="14" customWidth="true" width="14.4272727272727"/>
-    <col min="15" max="15" customWidth="true" width="15.5727272727273"/>
-    <col min="16" max="16" customWidth="true" width="14.4272727272727"/>
-    <col min="17" max="17" customWidth="true" width="39.4272727272727"/>
-    <col min="18" max="18" customWidth="true" width="11.7181818181818"/>
-    <col min="19" max="19" customWidth="true" width="11.8545454545455"/>
-    <col min="20" max="20" customWidth="true" width="6.42727272727273"/>
-    <col min="21" max="22" customWidth="true" width="6.57272727272727"/>
-    <col min="23" max="23" customWidth="true" width="37.1454545454545"/>
-    <col min="24" max="25" customWidth="true" width="8.0"/>
-    <col min="26" max="26" customWidth="true" width="7.71818181818182"/>
-    <col min="27" max="27" customWidth="true" width="6.28181818181818"/>
-    <col min="28" max="28" customWidth="true" width="9.28181818181818"/>
-    <col min="29" max="29" customWidth="true" width="9.71818181818182"/>
-    <col min="30" max="30" customWidth="true" width="12.8545454545455"/>
-    <col min="31" max="31" customWidth="true" width="16.1454545454545"/>
-    <col min="32" max="32" customWidth="true" width="15.4272727272727"/>
-    <col min="33" max="33" customWidth="true" width="24.5727272727273"/>
-    <col min="34" max="34" customWidth="true" width="8.57272727272727"/>
-    <col min="35" max="35" customWidth="true" width="14.7181818181818"/>
-    <col min="36" max="36" customWidth="true" width="18.5727272727273"/>
-    <col min="37" max="37" customWidth="true" width="14.1454545454545"/>
-    <col min="38" max="38" customWidth="true" width="14.7181818181818"/>
-    <col min="39" max="39" customWidth="true" width="17.4272727272727"/>
-    <col min="40" max="40" customWidth="true" width="22.0"/>
-    <col min="41" max="41" customWidth="true" width="17.5727272727273"/>
-    <col min="42" max="42" customWidth="true" width="25.2818181818182"/>
-    <col min="43" max="43" customWidth="true" width="13.0"/>
-    <col min="44" max="44" customWidth="true" width="23.7181818181818"/>
-    <col min="45" max="45" customWidth="true" width="10.0"/>
-    <col min="46" max="46" customWidth="true" width="13.0"/>
-    <col min="47" max="47" customWidth="true" width="15.5727272727273"/>
-    <col min="48" max="48" customWidth="true" width="21.1454545454545"/>
-    <col min="49" max="49" customWidth="true" width="11.5727272727273"/>
-    <col min="50" max="50" customWidth="true" width="16.7181818181818"/>
-    <col min="51" max="51" customWidth="true" width="14.0"/>
-    <col min="52" max="52" customWidth="true" width="19.4272727272727"/>
-    <col min="53" max="53" customWidth="true" width="18.8545454545455"/>
-    <col min="54" max="54" customWidth="true" width="23.2818181818182"/>
-    <col min="55" max="55" customWidth="true" width="15.5727272727273"/>
-    <col min="56" max="56" customWidth="true" width="14.2818181818182"/>
-    <col min="57" max="57" customWidth="true" width="17.0"/>
-    <col min="58" max="58" customWidth="true" width="16.2818181818182"/>
-    <col min="59" max="59" customWidth="true" width="13.5727272727273"/>
-    <col min="60" max="61" customWidth="true" width="12.7181818181818"/>
-    <col min="62" max="62" customWidth="true" width="21.8545454545455"/>
-    <col min="63" max="63" customWidth="true" width="30.5727272727273"/>
-    <col min="64" max="64" customWidth="true" width="10.0"/>
-    <col min="65" max="65" customWidth="true" width="42.5727272727273"/>
-    <col min="66" max="66" customWidth="true" width="38.1454545454545"/>
-    <col min="67" max="67" customWidth="true" width="19.4272727272727"/>
-    <col min="68" max="68" customWidth="true" width="35.4272727272727"/>
-    <col min="69" max="69" customWidth="true" width="9.57272727272727"/>
+    <col min="1" max="1" width="5.14285714285714" customWidth="1"/>
+    <col min="2" max="3" width="27.5714285714286" customWidth="1"/>
+    <col min="4" max="4" width="79.4285714285714" customWidth="1"/>
+    <col min="5" max="5" width="11.5714285714286" customWidth="1"/>
+    <col min="6" max="6" width="5.14285714285714" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="12.7142857142857" customWidth="1"/>
+    <col min="9" max="9" width="5.85714285714286" customWidth="1"/>
+    <col min="10" max="10" width="6" customWidth="1"/>
+    <col min="11" max="11" width="5.85714285714286" customWidth="1"/>
+    <col min="12" max="12" width="14.2857142857143" customWidth="1"/>
+    <col min="13" max="13" width="9.42857142857143" customWidth="1"/>
+    <col min="14" max="14" width="14.4285714285714" customWidth="1"/>
+    <col min="15" max="15" width="15.5714285714286" customWidth="1"/>
+    <col min="16" max="16" width="14.4285714285714" customWidth="1"/>
+    <col min="17" max="17" width="39.4285714285714" customWidth="1"/>
+    <col min="18" max="18" width="11.7142857142857" customWidth="1"/>
+    <col min="19" max="19" width="11.8571428571429" customWidth="1"/>
+    <col min="20" max="20" width="6.42857142857143" customWidth="1"/>
+    <col min="21" max="22" width="6.57142857142857" customWidth="1"/>
+    <col min="23" max="23" width="37.1428571428571" customWidth="1"/>
+    <col min="24" max="25" width="8" customWidth="1"/>
+    <col min="26" max="26" width="7.71428571428571" customWidth="1"/>
+    <col min="27" max="27" width="6.28571428571429" customWidth="1"/>
+    <col min="28" max="28" width="9.28571428571429" customWidth="1"/>
+    <col min="29" max="29" width="9.71428571428571" customWidth="1"/>
+    <col min="30" max="30" width="12.8571428571429" customWidth="1"/>
+    <col min="31" max="31" width="16.1428571428571" customWidth="1"/>
+    <col min="32" max="32" width="15.4285714285714" customWidth="1"/>
+    <col min="33" max="33" width="24.5714285714286" customWidth="1"/>
+    <col min="34" max="34" width="8.57142857142857" customWidth="1"/>
+    <col min="35" max="35" width="14.7142857142857" customWidth="1"/>
+    <col min="36" max="36" width="18.5714285714286" customWidth="1"/>
+    <col min="37" max="37" width="14.1428571428571" customWidth="1"/>
+    <col min="38" max="38" width="14.7142857142857" customWidth="1"/>
+    <col min="39" max="39" width="17.4285714285714" customWidth="1"/>
+    <col min="40" max="40" width="22" customWidth="1"/>
+    <col min="41" max="41" width="17.5714285714286" customWidth="1"/>
+    <col min="42" max="42" width="25.2857142857143" customWidth="1"/>
+    <col min="43" max="43" width="13" customWidth="1"/>
+    <col min="44" max="44" width="23.7142857142857" customWidth="1"/>
+    <col min="45" max="45" width="10" customWidth="1"/>
+    <col min="46" max="46" width="13" customWidth="1"/>
+    <col min="47" max="47" width="15.5714285714286" customWidth="1"/>
+    <col min="48" max="48" width="21.1428571428571" customWidth="1"/>
+    <col min="49" max="49" width="11.5714285714286" customWidth="1"/>
+    <col min="50" max="50" width="16.7142857142857" customWidth="1"/>
+    <col min="51" max="51" width="14" customWidth="1"/>
+    <col min="52" max="52" width="19.4285714285714" customWidth="1"/>
+    <col min="53" max="53" width="18.8571428571429" customWidth="1"/>
+    <col min="54" max="54" width="23.2857142857143" customWidth="1"/>
+    <col min="55" max="55" width="15.5714285714286" customWidth="1"/>
+    <col min="56" max="56" width="14.2857142857143" customWidth="1"/>
+    <col min="57" max="57" width="17" customWidth="1"/>
+    <col min="58" max="58" width="16.2857142857143" customWidth="1"/>
+    <col min="59" max="59" width="13.5714285714286" customWidth="1"/>
+    <col min="60" max="61" width="12.7142857142857" customWidth="1"/>
+    <col min="62" max="62" width="21.8571428571429" customWidth="1"/>
+    <col min="63" max="63" width="30.5714285714286" customWidth="1"/>
+    <col min="64" max="64" width="10" customWidth="1"/>
+    <col min="65" max="65" width="42.5714285714286" customWidth="1"/>
+    <col min="66" max="66" width="38.1428571428571" customWidth="1"/>
+    <col min="67" max="67" width="19.4285714285714" customWidth="1"/>
+    <col min="68" max="68" width="35.4285714285714" customWidth="1"/>
+    <col min="69" max="69" width="9.57142857142857" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -14996,7 +14817,7 @@
       <c r="BP2" s="27"/>
       <c r="BQ2" s="27"/>
     </row>
-    <row r="3" ht="15.25" spans="1:69">
+    <row r="3" ht="15.75" spans="1:69">
       <c r="A3" s="28" t="s">
         <v>9</v>
       </c>
@@ -15043,7 +14864,7 @@
         <v>25</v>
       </c>
       <c r="P3" s="30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="Q3" s="30" t="s">
         <v>23</v>
@@ -15052,13 +14873,13 @@
         <v>26</v>
       </c>
       <c r="S3" s="28" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="T3" s="28" t="s">
         <v>28</v>
       </c>
       <c r="U3" s="31" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="V3" s="31" t="s">
         <v>30</v>
@@ -15127,7 +14948,7 @@
         <v>51</v>
       </c>
       <c r="AR3" s="33" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AS3" s="28" t="s">
         <v>53</v>
@@ -15205,15 +15026,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.25" spans="1:69">
+    <row r="4" ht="15.75" spans="1:69">
       <c r="A4" s="26">
         <v>1</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="C4" s="26" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D4" s="26" t="s">
         <v>76</v>
@@ -15369,11 +15190,11 @@
       <c r="AT4" s="35" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" t="s" s="0">
-        <v>212</v>
-      </c>
-      <c r="AV4" t="s" s="0">
-        <v>213</v>
+      <c r="AU4" t="s">
+        <v>153</v>
+      </c>
+      <c r="AV4" t="s">
+        <v>154</v>
       </c>
       <c r="AW4" s="35">
         <f>AM4</f>
@@ -15413,11 +15234,11 @@
       <c r="BL4" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="BM4" t="s" s="0">
-        <v>215</v>
-      </c>
-      <c r="BN4" t="s" s="0">
-        <v>214</v>
+      <c r="BM4" t="s">
+        <v>155</v>
+      </c>
+      <c r="BN4" t="s">
+        <v>156</v>
       </c>
       <c r="BO4" s="35">
         <f>ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
@@ -15574,73 +15395,73 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ5"/>
-  <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="8.7047619047619" defaultRowHeight="15" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="5.14545454545455"/>
-    <col min="2" max="3" customWidth="true" width="27.5727272727273"/>
-    <col min="4" max="4" customWidth="true" width="79.4272727272727"/>
-    <col min="5" max="5" customWidth="true" width="11.5727272727273"/>
-    <col min="6" max="6" customWidth="true" width="5.14545454545455"/>
-    <col min="7" max="7" customWidth="true" width="11.0"/>
-    <col min="8" max="8" customWidth="true" width="12.7181818181818"/>
-    <col min="9" max="9" customWidth="true" width="5.85454545454545"/>
-    <col min="10" max="10" customWidth="true" width="6.0"/>
-    <col min="11" max="11" customWidth="true" width="5.85454545454545"/>
-    <col min="12" max="12" customWidth="true" width="14.2818181818182"/>
-    <col min="13" max="13" customWidth="true" width="9.42727272727273"/>
-    <col min="14" max="14" customWidth="true" width="14.4272727272727"/>
-    <col min="15" max="15" customWidth="true" width="15.5727272727273"/>
-    <col min="16" max="16" customWidth="true" width="14.4272727272727"/>
-    <col min="17" max="17" customWidth="true" width="39.4272727272727"/>
-    <col min="18" max="18" customWidth="true" width="11.7181818181818"/>
-    <col min="19" max="19" customWidth="true" width="11.8545454545455"/>
-    <col min="20" max="20" customWidth="true" width="6.42727272727273"/>
-    <col min="21" max="22" customWidth="true" width="6.57272727272727"/>
-    <col min="23" max="23" customWidth="true" width="37.1454545454545"/>
-    <col min="24" max="25" customWidth="true" width="8.0"/>
-    <col min="26" max="26" customWidth="true" width="7.71818181818182"/>
-    <col min="27" max="27" customWidth="true" width="6.28181818181818"/>
-    <col min="28" max="28" customWidth="true" width="9.28181818181818"/>
-    <col min="29" max="29" customWidth="true" width="9.71818181818182"/>
-    <col min="30" max="30" customWidth="true" width="12.8545454545455"/>
-    <col min="31" max="31" customWidth="true" width="16.1454545454545"/>
-    <col min="32" max="32" customWidth="true" width="15.4272727272727"/>
-    <col min="33" max="33" customWidth="true" width="24.5727272727273"/>
-    <col min="34" max="34" customWidth="true" width="8.57272727272727"/>
-    <col min="35" max="35" customWidth="true" width="14.7181818181818"/>
-    <col min="36" max="36" customWidth="true" width="18.5727272727273"/>
-    <col min="37" max="37" customWidth="true" width="14.1454545454545"/>
-    <col min="38" max="38" customWidth="true" width="14.7181818181818"/>
-    <col min="39" max="39" customWidth="true" width="17.4272727272727"/>
-    <col min="40" max="40" customWidth="true" width="22.0"/>
-    <col min="41" max="41" customWidth="true" width="17.5727272727273"/>
-    <col min="42" max="42" customWidth="true" width="25.2818181818182"/>
-    <col min="43" max="43" customWidth="true" width="13.0"/>
-    <col min="44" max="44" customWidth="true" width="23.7181818181818"/>
-    <col min="45" max="45" customWidth="true" width="10.0"/>
-    <col min="46" max="46" customWidth="true" width="13.0"/>
-    <col min="47" max="47" customWidth="true" width="15.5727272727273"/>
-    <col min="48" max="48" customWidth="true" width="21.1454545454545"/>
-    <col min="49" max="49" customWidth="true" width="11.5727272727273"/>
-    <col min="50" max="50" customWidth="true" width="16.7181818181818"/>
-    <col min="51" max="51" customWidth="true" width="14.0"/>
-    <col min="52" max="52" customWidth="true" width="19.4272727272727"/>
-    <col min="53" max="53" customWidth="true" width="18.8545454545455"/>
-    <col min="54" max="54" customWidth="true" width="23.2818181818182"/>
-    <col min="55" max="55" customWidth="true" width="15.5727272727273"/>
-    <col min="56" max="56" customWidth="true" width="14.2818181818182"/>
-    <col min="57" max="57" customWidth="true" width="17.0"/>
-    <col min="58" max="58" customWidth="true" width="16.2818181818182"/>
-    <col min="59" max="59" customWidth="true" width="13.5727272727273"/>
-    <col min="60" max="61" customWidth="true" width="12.7181818181818"/>
-    <col min="62" max="62" customWidth="true" width="21.8545454545455"/>
-    <col min="63" max="63" customWidth="true" width="30.5727272727273"/>
-    <col min="64" max="64" customWidth="true" width="10.0"/>
-    <col min="65" max="65" customWidth="true" width="42.5727272727273"/>
-    <col min="66" max="66" customWidth="true" width="38.1454545454545"/>
-    <col min="67" max="67" customWidth="true" width="19.4272727272727"/>
-    <col min="68" max="68" customWidth="true" width="35.4272727272727"/>
-    <col min="69" max="69" customWidth="true" width="9.57272727272727"/>
+    <col min="1" max="1" width="5.14285714285714" customWidth="1"/>
+    <col min="2" max="3" width="27.5714285714286" customWidth="1"/>
+    <col min="4" max="4" width="79.4285714285714" customWidth="1"/>
+    <col min="5" max="5" width="11.5714285714286" customWidth="1"/>
+    <col min="6" max="6" width="5.14285714285714" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="12.7142857142857" customWidth="1"/>
+    <col min="9" max="9" width="5.85714285714286" customWidth="1"/>
+    <col min="10" max="10" width="6" customWidth="1"/>
+    <col min="11" max="11" width="5.85714285714286" customWidth="1"/>
+    <col min="12" max="12" width="14.2857142857143" customWidth="1"/>
+    <col min="13" max="13" width="9.42857142857143" customWidth="1"/>
+    <col min="14" max="14" width="14.4285714285714" customWidth="1"/>
+    <col min="15" max="15" width="15.5714285714286" customWidth="1"/>
+    <col min="16" max="16" width="14.4285714285714" customWidth="1"/>
+    <col min="17" max="17" width="39.4285714285714" customWidth="1"/>
+    <col min="18" max="18" width="11.7142857142857" customWidth="1"/>
+    <col min="19" max="19" width="11.8571428571429" customWidth="1"/>
+    <col min="20" max="20" width="6.42857142857143" customWidth="1"/>
+    <col min="21" max="22" width="6.57142857142857" customWidth="1"/>
+    <col min="23" max="23" width="37.1428571428571" customWidth="1"/>
+    <col min="24" max="25" width="8" customWidth="1"/>
+    <col min="26" max="26" width="7.71428571428571" customWidth="1"/>
+    <col min="27" max="27" width="6.28571428571429" customWidth="1"/>
+    <col min="28" max="28" width="9.28571428571429" customWidth="1"/>
+    <col min="29" max="29" width="9.71428571428571" customWidth="1"/>
+    <col min="30" max="30" width="12.8571428571429" customWidth="1"/>
+    <col min="31" max="31" width="16.1428571428571" customWidth="1"/>
+    <col min="32" max="32" width="15.4285714285714" customWidth="1"/>
+    <col min="33" max="33" width="24.5714285714286" customWidth="1"/>
+    <col min="34" max="34" width="8.57142857142857" customWidth="1"/>
+    <col min="35" max="35" width="14.7142857142857" customWidth="1"/>
+    <col min="36" max="36" width="18.5714285714286" customWidth="1"/>
+    <col min="37" max="37" width="14.1428571428571" customWidth="1"/>
+    <col min="38" max="38" width="14.7142857142857" customWidth="1"/>
+    <col min="39" max="39" width="17.4285714285714" customWidth="1"/>
+    <col min="40" max="40" width="22" customWidth="1"/>
+    <col min="41" max="41" width="17.5714285714286" customWidth="1"/>
+    <col min="42" max="42" width="25.2857142857143" customWidth="1"/>
+    <col min="43" max="43" width="13" customWidth="1"/>
+    <col min="44" max="44" width="23.7142857142857" customWidth="1"/>
+    <col min="45" max="45" width="10" customWidth="1"/>
+    <col min="46" max="46" width="13" customWidth="1"/>
+    <col min="47" max="47" width="15.5714285714286" customWidth="1"/>
+    <col min="48" max="48" width="21.1428571428571" customWidth="1"/>
+    <col min="49" max="49" width="11.5714285714286" customWidth="1"/>
+    <col min="50" max="50" width="16.7142857142857" customWidth="1"/>
+    <col min="51" max="51" width="14" customWidth="1"/>
+    <col min="52" max="52" width="19.4285714285714" customWidth="1"/>
+    <col min="53" max="53" width="18.8571428571429" customWidth="1"/>
+    <col min="54" max="54" width="23.2857142857143" customWidth="1"/>
+    <col min="55" max="55" width="15.5714285714286" customWidth="1"/>
+    <col min="56" max="56" width="14.2857142857143" customWidth="1"/>
+    <col min="57" max="57" width="17" customWidth="1"/>
+    <col min="58" max="58" width="16.2857142857143" customWidth="1"/>
+    <col min="59" max="59" width="13.5714285714286" customWidth="1"/>
+    <col min="60" max="61" width="12.7142857142857" customWidth="1"/>
+    <col min="62" max="62" width="21.8571428571429" customWidth="1"/>
+    <col min="63" max="63" width="30.5714285714286" customWidth="1"/>
+    <col min="64" max="64" width="10" customWidth="1"/>
+    <col min="65" max="65" width="42.5714285714286" customWidth="1"/>
+    <col min="66" max="66" width="38.1428571428571" customWidth="1"/>
+    <col min="67" max="67" width="19.4285714285714" customWidth="1"/>
+    <col min="68" max="68" width="35.4285714285714" customWidth="1"/>
+    <col min="69" max="69" width="9.57142857142857" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -15811,7 +15632,7 @@
       <c r="BP2" s="27"/>
       <c r="BQ2" s="27"/>
     </row>
-    <row r="3" ht="15.25" spans="1:69">
+    <row r="3" ht="15.75" spans="1:69">
       <c r="A3" s="28" t="s">
         <v>9</v>
       </c>
@@ -15858,7 +15679,7 @@
         <v>25</v>
       </c>
       <c r="P3" s="30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="Q3" s="30" t="s">
         <v>23</v>
@@ -15867,13 +15688,13 @@
         <v>26</v>
       </c>
       <c r="S3" s="28" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="T3" s="28" t="s">
         <v>28</v>
       </c>
       <c r="U3" s="31" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="V3" s="31" t="s">
         <v>30</v>
@@ -15942,7 +15763,7 @@
         <v>51</v>
       </c>
       <c r="AR3" s="33" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AS3" s="28" t="s">
         <v>53</v>
@@ -16020,15 +15841,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.25" spans="1:69">
+    <row r="4" ht="15.75" spans="1:69">
       <c r="A4" s="26">
         <v>1</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C4" s="26" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="D4" s="26" t="s">
         <v>76</v>
@@ -16184,11 +16005,11 @@
       <c r="AT4" s="35" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" t="s" s="0">
-        <v>216</v>
-      </c>
-      <c r="AV4" t="s" s="0">
-        <v>217</v>
+      <c r="AU4" t="s">
+        <v>158</v>
+      </c>
+      <c r="AV4" t="s">
+        <v>159</v>
       </c>
       <c r="AW4" s="35">
         <f>AM4</f>
@@ -16228,11 +16049,11 @@
       <c r="BL4" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="BM4" t="s" s="0">
-        <v>219</v>
-      </c>
-      <c r="BN4" t="s" s="0">
-        <v>218</v>
+      <c r="BM4" t="s">
+        <v>160</v>
+      </c>
+      <c r="BN4" t="s">
+        <v>161</v>
       </c>
       <c r="BO4" s="35">
         <f>ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
@@ -16389,73 +16210,73 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ5"/>
-  <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="8.7047619047619" defaultRowHeight="15" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="5.14545454545455"/>
-    <col min="2" max="3" customWidth="true" width="27.5727272727273"/>
-    <col min="4" max="4" customWidth="true" width="79.4272727272727"/>
-    <col min="5" max="5" customWidth="true" width="11.5727272727273"/>
-    <col min="6" max="6" customWidth="true" width="5.14545454545455"/>
-    <col min="7" max="7" customWidth="true" width="11.0"/>
-    <col min="8" max="8" customWidth="true" width="12.7181818181818"/>
-    <col min="9" max="9" customWidth="true" width="5.85454545454545"/>
-    <col min="10" max="10" customWidth="true" width="6.0"/>
-    <col min="11" max="11" customWidth="true" width="5.85454545454545"/>
-    <col min="12" max="12" customWidth="true" width="14.2818181818182"/>
-    <col min="13" max="13" customWidth="true" width="9.42727272727273"/>
-    <col min="14" max="14" customWidth="true" width="14.4272727272727"/>
-    <col min="15" max="15" customWidth="true" width="15.5727272727273"/>
-    <col min="16" max="16" customWidth="true" width="14.4272727272727"/>
-    <col min="17" max="17" customWidth="true" width="39.4272727272727"/>
-    <col min="18" max="18" customWidth="true" width="11.7181818181818"/>
-    <col min="19" max="19" customWidth="true" width="11.8545454545455"/>
-    <col min="20" max="20" customWidth="true" width="6.42727272727273"/>
-    <col min="21" max="22" customWidth="true" width="6.57272727272727"/>
-    <col min="23" max="23" customWidth="true" width="37.1454545454545"/>
-    <col min="24" max="25" customWidth="true" width="8.0"/>
-    <col min="26" max="26" customWidth="true" width="7.71818181818182"/>
-    <col min="27" max="27" customWidth="true" width="6.28181818181818"/>
-    <col min="28" max="28" customWidth="true" width="9.28181818181818"/>
-    <col min="29" max="29" customWidth="true" width="9.71818181818182"/>
-    <col min="30" max="30" customWidth="true" width="12.8545454545455"/>
-    <col min="31" max="31" customWidth="true" width="16.1454545454545"/>
-    <col min="32" max="32" customWidth="true" width="15.4272727272727"/>
-    <col min="33" max="33" customWidth="true" width="24.5727272727273"/>
-    <col min="34" max="34" customWidth="true" width="8.57272727272727"/>
-    <col min="35" max="35" customWidth="true" width="14.7181818181818"/>
-    <col min="36" max="36" customWidth="true" width="18.5727272727273"/>
-    <col min="37" max="37" customWidth="true" width="14.1454545454545"/>
-    <col min="38" max="38" customWidth="true" width="14.7181818181818"/>
-    <col min="39" max="39" customWidth="true" width="17.4272727272727"/>
-    <col min="40" max="40" customWidth="true" width="22.0"/>
-    <col min="41" max="41" customWidth="true" width="17.5727272727273"/>
-    <col min="42" max="42" customWidth="true" width="25.2818181818182"/>
-    <col min="43" max="43" customWidth="true" width="13.0"/>
-    <col min="44" max="44" customWidth="true" width="23.7181818181818"/>
-    <col min="45" max="45" customWidth="true" width="10.0"/>
-    <col min="46" max="46" customWidth="true" width="13.0"/>
-    <col min="47" max="47" customWidth="true" width="15.5727272727273"/>
-    <col min="48" max="48" customWidth="true" width="21.1454545454545"/>
-    <col min="49" max="49" customWidth="true" width="11.5727272727273"/>
-    <col min="50" max="50" customWidth="true" width="16.7181818181818"/>
-    <col min="51" max="51" customWidth="true" width="14.0"/>
-    <col min="52" max="52" customWidth="true" width="19.4272727272727"/>
-    <col min="53" max="53" customWidth="true" width="18.8545454545455"/>
-    <col min="54" max="54" customWidth="true" width="23.2818181818182"/>
-    <col min="55" max="55" customWidth="true" width="15.5727272727273"/>
-    <col min="56" max="56" customWidth="true" width="14.2818181818182"/>
-    <col min="57" max="57" customWidth="true" width="17.0"/>
-    <col min="58" max="58" customWidth="true" width="16.2818181818182"/>
-    <col min="59" max="59" customWidth="true" width="13.5727272727273"/>
-    <col min="60" max="61" customWidth="true" width="12.7181818181818"/>
-    <col min="62" max="62" customWidth="true" width="21.8545454545455"/>
-    <col min="63" max="63" customWidth="true" width="30.5727272727273"/>
-    <col min="64" max="64" customWidth="true" width="10.0"/>
-    <col min="65" max="65" customWidth="true" width="42.5727272727273"/>
-    <col min="66" max="66" customWidth="true" width="38.1454545454545"/>
-    <col min="67" max="67" customWidth="true" width="19.4272727272727"/>
-    <col min="68" max="68" customWidth="true" width="35.4272727272727"/>
-    <col min="69" max="69" customWidth="true" width="9.57272727272727"/>
+    <col min="1" max="1" width="5.14285714285714" customWidth="1"/>
+    <col min="2" max="3" width="27.5714285714286" customWidth="1"/>
+    <col min="4" max="4" width="79.4285714285714" customWidth="1"/>
+    <col min="5" max="5" width="11.5714285714286" customWidth="1"/>
+    <col min="6" max="6" width="5.14285714285714" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="12.7142857142857" customWidth="1"/>
+    <col min="9" max="9" width="5.85714285714286" customWidth="1"/>
+    <col min="10" max="10" width="6" customWidth="1"/>
+    <col min="11" max="11" width="5.85714285714286" customWidth="1"/>
+    <col min="12" max="12" width="14.2857142857143" customWidth="1"/>
+    <col min="13" max="13" width="9.42857142857143" customWidth="1"/>
+    <col min="14" max="14" width="14.4285714285714" customWidth="1"/>
+    <col min="15" max="15" width="15.5714285714286" customWidth="1"/>
+    <col min="16" max="16" width="14.4285714285714" customWidth="1"/>
+    <col min="17" max="17" width="39.4285714285714" customWidth="1"/>
+    <col min="18" max="18" width="11.7142857142857" customWidth="1"/>
+    <col min="19" max="19" width="11.8571428571429" customWidth="1"/>
+    <col min="20" max="20" width="6.42857142857143" customWidth="1"/>
+    <col min="21" max="22" width="6.57142857142857" customWidth="1"/>
+    <col min="23" max="23" width="37.1428571428571" customWidth="1"/>
+    <col min="24" max="25" width="8" customWidth="1"/>
+    <col min="26" max="26" width="7.71428571428571" customWidth="1"/>
+    <col min="27" max="27" width="6.28571428571429" customWidth="1"/>
+    <col min="28" max="28" width="9.28571428571429" customWidth="1"/>
+    <col min="29" max="29" width="9.71428571428571" customWidth="1"/>
+    <col min="30" max="30" width="12.8571428571429" customWidth="1"/>
+    <col min="31" max="31" width="16.1428571428571" customWidth="1"/>
+    <col min="32" max="32" width="15.4285714285714" customWidth="1"/>
+    <col min="33" max="33" width="24.5714285714286" customWidth="1"/>
+    <col min="34" max="34" width="8.57142857142857" customWidth="1"/>
+    <col min="35" max="35" width="14.7142857142857" customWidth="1"/>
+    <col min="36" max="36" width="18.5714285714286" customWidth="1"/>
+    <col min="37" max="37" width="14.1428571428571" customWidth="1"/>
+    <col min="38" max="38" width="14.7142857142857" customWidth="1"/>
+    <col min="39" max="39" width="17.4285714285714" customWidth="1"/>
+    <col min="40" max="40" width="22" customWidth="1"/>
+    <col min="41" max="41" width="17.5714285714286" customWidth="1"/>
+    <col min="42" max="42" width="25.2857142857143" customWidth="1"/>
+    <col min="43" max="43" width="13" customWidth="1"/>
+    <col min="44" max="44" width="23.7142857142857" customWidth="1"/>
+    <col min="45" max="45" width="10" customWidth="1"/>
+    <col min="46" max="46" width="13" customWidth="1"/>
+    <col min="47" max="47" width="15.5714285714286" customWidth="1"/>
+    <col min="48" max="48" width="21.1428571428571" customWidth="1"/>
+    <col min="49" max="49" width="11.5714285714286" customWidth="1"/>
+    <col min="50" max="50" width="16.7142857142857" customWidth="1"/>
+    <col min="51" max="51" width="14" customWidth="1"/>
+    <col min="52" max="52" width="19.4285714285714" customWidth="1"/>
+    <col min="53" max="53" width="18.8571428571429" customWidth="1"/>
+    <col min="54" max="54" width="23.2857142857143" customWidth="1"/>
+    <col min="55" max="55" width="15.5714285714286" customWidth="1"/>
+    <col min="56" max="56" width="14.2857142857143" customWidth="1"/>
+    <col min="57" max="57" width="17" customWidth="1"/>
+    <col min="58" max="58" width="16.2857142857143" customWidth="1"/>
+    <col min="59" max="59" width="13.5714285714286" customWidth="1"/>
+    <col min="60" max="61" width="12.7142857142857" customWidth="1"/>
+    <col min="62" max="62" width="21.8571428571429" customWidth="1"/>
+    <col min="63" max="63" width="30.5714285714286" customWidth="1"/>
+    <col min="64" max="64" width="10" customWidth="1"/>
+    <col min="65" max="65" width="42.5714285714286" customWidth="1"/>
+    <col min="66" max="66" width="38.1428571428571" customWidth="1"/>
+    <col min="67" max="67" width="19.4285714285714" customWidth="1"/>
+    <col min="68" max="68" width="35.4285714285714" customWidth="1"/>
+    <col min="69" max="69" width="9.57142857142857" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -16626,7 +16447,7 @@
       <c r="BP2" s="8"/>
       <c r="BQ2" s="8"/>
     </row>
-    <row r="3" ht="15.25" spans="1:69">
+    <row r="3" ht="15.75" spans="1:69">
       <c r="A3" s="9" t="s">
         <v>9</v>
       </c>
@@ -16673,7 +16494,7 @@
         <v>25</v>
       </c>
       <c r="P3" s="11" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="Q3" s="11" t="s">
         <v>23</v>
@@ -16682,13 +16503,13 @@
         <v>26</v>
       </c>
       <c r="S3" s="9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="T3" s="9" t="s">
         <v>28</v>
       </c>
       <c r="U3" s="12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="V3" s="12" t="s">
         <v>30</v>
@@ -16757,7 +16578,7 @@
         <v>51</v>
       </c>
       <c r="AR3" s="14" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AS3" s="9" t="s">
         <v>53</v>
@@ -16835,15 +16656,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.25" spans="1:69">
+    <row r="4" ht="15.75" spans="1:69">
       <c r="A4" s="6">
         <v>1</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>76</v>
@@ -16862,7 +16683,7 @@
         <v>400</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J4" s="16">
         <v>2</v>
@@ -16999,11 +16820,11 @@
       <c r="AT4" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" t="s" s="0">
-        <v>212</v>
-      </c>
-      <c r="AV4" t="s" s="0">
-        <v>213</v>
+      <c r="AU4" t="s">
+        <v>153</v>
+      </c>
+      <c r="AV4" t="s">
+        <v>154</v>
       </c>
       <c r="AW4" s="16">
         <f>AM4</f>
@@ -17043,11 +16864,11 @@
       <c r="BL4" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="BM4" t="s" s="0">
-        <v>215</v>
-      </c>
-      <c r="BN4" t="s" s="0">
-        <v>214</v>
+      <c r="BM4" t="s">
+        <v>155</v>
+      </c>
+      <c r="BN4" t="s">
+        <v>156</v>
       </c>
       <c r="BO4" s="16">
         <f>ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
@@ -17192,73 +17013,73 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ5"/>
-  <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="8.7047619047619" defaultRowHeight="15" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="5.14545454545455"/>
-    <col min="2" max="3" customWidth="true" width="27.5727272727273"/>
-    <col min="4" max="4" customWidth="true" width="79.4272727272727"/>
-    <col min="5" max="5" customWidth="true" width="11.5727272727273"/>
-    <col min="6" max="6" customWidth="true" width="5.14545454545455"/>
-    <col min="7" max="7" customWidth="true" width="11.0"/>
-    <col min="8" max="8" customWidth="true" width="12.7181818181818"/>
-    <col min="9" max="9" customWidth="true" width="5.85454545454545"/>
-    <col min="10" max="10" customWidth="true" width="6.0"/>
-    <col min="11" max="11" customWidth="true" width="5.85454545454545"/>
-    <col min="12" max="12" customWidth="true" width="14.2818181818182"/>
-    <col min="13" max="13" customWidth="true" width="9.42727272727273"/>
-    <col min="14" max="14" customWidth="true" width="14.4272727272727"/>
-    <col min="15" max="15" customWidth="true" width="15.5727272727273"/>
-    <col min="16" max="16" customWidth="true" width="14.4272727272727"/>
-    <col min="17" max="17" customWidth="true" width="39.4272727272727"/>
-    <col min="18" max="18" customWidth="true" width="11.7181818181818"/>
-    <col min="19" max="19" customWidth="true" width="11.8545454545455"/>
-    <col min="20" max="20" customWidth="true" width="6.42727272727273"/>
-    <col min="21" max="22" customWidth="true" width="6.57272727272727"/>
-    <col min="23" max="23" customWidth="true" width="37.1454545454545"/>
-    <col min="24" max="25" customWidth="true" width="8.0"/>
-    <col min="26" max="26" customWidth="true" width="7.71818181818182"/>
-    <col min="27" max="27" customWidth="true" width="6.28181818181818"/>
-    <col min="28" max="28" customWidth="true" width="9.28181818181818"/>
-    <col min="29" max="29" customWidth="true" width="9.71818181818182"/>
-    <col min="30" max="30" customWidth="true" width="12.8545454545455"/>
-    <col min="31" max="31" customWidth="true" width="16.1454545454545"/>
-    <col min="32" max="32" customWidth="true" width="15.4272727272727"/>
-    <col min="33" max="33" customWidth="true" width="24.5727272727273"/>
-    <col min="34" max="34" customWidth="true" width="8.57272727272727"/>
-    <col min="35" max="35" customWidth="true" width="14.7181818181818"/>
-    <col min="36" max="36" customWidth="true" width="18.5727272727273"/>
-    <col min="37" max="37" customWidth="true" width="14.1454545454545"/>
-    <col min="38" max="38" customWidth="true" width="14.7181818181818"/>
-    <col min="39" max="39" customWidth="true" width="17.4272727272727"/>
-    <col min="40" max="40" customWidth="true" width="22.0"/>
-    <col min="41" max="41" customWidth="true" width="17.5727272727273"/>
-    <col min="42" max="42" customWidth="true" width="25.2818181818182"/>
-    <col min="43" max="43" customWidth="true" width="13.0"/>
-    <col min="44" max="44" customWidth="true" width="23.7181818181818"/>
-    <col min="45" max="45" customWidth="true" width="10.0"/>
-    <col min="46" max="46" customWidth="true" width="13.0"/>
-    <col min="47" max="47" customWidth="true" width="15.5727272727273"/>
-    <col min="48" max="48" customWidth="true" width="21.1454545454545"/>
-    <col min="49" max="49" customWidth="true" width="11.5727272727273"/>
-    <col min="50" max="50" customWidth="true" width="16.7181818181818"/>
-    <col min="51" max="51" customWidth="true" width="14.0"/>
-    <col min="52" max="52" customWidth="true" width="19.4272727272727"/>
-    <col min="53" max="53" customWidth="true" width="18.8545454545455"/>
-    <col min="54" max="54" customWidth="true" width="23.2818181818182"/>
-    <col min="55" max="55" customWidth="true" width="15.5727272727273"/>
-    <col min="56" max="56" customWidth="true" width="14.2818181818182"/>
-    <col min="57" max="57" customWidth="true" width="17.0"/>
-    <col min="58" max="58" customWidth="true" width="16.2818181818182"/>
-    <col min="59" max="59" customWidth="true" width="13.5727272727273"/>
-    <col min="60" max="61" customWidth="true" width="12.7181818181818"/>
-    <col min="62" max="62" customWidth="true" width="21.8545454545455"/>
-    <col min="63" max="63" customWidth="true" width="30.5727272727273"/>
-    <col min="64" max="64" customWidth="true" width="10.0"/>
-    <col min="65" max="65" customWidth="true" width="42.5727272727273"/>
-    <col min="66" max="66" customWidth="true" width="38.1454545454545"/>
-    <col min="67" max="67" customWidth="true" width="19.4272727272727"/>
-    <col min="68" max="68" customWidth="true" width="35.4272727272727"/>
-    <col min="69" max="69" customWidth="true" width="9.57272727272727"/>
+    <col min="1" max="1" width="5.14285714285714" customWidth="1"/>
+    <col min="2" max="3" width="27.5714285714286" customWidth="1"/>
+    <col min="4" max="4" width="79.4285714285714" customWidth="1"/>
+    <col min="5" max="5" width="11.5714285714286" customWidth="1"/>
+    <col min="6" max="6" width="5.14285714285714" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="12.7142857142857" customWidth="1"/>
+    <col min="9" max="9" width="5.85714285714286" customWidth="1"/>
+    <col min="10" max="10" width="6" customWidth="1"/>
+    <col min="11" max="11" width="5.85714285714286" customWidth="1"/>
+    <col min="12" max="12" width="14.2857142857143" customWidth="1"/>
+    <col min="13" max="13" width="9.42857142857143" customWidth="1"/>
+    <col min="14" max="14" width="14.4285714285714" customWidth="1"/>
+    <col min="15" max="15" width="15.5714285714286" customWidth="1"/>
+    <col min="16" max="16" width="14.4285714285714" customWidth="1"/>
+    <col min="17" max="17" width="39.4285714285714" customWidth="1"/>
+    <col min="18" max="18" width="11.7142857142857" customWidth="1"/>
+    <col min="19" max="19" width="11.8571428571429" customWidth="1"/>
+    <col min="20" max="20" width="6.42857142857143" customWidth="1"/>
+    <col min="21" max="22" width="6.57142857142857" customWidth="1"/>
+    <col min="23" max="23" width="37.1428571428571" customWidth="1"/>
+    <col min="24" max="25" width="8" customWidth="1"/>
+    <col min="26" max="26" width="7.71428571428571" customWidth="1"/>
+    <col min="27" max="27" width="6.28571428571429" customWidth="1"/>
+    <col min="28" max="28" width="9.28571428571429" customWidth="1"/>
+    <col min="29" max="29" width="9.71428571428571" customWidth="1"/>
+    <col min="30" max="30" width="12.8571428571429" customWidth="1"/>
+    <col min="31" max="31" width="16.1428571428571" customWidth="1"/>
+    <col min="32" max="32" width="15.4285714285714" customWidth="1"/>
+    <col min="33" max="33" width="24.5714285714286" customWidth="1"/>
+    <col min="34" max="34" width="8.57142857142857" customWidth="1"/>
+    <col min="35" max="35" width="14.7142857142857" customWidth="1"/>
+    <col min="36" max="36" width="18.5714285714286" customWidth="1"/>
+    <col min="37" max="37" width="14.1428571428571" customWidth="1"/>
+    <col min="38" max="38" width="14.7142857142857" customWidth="1"/>
+    <col min="39" max="39" width="17.4285714285714" customWidth="1"/>
+    <col min="40" max="40" width="22" customWidth="1"/>
+    <col min="41" max="41" width="17.5714285714286" customWidth="1"/>
+    <col min="42" max="42" width="25.2857142857143" customWidth="1"/>
+    <col min="43" max="43" width="13" customWidth="1"/>
+    <col min="44" max="44" width="23.7142857142857" customWidth="1"/>
+    <col min="45" max="45" width="10" customWidth="1"/>
+    <col min="46" max="46" width="13" customWidth="1"/>
+    <col min="47" max="47" width="15.5714285714286" customWidth="1"/>
+    <col min="48" max="48" width="21.1428571428571" customWidth="1"/>
+    <col min="49" max="49" width="11.5714285714286" customWidth="1"/>
+    <col min="50" max="50" width="16.7142857142857" customWidth="1"/>
+    <col min="51" max="51" width="14" customWidth="1"/>
+    <col min="52" max="52" width="19.4285714285714" customWidth="1"/>
+    <col min="53" max="53" width="18.8571428571429" customWidth="1"/>
+    <col min="54" max="54" width="23.2857142857143" customWidth="1"/>
+    <col min="55" max="55" width="15.5714285714286" customWidth="1"/>
+    <col min="56" max="56" width="14.2857142857143" customWidth="1"/>
+    <col min="57" max="57" width="17" customWidth="1"/>
+    <col min="58" max="58" width="16.2857142857143" customWidth="1"/>
+    <col min="59" max="59" width="13.5714285714286" customWidth="1"/>
+    <col min="60" max="61" width="12.7142857142857" customWidth="1"/>
+    <col min="62" max="62" width="21.8571428571429" customWidth="1"/>
+    <col min="63" max="63" width="30.5714285714286" customWidth="1"/>
+    <col min="64" max="64" width="10" customWidth="1"/>
+    <col min="65" max="65" width="42.5714285714286" customWidth="1"/>
+    <col min="66" max="66" width="38.1428571428571" customWidth="1"/>
+    <col min="67" max="67" width="19.4285714285714" customWidth="1"/>
+    <col min="68" max="68" width="35.4285714285714" customWidth="1"/>
+    <col min="69" max="69" width="9.57142857142857" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -17429,7 +17250,7 @@
       <c r="BP2" s="8"/>
       <c r="BQ2" s="8"/>
     </row>
-    <row r="3" ht="15.25" spans="1:69">
+    <row r="3" ht="15.75" spans="1:69">
       <c r="A3" s="9" t="s">
         <v>9</v>
       </c>
@@ -17476,7 +17297,7 @@
         <v>25</v>
       </c>
       <c r="P3" s="11" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="Q3" s="11" t="s">
         <v>23</v>
@@ -17485,13 +17306,13 @@
         <v>26</v>
       </c>
       <c r="S3" s="9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="T3" s="9" t="s">
         <v>28</v>
       </c>
       <c r="U3" s="12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="V3" s="12" t="s">
         <v>30</v>
@@ -17560,7 +17381,7 @@
         <v>51</v>
       </c>
       <c r="AR3" s="14" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AS3" s="9" t="s">
         <v>53</v>
@@ -17638,15 +17459,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.25" spans="1:69">
+    <row r="4" ht="15.75" spans="1:69">
       <c r="A4" s="6">
         <v>1</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>76</v>
@@ -17665,7 +17486,7 @@
         <v>400</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J4" s="16">
         <v>2</v>
@@ -17802,11 +17623,11 @@
       <c r="AT4" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" t="s" s="0">
-        <v>220</v>
-      </c>
-      <c r="AV4" t="s" s="0">
-        <v>221</v>
+      <c r="AU4" t="s">
+        <v>163</v>
+      </c>
+      <c r="AV4" t="s">
+        <v>164</v>
       </c>
       <c r="AW4" s="16">
         <f>AM4</f>
@@ -17846,11 +17667,11 @@
       <c r="BL4" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="BM4" t="s" s="0">
-        <v>223</v>
-      </c>
-      <c r="BN4" t="s" s="0">
-        <v>222</v>
+      <c r="BM4" t="s">
+        <v>165</v>
+      </c>
+      <c r="BN4" t="s">
+        <v>166</v>
       </c>
       <c r="BO4" s="16">
         <f>ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
@@ -17995,73 +17816,73 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ5"/>
-  <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="8.7047619047619" defaultRowHeight="15" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="5.14545454545455"/>
-    <col min="2" max="3" customWidth="true" width="22.0"/>
-    <col min="4" max="4" customWidth="true" width="79.4272727272727"/>
-    <col min="5" max="5" customWidth="true" width="11.5727272727273"/>
-    <col min="6" max="6" customWidth="true" width="5.14545454545455"/>
-    <col min="7" max="7" customWidth="true" width="11.0"/>
-    <col min="8" max="8" customWidth="true" width="12.7181818181818"/>
-    <col min="9" max="9" customWidth="true" width="5.85454545454545"/>
-    <col min="10" max="10" customWidth="true" width="6.0"/>
-    <col min="11" max="11" customWidth="true" width="5.85454545454545"/>
-    <col min="12" max="12" customWidth="true" width="14.2818181818182"/>
-    <col min="13" max="13" customWidth="true" width="9.42727272727273"/>
-    <col min="14" max="14" customWidth="true" width="14.4272727272727"/>
-    <col min="15" max="15" customWidth="true" width="15.5727272727273"/>
-    <col min="16" max="16" customWidth="true" width="14.4272727272727"/>
-    <col min="17" max="17" customWidth="true" width="39.4272727272727"/>
-    <col min="18" max="18" customWidth="true" width="11.7181818181818"/>
-    <col min="19" max="19" customWidth="true" width="11.8545454545455"/>
-    <col min="20" max="20" customWidth="true" width="6.42727272727273"/>
-    <col min="21" max="22" customWidth="true" width="6.57272727272727"/>
-    <col min="23" max="23" customWidth="true" width="37.1454545454545"/>
-    <col min="24" max="25" customWidth="true" width="8.0"/>
-    <col min="26" max="26" customWidth="true" width="7.71818181818182"/>
-    <col min="27" max="27" customWidth="true" width="6.28181818181818"/>
-    <col min="28" max="28" customWidth="true" width="9.28181818181818"/>
-    <col min="29" max="29" customWidth="true" width="9.71818181818182"/>
-    <col min="30" max="30" customWidth="true" width="12.8545454545455"/>
-    <col min="31" max="31" customWidth="true" width="16.1454545454545"/>
-    <col min="32" max="32" customWidth="true" width="15.4272727272727"/>
-    <col min="33" max="33" customWidth="true" width="24.5727272727273"/>
-    <col min="34" max="34" customWidth="true" width="8.57272727272727"/>
-    <col min="35" max="35" customWidth="true" width="14.7181818181818"/>
-    <col min="36" max="36" customWidth="true" width="18.5727272727273"/>
-    <col min="37" max="37" customWidth="true" width="14.1454545454545"/>
-    <col min="38" max="38" customWidth="true" width="14.7181818181818"/>
-    <col min="39" max="39" customWidth="true" width="17.4272727272727"/>
-    <col min="40" max="40" customWidth="true" width="22.0"/>
-    <col min="41" max="41" customWidth="true" width="17.5727272727273"/>
-    <col min="42" max="42" customWidth="true" width="25.2818181818182"/>
-    <col min="43" max="43" customWidth="true" width="13.0"/>
-    <col min="44" max="44" customWidth="true" width="23.7181818181818"/>
-    <col min="45" max="45" customWidth="true" width="10.0"/>
-    <col min="46" max="46" customWidth="true" width="13.0"/>
-    <col min="47" max="47" customWidth="true" width="15.5727272727273"/>
-    <col min="48" max="48" customWidth="true" width="21.1454545454545"/>
-    <col min="49" max="49" customWidth="true" width="11.5727272727273"/>
-    <col min="50" max="50" customWidth="true" width="16.7181818181818"/>
-    <col min="51" max="51" customWidth="true" width="14.0"/>
-    <col min="52" max="52" customWidth="true" width="19.4272727272727"/>
-    <col min="53" max="53" customWidth="true" width="18.8545454545455"/>
-    <col min="54" max="54" customWidth="true" width="23.2818181818182"/>
-    <col min="55" max="55" customWidth="true" width="15.5727272727273"/>
-    <col min="56" max="56" customWidth="true" width="14.2818181818182"/>
-    <col min="57" max="57" customWidth="true" width="17.0"/>
-    <col min="58" max="58" customWidth="true" width="16.2818181818182"/>
-    <col min="59" max="59" customWidth="true" width="13.5727272727273"/>
-    <col min="60" max="61" customWidth="true" width="12.7181818181818"/>
-    <col min="62" max="62" customWidth="true" width="21.8545454545455"/>
-    <col min="63" max="63" customWidth="true" width="30.5727272727273"/>
-    <col min="64" max="64" customWidth="true" width="10.0"/>
-    <col min="65" max="65" customWidth="true" width="42.5727272727273"/>
-    <col min="66" max="66" customWidth="true" width="38.1454545454545"/>
-    <col min="67" max="67" customWidth="true" width="19.4272727272727"/>
-    <col min="68" max="68" customWidth="true" width="35.4272727272727"/>
-    <col min="69" max="69" customWidth="true" width="9.57272727272727"/>
+    <col min="1" max="1" width="5.14285714285714" customWidth="1"/>
+    <col min="2" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="79.4285714285714" customWidth="1"/>
+    <col min="5" max="5" width="11.5714285714286" customWidth="1"/>
+    <col min="6" max="6" width="5.14285714285714" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="12.7142857142857" customWidth="1"/>
+    <col min="9" max="9" width="5.85714285714286" customWidth="1"/>
+    <col min="10" max="10" width="6" customWidth="1"/>
+    <col min="11" max="11" width="5.85714285714286" customWidth="1"/>
+    <col min="12" max="12" width="14.2857142857143" customWidth="1"/>
+    <col min="13" max="13" width="9.42857142857143" customWidth="1"/>
+    <col min="14" max="14" width="14.4285714285714" customWidth="1"/>
+    <col min="15" max="15" width="15.5714285714286" customWidth="1"/>
+    <col min="16" max="16" width="14.4285714285714" customWidth="1"/>
+    <col min="17" max="17" width="39.4285714285714" customWidth="1"/>
+    <col min="18" max="18" width="11.7142857142857" customWidth="1"/>
+    <col min="19" max="19" width="11.8571428571429" customWidth="1"/>
+    <col min="20" max="20" width="6.42857142857143" customWidth="1"/>
+    <col min="21" max="22" width="6.57142857142857" customWidth="1"/>
+    <col min="23" max="23" width="37.1428571428571" customWidth="1"/>
+    <col min="24" max="25" width="8" customWidth="1"/>
+    <col min="26" max="26" width="7.71428571428571" customWidth="1"/>
+    <col min="27" max="27" width="6.28571428571429" customWidth="1"/>
+    <col min="28" max="28" width="9.28571428571429" customWidth="1"/>
+    <col min="29" max="29" width="9.71428571428571" customWidth="1"/>
+    <col min="30" max="30" width="12.8571428571429" customWidth="1"/>
+    <col min="31" max="31" width="16.1428571428571" customWidth="1"/>
+    <col min="32" max="32" width="15.4285714285714" customWidth="1"/>
+    <col min="33" max="33" width="24.5714285714286" customWidth="1"/>
+    <col min="34" max="34" width="8.57142857142857" customWidth="1"/>
+    <col min="35" max="35" width="14.7142857142857" customWidth="1"/>
+    <col min="36" max="36" width="18.5714285714286" customWidth="1"/>
+    <col min="37" max="37" width="14.1428571428571" customWidth="1"/>
+    <col min="38" max="38" width="14.7142857142857" customWidth="1"/>
+    <col min="39" max="39" width="17.4285714285714" customWidth="1"/>
+    <col min="40" max="40" width="22" customWidth="1"/>
+    <col min="41" max="41" width="17.5714285714286" customWidth="1"/>
+    <col min="42" max="42" width="25.2857142857143" customWidth="1"/>
+    <col min="43" max="43" width="13" customWidth="1"/>
+    <col min="44" max="44" width="23.7142857142857" customWidth="1"/>
+    <col min="45" max="45" width="10" customWidth="1"/>
+    <col min="46" max="46" width="13" customWidth="1"/>
+    <col min="47" max="47" width="15.5714285714286" customWidth="1"/>
+    <col min="48" max="48" width="21.1428571428571" customWidth="1"/>
+    <col min="49" max="49" width="11.5714285714286" customWidth="1"/>
+    <col min="50" max="50" width="16.7142857142857" customWidth="1"/>
+    <col min="51" max="51" width="14" customWidth="1"/>
+    <col min="52" max="52" width="19.4285714285714" customWidth="1"/>
+    <col min="53" max="53" width="18.8571428571429" customWidth="1"/>
+    <col min="54" max="54" width="23.2857142857143" customWidth="1"/>
+    <col min="55" max="55" width="15.5714285714286" customWidth="1"/>
+    <col min="56" max="56" width="14.2857142857143" customWidth="1"/>
+    <col min="57" max="57" width="17" customWidth="1"/>
+    <col min="58" max="58" width="16.2857142857143" customWidth="1"/>
+    <col min="59" max="59" width="13.5714285714286" customWidth="1"/>
+    <col min="60" max="61" width="12.7142857142857" customWidth="1"/>
+    <col min="62" max="62" width="21.8571428571429" customWidth="1"/>
+    <col min="63" max="63" width="30.5714285714286" customWidth="1"/>
+    <col min="64" max="64" width="10" customWidth="1"/>
+    <col min="65" max="65" width="42.5714285714286" customWidth="1"/>
+    <col min="66" max="66" width="38.1428571428571" customWidth="1"/>
+    <col min="67" max="67" width="19.4285714285714" customWidth="1"/>
+    <col min="68" max="68" width="35.4285714285714" customWidth="1"/>
+    <col min="69" max="69" width="9.57142857142857" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -18232,7 +18053,7 @@
       <c r="BP2" s="27"/>
       <c r="BQ2" s="27"/>
     </row>
-    <row r="3" ht="15.25" spans="1:69">
+    <row r="3" spans="1:69">
       <c r="A3" s="28" t="s">
         <v>9</v>
       </c>
@@ -18279,7 +18100,7 @@
         <v>25</v>
       </c>
       <c r="P3" s="30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="Q3" s="30" t="s">
         <v>23</v>
@@ -18288,13 +18109,13 @@
         <v>26</v>
       </c>
       <c r="S3" s="28" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="T3" s="28" t="s">
         <v>28</v>
       </c>
       <c r="U3" s="31" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="V3" s="31" t="s">
         <v>30</v>
@@ -18363,7 +18184,7 @@
         <v>51</v>
       </c>
       <c r="AR3" s="33" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AS3" s="28" t="s">
         <v>53</v>
@@ -18441,15 +18262,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.25" spans="1:69">
+    <row r="4" spans="1:69">
       <c r="A4" s="26">
         <v>1</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C4" s="26" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D4" s="26" t="s">
         <v>76</v>
@@ -18646,10 +18467,10 @@
         <v>85</v>
       </c>
       <c r="BM4" s="27" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="BN4" s="27" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="BO4" s="35">
         <f>ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
@@ -18794,73 +18615,73 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ5"/>
-  <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="8.7047619047619" defaultRowHeight="15" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="5.14545454545455"/>
-    <col min="2" max="3" customWidth="true" width="25.0"/>
-    <col min="4" max="4" customWidth="true" width="79.4272727272727"/>
-    <col min="5" max="5" customWidth="true" width="11.5727272727273"/>
-    <col min="6" max="6" customWidth="true" width="5.14545454545455"/>
-    <col min="7" max="7" customWidth="true" width="11.0"/>
-    <col min="8" max="8" customWidth="true" width="12.7181818181818"/>
-    <col min="9" max="9" customWidth="true" width="5.85454545454545"/>
-    <col min="10" max="10" customWidth="true" width="6.0"/>
-    <col min="11" max="11" customWidth="true" width="5.85454545454545"/>
-    <col min="12" max="12" customWidth="true" width="14.2818181818182"/>
-    <col min="13" max="13" customWidth="true" width="9.42727272727273"/>
-    <col min="14" max="14" customWidth="true" width="14.4272727272727"/>
-    <col min="15" max="15" customWidth="true" width="15.5727272727273"/>
-    <col min="16" max="16" customWidth="true" width="14.4272727272727"/>
-    <col min="17" max="17" customWidth="true" width="39.4272727272727"/>
-    <col min="18" max="18" customWidth="true" width="11.7181818181818"/>
-    <col min="19" max="19" customWidth="true" width="11.8545454545455"/>
-    <col min="20" max="20" customWidth="true" width="6.42727272727273"/>
-    <col min="21" max="22" customWidth="true" width="6.57272727272727"/>
-    <col min="23" max="23" customWidth="true" width="37.1454545454545"/>
-    <col min="24" max="25" customWidth="true" width="8.0"/>
-    <col min="26" max="26" customWidth="true" width="7.71818181818182"/>
-    <col min="27" max="27" customWidth="true" width="6.28181818181818"/>
-    <col min="28" max="28" customWidth="true" width="9.28181818181818"/>
-    <col min="29" max="29" customWidth="true" width="9.71818181818182"/>
-    <col min="30" max="30" customWidth="true" width="12.8545454545455"/>
-    <col min="31" max="31" customWidth="true" width="16.1454545454545"/>
-    <col min="32" max="32" customWidth="true" width="15.4272727272727"/>
-    <col min="33" max="33" customWidth="true" width="24.5727272727273"/>
-    <col min="34" max="34" customWidth="true" width="8.57272727272727"/>
-    <col min="35" max="35" customWidth="true" width="14.7181818181818"/>
-    <col min="36" max="36" customWidth="true" width="18.5727272727273"/>
-    <col min="37" max="37" customWidth="true" width="14.1454545454545"/>
-    <col min="38" max="38" customWidth="true" width="14.7181818181818"/>
-    <col min="39" max="39" customWidth="true" width="17.4272727272727"/>
-    <col min="40" max="40" customWidth="true" width="22.0"/>
-    <col min="41" max="41" customWidth="true" width="17.5727272727273"/>
-    <col min="42" max="42" customWidth="true" width="25.2818181818182"/>
-    <col min="43" max="43" customWidth="true" width="13.0"/>
-    <col min="44" max="44" customWidth="true" width="23.7181818181818"/>
-    <col min="45" max="45" customWidth="true" width="10.0"/>
-    <col min="46" max="46" customWidth="true" width="13.0"/>
-    <col min="47" max="47" customWidth="true" width="15.5727272727273"/>
-    <col min="48" max="48" customWidth="true" width="21.1454545454545"/>
-    <col min="49" max="49" customWidth="true" width="11.5727272727273"/>
-    <col min="50" max="50" customWidth="true" width="16.7181818181818"/>
-    <col min="51" max="51" customWidth="true" width="14.0"/>
-    <col min="52" max="52" customWidth="true" width="19.4272727272727"/>
-    <col min="53" max="53" customWidth="true" width="18.8545454545455"/>
-    <col min="54" max="54" customWidth="true" width="23.2818181818182"/>
-    <col min="55" max="55" customWidth="true" width="15.5727272727273"/>
-    <col min="56" max="56" customWidth="true" width="14.2818181818182"/>
-    <col min="57" max="57" customWidth="true" width="17.0"/>
-    <col min="58" max="58" customWidth="true" width="16.2818181818182"/>
-    <col min="59" max="59" customWidth="true" width="13.5727272727273"/>
-    <col min="60" max="61" customWidth="true" width="12.7181818181818"/>
-    <col min="62" max="62" customWidth="true" width="21.8545454545455"/>
-    <col min="63" max="63" customWidth="true" width="30.5727272727273"/>
-    <col min="64" max="64" customWidth="true" width="10.0"/>
-    <col min="65" max="65" customWidth="true" width="42.5727272727273"/>
-    <col min="66" max="66" customWidth="true" width="38.1454545454545"/>
-    <col min="67" max="67" customWidth="true" width="19.4272727272727"/>
-    <col min="68" max="68" customWidth="true" width="35.4272727272727"/>
-    <col min="69" max="69" customWidth="true" width="9.57272727272727"/>
+    <col min="1" max="1" width="5.14285714285714" customWidth="1"/>
+    <col min="2" max="3" width="25" customWidth="1"/>
+    <col min="4" max="4" width="79.4285714285714" customWidth="1"/>
+    <col min="5" max="5" width="11.5714285714286" customWidth="1"/>
+    <col min="6" max="6" width="5.14285714285714" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="12.7142857142857" customWidth="1"/>
+    <col min="9" max="9" width="5.85714285714286" customWidth="1"/>
+    <col min="10" max="10" width="6" customWidth="1"/>
+    <col min="11" max="11" width="5.85714285714286" customWidth="1"/>
+    <col min="12" max="12" width="14.2857142857143" customWidth="1"/>
+    <col min="13" max="13" width="9.42857142857143" customWidth="1"/>
+    <col min="14" max="14" width="14.4285714285714" customWidth="1"/>
+    <col min="15" max="15" width="15.5714285714286" customWidth="1"/>
+    <col min="16" max="16" width="14.4285714285714" customWidth="1"/>
+    <col min="17" max="17" width="39.4285714285714" customWidth="1"/>
+    <col min="18" max="18" width="11.7142857142857" customWidth="1"/>
+    <col min="19" max="19" width="11.8571428571429" customWidth="1"/>
+    <col min="20" max="20" width="6.42857142857143" customWidth="1"/>
+    <col min="21" max="22" width="6.57142857142857" customWidth="1"/>
+    <col min="23" max="23" width="37.1428571428571" customWidth="1"/>
+    <col min="24" max="25" width="8" customWidth="1"/>
+    <col min="26" max="26" width="7.71428571428571" customWidth="1"/>
+    <col min="27" max="27" width="6.28571428571429" customWidth="1"/>
+    <col min="28" max="28" width="9.28571428571429" customWidth="1"/>
+    <col min="29" max="29" width="9.71428571428571" customWidth="1"/>
+    <col min="30" max="30" width="12.8571428571429" customWidth="1"/>
+    <col min="31" max="31" width="16.1428571428571" customWidth="1"/>
+    <col min="32" max="32" width="15.4285714285714" customWidth="1"/>
+    <col min="33" max="33" width="24.5714285714286" customWidth="1"/>
+    <col min="34" max="34" width="8.57142857142857" customWidth="1"/>
+    <col min="35" max="35" width="14.7142857142857" customWidth="1"/>
+    <col min="36" max="36" width="18.5714285714286" customWidth="1"/>
+    <col min="37" max="37" width="14.1428571428571" customWidth="1"/>
+    <col min="38" max="38" width="14.7142857142857" customWidth="1"/>
+    <col min="39" max="39" width="17.4285714285714" customWidth="1"/>
+    <col min="40" max="40" width="22" customWidth="1"/>
+    <col min="41" max="41" width="17.5714285714286" customWidth="1"/>
+    <col min="42" max="42" width="25.2857142857143" customWidth="1"/>
+    <col min="43" max="43" width="13" customWidth="1"/>
+    <col min="44" max="44" width="23.7142857142857" customWidth="1"/>
+    <col min="45" max="45" width="10" customWidth="1"/>
+    <col min="46" max="46" width="13" customWidth="1"/>
+    <col min="47" max="47" width="15.5714285714286" customWidth="1"/>
+    <col min="48" max="48" width="21.1428571428571" customWidth="1"/>
+    <col min="49" max="49" width="11.5714285714286" customWidth="1"/>
+    <col min="50" max="50" width="16.7142857142857" customWidth="1"/>
+    <col min="51" max="51" width="14" customWidth="1"/>
+    <col min="52" max="52" width="19.4285714285714" customWidth="1"/>
+    <col min="53" max="53" width="18.8571428571429" customWidth="1"/>
+    <col min="54" max="54" width="23.2857142857143" customWidth="1"/>
+    <col min="55" max="55" width="15.5714285714286" customWidth="1"/>
+    <col min="56" max="56" width="14.2857142857143" customWidth="1"/>
+    <col min="57" max="57" width="17" customWidth="1"/>
+    <col min="58" max="58" width="16.2857142857143" customWidth="1"/>
+    <col min="59" max="59" width="13.5714285714286" customWidth="1"/>
+    <col min="60" max="61" width="12.7142857142857" customWidth="1"/>
+    <col min="62" max="62" width="21.8571428571429" customWidth="1"/>
+    <col min="63" max="63" width="30.5714285714286" customWidth="1"/>
+    <col min="64" max="64" width="10" customWidth="1"/>
+    <col min="65" max="65" width="42.5714285714286" customWidth="1"/>
+    <col min="66" max="66" width="38.1428571428571" customWidth="1"/>
+    <col min="67" max="67" width="19.4285714285714" customWidth="1"/>
+    <col min="68" max="68" width="35.4285714285714" customWidth="1"/>
+    <col min="69" max="69" width="9.57142857142857" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -19031,7 +18852,7 @@
       <c r="BP2" s="27"/>
       <c r="BQ2" s="27"/>
     </row>
-    <row r="3" ht="15.25" spans="1:69">
+    <row r="3" ht="15.75" spans="1:69">
       <c r="A3" s="28" t="s">
         <v>9</v>
       </c>
@@ -19078,7 +18899,7 @@
         <v>25</v>
       </c>
       <c r="P3" s="30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="Q3" s="30" t="s">
         <v>23</v>
@@ -19087,13 +18908,13 @@
         <v>26</v>
       </c>
       <c r="S3" s="28" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="T3" s="28" t="s">
         <v>28</v>
       </c>
       <c r="U3" s="31" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="V3" s="31" t="s">
         <v>30</v>
@@ -19162,7 +18983,7 @@
         <v>51</v>
       </c>
       <c r="AR3" s="33" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AS3" s="28" t="s">
         <v>53</v>
@@ -19240,15 +19061,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.25" spans="1:69">
+    <row r="4" ht="15.75" spans="1:69">
       <c r="A4" s="26">
         <v>1</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C4" s="26" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D4" s="26" t="s">
         <v>76</v>
@@ -19267,7 +19088,7 @@
         <v>400</v>
       </c>
       <c r="I4" s="27" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J4" s="35">
         <v>2</v>
@@ -19404,8 +19225,6 @@
       <c r="AT4" s="35" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" s="0"/>
-      <c r="AV4" s="0"/>
       <c r="AW4" s="35">
         <f>AM4</f>
         <v>4</v>
@@ -19444,11 +19263,11 @@
       <c r="BL4" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="BM4" t="s" s="0">
-        <v>100</v>
-      </c>
-      <c r="BN4" t="s" s="0">
-        <v>100</v>
+      <c r="BM4" t="s">
+        <v>99</v>
+      </c>
+      <c r="BN4" t="s">
+        <v>99</v>
       </c>
       <c r="BO4" s="35">
         <f>ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
@@ -19593,73 +19412,73 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ5"/>
-  <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="8.7047619047619" defaultRowHeight="15" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="5.14545454545455"/>
-    <col min="2" max="3" customWidth="true" width="25.0"/>
-    <col min="4" max="4" customWidth="true" width="79.4272727272727"/>
-    <col min="5" max="5" customWidth="true" width="11.5727272727273"/>
-    <col min="6" max="6" customWidth="true" width="5.14545454545455"/>
-    <col min="7" max="7" customWidth="true" width="11.0"/>
-    <col min="8" max="8" customWidth="true" width="12.7181818181818"/>
-    <col min="9" max="9" customWidth="true" width="5.85454545454545"/>
-    <col min="10" max="10" customWidth="true" width="6.0"/>
-    <col min="11" max="11" customWidth="true" width="5.85454545454545"/>
-    <col min="12" max="12" customWidth="true" width="14.2818181818182"/>
-    <col min="13" max="13" customWidth="true" width="9.42727272727273"/>
-    <col min="14" max="14" customWidth="true" width="14.4272727272727"/>
-    <col min="15" max="15" customWidth="true" width="15.5727272727273"/>
-    <col min="16" max="16" customWidth="true" width="14.4272727272727"/>
-    <col min="17" max="17" customWidth="true" width="39.4272727272727"/>
-    <col min="18" max="18" customWidth="true" width="11.7181818181818"/>
-    <col min="19" max="19" customWidth="true" width="11.8545454545455"/>
-    <col min="20" max="20" customWidth="true" width="6.42727272727273"/>
-    <col min="21" max="22" customWidth="true" width="6.57272727272727"/>
-    <col min="23" max="23" customWidth="true" width="37.1454545454545"/>
-    <col min="24" max="25" customWidth="true" width="8.0"/>
-    <col min="26" max="26" customWidth="true" width="7.71818181818182"/>
-    <col min="27" max="27" customWidth="true" width="6.28181818181818"/>
-    <col min="28" max="28" customWidth="true" width="9.28181818181818"/>
-    <col min="29" max="29" customWidth="true" width="9.71818181818182"/>
-    <col min="30" max="30" customWidth="true" width="12.8545454545455"/>
-    <col min="31" max="31" customWidth="true" width="16.1454545454545"/>
-    <col min="32" max="32" customWidth="true" width="15.4272727272727"/>
-    <col min="33" max="33" customWidth="true" width="24.5727272727273"/>
-    <col min="34" max="34" customWidth="true" width="8.57272727272727"/>
-    <col min="35" max="35" customWidth="true" width="14.7181818181818"/>
-    <col min="36" max="36" customWidth="true" width="18.5727272727273"/>
-    <col min="37" max="37" customWidth="true" width="14.1454545454545"/>
-    <col min="38" max="38" customWidth="true" width="14.7181818181818"/>
-    <col min="39" max="39" customWidth="true" width="17.4272727272727"/>
-    <col min="40" max="40" customWidth="true" width="22.0"/>
-    <col min="41" max="41" customWidth="true" width="17.5727272727273"/>
-    <col min="42" max="42" customWidth="true" width="25.2818181818182"/>
-    <col min="43" max="43" customWidth="true" width="13.0"/>
-    <col min="44" max="44" customWidth="true" width="23.7181818181818"/>
-    <col min="45" max="45" customWidth="true" width="10.0"/>
-    <col min="46" max="46" customWidth="true" width="13.0"/>
-    <col min="47" max="47" customWidth="true" width="15.5727272727273"/>
-    <col min="48" max="48" customWidth="true" width="21.1454545454545"/>
-    <col min="49" max="49" customWidth="true" width="11.5727272727273"/>
-    <col min="50" max="50" customWidth="true" width="16.7181818181818"/>
-    <col min="51" max="51" customWidth="true" width="14.0"/>
-    <col min="52" max="52" customWidth="true" width="19.4272727272727"/>
-    <col min="53" max="53" customWidth="true" width="18.8545454545455"/>
-    <col min="54" max="54" customWidth="true" width="23.2818181818182"/>
-    <col min="55" max="55" customWidth="true" width="15.5727272727273"/>
-    <col min="56" max="56" customWidth="true" width="14.2818181818182"/>
-    <col min="57" max="57" customWidth="true" width="17.0"/>
-    <col min="58" max="58" customWidth="true" width="16.2818181818182"/>
-    <col min="59" max="59" customWidth="true" width="13.5727272727273"/>
-    <col min="60" max="61" customWidth="true" width="12.7181818181818"/>
-    <col min="62" max="62" customWidth="true" width="21.8545454545455"/>
-    <col min="63" max="63" customWidth="true" width="30.5727272727273"/>
-    <col min="64" max="64" customWidth="true" width="10.0"/>
-    <col min="65" max="65" customWidth="true" width="42.5727272727273"/>
-    <col min="66" max="66" customWidth="true" width="38.1454545454545"/>
-    <col min="67" max="67" customWidth="true" width="19.4272727272727"/>
-    <col min="68" max="68" customWidth="true" width="35.4272727272727"/>
-    <col min="69" max="69" customWidth="true" width="9.57272727272727"/>
+    <col min="1" max="1" width="5.14285714285714" customWidth="1"/>
+    <col min="2" max="3" width="25" customWidth="1"/>
+    <col min="4" max="4" width="79.4285714285714" customWidth="1"/>
+    <col min="5" max="5" width="11.5714285714286" customWidth="1"/>
+    <col min="6" max="6" width="5.14285714285714" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="12.7142857142857" customWidth="1"/>
+    <col min="9" max="9" width="5.85714285714286" customWidth="1"/>
+    <col min="10" max="10" width="6" customWidth="1"/>
+    <col min="11" max="11" width="5.85714285714286" customWidth="1"/>
+    <col min="12" max="12" width="14.2857142857143" customWidth="1"/>
+    <col min="13" max="13" width="9.42857142857143" customWidth="1"/>
+    <col min="14" max="14" width="14.4285714285714" customWidth="1"/>
+    <col min="15" max="15" width="15.5714285714286" customWidth="1"/>
+    <col min="16" max="16" width="14.4285714285714" customWidth="1"/>
+    <col min="17" max="17" width="39.4285714285714" customWidth="1"/>
+    <col min="18" max="18" width="11.7142857142857" customWidth="1"/>
+    <col min="19" max="19" width="11.8571428571429" customWidth="1"/>
+    <col min="20" max="20" width="6.42857142857143" customWidth="1"/>
+    <col min="21" max="22" width="6.57142857142857" customWidth="1"/>
+    <col min="23" max="23" width="37.1428571428571" customWidth="1"/>
+    <col min="24" max="25" width="8" customWidth="1"/>
+    <col min="26" max="26" width="7.71428571428571" customWidth="1"/>
+    <col min="27" max="27" width="6.28571428571429" customWidth="1"/>
+    <col min="28" max="28" width="9.28571428571429" customWidth="1"/>
+    <col min="29" max="29" width="9.71428571428571" customWidth="1"/>
+    <col min="30" max="30" width="12.8571428571429" customWidth="1"/>
+    <col min="31" max="31" width="16.1428571428571" customWidth="1"/>
+    <col min="32" max="32" width="15.4285714285714" customWidth="1"/>
+    <col min="33" max="33" width="24.5714285714286" customWidth="1"/>
+    <col min="34" max="34" width="8.57142857142857" customWidth="1"/>
+    <col min="35" max="35" width="14.7142857142857" customWidth="1"/>
+    <col min="36" max="36" width="18.5714285714286" customWidth="1"/>
+    <col min="37" max="37" width="14.1428571428571" customWidth="1"/>
+    <col min="38" max="38" width="14.7142857142857" customWidth="1"/>
+    <col min="39" max="39" width="17.4285714285714" customWidth="1"/>
+    <col min="40" max="40" width="22" customWidth="1"/>
+    <col min="41" max="41" width="17.5714285714286" customWidth="1"/>
+    <col min="42" max="42" width="25.2857142857143" customWidth="1"/>
+    <col min="43" max="43" width="13" customWidth="1"/>
+    <col min="44" max="44" width="23.7142857142857" customWidth="1"/>
+    <col min="45" max="45" width="10" customWidth="1"/>
+    <col min="46" max="46" width="13" customWidth="1"/>
+    <col min="47" max="47" width="15.5714285714286" customWidth="1"/>
+    <col min="48" max="48" width="21.1428571428571" customWidth="1"/>
+    <col min="49" max="49" width="11.5714285714286" customWidth="1"/>
+    <col min="50" max="50" width="16.7142857142857" customWidth="1"/>
+    <col min="51" max="51" width="14" customWidth="1"/>
+    <col min="52" max="52" width="19.4285714285714" customWidth="1"/>
+    <col min="53" max="53" width="18.8571428571429" customWidth="1"/>
+    <col min="54" max="54" width="23.2857142857143" customWidth="1"/>
+    <col min="55" max="55" width="15.5714285714286" customWidth="1"/>
+    <col min="56" max="56" width="14.2857142857143" customWidth="1"/>
+    <col min="57" max="57" width="17" customWidth="1"/>
+    <col min="58" max="58" width="16.2857142857143" customWidth="1"/>
+    <col min="59" max="59" width="13.5714285714286" customWidth="1"/>
+    <col min="60" max="61" width="12.7142857142857" customWidth="1"/>
+    <col min="62" max="62" width="21.8571428571429" customWidth="1"/>
+    <col min="63" max="63" width="30.5714285714286" customWidth="1"/>
+    <col min="64" max="64" width="10" customWidth="1"/>
+    <col min="65" max="65" width="42.5714285714286" customWidth="1"/>
+    <col min="66" max="66" width="38.1428571428571" customWidth="1"/>
+    <col min="67" max="67" width="19.4285714285714" customWidth="1"/>
+    <col min="68" max="68" width="35.4285714285714" customWidth="1"/>
+    <col min="69" max="69" width="9.57142857142857" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -19830,7 +19649,7 @@
       <c r="BP2" s="27"/>
       <c r="BQ2" s="27"/>
     </row>
-    <row r="3" ht="15.25" spans="1:69">
+    <row r="3" ht="15.75" spans="1:69">
       <c r="A3" s="28" t="s">
         <v>9</v>
       </c>
@@ -19877,7 +19696,7 @@
         <v>25</v>
       </c>
       <c r="P3" s="30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="Q3" s="30" t="s">
         <v>23</v>
@@ -19886,13 +19705,13 @@
         <v>26</v>
       </c>
       <c r="S3" s="28" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="T3" s="28" t="s">
         <v>28</v>
       </c>
       <c r="U3" s="31" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="V3" s="31" t="s">
         <v>30</v>
@@ -19961,7 +19780,7 @@
         <v>51</v>
       </c>
       <c r="AR3" s="33" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AS3" s="28" t="s">
         <v>53</v>
@@ -20039,15 +19858,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.25" spans="1:69">
+    <row r="4" ht="15.75" spans="1:69">
       <c r="A4" s="26">
         <v>1</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C4" s="26" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D4" s="26" t="s">
         <v>76</v>
@@ -20066,7 +19885,7 @@
         <v>400</v>
       </c>
       <c r="I4" s="27" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J4" s="35">
         <v>2</v>
@@ -20203,8 +20022,6 @@
       <c r="AT4" s="35" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" s="0"/>
-      <c r="AV4" s="0"/>
       <c r="AW4" s="35">
         <f>AM4</f>
         <v>4</v>
@@ -20243,11 +20060,11 @@
       <c r="BL4" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="BM4" t="s" s="0">
-        <v>100</v>
-      </c>
-      <c r="BN4" t="s" s="0">
-        <v>100</v>
+      <c r="BM4" t="s">
+        <v>99</v>
+      </c>
+      <c r="BN4" t="s">
+        <v>99</v>
       </c>
       <c r="BO4" s="35">
         <f>ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
@@ -20392,73 +20209,73 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ5"/>
-  <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="8.7047619047619" defaultRowHeight="15" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="5.14545454545455"/>
-    <col min="2" max="3" customWidth="true" width="25.2818181818182"/>
-    <col min="4" max="4" customWidth="true" width="79.4272727272727"/>
-    <col min="5" max="5" customWidth="true" width="11.5727272727273"/>
-    <col min="6" max="6" customWidth="true" width="5.14545454545455"/>
-    <col min="7" max="7" customWidth="true" width="11.0"/>
-    <col min="8" max="8" customWidth="true" width="12.7181818181818"/>
-    <col min="9" max="9" customWidth="true" width="5.85454545454545"/>
-    <col min="10" max="10" customWidth="true" width="6.0"/>
-    <col min="11" max="11" customWidth="true" width="5.85454545454545"/>
-    <col min="12" max="12" customWidth="true" width="14.2818181818182"/>
-    <col min="13" max="13" customWidth="true" width="9.42727272727273"/>
-    <col min="14" max="14" customWidth="true" width="14.4272727272727"/>
-    <col min="15" max="15" customWidth="true" width="15.5727272727273"/>
-    <col min="16" max="16" customWidth="true" width="14.4272727272727"/>
-    <col min="17" max="17" customWidth="true" width="39.4272727272727"/>
-    <col min="18" max="18" customWidth="true" width="11.7181818181818"/>
-    <col min="19" max="19" customWidth="true" width="11.8545454545455"/>
-    <col min="20" max="20" customWidth="true" width="6.42727272727273"/>
-    <col min="21" max="22" customWidth="true" width="6.57272727272727"/>
-    <col min="23" max="23" customWidth="true" width="37.1454545454545"/>
-    <col min="24" max="25" customWidth="true" width="8.0"/>
-    <col min="26" max="26" customWidth="true" width="7.71818181818182"/>
-    <col min="27" max="27" customWidth="true" width="6.28181818181818"/>
-    <col min="28" max="28" customWidth="true" width="9.28181818181818"/>
-    <col min="29" max="29" customWidth="true" width="9.71818181818182"/>
-    <col min="30" max="30" customWidth="true" width="12.8545454545455"/>
-    <col min="31" max="31" customWidth="true" width="16.1454545454545"/>
-    <col min="32" max="32" customWidth="true" width="15.4272727272727"/>
-    <col min="33" max="33" customWidth="true" width="24.5727272727273"/>
-    <col min="34" max="34" customWidth="true" width="8.57272727272727"/>
-    <col min="35" max="35" customWidth="true" width="14.7181818181818"/>
-    <col min="36" max="36" customWidth="true" width="18.5727272727273"/>
-    <col min="37" max="37" customWidth="true" width="14.1454545454545"/>
-    <col min="38" max="38" customWidth="true" width="14.7181818181818"/>
-    <col min="39" max="39" customWidth="true" width="17.4272727272727"/>
-    <col min="40" max="40" customWidth="true" width="22.0"/>
-    <col min="41" max="41" customWidth="true" width="17.5727272727273"/>
-    <col min="42" max="42" customWidth="true" width="25.2818181818182"/>
-    <col min="43" max="43" customWidth="true" width="13.0"/>
-    <col min="44" max="44" customWidth="true" width="23.7181818181818"/>
-    <col min="45" max="45" customWidth="true" width="10.0"/>
-    <col min="46" max="46" customWidth="true" width="13.0"/>
-    <col min="47" max="47" customWidth="true" width="15.5727272727273"/>
-    <col min="48" max="48" customWidth="true" width="21.1454545454545"/>
-    <col min="49" max="49" customWidth="true" width="11.5727272727273"/>
-    <col min="50" max="50" customWidth="true" width="16.7181818181818"/>
-    <col min="51" max="51" customWidth="true" width="14.0"/>
-    <col min="52" max="52" customWidth="true" width="19.4272727272727"/>
-    <col min="53" max="53" customWidth="true" width="18.8545454545455"/>
-    <col min="54" max="54" customWidth="true" width="23.2818181818182"/>
-    <col min="55" max="55" customWidth="true" width="15.5727272727273"/>
-    <col min="56" max="56" customWidth="true" width="14.2818181818182"/>
-    <col min="57" max="57" customWidth="true" width="17.0"/>
-    <col min="58" max="58" customWidth="true" width="16.2818181818182"/>
-    <col min="59" max="59" customWidth="true" width="13.5727272727273"/>
-    <col min="60" max="61" customWidth="true" width="12.7181818181818"/>
-    <col min="62" max="62" customWidth="true" width="21.8545454545455"/>
-    <col min="63" max="63" customWidth="true" width="30.5727272727273"/>
-    <col min="64" max="64" customWidth="true" width="10.0"/>
-    <col min="65" max="65" customWidth="true" width="42.5727272727273"/>
-    <col min="66" max="66" customWidth="true" width="38.1454545454545"/>
-    <col min="67" max="67" customWidth="true" width="19.4272727272727"/>
-    <col min="68" max="68" customWidth="true" width="35.4272727272727"/>
-    <col min="69" max="69" customWidth="true" width="9.57272727272727"/>
+    <col min="1" max="1" width="5.14285714285714" customWidth="1"/>
+    <col min="2" max="3" width="25.2857142857143" customWidth="1"/>
+    <col min="4" max="4" width="79.4285714285714" customWidth="1"/>
+    <col min="5" max="5" width="11.5714285714286" customWidth="1"/>
+    <col min="6" max="6" width="5.14285714285714" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="12.7142857142857" customWidth="1"/>
+    <col min="9" max="9" width="5.85714285714286" customWidth="1"/>
+    <col min="10" max="10" width="6" customWidth="1"/>
+    <col min="11" max="11" width="5.85714285714286" customWidth="1"/>
+    <col min="12" max="12" width="14.2857142857143" customWidth="1"/>
+    <col min="13" max="13" width="9.42857142857143" customWidth="1"/>
+    <col min="14" max="14" width="14.4285714285714" customWidth="1"/>
+    <col min="15" max="15" width="15.5714285714286" customWidth="1"/>
+    <col min="16" max="16" width="14.4285714285714" customWidth="1"/>
+    <col min="17" max="17" width="39.4285714285714" customWidth="1"/>
+    <col min="18" max="18" width="11.7142857142857" customWidth="1"/>
+    <col min="19" max="19" width="11.8571428571429" customWidth="1"/>
+    <col min="20" max="20" width="6.42857142857143" customWidth="1"/>
+    <col min="21" max="22" width="6.57142857142857" customWidth="1"/>
+    <col min="23" max="23" width="37.1428571428571" customWidth="1"/>
+    <col min="24" max="25" width="8" customWidth="1"/>
+    <col min="26" max="26" width="7.71428571428571" customWidth="1"/>
+    <col min="27" max="27" width="6.28571428571429" customWidth="1"/>
+    <col min="28" max="28" width="9.28571428571429" customWidth="1"/>
+    <col min="29" max="29" width="9.71428571428571" customWidth="1"/>
+    <col min="30" max="30" width="12.8571428571429" customWidth="1"/>
+    <col min="31" max="31" width="16.1428571428571" customWidth="1"/>
+    <col min="32" max="32" width="15.4285714285714" customWidth="1"/>
+    <col min="33" max="33" width="24.5714285714286" customWidth="1"/>
+    <col min="34" max="34" width="8.57142857142857" customWidth="1"/>
+    <col min="35" max="35" width="14.7142857142857" customWidth="1"/>
+    <col min="36" max="36" width="18.5714285714286" customWidth="1"/>
+    <col min="37" max="37" width="14.1428571428571" customWidth="1"/>
+    <col min="38" max="38" width="14.7142857142857" customWidth="1"/>
+    <col min="39" max="39" width="17.4285714285714" customWidth="1"/>
+    <col min="40" max="40" width="22" customWidth="1"/>
+    <col min="41" max="41" width="17.5714285714286" customWidth="1"/>
+    <col min="42" max="42" width="25.2857142857143" customWidth="1"/>
+    <col min="43" max="43" width="13" customWidth="1"/>
+    <col min="44" max="44" width="23.7142857142857" customWidth="1"/>
+    <col min="45" max="45" width="10" customWidth="1"/>
+    <col min="46" max="46" width="13" customWidth="1"/>
+    <col min="47" max="47" width="15.5714285714286" customWidth="1"/>
+    <col min="48" max="48" width="21.1428571428571" customWidth="1"/>
+    <col min="49" max="49" width="11.5714285714286" customWidth="1"/>
+    <col min="50" max="50" width="16.7142857142857" customWidth="1"/>
+    <col min="51" max="51" width="14" customWidth="1"/>
+    <col min="52" max="52" width="19.4285714285714" customWidth="1"/>
+    <col min="53" max="53" width="18.8571428571429" customWidth="1"/>
+    <col min="54" max="54" width="23.2857142857143" customWidth="1"/>
+    <col min="55" max="55" width="15.5714285714286" customWidth="1"/>
+    <col min="56" max="56" width="14.2857142857143" customWidth="1"/>
+    <col min="57" max="57" width="17" customWidth="1"/>
+    <col min="58" max="58" width="16.2857142857143" customWidth="1"/>
+    <col min="59" max="59" width="13.5714285714286" customWidth="1"/>
+    <col min="60" max="61" width="12.7142857142857" customWidth="1"/>
+    <col min="62" max="62" width="21.8571428571429" customWidth="1"/>
+    <col min="63" max="63" width="30.5714285714286" customWidth="1"/>
+    <col min="64" max="64" width="10" customWidth="1"/>
+    <col min="65" max="65" width="42.5714285714286" customWidth="1"/>
+    <col min="66" max="66" width="38.1428571428571" customWidth="1"/>
+    <col min="67" max="67" width="19.4285714285714" customWidth="1"/>
+    <col min="68" max="68" width="35.4285714285714" customWidth="1"/>
+    <col min="69" max="69" width="9.57142857142857" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -20629,7 +20446,7 @@
       <c r="BP2" s="27"/>
       <c r="BQ2" s="27"/>
     </row>
-    <row r="3" ht="15.25" spans="1:69">
+    <row r="3" ht="15.75" spans="1:69">
       <c r="A3" s="28" t="s">
         <v>9</v>
       </c>
@@ -20676,7 +20493,7 @@
         <v>25</v>
       </c>
       <c r="P3" s="30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="Q3" s="30" t="s">
         <v>23</v>
@@ -20685,13 +20502,13 @@
         <v>26</v>
       </c>
       <c r="S3" s="28" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="T3" s="28" t="s">
         <v>28</v>
       </c>
       <c r="U3" s="31" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="V3" s="31" t="s">
         <v>30</v>
@@ -20760,7 +20577,7 @@
         <v>51</v>
       </c>
       <c r="AR3" s="33" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AS3" s="28" t="s">
         <v>53</v>
@@ -20838,15 +20655,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.25" spans="1:69">
+    <row r="4" ht="15.75" spans="1:69">
       <c r="A4" s="26">
         <v>1</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C4" s="26" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D4" s="26" t="s">
         <v>76</v>
@@ -21002,11 +20819,11 @@
       <c r="AT4" s="35" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" t="s" s="0">
-        <v>181</v>
-      </c>
-      <c r="AV4" t="s" s="0">
-        <v>182</v>
+      <c r="AU4" t="s">
+        <v>104</v>
+      </c>
+      <c r="AV4" t="s">
+        <v>105</v>
       </c>
       <c r="AW4" s="35">
         <f>AM4</f>
@@ -21046,11 +20863,11 @@
       <c r="BL4" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="BM4" t="s" s="0">
-        <v>184</v>
-      </c>
-      <c r="BN4" t="s" s="0">
-        <v>183</v>
+      <c r="BM4" t="s">
+        <v>106</v>
+      </c>
+      <c r="BN4" t="s">
+        <v>107</v>
       </c>
       <c r="BO4" s="35">
         <f>ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
@@ -21207,73 +21024,73 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ5"/>
-  <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="8.7047619047619" defaultRowHeight="15" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="5.14545454545455"/>
-    <col min="2" max="3" customWidth="true" width="25.2818181818182"/>
-    <col min="4" max="4" customWidth="true" width="79.4272727272727"/>
-    <col min="5" max="5" customWidth="true" width="11.5727272727273"/>
-    <col min="6" max="6" customWidth="true" width="5.14545454545455"/>
-    <col min="7" max="7" customWidth="true" width="11.0"/>
-    <col min="8" max="8" customWidth="true" width="12.7181818181818"/>
-    <col min="9" max="9" customWidth="true" width="5.85454545454545"/>
-    <col min="10" max="10" customWidth="true" width="6.0"/>
-    <col min="11" max="11" customWidth="true" width="5.85454545454545"/>
-    <col min="12" max="12" customWidth="true" width="14.2818181818182"/>
-    <col min="13" max="13" customWidth="true" width="9.42727272727273"/>
-    <col min="14" max="14" customWidth="true" width="14.4272727272727"/>
-    <col min="15" max="15" customWidth="true" width="15.5727272727273"/>
-    <col min="16" max="16" customWidth="true" width="14.4272727272727"/>
-    <col min="17" max="17" customWidth="true" width="39.4272727272727"/>
-    <col min="18" max="18" customWidth="true" width="11.7181818181818"/>
-    <col min="19" max="19" customWidth="true" width="11.8545454545455"/>
-    <col min="20" max="20" customWidth="true" width="6.42727272727273"/>
-    <col min="21" max="22" customWidth="true" width="6.57272727272727"/>
-    <col min="23" max="23" customWidth="true" width="37.1454545454545"/>
-    <col min="24" max="25" customWidth="true" width="8.0"/>
-    <col min="26" max="26" customWidth="true" width="7.71818181818182"/>
-    <col min="27" max="27" customWidth="true" width="6.28181818181818"/>
-    <col min="28" max="28" customWidth="true" width="9.28181818181818"/>
-    <col min="29" max="29" customWidth="true" width="9.71818181818182"/>
-    <col min="30" max="30" customWidth="true" width="12.8545454545455"/>
-    <col min="31" max="31" customWidth="true" width="16.1454545454545"/>
-    <col min="32" max="32" customWidth="true" width="15.4272727272727"/>
-    <col min="33" max="33" customWidth="true" width="24.5727272727273"/>
-    <col min="34" max="34" customWidth="true" width="8.57272727272727"/>
-    <col min="35" max="35" customWidth="true" width="14.7181818181818"/>
-    <col min="36" max="36" customWidth="true" width="18.5727272727273"/>
-    <col min="37" max="37" customWidth="true" width="14.1454545454545"/>
-    <col min="38" max="38" customWidth="true" width="14.7181818181818"/>
-    <col min="39" max="39" customWidth="true" width="17.4272727272727"/>
-    <col min="40" max="40" customWidth="true" width="22.0"/>
-    <col min="41" max="41" customWidth="true" width="17.5727272727273"/>
-    <col min="42" max="42" customWidth="true" width="25.2818181818182"/>
-    <col min="43" max="43" customWidth="true" width="13.0"/>
-    <col min="44" max="44" customWidth="true" width="23.7181818181818"/>
-    <col min="45" max="45" customWidth="true" width="10.0"/>
-    <col min="46" max="46" customWidth="true" width="13.0"/>
-    <col min="47" max="47" customWidth="true" width="15.5727272727273"/>
-    <col min="48" max="48" customWidth="true" width="21.1454545454545"/>
-    <col min="49" max="49" customWidth="true" width="11.5727272727273"/>
-    <col min="50" max="50" customWidth="true" width="16.7181818181818"/>
-    <col min="51" max="51" customWidth="true" width="14.0"/>
-    <col min="52" max="52" customWidth="true" width="19.4272727272727"/>
-    <col min="53" max="53" customWidth="true" width="18.8545454545455"/>
-    <col min="54" max="54" customWidth="true" width="23.2818181818182"/>
-    <col min="55" max="55" customWidth="true" width="15.5727272727273"/>
-    <col min="56" max="56" customWidth="true" width="14.2818181818182"/>
-    <col min="57" max="57" customWidth="true" width="17.0"/>
-    <col min="58" max="58" customWidth="true" width="16.2818181818182"/>
-    <col min="59" max="59" customWidth="true" width="13.5727272727273"/>
-    <col min="60" max="61" customWidth="true" width="12.7181818181818"/>
-    <col min="62" max="62" customWidth="true" width="21.8545454545455"/>
-    <col min="63" max="63" customWidth="true" width="30.5727272727273"/>
-    <col min="64" max="64" customWidth="true" width="10.0"/>
-    <col min="65" max="65" customWidth="true" width="42.5727272727273"/>
-    <col min="66" max="66" customWidth="true" width="38.1454545454545"/>
-    <col min="67" max="67" customWidth="true" width="19.4272727272727"/>
-    <col min="68" max="68" customWidth="true" width="35.4272727272727"/>
-    <col min="69" max="69" customWidth="true" width="9.57272727272727"/>
+    <col min="1" max="1" width="5.14285714285714" customWidth="1"/>
+    <col min="2" max="3" width="25.2857142857143" customWidth="1"/>
+    <col min="4" max="4" width="79.4285714285714" customWidth="1"/>
+    <col min="5" max="5" width="11.5714285714286" customWidth="1"/>
+    <col min="6" max="6" width="5.14285714285714" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="12.7142857142857" customWidth="1"/>
+    <col min="9" max="9" width="5.85714285714286" customWidth="1"/>
+    <col min="10" max="10" width="6" customWidth="1"/>
+    <col min="11" max="11" width="5.85714285714286" customWidth="1"/>
+    <col min="12" max="12" width="14.2857142857143" customWidth="1"/>
+    <col min="13" max="13" width="9.42857142857143" customWidth="1"/>
+    <col min="14" max="14" width="14.4285714285714" customWidth="1"/>
+    <col min="15" max="15" width="15.5714285714286" customWidth="1"/>
+    <col min="16" max="16" width="14.4285714285714" customWidth="1"/>
+    <col min="17" max="17" width="39.4285714285714" customWidth="1"/>
+    <col min="18" max="18" width="11.7142857142857" customWidth="1"/>
+    <col min="19" max="19" width="11.8571428571429" customWidth="1"/>
+    <col min="20" max="20" width="6.42857142857143" customWidth="1"/>
+    <col min="21" max="22" width="6.57142857142857" customWidth="1"/>
+    <col min="23" max="23" width="37.1428571428571" customWidth="1"/>
+    <col min="24" max="25" width="8" customWidth="1"/>
+    <col min="26" max="26" width="7.71428571428571" customWidth="1"/>
+    <col min="27" max="27" width="6.28571428571429" customWidth="1"/>
+    <col min="28" max="28" width="9.28571428571429" customWidth="1"/>
+    <col min="29" max="29" width="9.71428571428571" customWidth="1"/>
+    <col min="30" max="30" width="12.8571428571429" customWidth="1"/>
+    <col min="31" max="31" width="16.1428571428571" customWidth="1"/>
+    <col min="32" max="32" width="15.4285714285714" customWidth="1"/>
+    <col min="33" max="33" width="24.5714285714286" customWidth="1"/>
+    <col min="34" max="34" width="8.57142857142857" customWidth="1"/>
+    <col min="35" max="35" width="14.7142857142857" customWidth="1"/>
+    <col min="36" max="36" width="18.5714285714286" customWidth="1"/>
+    <col min="37" max="37" width="14.1428571428571" customWidth="1"/>
+    <col min="38" max="38" width="14.7142857142857" customWidth="1"/>
+    <col min="39" max="39" width="17.4285714285714" customWidth="1"/>
+    <col min="40" max="40" width="22" customWidth="1"/>
+    <col min="41" max="41" width="17.5714285714286" customWidth="1"/>
+    <col min="42" max="42" width="25.2857142857143" customWidth="1"/>
+    <col min="43" max="43" width="13" customWidth="1"/>
+    <col min="44" max="44" width="23.7142857142857" customWidth="1"/>
+    <col min="45" max="45" width="10" customWidth="1"/>
+    <col min="46" max="46" width="13" customWidth="1"/>
+    <col min="47" max="47" width="15.5714285714286" customWidth="1"/>
+    <col min="48" max="48" width="21.1428571428571" customWidth="1"/>
+    <col min="49" max="49" width="11.5714285714286" customWidth="1"/>
+    <col min="50" max="50" width="16.7142857142857" customWidth="1"/>
+    <col min="51" max="51" width="14" customWidth="1"/>
+    <col min="52" max="52" width="19.4285714285714" customWidth="1"/>
+    <col min="53" max="53" width="18.8571428571429" customWidth="1"/>
+    <col min="54" max="54" width="23.2857142857143" customWidth="1"/>
+    <col min="55" max="55" width="15.5714285714286" customWidth="1"/>
+    <col min="56" max="56" width="14.2857142857143" customWidth="1"/>
+    <col min="57" max="57" width="17" customWidth="1"/>
+    <col min="58" max="58" width="16.2857142857143" customWidth="1"/>
+    <col min="59" max="59" width="13.5714285714286" customWidth="1"/>
+    <col min="60" max="61" width="12.7142857142857" customWidth="1"/>
+    <col min="62" max="62" width="21.8571428571429" customWidth="1"/>
+    <col min="63" max="63" width="30.5714285714286" customWidth="1"/>
+    <col min="64" max="64" width="10" customWidth="1"/>
+    <col min="65" max="65" width="42.5714285714286" customWidth="1"/>
+    <col min="66" max="66" width="38.1428571428571" customWidth="1"/>
+    <col min="67" max="67" width="19.4285714285714" customWidth="1"/>
+    <col min="68" max="68" width="35.4285714285714" customWidth="1"/>
+    <col min="69" max="69" width="9.57142857142857" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -21444,7 +21261,7 @@
       <c r="BP2" s="27"/>
       <c r="BQ2" s="27"/>
     </row>
-    <row r="3" ht="15.25" spans="1:69">
+    <row r="3" ht="15.75" spans="1:69">
       <c r="A3" s="28" t="s">
         <v>9</v>
       </c>
@@ -21491,7 +21308,7 @@
         <v>25</v>
       </c>
       <c r="P3" s="30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="Q3" s="30" t="s">
         <v>23</v>
@@ -21500,13 +21317,13 @@
         <v>26</v>
       </c>
       <c r="S3" s="28" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="T3" s="28" t="s">
         <v>28</v>
       </c>
       <c r="U3" s="31" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="V3" s="31" t="s">
         <v>30</v>
@@ -21575,7 +21392,7 @@
         <v>51</v>
       </c>
       <c r="AR3" s="33" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AS3" s="28" t="s">
         <v>53</v>
@@ -21653,15 +21470,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.25" spans="1:69">
+    <row r="4" ht="15.75" spans="1:69">
       <c r="A4" s="26">
         <v>1</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C4" s="26" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D4" s="26" t="s">
         <v>76</v>
@@ -21817,11 +21634,11 @@
       <c r="AT4" s="35" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" t="s" s="0">
-        <v>173</v>
-      </c>
-      <c r="AV4" t="s" s="0">
-        <v>185</v>
+      <c r="AU4" t="s">
+        <v>79</v>
+      </c>
+      <c r="AV4" t="s">
+        <v>109</v>
       </c>
       <c r="AW4" s="35">
         <f>AM4</f>
@@ -21861,11 +21678,11 @@
       <c r="BL4" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="BM4" t="s" s="0">
-        <v>187</v>
-      </c>
-      <c r="BN4" t="s" s="0">
-        <v>186</v>
+      <c r="BM4" t="s">
+        <v>110</v>
+      </c>
+      <c r="BN4" t="s">
+        <v>111</v>
       </c>
       <c r="BO4" s="35">
         <f>ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
@@ -22010,73 +21827,73 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ5"/>
-  <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="8.7047619047619" defaultRowHeight="15" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="5.14545454545455"/>
-    <col min="2" max="3" customWidth="true" width="25.5727272727273"/>
-    <col min="4" max="4" customWidth="true" width="79.4272727272727"/>
-    <col min="5" max="5" customWidth="true" width="11.5727272727273"/>
-    <col min="6" max="6" customWidth="true" width="5.14545454545455"/>
-    <col min="7" max="7" customWidth="true" width="11.0"/>
-    <col min="8" max="8" customWidth="true" width="12.7181818181818"/>
-    <col min="9" max="9" customWidth="true" width="5.85454545454545"/>
-    <col min="10" max="10" customWidth="true" width="6.0"/>
-    <col min="11" max="11" customWidth="true" width="5.85454545454545"/>
-    <col min="12" max="12" customWidth="true" width="14.2818181818182"/>
-    <col min="13" max="13" customWidth="true" width="9.42727272727273"/>
-    <col min="14" max="14" customWidth="true" width="14.4272727272727"/>
-    <col min="15" max="15" customWidth="true" width="15.5727272727273"/>
-    <col min="16" max="16" customWidth="true" width="14.4272727272727"/>
-    <col min="17" max="17" customWidth="true" width="39.4272727272727"/>
-    <col min="18" max="18" customWidth="true" width="11.7181818181818"/>
-    <col min="19" max="19" customWidth="true" width="11.8545454545455"/>
-    <col min="20" max="20" customWidth="true" width="6.42727272727273"/>
-    <col min="21" max="22" customWidth="true" width="6.57272727272727"/>
-    <col min="23" max="23" customWidth="true" width="37.1454545454545"/>
-    <col min="24" max="25" customWidth="true" width="8.0"/>
-    <col min="26" max="26" customWidth="true" width="7.71818181818182"/>
-    <col min="27" max="27" customWidth="true" width="6.28181818181818"/>
-    <col min="28" max="28" customWidth="true" width="9.28181818181818"/>
-    <col min="29" max="29" customWidth="true" width="9.71818181818182"/>
-    <col min="30" max="30" customWidth="true" width="12.8545454545455"/>
-    <col min="31" max="31" customWidth="true" width="16.1454545454545"/>
-    <col min="32" max="32" customWidth="true" width="15.4272727272727"/>
-    <col min="33" max="33" customWidth="true" width="24.5727272727273"/>
-    <col min="34" max="34" customWidth="true" width="8.57272727272727"/>
-    <col min="35" max="35" customWidth="true" width="14.7181818181818"/>
-    <col min="36" max="36" customWidth="true" width="18.5727272727273"/>
-    <col min="37" max="37" customWidth="true" width="14.1454545454545"/>
-    <col min="38" max="38" customWidth="true" width="14.7181818181818"/>
-    <col min="39" max="39" customWidth="true" width="17.4272727272727"/>
-    <col min="40" max="40" customWidth="true" width="22.0"/>
-    <col min="41" max="41" customWidth="true" width="17.5727272727273"/>
-    <col min="42" max="42" customWidth="true" width="25.2818181818182"/>
-    <col min="43" max="43" customWidth="true" width="13.0"/>
-    <col min="44" max="44" customWidth="true" width="23.7181818181818"/>
-    <col min="45" max="45" customWidth="true" width="10.0"/>
-    <col min="46" max="46" customWidth="true" width="13.0"/>
-    <col min="47" max="47" customWidth="true" width="15.5727272727273"/>
-    <col min="48" max="48" customWidth="true" width="21.1454545454545"/>
-    <col min="49" max="49" customWidth="true" width="11.5727272727273"/>
-    <col min="50" max="50" customWidth="true" width="16.7181818181818"/>
-    <col min="51" max="51" customWidth="true" width="14.0"/>
-    <col min="52" max="52" customWidth="true" width="19.4272727272727"/>
-    <col min="53" max="53" customWidth="true" width="18.8545454545455"/>
-    <col min="54" max="54" customWidth="true" width="23.2818181818182"/>
-    <col min="55" max="55" customWidth="true" width="15.5727272727273"/>
-    <col min="56" max="56" customWidth="true" width="14.2818181818182"/>
-    <col min="57" max="57" customWidth="true" width="17.0"/>
-    <col min="58" max="58" customWidth="true" width="16.2818181818182"/>
-    <col min="59" max="59" customWidth="true" width="13.5727272727273"/>
-    <col min="60" max="61" customWidth="true" width="12.7181818181818"/>
-    <col min="62" max="62" customWidth="true" width="21.8545454545455"/>
-    <col min="63" max="63" customWidth="true" width="30.5727272727273"/>
-    <col min="64" max="64" customWidth="true" width="10.0"/>
-    <col min="65" max="65" customWidth="true" width="42.5727272727273"/>
-    <col min="66" max="66" customWidth="true" width="38.1454545454545"/>
-    <col min="67" max="67" customWidth="true" width="19.4272727272727"/>
-    <col min="68" max="68" customWidth="true" width="35.4272727272727"/>
-    <col min="69" max="69" customWidth="true" width="9.57272727272727"/>
+    <col min="1" max="1" width="5.14285714285714" customWidth="1"/>
+    <col min="2" max="3" width="25.5714285714286" customWidth="1"/>
+    <col min="4" max="4" width="79.4285714285714" customWidth="1"/>
+    <col min="5" max="5" width="11.5714285714286" customWidth="1"/>
+    <col min="6" max="6" width="5.14285714285714" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="12.7142857142857" customWidth="1"/>
+    <col min="9" max="9" width="5.85714285714286" customWidth="1"/>
+    <col min="10" max="10" width="6" customWidth="1"/>
+    <col min="11" max="11" width="5.85714285714286" customWidth="1"/>
+    <col min="12" max="12" width="14.2857142857143" customWidth="1"/>
+    <col min="13" max="13" width="9.42857142857143" customWidth="1"/>
+    <col min="14" max="14" width="14.4285714285714" customWidth="1"/>
+    <col min="15" max="15" width="15.5714285714286" customWidth="1"/>
+    <col min="16" max="16" width="14.4285714285714" customWidth="1"/>
+    <col min="17" max="17" width="39.4285714285714" customWidth="1"/>
+    <col min="18" max="18" width="11.7142857142857" customWidth="1"/>
+    <col min="19" max="19" width="11.8571428571429" customWidth="1"/>
+    <col min="20" max="20" width="6.42857142857143" customWidth="1"/>
+    <col min="21" max="22" width="6.57142857142857" customWidth="1"/>
+    <col min="23" max="23" width="37.1428571428571" customWidth="1"/>
+    <col min="24" max="25" width="8" customWidth="1"/>
+    <col min="26" max="26" width="7.71428571428571" customWidth="1"/>
+    <col min="27" max="27" width="6.28571428571429" customWidth="1"/>
+    <col min="28" max="28" width="9.28571428571429" customWidth="1"/>
+    <col min="29" max="29" width="9.71428571428571" customWidth="1"/>
+    <col min="30" max="30" width="12.8571428571429" customWidth="1"/>
+    <col min="31" max="31" width="16.1428571428571" customWidth="1"/>
+    <col min="32" max="32" width="15.4285714285714" customWidth="1"/>
+    <col min="33" max="33" width="24.5714285714286" customWidth="1"/>
+    <col min="34" max="34" width="8.57142857142857" customWidth="1"/>
+    <col min="35" max="35" width="14.7142857142857" customWidth="1"/>
+    <col min="36" max="36" width="18.5714285714286" customWidth="1"/>
+    <col min="37" max="37" width="14.1428571428571" customWidth="1"/>
+    <col min="38" max="38" width="14.7142857142857" customWidth="1"/>
+    <col min="39" max="39" width="17.4285714285714" customWidth="1"/>
+    <col min="40" max="40" width="22" customWidth="1"/>
+    <col min="41" max="41" width="17.5714285714286" customWidth="1"/>
+    <col min="42" max="42" width="25.2857142857143" customWidth="1"/>
+    <col min="43" max="43" width="13" customWidth="1"/>
+    <col min="44" max="44" width="23.7142857142857" customWidth="1"/>
+    <col min="45" max="45" width="10" customWidth="1"/>
+    <col min="46" max="46" width="13" customWidth="1"/>
+    <col min="47" max="47" width="15.5714285714286" customWidth="1"/>
+    <col min="48" max="48" width="21.1428571428571" customWidth="1"/>
+    <col min="49" max="49" width="11.5714285714286" customWidth="1"/>
+    <col min="50" max="50" width="16.7142857142857" customWidth="1"/>
+    <col min="51" max="51" width="14" customWidth="1"/>
+    <col min="52" max="52" width="19.4285714285714" customWidth="1"/>
+    <col min="53" max="53" width="18.8571428571429" customWidth="1"/>
+    <col min="54" max="54" width="23.2857142857143" customWidth="1"/>
+    <col min="55" max="55" width="15.5714285714286" customWidth="1"/>
+    <col min="56" max="56" width="14.2857142857143" customWidth="1"/>
+    <col min="57" max="57" width="17" customWidth="1"/>
+    <col min="58" max="58" width="16.2857142857143" customWidth="1"/>
+    <col min="59" max="59" width="13.5714285714286" customWidth="1"/>
+    <col min="60" max="61" width="12.7142857142857" customWidth="1"/>
+    <col min="62" max="62" width="21.8571428571429" customWidth="1"/>
+    <col min="63" max="63" width="30.5714285714286" customWidth="1"/>
+    <col min="64" max="64" width="10" customWidth="1"/>
+    <col min="65" max="65" width="42.5714285714286" customWidth="1"/>
+    <col min="66" max="66" width="38.1428571428571" customWidth="1"/>
+    <col min="67" max="67" width="19.4285714285714" customWidth="1"/>
+    <col min="68" max="68" width="35.4285714285714" customWidth="1"/>
+    <col min="69" max="69" width="9.57142857142857" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -22247,7 +22064,7 @@
       <c r="BP2" s="27"/>
       <c r="BQ2" s="27"/>
     </row>
-    <row r="3" ht="15.25" spans="1:69">
+    <row r="3" ht="15.75" spans="1:69">
       <c r="A3" s="28" t="s">
         <v>9</v>
       </c>
@@ -22294,7 +22111,7 @@
         <v>25</v>
       </c>
       <c r="P3" s="30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="Q3" s="30" t="s">
         <v>23</v>
@@ -22303,13 +22120,13 @@
         <v>26</v>
       </c>
       <c r="S3" s="28" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="T3" s="28" t="s">
         <v>28</v>
       </c>
       <c r="U3" s="31" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="V3" s="31" t="s">
         <v>30</v>
@@ -22378,7 +22195,7 @@
         <v>51</v>
       </c>
       <c r="AR3" s="33" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AS3" s="28" t="s">
         <v>53</v>
@@ -22456,15 +22273,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.25" spans="1:69">
+    <row r="4" ht="15.75" spans="1:69">
       <c r="A4" s="26">
         <v>1</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C4" s="26" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D4" s="26" t="s">
         <v>76</v>
@@ -22661,10 +22478,10 @@
         <v>85</v>
       </c>
       <c r="BM4" s="27" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="BN4" s="27" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="BO4" s="35">
         <f>ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
@@ -22809,73 +22626,73 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ5"/>
-  <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="8.7047619047619" defaultRowHeight="15" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="5.14545454545455"/>
-    <col min="2" max="3" customWidth="true" width="28.2818181818182"/>
-    <col min="4" max="4" customWidth="true" width="79.4272727272727"/>
-    <col min="5" max="5" customWidth="true" width="11.5727272727273"/>
-    <col min="6" max="6" customWidth="true" width="5.14545454545455"/>
-    <col min="7" max="7" customWidth="true" width="11.0"/>
-    <col min="8" max="8" customWidth="true" width="12.7181818181818"/>
-    <col min="9" max="9" customWidth="true" width="5.85454545454545"/>
-    <col min="10" max="10" customWidth="true" width="6.0"/>
-    <col min="11" max="11" customWidth="true" width="5.85454545454545"/>
-    <col min="12" max="12" customWidth="true" width="14.2818181818182"/>
-    <col min="13" max="13" customWidth="true" width="9.42727272727273"/>
-    <col min="14" max="14" customWidth="true" width="14.4272727272727"/>
-    <col min="15" max="15" customWidth="true" width="15.5727272727273"/>
-    <col min="16" max="16" customWidth="true" width="14.4272727272727"/>
-    <col min="17" max="17" customWidth="true" width="39.4272727272727"/>
-    <col min="18" max="18" customWidth="true" width="11.7181818181818"/>
-    <col min="19" max="19" customWidth="true" width="11.8545454545455"/>
-    <col min="20" max="20" customWidth="true" width="6.42727272727273"/>
-    <col min="21" max="22" customWidth="true" width="6.57272727272727"/>
-    <col min="23" max="23" customWidth="true" width="37.1454545454545"/>
-    <col min="24" max="25" customWidth="true" width="8.0"/>
-    <col min="26" max="26" customWidth="true" width="7.71818181818182"/>
-    <col min="27" max="27" customWidth="true" width="6.28181818181818"/>
-    <col min="28" max="28" customWidth="true" width="9.28181818181818"/>
-    <col min="29" max="29" customWidth="true" width="9.71818181818182"/>
-    <col min="30" max="30" customWidth="true" width="12.8545454545455"/>
-    <col min="31" max="31" customWidth="true" width="16.1454545454545"/>
-    <col min="32" max="32" customWidth="true" width="15.4272727272727"/>
-    <col min="33" max="33" customWidth="true" width="24.5727272727273"/>
-    <col min="34" max="34" customWidth="true" width="8.57272727272727"/>
-    <col min="35" max="35" customWidth="true" width="14.7181818181818"/>
-    <col min="36" max="36" customWidth="true" width="18.5727272727273"/>
-    <col min="37" max="37" customWidth="true" width="14.1454545454545"/>
-    <col min="38" max="38" customWidth="true" width="14.7181818181818"/>
-    <col min="39" max="39" customWidth="true" width="17.4272727272727"/>
-    <col min="40" max="40" customWidth="true" width="22.0"/>
-    <col min="41" max="41" customWidth="true" width="17.5727272727273"/>
-    <col min="42" max="42" customWidth="true" width="25.2818181818182"/>
-    <col min="43" max="43" customWidth="true" width="13.0"/>
-    <col min="44" max="44" customWidth="true" width="23.7181818181818"/>
-    <col min="45" max="45" customWidth="true" width="10.0"/>
-    <col min="46" max="46" customWidth="true" width="13.0"/>
-    <col min="47" max="47" customWidth="true" width="15.5727272727273"/>
-    <col min="48" max="48" customWidth="true" width="21.1454545454545"/>
-    <col min="49" max="49" customWidth="true" width="11.5727272727273"/>
-    <col min="50" max="50" customWidth="true" width="16.7181818181818"/>
-    <col min="51" max="51" customWidth="true" width="14.0"/>
-    <col min="52" max="52" customWidth="true" width="19.4272727272727"/>
-    <col min="53" max="53" customWidth="true" width="18.8545454545455"/>
-    <col min="54" max="54" customWidth="true" width="23.2818181818182"/>
-    <col min="55" max="55" customWidth="true" width="15.5727272727273"/>
-    <col min="56" max="56" customWidth="true" width="14.2818181818182"/>
-    <col min="57" max="57" customWidth="true" width="17.0"/>
-    <col min="58" max="58" customWidth="true" width="16.2818181818182"/>
-    <col min="59" max="59" customWidth="true" width="13.5727272727273"/>
-    <col min="60" max="61" customWidth="true" width="12.7181818181818"/>
-    <col min="62" max="62" customWidth="true" width="21.8545454545455"/>
-    <col min="63" max="63" customWidth="true" width="30.5727272727273"/>
-    <col min="64" max="64" customWidth="true" width="10.0"/>
-    <col min="65" max="65" customWidth="true" width="42.5727272727273"/>
-    <col min="66" max="66" customWidth="true" width="38.1454545454545"/>
-    <col min="67" max="67" customWidth="true" width="19.4272727272727"/>
-    <col min="68" max="68" customWidth="true" width="35.4272727272727"/>
-    <col min="69" max="69" customWidth="true" width="9.57272727272727"/>
+    <col min="1" max="1" width="5.14285714285714" customWidth="1"/>
+    <col min="2" max="3" width="28.2857142857143" customWidth="1"/>
+    <col min="4" max="4" width="79.4285714285714" customWidth="1"/>
+    <col min="5" max="5" width="11.5714285714286" customWidth="1"/>
+    <col min="6" max="6" width="5.14285714285714" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="12.7142857142857" customWidth="1"/>
+    <col min="9" max="9" width="5.85714285714286" customWidth="1"/>
+    <col min="10" max="10" width="6" customWidth="1"/>
+    <col min="11" max="11" width="5.85714285714286" customWidth="1"/>
+    <col min="12" max="12" width="14.2857142857143" customWidth="1"/>
+    <col min="13" max="13" width="9.42857142857143" customWidth="1"/>
+    <col min="14" max="14" width="14.4285714285714" customWidth="1"/>
+    <col min="15" max="15" width="15.5714285714286" customWidth="1"/>
+    <col min="16" max="16" width="14.4285714285714" customWidth="1"/>
+    <col min="17" max="17" width="39.4285714285714" customWidth="1"/>
+    <col min="18" max="18" width="11.7142857142857" customWidth="1"/>
+    <col min="19" max="19" width="11.8571428571429" customWidth="1"/>
+    <col min="20" max="20" width="6.42857142857143" customWidth="1"/>
+    <col min="21" max="22" width="6.57142857142857" customWidth="1"/>
+    <col min="23" max="23" width="37.1428571428571" customWidth="1"/>
+    <col min="24" max="25" width="8" customWidth="1"/>
+    <col min="26" max="26" width="7.71428571428571" customWidth="1"/>
+    <col min="27" max="27" width="6.28571428571429" customWidth="1"/>
+    <col min="28" max="28" width="9.28571428571429" customWidth="1"/>
+    <col min="29" max="29" width="9.71428571428571" customWidth="1"/>
+    <col min="30" max="30" width="12.8571428571429" customWidth="1"/>
+    <col min="31" max="31" width="16.1428571428571" customWidth="1"/>
+    <col min="32" max="32" width="15.4285714285714" customWidth="1"/>
+    <col min="33" max="33" width="24.5714285714286" customWidth="1"/>
+    <col min="34" max="34" width="8.57142857142857" customWidth="1"/>
+    <col min="35" max="35" width="14.7142857142857" customWidth="1"/>
+    <col min="36" max="36" width="18.5714285714286" customWidth="1"/>
+    <col min="37" max="37" width="14.1428571428571" customWidth="1"/>
+    <col min="38" max="38" width="14.7142857142857" customWidth="1"/>
+    <col min="39" max="39" width="17.4285714285714" customWidth="1"/>
+    <col min="40" max="40" width="22" customWidth="1"/>
+    <col min="41" max="41" width="17.5714285714286" customWidth="1"/>
+    <col min="42" max="42" width="25.2857142857143" customWidth="1"/>
+    <col min="43" max="43" width="13" customWidth="1"/>
+    <col min="44" max="44" width="23.7142857142857" customWidth="1"/>
+    <col min="45" max="45" width="10" customWidth="1"/>
+    <col min="46" max="46" width="13" customWidth="1"/>
+    <col min="47" max="47" width="15.5714285714286" customWidth="1"/>
+    <col min="48" max="48" width="21.1428571428571" customWidth="1"/>
+    <col min="49" max="49" width="11.5714285714286" customWidth="1"/>
+    <col min="50" max="50" width="16.7142857142857" customWidth="1"/>
+    <col min="51" max="51" width="14" customWidth="1"/>
+    <col min="52" max="52" width="19.4285714285714" customWidth="1"/>
+    <col min="53" max="53" width="18.8571428571429" customWidth="1"/>
+    <col min="54" max="54" width="23.2857142857143" customWidth="1"/>
+    <col min="55" max="55" width="15.5714285714286" customWidth="1"/>
+    <col min="56" max="56" width="14.2857142857143" customWidth="1"/>
+    <col min="57" max="57" width="17" customWidth="1"/>
+    <col min="58" max="58" width="16.2857142857143" customWidth="1"/>
+    <col min="59" max="59" width="13.5714285714286" customWidth="1"/>
+    <col min="60" max="61" width="12.7142857142857" customWidth="1"/>
+    <col min="62" max="62" width="21.8571428571429" customWidth="1"/>
+    <col min="63" max="63" width="30.5714285714286" customWidth="1"/>
+    <col min="64" max="64" width="10" customWidth="1"/>
+    <col min="65" max="65" width="42.5714285714286" customWidth="1"/>
+    <col min="66" max="66" width="38.1428571428571" customWidth="1"/>
+    <col min="67" max="67" width="19.4285714285714" customWidth="1"/>
+    <col min="68" max="68" width="35.4285714285714" customWidth="1"/>
+    <col min="69" max="69" width="9.57142857142857" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -23046,7 +22863,7 @@
       <c r="BP2" s="27"/>
       <c r="BQ2" s="27"/>
     </row>
-    <row r="3" ht="15.25" spans="1:69">
+    <row r="3" ht="15.75" spans="1:69">
       <c r="A3" s="28" t="s">
         <v>9</v>
       </c>
@@ -23093,7 +22910,7 @@
         <v>25</v>
       </c>
       <c r="P3" s="30" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="Q3" s="30" t="s">
         <v>23</v>
@@ -23102,13 +22919,13 @@
         <v>26</v>
       </c>
       <c r="S3" s="28" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="T3" s="28" t="s">
         <v>28</v>
       </c>
       <c r="U3" s="31" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="V3" s="31" t="s">
         <v>30</v>
@@ -23177,7 +22994,7 @@
         <v>51</v>
       </c>
       <c r="AR3" s="33" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AS3" s="28" t="s">
         <v>53</v>
@@ -23255,15 +23072,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.25" spans="1:69">
+    <row r="4" ht="15.75" spans="1:69">
       <c r="A4" s="26">
         <v>1</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C4" s="26" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D4" s="26" t="s">
         <v>76</v>
@@ -23282,7 +23099,7 @@
         <v>400</v>
       </c>
       <c r="I4" s="27" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J4" s="35">
         <v>2</v>
@@ -23419,8 +23236,6 @@
       <c r="AT4" s="35" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" s="0"/>
-      <c r="AV4" s="0"/>
       <c r="AW4" s="35">
         <f>AM4</f>
         <v>4</v>
@@ -23459,11 +23274,11 @@
       <c r="BL4" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="BM4" t="s" s="0">
-        <v>100</v>
-      </c>
-      <c r="BN4" t="s" s="0">
-        <v>100</v>
+      <c r="BM4" t="s">
+        <v>99</v>
+      </c>
+      <c r="BN4" t="s">
+        <v>99</v>
       </c>
       <c r="BO4" s="35">
         <f>ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>

--- a/testdata/PoToGRN-FOC Scenarios.xlsx
+++ b/testdata/PoToGRN-FOC Scenarios.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="6920" firstSheet="25" activeTab="26"/>
+    <workbookView windowWidth="20490" windowHeight="7620" firstSheet="25" activeTab="26"/>
   </bookViews>
   <sheets>
     <sheet name="D-PoToGRNFOCUDGeneralSameUOMWI" sheetId="32" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2577" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2585" uniqueCount="121">
   <si>
     <t>Purchase Order &amp; GRN</t>
   </si>
@@ -401,6 +401,21 @@
   </si>
   <si>
     <t>GWL_Item_Dissimilar_Pl_03</t>
+  </si>
+  <si>
+    <t>646</t>
+  </si>
+  <si>
+    <t>6864.88992</t>
+  </si>
+  <si>
+    <t>1134</t>
+  </si>
+  <si>
+    <t>5044.62017</t>
+  </si>
+  <si>
+    <t>650</t>
   </si>
 </sst>
 </file>
@@ -1547,73 +1562,73 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ5"/>
-  <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="8.7047619047619" defaultRowHeight="15" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" width="5.14545454545455" customWidth="1"/>
-    <col min="2" max="3" width="20.5727272727273" customWidth="1"/>
-    <col min="4" max="4" width="79.4272727272727" customWidth="1"/>
-    <col min="5" max="5" width="11.5727272727273" customWidth="1"/>
-    <col min="6" max="6" width="5.14545454545455" customWidth="1"/>
-    <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="12.7181818181818" customWidth="1"/>
-    <col min="9" max="10" width="5.85454545454545" customWidth="1"/>
-    <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="14.2818181818182" customWidth="1"/>
-    <col min="13" max="13" width="9.42727272727273" customWidth="1"/>
-    <col min="14" max="14" width="14.2818181818182" customWidth="1"/>
-    <col min="15" max="15" width="15.5727272727273" customWidth="1"/>
-    <col min="16" max="16" width="14.4272727272727" customWidth="1"/>
-    <col min="17" max="17" width="39.4272727272727" customWidth="1"/>
-    <col min="18" max="18" width="11.7181818181818" customWidth="1"/>
-    <col min="19" max="19" width="10" customWidth="1"/>
-    <col min="20" max="20" width="6.42727272727273" customWidth="1"/>
-    <col min="21" max="21" width="9.85454545454546" customWidth="1"/>
-    <col min="22" max="22" width="6.57272727272727" customWidth="1"/>
-    <col min="23" max="23" width="37.1454545454545" customWidth="1"/>
-    <col min="24" max="25" width="8" customWidth="1"/>
-    <col min="26" max="26" width="7.71818181818182" customWidth="1"/>
-    <col min="27" max="27" width="6.28181818181818" customWidth="1"/>
-    <col min="28" max="28" width="9.28181818181818" customWidth="1"/>
-    <col min="29" max="29" width="9.71818181818182" customWidth="1"/>
-    <col min="30" max="30" width="12.8545454545455" customWidth="1"/>
-    <col min="31" max="31" width="16.1454545454545" customWidth="1"/>
-    <col min="32" max="32" width="15.4272727272727" customWidth="1"/>
-    <col min="33" max="33" width="24.5727272727273" customWidth="1"/>
-    <col min="34" max="34" width="8.57272727272727" customWidth="1"/>
-    <col min="35" max="35" width="14.7181818181818" customWidth="1"/>
-    <col min="36" max="36" width="18.5727272727273" customWidth="1"/>
-    <col min="37" max="37" width="14.1454545454545" customWidth="1"/>
-    <col min="38" max="38" width="14.7181818181818" customWidth="1"/>
-    <col min="39" max="39" width="17.4272727272727" customWidth="1"/>
-    <col min="40" max="40" width="22" customWidth="1"/>
-    <col min="41" max="41" width="17.5727272727273" customWidth="1"/>
-    <col min="42" max="42" width="25.2818181818182" customWidth="1"/>
-    <col min="43" max="43" width="13" customWidth="1"/>
-    <col min="44" max="44" width="25.7181818181818" customWidth="1"/>
-    <col min="45" max="45" width="10" customWidth="1"/>
-    <col min="46" max="46" width="13" customWidth="1"/>
-    <col min="47" max="47" width="15.5727272727273" customWidth="1"/>
-    <col min="48" max="48" width="21.1454545454545" customWidth="1"/>
-    <col min="49" max="49" width="11.5727272727273" customWidth="1"/>
-    <col min="50" max="50" width="16.7181818181818" customWidth="1"/>
-    <col min="51" max="51" width="14" customWidth="1"/>
-    <col min="52" max="52" width="19.4272727272727" customWidth="1"/>
-    <col min="53" max="53" width="18.8545454545455" customWidth="1"/>
-    <col min="54" max="54" width="23.2818181818182" customWidth="1"/>
-    <col min="55" max="55" width="15.5727272727273" customWidth="1"/>
-    <col min="56" max="56" width="14.2818181818182" customWidth="1"/>
-    <col min="57" max="57" width="17" customWidth="1"/>
-    <col min="58" max="58" width="16.2818181818182" customWidth="1"/>
-    <col min="59" max="59" width="13.5727272727273" customWidth="1"/>
-    <col min="60" max="61" width="12.7181818181818" customWidth="1"/>
-    <col min="62" max="62" width="21.8545454545455" customWidth="1"/>
-    <col min="63" max="63" width="30.5727272727273" customWidth="1"/>
-    <col min="64" max="64" width="10" customWidth="1"/>
-    <col min="65" max="65" width="42.5727272727273" customWidth="1"/>
-    <col min="66" max="66" width="38.1454545454545" customWidth="1"/>
-    <col min="67" max="67" width="19.4272727272727" customWidth="1"/>
-    <col min="68" max="68" width="35.4272727272727" customWidth="1"/>
-    <col min="69" max="69" width="9.57272727272727" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="5.14285714285714"/>
+    <col min="2" max="3" customWidth="true" width="20.5714285714286"/>
+    <col min="4" max="4" customWidth="true" width="79.4285714285714"/>
+    <col min="5" max="5" customWidth="true" width="11.5714285714286"/>
+    <col min="6" max="6" customWidth="true" width="5.14285714285714"/>
+    <col min="7" max="7" customWidth="true" width="11.0"/>
+    <col min="8" max="8" customWidth="true" width="12.7142857142857"/>
+    <col min="9" max="10" customWidth="true" width="5.85714285714286"/>
+    <col min="11" max="11" customWidth="true" width="6.0"/>
+    <col min="12" max="12" customWidth="true" width="14.2857142857143"/>
+    <col min="13" max="13" customWidth="true" width="9.42857142857143"/>
+    <col min="14" max="14" customWidth="true" width="14.2857142857143"/>
+    <col min="15" max="15" customWidth="true" width="15.5714285714286"/>
+    <col min="16" max="16" customWidth="true" width="14.4285714285714"/>
+    <col min="17" max="17" customWidth="true" width="39.4285714285714"/>
+    <col min="18" max="18" customWidth="true" width="11.7142857142857"/>
+    <col min="19" max="19" customWidth="true" width="10.0"/>
+    <col min="20" max="20" customWidth="true" width="10.7142857142857"/>
+    <col min="21" max="21" customWidth="true" width="9.85714285714286"/>
+    <col min="22" max="22" customWidth="true" width="6.57142857142857"/>
+    <col min="23" max="23" customWidth="true" width="37.1428571428571"/>
+    <col min="24" max="25" customWidth="true" width="8.0"/>
+    <col min="26" max="26" customWidth="true" width="7.71428571428571"/>
+    <col min="27" max="27" customWidth="true" width="6.28571428571429"/>
+    <col min="28" max="28" customWidth="true" width="9.28571428571429"/>
+    <col min="29" max="29" customWidth="true" width="9.71428571428571"/>
+    <col min="30" max="30" customWidth="true" width="12.8571428571429"/>
+    <col min="31" max="31" customWidth="true" width="16.1428571428571"/>
+    <col min="32" max="32" customWidth="true" width="15.4285714285714"/>
+    <col min="33" max="33" customWidth="true" width="24.5714285714286"/>
+    <col min="34" max="34" customWidth="true" width="8.57142857142857"/>
+    <col min="35" max="35" customWidth="true" width="14.7142857142857"/>
+    <col min="36" max="36" customWidth="true" width="18.5714285714286"/>
+    <col min="37" max="37" customWidth="true" width="14.1428571428571"/>
+    <col min="38" max="38" customWidth="true" width="14.7142857142857"/>
+    <col min="39" max="39" customWidth="true" width="17.4285714285714"/>
+    <col min="40" max="40" customWidth="true" width="22.0"/>
+    <col min="41" max="41" customWidth="true" width="17.5714285714286"/>
+    <col min="42" max="42" customWidth="true" width="25.2857142857143"/>
+    <col min="43" max="43" customWidth="true" width="13.0"/>
+    <col min="44" max="44" customWidth="true" width="25.7142857142857"/>
+    <col min="45" max="45" customWidth="true" width="10.0"/>
+    <col min="46" max="46" customWidth="true" width="13.0"/>
+    <col min="47" max="47" customWidth="true" width="15.5714285714286"/>
+    <col min="48" max="48" customWidth="true" width="21.1428571428571"/>
+    <col min="49" max="49" customWidth="true" width="11.5714285714286"/>
+    <col min="50" max="50" customWidth="true" width="16.7142857142857"/>
+    <col min="51" max="51" customWidth="true" width="14.0"/>
+    <col min="52" max="52" customWidth="true" width="19.4285714285714"/>
+    <col min="53" max="53" customWidth="true" width="18.8571428571429"/>
+    <col min="54" max="54" customWidth="true" width="23.2857142857143"/>
+    <col min="55" max="55" customWidth="true" width="15.5714285714286"/>
+    <col min="56" max="56" customWidth="true" width="14.2857142857143"/>
+    <col min="57" max="57" customWidth="true" width="17.0"/>
+    <col min="58" max="58" customWidth="true" width="16.2857142857143"/>
+    <col min="59" max="59" customWidth="true" width="13.5714285714286"/>
+    <col min="60" max="61" customWidth="true" width="12.7142857142857"/>
+    <col min="62" max="62" customWidth="true" width="21.8571428571429"/>
+    <col min="63" max="63" customWidth="true" width="30.5714285714286"/>
+    <col min="64" max="64" customWidth="true" width="10.0"/>
+    <col min="65" max="65" customWidth="true" width="42.5714285714286"/>
+    <col min="66" max="66" customWidth="true" width="38.1428571428571"/>
+    <col min="67" max="67" customWidth="true" width="19.4285714285714"/>
+    <col min="68" max="68" customWidth="true" width="35.4285714285714"/>
+    <col min="69" max="69" customWidth="true" width="9.57142857142857"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -1784,7 +1799,7 @@
       <c r="BP2" s="32"/>
       <c r="BQ2" s="32"/>
     </row>
-    <row r="3" ht="15.25" spans="1:69">
+    <row r="3" ht="15.75" spans="1:69">
       <c r="A3" s="33" t="s">
         <v>9</v>
       </c>
@@ -1993,7 +2008,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.25" spans="1:69">
+    <row r="4" ht="15.75" spans="1:69">
       <c r="A4" s="31">
         <v>1</v>
       </c>
@@ -2064,7 +2079,7 @@
         <v>88363222</v>
       </c>
       <c r="U4" s="17">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="V4" s="17">
         <f>IF(OR($C$2=1,$C$2=4),ROUND((((S4*U4)/100)/2),2),0)</f>
@@ -2076,7 +2091,7 @@
       </c>
       <c r="X4" s="17">
         <f>IF($C$2=2,ROUND(((S4*U4)/100),2),0)</f>
-        <v>0</v>
+        <v>68.46</v>
       </c>
       <c r="Y4" s="17">
         <f>IF($C$2=4,ROUND((((S4*U4)/100)/2),2),0)</f>
@@ -2091,11 +2106,11 @@
       </c>
       <c r="AB4" s="17">
         <f>V4+W4+X4+Y4+AA4</f>
-        <v>15.2128</v>
+        <v>83.6728</v>
       </c>
       <c r="AC4" s="17">
         <f>IF($V2=1,S4+AB4,S4)</f>
-        <v>395.5328</v>
+        <v>463.9928</v>
       </c>
       <c r="AD4" s="17">
         <v>120</v>
@@ -2157,11 +2172,11 @@
       <c r="AT4" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="AU4" s="20" t="s">
-        <v>78</v>
-      </c>
-      <c r="AV4" s="20" t="s">
-        <v>79</v>
+      <c r="AU4" t="s" s="0">
+        <v>120</v>
+      </c>
+      <c r="AV4" t="s" s="0">
+        <v>117</v>
       </c>
       <c r="AW4" s="19">
         <f>AM4</f>
@@ -2201,11 +2216,11 @@
       <c r="BL4" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="BM4" s="20" t="s">
-        <v>85</v>
-      </c>
-      <c r="BN4" s="20" t="s">
-        <v>86</v>
+      <c r="BM4" t="s" s="0">
+        <v>119</v>
+      </c>
+      <c r="BN4" t="s" s="0">
+        <v>118</v>
       </c>
       <c r="BO4" s="19">
         <f>ROUND((((AW4*AZ4)+(BN4*BM4))/(AW4+BN4)),5)</f>
@@ -2262,7 +2277,7 @@
       </c>
       <c r="X5" s="42">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>68.46</v>
       </c>
       <c r="Y5" s="42">
         <f t="shared" si="0"/>
@@ -2278,11 +2293,11 @@
       </c>
       <c r="AB5" s="42">
         <f t="shared" si="0"/>
-        <v>15.2128</v>
+        <v>83.6728</v>
       </c>
       <c r="AC5" s="42">
         <f t="shared" si="0"/>
-        <v>395.5328</v>
+        <v>463.9928</v>
       </c>
       <c r="AD5" s="42">
         <f t="shared" si="0"/>
@@ -2362,73 +2377,73 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ5"/>
-  <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="8.7047619047619" defaultRowHeight="15" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" width="5.14545454545455" customWidth="1"/>
-    <col min="2" max="3" width="28.2818181818182" customWidth="1"/>
-    <col min="4" max="4" width="79.4272727272727" customWidth="1"/>
-    <col min="5" max="5" width="11.5727272727273" customWidth="1"/>
-    <col min="6" max="6" width="5.14545454545455" customWidth="1"/>
-    <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="12.7181818181818" customWidth="1"/>
-    <col min="9" max="9" width="5.85454545454545" customWidth="1"/>
-    <col min="10" max="10" width="6" customWidth="1"/>
-    <col min="11" max="11" width="5.85454545454545" customWidth="1"/>
-    <col min="12" max="12" width="14.2818181818182" customWidth="1"/>
-    <col min="13" max="13" width="9.42727272727273" customWidth="1"/>
-    <col min="14" max="14" width="14.4272727272727" customWidth="1"/>
-    <col min="15" max="15" width="15.5727272727273" customWidth="1"/>
-    <col min="16" max="16" width="14.4272727272727" customWidth="1"/>
-    <col min="17" max="17" width="39.4272727272727" customWidth="1"/>
-    <col min="18" max="18" width="11.7181818181818" customWidth="1"/>
-    <col min="19" max="19" width="11.8545454545455" customWidth="1"/>
-    <col min="20" max="20" width="6.42727272727273" customWidth="1"/>
-    <col min="21" max="22" width="6.57272727272727" customWidth="1"/>
-    <col min="23" max="23" width="37.1454545454545" customWidth="1"/>
-    <col min="24" max="25" width="8" customWidth="1"/>
-    <col min="26" max="26" width="7.71818181818182" customWidth="1"/>
-    <col min="27" max="27" width="6.28181818181818" customWidth="1"/>
-    <col min="28" max="28" width="9.28181818181818" customWidth="1"/>
-    <col min="29" max="29" width="9.71818181818182" customWidth="1"/>
-    <col min="30" max="30" width="12.8545454545455" customWidth="1"/>
-    <col min="31" max="31" width="16.1454545454545" customWidth="1"/>
-    <col min="32" max="32" width="15.4272727272727" customWidth="1"/>
-    <col min="33" max="33" width="24.5727272727273" customWidth="1"/>
-    <col min="34" max="34" width="8.57272727272727" customWidth="1"/>
-    <col min="35" max="35" width="14.7181818181818" customWidth="1"/>
-    <col min="36" max="36" width="18.5727272727273" customWidth="1"/>
-    <col min="37" max="37" width="14.1454545454545" customWidth="1"/>
-    <col min="38" max="38" width="14.7181818181818" customWidth="1"/>
-    <col min="39" max="39" width="17.4272727272727" customWidth="1"/>
-    <col min="40" max="40" width="22" customWidth="1"/>
-    <col min="41" max="41" width="17.5727272727273" customWidth="1"/>
-    <col min="42" max="42" width="25.2818181818182" customWidth="1"/>
-    <col min="43" max="43" width="13" customWidth="1"/>
-    <col min="44" max="44" width="23.7181818181818" customWidth="1"/>
-    <col min="45" max="45" width="10" customWidth="1"/>
-    <col min="46" max="46" width="13" customWidth="1"/>
-    <col min="47" max="47" width="15.5727272727273" customWidth="1"/>
-    <col min="48" max="48" width="21.1454545454545" customWidth="1"/>
-    <col min="49" max="49" width="11.5727272727273" customWidth="1"/>
-    <col min="50" max="50" width="16.7181818181818" customWidth="1"/>
-    <col min="51" max="51" width="14" customWidth="1"/>
-    <col min="52" max="52" width="19.4272727272727" customWidth="1"/>
-    <col min="53" max="53" width="18.8545454545455" customWidth="1"/>
-    <col min="54" max="54" width="23.2818181818182" customWidth="1"/>
-    <col min="55" max="55" width="15.5727272727273" customWidth="1"/>
-    <col min="56" max="56" width="14.2818181818182" customWidth="1"/>
-    <col min="57" max="57" width="17" customWidth="1"/>
-    <col min="58" max="58" width="16.2818181818182" customWidth="1"/>
-    <col min="59" max="59" width="13.5727272727273" customWidth="1"/>
-    <col min="60" max="61" width="12.7181818181818" customWidth="1"/>
-    <col min="62" max="62" width="21.8545454545455" customWidth="1"/>
-    <col min="63" max="63" width="30.5727272727273" customWidth="1"/>
-    <col min="64" max="64" width="10" customWidth="1"/>
-    <col min="65" max="65" width="42.5727272727273" customWidth="1"/>
-    <col min="66" max="66" width="38.1454545454545" customWidth="1"/>
-    <col min="67" max="67" width="19.4272727272727" customWidth="1"/>
-    <col min="68" max="68" width="35.4272727272727" customWidth="1"/>
-    <col min="69" max="69" width="9.57272727272727" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="5.14285714285714"/>
+    <col min="2" max="3" customWidth="true" width="28.2857142857143"/>
+    <col min="4" max="4" customWidth="true" width="79.4285714285714"/>
+    <col min="5" max="5" customWidth="true" width="11.5714285714286"/>
+    <col min="6" max="6" customWidth="true" width="5.14285714285714"/>
+    <col min="7" max="7" customWidth="true" width="11.0"/>
+    <col min="8" max="8" customWidth="true" width="12.7142857142857"/>
+    <col min="9" max="9" customWidth="true" width="5.85714285714286"/>
+    <col min="10" max="10" customWidth="true" width="6.0"/>
+    <col min="11" max="11" customWidth="true" width="5.85714285714286"/>
+    <col min="12" max="12" customWidth="true" width="14.2857142857143"/>
+    <col min="13" max="13" customWidth="true" width="9.42857142857143"/>
+    <col min="14" max="14" customWidth="true" width="14.4285714285714"/>
+    <col min="15" max="15" customWidth="true" width="15.5714285714286"/>
+    <col min="16" max="16" customWidth="true" width="14.4285714285714"/>
+    <col min="17" max="17" customWidth="true" width="39.4285714285714"/>
+    <col min="18" max="18" customWidth="true" width="11.7142857142857"/>
+    <col min="19" max="19" customWidth="true" width="11.8571428571429"/>
+    <col min="20" max="20" customWidth="true" width="6.42857142857143"/>
+    <col min="21" max="22" customWidth="true" width="6.57142857142857"/>
+    <col min="23" max="23" customWidth="true" width="37.1428571428571"/>
+    <col min="24" max="25" customWidth="true" width="8.0"/>
+    <col min="26" max="26" customWidth="true" width="7.71428571428571"/>
+    <col min="27" max="27" customWidth="true" width="6.28571428571429"/>
+    <col min="28" max="28" customWidth="true" width="9.28571428571429"/>
+    <col min="29" max="29" customWidth="true" width="9.71428571428571"/>
+    <col min="30" max="30" customWidth="true" width="12.8571428571429"/>
+    <col min="31" max="31" customWidth="true" width="16.1428571428571"/>
+    <col min="32" max="32" customWidth="true" width="15.4285714285714"/>
+    <col min="33" max="33" customWidth="true" width="24.5714285714286"/>
+    <col min="34" max="34" customWidth="true" width="8.57142857142857"/>
+    <col min="35" max="35" customWidth="true" width="14.7142857142857"/>
+    <col min="36" max="36" customWidth="true" width="18.5714285714286"/>
+    <col min="37" max="37" customWidth="true" width="14.1428571428571"/>
+    <col min="38" max="38" customWidth="true" width="14.7142857142857"/>
+    <col min="39" max="39" customWidth="true" width="17.4285714285714"/>
+    <col min="40" max="40" customWidth="true" width="22.0"/>
+    <col min="41" max="41" customWidth="true" width="17.5714285714286"/>
+    <col min="42" max="42" customWidth="true" width="25.2857142857143"/>
+    <col min="43" max="43" customWidth="true" width="13.0"/>
+    <col min="44" max="44" customWidth="true" width="23.7142857142857"/>
+    <col min="45" max="45" customWidth="true" width="10.0"/>
+    <col min="46" max="46" customWidth="true" width="13.0"/>
+    <col min="47" max="47" customWidth="true" width="15.5714285714286"/>
+    <col min="48" max="48" customWidth="true" width="21.1428571428571"/>
+    <col min="49" max="49" customWidth="true" width="11.5714285714286"/>
+    <col min="50" max="50" customWidth="true" width="16.7142857142857"/>
+    <col min="51" max="51" customWidth="true" width="14.0"/>
+    <col min="52" max="52" customWidth="true" width="19.4285714285714"/>
+    <col min="53" max="53" customWidth="true" width="18.8571428571429"/>
+    <col min="54" max="54" customWidth="true" width="23.2857142857143"/>
+    <col min="55" max="55" customWidth="true" width="15.5714285714286"/>
+    <col min="56" max="56" customWidth="true" width="14.2857142857143"/>
+    <col min="57" max="57" customWidth="true" width="17.0"/>
+    <col min="58" max="58" customWidth="true" width="16.2857142857143"/>
+    <col min="59" max="59" customWidth="true" width="13.5714285714286"/>
+    <col min="60" max="61" customWidth="true" width="12.7142857142857"/>
+    <col min="62" max="62" customWidth="true" width="21.8571428571429"/>
+    <col min="63" max="63" customWidth="true" width="30.5714285714286"/>
+    <col min="64" max="64" customWidth="true" width="10.0"/>
+    <col min="65" max="65" customWidth="true" width="42.5714285714286"/>
+    <col min="66" max="66" customWidth="true" width="38.1428571428571"/>
+    <col min="67" max="67" customWidth="true" width="19.4285714285714"/>
+    <col min="68" max="68" customWidth="true" width="35.4285714285714"/>
+    <col min="69" max="69" customWidth="true" width="9.57142857142857"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -2599,7 +2614,7 @@
       <c r="BP2" s="32"/>
       <c r="BQ2" s="32"/>
     </row>
-    <row r="3" ht="15.25" spans="1:69">
+    <row r="3" ht="15.75" spans="1:69">
       <c r="A3" s="33" t="s">
         <v>9</v>
       </c>
@@ -2808,7 +2823,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.25" spans="1:69">
+    <row r="4" ht="15.75" spans="1:69">
       <c r="A4" s="31">
         <v>1</v>
       </c>
@@ -2879,7 +2894,7 @@
         <v>88363222</v>
       </c>
       <c r="U4" s="17">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="V4" s="17">
         <f>IF(OR($C$2=1,$C$2=4),ROUND((((S4*U4)/100)/2),2),0)</f>
@@ -2891,7 +2906,7 @@
       </c>
       <c r="X4" s="17">
         <f>IF($C$2=2,ROUND(((S4*U4)/100),2),0)</f>
-        <v>0</v>
+        <v>67.77</v>
       </c>
       <c r="Y4" s="17">
         <f>IF($C$2=4,ROUND((((S4*U4)/100)/2),2),0)</f>
@@ -2906,11 +2921,11 @@
       </c>
       <c r="AB4" s="17">
         <f>V4+W4+X4+Y4+AA4</f>
-        <v>15.0592</v>
+        <v>82.8292</v>
       </c>
       <c r="AC4" s="17">
         <f>IF($V2=1,S4+AB4,S4)</f>
-        <v>391.5392</v>
+        <v>459.3092</v>
       </c>
       <c r="AD4" s="17">
         <v>120</v>
@@ -3077,18 +3092,18 @@
       </c>
       <c r="X5" s="42">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>67.77</v>
       </c>
       <c r="Y5" s="44"/>
       <c r="Z5" s="44"/>
       <c r="AA5" s="44"/>
       <c r="AB5" s="42">
         <f t="shared" ref="AB5:AE5" si="1">SUM(AB4:AB4)</f>
-        <v>15.0592</v>
+        <v>82.8292</v>
       </c>
       <c r="AC5" s="42">
         <f t="shared" si="1"/>
-        <v>391.5392</v>
+        <v>459.3092</v>
       </c>
       <c r="AD5" s="42">
         <f t="shared" si="1"/>
@@ -3165,73 +3180,73 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ5"/>
-  <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="8.7047619047619" defaultRowHeight="15" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" width="5.14545454545455" customWidth="1"/>
-    <col min="2" max="3" width="24.7181818181818" customWidth="1"/>
-    <col min="4" max="4" width="79.4272727272727" customWidth="1"/>
-    <col min="5" max="5" width="11.5727272727273" customWidth="1"/>
-    <col min="6" max="6" width="5.14545454545455" customWidth="1"/>
-    <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="12.7181818181818" customWidth="1"/>
-    <col min="9" max="9" width="5.85454545454545" customWidth="1"/>
-    <col min="10" max="10" width="6" customWidth="1"/>
-    <col min="11" max="11" width="5.85454545454545" customWidth="1"/>
-    <col min="12" max="12" width="14.2818181818182" customWidth="1"/>
-    <col min="13" max="13" width="9.42727272727273" customWidth="1"/>
-    <col min="14" max="14" width="14.4272727272727" customWidth="1"/>
-    <col min="15" max="15" width="15.5727272727273" customWidth="1"/>
-    <col min="16" max="16" width="14.4272727272727" customWidth="1"/>
-    <col min="17" max="17" width="39.4272727272727" customWidth="1"/>
-    <col min="18" max="18" width="11.7181818181818" customWidth="1"/>
-    <col min="19" max="19" width="11.8545454545455" customWidth="1"/>
-    <col min="20" max="20" width="6.42727272727273" customWidth="1"/>
-    <col min="21" max="22" width="6.57272727272727" customWidth="1"/>
-    <col min="23" max="23" width="37.1454545454545" customWidth="1"/>
-    <col min="24" max="25" width="8" customWidth="1"/>
-    <col min="26" max="26" width="7.71818181818182" customWidth="1"/>
-    <col min="27" max="27" width="6.28181818181818" customWidth="1"/>
-    <col min="28" max="28" width="9.28181818181818" customWidth="1"/>
-    <col min="29" max="29" width="9.71818181818182" customWidth="1"/>
-    <col min="30" max="30" width="12.8545454545455" customWidth="1"/>
-    <col min="31" max="31" width="16.1454545454545" customWidth="1"/>
-    <col min="32" max="32" width="15.4272727272727" customWidth="1"/>
-    <col min="33" max="33" width="24.5727272727273" customWidth="1"/>
-    <col min="34" max="34" width="8.57272727272727" customWidth="1"/>
-    <col min="35" max="35" width="14.7181818181818" customWidth="1"/>
-    <col min="36" max="36" width="18.5727272727273" customWidth="1"/>
-    <col min="37" max="37" width="14.1454545454545" customWidth="1"/>
-    <col min="38" max="38" width="14.7181818181818" customWidth="1"/>
-    <col min="39" max="39" width="17.4272727272727" customWidth="1"/>
-    <col min="40" max="40" width="22" customWidth="1"/>
-    <col min="41" max="41" width="17.5727272727273" customWidth="1"/>
-    <col min="42" max="42" width="25.2818181818182" customWidth="1"/>
-    <col min="43" max="43" width="13" customWidth="1"/>
-    <col min="44" max="44" width="23.7181818181818" customWidth="1"/>
-    <col min="45" max="45" width="10" customWidth="1"/>
-    <col min="46" max="46" width="13" customWidth="1"/>
-    <col min="47" max="47" width="15.5727272727273" customWidth="1"/>
-    <col min="48" max="48" width="21.1454545454545" customWidth="1"/>
-    <col min="49" max="49" width="11.5727272727273" customWidth="1"/>
-    <col min="50" max="50" width="16.7181818181818" customWidth="1"/>
-    <col min="51" max="51" width="14" customWidth="1"/>
-    <col min="52" max="52" width="19.4272727272727" customWidth="1"/>
-    <col min="53" max="53" width="18.8545454545455" customWidth="1"/>
-    <col min="54" max="54" width="23.2818181818182" customWidth="1"/>
-    <col min="55" max="55" width="15.5727272727273" customWidth="1"/>
-    <col min="56" max="56" width="14.2818181818182" customWidth="1"/>
-    <col min="57" max="57" width="17" customWidth="1"/>
-    <col min="58" max="58" width="16.2818181818182" customWidth="1"/>
-    <col min="59" max="59" width="13.5727272727273" customWidth="1"/>
-    <col min="60" max="61" width="12.7181818181818" customWidth="1"/>
-    <col min="62" max="62" width="21.8545454545455" customWidth="1"/>
-    <col min="63" max="63" width="30.5727272727273" customWidth="1"/>
-    <col min="64" max="64" width="10" customWidth="1"/>
-    <col min="65" max="65" width="42.5727272727273" customWidth="1"/>
-    <col min="66" max="66" width="38.1454545454545" customWidth="1"/>
-    <col min="67" max="67" width="19.4272727272727" customWidth="1"/>
-    <col min="68" max="68" width="35.4272727272727" customWidth="1"/>
-    <col min="69" max="69" width="9.57272727272727" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="5.14285714285714"/>
+    <col min="2" max="3" customWidth="true" width="24.7142857142857"/>
+    <col min="4" max="4" customWidth="true" width="79.4285714285714"/>
+    <col min="5" max="5" customWidth="true" width="11.5714285714286"/>
+    <col min="6" max="6" customWidth="true" width="5.14285714285714"/>
+    <col min="7" max="7" customWidth="true" width="11.0"/>
+    <col min="8" max="8" customWidth="true" width="12.7142857142857"/>
+    <col min="9" max="9" customWidth="true" width="5.85714285714286"/>
+    <col min="10" max="10" customWidth="true" width="6.0"/>
+    <col min="11" max="11" customWidth="true" width="5.85714285714286"/>
+    <col min="12" max="12" customWidth="true" width="14.2857142857143"/>
+    <col min="13" max="13" customWidth="true" width="9.42857142857143"/>
+    <col min="14" max="14" customWidth="true" width="14.4285714285714"/>
+    <col min="15" max="15" customWidth="true" width="15.5714285714286"/>
+    <col min="16" max="16" customWidth="true" width="14.4285714285714"/>
+    <col min="17" max="17" customWidth="true" width="39.4285714285714"/>
+    <col min="18" max="18" customWidth="true" width="11.7142857142857"/>
+    <col min="19" max="19" customWidth="true" width="11.8571428571429"/>
+    <col min="20" max="20" customWidth="true" width="6.42857142857143"/>
+    <col min="21" max="22" customWidth="true" width="6.57142857142857"/>
+    <col min="23" max="23" customWidth="true" width="37.1428571428571"/>
+    <col min="24" max="25" customWidth="true" width="8.0"/>
+    <col min="26" max="26" customWidth="true" width="7.71428571428571"/>
+    <col min="27" max="27" customWidth="true" width="6.28571428571429"/>
+    <col min="28" max="28" customWidth="true" width="9.28571428571429"/>
+    <col min="29" max="29" customWidth="true" width="9.71428571428571"/>
+    <col min="30" max="30" customWidth="true" width="12.8571428571429"/>
+    <col min="31" max="31" customWidth="true" width="16.1428571428571"/>
+    <col min="32" max="32" customWidth="true" width="15.4285714285714"/>
+    <col min="33" max="33" customWidth="true" width="24.5714285714286"/>
+    <col min="34" max="34" customWidth="true" width="8.57142857142857"/>
+    <col min="35" max="35" customWidth="true" width="14.7142857142857"/>
+    <col min="36" max="36" customWidth="true" width="18.5714285714286"/>
+    <col min="37" max="37" customWidth="true" width="14.1428571428571"/>
+    <col min="38" max="38" customWidth="true" width="14.7142857142857"/>
+    <col min="39" max="39" customWidth="true" width="17.4285714285714"/>
+    <col min="40" max="40" customWidth="true" width="22.0"/>
+    <col min="41" max="41" customWidth="true" width="17.5714285714286"/>
+    <col min="42" max="42" customWidth="true" width="25.2857142857143"/>
+    <col min="43" max="43" customWidth="true" width="13.0"/>
+    <col min="44" max="44" customWidth="true" width="23.7142857142857"/>
+    <col min="45" max="45" customWidth="true" width="10.0"/>
+    <col min="46" max="46" customWidth="true" width="13.0"/>
+    <col min="47" max="47" customWidth="true" width="15.5714285714286"/>
+    <col min="48" max="48" customWidth="true" width="21.1428571428571"/>
+    <col min="49" max="49" customWidth="true" width="11.5714285714286"/>
+    <col min="50" max="50" customWidth="true" width="16.7142857142857"/>
+    <col min="51" max="51" customWidth="true" width="14.0"/>
+    <col min="52" max="52" customWidth="true" width="19.4285714285714"/>
+    <col min="53" max="53" customWidth="true" width="18.8571428571429"/>
+    <col min="54" max="54" customWidth="true" width="23.2857142857143"/>
+    <col min="55" max="55" customWidth="true" width="15.5714285714286"/>
+    <col min="56" max="56" customWidth="true" width="14.2857142857143"/>
+    <col min="57" max="57" customWidth="true" width="17.0"/>
+    <col min="58" max="58" customWidth="true" width="16.2857142857143"/>
+    <col min="59" max="59" customWidth="true" width="13.5714285714286"/>
+    <col min="60" max="61" customWidth="true" width="12.7142857142857"/>
+    <col min="62" max="62" customWidth="true" width="21.8571428571429"/>
+    <col min="63" max="63" customWidth="true" width="30.5714285714286"/>
+    <col min="64" max="64" customWidth="true" width="10.0"/>
+    <col min="65" max="65" customWidth="true" width="42.5714285714286"/>
+    <col min="66" max="66" customWidth="true" width="38.1428571428571"/>
+    <col min="67" max="67" customWidth="true" width="19.4285714285714"/>
+    <col min="68" max="68" customWidth="true" width="35.4285714285714"/>
+    <col min="69" max="69" customWidth="true" width="9.57142857142857"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -3402,7 +3417,7 @@
       <c r="BP2" s="32"/>
       <c r="BQ2" s="32"/>
     </row>
-    <row r="3" ht="15.25" spans="1:69">
+    <row r="3" ht="15.75" spans="1:69">
       <c r="A3" s="33" t="s">
         <v>9</v>
       </c>
@@ -3611,7 +3626,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.25" spans="1:69">
+    <row r="4" ht="15.75" spans="1:69">
       <c r="A4" s="31">
         <v>1</v>
       </c>
@@ -3682,7 +3697,7 @@
         <v>88363222</v>
       </c>
       <c r="U4" s="17">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="V4" s="17">
         <f>IF(OR($C$2=1,$C$2=4),ROUND((((S4*U4)/100)/2),2),0)</f>
@@ -3694,7 +3709,7 @@
       </c>
       <c r="X4" s="17">
         <f>IF($C$2=2,ROUND(((S4*U4)/100),2),0)</f>
-        <v>0</v>
+        <v>68.46</v>
       </c>
       <c r="Y4" s="17">
         <f>IF($C$2=4,ROUND((((S4*U4)/100)/2),2),0)</f>
@@ -3709,11 +3724,11 @@
       </c>
       <c r="AB4" s="17">
         <f>V4+W4+X4+Y4+AA4</f>
-        <v>15.2128</v>
+        <v>83.6728</v>
       </c>
       <c r="AC4" s="17">
         <f>IF($V2=1,S4+AB4,S4)</f>
-        <v>395.5328</v>
+        <v>463.9928</v>
       </c>
       <c r="AD4" s="17">
         <v>120</v>
@@ -3880,7 +3895,7 @@
       </c>
       <c r="X5" s="42">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>68.46</v>
       </c>
       <c r="Y5" s="42">
         <f t="shared" si="0"/>
@@ -3896,11 +3911,11 @@
       </c>
       <c r="AB5" s="42">
         <f t="shared" si="0"/>
-        <v>15.2128</v>
+        <v>83.6728</v>
       </c>
       <c r="AC5" s="42">
         <f t="shared" si="0"/>
-        <v>395.5328</v>
+        <v>463.9928</v>
       </c>
       <c r="AD5" s="42">
         <f t="shared" si="0"/>
@@ -3980,73 +3995,73 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ5"/>
-  <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="8.7047619047619" defaultRowHeight="15" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" width="5.14545454545455" customWidth="1"/>
-    <col min="2" max="3" width="24.7181818181818" customWidth="1"/>
-    <col min="4" max="4" width="79.4272727272727" customWidth="1"/>
-    <col min="5" max="5" width="11.5727272727273" customWidth="1"/>
-    <col min="6" max="6" width="5.14545454545455" customWidth="1"/>
-    <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="12.7181818181818" customWidth="1"/>
-    <col min="9" max="9" width="5.85454545454545" customWidth="1"/>
-    <col min="10" max="10" width="6" customWidth="1"/>
-    <col min="11" max="11" width="5.85454545454545" customWidth="1"/>
-    <col min="12" max="12" width="14.2818181818182" customWidth="1"/>
-    <col min="13" max="13" width="9.42727272727273" customWidth="1"/>
-    <col min="14" max="14" width="14.4272727272727" customWidth="1"/>
-    <col min="15" max="15" width="15.5727272727273" customWidth="1"/>
-    <col min="16" max="16" width="14.4272727272727" customWidth="1"/>
-    <col min="17" max="17" width="39.4272727272727" customWidth="1"/>
-    <col min="18" max="18" width="11.7181818181818" customWidth="1"/>
-    <col min="19" max="19" width="11.8545454545455" customWidth="1"/>
-    <col min="20" max="20" width="6.42727272727273" customWidth="1"/>
-    <col min="21" max="22" width="6.57272727272727" customWidth="1"/>
-    <col min="23" max="23" width="37.1454545454545" customWidth="1"/>
-    <col min="24" max="25" width="8" customWidth="1"/>
-    <col min="26" max="26" width="7.71818181818182" customWidth="1"/>
-    <col min="27" max="27" width="6.28181818181818" customWidth="1"/>
-    <col min="28" max="28" width="9.28181818181818" customWidth="1"/>
-    <col min="29" max="29" width="9.71818181818182" customWidth="1"/>
-    <col min="30" max="30" width="12.8545454545455" customWidth="1"/>
-    <col min="31" max="31" width="16.1454545454545" customWidth="1"/>
-    <col min="32" max="32" width="15.4272727272727" customWidth="1"/>
-    <col min="33" max="33" width="24.5727272727273" customWidth="1"/>
-    <col min="34" max="34" width="8.57272727272727" customWidth="1"/>
-    <col min="35" max="35" width="14.7181818181818" customWidth="1"/>
-    <col min="36" max="36" width="18.5727272727273" customWidth="1"/>
-    <col min="37" max="37" width="14.1454545454545" customWidth="1"/>
-    <col min="38" max="38" width="14.7181818181818" customWidth="1"/>
-    <col min="39" max="39" width="17.4272727272727" customWidth="1"/>
-    <col min="40" max="40" width="22" customWidth="1"/>
-    <col min="41" max="41" width="17.5727272727273" customWidth="1"/>
-    <col min="42" max="42" width="25.2818181818182" customWidth="1"/>
-    <col min="43" max="43" width="13" customWidth="1"/>
-    <col min="44" max="44" width="23.7181818181818" customWidth="1"/>
-    <col min="45" max="45" width="10" customWidth="1"/>
-    <col min="46" max="46" width="13" customWidth="1"/>
-    <col min="47" max="47" width="15.5727272727273" customWidth="1"/>
-    <col min="48" max="48" width="21.1454545454545" customWidth="1"/>
-    <col min="49" max="49" width="11.5727272727273" customWidth="1"/>
-    <col min="50" max="50" width="16.7181818181818" customWidth="1"/>
-    <col min="51" max="51" width="14" customWidth="1"/>
-    <col min="52" max="52" width="19.4272727272727" customWidth="1"/>
-    <col min="53" max="53" width="18.8545454545455" customWidth="1"/>
-    <col min="54" max="54" width="23.2818181818182" customWidth="1"/>
-    <col min="55" max="55" width="15.5727272727273" customWidth="1"/>
-    <col min="56" max="56" width="14.2818181818182" customWidth="1"/>
-    <col min="57" max="57" width="17" customWidth="1"/>
-    <col min="58" max="58" width="16.2818181818182" customWidth="1"/>
-    <col min="59" max="59" width="13.5727272727273" customWidth="1"/>
-    <col min="60" max="61" width="12.7181818181818" customWidth="1"/>
-    <col min="62" max="62" width="21.8545454545455" customWidth="1"/>
-    <col min="63" max="63" width="30.5727272727273" customWidth="1"/>
-    <col min="64" max="64" width="10" customWidth="1"/>
-    <col min="65" max="65" width="42.5727272727273" customWidth="1"/>
-    <col min="66" max="66" width="38.1454545454545" customWidth="1"/>
-    <col min="67" max="67" width="19.4272727272727" customWidth="1"/>
-    <col min="68" max="68" width="35.4272727272727" customWidth="1"/>
-    <col min="69" max="69" width="9.57272727272727" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="5.14285714285714"/>
+    <col min="2" max="3" customWidth="true" width="24.7142857142857"/>
+    <col min="4" max="4" customWidth="true" width="79.4285714285714"/>
+    <col min="5" max="5" customWidth="true" width="11.5714285714286"/>
+    <col min="6" max="6" customWidth="true" width="5.14285714285714"/>
+    <col min="7" max="7" customWidth="true" width="11.0"/>
+    <col min="8" max="8" customWidth="true" width="12.7142857142857"/>
+    <col min="9" max="9" customWidth="true" width="5.85714285714286"/>
+    <col min="10" max="10" customWidth="true" width="6.0"/>
+    <col min="11" max="11" customWidth="true" width="5.85714285714286"/>
+    <col min="12" max="12" customWidth="true" width="14.2857142857143"/>
+    <col min="13" max="13" customWidth="true" width="9.42857142857143"/>
+    <col min="14" max="14" customWidth="true" width="14.4285714285714"/>
+    <col min="15" max="15" customWidth="true" width="15.5714285714286"/>
+    <col min="16" max="16" customWidth="true" width="14.4285714285714"/>
+    <col min="17" max="17" customWidth="true" width="39.4285714285714"/>
+    <col min="18" max="18" customWidth="true" width="11.7142857142857"/>
+    <col min="19" max="19" customWidth="true" width="11.8571428571429"/>
+    <col min="20" max="20" customWidth="true" width="6.42857142857143"/>
+    <col min="21" max="22" customWidth="true" width="6.57142857142857"/>
+    <col min="23" max="23" customWidth="true" width="37.1428571428571"/>
+    <col min="24" max="25" customWidth="true" width="8.0"/>
+    <col min="26" max="26" customWidth="true" width="7.71428571428571"/>
+    <col min="27" max="27" customWidth="true" width="6.28571428571429"/>
+    <col min="28" max="28" customWidth="true" width="9.28571428571429"/>
+    <col min="29" max="29" customWidth="true" width="9.71428571428571"/>
+    <col min="30" max="30" customWidth="true" width="12.8571428571429"/>
+    <col min="31" max="31" customWidth="true" width="16.1428571428571"/>
+    <col min="32" max="32" customWidth="true" width="15.4285714285714"/>
+    <col min="33" max="33" customWidth="true" width="24.5714285714286"/>
+    <col min="34" max="34" customWidth="true" width="8.57142857142857"/>
+    <col min="35" max="35" customWidth="true" width="14.7142857142857"/>
+    <col min="36" max="36" customWidth="true" width="18.5714285714286"/>
+    <col min="37" max="37" customWidth="true" width="14.1428571428571"/>
+    <col min="38" max="38" customWidth="true" width="14.7142857142857"/>
+    <col min="39" max="39" customWidth="true" width="17.4285714285714"/>
+    <col min="40" max="40" customWidth="true" width="22.0"/>
+    <col min="41" max="41" customWidth="true" width="17.5714285714286"/>
+    <col min="42" max="42" customWidth="true" width="25.2857142857143"/>
+    <col min="43" max="43" customWidth="true" width="13.0"/>
+    <col min="44" max="44" customWidth="true" width="23.7142857142857"/>
+    <col min="45" max="45" customWidth="true" width="10.0"/>
+    <col min="46" max="46" customWidth="true" width="13.0"/>
+    <col min="47" max="47" customWidth="true" width="15.5714285714286"/>
+    <col min="48" max="48" customWidth="true" width="21.1428571428571"/>
+    <col min="49" max="49" customWidth="true" width="11.5714285714286"/>
+    <col min="50" max="50" customWidth="true" width="16.7142857142857"/>
+    <col min="51" max="51" customWidth="true" width="14.0"/>
+    <col min="52" max="52" customWidth="true" width="19.4285714285714"/>
+    <col min="53" max="53" customWidth="true" width="18.8571428571429"/>
+    <col min="54" max="54" customWidth="true" width="23.2857142857143"/>
+    <col min="55" max="55" customWidth="true" width="15.5714285714286"/>
+    <col min="56" max="56" customWidth="true" width="14.2857142857143"/>
+    <col min="57" max="57" customWidth="true" width="17.0"/>
+    <col min="58" max="58" customWidth="true" width="16.2857142857143"/>
+    <col min="59" max="59" customWidth="true" width="13.5714285714286"/>
+    <col min="60" max="61" customWidth="true" width="12.7142857142857"/>
+    <col min="62" max="62" customWidth="true" width="21.8571428571429"/>
+    <col min="63" max="63" customWidth="true" width="30.5714285714286"/>
+    <col min="64" max="64" customWidth="true" width="10.0"/>
+    <col min="65" max="65" customWidth="true" width="42.5714285714286"/>
+    <col min="66" max="66" customWidth="true" width="38.1428571428571"/>
+    <col min="67" max="67" customWidth="true" width="19.4285714285714"/>
+    <col min="68" max="68" customWidth="true" width="35.4285714285714"/>
+    <col min="69" max="69" customWidth="true" width="9.57142857142857"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -4217,7 +4232,7 @@
       <c r="BP2" s="32"/>
       <c r="BQ2" s="32"/>
     </row>
-    <row r="3" ht="15.25" spans="1:69">
+    <row r="3" ht="15.75" spans="1:69">
       <c r="A3" s="33" t="s">
         <v>9</v>
       </c>
@@ -4426,7 +4441,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.25" spans="1:69">
+    <row r="4" ht="15.75" spans="1:69">
       <c r="A4" s="31">
         <v>1</v>
       </c>
@@ -4497,7 +4512,7 @@
         <v>88363222</v>
       </c>
       <c r="U4" s="17">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="V4" s="17">
         <f>IF(OR($C$2=1,$C$2=4),ROUND((((S4*U4)/100)/2),2),0)</f>
@@ -4509,7 +4524,7 @@
       </c>
       <c r="X4" s="17">
         <f>IF($C$2=2,ROUND(((S4*U4)/100),2),0)</f>
-        <v>0</v>
+        <v>68.46</v>
       </c>
       <c r="Y4" s="17">
         <f>IF($C$2=4,ROUND((((S4*U4)/100)/2),2),0)</f>
@@ -4524,11 +4539,11 @@
       </c>
       <c r="AB4" s="17">
         <f>V4+W4+X4+Y4+AA4</f>
-        <v>15.2128</v>
+        <v>83.6728</v>
       </c>
       <c r="AC4" s="17">
         <f>IF($V2=1,S4+AB4,S4)</f>
-        <v>395.5328</v>
+        <v>463.9928</v>
       </c>
       <c r="AD4" s="17">
         <v>120</v>
@@ -4695,18 +4710,18 @@
       </c>
       <c r="X5" s="42">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>68.46</v>
       </c>
       <c r="Y5" s="44"/>
       <c r="Z5" s="44"/>
       <c r="AA5" s="44"/>
       <c r="AB5" s="42">
         <f t="shared" ref="AB5:AE5" si="1">SUM(AB4:AB4)</f>
-        <v>15.2128</v>
+        <v>83.6728</v>
       </c>
       <c r="AC5" s="42">
         <f t="shared" si="1"/>
-        <v>395.5328</v>
+        <v>463.9928</v>
       </c>
       <c r="AD5" s="42">
         <f t="shared" si="1"/>
@@ -4783,73 +4798,73 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ5"/>
-  <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="8.7047619047619" defaultRowHeight="15" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" width="5.14545454545455" customWidth="1"/>
-    <col min="2" max="3" width="25.1454545454545" customWidth="1"/>
-    <col min="4" max="4" width="79.4272727272727" customWidth="1"/>
-    <col min="5" max="5" width="11.5727272727273" customWidth="1"/>
-    <col min="6" max="6" width="5.14545454545455" customWidth="1"/>
-    <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="12.7181818181818" customWidth="1"/>
-    <col min="9" max="9" width="5.85454545454545" customWidth="1"/>
-    <col min="10" max="10" width="6" customWidth="1"/>
-    <col min="11" max="11" width="5.85454545454545" customWidth="1"/>
-    <col min="12" max="12" width="14.2818181818182" customWidth="1"/>
-    <col min="13" max="13" width="9.42727272727273" customWidth="1"/>
-    <col min="14" max="14" width="14.4272727272727" customWidth="1"/>
-    <col min="15" max="15" width="15.5727272727273" customWidth="1"/>
-    <col min="16" max="16" width="14.4272727272727" customWidth="1"/>
-    <col min="17" max="17" width="39.4272727272727" customWidth="1"/>
-    <col min="18" max="18" width="11.7181818181818" customWidth="1"/>
-    <col min="19" max="19" width="11.8545454545455" customWidth="1"/>
-    <col min="20" max="20" width="6.42727272727273" customWidth="1"/>
-    <col min="21" max="22" width="6.57272727272727" customWidth="1"/>
-    <col min="23" max="23" width="37.1454545454545" customWidth="1"/>
-    <col min="24" max="25" width="8" customWidth="1"/>
-    <col min="26" max="26" width="7.71818181818182" customWidth="1"/>
-    <col min="27" max="27" width="6.28181818181818" customWidth="1"/>
-    <col min="28" max="28" width="9.28181818181818" customWidth="1"/>
-    <col min="29" max="29" width="9.71818181818182" customWidth="1"/>
-    <col min="30" max="30" width="12.8545454545455" customWidth="1"/>
-    <col min="31" max="31" width="16.1454545454545" customWidth="1"/>
-    <col min="32" max="32" width="15.4272727272727" customWidth="1"/>
-    <col min="33" max="33" width="24.5727272727273" customWidth="1"/>
-    <col min="34" max="34" width="8.57272727272727" customWidth="1"/>
-    <col min="35" max="35" width="14.7181818181818" customWidth="1"/>
-    <col min="36" max="36" width="18.5727272727273" customWidth="1"/>
-    <col min="37" max="37" width="14.1454545454545" customWidth="1"/>
-    <col min="38" max="38" width="14.7181818181818" customWidth="1"/>
-    <col min="39" max="39" width="17.4272727272727" customWidth="1"/>
-    <col min="40" max="40" width="22" customWidth="1"/>
-    <col min="41" max="41" width="17.5727272727273" customWidth="1"/>
-    <col min="42" max="42" width="25.2818181818182" customWidth="1"/>
-    <col min="43" max="43" width="13" customWidth="1"/>
-    <col min="44" max="44" width="23.7181818181818" customWidth="1"/>
-    <col min="45" max="45" width="10" customWidth="1"/>
-    <col min="46" max="46" width="13" customWidth="1"/>
-    <col min="47" max="47" width="15.5727272727273" customWidth="1"/>
-    <col min="48" max="48" width="21.1454545454545" customWidth="1"/>
-    <col min="49" max="49" width="11.5727272727273" customWidth="1"/>
-    <col min="50" max="50" width="16.7181818181818" customWidth="1"/>
-    <col min="51" max="51" width="14" customWidth="1"/>
-    <col min="52" max="52" width="19.4272727272727" customWidth="1"/>
-    <col min="53" max="53" width="18.8545454545455" customWidth="1"/>
-    <col min="54" max="54" width="23.2818181818182" customWidth="1"/>
-    <col min="55" max="55" width="15.5727272727273" customWidth="1"/>
-    <col min="56" max="56" width="14.2818181818182" customWidth="1"/>
-    <col min="57" max="57" width="17" customWidth="1"/>
-    <col min="58" max="58" width="16.2818181818182" customWidth="1"/>
-    <col min="59" max="59" width="13.5727272727273" customWidth="1"/>
-    <col min="60" max="61" width="12.7181818181818" customWidth="1"/>
-    <col min="62" max="62" width="21.8545454545455" customWidth="1"/>
-    <col min="63" max="63" width="30.5727272727273" customWidth="1"/>
-    <col min="64" max="64" width="10" customWidth="1"/>
-    <col min="65" max="65" width="42.5727272727273" customWidth="1"/>
-    <col min="66" max="66" width="38.1454545454545" customWidth="1"/>
-    <col min="67" max="67" width="19.4272727272727" customWidth="1"/>
-    <col min="68" max="68" width="35.4272727272727" customWidth="1"/>
-    <col min="69" max="69" width="9.57272727272727" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="5.14285714285714"/>
+    <col min="2" max="3" customWidth="true" width="25.1428571428571"/>
+    <col min="4" max="4" customWidth="true" width="79.4285714285714"/>
+    <col min="5" max="5" customWidth="true" width="11.5714285714286"/>
+    <col min="6" max="6" customWidth="true" width="5.14285714285714"/>
+    <col min="7" max="7" customWidth="true" width="11.0"/>
+    <col min="8" max="8" customWidth="true" width="12.7142857142857"/>
+    <col min="9" max="9" customWidth="true" width="5.85714285714286"/>
+    <col min="10" max="10" customWidth="true" width="6.0"/>
+    <col min="11" max="11" customWidth="true" width="5.85714285714286"/>
+    <col min="12" max="12" customWidth="true" width="14.2857142857143"/>
+    <col min="13" max="13" customWidth="true" width="9.42857142857143"/>
+    <col min="14" max="14" customWidth="true" width="14.4285714285714"/>
+    <col min="15" max="15" customWidth="true" width="15.5714285714286"/>
+    <col min="16" max="16" customWidth="true" width="14.4285714285714"/>
+    <col min="17" max="17" customWidth="true" width="39.4285714285714"/>
+    <col min="18" max="18" customWidth="true" width="11.7142857142857"/>
+    <col min="19" max="19" customWidth="true" width="11.8571428571429"/>
+    <col min="20" max="20" customWidth="true" width="6.42857142857143"/>
+    <col min="21" max="22" customWidth="true" width="6.57142857142857"/>
+    <col min="23" max="23" customWidth="true" width="37.1428571428571"/>
+    <col min="24" max="25" customWidth="true" width="8.0"/>
+    <col min="26" max="26" customWidth="true" width="7.71428571428571"/>
+    <col min="27" max="27" customWidth="true" width="6.28571428571429"/>
+    <col min="28" max="28" customWidth="true" width="9.28571428571429"/>
+    <col min="29" max="29" customWidth="true" width="9.71428571428571"/>
+    <col min="30" max="30" customWidth="true" width="12.8571428571429"/>
+    <col min="31" max="31" customWidth="true" width="16.1428571428571"/>
+    <col min="32" max="32" customWidth="true" width="15.4285714285714"/>
+    <col min="33" max="33" customWidth="true" width="24.5714285714286"/>
+    <col min="34" max="34" customWidth="true" width="8.57142857142857"/>
+    <col min="35" max="35" customWidth="true" width="14.7142857142857"/>
+    <col min="36" max="36" customWidth="true" width="18.5714285714286"/>
+    <col min="37" max="37" customWidth="true" width="14.1428571428571"/>
+    <col min="38" max="38" customWidth="true" width="14.7142857142857"/>
+    <col min="39" max="39" customWidth="true" width="17.4285714285714"/>
+    <col min="40" max="40" customWidth="true" width="22.0"/>
+    <col min="41" max="41" customWidth="true" width="17.5714285714286"/>
+    <col min="42" max="42" customWidth="true" width="25.2857142857143"/>
+    <col min="43" max="43" customWidth="true" width="13.0"/>
+    <col min="44" max="44" customWidth="true" width="23.7142857142857"/>
+    <col min="45" max="45" customWidth="true" width="10.0"/>
+    <col min="46" max="46" customWidth="true" width="13.0"/>
+    <col min="47" max="47" customWidth="true" width="15.5714285714286"/>
+    <col min="48" max="48" customWidth="true" width="21.1428571428571"/>
+    <col min="49" max="49" customWidth="true" width="11.5714285714286"/>
+    <col min="50" max="50" customWidth="true" width="16.7142857142857"/>
+    <col min="51" max="51" customWidth="true" width="14.0"/>
+    <col min="52" max="52" customWidth="true" width="19.4285714285714"/>
+    <col min="53" max="53" customWidth="true" width="18.8571428571429"/>
+    <col min="54" max="54" customWidth="true" width="23.2857142857143"/>
+    <col min="55" max="55" customWidth="true" width="15.5714285714286"/>
+    <col min="56" max="56" customWidth="true" width="14.2857142857143"/>
+    <col min="57" max="57" customWidth="true" width="17.0"/>
+    <col min="58" max="58" customWidth="true" width="16.2857142857143"/>
+    <col min="59" max="59" customWidth="true" width="13.5714285714286"/>
+    <col min="60" max="61" customWidth="true" width="12.7142857142857"/>
+    <col min="62" max="62" customWidth="true" width="21.8571428571429"/>
+    <col min="63" max="63" customWidth="true" width="30.5714285714286"/>
+    <col min="64" max="64" customWidth="true" width="10.0"/>
+    <col min="65" max="65" customWidth="true" width="42.5714285714286"/>
+    <col min="66" max="66" customWidth="true" width="38.1428571428571"/>
+    <col min="67" max="67" customWidth="true" width="19.4285714285714"/>
+    <col min="68" max="68" customWidth="true" width="35.4285714285714"/>
+    <col min="69" max="69" customWidth="true" width="9.57142857142857"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -5020,7 +5035,7 @@
       <c r="BP2" s="32"/>
       <c r="BQ2" s="32"/>
     </row>
-    <row r="3" ht="15.25" spans="1:69">
+    <row r="3" ht="15.75" spans="1:69">
       <c r="A3" s="33" t="s">
         <v>9</v>
       </c>
@@ -5229,7 +5244,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.25" spans="1:69">
+    <row r="4" ht="15.75" spans="1:69">
       <c r="A4" s="31">
         <v>1</v>
       </c>
@@ -5300,7 +5315,7 @@
         <v>88363222</v>
       </c>
       <c r="U4" s="17">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="V4" s="17">
         <f>IF(OR($C$2=1,$C$2=4),ROUND((((S4*U4)/100)/2),2),0)</f>
@@ -5312,7 +5327,7 @@
       </c>
       <c r="X4" s="17">
         <f>IF($C$2=2,ROUND(((S4*U4)/100),2),0)</f>
-        <v>0</v>
+        <v>68.46</v>
       </c>
       <c r="Y4" s="17">
         <f>IF($C$2=4,ROUND((((S4*U4)/100)/2),2),0)</f>
@@ -5327,11 +5342,11 @@
       </c>
       <c r="AB4" s="17">
         <f>V4+W4+X4+Y4+AA4</f>
-        <v>15.2128</v>
+        <v>83.6728</v>
       </c>
       <c r="AC4" s="17">
         <f>IF($V2=1,S4+AB4,S4)</f>
-        <v>395.5328</v>
+        <v>463.9928</v>
       </c>
       <c r="AD4" s="17">
         <v>120</v>
@@ -5498,18 +5513,18 @@
       </c>
       <c r="X5" s="42">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>68.46</v>
       </c>
       <c r="Y5" s="44"/>
       <c r="Z5" s="44"/>
       <c r="AA5" s="44"/>
       <c r="AB5" s="42">
         <f t="shared" ref="AB5:AE5" si="1">SUM(AB4:AB4)</f>
-        <v>15.2128</v>
+        <v>83.6728</v>
       </c>
       <c r="AC5" s="42">
         <f t="shared" si="1"/>
-        <v>395.5328</v>
+        <v>463.9928</v>
       </c>
       <c r="AD5" s="42">
         <f t="shared" si="1"/>
@@ -5586,73 +5601,73 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ5"/>
-  <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="8.7047619047619" defaultRowHeight="15" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" width="5.14545454545455" customWidth="1"/>
-    <col min="2" max="3" width="22" customWidth="1"/>
-    <col min="4" max="4" width="79.4272727272727" customWidth="1"/>
-    <col min="5" max="5" width="11.5727272727273" customWidth="1"/>
-    <col min="6" max="6" width="5.14545454545455" customWidth="1"/>
-    <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="12.7181818181818" customWidth="1"/>
-    <col min="9" max="9" width="5.85454545454545" customWidth="1"/>
-    <col min="10" max="10" width="6" customWidth="1"/>
-    <col min="11" max="11" width="5.85454545454545" customWidth="1"/>
-    <col min="12" max="12" width="14.2818181818182" customWidth="1"/>
-    <col min="13" max="13" width="9.42727272727273" customWidth="1"/>
-    <col min="14" max="14" width="14.4272727272727" customWidth="1"/>
-    <col min="15" max="15" width="15.5727272727273" customWidth="1"/>
-    <col min="16" max="16" width="14.4272727272727" customWidth="1"/>
-    <col min="17" max="17" width="39.4272727272727" customWidth="1"/>
-    <col min="18" max="18" width="11.7181818181818" customWidth="1"/>
-    <col min="19" max="19" width="11.8545454545455" customWidth="1"/>
-    <col min="20" max="20" width="6.42727272727273" customWidth="1"/>
-    <col min="21" max="22" width="6.57272727272727" customWidth="1"/>
-    <col min="23" max="23" width="37.1454545454545" customWidth="1"/>
-    <col min="24" max="25" width="8" customWidth="1"/>
-    <col min="26" max="26" width="7.71818181818182" customWidth="1"/>
-    <col min="27" max="27" width="6.28181818181818" customWidth="1"/>
-    <col min="28" max="28" width="9.28181818181818" customWidth="1"/>
-    <col min="29" max="29" width="9.71818181818182" customWidth="1"/>
-    <col min="30" max="30" width="12.8545454545455" customWidth="1"/>
-    <col min="31" max="31" width="16.1454545454545" customWidth="1"/>
-    <col min="32" max="32" width="15.4272727272727" customWidth="1"/>
-    <col min="33" max="33" width="24.5727272727273" customWidth="1"/>
-    <col min="34" max="34" width="8.57272727272727" customWidth="1"/>
-    <col min="35" max="35" width="14.7181818181818" customWidth="1"/>
-    <col min="36" max="36" width="18.5727272727273" customWidth="1"/>
-    <col min="37" max="37" width="14.1454545454545" customWidth="1"/>
-    <col min="38" max="38" width="14.7181818181818" customWidth="1"/>
-    <col min="39" max="39" width="17.4272727272727" customWidth="1"/>
-    <col min="40" max="40" width="22" customWidth="1"/>
-    <col min="41" max="41" width="17.5727272727273" customWidth="1"/>
-    <col min="42" max="42" width="25.2818181818182" customWidth="1"/>
-    <col min="43" max="43" width="13" customWidth="1"/>
-    <col min="44" max="44" width="23.7181818181818" customWidth="1"/>
-    <col min="45" max="45" width="10" customWidth="1"/>
-    <col min="46" max="46" width="13" customWidth="1"/>
-    <col min="47" max="47" width="15.5727272727273" customWidth="1"/>
-    <col min="48" max="48" width="21.1454545454545" customWidth="1"/>
-    <col min="49" max="49" width="11.5727272727273" customWidth="1"/>
-    <col min="50" max="50" width="16.7181818181818" customWidth="1"/>
-    <col min="51" max="51" width="14" customWidth="1"/>
-    <col min="52" max="52" width="19.4272727272727" customWidth="1"/>
-    <col min="53" max="53" width="18.8545454545455" customWidth="1"/>
-    <col min="54" max="54" width="23.2818181818182" customWidth="1"/>
-    <col min="55" max="55" width="15.5727272727273" customWidth="1"/>
-    <col min="56" max="56" width="14.2818181818182" customWidth="1"/>
-    <col min="57" max="57" width="17" customWidth="1"/>
-    <col min="58" max="58" width="16.2818181818182" customWidth="1"/>
-    <col min="59" max="59" width="13.5727272727273" customWidth="1"/>
-    <col min="60" max="61" width="12.7181818181818" customWidth="1"/>
-    <col min="62" max="62" width="21.8545454545455" customWidth="1"/>
-    <col min="63" max="63" width="30.5727272727273" customWidth="1"/>
-    <col min="64" max="64" width="10" customWidth="1"/>
-    <col min="65" max="65" width="42.5727272727273" customWidth="1"/>
-    <col min="66" max="66" width="38.1454545454545" customWidth="1"/>
-    <col min="67" max="67" width="19.4272727272727" customWidth="1"/>
-    <col min="68" max="68" width="35.4272727272727" customWidth="1"/>
-    <col min="69" max="69" width="9.57272727272727" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="5.14285714285714"/>
+    <col min="2" max="3" customWidth="true" width="22.0"/>
+    <col min="4" max="4" customWidth="true" width="79.4285714285714"/>
+    <col min="5" max="5" customWidth="true" width="11.5714285714286"/>
+    <col min="6" max="6" customWidth="true" width="5.14285714285714"/>
+    <col min="7" max="7" customWidth="true" width="11.0"/>
+    <col min="8" max="8" customWidth="true" width="12.7142857142857"/>
+    <col min="9" max="9" customWidth="true" width="5.85714285714286"/>
+    <col min="10" max="10" customWidth="true" width="6.0"/>
+    <col min="11" max="11" customWidth="true" width="5.85714285714286"/>
+    <col min="12" max="12" customWidth="true" width="14.2857142857143"/>
+    <col min="13" max="13" customWidth="true" width="9.42857142857143"/>
+    <col min="14" max="14" customWidth="true" width="14.4285714285714"/>
+    <col min="15" max="15" customWidth="true" width="15.5714285714286"/>
+    <col min="16" max="16" customWidth="true" width="14.4285714285714"/>
+    <col min="17" max="17" customWidth="true" width="39.4285714285714"/>
+    <col min="18" max="18" customWidth="true" width="11.7142857142857"/>
+    <col min="19" max="19" customWidth="true" width="11.8571428571429"/>
+    <col min="20" max="20" customWidth="true" width="6.42857142857143"/>
+    <col min="21" max="22" customWidth="true" width="6.57142857142857"/>
+    <col min="23" max="23" customWidth="true" width="37.1428571428571"/>
+    <col min="24" max="25" customWidth="true" width="8.0"/>
+    <col min="26" max="26" customWidth="true" width="7.71428571428571"/>
+    <col min="27" max="27" customWidth="true" width="6.28571428571429"/>
+    <col min="28" max="28" customWidth="true" width="9.28571428571429"/>
+    <col min="29" max="29" customWidth="true" width="9.71428571428571"/>
+    <col min="30" max="30" customWidth="true" width="12.8571428571429"/>
+    <col min="31" max="31" customWidth="true" width="16.1428571428571"/>
+    <col min="32" max="32" customWidth="true" width="15.4285714285714"/>
+    <col min="33" max="33" customWidth="true" width="24.5714285714286"/>
+    <col min="34" max="34" customWidth="true" width="8.57142857142857"/>
+    <col min="35" max="35" customWidth="true" width="14.7142857142857"/>
+    <col min="36" max="36" customWidth="true" width="18.5714285714286"/>
+    <col min="37" max="37" customWidth="true" width="14.1428571428571"/>
+    <col min="38" max="38" customWidth="true" width="14.7142857142857"/>
+    <col min="39" max="39" customWidth="true" width="17.4285714285714"/>
+    <col min="40" max="40" customWidth="true" width="22.0"/>
+    <col min="41" max="41" customWidth="true" width="17.5714285714286"/>
+    <col min="42" max="42" customWidth="true" width="25.2857142857143"/>
+    <col min="43" max="43" customWidth="true" width="13.0"/>
+    <col min="44" max="44" customWidth="true" width="23.7142857142857"/>
+    <col min="45" max="45" customWidth="true" width="10.0"/>
+    <col min="46" max="46" customWidth="true" width="13.0"/>
+    <col min="47" max="47" customWidth="true" width="15.5714285714286"/>
+    <col min="48" max="48" customWidth="true" width="21.1428571428571"/>
+    <col min="49" max="49" customWidth="true" width="11.5714285714286"/>
+    <col min="50" max="50" customWidth="true" width="16.7142857142857"/>
+    <col min="51" max="51" customWidth="true" width="14.0"/>
+    <col min="52" max="52" customWidth="true" width="19.4285714285714"/>
+    <col min="53" max="53" customWidth="true" width="18.8571428571429"/>
+    <col min="54" max="54" customWidth="true" width="23.2857142857143"/>
+    <col min="55" max="55" customWidth="true" width="15.5714285714286"/>
+    <col min="56" max="56" customWidth="true" width="14.2857142857143"/>
+    <col min="57" max="57" customWidth="true" width="17.0"/>
+    <col min="58" max="58" customWidth="true" width="16.2857142857143"/>
+    <col min="59" max="59" customWidth="true" width="13.5714285714286"/>
+    <col min="60" max="61" customWidth="true" width="12.7142857142857"/>
+    <col min="62" max="62" customWidth="true" width="21.8571428571429"/>
+    <col min="63" max="63" customWidth="true" width="30.5714285714286"/>
+    <col min="64" max="64" customWidth="true" width="10.0"/>
+    <col min="65" max="65" customWidth="true" width="42.5714285714286"/>
+    <col min="66" max="66" customWidth="true" width="38.1428571428571"/>
+    <col min="67" max="67" customWidth="true" width="19.4285714285714"/>
+    <col min="68" max="68" customWidth="true" width="35.4285714285714"/>
+    <col min="69" max="69" customWidth="true" width="9.57142857142857"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -5823,7 +5838,7 @@
       <c r="BP2" s="32"/>
       <c r="BQ2" s="32"/>
     </row>
-    <row r="3" ht="15.25" spans="1:69">
+    <row r="3" ht="15.75" spans="1:69">
       <c r="A3" s="33" t="s">
         <v>9</v>
       </c>
@@ -6032,7 +6047,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.25" spans="1:69">
+    <row r="4" ht="15.75" spans="1:69">
       <c r="A4" s="31">
         <v>1</v>
       </c>
@@ -6103,7 +6118,7 @@
         <v>88363222</v>
       </c>
       <c r="U4" s="17">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="V4" s="17">
         <f>IF(OR($C$2=1,$C$2=4),ROUND((((S4*U4)/100)/2),2),0)</f>
@@ -6115,7 +6130,7 @@
       </c>
       <c r="X4" s="17">
         <f>IF($C$2=2,ROUND(((S4*U4)/100),2),0)</f>
-        <v>0</v>
+        <v>67.77</v>
       </c>
       <c r="Y4" s="17">
         <f>IF($C$2=4,ROUND((((S4*U4)/100)/2),2),0)</f>
@@ -6130,11 +6145,11 @@
       </c>
       <c r="AB4" s="17">
         <f>V4+W4+X4+Y4+AA4</f>
-        <v>15.0592</v>
+        <v>82.8292</v>
       </c>
       <c r="AC4" s="17">
         <f>IF($V2=1,S4+AB4,S4)</f>
-        <v>391.5392</v>
+        <v>459.3092</v>
       </c>
       <c r="AD4" s="17">
         <v>120</v>
@@ -6301,18 +6316,18 @@
       </c>
       <c r="X5" s="42">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>67.77</v>
       </c>
       <c r="Y5" s="44"/>
       <c r="Z5" s="44"/>
       <c r="AA5" s="44"/>
       <c r="AB5" s="42">
         <f t="shared" ref="AB5:AE5" si="1">SUM(AB4:AB4)</f>
-        <v>15.0592</v>
+        <v>82.8292</v>
       </c>
       <c r="AC5" s="42">
         <f t="shared" si="1"/>
-        <v>391.5392</v>
+        <v>459.3092</v>
       </c>
       <c r="AD5" s="42">
         <f t="shared" si="1"/>
@@ -6389,73 +6404,73 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ5"/>
-  <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="8.7047619047619" defaultRowHeight="15" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" width="5.14545454545455" customWidth="1"/>
-    <col min="2" max="3" width="22" customWidth="1"/>
-    <col min="4" max="4" width="79.4272727272727" customWidth="1"/>
-    <col min="5" max="5" width="11.5727272727273" customWidth="1"/>
-    <col min="6" max="6" width="5.14545454545455" customWidth="1"/>
-    <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="12.7181818181818" customWidth="1"/>
-    <col min="9" max="9" width="5.85454545454545" customWidth="1"/>
-    <col min="10" max="10" width="6" customWidth="1"/>
-    <col min="11" max="11" width="5.85454545454545" customWidth="1"/>
-    <col min="12" max="12" width="14.2818181818182" customWidth="1"/>
-    <col min="13" max="13" width="9.42727272727273" customWidth="1"/>
-    <col min="14" max="14" width="14.4272727272727" customWidth="1"/>
-    <col min="15" max="15" width="15.5727272727273" customWidth="1"/>
-    <col min="16" max="16" width="14.4272727272727" customWidth="1"/>
-    <col min="17" max="17" width="39.4272727272727" customWidth="1"/>
-    <col min="18" max="18" width="11.7181818181818" customWidth="1"/>
-    <col min="19" max="19" width="11.8545454545455" customWidth="1"/>
-    <col min="20" max="20" width="6.42727272727273" customWidth="1"/>
-    <col min="21" max="22" width="6.57272727272727" customWidth="1"/>
-    <col min="23" max="23" width="37.1454545454545" customWidth="1"/>
-    <col min="24" max="25" width="8" customWidth="1"/>
-    <col min="26" max="26" width="7.71818181818182" customWidth="1"/>
-    <col min="27" max="27" width="6.28181818181818" customWidth="1"/>
-    <col min="28" max="28" width="9.28181818181818" customWidth="1"/>
-    <col min="29" max="29" width="9.71818181818182" customWidth="1"/>
-    <col min="30" max="30" width="12.8545454545455" customWidth="1"/>
-    <col min="31" max="31" width="16.1454545454545" customWidth="1"/>
-    <col min="32" max="32" width="15.4272727272727" customWidth="1"/>
-    <col min="33" max="33" width="24.5727272727273" customWidth="1"/>
-    <col min="34" max="34" width="8.57272727272727" customWidth="1"/>
-    <col min="35" max="35" width="14.7181818181818" customWidth="1"/>
-    <col min="36" max="36" width="18.5727272727273" customWidth="1"/>
-    <col min="37" max="37" width="14.1454545454545" customWidth="1"/>
-    <col min="38" max="38" width="14.7181818181818" customWidth="1"/>
-    <col min="39" max="39" width="17.4272727272727" customWidth="1"/>
-    <col min="40" max="40" width="22" customWidth="1"/>
-    <col min="41" max="41" width="17.5727272727273" customWidth="1"/>
-    <col min="42" max="42" width="25.2818181818182" customWidth="1"/>
-    <col min="43" max="43" width="13" customWidth="1"/>
-    <col min="44" max="44" width="23.7181818181818" customWidth="1"/>
-    <col min="45" max="45" width="10" customWidth="1"/>
-    <col min="46" max="46" width="13" customWidth="1"/>
-    <col min="47" max="47" width="15.5727272727273" customWidth="1"/>
-    <col min="48" max="48" width="21.1454545454545" customWidth="1"/>
-    <col min="49" max="49" width="11.5727272727273" customWidth="1"/>
-    <col min="50" max="50" width="16.7181818181818" customWidth="1"/>
-    <col min="51" max="51" width="14" customWidth="1"/>
-    <col min="52" max="52" width="19.4272727272727" customWidth="1"/>
-    <col min="53" max="53" width="18.8545454545455" customWidth="1"/>
-    <col min="54" max="54" width="23.2818181818182" customWidth="1"/>
-    <col min="55" max="55" width="15.5727272727273" customWidth="1"/>
-    <col min="56" max="56" width="14.2818181818182" customWidth="1"/>
-    <col min="57" max="57" width="17" customWidth="1"/>
-    <col min="58" max="58" width="16.2818181818182" customWidth="1"/>
-    <col min="59" max="59" width="13.5727272727273" customWidth="1"/>
-    <col min="60" max="61" width="12.7181818181818" customWidth="1"/>
-    <col min="62" max="62" width="21.8545454545455" customWidth="1"/>
-    <col min="63" max="63" width="30.5727272727273" customWidth="1"/>
-    <col min="64" max="64" width="10" customWidth="1"/>
-    <col min="65" max="65" width="42.5727272727273" customWidth="1"/>
-    <col min="66" max="66" width="38.1454545454545" customWidth="1"/>
-    <col min="67" max="67" width="19.4272727272727" customWidth="1"/>
-    <col min="68" max="68" width="35.4272727272727" customWidth="1"/>
-    <col min="69" max="69" width="9.57272727272727" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="5.14285714285714"/>
+    <col min="2" max="3" customWidth="true" width="22.0"/>
+    <col min="4" max="4" customWidth="true" width="79.4285714285714"/>
+    <col min="5" max="5" customWidth="true" width="11.5714285714286"/>
+    <col min="6" max="6" customWidth="true" width="5.14285714285714"/>
+    <col min="7" max="7" customWidth="true" width="11.0"/>
+    <col min="8" max="8" customWidth="true" width="12.7142857142857"/>
+    <col min="9" max="9" customWidth="true" width="5.85714285714286"/>
+    <col min="10" max="10" customWidth="true" width="6.0"/>
+    <col min="11" max="11" customWidth="true" width="5.85714285714286"/>
+    <col min="12" max="12" customWidth="true" width="14.2857142857143"/>
+    <col min="13" max="13" customWidth="true" width="9.42857142857143"/>
+    <col min="14" max="14" customWidth="true" width="14.4285714285714"/>
+    <col min="15" max="15" customWidth="true" width="15.5714285714286"/>
+    <col min="16" max="16" customWidth="true" width="14.4285714285714"/>
+    <col min="17" max="17" customWidth="true" width="39.4285714285714"/>
+    <col min="18" max="18" customWidth="true" width="11.7142857142857"/>
+    <col min="19" max="19" customWidth="true" width="11.8571428571429"/>
+    <col min="20" max="20" customWidth="true" width="6.42857142857143"/>
+    <col min="21" max="22" customWidth="true" width="6.57142857142857"/>
+    <col min="23" max="23" customWidth="true" width="37.1428571428571"/>
+    <col min="24" max="25" customWidth="true" width="8.0"/>
+    <col min="26" max="26" customWidth="true" width="7.71428571428571"/>
+    <col min="27" max="27" customWidth="true" width="6.28571428571429"/>
+    <col min="28" max="28" customWidth="true" width="9.28571428571429"/>
+    <col min="29" max="29" customWidth="true" width="9.71428571428571"/>
+    <col min="30" max="30" customWidth="true" width="12.8571428571429"/>
+    <col min="31" max="31" customWidth="true" width="16.1428571428571"/>
+    <col min="32" max="32" customWidth="true" width="15.4285714285714"/>
+    <col min="33" max="33" customWidth="true" width="24.5714285714286"/>
+    <col min="34" max="34" customWidth="true" width="8.57142857142857"/>
+    <col min="35" max="35" customWidth="true" width="14.7142857142857"/>
+    <col min="36" max="36" customWidth="true" width="18.5714285714286"/>
+    <col min="37" max="37" customWidth="true" width="14.1428571428571"/>
+    <col min="38" max="38" customWidth="true" width="14.7142857142857"/>
+    <col min="39" max="39" customWidth="true" width="17.4285714285714"/>
+    <col min="40" max="40" customWidth="true" width="22.0"/>
+    <col min="41" max="41" customWidth="true" width="17.5714285714286"/>
+    <col min="42" max="42" customWidth="true" width="25.2857142857143"/>
+    <col min="43" max="43" customWidth="true" width="13.0"/>
+    <col min="44" max="44" customWidth="true" width="23.7142857142857"/>
+    <col min="45" max="45" customWidth="true" width="10.0"/>
+    <col min="46" max="46" customWidth="true" width="13.0"/>
+    <col min="47" max="47" customWidth="true" width="15.5714285714286"/>
+    <col min="48" max="48" customWidth="true" width="21.1428571428571"/>
+    <col min="49" max="49" customWidth="true" width="11.5714285714286"/>
+    <col min="50" max="50" customWidth="true" width="16.7142857142857"/>
+    <col min="51" max="51" customWidth="true" width="14.0"/>
+    <col min="52" max="52" customWidth="true" width="19.4285714285714"/>
+    <col min="53" max="53" customWidth="true" width="18.8571428571429"/>
+    <col min="54" max="54" customWidth="true" width="23.2857142857143"/>
+    <col min="55" max="55" customWidth="true" width="15.5714285714286"/>
+    <col min="56" max="56" customWidth="true" width="14.2857142857143"/>
+    <col min="57" max="57" customWidth="true" width="17.0"/>
+    <col min="58" max="58" customWidth="true" width="16.2857142857143"/>
+    <col min="59" max="59" customWidth="true" width="13.5714285714286"/>
+    <col min="60" max="61" customWidth="true" width="12.7142857142857"/>
+    <col min="62" max="62" customWidth="true" width="21.8571428571429"/>
+    <col min="63" max="63" customWidth="true" width="30.5714285714286"/>
+    <col min="64" max="64" customWidth="true" width="10.0"/>
+    <col min="65" max="65" customWidth="true" width="42.5714285714286"/>
+    <col min="66" max="66" customWidth="true" width="38.1428571428571"/>
+    <col min="67" max="67" customWidth="true" width="19.4285714285714"/>
+    <col min="68" max="68" customWidth="true" width="35.4285714285714"/>
+    <col min="69" max="69" customWidth="true" width="9.57142857142857"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -6626,7 +6641,7 @@
       <c r="BP2" s="32"/>
       <c r="BQ2" s="32"/>
     </row>
-    <row r="3" ht="15.25" spans="1:69">
+    <row r="3" ht="15.75" spans="1:69">
       <c r="A3" s="33" t="s">
         <v>9</v>
       </c>
@@ -6835,7 +6850,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.25" spans="1:69">
+    <row r="4" ht="15.75" spans="1:69">
       <c r="A4" s="31">
         <v>1</v>
       </c>
@@ -6906,7 +6921,7 @@
         <v>88363222</v>
       </c>
       <c r="U4" s="17">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="V4" s="17">
         <f>IF(OR($C$2=1,$C$2=4),ROUND((((S4*U4)/100)/2),2),0)</f>
@@ -6918,7 +6933,7 @@
       </c>
       <c r="X4" s="17">
         <f>IF($C$2=2,ROUND(((S4*U4)/100),2),0)</f>
-        <v>0</v>
+        <v>67.77</v>
       </c>
       <c r="Y4" s="17">
         <f>IF($C$2=4,ROUND((((S4*U4)/100)/2),2),0)</f>
@@ -6933,11 +6948,11 @@
       </c>
       <c r="AB4" s="17">
         <f>V4+W4+X4+Y4+AA4</f>
-        <v>15.0592</v>
+        <v>82.8292</v>
       </c>
       <c r="AC4" s="17">
         <f>IF($V2=1,S4+AB4,S4)</f>
-        <v>391.5392</v>
+        <v>459.3092</v>
       </c>
       <c r="AD4" s="17">
         <v>120</v>
@@ -7104,18 +7119,18 @@
       </c>
       <c r="X5" s="42">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>67.77</v>
       </c>
       <c r="Y5" s="44"/>
       <c r="Z5" s="44"/>
       <c r="AA5" s="44"/>
       <c r="AB5" s="42">
         <f t="shared" ref="AB5:AE5" si="1">SUM(AB4:AB4)</f>
-        <v>15.0592</v>
+        <v>82.8292</v>
       </c>
       <c r="AC5" s="42">
         <f t="shared" si="1"/>
-        <v>391.5392</v>
+        <v>459.3092</v>
       </c>
       <c r="AD5" s="42">
         <f t="shared" si="1"/>
@@ -7192,73 +7207,73 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ5"/>
-  <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="8.7047619047619" defaultRowHeight="15" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" width="5.14545454545455" customWidth="1"/>
-    <col min="2" max="3" width="24.5727272727273" customWidth="1"/>
-    <col min="4" max="4" width="79.4272727272727" customWidth="1"/>
-    <col min="5" max="5" width="11.5727272727273" customWidth="1"/>
-    <col min="6" max="6" width="5.14545454545455" customWidth="1"/>
-    <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="12.7181818181818" customWidth="1"/>
-    <col min="9" max="9" width="5.85454545454545" customWidth="1"/>
-    <col min="10" max="10" width="6" customWidth="1"/>
-    <col min="11" max="11" width="5.85454545454545" customWidth="1"/>
-    <col min="12" max="12" width="14.2818181818182" customWidth="1"/>
-    <col min="13" max="13" width="9.42727272727273" customWidth="1"/>
-    <col min="14" max="14" width="14.4272727272727" customWidth="1"/>
-    <col min="15" max="15" width="15.5727272727273" customWidth="1"/>
-    <col min="16" max="16" width="14.4272727272727" customWidth="1"/>
-    <col min="17" max="17" width="39.4272727272727" customWidth="1"/>
-    <col min="18" max="18" width="11.7181818181818" customWidth="1"/>
-    <col min="19" max="19" width="11.8545454545455" customWidth="1"/>
-    <col min="20" max="20" width="6.42727272727273" customWidth="1"/>
-    <col min="21" max="22" width="6.57272727272727" customWidth="1"/>
-    <col min="23" max="23" width="37.1454545454545" customWidth="1"/>
-    <col min="24" max="25" width="8" customWidth="1"/>
-    <col min="26" max="26" width="7.71818181818182" customWidth="1"/>
-    <col min="27" max="27" width="6.28181818181818" customWidth="1"/>
-    <col min="28" max="28" width="9.28181818181818" customWidth="1"/>
-    <col min="29" max="29" width="9.71818181818182" customWidth="1"/>
-    <col min="30" max="30" width="12.8545454545455" customWidth="1"/>
-    <col min="31" max="31" width="16.1454545454545" customWidth="1"/>
-    <col min="32" max="32" width="15.4272727272727" customWidth="1"/>
-    <col min="33" max="33" width="24.5727272727273" customWidth="1"/>
-    <col min="34" max="34" width="8.57272727272727" customWidth="1"/>
-    <col min="35" max="35" width="14.7181818181818" customWidth="1"/>
-    <col min="36" max="36" width="18.5727272727273" customWidth="1"/>
-    <col min="37" max="37" width="14.1454545454545" customWidth="1"/>
-    <col min="38" max="38" width="14.7181818181818" customWidth="1"/>
-    <col min="39" max="39" width="17.4272727272727" customWidth="1"/>
-    <col min="40" max="40" width="22" customWidth="1"/>
-    <col min="41" max="41" width="17.5727272727273" customWidth="1"/>
-    <col min="42" max="42" width="25.2818181818182" customWidth="1"/>
-    <col min="43" max="43" width="13" customWidth="1"/>
-    <col min="44" max="44" width="23.7181818181818" customWidth="1"/>
-    <col min="45" max="45" width="10" customWidth="1"/>
-    <col min="46" max="46" width="13" customWidth="1"/>
-    <col min="47" max="47" width="15.5727272727273" customWidth="1"/>
-    <col min="48" max="48" width="21.1454545454545" customWidth="1"/>
-    <col min="49" max="49" width="11.5727272727273" customWidth="1"/>
-    <col min="50" max="50" width="16.7181818181818" customWidth="1"/>
-    <col min="51" max="51" width="14" customWidth="1"/>
-    <col min="52" max="52" width="19.4272727272727" customWidth="1"/>
-    <col min="53" max="53" width="18.8545454545455" customWidth="1"/>
-    <col min="54" max="54" width="23.2818181818182" customWidth="1"/>
-    <col min="55" max="55" width="15.5727272727273" customWidth="1"/>
-    <col min="56" max="56" width="14.2818181818182" customWidth="1"/>
-    <col min="57" max="57" width="17" customWidth="1"/>
-    <col min="58" max="58" width="16.2818181818182" customWidth="1"/>
-    <col min="59" max="59" width="13.5727272727273" customWidth="1"/>
-    <col min="60" max="61" width="12.7181818181818" customWidth="1"/>
-    <col min="62" max="62" width="21.8545454545455" customWidth="1"/>
-    <col min="63" max="63" width="30.5727272727273" customWidth="1"/>
-    <col min="64" max="64" width="10" customWidth="1"/>
-    <col min="65" max="65" width="42.5727272727273" customWidth="1"/>
-    <col min="66" max="66" width="38.1454545454545" customWidth="1"/>
-    <col min="67" max="67" width="19.4272727272727" customWidth="1"/>
-    <col min="68" max="68" width="35.4272727272727" customWidth="1"/>
-    <col min="69" max="69" width="9.57272727272727" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="5.14285714285714"/>
+    <col min="2" max="3" customWidth="true" width="24.5714285714286"/>
+    <col min="4" max="4" customWidth="true" width="79.4285714285714"/>
+    <col min="5" max="5" customWidth="true" width="11.5714285714286"/>
+    <col min="6" max="6" customWidth="true" width="5.14285714285714"/>
+    <col min="7" max="7" customWidth="true" width="11.0"/>
+    <col min="8" max="8" customWidth="true" width="12.7142857142857"/>
+    <col min="9" max="9" customWidth="true" width="5.85714285714286"/>
+    <col min="10" max="10" customWidth="true" width="6.0"/>
+    <col min="11" max="11" customWidth="true" width="5.85714285714286"/>
+    <col min="12" max="12" customWidth="true" width="14.2857142857143"/>
+    <col min="13" max="13" customWidth="true" width="9.42857142857143"/>
+    <col min="14" max="14" customWidth="true" width="14.4285714285714"/>
+    <col min="15" max="15" customWidth="true" width="15.5714285714286"/>
+    <col min="16" max="16" customWidth="true" width="14.4285714285714"/>
+    <col min="17" max="17" customWidth="true" width="39.4285714285714"/>
+    <col min="18" max="18" customWidth="true" width="11.7142857142857"/>
+    <col min="19" max="19" customWidth="true" width="11.8571428571429"/>
+    <col min="20" max="20" customWidth="true" width="6.42857142857143"/>
+    <col min="21" max="22" customWidth="true" width="6.57142857142857"/>
+    <col min="23" max="23" customWidth="true" width="37.1428571428571"/>
+    <col min="24" max="25" customWidth="true" width="8.0"/>
+    <col min="26" max="26" customWidth="true" width="7.71428571428571"/>
+    <col min="27" max="27" customWidth="true" width="6.28571428571429"/>
+    <col min="28" max="28" customWidth="true" width="9.28571428571429"/>
+    <col min="29" max="29" customWidth="true" width="9.71428571428571"/>
+    <col min="30" max="30" customWidth="true" width="12.8571428571429"/>
+    <col min="31" max="31" customWidth="true" width="16.1428571428571"/>
+    <col min="32" max="32" customWidth="true" width="15.4285714285714"/>
+    <col min="33" max="33" customWidth="true" width="24.5714285714286"/>
+    <col min="34" max="34" customWidth="true" width="8.57142857142857"/>
+    <col min="35" max="35" customWidth="true" width="14.7142857142857"/>
+    <col min="36" max="36" customWidth="true" width="18.5714285714286"/>
+    <col min="37" max="37" customWidth="true" width="14.1428571428571"/>
+    <col min="38" max="38" customWidth="true" width="14.7142857142857"/>
+    <col min="39" max="39" customWidth="true" width="17.4285714285714"/>
+    <col min="40" max="40" customWidth="true" width="22.0"/>
+    <col min="41" max="41" customWidth="true" width="17.5714285714286"/>
+    <col min="42" max="42" customWidth="true" width="25.2857142857143"/>
+    <col min="43" max="43" customWidth="true" width="13.0"/>
+    <col min="44" max="44" customWidth="true" width="23.7142857142857"/>
+    <col min="45" max="45" customWidth="true" width="10.0"/>
+    <col min="46" max="46" customWidth="true" width="13.0"/>
+    <col min="47" max="47" customWidth="true" width="15.5714285714286"/>
+    <col min="48" max="48" customWidth="true" width="21.1428571428571"/>
+    <col min="49" max="49" customWidth="true" width="11.5714285714286"/>
+    <col min="50" max="50" customWidth="true" width="16.7142857142857"/>
+    <col min="51" max="51" customWidth="true" width="14.0"/>
+    <col min="52" max="52" customWidth="true" width="19.4285714285714"/>
+    <col min="53" max="53" customWidth="true" width="18.8571428571429"/>
+    <col min="54" max="54" customWidth="true" width="23.2857142857143"/>
+    <col min="55" max="55" customWidth="true" width="15.5714285714286"/>
+    <col min="56" max="56" customWidth="true" width="14.2857142857143"/>
+    <col min="57" max="57" customWidth="true" width="17.0"/>
+    <col min="58" max="58" customWidth="true" width="16.2857142857143"/>
+    <col min="59" max="59" customWidth="true" width="13.5714285714286"/>
+    <col min="60" max="61" customWidth="true" width="12.7142857142857"/>
+    <col min="62" max="62" customWidth="true" width="21.8571428571429"/>
+    <col min="63" max="63" customWidth="true" width="30.5714285714286"/>
+    <col min="64" max="64" customWidth="true" width="10.0"/>
+    <col min="65" max="65" customWidth="true" width="42.5714285714286"/>
+    <col min="66" max="66" customWidth="true" width="38.1428571428571"/>
+    <col min="67" max="67" customWidth="true" width="19.4285714285714"/>
+    <col min="68" max="68" customWidth="true" width="35.4285714285714"/>
+    <col min="69" max="69" customWidth="true" width="9.57142857142857"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -7429,7 +7444,7 @@
       <c r="BP2" s="32"/>
       <c r="BQ2" s="32"/>
     </row>
-    <row r="3" ht="15.25" spans="1:69">
+    <row r="3" ht="15.75" spans="1:69">
       <c r="A3" s="33" t="s">
         <v>9</v>
       </c>
@@ -7638,7 +7653,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.25" spans="1:69">
+    <row r="4" ht="15.75" spans="1:69">
       <c r="A4" s="31">
         <v>1</v>
       </c>
@@ -7709,7 +7724,7 @@
         <v>88363222</v>
       </c>
       <c r="U4" s="17">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="V4" s="17">
         <f>IF(OR($C$2=1,$C$2=4),ROUND((((S4*U4)/100)/2),2),0)</f>
@@ -7721,7 +7736,7 @@
       </c>
       <c r="X4" s="17">
         <f>IF($C$2=2,ROUND(((S4*U4)/100),2),0)</f>
-        <v>0</v>
+        <v>68.46</v>
       </c>
       <c r="Y4" s="17">
         <f>IF($C$2=4,ROUND((((S4*U4)/100)/2),2),0)</f>
@@ -7736,11 +7751,11 @@
       </c>
       <c r="AB4" s="17">
         <f>V4+W4+X4+Y4+AA4</f>
-        <v>15.2128</v>
+        <v>83.6728</v>
       </c>
       <c r="AC4" s="17">
         <f>IF($V2=1,S4+AB4,S4)</f>
-        <v>395.5328</v>
+        <v>463.9928</v>
       </c>
       <c r="AD4" s="17">
         <v>120</v>
@@ -7907,7 +7922,7 @@
       </c>
       <c r="X5" s="42">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>68.46</v>
       </c>
       <c r="Y5" s="42">
         <f t="shared" si="0"/>
@@ -7923,11 +7938,11 @@
       </c>
       <c r="AB5" s="42">
         <f t="shared" si="0"/>
-        <v>15.2128</v>
+        <v>83.6728</v>
       </c>
       <c r="AC5" s="42">
         <f t="shared" si="0"/>
-        <v>395.5328</v>
+        <v>463.9928</v>
       </c>
       <c r="AD5" s="42">
         <f t="shared" si="0"/>
@@ -8007,73 +8022,73 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ5"/>
-  <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="8.7047619047619" defaultRowHeight="15" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" width="5.14545454545455" customWidth="1"/>
-    <col min="2" max="3" width="24.5727272727273" customWidth="1"/>
-    <col min="4" max="4" width="79.4272727272727" customWidth="1"/>
-    <col min="5" max="5" width="11.5727272727273" customWidth="1"/>
-    <col min="6" max="6" width="5.14545454545455" customWidth="1"/>
-    <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="12.7181818181818" customWidth="1"/>
-    <col min="9" max="9" width="5.85454545454545" customWidth="1"/>
-    <col min="10" max="10" width="6" customWidth="1"/>
-    <col min="11" max="11" width="5.85454545454545" customWidth="1"/>
-    <col min="12" max="12" width="14.2818181818182" customWidth="1"/>
-    <col min="13" max="13" width="9.42727272727273" customWidth="1"/>
-    <col min="14" max="14" width="14.4272727272727" customWidth="1"/>
-    <col min="15" max="15" width="15.5727272727273" customWidth="1"/>
-    <col min="16" max="16" width="14.4272727272727" customWidth="1"/>
-    <col min="17" max="17" width="39.4272727272727" customWidth="1"/>
-    <col min="18" max="18" width="11.7181818181818" customWidth="1"/>
-    <col min="19" max="19" width="11.8545454545455" customWidth="1"/>
-    <col min="20" max="20" width="6.42727272727273" customWidth="1"/>
-    <col min="21" max="22" width="6.57272727272727" customWidth="1"/>
-    <col min="23" max="23" width="37.1454545454545" customWidth="1"/>
-    <col min="24" max="25" width="8" customWidth="1"/>
-    <col min="26" max="26" width="7.71818181818182" customWidth="1"/>
-    <col min="27" max="27" width="6.28181818181818" customWidth="1"/>
-    <col min="28" max="28" width="9.28181818181818" customWidth="1"/>
-    <col min="29" max="29" width="9.71818181818182" customWidth="1"/>
-    <col min="30" max="30" width="12.8545454545455" customWidth="1"/>
-    <col min="31" max="31" width="16.1454545454545" customWidth="1"/>
-    <col min="32" max="32" width="15.4272727272727" customWidth="1"/>
-    <col min="33" max="33" width="24.5727272727273" customWidth="1"/>
-    <col min="34" max="34" width="8.57272727272727" customWidth="1"/>
-    <col min="35" max="35" width="14.7181818181818" customWidth="1"/>
-    <col min="36" max="36" width="18.5727272727273" customWidth="1"/>
-    <col min="37" max="37" width="14.1454545454545" customWidth="1"/>
-    <col min="38" max="38" width="14.7181818181818" customWidth="1"/>
-    <col min="39" max="39" width="17.4272727272727" customWidth="1"/>
-    <col min="40" max="40" width="22" customWidth="1"/>
-    <col min="41" max="41" width="17.5727272727273" customWidth="1"/>
-    <col min="42" max="42" width="25.2818181818182" customWidth="1"/>
-    <col min="43" max="43" width="13" customWidth="1"/>
-    <col min="44" max="44" width="23.7181818181818" customWidth="1"/>
-    <col min="45" max="45" width="10" customWidth="1"/>
-    <col min="46" max="46" width="13" customWidth="1"/>
-    <col min="47" max="47" width="15.5727272727273" customWidth="1"/>
-    <col min="48" max="48" width="21.1454545454545" customWidth="1"/>
-    <col min="49" max="49" width="11.5727272727273" customWidth="1"/>
-    <col min="50" max="50" width="16.7181818181818" customWidth="1"/>
-    <col min="51" max="51" width="14" customWidth="1"/>
-    <col min="52" max="52" width="19.4272727272727" customWidth="1"/>
-    <col min="53" max="53" width="18.8545454545455" customWidth="1"/>
-    <col min="54" max="54" width="23.2818181818182" customWidth="1"/>
-    <col min="55" max="55" width="15.5727272727273" customWidth="1"/>
-    <col min="56" max="56" width="14.2818181818182" customWidth="1"/>
-    <col min="57" max="57" width="17" customWidth="1"/>
-    <col min="58" max="58" width="16.2818181818182" customWidth="1"/>
-    <col min="59" max="59" width="13.5727272727273" customWidth="1"/>
-    <col min="60" max="61" width="12.7181818181818" customWidth="1"/>
-    <col min="62" max="62" width="21.8545454545455" customWidth="1"/>
-    <col min="63" max="63" width="30.5727272727273" customWidth="1"/>
-    <col min="64" max="64" width="10" customWidth="1"/>
-    <col min="65" max="65" width="42.5727272727273" customWidth="1"/>
-    <col min="66" max="66" width="38.1454545454545" customWidth="1"/>
-    <col min="67" max="67" width="19.4272727272727" customWidth="1"/>
-    <col min="68" max="68" width="35.4272727272727" customWidth="1"/>
-    <col min="69" max="69" width="9.57272727272727" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="5.14285714285714"/>
+    <col min="2" max="3" customWidth="true" width="24.5714285714286"/>
+    <col min="4" max="4" customWidth="true" width="79.4285714285714"/>
+    <col min="5" max="5" customWidth="true" width="11.5714285714286"/>
+    <col min="6" max="6" customWidth="true" width="5.14285714285714"/>
+    <col min="7" max="7" customWidth="true" width="11.0"/>
+    <col min="8" max="8" customWidth="true" width="12.7142857142857"/>
+    <col min="9" max="9" customWidth="true" width="5.85714285714286"/>
+    <col min="10" max="10" customWidth="true" width="6.0"/>
+    <col min="11" max="11" customWidth="true" width="5.85714285714286"/>
+    <col min="12" max="12" customWidth="true" width="14.2857142857143"/>
+    <col min="13" max="13" customWidth="true" width="9.42857142857143"/>
+    <col min="14" max="14" customWidth="true" width="14.4285714285714"/>
+    <col min="15" max="15" customWidth="true" width="15.5714285714286"/>
+    <col min="16" max="16" customWidth="true" width="14.4285714285714"/>
+    <col min="17" max="17" customWidth="true" width="39.4285714285714"/>
+    <col min="18" max="18" customWidth="true" width="11.7142857142857"/>
+    <col min="19" max="19" customWidth="true" width="11.8571428571429"/>
+    <col min="20" max="20" customWidth="true" width="6.42857142857143"/>
+    <col min="21" max="22" customWidth="true" width="6.57142857142857"/>
+    <col min="23" max="23" customWidth="true" width="37.1428571428571"/>
+    <col min="24" max="25" customWidth="true" width="8.0"/>
+    <col min="26" max="26" customWidth="true" width="7.71428571428571"/>
+    <col min="27" max="27" customWidth="true" width="6.28571428571429"/>
+    <col min="28" max="28" customWidth="true" width="9.28571428571429"/>
+    <col min="29" max="29" customWidth="true" width="9.71428571428571"/>
+    <col min="30" max="30" customWidth="true" width="12.8571428571429"/>
+    <col min="31" max="31" customWidth="true" width="16.1428571428571"/>
+    <col min="32" max="32" customWidth="true" width="15.4285714285714"/>
+    <col min="33" max="33" customWidth="true" width="24.5714285714286"/>
+    <col min="34" max="34" customWidth="true" width="8.57142857142857"/>
+    <col min="35" max="35" customWidth="true" width="14.7142857142857"/>
+    <col min="36" max="36" customWidth="true" width="18.5714285714286"/>
+    <col min="37" max="37" customWidth="true" width="14.1428571428571"/>
+    <col min="38" max="38" customWidth="true" width="14.7142857142857"/>
+    <col min="39" max="39" customWidth="true" width="17.4285714285714"/>
+    <col min="40" max="40" customWidth="true" width="22.0"/>
+    <col min="41" max="41" customWidth="true" width="17.5714285714286"/>
+    <col min="42" max="42" customWidth="true" width="25.2857142857143"/>
+    <col min="43" max="43" customWidth="true" width="13.0"/>
+    <col min="44" max="44" customWidth="true" width="23.7142857142857"/>
+    <col min="45" max="45" customWidth="true" width="10.0"/>
+    <col min="46" max="46" customWidth="true" width="13.0"/>
+    <col min="47" max="47" customWidth="true" width="15.5714285714286"/>
+    <col min="48" max="48" customWidth="true" width="21.1428571428571"/>
+    <col min="49" max="49" customWidth="true" width="11.5714285714286"/>
+    <col min="50" max="50" customWidth="true" width="16.7142857142857"/>
+    <col min="51" max="51" customWidth="true" width="14.0"/>
+    <col min="52" max="52" customWidth="true" width="19.4285714285714"/>
+    <col min="53" max="53" customWidth="true" width="18.8571428571429"/>
+    <col min="54" max="54" customWidth="true" width="23.2857142857143"/>
+    <col min="55" max="55" customWidth="true" width="15.5714285714286"/>
+    <col min="56" max="56" customWidth="true" width="14.2857142857143"/>
+    <col min="57" max="57" customWidth="true" width="17.0"/>
+    <col min="58" max="58" customWidth="true" width="16.2857142857143"/>
+    <col min="59" max="59" customWidth="true" width="13.5714285714286"/>
+    <col min="60" max="61" customWidth="true" width="12.7142857142857"/>
+    <col min="62" max="62" customWidth="true" width="21.8571428571429"/>
+    <col min="63" max="63" customWidth="true" width="30.5714285714286"/>
+    <col min="64" max="64" customWidth="true" width="10.0"/>
+    <col min="65" max="65" customWidth="true" width="42.5714285714286"/>
+    <col min="66" max="66" customWidth="true" width="38.1428571428571"/>
+    <col min="67" max="67" customWidth="true" width="19.4285714285714"/>
+    <col min="68" max="68" customWidth="true" width="35.4285714285714"/>
+    <col min="69" max="69" customWidth="true" width="9.57142857142857"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -8244,7 +8259,7 @@
       <c r="BP2" s="32"/>
       <c r="BQ2" s="32"/>
     </row>
-    <row r="3" ht="15.25" spans="1:69">
+    <row r="3" ht="15.75" spans="1:69">
       <c r="A3" s="33" t="s">
         <v>9</v>
       </c>
@@ -8453,7 +8468,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.25" spans="1:69">
+    <row r="4" ht="15.75" spans="1:69">
       <c r="A4" s="31">
         <v>1</v>
       </c>
@@ -8524,7 +8539,7 @@
         <v>88363222</v>
       </c>
       <c r="U4" s="17">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="V4" s="17">
         <f>IF(OR($C$2=1,$C$2=4),ROUND((((S4*U4)/100)/2),2),0)</f>
@@ -8536,7 +8551,7 @@
       </c>
       <c r="X4" s="17">
         <f>IF($C$2=2,ROUND(((S4*U4)/100),2),0)</f>
-        <v>0</v>
+        <v>68.46</v>
       </c>
       <c r="Y4" s="17">
         <f>IF($C$2=4,ROUND((((S4*U4)/100)/2),2),0)</f>
@@ -8551,11 +8566,11 @@
       </c>
       <c r="AB4" s="17">
         <f>V4+W4+X4+Y4+AA4</f>
-        <v>15.2128</v>
+        <v>83.6728</v>
       </c>
       <c r="AC4" s="17">
         <f>IF($V2=1,S4+AB4,S4)</f>
-        <v>395.5328</v>
+        <v>463.9928</v>
       </c>
       <c r="AD4" s="17">
         <v>120</v>
@@ -8722,7 +8737,7 @@
       </c>
       <c r="X5" s="42">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>68.46</v>
       </c>
       <c r="Y5" s="42">
         <f t="shared" si="0"/>
@@ -8738,11 +8753,11 @@
       </c>
       <c r="AB5" s="42">
         <f t="shared" si="0"/>
-        <v>15.2128</v>
+        <v>83.6728</v>
       </c>
       <c r="AC5" s="42">
         <f t="shared" si="0"/>
-        <v>395.5328</v>
+        <v>463.9928</v>
       </c>
       <c r="AD5" s="42">
         <f t="shared" si="0"/>
@@ -8822,73 +8837,73 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ5"/>
-  <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="8.7047619047619" defaultRowHeight="15" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" width="5.14545454545455" customWidth="1"/>
-    <col min="2" max="3" width="22" customWidth="1"/>
-    <col min="4" max="4" width="79.4272727272727" customWidth="1"/>
-    <col min="5" max="5" width="11.5727272727273" customWidth="1"/>
-    <col min="6" max="6" width="5.14545454545455" customWidth="1"/>
-    <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="12.7181818181818" customWidth="1"/>
-    <col min="9" max="9" width="5.85454545454545" customWidth="1"/>
-    <col min="10" max="10" width="6" customWidth="1"/>
-    <col min="11" max="11" width="5.85454545454545" customWidth="1"/>
-    <col min="12" max="12" width="14.2818181818182" customWidth="1"/>
-    <col min="13" max="13" width="9.42727272727273" customWidth="1"/>
-    <col min="14" max="14" width="14.4272727272727" customWidth="1"/>
-    <col min="15" max="15" width="15.5727272727273" customWidth="1"/>
-    <col min="16" max="16" width="14.4272727272727" customWidth="1"/>
-    <col min="17" max="17" width="39.4272727272727" customWidth="1"/>
-    <col min="18" max="18" width="11.7181818181818" customWidth="1"/>
-    <col min="19" max="19" width="11.8545454545455" customWidth="1"/>
-    <col min="20" max="20" width="6.42727272727273" customWidth="1"/>
-    <col min="21" max="22" width="6.57272727272727" customWidth="1"/>
-    <col min="23" max="23" width="37.1454545454545" customWidth="1"/>
-    <col min="24" max="25" width="8" customWidth="1"/>
-    <col min="26" max="26" width="7.71818181818182" customWidth="1"/>
-    <col min="27" max="27" width="6.28181818181818" customWidth="1"/>
-    <col min="28" max="28" width="9.28181818181818" customWidth="1"/>
-    <col min="29" max="29" width="9.71818181818182" customWidth="1"/>
-    <col min="30" max="30" width="12.8545454545455" customWidth="1"/>
-    <col min="31" max="31" width="16.1454545454545" customWidth="1"/>
-    <col min="32" max="32" width="15.4272727272727" customWidth="1"/>
-    <col min="33" max="33" width="24.5727272727273" customWidth="1"/>
-    <col min="34" max="34" width="8.57272727272727" customWidth="1"/>
-    <col min="35" max="35" width="14.7181818181818" customWidth="1"/>
-    <col min="36" max="36" width="18.5727272727273" customWidth="1"/>
-    <col min="37" max="37" width="14.1454545454545" customWidth="1"/>
-    <col min="38" max="38" width="14.7181818181818" customWidth="1"/>
-    <col min="39" max="39" width="17.4272727272727" customWidth="1"/>
-    <col min="40" max="40" width="22" customWidth="1"/>
-    <col min="41" max="41" width="17.5727272727273" customWidth="1"/>
-    <col min="42" max="42" width="25.2818181818182" customWidth="1"/>
-    <col min="43" max="43" width="13" customWidth="1"/>
-    <col min="44" max="44" width="23.7181818181818" customWidth="1"/>
-    <col min="45" max="45" width="10" customWidth="1"/>
-    <col min="46" max="46" width="13" customWidth="1"/>
-    <col min="47" max="47" width="15.5727272727273" customWidth="1"/>
-    <col min="48" max="48" width="21.1454545454545" customWidth="1"/>
-    <col min="49" max="49" width="11.5727272727273" customWidth="1"/>
-    <col min="50" max="50" width="16.7181818181818" customWidth="1"/>
-    <col min="51" max="51" width="14" customWidth="1"/>
-    <col min="52" max="52" width="19.4272727272727" customWidth="1"/>
-    <col min="53" max="53" width="18.8545454545455" customWidth="1"/>
-    <col min="54" max="54" width="23.2818181818182" customWidth="1"/>
-    <col min="55" max="55" width="15.5727272727273" customWidth="1"/>
-    <col min="56" max="56" width="14.2818181818182" customWidth="1"/>
-    <col min="57" max="57" width="17" customWidth="1"/>
-    <col min="58" max="58" width="16.2818181818182" customWidth="1"/>
-    <col min="59" max="59" width="13.5727272727273" customWidth="1"/>
-    <col min="60" max="61" width="12.7181818181818" customWidth="1"/>
-    <col min="62" max="62" width="21.8545454545455" customWidth="1"/>
-    <col min="63" max="63" width="30.5727272727273" customWidth="1"/>
-    <col min="64" max="64" width="10" customWidth="1"/>
-    <col min="65" max="65" width="42.5727272727273" customWidth="1"/>
-    <col min="66" max="66" width="38.1454545454545" customWidth="1"/>
-    <col min="67" max="67" width="19.4272727272727" customWidth="1"/>
-    <col min="68" max="68" width="35.4272727272727" customWidth="1"/>
-    <col min="69" max="69" width="9.57272727272727" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="5.14285714285714"/>
+    <col min="2" max="3" customWidth="true" width="22.0"/>
+    <col min="4" max="4" customWidth="true" width="79.4285714285714"/>
+    <col min="5" max="5" customWidth="true" width="11.5714285714286"/>
+    <col min="6" max="6" customWidth="true" width="5.14285714285714"/>
+    <col min="7" max="7" customWidth="true" width="11.0"/>
+    <col min="8" max="8" customWidth="true" width="12.7142857142857"/>
+    <col min="9" max="9" customWidth="true" width="5.85714285714286"/>
+    <col min="10" max="10" customWidth="true" width="6.0"/>
+    <col min="11" max="11" customWidth="true" width="5.85714285714286"/>
+    <col min="12" max="12" customWidth="true" width="14.2857142857143"/>
+    <col min="13" max="13" customWidth="true" width="9.42857142857143"/>
+    <col min="14" max="14" customWidth="true" width="14.4285714285714"/>
+    <col min="15" max="15" customWidth="true" width="15.5714285714286"/>
+    <col min="16" max="16" customWidth="true" width="14.4285714285714"/>
+    <col min="17" max="17" customWidth="true" width="39.4285714285714"/>
+    <col min="18" max="18" customWidth="true" width="11.7142857142857"/>
+    <col min="19" max="19" customWidth="true" width="11.8571428571429"/>
+    <col min="20" max="20" customWidth="true" width="6.42857142857143"/>
+    <col min="21" max="22" customWidth="true" width="6.57142857142857"/>
+    <col min="23" max="23" customWidth="true" width="37.1428571428571"/>
+    <col min="24" max="25" customWidth="true" width="8.0"/>
+    <col min="26" max="26" customWidth="true" width="7.71428571428571"/>
+    <col min="27" max="27" customWidth="true" width="6.28571428571429"/>
+    <col min="28" max="28" customWidth="true" width="9.28571428571429"/>
+    <col min="29" max="29" customWidth="true" width="9.71428571428571"/>
+    <col min="30" max="30" customWidth="true" width="12.8571428571429"/>
+    <col min="31" max="31" customWidth="true" width="16.1428571428571"/>
+    <col min="32" max="32" customWidth="true" width="15.4285714285714"/>
+    <col min="33" max="33" customWidth="true" width="24.5714285714286"/>
+    <col min="34" max="34" customWidth="true" width="8.57142857142857"/>
+    <col min="35" max="35" customWidth="true" width="14.7142857142857"/>
+    <col min="36" max="36" customWidth="true" width="18.5714285714286"/>
+    <col min="37" max="37" customWidth="true" width="14.1428571428571"/>
+    <col min="38" max="38" customWidth="true" width="14.7142857142857"/>
+    <col min="39" max="39" customWidth="true" width="17.4285714285714"/>
+    <col min="40" max="40" customWidth="true" width="22.0"/>
+    <col min="41" max="41" customWidth="true" width="17.5714285714286"/>
+    <col min="42" max="42" customWidth="true" width="25.2857142857143"/>
+    <col min="43" max="43" customWidth="true" width="13.0"/>
+    <col min="44" max="44" customWidth="true" width="23.7142857142857"/>
+    <col min="45" max="45" customWidth="true" width="10.0"/>
+    <col min="46" max="46" customWidth="true" width="13.0"/>
+    <col min="47" max="47" customWidth="true" width="15.5714285714286"/>
+    <col min="48" max="48" customWidth="true" width="21.1428571428571"/>
+    <col min="49" max="49" customWidth="true" width="11.5714285714286"/>
+    <col min="50" max="50" customWidth="true" width="16.7142857142857"/>
+    <col min="51" max="51" customWidth="true" width="14.0"/>
+    <col min="52" max="52" customWidth="true" width="19.4285714285714"/>
+    <col min="53" max="53" customWidth="true" width="18.8571428571429"/>
+    <col min="54" max="54" customWidth="true" width="23.2857142857143"/>
+    <col min="55" max="55" customWidth="true" width="15.5714285714286"/>
+    <col min="56" max="56" customWidth="true" width="14.2857142857143"/>
+    <col min="57" max="57" customWidth="true" width="17.0"/>
+    <col min="58" max="58" customWidth="true" width="16.2857142857143"/>
+    <col min="59" max="59" customWidth="true" width="13.5714285714286"/>
+    <col min="60" max="61" customWidth="true" width="12.7142857142857"/>
+    <col min="62" max="62" customWidth="true" width="21.8571428571429"/>
+    <col min="63" max="63" customWidth="true" width="30.5714285714286"/>
+    <col min="64" max="64" customWidth="true" width="10.0"/>
+    <col min="65" max="65" customWidth="true" width="42.5714285714286"/>
+    <col min="66" max="66" customWidth="true" width="38.1428571428571"/>
+    <col min="67" max="67" customWidth="true" width="19.4285714285714"/>
+    <col min="68" max="68" customWidth="true" width="35.4285714285714"/>
+    <col min="69" max="69" customWidth="true" width="9.57142857142857"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -9059,7 +9074,7 @@
       <c r="BP2" s="32"/>
       <c r="BQ2" s="32"/>
     </row>
-    <row r="3" ht="15.25" spans="1:69">
+    <row r="3" ht="15.75" spans="1:69">
       <c r="A3" s="33" t="s">
         <v>9</v>
       </c>
@@ -9268,7 +9283,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.25" spans="1:69">
+    <row r="4" ht="15.75" spans="1:69">
       <c r="A4" s="31">
         <v>1</v>
       </c>
@@ -9339,7 +9354,7 @@
         <v>88363222</v>
       </c>
       <c r="U4" s="17">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="V4" s="17">
         <f>IF(OR($C$2=1,$C$2=4),ROUND((((S4*U4)/100)/2),2),0)</f>
@@ -9351,7 +9366,7 @@
       </c>
       <c r="X4" s="17">
         <f>IF($C$2=2,ROUND(((S4*U4)/100),2),0)</f>
-        <v>0</v>
+        <v>67.77</v>
       </c>
       <c r="Y4" s="17">
         <f>IF($C$2=4,ROUND((((S4*U4)/100)/2),2),0)</f>
@@ -9366,11 +9381,11 @@
       </c>
       <c r="AB4" s="17">
         <f>V4+W4+X4+Y4+AA4</f>
-        <v>15.0592</v>
+        <v>82.8292</v>
       </c>
       <c r="AC4" s="17">
         <f>IF($V2=1,S4+AB4,S4)</f>
-        <v>391.5392</v>
+        <v>459.3092</v>
       </c>
       <c r="AD4" s="17">
         <v>120</v>
@@ -9537,18 +9552,18 @@
       </c>
       <c r="X5" s="42">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>67.77</v>
       </c>
       <c r="Y5" s="44"/>
       <c r="Z5" s="44"/>
       <c r="AA5" s="44"/>
       <c r="AB5" s="42">
         <f t="shared" ref="AB5:AE5" si="1">SUM(AB4:AB4)</f>
-        <v>15.0592</v>
+        <v>82.8292</v>
       </c>
       <c r="AC5" s="42">
         <f t="shared" si="1"/>
-        <v>391.5392</v>
+        <v>459.3092</v>
       </c>
       <c r="AD5" s="42">
         <f t="shared" si="1"/>
@@ -9625,73 +9640,73 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ5"/>
-  <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="8.7047619047619" defaultRowHeight="15" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" width="5.14545454545455" customWidth="1"/>
-    <col min="2" max="3" width="22" customWidth="1"/>
-    <col min="4" max="4" width="79.4272727272727" customWidth="1"/>
-    <col min="5" max="5" width="11.5727272727273" customWidth="1"/>
-    <col min="6" max="6" width="5.14545454545455" customWidth="1"/>
-    <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="12.7181818181818" customWidth="1"/>
-    <col min="9" max="9" width="5.85454545454545" customWidth="1"/>
-    <col min="10" max="10" width="6" customWidth="1"/>
-    <col min="11" max="11" width="5.85454545454545" customWidth="1"/>
-    <col min="12" max="12" width="14.2818181818182" customWidth="1"/>
-    <col min="13" max="13" width="9.42727272727273" customWidth="1"/>
-    <col min="14" max="14" width="14.4272727272727" customWidth="1"/>
-    <col min="15" max="15" width="15.5727272727273" customWidth="1"/>
-    <col min="16" max="16" width="14.4272727272727" customWidth="1"/>
-    <col min="17" max="17" width="39.4272727272727" customWidth="1"/>
-    <col min="18" max="18" width="11.7181818181818" customWidth="1"/>
-    <col min="19" max="19" width="11.8545454545455" customWidth="1"/>
-    <col min="20" max="20" width="6.42727272727273" customWidth="1"/>
-    <col min="21" max="22" width="6.57272727272727" customWidth="1"/>
-    <col min="23" max="23" width="37.1454545454545" customWidth="1"/>
-    <col min="24" max="25" width="8" customWidth="1"/>
-    <col min="26" max="26" width="7.71818181818182" customWidth="1"/>
-    <col min="27" max="27" width="6.28181818181818" customWidth="1"/>
-    <col min="28" max="28" width="9.28181818181818" customWidth="1"/>
-    <col min="29" max="29" width="9.71818181818182" customWidth="1"/>
-    <col min="30" max="30" width="12.8545454545455" customWidth="1"/>
-    <col min="31" max="31" width="16.1454545454545" customWidth="1"/>
-    <col min="32" max="32" width="15.4272727272727" customWidth="1"/>
-    <col min="33" max="33" width="24.5727272727273" customWidth="1"/>
-    <col min="34" max="34" width="8.57272727272727" customWidth="1"/>
-    <col min="35" max="35" width="14.7181818181818" customWidth="1"/>
-    <col min="36" max="36" width="18.5727272727273" customWidth="1"/>
-    <col min="37" max="37" width="14.1454545454545" customWidth="1"/>
-    <col min="38" max="38" width="14.7181818181818" customWidth="1"/>
-    <col min="39" max="39" width="17.4272727272727" customWidth="1"/>
-    <col min="40" max="40" width="22" customWidth="1"/>
-    <col min="41" max="41" width="17.5727272727273" customWidth="1"/>
-    <col min="42" max="42" width="25.2818181818182" customWidth="1"/>
-    <col min="43" max="43" width="13" customWidth="1"/>
-    <col min="44" max="44" width="23.7181818181818" customWidth="1"/>
-    <col min="45" max="45" width="10" customWidth="1"/>
-    <col min="46" max="46" width="13" customWidth="1"/>
-    <col min="47" max="47" width="15.5727272727273" customWidth="1"/>
-    <col min="48" max="48" width="21.1454545454545" customWidth="1"/>
-    <col min="49" max="49" width="11.5727272727273" customWidth="1"/>
-    <col min="50" max="50" width="16.7181818181818" customWidth="1"/>
-    <col min="51" max="51" width="14" customWidth="1"/>
-    <col min="52" max="52" width="19.4272727272727" customWidth="1"/>
-    <col min="53" max="53" width="18.8545454545455" customWidth="1"/>
-    <col min="54" max="54" width="23.2818181818182" customWidth="1"/>
-    <col min="55" max="55" width="15.5727272727273" customWidth="1"/>
-    <col min="56" max="56" width="14.2818181818182" customWidth="1"/>
-    <col min="57" max="57" width="17" customWidth="1"/>
-    <col min="58" max="58" width="16.2818181818182" customWidth="1"/>
-    <col min="59" max="59" width="13.5727272727273" customWidth="1"/>
-    <col min="60" max="61" width="12.7181818181818" customWidth="1"/>
-    <col min="62" max="62" width="21.8545454545455" customWidth="1"/>
-    <col min="63" max="63" width="30.5727272727273" customWidth="1"/>
-    <col min="64" max="64" width="10" customWidth="1"/>
-    <col min="65" max="65" width="42.5727272727273" customWidth="1"/>
-    <col min="66" max="66" width="38.1454545454545" customWidth="1"/>
-    <col min="67" max="67" width="19.4272727272727" customWidth="1"/>
-    <col min="68" max="68" width="35.4272727272727" customWidth="1"/>
-    <col min="69" max="69" width="9.57272727272727" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="5.14285714285714"/>
+    <col min="2" max="3" customWidth="true" width="22.0"/>
+    <col min="4" max="4" customWidth="true" width="79.4285714285714"/>
+    <col min="5" max="5" customWidth="true" width="11.5714285714286"/>
+    <col min="6" max="6" customWidth="true" width="5.14285714285714"/>
+    <col min="7" max="7" customWidth="true" width="11.0"/>
+    <col min="8" max="8" customWidth="true" width="12.7142857142857"/>
+    <col min="9" max="9" customWidth="true" width="5.85714285714286"/>
+    <col min="10" max="10" customWidth="true" width="6.0"/>
+    <col min="11" max="11" customWidth="true" width="5.85714285714286"/>
+    <col min="12" max="12" customWidth="true" width="14.2857142857143"/>
+    <col min="13" max="13" customWidth="true" width="9.42857142857143"/>
+    <col min="14" max="14" customWidth="true" width="14.4285714285714"/>
+    <col min="15" max="15" customWidth="true" width="15.5714285714286"/>
+    <col min="16" max="16" customWidth="true" width="14.4285714285714"/>
+    <col min="17" max="17" customWidth="true" width="39.4285714285714"/>
+    <col min="18" max="18" customWidth="true" width="11.7142857142857"/>
+    <col min="19" max="19" customWidth="true" width="11.8571428571429"/>
+    <col min="20" max="20" customWidth="true" width="6.42857142857143"/>
+    <col min="21" max="22" customWidth="true" width="6.57142857142857"/>
+    <col min="23" max="23" customWidth="true" width="37.1428571428571"/>
+    <col min="24" max="25" customWidth="true" width="8.0"/>
+    <col min="26" max="26" customWidth="true" width="7.71428571428571"/>
+    <col min="27" max="27" customWidth="true" width="6.28571428571429"/>
+    <col min="28" max="28" customWidth="true" width="9.28571428571429"/>
+    <col min="29" max="29" customWidth="true" width="9.71428571428571"/>
+    <col min="30" max="30" customWidth="true" width="12.8571428571429"/>
+    <col min="31" max="31" customWidth="true" width="16.1428571428571"/>
+    <col min="32" max="32" customWidth="true" width="15.4285714285714"/>
+    <col min="33" max="33" customWidth="true" width="24.5714285714286"/>
+    <col min="34" max="34" customWidth="true" width="8.57142857142857"/>
+    <col min="35" max="35" customWidth="true" width="14.7142857142857"/>
+    <col min="36" max="36" customWidth="true" width="18.5714285714286"/>
+    <col min="37" max="37" customWidth="true" width="14.1428571428571"/>
+    <col min="38" max="38" customWidth="true" width="14.7142857142857"/>
+    <col min="39" max="39" customWidth="true" width="17.4285714285714"/>
+    <col min="40" max="40" customWidth="true" width="22.0"/>
+    <col min="41" max="41" customWidth="true" width="17.5714285714286"/>
+    <col min="42" max="42" customWidth="true" width="25.2857142857143"/>
+    <col min="43" max="43" customWidth="true" width="13.0"/>
+    <col min="44" max="44" customWidth="true" width="23.7142857142857"/>
+    <col min="45" max="45" customWidth="true" width="10.0"/>
+    <col min="46" max="46" customWidth="true" width="13.0"/>
+    <col min="47" max="47" customWidth="true" width="15.5714285714286"/>
+    <col min="48" max="48" customWidth="true" width="21.1428571428571"/>
+    <col min="49" max="49" customWidth="true" width="11.5714285714286"/>
+    <col min="50" max="50" customWidth="true" width="16.7142857142857"/>
+    <col min="51" max="51" customWidth="true" width="14.0"/>
+    <col min="52" max="52" customWidth="true" width="19.4285714285714"/>
+    <col min="53" max="53" customWidth="true" width="18.8571428571429"/>
+    <col min="54" max="54" customWidth="true" width="23.2857142857143"/>
+    <col min="55" max="55" customWidth="true" width="15.5714285714286"/>
+    <col min="56" max="56" customWidth="true" width="14.2857142857143"/>
+    <col min="57" max="57" customWidth="true" width="17.0"/>
+    <col min="58" max="58" customWidth="true" width="16.2857142857143"/>
+    <col min="59" max="59" customWidth="true" width="13.5714285714286"/>
+    <col min="60" max="61" customWidth="true" width="12.7142857142857"/>
+    <col min="62" max="62" customWidth="true" width="21.8571428571429"/>
+    <col min="63" max="63" customWidth="true" width="30.5714285714286"/>
+    <col min="64" max="64" customWidth="true" width="10.0"/>
+    <col min="65" max="65" customWidth="true" width="42.5714285714286"/>
+    <col min="66" max="66" customWidth="true" width="38.1428571428571"/>
+    <col min="67" max="67" customWidth="true" width="19.4285714285714"/>
+    <col min="68" max="68" customWidth="true" width="35.4285714285714"/>
+    <col min="69" max="69" customWidth="true" width="9.57142857142857"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -9862,7 +9877,7 @@
       <c r="BP2" s="32"/>
       <c r="BQ2" s="32"/>
     </row>
-    <row r="3" ht="15.25" spans="1:69">
+    <row r="3" ht="15.75" spans="1:69">
       <c r="A3" s="33" t="s">
         <v>9</v>
       </c>
@@ -10071,7 +10086,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.25" spans="1:69">
+    <row r="4" ht="15.75" spans="1:69">
       <c r="A4" s="31">
         <v>1</v>
       </c>
@@ -10142,7 +10157,7 @@
         <v>88363222</v>
       </c>
       <c r="U4" s="17">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="V4" s="17">
         <f>IF(OR($C$2=1,$C$2=4),ROUND((((S4*U4)/100)/2),2),0)</f>
@@ -10154,7 +10169,7 @@
       </c>
       <c r="X4" s="17">
         <f>IF($C$2=2,ROUND(((S4*U4)/100),2),0)</f>
-        <v>0</v>
+        <v>67.77</v>
       </c>
       <c r="Y4" s="17">
         <f>IF($C$2=4,ROUND((((S4*U4)/100)/2),2),0)</f>
@@ -10169,11 +10184,11 @@
       </c>
       <c r="AB4" s="17">
         <f>V4+W4+X4+Y4+AA4</f>
-        <v>15.0592</v>
+        <v>82.8292</v>
       </c>
       <c r="AC4" s="17">
         <f>IF($V2=1,S4+AB4,S4)</f>
-        <v>391.5392</v>
+        <v>459.3092</v>
       </c>
       <c r="AD4" s="17">
         <v>120</v>
@@ -10340,18 +10355,18 @@
       </c>
       <c r="X5" s="42">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>67.77</v>
       </c>
       <c r="Y5" s="44"/>
       <c r="Z5" s="44"/>
       <c r="AA5" s="44"/>
       <c r="AB5" s="42">
         <f t="shared" ref="AB5:AE5" si="1">SUM(AB4:AB4)</f>
-        <v>15.0592</v>
+        <v>82.8292</v>
       </c>
       <c r="AC5" s="42">
         <f t="shared" si="1"/>
-        <v>391.5392</v>
+        <v>459.3092</v>
       </c>
       <c r="AD5" s="42">
         <f t="shared" si="1"/>
@@ -10428,74 +10443,74 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ5"/>
-  <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="8.7047619047619" defaultRowHeight="15" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" width="5.14545454545455" customWidth="1"/>
-    <col min="2" max="2" width="21.8545454545455" customWidth="1"/>
-    <col min="3" max="3" width="27.5727272727273" customWidth="1"/>
-    <col min="4" max="4" width="79.4272727272727" customWidth="1"/>
-    <col min="5" max="5" width="11.5727272727273" customWidth="1"/>
-    <col min="6" max="6" width="5.14545454545455" customWidth="1"/>
-    <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="12.7181818181818" customWidth="1"/>
-    <col min="9" max="10" width="5.85454545454545" customWidth="1"/>
-    <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="14.2818181818182" customWidth="1"/>
-    <col min="13" max="13" width="9.42727272727273" customWidth="1"/>
-    <col min="14" max="14" width="14.2818181818182" customWidth="1"/>
-    <col min="15" max="15" width="15.5727272727273" customWidth="1"/>
-    <col min="16" max="16" width="14.4272727272727" customWidth="1"/>
-    <col min="17" max="17" width="39.4272727272727" customWidth="1"/>
-    <col min="18" max="18" width="11.7181818181818" customWidth="1"/>
-    <col min="19" max="19" width="10" customWidth="1"/>
-    <col min="20" max="20" width="6.42727272727273" customWidth="1"/>
-    <col min="21" max="21" width="9.85454545454546" customWidth="1"/>
-    <col min="22" max="22" width="6.57272727272727" customWidth="1"/>
-    <col min="23" max="23" width="37.1454545454545" customWidth="1"/>
-    <col min="24" max="25" width="8" customWidth="1"/>
-    <col min="26" max="26" width="7.71818181818182" customWidth="1"/>
-    <col min="27" max="27" width="6.28181818181818" customWidth="1"/>
-    <col min="28" max="28" width="9.28181818181818" customWidth="1"/>
-    <col min="29" max="29" width="9.71818181818182" customWidth="1"/>
-    <col min="30" max="30" width="12.8545454545455" customWidth="1"/>
-    <col min="31" max="31" width="16.1454545454545" customWidth="1"/>
-    <col min="32" max="32" width="15.4272727272727" customWidth="1"/>
-    <col min="33" max="33" width="24.5727272727273" customWidth="1"/>
-    <col min="34" max="34" width="8.57272727272727" customWidth="1"/>
-    <col min="35" max="35" width="14.7181818181818" customWidth="1"/>
-    <col min="36" max="36" width="18.5727272727273" customWidth="1"/>
-    <col min="37" max="37" width="14.1454545454545" customWidth="1"/>
-    <col min="38" max="38" width="14.7181818181818" customWidth="1"/>
-    <col min="39" max="39" width="17.4272727272727" customWidth="1"/>
-    <col min="40" max="40" width="22" customWidth="1"/>
-    <col min="41" max="41" width="17.5727272727273" customWidth="1"/>
-    <col min="42" max="42" width="25.2818181818182" customWidth="1"/>
-    <col min="43" max="43" width="13" customWidth="1"/>
-    <col min="44" max="44" width="25.7181818181818" customWidth="1"/>
-    <col min="45" max="45" width="10" customWidth="1"/>
-    <col min="46" max="46" width="13" customWidth="1"/>
-    <col min="47" max="47" width="15.5727272727273" customWidth="1"/>
-    <col min="48" max="48" width="21.1454545454545" customWidth="1"/>
-    <col min="49" max="49" width="11.5727272727273" customWidth="1"/>
-    <col min="50" max="50" width="16.7181818181818" customWidth="1"/>
-    <col min="51" max="51" width="14" customWidth="1"/>
-    <col min="52" max="52" width="19.4272727272727" customWidth="1"/>
-    <col min="53" max="53" width="18.8545454545455" customWidth="1"/>
-    <col min="54" max="54" width="23.2818181818182" customWidth="1"/>
-    <col min="55" max="55" width="15.5727272727273" customWidth="1"/>
-    <col min="56" max="56" width="14.2818181818182" customWidth="1"/>
-    <col min="57" max="57" width="17" customWidth="1"/>
-    <col min="58" max="58" width="16.2818181818182" customWidth="1"/>
-    <col min="59" max="59" width="13.5727272727273" customWidth="1"/>
-    <col min="60" max="61" width="12.7181818181818" customWidth="1"/>
-    <col min="62" max="62" width="21.8545454545455" customWidth="1"/>
-    <col min="63" max="63" width="30.5727272727273" customWidth="1"/>
-    <col min="64" max="64" width="10" customWidth="1"/>
-    <col min="65" max="65" width="42.5727272727273" customWidth="1"/>
-    <col min="66" max="66" width="38.1454545454545" customWidth="1"/>
-    <col min="67" max="67" width="19.4272727272727" customWidth="1"/>
-    <col min="68" max="68" width="35.4272727272727" customWidth="1"/>
-    <col min="69" max="69" width="9.57272727272727" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="5.14285714285714"/>
+    <col min="2" max="2" customWidth="true" width="21.8571428571429"/>
+    <col min="3" max="3" customWidth="true" width="27.5714285714286"/>
+    <col min="4" max="4" customWidth="true" width="79.4285714285714"/>
+    <col min="5" max="5" customWidth="true" width="11.5714285714286"/>
+    <col min="6" max="6" customWidth="true" width="5.14285714285714"/>
+    <col min="7" max="7" customWidth="true" width="11.0"/>
+    <col min="8" max="8" customWidth="true" width="12.7142857142857"/>
+    <col min="9" max="10" customWidth="true" width="5.85714285714286"/>
+    <col min="11" max="11" customWidth="true" width="6.0"/>
+    <col min="12" max="12" customWidth="true" width="14.2857142857143"/>
+    <col min="13" max="13" customWidth="true" width="9.42857142857143"/>
+    <col min="14" max="14" customWidth="true" width="14.2857142857143"/>
+    <col min="15" max="15" customWidth="true" width="15.5714285714286"/>
+    <col min="16" max="16" customWidth="true" width="14.4285714285714"/>
+    <col min="17" max="17" customWidth="true" width="39.4285714285714"/>
+    <col min="18" max="18" customWidth="true" width="11.7142857142857"/>
+    <col min="19" max="19" customWidth="true" width="10.0"/>
+    <col min="20" max="20" customWidth="true" width="6.42857142857143"/>
+    <col min="21" max="21" customWidth="true" width="9.85714285714286"/>
+    <col min="22" max="22" customWidth="true" width="6.57142857142857"/>
+    <col min="23" max="23" customWidth="true" width="37.1428571428571"/>
+    <col min="24" max="25" customWidth="true" width="8.0"/>
+    <col min="26" max="26" customWidth="true" width="7.71428571428571"/>
+    <col min="27" max="27" customWidth="true" width="6.28571428571429"/>
+    <col min="28" max="28" customWidth="true" width="9.28571428571429"/>
+    <col min="29" max="29" customWidth="true" width="9.71428571428571"/>
+    <col min="30" max="30" customWidth="true" width="12.8571428571429"/>
+    <col min="31" max="31" customWidth="true" width="16.1428571428571"/>
+    <col min="32" max="32" customWidth="true" width="15.4285714285714"/>
+    <col min="33" max="33" customWidth="true" width="24.5714285714286"/>
+    <col min="34" max="34" customWidth="true" width="8.57142857142857"/>
+    <col min="35" max="35" customWidth="true" width="14.7142857142857"/>
+    <col min="36" max="36" customWidth="true" width="18.5714285714286"/>
+    <col min="37" max="37" customWidth="true" width="14.1428571428571"/>
+    <col min="38" max="38" customWidth="true" width="14.7142857142857"/>
+    <col min="39" max="39" customWidth="true" width="17.4285714285714"/>
+    <col min="40" max="40" customWidth="true" width="22.0"/>
+    <col min="41" max="41" customWidth="true" width="17.5714285714286"/>
+    <col min="42" max="42" customWidth="true" width="25.2857142857143"/>
+    <col min="43" max="43" customWidth="true" width="13.0"/>
+    <col min="44" max="44" customWidth="true" width="25.7142857142857"/>
+    <col min="45" max="45" customWidth="true" width="10.0"/>
+    <col min="46" max="46" customWidth="true" width="13.0"/>
+    <col min="47" max="47" customWidth="true" width="15.5714285714286"/>
+    <col min="48" max="48" customWidth="true" width="21.1428571428571"/>
+    <col min="49" max="49" customWidth="true" width="11.5714285714286"/>
+    <col min="50" max="50" customWidth="true" width="16.7142857142857"/>
+    <col min="51" max="51" customWidth="true" width="14.0"/>
+    <col min="52" max="52" customWidth="true" width="19.4285714285714"/>
+    <col min="53" max="53" customWidth="true" width="18.8571428571429"/>
+    <col min="54" max="54" customWidth="true" width="23.2857142857143"/>
+    <col min="55" max="55" customWidth="true" width="15.5714285714286"/>
+    <col min="56" max="56" customWidth="true" width="14.2857142857143"/>
+    <col min="57" max="57" customWidth="true" width="17.0"/>
+    <col min="58" max="58" customWidth="true" width="16.2857142857143"/>
+    <col min="59" max="59" customWidth="true" width="13.5714285714286"/>
+    <col min="60" max="61" customWidth="true" width="12.7142857142857"/>
+    <col min="62" max="62" customWidth="true" width="21.8571428571429"/>
+    <col min="63" max="63" customWidth="true" width="30.5714285714286"/>
+    <col min="64" max="64" customWidth="true" width="10.0"/>
+    <col min="65" max="65" customWidth="true" width="42.5714285714286"/>
+    <col min="66" max="66" customWidth="true" width="38.1428571428571"/>
+    <col min="67" max="67" customWidth="true" width="19.4285714285714"/>
+    <col min="68" max="68" customWidth="true" width="35.4285714285714"/>
+    <col min="69" max="69" customWidth="true" width="9.57142857142857"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -10666,7 +10681,7 @@
       <c r="BP2" s="32"/>
       <c r="BQ2" s="32"/>
     </row>
-    <row r="3" ht="15.25" spans="1:69">
+    <row r="3" ht="15.75" spans="1:69">
       <c r="A3" s="33" t="s">
         <v>9</v>
       </c>
@@ -10875,7 +10890,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.25" spans="1:69">
+    <row r="4" spans="1:69">
       <c r="A4" s="31">
         <v>1</v>
       </c>
@@ -10946,7 +10961,7 @@
         <v>88363222</v>
       </c>
       <c r="U4" s="17">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="V4" s="17">
         <f>IF(OR($C$2=1,$C$2=4),ROUND((((S4*U4)/100)/2),2),0)</f>
@@ -10958,7 +10973,7 @@
       </c>
       <c r="X4" s="17">
         <f>IF($C$2=2,ROUND(((S4*U4)/100),2),0)</f>
-        <v>0</v>
+        <v>68.46</v>
       </c>
       <c r="Y4" s="17">
         <f>IF($C$2=4,ROUND((((S4*U4)/100)/2),2),0)</f>
@@ -10973,11 +10988,11 @@
       </c>
       <c r="AB4" s="17">
         <f>V4+W4+X4+Y4+AA4</f>
-        <v>15.2128</v>
+        <v>83.6728</v>
       </c>
       <c r="AC4" s="17">
         <f>IF($V2=1,S4+AB4,S4)</f>
-        <v>395.5328</v>
+        <v>463.9928</v>
       </c>
       <c r="AD4" s="17">
         <v>120</v>
@@ -11144,18 +11159,18 @@
       </c>
       <c r="X5" s="42">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>68.46</v>
       </c>
       <c r="Y5" s="44"/>
       <c r="Z5" s="44"/>
       <c r="AA5" s="44"/>
       <c r="AB5" s="42">
         <f t="shared" ref="AB5:AE5" si="1">SUM(AB4:AB4)</f>
-        <v>15.2128</v>
+        <v>83.6728</v>
       </c>
       <c r="AC5" s="42">
         <f t="shared" si="1"/>
-        <v>395.5328</v>
+        <v>463.9928</v>
       </c>
       <c r="AD5" s="42">
         <f t="shared" si="1"/>
@@ -11232,73 +11247,73 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ5"/>
-  <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="8.7047619047619" defaultRowHeight="15" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" width="5.14545454545455" customWidth="1"/>
-    <col min="2" max="3" width="28" customWidth="1"/>
-    <col min="4" max="4" width="79.4272727272727" customWidth="1"/>
-    <col min="5" max="5" width="11.5727272727273" customWidth="1"/>
-    <col min="6" max="6" width="5.14545454545455" customWidth="1"/>
-    <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="12.7181818181818" customWidth="1"/>
-    <col min="9" max="9" width="5.85454545454545" customWidth="1"/>
-    <col min="10" max="10" width="6" customWidth="1"/>
-    <col min="11" max="11" width="5.85454545454545" customWidth="1"/>
-    <col min="12" max="12" width="14.2818181818182" customWidth="1"/>
-    <col min="13" max="13" width="9.42727272727273" customWidth="1"/>
-    <col min="14" max="14" width="14.4272727272727" customWidth="1"/>
-    <col min="15" max="15" width="15.5727272727273" customWidth="1"/>
-    <col min="16" max="16" width="14.4272727272727" customWidth="1"/>
-    <col min="17" max="17" width="39.4272727272727" customWidth="1"/>
-    <col min="18" max="18" width="11.7181818181818" customWidth="1"/>
-    <col min="19" max="19" width="11.8545454545455" customWidth="1"/>
-    <col min="20" max="20" width="6.42727272727273" customWidth="1"/>
-    <col min="21" max="22" width="6.57272727272727" customWidth="1"/>
-    <col min="23" max="23" width="37.1454545454545" customWidth="1"/>
-    <col min="24" max="25" width="8" customWidth="1"/>
-    <col min="26" max="26" width="7.71818181818182" customWidth="1"/>
-    <col min="27" max="27" width="6.28181818181818" customWidth="1"/>
-    <col min="28" max="28" width="9.28181818181818" customWidth="1"/>
-    <col min="29" max="29" width="9.71818181818182" customWidth="1"/>
-    <col min="30" max="30" width="12.8545454545455" customWidth="1"/>
-    <col min="31" max="31" width="16.1454545454545" customWidth="1"/>
-    <col min="32" max="32" width="15.4272727272727" customWidth="1"/>
-    <col min="33" max="33" width="24.5727272727273" customWidth="1"/>
-    <col min="34" max="34" width="8.57272727272727" customWidth="1"/>
-    <col min="35" max="35" width="14.7181818181818" customWidth="1"/>
-    <col min="36" max="36" width="18.5727272727273" customWidth="1"/>
-    <col min="37" max="37" width="14.1454545454545" customWidth="1"/>
-    <col min="38" max="38" width="14.7181818181818" customWidth="1"/>
-    <col min="39" max="39" width="17.4272727272727" customWidth="1"/>
-    <col min="40" max="40" width="22" customWidth="1"/>
-    <col min="41" max="41" width="17.5727272727273" customWidth="1"/>
-    <col min="42" max="42" width="25.2818181818182" customWidth="1"/>
-    <col min="43" max="43" width="13" customWidth="1"/>
-    <col min="44" max="44" width="23.7181818181818" customWidth="1"/>
-    <col min="45" max="45" width="10" customWidth="1"/>
-    <col min="46" max="46" width="13" customWidth="1"/>
-    <col min="47" max="47" width="15.5727272727273" customWidth="1"/>
-    <col min="48" max="48" width="21.1454545454545" customWidth="1"/>
-    <col min="49" max="49" width="11.5727272727273" customWidth="1"/>
-    <col min="50" max="50" width="16.7181818181818" customWidth="1"/>
-    <col min="51" max="51" width="14" customWidth="1"/>
-    <col min="52" max="52" width="19.4272727272727" customWidth="1"/>
-    <col min="53" max="53" width="18.8545454545455" customWidth="1"/>
-    <col min="54" max="54" width="23.2818181818182" customWidth="1"/>
-    <col min="55" max="55" width="15.5727272727273" customWidth="1"/>
-    <col min="56" max="56" width="14.2818181818182" customWidth="1"/>
-    <col min="57" max="57" width="17" customWidth="1"/>
-    <col min="58" max="58" width="16.2818181818182" customWidth="1"/>
-    <col min="59" max="59" width="13.5727272727273" customWidth="1"/>
-    <col min="60" max="61" width="12.7181818181818" customWidth="1"/>
-    <col min="62" max="62" width="21.8545454545455" customWidth="1"/>
-    <col min="63" max="63" width="30.5727272727273" customWidth="1"/>
-    <col min="64" max="64" width="10" customWidth="1"/>
-    <col min="65" max="65" width="42.5727272727273" customWidth="1"/>
-    <col min="66" max="66" width="38.1454545454545" customWidth="1"/>
-    <col min="67" max="67" width="19.4272727272727" customWidth="1"/>
-    <col min="68" max="68" width="35.4272727272727" customWidth="1"/>
-    <col min="69" max="69" width="9.57272727272727" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="5.14285714285714"/>
+    <col min="2" max="3" customWidth="true" width="28.0"/>
+    <col min="4" max="4" customWidth="true" width="79.4285714285714"/>
+    <col min="5" max="5" customWidth="true" width="11.5714285714286"/>
+    <col min="6" max="6" customWidth="true" width="5.14285714285714"/>
+    <col min="7" max="7" customWidth="true" width="11.0"/>
+    <col min="8" max="8" customWidth="true" width="12.7142857142857"/>
+    <col min="9" max="9" customWidth="true" width="5.85714285714286"/>
+    <col min="10" max="10" customWidth="true" width="6.0"/>
+    <col min="11" max="11" customWidth="true" width="5.85714285714286"/>
+    <col min="12" max="12" customWidth="true" width="14.2857142857143"/>
+    <col min="13" max="13" customWidth="true" width="9.42857142857143"/>
+    <col min="14" max="14" customWidth="true" width="14.4285714285714"/>
+    <col min="15" max="15" customWidth="true" width="15.5714285714286"/>
+    <col min="16" max="16" customWidth="true" width="14.4285714285714"/>
+    <col min="17" max="17" customWidth="true" width="39.4285714285714"/>
+    <col min="18" max="18" customWidth="true" width="11.7142857142857"/>
+    <col min="19" max="19" customWidth="true" width="11.8571428571429"/>
+    <col min="20" max="20" customWidth="true" width="6.42857142857143"/>
+    <col min="21" max="22" customWidth="true" width="6.57142857142857"/>
+    <col min="23" max="23" customWidth="true" width="37.1428571428571"/>
+    <col min="24" max="25" customWidth="true" width="8.0"/>
+    <col min="26" max="26" customWidth="true" width="7.71428571428571"/>
+    <col min="27" max="27" customWidth="true" width="6.28571428571429"/>
+    <col min="28" max="28" customWidth="true" width="9.28571428571429"/>
+    <col min="29" max="29" customWidth="true" width="9.71428571428571"/>
+    <col min="30" max="30" customWidth="true" width="12.8571428571429"/>
+    <col min="31" max="31" customWidth="true" width="16.1428571428571"/>
+    <col min="32" max="32" customWidth="true" width="15.4285714285714"/>
+    <col min="33" max="33" customWidth="true" width="24.5714285714286"/>
+    <col min="34" max="34" customWidth="true" width="8.57142857142857"/>
+    <col min="35" max="35" customWidth="true" width="14.7142857142857"/>
+    <col min="36" max="36" customWidth="true" width="18.5714285714286"/>
+    <col min="37" max="37" customWidth="true" width="14.1428571428571"/>
+    <col min="38" max="38" customWidth="true" width="14.7142857142857"/>
+    <col min="39" max="39" customWidth="true" width="17.4285714285714"/>
+    <col min="40" max="40" customWidth="true" width="22.0"/>
+    <col min="41" max="41" customWidth="true" width="17.5714285714286"/>
+    <col min="42" max="42" customWidth="true" width="25.2857142857143"/>
+    <col min="43" max="43" customWidth="true" width="13.0"/>
+    <col min="44" max="44" customWidth="true" width="23.7142857142857"/>
+    <col min="45" max="45" customWidth="true" width="10.0"/>
+    <col min="46" max="46" customWidth="true" width="13.0"/>
+    <col min="47" max="47" customWidth="true" width="15.5714285714286"/>
+    <col min="48" max="48" customWidth="true" width="21.1428571428571"/>
+    <col min="49" max="49" customWidth="true" width="11.5714285714286"/>
+    <col min="50" max="50" customWidth="true" width="16.7142857142857"/>
+    <col min="51" max="51" customWidth="true" width="14.0"/>
+    <col min="52" max="52" customWidth="true" width="19.4285714285714"/>
+    <col min="53" max="53" customWidth="true" width="18.8571428571429"/>
+    <col min="54" max="54" customWidth="true" width="23.2857142857143"/>
+    <col min="55" max="55" customWidth="true" width="15.5714285714286"/>
+    <col min="56" max="56" customWidth="true" width="14.2857142857143"/>
+    <col min="57" max="57" customWidth="true" width="17.0"/>
+    <col min="58" max="58" customWidth="true" width="16.2857142857143"/>
+    <col min="59" max="59" customWidth="true" width="13.5714285714286"/>
+    <col min="60" max="61" customWidth="true" width="12.7142857142857"/>
+    <col min="62" max="62" customWidth="true" width="21.8571428571429"/>
+    <col min="63" max="63" customWidth="true" width="30.5714285714286"/>
+    <col min="64" max="64" customWidth="true" width="10.0"/>
+    <col min="65" max="65" customWidth="true" width="42.5714285714286"/>
+    <col min="66" max="66" customWidth="true" width="38.1428571428571"/>
+    <col min="67" max="67" customWidth="true" width="19.4285714285714"/>
+    <col min="68" max="68" customWidth="true" width="35.4285714285714"/>
+    <col min="69" max="69" customWidth="true" width="9.57142857142857"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -11469,7 +11484,7 @@
       <c r="BP2" s="32"/>
       <c r="BQ2" s="32"/>
     </row>
-    <row r="3" ht="15.25" spans="1:69">
+    <row r="3" ht="15.75" spans="1:69">
       <c r="A3" s="33" t="s">
         <v>9</v>
       </c>
@@ -11678,7 +11693,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.25" spans="1:69">
+    <row r="4" ht="15.75" spans="1:69">
       <c r="A4" s="31">
         <v>1</v>
       </c>
@@ -11749,7 +11764,7 @@
         <v>88363222</v>
       </c>
       <c r="U4" s="17">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="V4" s="17">
         <f>IF(OR($C$2=1,$C$2=4),ROUND((((S4*U4)/100)/2),2),0)</f>
@@ -11761,7 +11776,7 @@
       </c>
       <c r="X4" s="17">
         <f>IF($C$2=2,ROUND(((S4*U4)/100),2),0)</f>
-        <v>0</v>
+        <v>68.46</v>
       </c>
       <c r="Y4" s="17">
         <f>IF($C$2=4,ROUND((((S4*U4)/100)/2),2),0)</f>
@@ -11776,11 +11791,11 @@
       </c>
       <c r="AB4" s="17">
         <f>V4+W4+X4+Y4+AA4</f>
-        <v>15.2128</v>
+        <v>83.6728</v>
       </c>
       <c r="AC4" s="17">
         <f>IF($V2=1,S4+AB4,S4)</f>
-        <v>395.5328</v>
+        <v>463.9928</v>
       </c>
       <c r="AD4" s="17">
         <v>120</v>
@@ -11947,7 +11962,7 @@
       </c>
       <c r="X5" s="42">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>68.46</v>
       </c>
       <c r="Y5" s="42">
         <f t="shared" si="0"/>
@@ -11963,11 +11978,11 @@
       </c>
       <c r="AB5" s="42">
         <f t="shared" si="0"/>
-        <v>15.2128</v>
+        <v>83.6728</v>
       </c>
       <c r="AC5" s="42">
         <f t="shared" si="0"/>
-        <v>395.5328</v>
+        <v>463.9928</v>
       </c>
       <c r="AD5" s="42">
         <f t="shared" si="0"/>
@@ -12047,73 +12062,73 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ5"/>
-  <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="8.7047619047619" defaultRowHeight="15" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" width="5.14545454545455" customWidth="1"/>
-    <col min="2" max="3" width="28" customWidth="1"/>
-    <col min="4" max="4" width="79.4272727272727" customWidth="1"/>
-    <col min="5" max="5" width="11.5727272727273" customWidth="1"/>
-    <col min="6" max="6" width="5.14545454545455" customWidth="1"/>
-    <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="12.7181818181818" customWidth="1"/>
-    <col min="9" max="9" width="5.85454545454545" customWidth="1"/>
-    <col min="10" max="10" width="6" customWidth="1"/>
-    <col min="11" max="11" width="5.85454545454545" customWidth="1"/>
-    <col min="12" max="12" width="14.2818181818182" customWidth="1"/>
-    <col min="13" max="13" width="9.42727272727273" customWidth="1"/>
-    <col min="14" max="14" width="14.4272727272727" customWidth="1"/>
-    <col min="15" max="15" width="15.5727272727273" customWidth="1"/>
-    <col min="16" max="16" width="14.4272727272727" customWidth="1"/>
-    <col min="17" max="17" width="39.4272727272727" customWidth="1"/>
-    <col min="18" max="18" width="11.7181818181818" customWidth="1"/>
-    <col min="19" max="19" width="11.8545454545455" customWidth="1"/>
-    <col min="20" max="20" width="6.42727272727273" customWidth="1"/>
-    <col min="21" max="22" width="6.57272727272727" customWidth="1"/>
-    <col min="23" max="23" width="37.1454545454545" customWidth="1"/>
-    <col min="24" max="25" width="8" customWidth="1"/>
-    <col min="26" max="26" width="7.71818181818182" customWidth="1"/>
-    <col min="27" max="27" width="6.28181818181818" customWidth="1"/>
-    <col min="28" max="28" width="9.28181818181818" customWidth="1"/>
-    <col min="29" max="29" width="9.71818181818182" customWidth="1"/>
-    <col min="30" max="30" width="12.8545454545455" customWidth="1"/>
-    <col min="31" max="31" width="16.1454545454545" customWidth="1"/>
-    <col min="32" max="32" width="15.4272727272727" customWidth="1"/>
-    <col min="33" max="33" width="24.5727272727273" customWidth="1"/>
-    <col min="34" max="34" width="8.57272727272727" customWidth="1"/>
-    <col min="35" max="35" width="14.7181818181818" customWidth="1"/>
-    <col min="36" max="36" width="18.5727272727273" customWidth="1"/>
-    <col min="37" max="37" width="14.1454545454545" customWidth="1"/>
-    <col min="38" max="38" width="14.7181818181818" customWidth="1"/>
-    <col min="39" max="39" width="17.4272727272727" customWidth="1"/>
-    <col min="40" max="40" width="22" customWidth="1"/>
-    <col min="41" max="41" width="17.5727272727273" customWidth="1"/>
-    <col min="42" max="42" width="25.2818181818182" customWidth="1"/>
-    <col min="43" max="43" width="13" customWidth="1"/>
-    <col min="44" max="44" width="23.7181818181818" customWidth="1"/>
-    <col min="45" max="45" width="10" customWidth="1"/>
-    <col min="46" max="46" width="13" customWidth="1"/>
-    <col min="47" max="47" width="15.5727272727273" customWidth="1"/>
-    <col min="48" max="48" width="21.1454545454545" customWidth="1"/>
-    <col min="49" max="49" width="11.5727272727273" customWidth="1"/>
-    <col min="50" max="50" width="16.7181818181818" customWidth="1"/>
-    <col min="51" max="51" width="14" customWidth="1"/>
-    <col min="52" max="52" width="19.4272727272727" customWidth="1"/>
-    <col min="53" max="53" width="18.8545454545455" customWidth="1"/>
-    <col min="54" max="54" width="23.2818181818182" customWidth="1"/>
-    <col min="55" max="55" width="15.5727272727273" customWidth="1"/>
-    <col min="56" max="56" width="14.2818181818182" customWidth="1"/>
-    <col min="57" max="57" width="17" customWidth="1"/>
-    <col min="58" max="58" width="16.2818181818182" customWidth="1"/>
-    <col min="59" max="59" width="13.5727272727273" customWidth="1"/>
-    <col min="60" max="61" width="12.7181818181818" customWidth="1"/>
-    <col min="62" max="62" width="21.8545454545455" customWidth="1"/>
-    <col min="63" max="63" width="30.5727272727273" customWidth="1"/>
-    <col min="64" max="64" width="10" customWidth="1"/>
-    <col min="65" max="65" width="42.5727272727273" customWidth="1"/>
-    <col min="66" max="66" width="38.1454545454545" customWidth="1"/>
-    <col min="67" max="67" width="19.4272727272727" customWidth="1"/>
-    <col min="68" max="68" width="35.4272727272727" customWidth="1"/>
-    <col min="69" max="69" width="9.57272727272727" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="5.14285714285714"/>
+    <col min="2" max="3" customWidth="true" width="28.0"/>
+    <col min="4" max="4" customWidth="true" width="79.4285714285714"/>
+    <col min="5" max="5" customWidth="true" width="11.5714285714286"/>
+    <col min="6" max="6" customWidth="true" width="5.14285714285714"/>
+    <col min="7" max="7" customWidth="true" width="11.0"/>
+    <col min="8" max="8" customWidth="true" width="12.7142857142857"/>
+    <col min="9" max="9" customWidth="true" width="5.85714285714286"/>
+    <col min="10" max="10" customWidth="true" width="6.0"/>
+    <col min="11" max="11" customWidth="true" width="5.85714285714286"/>
+    <col min="12" max="12" customWidth="true" width="14.2857142857143"/>
+    <col min="13" max="13" customWidth="true" width="9.42857142857143"/>
+    <col min="14" max="14" customWidth="true" width="14.4285714285714"/>
+    <col min="15" max="15" customWidth="true" width="15.5714285714286"/>
+    <col min="16" max="16" customWidth="true" width="14.4285714285714"/>
+    <col min="17" max="17" customWidth="true" width="39.4285714285714"/>
+    <col min="18" max="18" customWidth="true" width="11.7142857142857"/>
+    <col min="19" max="19" customWidth="true" width="11.8571428571429"/>
+    <col min="20" max="20" customWidth="true" width="6.42857142857143"/>
+    <col min="21" max="22" customWidth="true" width="6.57142857142857"/>
+    <col min="23" max="23" customWidth="true" width="37.1428571428571"/>
+    <col min="24" max="25" customWidth="true" width="8.0"/>
+    <col min="26" max="26" customWidth="true" width="7.71428571428571"/>
+    <col min="27" max="27" customWidth="true" width="6.28571428571429"/>
+    <col min="28" max="28" customWidth="true" width="9.28571428571429"/>
+    <col min="29" max="29" customWidth="true" width="9.71428571428571"/>
+    <col min="30" max="30" customWidth="true" width="12.8571428571429"/>
+    <col min="31" max="31" customWidth="true" width="16.1428571428571"/>
+    <col min="32" max="32" customWidth="true" width="15.4285714285714"/>
+    <col min="33" max="33" customWidth="true" width="24.5714285714286"/>
+    <col min="34" max="34" customWidth="true" width="8.57142857142857"/>
+    <col min="35" max="35" customWidth="true" width="14.7142857142857"/>
+    <col min="36" max="36" customWidth="true" width="18.5714285714286"/>
+    <col min="37" max="37" customWidth="true" width="14.1428571428571"/>
+    <col min="38" max="38" customWidth="true" width="14.7142857142857"/>
+    <col min="39" max="39" customWidth="true" width="17.4285714285714"/>
+    <col min="40" max="40" customWidth="true" width="22.0"/>
+    <col min="41" max="41" customWidth="true" width="17.5714285714286"/>
+    <col min="42" max="42" customWidth="true" width="25.2857142857143"/>
+    <col min="43" max="43" customWidth="true" width="13.0"/>
+    <col min="44" max="44" customWidth="true" width="23.7142857142857"/>
+    <col min="45" max="45" customWidth="true" width="10.0"/>
+    <col min="46" max="46" customWidth="true" width="13.0"/>
+    <col min="47" max="47" customWidth="true" width="15.5714285714286"/>
+    <col min="48" max="48" customWidth="true" width="21.1428571428571"/>
+    <col min="49" max="49" customWidth="true" width="11.5714285714286"/>
+    <col min="50" max="50" customWidth="true" width="16.7142857142857"/>
+    <col min="51" max="51" customWidth="true" width="14.0"/>
+    <col min="52" max="52" customWidth="true" width="19.4285714285714"/>
+    <col min="53" max="53" customWidth="true" width="18.8571428571429"/>
+    <col min="54" max="54" customWidth="true" width="23.2857142857143"/>
+    <col min="55" max="55" customWidth="true" width="15.5714285714286"/>
+    <col min="56" max="56" customWidth="true" width="14.2857142857143"/>
+    <col min="57" max="57" customWidth="true" width="17.0"/>
+    <col min="58" max="58" customWidth="true" width="16.2857142857143"/>
+    <col min="59" max="59" customWidth="true" width="13.5714285714286"/>
+    <col min="60" max="61" customWidth="true" width="12.7142857142857"/>
+    <col min="62" max="62" customWidth="true" width="21.8571428571429"/>
+    <col min="63" max="63" customWidth="true" width="30.5714285714286"/>
+    <col min="64" max="64" customWidth="true" width="10.0"/>
+    <col min="65" max="65" customWidth="true" width="42.5714285714286"/>
+    <col min="66" max="66" customWidth="true" width="38.1428571428571"/>
+    <col min="67" max="67" customWidth="true" width="19.4285714285714"/>
+    <col min="68" max="68" customWidth="true" width="35.4285714285714"/>
+    <col min="69" max="69" customWidth="true" width="9.57142857142857"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -12284,7 +12299,7 @@
       <c r="BP2" s="32"/>
       <c r="BQ2" s="32"/>
     </row>
-    <row r="3" ht="15.25" spans="1:69">
+    <row r="3" ht="15.75" spans="1:69">
       <c r="A3" s="33" t="s">
         <v>9</v>
       </c>
@@ -12493,7 +12508,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.25" spans="1:69">
+    <row r="4" ht="15.75" spans="1:69">
       <c r="A4" s="31">
         <v>1</v>
       </c>
@@ -12564,7 +12579,7 @@
         <v>88363222</v>
       </c>
       <c r="U4" s="17">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="V4" s="17">
         <f>IF(OR($C$2=1,$C$2=4),ROUND((((S4*U4)/100)/2),2),0)</f>
@@ -12576,7 +12591,7 @@
       </c>
       <c r="X4" s="17">
         <f>IF($C$2=2,ROUND(((S4*U4)/100),2),0)</f>
-        <v>0</v>
+        <v>68.46</v>
       </c>
       <c r="Y4" s="17">
         <f>IF($C$2=4,ROUND((((S4*U4)/100)/2),2),0)</f>
@@ -12591,11 +12606,11 @@
       </c>
       <c r="AB4" s="17">
         <f>V4+W4+X4+Y4+AA4</f>
-        <v>15.2128</v>
+        <v>83.6728</v>
       </c>
       <c r="AC4" s="17">
         <f>IF($V2=1,S4+AB4,S4)</f>
-        <v>395.5328</v>
+        <v>463.9928</v>
       </c>
       <c r="AD4" s="17">
         <v>120</v>
@@ -12762,7 +12777,7 @@
       </c>
       <c r="X5" s="42">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>68.46</v>
       </c>
       <c r="Y5" s="42">
         <f t="shared" si="0"/>
@@ -12778,11 +12793,11 @@
       </c>
       <c r="AB5" s="42">
         <f t="shared" si="0"/>
-        <v>15.2128</v>
+        <v>83.6728</v>
       </c>
       <c r="AC5" s="42">
         <f t="shared" si="0"/>
-        <v>395.5328</v>
+        <v>463.9928</v>
       </c>
       <c r="AD5" s="42">
         <f t="shared" si="0"/>
@@ -12862,73 +12877,73 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ5"/>
-  <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="8.7047619047619" defaultRowHeight="15" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" width="5.14545454545455" customWidth="1"/>
-    <col min="2" max="3" width="28" customWidth="1"/>
-    <col min="4" max="4" width="79.4272727272727" customWidth="1"/>
-    <col min="5" max="5" width="11.5727272727273" customWidth="1"/>
-    <col min="6" max="6" width="5.14545454545455" customWidth="1"/>
-    <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="12.7181818181818" customWidth="1"/>
-    <col min="9" max="9" width="5.85454545454545" customWidth="1"/>
-    <col min="10" max="10" width="6" customWidth="1"/>
-    <col min="11" max="11" width="5.85454545454545" customWidth="1"/>
-    <col min="12" max="12" width="14.2818181818182" customWidth="1"/>
-    <col min="13" max="13" width="9.42727272727273" customWidth="1"/>
-    <col min="14" max="14" width="14.4272727272727" customWidth="1"/>
-    <col min="15" max="15" width="15.5727272727273" customWidth="1"/>
-    <col min="16" max="16" width="14.4272727272727" customWidth="1"/>
-    <col min="17" max="17" width="39.4272727272727" customWidth="1"/>
-    <col min="18" max="18" width="11.7181818181818" customWidth="1"/>
-    <col min="19" max="19" width="11.8545454545455" customWidth="1"/>
-    <col min="20" max="20" width="6.42727272727273" customWidth="1"/>
-    <col min="21" max="22" width="6.57272727272727" customWidth="1"/>
-    <col min="23" max="23" width="37.1454545454545" customWidth="1"/>
-    <col min="24" max="25" width="8" customWidth="1"/>
-    <col min="26" max="26" width="7.71818181818182" customWidth="1"/>
-    <col min="27" max="27" width="6.28181818181818" customWidth="1"/>
-    <col min="28" max="28" width="9.28181818181818" customWidth="1"/>
-    <col min="29" max="29" width="9.71818181818182" customWidth="1"/>
-    <col min="30" max="30" width="12.8545454545455" customWidth="1"/>
-    <col min="31" max="31" width="16.1454545454545" customWidth="1"/>
-    <col min="32" max="32" width="15.4272727272727" customWidth="1"/>
-    <col min="33" max="33" width="24.5727272727273" customWidth="1"/>
-    <col min="34" max="34" width="8.57272727272727" customWidth="1"/>
-    <col min="35" max="35" width="14.7181818181818" customWidth="1"/>
-    <col min="36" max="36" width="18.5727272727273" customWidth="1"/>
-    <col min="37" max="37" width="14.1454545454545" customWidth="1"/>
-    <col min="38" max="38" width="14.7181818181818" customWidth="1"/>
-    <col min="39" max="39" width="17.4272727272727" customWidth="1"/>
-    <col min="40" max="40" width="22" customWidth="1"/>
-    <col min="41" max="41" width="17.5727272727273" customWidth="1"/>
-    <col min="42" max="42" width="25.2818181818182" customWidth="1"/>
-    <col min="43" max="43" width="13" customWidth="1"/>
-    <col min="44" max="44" width="23.7181818181818" customWidth="1"/>
-    <col min="45" max="45" width="10" customWidth="1"/>
-    <col min="46" max="46" width="13" customWidth="1"/>
-    <col min="47" max="47" width="15.5727272727273" customWidth="1"/>
-    <col min="48" max="48" width="21.1454545454545" customWidth="1"/>
-    <col min="49" max="49" width="11.5727272727273" customWidth="1"/>
-    <col min="50" max="50" width="16.7181818181818" customWidth="1"/>
-    <col min="51" max="51" width="14" customWidth="1"/>
-    <col min="52" max="52" width="19.4272727272727" customWidth="1"/>
-    <col min="53" max="53" width="18.8545454545455" customWidth="1"/>
-    <col min="54" max="54" width="23.2818181818182" customWidth="1"/>
-    <col min="55" max="55" width="15.5727272727273" customWidth="1"/>
-    <col min="56" max="56" width="14.2818181818182" customWidth="1"/>
-    <col min="57" max="57" width="17" customWidth="1"/>
-    <col min="58" max="58" width="16.2818181818182" customWidth="1"/>
-    <col min="59" max="59" width="13.5727272727273" customWidth="1"/>
-    <col min="60" max="61" width="12.7181818181818" customWidth="1"/>
-    <col min="62" max="62" width="21.8545454545455" customWidth="1"/>
-    <col min="63" max="63" width="30.5727272727273" customWidth="1"/>
-    <col min="64" max="64" width="10" customWidth="1"/>
-    <col min="65" max="65" width="42.5727272727273" customWidth="1"/>
-    <col min="66" max="66" width="38.1454545454545" customWidth="1"/>
-    <col min="67" max="67" width="19.4272727272727" customWidth="1"/>
-    <col min="68" max="68" width="35.4272727272727" customWidth="1"/>
-    <col min="69" max="69" width="9.57272727272727" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="5.14285714285714"/>
+    <col min="2" max="3" customWidth="true" width="28.0"/>
+    <col min="4" max="4" customWidth="true" width="79.4285714285714"/>
+    <col min="5" max="5" customWidth="true" width="11.5714285714286"/>
+    <col min="6" max="6" customWidth="true" width="5.14285714285714"/>
+    <col min="7" max="7" customWidth="true" width="11.0"/>
+    <col min="8" max="8" customWidth="true" width="12.7142857142857"/>
+    <col min="9" max="9" customWidth="true" width="5.85714285714286"/>
+    <col min="10" max="10" customWidth="true" width="6.0"/>
+    <col min="11" max="11" customWidth="true" width="5.85714285714286"/>
+    <col min="12" max="12" customWidth="true" width="14.2857142857143"/>
+    <col min="13" max="13" customWidth="true" width="9.42857142857143"/>
+    <col min="14" max="14" customWidth="true" width="14.4285714285714"/>
+    <col min="15" max="15" customWidth="true" width="15.5714285714286"/>
+    <col min="16" max="16" customWidth="true" width="14.4285714285714"/>
+    <col min="17" max="17" customWidth="true" width="39.4285714285714"/>
+    <col min="18" max="18" customWidth="true" width="11.7142857142857"/>
+    <col min="19" max="19" customWidth="true" width="11.8571428571429"/>
+    <col min="20" max="20" customWidth="true" width="6.42857142857143"/>
+    <col min="21" max="22" customWidth="true" width="6.57142857142857"/>
+    <col min="23" max="23" customWidth="true" width="37.1428571428571"/>
+    <col min="24" max="25" customWidth="true" width="8.0"/>
+    <col min="26" max="26" customWidth="true" width="7.71428571428571"/>
+    <col min="27" max="27" customWidth="true" width="6.28571428571429"/>
+    <col min="28" max="28" customWidth="true" width="9.28571428571429"/>
+    <col min="29" max="29" customWidth="true" width="9.71428571428571"/>
+    <col min="30" max="30" customWidth="true" width="12.8571428571429"/>
+    <col min="31" max="31" customWidth="true" width="16.1428571428571"/>
+    <col min="32" max="32" customWidth="true" width="15.4285714285714"/>
+    <col min="33" max="33" customWidth="true" width="24.5714285714286"/>
+    <col min="34" max="34" customWidth="true" width="8.57142857142857"/>
+    <col min="35" max="35" customWidth="true" width="14.7142857142857"/>
+    <col min="36" max="36" customWidth="true" width="18.5714285714286"/>
+    <col min="37" max="37" customWidth="true" width="14.1428571428571"/>
+    <col min="38" max="38" customWidth="true" width="14.7142857142857"/>
+    <col min="39" max="39" customWidth="true" width="17.4285714285714"/>
+    <col min="40" max="40" customWidth="true" width="22.0"/>
+    <col min="41" max="41" customWidth="true" width="17.5714285714286"/>
+    <col min="42" max="42" customWidth="true" width="25.2857142857143"/>
+    <col min="43" max="43" customWidth="true" width="13.0"/>
+    <col min="44" max="44" customWidth="true" width="23.7142857142857"/>
+    <col min="45" max="45" customWidth="true" width="10.0"/>
+    <col min="46" max="46" customWidth="true" width="13.0"/>
+    <col min="47" max="47" customWidth="true" width="15.5714285714286"/>
+    <col min="48" max="48" customWidth="true" width="21.1428571428571"/>
+    <col min="49" max="49" customWidth="true" width="11.5714285714286"/>
+    <col min="50" max="50" customWidth="true" width="16.7142857142857"/>
+    <col min="51" max="51" customWidth="true" width="14.0"/>
+    <col min="52" max="52" customWidth="true" width="19.4285714285714"/>
+    <col min="53" max="53" customWidth="true" width="18.8571428571429"/>
+    <col min="54" max="54" customWidth="true" width="23.2857142857143"/>
+    <col min="55" max="55" customWidth="true" width="15.5714285714286"/>
+    <col min="56" max="56" customWidth="true" width="14.2857142857143"/>
+    <col min="57" max="57" customWidth="true" width="17.0"/>
+    <col min="58" max="58" customWidth="true" width="16.2857142857143"/>
+    <col min="59" max="59" customWidth="true" width="13.5714285714286"/>
+    <col min="60" max="61" customWidth="true" width="12.7142857142857"/>
+    <col min="62" max="62" customWidth="true" width="21.8571428571429"/>
+    <col min="63" max="63" customWidth="true" width="30.5714285714286"/>
+    <col min="64" max="64" customWidth="true" width="10.0"/>
+    <col min="65" max="65" customWidth="true" width="42.5714285714286"/>
+    <col min="66" max="66" customWidth="true" width="38.1428571428571"/>
+    <col min="67" max="67" customWidth="true" width="19.4285714285714"/>
+    <col min="68" max="68" customWidth="true" width="35.4285714285714"/>
+    <col min="69" max="69" customWidth="true" width="9.57142857142857"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -13099,7 +13114,7 @@
       <c r="BP2" s="32"/>
       <c r="BQ2" s="32"/>
     </row>
-    <row r="3" ht="15.25" spans="1:69">
+    <row r="3" ht="15.75" spans="1:69">
       <c r="A3" s="33" t="s">
         <v>9</v>
       </c>
@@ -13308,7 +13323,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.25" spans="1:69">
+    <row r="4" ht="15.75" spans="1:69">
       <c r="A4" s="31">
         <v>1</v>
       </c>
@@ -13379,7 +13394,7 @@
         <v>88363222</v>
       </c>
       <c r="U4" s="17">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="V4" s="17">
         <f>IF(OR($C$2=1,$C$2=4),ROUND((((S4*U4)/100)/2),2),0)</f>
@@ -13391,7 +13406,7 @@
       </c>
       <c r="X4" s="17">
         <f>IF($C$2=2,ROUND(((S4*U4)/100),2),0)</f>
-        <v>0</v>
+        <v>67.77</v>
       </c>
       <c r="Y4" s="17">
         <f>IF($C$2=4,ROUND((((S4*U4)/100)/2),2),0)</f>
@@ -13406,11 +13421,11 @@
       </c>
       <c r="AB4" s="17">
         <f>V4+W4+X4+Y4+AA4</f>
-        <v>15.0592</v>
+        <v>82.8292</v>
       </c>
       <c r="AC4" s="17">
         <f>IF($V2=1,S4+AB4,S4)</f>
-        <v>391.5392</v>
+        <v>459.3092</v>
       </c>
       <c r="AD4" s="17">
         <v>120</v>
@@ -13577,18 +13592,18 @@
       </c>
       <c r="X5" s="42">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>67.77</v>
       </c>
       <c r="Y5" s="44"/>
       <c r="Z5" s="44"/>
       <c r="AA5" s="44"/>
       <c r="AB5" s="42">
         <f t="shared" ref="AB5:AE5" si="1">SUM(AB4:AB4)</f>
-        <v>15.0592</v>
+        <v>82.8292</v>
       </c>
       <c r="AC5" s="42">
         <f t="shared" si="1"/>
-        <v>391.5392</v>
+        <v>459.3092</v>
       </c>
       <c r="AD5" s="42">
         <f t="shared" si="1"/>
@@ -13665,73 +13680,73 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ5"/>
-  <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="8.7047619047619" defaultRowHeight="15" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" width="5.14545454545455" customWidth="1"/>
-    <col min="2" max="3" width="28" customWidth="1"/>
-    <col min="4" max="4" width="79.4272727272727" customWidth="1"/>
-    <col min="5" max="5" width="11.5727272727273" customWidth="1"/>
-    <col min="6" max="6" width="5.14545454545455" customWidth="1"/>
-    <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="12.7181818181818" customWidth="1"/>
-    <col min="9" max="9" width="5.85454545454545" customWidth="1"/>
-    <col min="10" max="10" width="6" customWidth="1"/>
-    <col min="11" max="11" width="5.85454545454545" customWidth="1"/>
-    <col min="12" max="12" width="14.2818181818182" customWidth="1"/>
-    <col min="13" max="13" width="9.42727272727273" customWidth="1"/>
-    <col min="14" max="14" width="14.4272727272727" customWidth="1"/>
-    <col min="15" max="15" width="15.5727272727273" customWidth="1"/>
-    <col min="16" max="16" width="14.4272727272727" customWidth="1"/>
-    <col min="17" max="17" width="39.4272727272727" customWidth="1"/>
-    <col min="18" max="18" width="11.7181818181818" customWidth="1"/>
-    <col min="19" max="19" width="11.8545454545455" customWidth="1"/>
-    <col min="20" max="20" width="6.42727272727273" customWidth="1"/>
-    <col min="21" max="22" width="6.57272727272727" customWidth="1"/>
-    <col min="23" max="23" width="37.1454545454545" customWidth="1"/>
-    <col min="24" max="25" width="8" customWidth="1"/>
-    <col min="26" max="26" width="7.71818181818182" customWidth="1"/>
-    <col min="27" max="27" width="6.28181818181818" customWidth="1"/>
-    <col min="28" max="28" width="9.28181818181818" customWidth="1"/>
-    <col min="29" max="29" width="9.71818181818182" customWidth="1"/>
-    <col min="30" max="30" width="12.8545454545455" customWidth="1"/>
-    <col min="31" max="31" width="16.1454545454545" customWidth="1"/>
-    <col min="32" max="32" width="15.4272727272727" customWidth="1"/>
-    <col min="33" max="33" width="24.5727272727273" customWidth="1"/>
-    <col min="34" max="34" width="8.57272727272727" customWidth="1"/>
-    <col min="35" max="35" width="14.7181818181818" customWidth="1"/>
-    <col min="36" max="36" width="18.5727272727273" customWidth="1"/>
-    <col min="37" max="37" width="14.1454545454545" customWidth="1"/>
-    <col min="38" max="38" width="14.7181818181818" customWidth="1"/>
-    <col min="39" max="39" width="17.4272727272727" customWidth="1"/>
-    <col min="40" max="40" width="22" customWidth="1"/>
-    <col min="41" max="41" width="17.5727272727273" customWidth="1"/>
-    <col min="42" max="42" width="25.2818181818182" customWidth="1"/>
-    <col min="43" max="43" width="13" customWidth="1"/>
-    <col min="44" max="44" width="23.7181818181818" customWidth="1"/>
-    <col min="45" max="45" width="10" customWidth="1"/>
-    <col min="46" max="46" width="13" customWidth="1"/>
-    <col min="47" max="47" width="15.5727272727273" customWidth="1"/>
-    <col min="48" max="48" width="21.1454545454545" customWidth="1"/>
-    <col min="49" max="49" width="11.5727272727273" customWidth="1"/>
-    <col min="50" max="50" width="16.7181818181818" customWidth="1"/>
-    <col min="51" max="51" width="14" customWidth="1"/>
-    <col min="52" max="52" width="19.4272727272727" customWidth="1"/>
-    <col min="53" max="53" width="18.8545454545455" customWidth="1"/>
-    <col min="54" max="54" width="23.2818181818182" customWidth="1"/>
-    <col min="55" max="55" width="15.5727272727273" customWidth="1"/>
-    <col min="56" max="56" width="14.2818181818182" customWidth="1"/>
-    <col min="57" max="57" width="17" customWidth="1"/>
-    <col min="58" max="58" width="16.2818181818182" customWidth="1"/>
-    <col min="59" max="59" width="13.5727272727273" customWidth="1"/>
-    <col min="60" max="61" width="12.7181818181818" customWidth="1"/>
-    <col min="62" max="62" width="21.8545454545455" customWidth="1"/>
-    <col min="63" max="63" width="30.5727272727273" customWidth="1"/>
-    <col min="64" max="64" width="10" customWidth="1"/>
-    <col min="65" max="65" width="42.5727272727273" customWidth="1"/>
-    <col min="66" max="66" width="38.1454545454545" customWidth="1"/>
-    <col min="67" max="67" width="19.4272727272727" customWidth="1"/>
-    <col min="68" max="68" width="35.4272727272727" customWidth="1"/>
-    <col min="69" max="69" width="9.57272727272727" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="5.14285714285714"/>
+    <col min="2" max="3" customWidth="true" width="28.0"/>
+    <col min="4" max="4" customWidth="true" width="79.4285714285714"/>
+    <col min="5" max="5" customWidth="true" width="11.5714285714286"/>
+    <col min="6" max="6" customWidth="true" width="5.14285714285714"/>
+    <col min="7" max="7" customWidth="true" width="11.0"/>
+    <col min="8" max="8" customWidth="true" width="12.7142857142857"/>
+    <col min="9" max="9" customWidth="true" width="5.85714285714286"/>
+    <col min="10" max="10" customWidth="true" width="6.0"/>
+    <col min="11" max="11" customWidth="true" width="5.85714285714286"/>
+    <col min="12" max="12" customWidth="true" width="14.2857142857143"/>
+    <col min="13" max="13" customWidth="true" width="9.42857142857143"/>
+    <col min="14" max="14" customWidth="true" width="14.4285714285714"/>
+    <col min="15" max="15" customWidth="true" width="15.5714285714286"/>
+    <col min="16" max="16" customWidth="true" width="14.4285714285714"/>
+    <col min="17" max="17" customWidth="true" width="39.4285714285714"/>
+    <col min="18" max="18" customWidth="true" width="11.7142857142857"/>
+    <col min="19" max="19" customWidth="true" width="11.8571428571429"/>
+    <col min="20" max="20" customWidth="true" width="6.42857142857143"/>
+    <col min="21" max="22" customWidth="true" width="6.57142857142857"/>
+    <col min="23" max="23" customWidth="true" width="37.1428571428571"/>
+    <col min="24" max="25" customWidth="true" width="8.0"/>
+    <col min="26" max="26" customWidth="true" width="7.71428571428571"/>
+    <col min="27" max="27" customWidth="true" width="6.28571428571429"/>
+    <col min="28" max="28" customWidth="true" width="9.28571428571429"/>
+    <col min="29" max="29" customWidth="true" width="9.71428571428571"/>
+    <col min="30" max="30" customWidth="true" width="12.8571428571429"/>
+    <col min="31" max="31" customWidth="true" width="16.1428571428571"/>
+    <col min="32" max="32" customWidth="true" width="15.4285714285714"/>
+    <col min="33" max="33" customWidth="true" width="24.5714285714286"/>
+    <col min="34" max="34" customWidth="true" width="8.57142857142857"/>
+    <col min="35" max="35" customWidth="true" width="14.7142857142857"/>
+    <col min="36" max="36" customWidth="true" width="18.5714285714286"/>
+    <col min="37" max="37" customWidth="true" width="14.1428571428571"/>
+    <col min="38" max="38" customWidth="true" width="14.7142857142857"/>
+    <col min="39" max="39" customWidth="true" width="17.4285714285714"/>
+    <col min="40" max="40" customWidth="true" width="22.0"/>
+    <col min="41" max="41" customWidth="true" width="17.5714285714286"/>
+    <col min="42" max="42" customWidth="true" width="25.2857142857143"/>
+    <col min="43" max="43" customWidth="true" width="13.0"/>
+    <col min="44" max="44" customWidth="true" width="23.7142857142857"/>
+    <col min="45" max="45" customWidth="true" width="10.0"/>
+    <col min="46" max="46" customWidth="true" width="13.0"/>
+    <col min="47" max="47" customWidth="true" width="15.5714285714286"/>
+    <col min="48" max="48" customWidth="true" width="21.1428571428571"/>
+    <col min="49" max="49" customWidth="true" width="11.5714285714286"/>
+    <col min="50" max="50" customWidth="true" width="16.7142857142857"/>
+    <col min="51" max="51" customWidth="true" width="14.0"/>
+    <col min="52" max="52" customWidth="true" width="19.4285714285714"/>
+    <col min="53" max="53" customWidth="true" width="18.8571428571429"/>
+    <col min="54" max="54" customWidth="true" width="23.2857142857143"/>
+    <col min="55" max="55" customWidth="true" width="15.5714285714286"/>
+    <col min="56" max="56" customWidth="true" width="14.2857142857143"/>
+    <col min="57" max="57" customWidth="true" width="17.0"/>
+    <col min="58" max="58" customWidth="true" width="16.2857142857143"/>
+    <col min="59" max="59" customWidth="true" width="13.5714285714286"/>
+    <col min="60" max="61" customWidth="true" width="12.7142857142857"/>
+    <col min="62" max="62" customWidth="true" width="21.8571428571429"/>
+    <col min="63" max="63" customWidth="true" width="30.5714285714286"/>
+    <col min="64" max="64" customWidth="true" width="10.0"/>
+    <col min="65" max="65" customWidth="true" width="42.5714285714286"/>
+    <col min="66" max="66" customWidth="true" width="38.1428571428571"/>
+    <col min="67" max="67" customWidth="true" width="19.4285714285714"/>
+    <col min="68" max="68" customWidth="true" width="35.4285714285714"/>
+    <col min="69" max="69" customWidth="true" width="9.57142857142857"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -13902,7 +13917,7 @@
       <c r="BP2" s="32"/>
       <c r="BQ2" s="32"/>
     </row>
-    <row r="3" ht="15.25" spans="1:69">
+    <row r="3" ht="15.75" spans="1:69">
       <c r="A3" s="33" t="s">
         <v>9</v>
       </c>
@@ -14111,7 +14126,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.25" spans="1:69">
+    <row r="4" ht="15.75" spans="1:69">
       <c r="A4" s="31">
         <v>1</v>
       </c>
@@ -14182,7 +14197,7 @@
         <v>88363222</v>
       </c>
       <c r="U4" s="17">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="V4" s="17">
         <f>IF(OR($C$2=1,$C$2=4),ROUND((((S4*U4)/100)/2),2),0)</f>
@@ -14194,7 +14209,7 @@
       </c>
       <c r="X4" s="17">
         <f>IF($C$2=2,ROUND(((S4*U4)/100),2),0)</f>
-        <v>0</v>
+        <v>67.77</v>
       </c>
       <c r="Y4" s="17">
         <f>IF($C$2=4,ROUND((((S4*U4)/100)/2),2),0)</f>
@@ -14209,11 +14224,11 @@
       </c>
       <c r="AB4" s="17">
         <f>V4+W4+X4+Y4+AA4</f>
-        <v>15.0592</v>
+        <v>82.8292</v>
       </c>
       <c r="AC4" s="17">
         <f>IF($V2=1,S4+AB4,S4)</f>
-        <v>391.5392</v>
+        <v>459.3092</v>
       </c>
       <c r="AD4" s="17">
         <v>120</v>
@@ -14380,18 +14395,18 @@
       </c>
       <c r="X5" s="42">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>67.77</v>
       </c>
       <c r="Y5" s="44"/>
       <c r="Z5" s="44"/>
       <c r="AA5" s="44"/>
       <c r="AB5" s="42">
         <f t="shared" ref="AB5:AE5" si="1">SUM(AB4:AB4)</f>
-        <v>15.0592</v>
+        <v>82.8292</v>
       </c>
       <c r="AC5" s="42">
         <f t="shared" si="1"/>
-        <v>391.5392</v>
+        <v>459.3092</v>
       </c>
       <c r="AD5" s="42">
         <f t="shared" si="1"/>
@@ -14468,73 +14483,73 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ5"/>
-  <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="8.7047619047619" defaultRowHeight="15" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" width="5.14545454545455" customWidth="1"/>
-    <col min="2" max="3" width="27.5727272727273" customWidth="1"/>
-    <col min="4" max="4" width="79.4272727272727" customWidth="1"/>
-    <col min="5" max="5" width="11.5727272727273" customWidth="1"/>
-    <col min="6" max="6" width="5.14545454545455" customWidth="1"/>
-    <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="12.7181818181818" customWidth="1"/>
-    <col min="9" max="9" width="5.85454545454545" customWidth="1"/>
-    <col min="10" max="10" width="6" customWidth="1"/>
-    <col min="11" max="11" width="5.85454545454545" customWidth="1"/>
-    <col min="12" max="12" width="14.2818181818182" customWidth="1"/>
-    <col min="13" max="13" width="9.42727272727273" customWidth="1"/>
-    <col min="14" max="14" width="14.4272727272727" customWidth="1"/>
-    <col min="15" max="15" width="15.5727272727273" customWidth="1"/>
-    <col min="16" max="16" width="14.4272727272727" customWidth="1"/>
-    <col min="17" max="17" width="39.4272727272727" customWidth="1"/>
-    <col min="18" max="18" width="11.7181818181818" customWidth="1"/>
-    <col min="19" max="19" width="11.8545454545455" customWidth="1"/>
-    <col min="20" max="20" width="6.42727272727273" customWidth="1"/>
-    <col min="21" max="22" width="6.57272727272727" customWidth="1"/>
-    <col min="23" max="23" width="37.1454545454545" customWidth="1"/>
-    <col min="24" max="25" width="8" customWidth="1"/>
-    <col min="26" max="26" width="7.71818181818182" customWidth="1"/>
-    <col min="27" max="27" width="6.28181818181818" customWidth="1"/>
-    <col min="28" max="28" width="9.28181818181818" customWidth="1"/>
-    <col min="29" max="29" width="9.71818181818182" customWidth="1"/>
-    <col min="30" max="30" width="12.8545454545455" customWidth="1"/>
-    <col min="31" max="31" width="16.1454545454545" customWidth="1"/>
-    <col min="32" max="32" width="15.4272727272727" customWidth="1"/>
-    <col min="33" max="33" width="24.5727272727273" customWidth="1"/>
-    <col min="34" max="34" width="8.57272727272727" customWidth="1"/>
-    <col min="35" max="35" width="14.7181818181818" customWidth="1"/>
-    <col min="36" max="36" width="18.5727272727273" customWidth="1"/>
-    <col min="37" max="37" width="14.1454545454545" customWidth="1"/>
-    <col min="38" max="38" width="14.7181818181818" customWidth="1"/>
-    <col min="39" max="39" width="17.4272727272727" customWidth="1"/>
-    <col min="40" max="40" width="22" customWidth="1"/>
-    <col min="41" max="41" width="17.5727272727273" customWidth="1"/>
-    <col min="42" max="42" width="25.2818181818182" customWidth="1"/>
-    <col min="43" max="43" width="13" customWidth="1"/>
-    <col min="44" max="44" width="23.7181818181818" customWidth="1"/>
-    <col min="45" max="45" width="10" customWidth="1"/>
-    <col min="46" max="46" width="13" customWidth="1"/>
-    <col min="47" max="47" width="15.5727272727273" customWidth="1"/>
-    <col min="48" max="48" width="21.1454545454545" customWidth="1"/>
-    <col min="49" max="49" width="11.5727272727273" customWidth="1"/>
-    <col min="50" max="50" width="16.7181818181818" customWidth="1"/>
-    <col min="51" max="51" width="14" customWidth="1"/>
-    <col min="52" max="52" width="19.4272727272727" customWidth="1"/>
-    <col min="53" max="53" width="18.8545454545455" customWidth="1"/>
-    <col min="54" max="54" width="23.2818181818182" customWidth="1"/>
-    <col min="55" max="55" width="15.5727272727273" customWidth="1"/>
-    <col min="56" max="56" width="14.2818181818182" customWidth="1"/>
-    <col min="57" max="57" width="17" customWidth="1"/>
-    <col min="58" max="58" width="16.2818181818182" customWidth="1"/>
-    <col min="59" max="59" width="13.5727272727273" customWidth="1"/>
-    <col min="60" max="61" width="12.7181818181818" customWidth="1"/>
-    <col min="62" max="62" width="21.8545454545455" customWidth="1"/>
-    <col min="63" max="63" width="30.5727272727273" customWidth="1"/>
-    <col min="64" max="64" width="10" customWidth="1"/>
-    <col min="65" max="65" width="42.5727272727273" customWidth="1"/>
-    <col min="66" max="66" width="38.1454545454545" customWidth="1"/>
-    <col min="67" max="67" width="19.4272727272727" customWidth="1"/>
-    <col min="68" max="68" width="35.4272727272727" customWidth="1"/>
-    <col min="69" max="69" width="9.57272727272727" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="5.14285714285714"/>
+    <col min="2" max="3" customWidth="true" width="27.5714285714286"/>
+    <col min="4" max="4" customWidth="true" width="79.4285714285714"/>
+    <col min="5" max="5" customWidth="true" width="11.5714285714286"/>
+    <col min="6" max="6" customWidth="true" width="5.14285714285714"/>
+    <col min="7" max="7" customWidth="true" width="11.0"/>
+    <col min="8" max="8" customWidth="true" width="12.7142857142857"/>
+    <col min="9" max="9" customWidth="true" width="5.85714285714286"/>
+    <col min="10" max="10" customWidth="true" width="6.0"/>
+    <col min="11" max="11" customWidth="true" width="5.85714285714286"/>
+    <col min="12" max="12" customWidth="true" width="14.2857142857143"/>
+    <col min="13" max="13" customWidth="true" width="9.42857142857143"/>
+    <col min="14" max="14" customWidth="true" width="14.4285714285714"/>
+    <col min="15" max="15" customWidth="true" width="15.5714285714286"/>
+    <col min="16" max="16" customWidth="true" width="14.4285714285714"/>
+    <col min="17" max="17" customWidth="true" width="39.4285714285714"/>
+    <col min="18" max="18" customWidth="true" width="11.7142857142857"/>
+    <col min="19" max="19" customWidth="true" width="11.8571428571429"/>
+    <col min="20" max="20" customWidth="true" width="6.42857142857143"/>
+    <col min="21" max="22" customWidth="true" width="6.57142857142857"/>
+    <col min="23" max="23" customWidth="true" width="37.1428571428571"/>
+    <col min="24" max="25" customWidth="true" width="8.0"/>
+    <col min="26" max="26" customWidth="true" width="7.71428571428571"/>
+    <col min="27" max="27" customWidth="true" width="6.28571428571429"/>
+    <col min="28" max="28" customWidth="true" width="9.28571428571429"/>
+    <col min="29" max="29" customWidth="true" width="9.71428571428571"/>
+    <col min="30" max="30" customWidth="true" width="12.8571428571429"/>
+    <col min="31" max="31" customWidth="true" width="16.1428571428571"/>
+    <col min="32" max="32" customWidth="true" width="15.4285714285714"/>
+    <col min="33" max="33" customWidth="true" width="24.5714285714286"/>
+    <col min="34" max="34" customWidth="true" width="8.57142857142857"/>
+    <col min="35" max="35" customWidth="true" width="14.7142857142857"/>
+    <col min="36" max="36" customWidth="true" width="18.5714285714286"/>
+    <col min="37" max="37" customWidth="true" width="14.1428571428571"/>
+    <col min="38" max="38" customWidth="true" width="14.7142857142857"/>
+    <col min="39" max="39" customWidth="true" width="17.4285714285714"/>
+    <col min="40" max="40" customWidth="true" width="22.0"/>
+    <col min="41" max="41" customWidth="true" width="17.5714285714286"/>
+    <col min="42" max="42" customWidth="true" width="25.2857142857143"/>
+    <col min="43" max="43" customWidth="true" width="13.0"/>
+    <col min="44" max="44" customWidth="true" width="23.7142857142857"/>
+    <col min="45" max="45" customWidth="true" width="10.0"/>
+    <col min="46" max="46" customWidth="true" width="13.0"/>
+    <col min="47" max="47" customWidth="true" width="15.5714285714286"/>
+    <col min="48" max="48" customWidth="true" width="21.1428571428571"/>
+    <col min="49" max="49" customWidth="true" width="11.5714285714286"/>
+    <col min="50" max="50" customWidth="true" width="16.7142857142857"/>
+    <col min="51" max="51" customWidth="true" width="14.0"/>
+    <col min="52" max="52" customWidth="true" width="19.4285714285714"/>
+    <col min="53" max="53" customWidth="true" width="18.8571428571429"/>
+    <col min="54" max="54" customWidth="true" width="23.2857142857143"/>
+    <col min="55" max="55" customWidth="true" width="15.5714285714286"/>
+    <col min="56" max="56" customWidth="true" width="14.2857142857143"/>
+    <col min="57" max="57" customWidth="true" width="17.0"/>
+    <col min="58" max="58" customWidth="true" width="16.2857142857143"/>
+    <col min="59" max="59" customWidth="true" width="13.5714285714286"/>
+    <col min="60" max="61" customWidth="true" width="12.7142857142857"/>
+    <col min="62" max="62" customWidth="true" width="21.8571428571429"/>
+    <col min="63" max="63" customWidth="true" width="30.5714285714286"/>
+    <col min="64" max="64" customWidth="true" width="10.0"/>
+    <col min="65" max="65" customWidth="true" width="42.5714285714286"/>
+    <col min="66" max="66" customWidth="true" width="38.1428571428571"/>
+    <col min="67" max="67" customWidth="true" width="19.4285714285714"/>
+    <col min="68" max="68" customWidth="true" width="35.4285714285714"/>
+    <col min="69" max="69" customWidth="true" width="9.57142857142857"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -14705,7 +14720,7 @@
       <c r="BP2" s="32"/>
       <c r="BQ2" s="32"/>
     </row>
-    <row r="3" ht="15.25" spans="1:69">
+    <row r="3" ht="15.75" spans="1:69">
       <c r="A3" s="33" t="s">
         <v>9</v>
       </c>
@@ -14914,7 +14929,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.25" spans="1:69">
+    <row r="4" ht="15.75" spans="1:69">
       <c r="A4" s="31">
         <v>1</v>
       </c>
@@ -14985,7 +15000,7 @@
         <v>88363222</v>
       </c>
       <c r="U4" s="17">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="V4" s="17">
         <f>IF(OR($C$2=1,$C$2=4),ROUND((((S4*U4)/100)/2),2),0)</f>
@@ -14997,7 +15012,7 @@
       </c>
       <c r="X4" s="17">
         <f>IF($C$2=2,ROUND(((S4*U4)/100),2),0)</f>
-        <v>0</v>
+        <v>68.46</v>
       </c>
       <c r="Y4" s="17">
         <f>IF($C$2=4,ROUND((((S4*U4)/100)/2),2),0)</f>
@@ -15012,11 +15027,11 @@
       </c>
       <c r="AB4" s="17">
         <f>V4+W4+X4+Y4+AA4</f>
-        <v>15.2128</v>
+        <v>83.6728</v>
       </c>
       <c r="AC4" s="17">
         <f>IF($V2=1,S4+AB4,S4)</f>
-        <v>395.5328</v>
+        <v>463.9928</v>
       </c>
       <c r="AD4" s="17">
         <v>120</v>
@@ -15183,7 +15198,7 @@
       </c>
       <c r="X5" s="42">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>68.46</v>
       </c>
       <c r="Y5" s="42">
         <f t="shared" si="0"/>
@@ -15199,11 +15214,11 @@
       </c>
       <c r="AB5" s="42">
         <f t="shared" si="0"/>
-        <v>15.2128</v>
+        <v>83.6728</v>
       </c>
       <c r="AC5" s="42">
         <f t="shared" si="0"/>
-        <v>395.5328</v>
+        <v>463.9928</v>
       </c>
       <c r="AD5" s="42">
         <f t="shared" si="0"/>
@@ -15283,73 +15298,73 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ5"/>
-  <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="8.7047619047619" defaultRowHeight="15" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" width="5.14545454545455" customWidth="1"/>
-    <col min="2" max="3" width="27.5727272727273" customWidth="1"/>
-    <col min="4" max="4" width="79.4272727272727" customWidth="1"/>
-    <col min="5" max="5" width="11.5727272727273" customWidth="1"/>
-    <col min="6" max="6" width="5.14545454545455" customWidth="1"/>
-    <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="12.7181818181818" customWidth="1"/>
-    <col min="9" max="9" width="5.85454545454545" customWidth="1"/>
-    <col min="10" max="10" width="6" customWidth="1"/>
-    <col min="11" max="11" width="5.85454545454545" customWidth="1"/>
-    <col min="12" max="12" width="14.2818181818182" customWidth="1"/>
-    <col min="13" max="13" width="9.42727272727273" customWidth="1"/>
-    <col min="14" max="14" width="14.4272727272727" customWidth="1"/>
-    <col min="15" max="15" width="15.5727272727273" customWidth="1"/>
-    <col min="16" max="16" width="14.4272727272727" customWidth="1"/>
-    <col min="17" max="17" width="39.4272727272727" customWidth="1"/>
-    <col min="18" max="18" width="11.7181818181818" customWidth="1"/>
-    <col min="19" max="19" width="11.8545454545455" customWidth="1"/>
-    <col min="20" max="20" width="6.42727272727273" customWidth="1"/>
-    <col min="21" max="22" width="6.57272727272727" customWidth="1"/>
-    <col min="23" max="23" width="37.1454545454545" customWidth="1"/>
-    <col min="24" max="25" width="8" customWidth="1"/>
-    <col min="26" max="26" width="7.71818181818182" customWidth="1"/>
-    <col min="27" max="27" width="6.28181818181818" customWidth="1"/>
-    <col min="28" max="28" width="9.28181818181818" customWidth="1"/>
-    <col min="29" max="29" width="9.71818181818182" customWidth="1"/>
-    <col min="30" max="30" width="12.8545454545455" customWidth="1"/>
-    <col min="31" max="31" width="16.1454545454545" customWidth="1"/>
-    <col min="32" max="32" width="15.4272727272727" customWidth="1"/>
-    <col min="33" max="33" width="24.5727272727273" customWidth="1"/>
-    <col min="34" max="34" width="8.57272727272727" customWidth="1"/>
-    <col min="35" max="35" width="14.7181818181818" customWidth="1"/>
-    <col min="36" max="36" width="18.5727272727273" customWidth="1"/>
-    <col min="37" max="37" width="14.1454545454545" customWidth="1"/>
-    <col min="38" max="38" width="14.7181818181818" customWidth="1"/>
-    <col min="39" max="39" width="17.4272727272727" customWidth="1"/>
-    <col min="40" max="40" width="22" customWidth="1"/>
-    <col min="41" max="41" width="17.5727272727273" customWidth="1"/>
-    <col min="42" max="42" width="25.2818181818182" customWidth="1"/>
-    <col min="43" max="43" width="13" customWidth="1"/>
-    <col min="44" max="44" width="23.7181818181818" customWidth="1"/>
-    <col min="45" max="45" width="10" customWidth="1"/>
-    <col min="46" max="46" width="13" customWidth="1"/>
-    <col min="47" max="47" width="15.5727272727273" customWidth="1"/>
-    <col min="48" max="48" width="21.1454545454545" customWidth="1"/>
-    <col min="49" max="49" width="11.5727272727273" customWidth="1"/>
-    <col min="50" max="50" width="16.7181818181818" customWidth="1"/>
-    <col min="51" max="51" width="14" customWidth="1"/>
-    <col min="52" max="52" width="19.4272727272727" customWidth="1"/>
-    <col min="53" max="53" width="18.8545454545455" customWidth="1"/>
-    <col min="54" max="54" width="23.2818181818182" customWidth="1"/>
-    <col min="55" max="55" width="15.5727272727273" customWidth="1"/>
-    <col min="56" max="56" width="14.2818181818182" customWidth="1"/>
-    <col min="57" max="57" width="17" customWidth="1"/>
-    <col min="58" max="58" width="16.2818181818182" customWidth="1"/>
-    <col min="59" max="59" width="13.5727272727273" customWidth="1"/>
-    <col min="60" max="61" width="12.7181818181818" customWidth="1"/>
-    <col min="62" max="62" width="21.8545454545455" customWidth="1"/>
-    <col min="63" max="63" width="30.5727272727273" customWidth="1"/>
-    <col min="64" max="64" width="10" customWidth="1"/>
-    <col min="65" max="65" width="42.5727272727273" customWidth="1"/>
-    <col min="66" max="66" width="38.1454545454545" customWidth="1"/>
-    <col min="67" max="67" width="19.4272727272727" customWidth="1"/>
-    <col min="68" max="68" width="35.4272727272727" customWidth="1"/>
-    <col min="69" max="69" width="9.57272727272727" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="5.14285714285714"/>
+    <col min="2" max="3" customWidth="true" width="27.5714285714286"/>
+    <col min="4" max="4" customWidth="true" width="79.4285714285714"/>
+    <col min="5" max="5" customWidth="true" width="11.5714285714286"/>
+    <col min="6" max="6" customWidth="true" width="5.14285714285714"/>
+    <col min="7" max="7" customWidth="true" width="11.0"/>
+    <col min="8" max="8" customWidth="true" width="12.7142857142857"/>
+    <col min="9" max="9" customWidth="true" width="5.85714285714286"/>
+    <col min="10" max="10" customWidth="true" width="6.0"/>
+    <col min="11" max="11" customWidth="true" width="5.85714285714286"/>
+    <col min="12" max="12" customWidth="true" width="14.2857142857143"/>
+    <col min="13" max="13" customWidth="true" width="9.42857142857143"/>
+    <col min="14" max="14" customWidth="true" width="14.4285714285714"/>
+    <col min="15" max="15" customWidth="true" width="15.5714285714286"/>
+    <col min="16" max="16" customWidth="true" width="14.4285714285714"/>
+    <col min="17" max="17" customWidth="true" width="39.4285714285714"/>
+    <col min="18" max="18" customWidth="true" width="11.7142857142857"/>
+    <col min="19" max="19" customWidth="true" width="11.8571428571429"/>
+    <col min="20" max="20" customWidth="true" width="6.42857142857143"/>
+    <col min="21" max="22" customWidth="true" width="6.57142857142857"/>
+    <col min="23" max="23" customWidth="true" width="37.1428571428571"/>
+    <col min="24" max="25" customWidth="true" width="8.0"/>
+    <col min="26" max="26" customWidth="true" width="7.71428571428571"/>
+    <col min="27" max="27" customWidth="true" width="6.28571428571429"/>
+    <col min="28" max="28" customWidth="true" width="9.28571428571429"/>
+    <col min="29" max="29" customWidth="true" width="9.71428571428571"/>
+    <col min="30" max="30" customWidth="true" width="12.8571428571429"/>
+    <col min="31" max="31" customWidth="true" width="16.1428571428571"/>
+    <col min="32" max="32" customWidth="true" width="15.4285714285714"/>
+    <col min="33" max="33" customWidth="true" width="24.5714285714286"/>
+    <col min="34" max="34" customWidth="true" width="8.57142857142857"/>
+    <col min="35" max="35" customWidth="true" width="14.7142857142857"/>
+    <col min="36" max="36" customWidth="true" width="18.5714285714286"/>
+    <col min="37" max="37" customWidth="true" width="14.1428571428571"/>
+    <col min="38" max="38" customWidth="true" width="14.7142857142857"/>
+    <col min="39" max="39" customWidth="true" width="17.4285714285714"/>
+    <col min="40" max="40" customWidth="true" width="22.0"/>
+    <col min="41" max="41" customWidth="true" width="17.5714285714286"/>
+    <col min="42" max="42" customWidth="true" width="25.2857142857143"/>
+    <col min="43" max="43" customWidth="true" width="13.0"/>
+    <col min="44" max="44" customWidth="true" width="23.7142857142857"/>
+    <col min="45" max="45" customWidth="true" width="10.0"/>
+    <col min="46" max="46" customWidth="true" width="13.0"/>
+    <col min="47" max="47" customWidth="true" width="15.5714285714286"/>
+    <col min="48" max="48" customWidth="true" width="21.1428571428571"/>
+    <col min="49" max="49" customWidth="true" width="11.5714285714286"/>
+    <col min="50" max="50" customWidth="true" width="16.7142857142857"/>
+    <col min="51" max="51" customWidth="true" width="14.0"/>
+    <col min="52" max="52" customWidth="true" width="19.4285714285714"/>
+    <col min="53" max="53" customWidth="true" width="18.8571428571429"/>
+    <col min="54" max="54" customWidth="true" width="23.2857142857143"/>
+    <col min="55" max="55" customWidth="true" width="15.5714285714286"/>
+    <col min="56" max="56" customWidth="true" width="14.2857142857143"/>
+    <col min="57" max="57" customWidth="true" width="17.0"/>
+    <col min="58" max="58" customWidth="true" width="16.2857142857143"/>
+    <col min="59" max="59" customWidth="true" width="13.5714285714286"/>
+    <col min="60" max="61" customWidth="true" width="12.7142857142857"/>
+    <col min="62" max="62" customWidth="true" width="21.8571428571429"/>
+    <col min="63" max="63" customWidth="true" width="30.5714285714286"/>
+    <col min="64" max="64" customWidth="true" width="10.0"/>
+    <col min="65" max="65" customWidth="true" width="42.5714285714286"/>
+    <col min="66" max="66" customWidth="true" width="38.1428571428571"/>
+    <col min="67" max="67" customWidth="true" width="19.4285714285714"/>
+    <col min="68" max="68" customWidth="true" width="35.4285714285714"/>
+    <col min="69" max="69" customWidth="true" width="9.57142857142857"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -15520,7 +15535,7 @@
       <c r="BP2" s="32"/>
       <c r="BQ2" s="32"/>
     </row>
-    <row r="3" ht="15.25" spans="1:69">
+    <row r="3" ht="15.75" spans="1:69">
       <c r="A3" s="33" t="s">
         <v>9</v>
       </c>
@@ -15729,7 +15744,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.25" spans="1:69">
+    <row r="4" ht="15.75" spans="1:69">
       <c r="A4" s="31">
         <v>1</v>
       </c>
@@ -15800,7 +15815,7 @@
         <v>88363222</v>
       </c>
       <c r="U4" s="17">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="V4" s="17">
         <f>IF(OR($C$2=1,$C$2=4),ROUND((((S4*U4)/100)/2),2),0)</f>
@@ -15812,7 +15827,7 @@
       </c>
       <c r="X4" s="17">
         <f>IF($C$2=2,ROUND(((S4*U4)/100),2),0)</f>
-        <v>0</v>
+        <v>68.46</v>
       </c>
       <c r="Y4" s="17">
         <f>IF($C$2=4,ROUND((((S4*U4)/100)/2),2),0)</f>
@@ -15827,11 +15842,11 @@
       </c>
       <c r="AB4" s="17">
         <f>V4+W4+X4+Y4+AA4</f>
-        <v>15.2128</v>
+        <v>83.6728</v>
       </c>
       <c r="AC4" s="17">
         <f>IF($V2=1,S4+AB4,S4)</f>
-        <v>395.5328</v>
+        <v>463.9928</v>
       </c>
       <c r="AD4" s="17">
         <v>120</v>
@@ -15998,7 +16013,7 @@
       </c>
       <c r="X5" s="42">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>68.46</v>
       </c>
       <c r="Y5" s="42">
         <f t="shared" si="0"/>
@@ -16014,11 +16029,11 @@
       </c>
       <c r="AB5" s="42">
         <f t="shared" si="0"/>
-        <v>15.2128</v>
+        <v>83.6728</v>
       </c>
       <c r="AC5" s="42">
         <f t="shared" si="0"/>
-        <v>395.5328</v>
+        <v>463.9928</v>
       </c>
       <c r="AD5" s="42">
         <f t="shared" si="0"/>
@@ -16098,73 +16113,73 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ5"/>
-  <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="8.7047619047619" defaultRowHeight="15" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" width="5.14545454545455" customWidth="1"/>
-    <col min="2" max="3" width="27.5727272727273" customWidth="1"/>
-    <col min="4" max="4" width="79.4272727272727" customWidth="1"/>
-    <col min="5" max="5" width="11.5727272727273" customWidth="1"/>
-    <col min="6" max="6" width="5.14545454545455" customWidth="1"/>
-    <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="12.7181818181818" customWidth="1"/>
-    <col min="9" max="9" width="5.85454545454545" customWidth="1"/>
-    <col min="10" max="10" width="6" customWidth="1"/>
-    <col min="11" max="11" width="5.85454545454545" customWidth="1"/>
-    <col min="12" max="12" width="14.2818181818182" customWidth="1"/>
-    <col min="13" max="13" width="9.42727272727273" customWidth="1"/>
-    <col min="14" max="14" width="14.4272727272727" customWidth="1"/>
-    <col min="15" max="15" width="15.5727272727273" customWidth="1"/>
-    <col min="16" max="16" width="14.4272727272727" customWidth="1"/>
-    <col min="17" max="17" width="39.4272727272727" customWidth="1"/>
-    <col min="18" max="18" width="11.7181818181818" customWidth="1"/>
-    <col min="19" max="19" width="11.8545454545455" customWidth="1"/>
-    <col min="20" max="20" width="6.42727272727273" customWidth="1"/>
-    <col min="21" max="22" width="6.57272727272727" customWidth="1"/>
-    <col min="23" max="23" width="37.1454545454545" customWidth="1"/>
-    <col min="24" max="25" width="8" customWidth="1"/>
-    <col min="26" max="26" width="7.71818181818182" customWidth="1"/>
-    <col min="27" max="27" width="6.28181818181818" customWidth="1"/>
-    <col min="28" max="28" width="9.28181818181818" customWidth="1"/>
-    <col min="29" max="29" width="9.71818181818182" customWidth="1"/>
-    <col min="30" max="30" width="12.8545454545455" customWidth="1"/>
-    <col min="31" max="31" width="16.1454545454545" customWidth="1"/>
-    <col min="32" max="32" width="15.4272727272727" customWidth="1"/>
-    <col min="33" max="33" width="24.5727272727273" customWidth="1"/>
-    <col min="34" max="34" width="8.57272727272727" customWidth="1"/>
-    <col min="35" max="35" width="14.7181818181818" customWidth="1"/>
-    <col min="36" max="36" width="18.5727272727273" customWidth="1"/>
-    <col min="37" max="37" width="14.1454545454545" customWidth="1"/>
-    <col min="38" max="38" width="14.7181818181818" customWidth="1"/>
-    <col min="39" max="39" width="17.4272727272727" customWidth="1"/>
-    <col min="40" max="40" width="22" customWidth="1"/>
-    <col min="41" max="41" width="17.5727272727273" customWidth="1"/>
-    <col min="42" max="42" width="25.2818181818182" customWidth="1"/>
-    <col min="43" max="43" width="13" customWidth="1"/>
-    <col min="44" max="44" width="23.7181818181818" customWidth="1"/>
-    <col min="45" max="45" width="10" customWidth="1"/>
-    <col min="46" max="46" width="13" customWidth="1"/>
-    <col min="47" max="47" width="15.5727272727273" customWidth="1"/>
-    <col min="48" max="48" width="21.1454545454545" customWidth="1"/>
-    <col min="49" max="49" width="11.5727272727273" customWidth="1"/>
-    <col min="50" max="50" width="16.7181818181818" customWidth="1"/>
-    <col min="51" max="51" width="14" customWidth="1"/>
-    <col min="52" max="52" width="19.4272727272727" customWidth="1"/>
-    <col min="53" max="53" width="18.8545454545455" customWidth="1"/>
-    <col min="54" max="54" width="23.2818181818182" customWidth="1"/>
-    <col min="55" max="55" width="15.5727272727273" customWidth="1"/>
-    <col min="56" max="56" width="14.2818181818182" customWidth="1"/>
-    <col min="57" max="57" width="17" customWidth="1"/>
-    <col min="58" max="58" width="16.2818181818182" customWidth="1"/>
-    <col min="59" max="59" width="13.5727272727273" customWidth="1"/>
-    <col min="60" max="61" width="12.7181818181818" customWidth="1"/>
-    <col min="62" max="62" width="21.8545454545455" customWidth="1"/>
-    <col min="63" max="63" width="30.5727272727273" customWidth="1"/>
-    <col min="64" max="64" width="10" customWidth="1"/>
-    <col min="65" max="65" width="42.5727272727273" customWidth="1"/>
-    <col min="66" max="66" width="38.1454545454545" customWidth="1"/>
-    <col min="67" max="67" width="19.4272727272727" customWidth="1"/>
-    <col min="68" max="68" width="35.4272727272727" customWidth="1"/>
-    <col min="69" max="69" width="9.57272727272727" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="5.14285714285714"/>
+    <col min="2" max="3" customWidth="true" width="27.5714285714286"/>
+    <col min="4" max="4" customWidth="true" width="79.4285714285714"/>
+    <col min="5" max="5" customWidth="true" width="11.5714285714286"/>
+    <col min="6" max="6" customWidth="true" width="5.14285714285714"/>
+    <col min="7" max="7" customWidth="true" width="11.0"/>
+    <col min="8" max="8" customWidth="true" width="12.7142857142857"/>
+    <col min="9" max="9" customWidth="true" width="5.85714285714286"/>
+    <col min="10" max="10" customWidth="true" width="6.0"/>
+    <col min="11" max="11" customWidth="true" width="5.85714285714286"/>
+    <col min="12" max="12" customWidth="true" width="14.2857142857143"/>
+    <col min="13" max="13" customWidth="true" width="9.42857142857143"/>
+    <col min="14" max="14" customWidth="true" width="14.4285714285714"/>
+    <col min="15" max="15" customWidth="true" width="15.5714285714286"/>
+    <col min="16" max="16" customWidth="true" width="14.4285714285714"/>
+    <col min="17" max="17" customWidth="true" width="39.4285714285714"/>
+    <col min="18" max="18" customWidth="true" width="11.7142857142857"/>
+    <col min="19" max="19" customWidth="true" width="11.8571428571429"/>
+    <col min="20" max="20" customWidth="true" width="6.42857142857143"/>
+    <col min="21" max="22" customWidth="true" width="6.57142857142857"/>
+    <col min="23" max="23" customWidth="true" width="37.1428571428571"/>
+    <col min="24" max="25" customWidth="true" width="8.0"/>
+    <col min="26" max="26" customWidth="true" width="7.71428571428571"/>
+    <col min="27" max="27" customWidth="true" width="6.28571428571429"/>
+    <col min="28" max="28" customWidth="true" width="9.28571428571429"/>
+    <col min="29" max="29" customWidth="true" width="9.71428571428571"/>
+    <col min="30" max="30" customWidth="true" width="12.8571428571429"/>
+    <col min="31" max="31" customWidth="true" width="16.1428571428571"/>
+    <col min="32" max="32" customWidth="true" width="15.4285714285714"/>
+    <col min="33" max="33" customWidth="true" width="24.5714285714286"/>
+    <col min="34" max="34" customWidth="true" width="8.57142857142857"/>
+    <col min="35" max="35" customWidth="true" width="14.7142857142857"/>
+    <col min="36" max="36" customWidth="true" width="18.5714285714286"/>
+    <col min="37" max="37" customWidth="true" width="14.1428571428571"/>
+    <col min="38" max="38" customWidth="true" width="14.7142857142857"/>
+    <col min="39" max="39" customWidth="true" width="17.4285714285714"/>
+    <col min="40" max="40" customWidth="true" width="22.0"/>
+    <col min="41" max="41" customWidth="true" width="17.5714285714286"/>
+    <col min="42" max="42" customWidth="true" width="25.2857142857143"/>
+    <col min="43" max="43" customWidth="true" width="13.0"/>
+    <col min="44" max="44" customWidth="true" width="23.7142857142857"/>
+    <col min="45" max="45" customWidth="true" width="10.0"/>
+    <col min="46" max="46" customWidth="true" width="13.0"/>
+    <col min="47" max="47" customWidth="true" width="15.5714285714286"/>
+    <col min="48" max="48" customWidth="true" width="21.1428571428571"/>
+    <col min="49" max="49" customWidth="true" width="11.5714285714286"/>
+    <col min="50" max="50" customWidth="true" width="16.7142857142857"/>
+    <col min="51" max="51" customWidth="true" width="14.0"/>
+    <col min="52" max="52" customWidth="true" width="19.4285714285714"/>
+    <col min="53" max="53" customWidth="true" width="18.8571428571429"/>
+    <col min="54" max="54" customWidth="true" width="23.2857142857143"/>
+    <col min="55" max="55" customWidth="true" width="15.5714285714286"/>
+    <col min="56" max="56" customWidth="true" width="14.2857142857143"/>
+    <col min="57" max="57" customWidth="true" width="17.0"/>
+    <col min="58" max="58" customWidth="true" width="16.2857142857143"/>
+    <col min="59" max="59" customWidth="true" width="13.5714285714286"/>
+    <col min="60" max="61" customWidth="true" width="12.7142857142857"/>
+    <col min="62" max="62" customWidth="true" width="21.8571428571429"/>
+    <col min="63" max="63" customWidth="true" width="30.5714285714286"/>
+    <col min="64" max="64" customWidth="true" width="10.0"/>
+    <col min="65" max="65" customWidth="true" width="42.5714285714286"/>
+    <col min="66" max="66" customWidth="true" width="38.1428571428571"/>
+    <col min="67" max="67" customWidth="true" width="19.4285714285714"/>
+    <col min="68" max="68" customWidth="true" width="35.4285714285714"/>
+    <col min="69" max="69" customWidth="true" width="9.57142857142857"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -16335,7 +16350,7 @@
       <c r="BP2" s="8"/>
       <c r="BQ2" s="8"/>
     </row>
-    <row r="3" ht="15.25" spans="1:69">
+    <row r="3" ht="15.75" spans="1:69">
       <c r="A3" s="9" t="s">
         <v>9</v>
       </c>
@@ -16544,7 +16559,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.25" spans="1:69">
+    <row r="4" ht="15.75" spans="1:69">
       <c r="A4" s="6">
         <v>1</v>
       </c>
@@ -16615,7 +16630,7 @@
         <v>88363222</v>
       </c>
       <c r="U4" s="17">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="V4" s="17">
         <f>IF(OR($C$2=1,$C$2=4),ROUND((((S4*U4)/100)/2),2),0)</f>
@@ -16627,7 +16642,7 @@
       </c>
       <c r="X4" s="17">
         <f>IF($C$2=2,ROUND(((S4*U4)/100),2),0)</f>
-        <v>0</v>
+        <v>67.77</v>
       </c>
       <c r="Y4" s="17">
         <f>IF($C$2=4,ROUND((((S4*U4)/100)/2),2),0)</f>
@@ -16642,11 +16657,11 @@
       </c>
       <c r="AB4" s="17">
         <f>V4+W4+X4+Y4+AA4</f>
-        <v>15.0592</v>
+        <v>82.8292</v>
       </c>
       <c r="AC4" s="17">
         <f>IF($V2=1,S4+AB4,S4)</f>
-        <v>391.5392</v>
+        <v>459.3092</v>
       </c>
       <c r="AD4" s="17">
         <v>120</v>
@@ -16813,18 +16828,18 @@
       </c>
       <c r="X5" s="27">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>67.77</v>
       </c>
       <c r="Y5" s="28"/>
       <c r="Z5" s="28"/>
       <c r="AA5" s="28"/>
       <c r="AB5" s="27">
         <f t="shared" ref="AB5:AE5" si="1">SUM(AB4:AB4)</f>
-        <v>15.0592</v>
+        <v>82.8292</v>
       </c>
       <c r="AC5" s="27">
         <f t="shared" si="1"/>
-        <v>391.5392</v>
+        <v>459.3092</v>
       </c>
       <c r="AD5" s="27">
         <f t="shared" si="1"/>
@@ -16901,73 +16916,73 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ5"/>
-  <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="8.7047619047619" defaultRowHeight="15" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" width="5.14545454545455" customWidth="1"/>
-    <col min="2" max="3" width="27.5727272727273" customWidth="1"/>
-    <col min="4" max="4" width="79.4272727272727" customWidth="1"/>
-    <col min="5" max="5" width="11.5727272727273" customWidth="1"/>
-    <col min="6" max="6" width="5.14545454545455" customWidth="1"/>
-    <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="12.7181818181818" customWidth="1"/>
-    <col min="9" max="9" width="5.85454545454545" customWidth="1"/>
-    <col min="10" max="10" width="6" customWidth="1"/>
-    <col min="11" max="11" width="5.85454545454545" customWidth="1"/>
-    <col min="12" max="12" width="14.2818181818182" customWidth="1"/>
-    <col min="13" max="13" width="9.42727272727273" customWidth="1"/>
-    <col min="14" max="14" width="14.4272727272727" customWidth="1"/>
-    <col min="15" max="15" width="15.5727272727273" customWidth="1"/>
-    <col min="16" max="16" width="14.4272727272727" customWidth="1"/>
-    <col min="17" max="17" width="39.4272727272727" customWidth="1"/>
-    <col min="18" max="18" width="11.7181818181818" customWidth="1"/>
-    <col min="19" max="19" width="11.8545454545455" customWidth="1"/>
-    <col min="20" max="20" width="6.42727272727273" customWidth="1"/>
-    <col min="21" max="22" width="6.57272727272727" customWidth="1"/>
-    <col min="23" max="23" width="37.1454545454545" customWidth="1"/>
-    <col min="24" max="25" width="8" customWidth="1"/>
-    <col min="26" max="26" width="7.71818181818182" customWidth="1"/>
-    <col min="27" max="27" width="6.28181818181818" customWidth="1"/>
-    <col min="28" max="28" width="9.28181818181818" customWidth="1"/>
-    <col min="29" max="29" width="9.71818181818182" customWidth="1"/>
-    <col min="30" max="30" width="12.8545454545455" customWidth="1"/>
-    <col min="31" max="31" width="16.1454545454545" customWidth="1"/>
-    <col min="32" max="32" width="15.4272727272727" customWidth="1"/>
-    <col min="33" max="33" width="24.5727272727273" customWidth="1"/>
-    <col min="34" max="34" width="8.57272727272727" customWidth="1"/>
-    <col min="35" max="35" width="14.7181818181818" customWidth="1"/>
-    <col min="36" max="36" width="18.5727272727273" customWidth="1"/>
-    <col min="37" max="37" width="14.1454545454545" customWidth="1"/>
-    <col min="38" max="38" width="14.7181818181818" customWidth="1"/>
-    <col min="39" max="39" width="17.4272727272727" customWidth="1"/>
-    <col min="40" max="40" width="22" customWidth="1"/>
-    <col min="41" max="41" width="17.5727272727273" customWidth="1"/>
-    <col min="42" max="42" width="25.2818181818182" customWidth="1"/>
-    <col min="43" max="43" width="13" customWidth="1"/>
-    <col min="44" max="44" width="23.7181818181818" customWidth="1"/>
-    <col min="45" max="45" width="10" customWidth="1"/>
-    <col min="46" max="46" width="13" customWidth="1"/>
-    <col min="47" max="47" width="15.5727272727273" customWidth="1"/>
-    <col min="48" max="48" width="21.1454545454545" customWidth="1"/>
-    <col min="49" max="49" width="11.5727272727273" customWidth="1"/>
-    <col min="50" max="50" width="16.7181818181818" customWidth="1"/>
-    <col min="51" max="51" width="14" customWidth="1"/>
-    <col min="52" max="52" width="19.4272727272727" customWidth="1"/>
-    <col min="53" max="53" width="18.8545454545455" customWidth="1"/>
-    <col min="54" max="54" width="23.2818181818182" customWidth="1"/>
-    <col min="55" max="55" width="15.5727272727273" customWidth="1"/>
-    <col min="56" max="56" width="14.2818181818182" customWidth="1"/>
-    <col min="57" max="57" width="17" customWidth="1"/>
-    <col min="58" max="58" width="16.2818181818182" customWidth="1"/>
-    <col min="59" max="59" width="13.5727272727273" customWidth="1"/>
-    <col min="60" max="61" width="12.7181818181818" customWidth="1"/>
-    <col min="62" max="62" width="21.8545454545455" customWidth="1"/>
-    <col min="63" max="63" width="30.5727272727273" customWidth="1"/>
-    <col min="64" max="64" width="10" customWidth="1"/>
-    <col min="65" max="65" width="42.5727272727273" customWidth="1"/>
-    <col min="66" max="66" width="38.1454545454545" customWidth="1"/>
-    <col min="67" max="67" width="19.4272727272727" customWidth="1"/>
-    <col min="68" max="68" width="35.4272727272727" customWidth="1"/>
-    <col min="69" max="69" width="9.57272727272727" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="5.14285714285714"/>
+    <col min="2" max="3" customWidth="true" width="27.5714285714286"/>
+    <col min="4" max="4" customWidth="true" width="79.4285714285714"/>
+    <col min="5" max="5" customWidth="true" width="11.5714285714286"/>
+    <col min="6" max="6" customWidth="true" width="5.14285714285714"/>
+    <col min="7" max="7" customWidth="true" width="11.0"/>
+    <col min="8" max="8" customWidth="true" width="12.7142857142857"/>
+    <col min="9" max="9" customWidth="true" width="5.85714285714286"/>
+    <col min="10" max="10" customWidth="true" width="6.0"/>
+    <col min="11" max="11" customWidth="true" width="5.85714285714286"/>
+    <col min="12" max="12" customWidth="true" width="14.2857142857143"/>
+    <col min="13" max="13" customWidth="true" width="9.42857142857143"/>
+    <col min="14" max="14" customWidth="true" width="14.4285714285714"/>
+    <col min="15" max="15" customWidth="true" width="15.5714285714286"/>
+    <col min="16" max="16" customWidth="true" width="14.4285714285714"/>
+    <col min="17" max="17" customWidth="true" width="39.4285714285714"/>
+    <col min="18" max="18" customWidth="true" width="11.7142857142857"/>
+    <col min="19" max="19" customWidth="true" width="11.8571428571429"/>
+    <col min="20" max="20" customWidth="true" width="6.42857142857143"/>
+    <col min="21" max="22" customWidth="true" width="6.57142857142857"/>
+    <col min="23" max="23" customWidth="true" width="37.1428571428571"/>
+    <col min="24" max="25" customWidth="true" width="8.0"/>
+    <col min="26" max="26" customWidth="true" width="7.71428571428571"/>
+    <col min="27" max="27" customWidth="true" width="6.28571428571429"/>
+    <col min="28" max="28" customWidth="true" width="9.28571428571429"/>
+    <col min="29" max="29" customWidth="true" width="9.71428571428571"/>
+    <col min="30" max="30" customWidth="true" width="12.8571428571429"/>
+    <col min="31" max="31" customWidth="true" width="16.1428571428571"/>
+    <col min="32" max="32" customWidth="true" width="15.4285714285714"/>
+    <col min="33" max="33" customWidth="true" width="24.5714285714286"/>
+    <col min="34" max="34" customWidth="true" width="8.57142857142857"/>
+    <col min="35" max="35" customWidth="true" width="14.7142857142857"/>
+    <col min="36" max="36" customWidth="true" width="18.5714285714286"/>
+    <col min="37" max="37" customWidth="true" width="14.1428571428571"/>
+    <col min="38" max="38" customWidth="true" width="14.7142857142857"/>
+    <col min="39" max="39" customWidth="true" width="17.4285714285714"/>
+    <col min="40" max="40" customWidth="true" width="22.0"/>
+    <col min="41" max="41" customWidth="true" width="17.5714285714286"/>
+    <col min="42" max="42" customWidth="true" width="25.2857142857143"/>
+    <col min="43" max="43" customWidth="true" width="13.0"/>
+    <col min="44" max="44" customWidth="true" width="23.7142857142857"/>
+    <col min="45" max="45" customWidth="true" width="10.0"/>
+    <col min="46" max="46" customWidth="true" width="13.0"/>
+    <col min="47" max="47" customWidth="true" width="15.5714285714286"/>
+    <col min="48" max="48" customWidth="true" width="21.1428571428571"/>
+    <col min="49" max="49" customWidth="true" width="11.5714285714286"/>
+    <col min="50" max="50" customWidth="true" width="16.7142857142857"/>
+    <col min="51" max="51" customWidth="true" width="14.0"/>
+    <col min="52" max="52" customWidth="true" width="19.4285714285714"/>
+    <col min="53" max="53" customWidth="true" width="18.8571428571429"/>
+    <col min="54" max="54" customWidth="true" width="23.2857142857143"/>
+    <col min="55" max="55" customWidth="true" width="15.5714285714286"/>
+    <col min="56" max="56" customWidth="true" width="14.2857142857143"/>
+    <col min="57" max="57" customWidth="true" width="17.0"/>
+    <col min="58" max="58" customWidth="true" width="16.2857142857143"/>
+    <col min="59" max="59" customWidth="true" width="13.5714285714286"/>
+    <col min="60" max="61" customWidth="true" width="12.7142857142857"/>
+    <col min="62" max="62" customWidth="true" width="21.8571428571429"/>
+    <col min="63" max="63" customWidth="true" width="30.5714285714286"/>
+    <col min="64" max="64" customWidth="true" width="10.0"/>
+    <col min="65" max="65" customWidth="true" width="42.5714285714286"/>
+    <col min="66" max="66" customWidth="true" width="38.1428571428571"/>
+    <col min="67" max="67" customWidth="true" width="19.4285714285714"/>
+    <col min="68" max="68" customWidth="true" width="35.4285714285714"/>
+    <col min="69" max="69" customWidth="true" width="9.57142857142857"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -17138,7 +17153,7 @@
       <c r="BP2" s="8"/>
       <c r="BQ2" s="8"/>
     </row>
-    <row r="3" ht="15.25" spans="1:69">
+    <row r="3" ht="15.75" spans="1:69">
       <c r="A3" s="9" t="s">
         <v>9</v>
       </c>
@@ -17347,7 +17362,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.25" spans="1:69">
+    <row r="4" ht="15.75" spans="1:69">
       <c r="A4" s="6">
         <v>1</v>
       </c>
@@ -17418,7 +17433,7 @@
         <v>88363222</v>
       </c>
       <c r="U4" s="17">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="V4" s="17">
         <f>IF(OR($C$2=1,$C$2=4),ROUND((((S4*U4)/100)/2),2),0)</f>
@@ -17430,7 +17445,7 @@
       </c>
       <c r="X4" s="17">
         <f>IF($C$2=2,ROUND(((S4*U4)/100),2),0)</f>
-        <v>0</v>
+        <v>67.77</v>
       </c>
       <c r="Y4" s="17">
         <f>IF($C$2=4,ROUND((((S4*U4)/100)/2),2),0)</f>
@@ -17445,11 +17460,11 @@
       </c>
       <c r="AB4" s="17">
         <f>V4+W4+X4+Y4+AA4</f>
-        <v>15.0592</v>
+        <v>82.8292</v>
       </c>
       <c r="AC4" s="17">
         <f>IF($V2=1,S4+AB4,S4)</f>
-        <v>391.5392</v>
+        <v>459.3092</v>
       </c>
       <c r="AD4" s="17">
         <v>120</v>
@@ -17616,18 +17631,18 @@
       </c>
       <c r="X5" s="27">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>67.77</v>
       </c>
       <c r="Y5" s="28"/>
       <c r="Z5" s="28"/>
       <c r="AA5" s="28"/>
       <c r="AB5" s="27">
         <f t="shared" ref="AB5:AE5" si="1">SUM(AB4:AB4)</f>
-        <v>15.0592</v>
+        <v>82.8292</v>
       </c>
       <c r="AC5" s="27">
         <f t="shared" si="1"/>
-        <v>391.5392</v>
+        <v>459.3092</v>
       </c>
       <c r="AD5" s="27">
         <f t="shared" si="1"/>
@@ -17704,73 +17719,73 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ5"/>
-  <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="8.7047619047619" defaultRowHeight="15" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" width="5.14545454545455" customWidth="1"/>
-    <col min="2" max="3" width="22" customWidth="1"/>
-    <col min="4" max="4" width="79.4272727272727" customWidth="1"/>
-    <col min="5" max="5" width="11.5727272727273" customWidth="1"/>
-    <col min="6" max="6" width="5.14545454545455" customWidth="1"/>
-    <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="12.7181818181818" customWidth="1"/>
-    <col min="9" max="9" width="5.85454545454545" customWidth="1"/>
-    <col min="10" max="10" width="6" customWidth="1"/>
-    <col min="11" max="11" width="5.85454545454545" customWidth="1"/>
-    <col min="12" max="12" width="14.2818181818182" customWidth="1"/>
-    <col min="13" max="13" width="9.42727272727273" customWidth="1"/>
-    <col min="14" max="14" width="14.4272727272727" customWidth="1"/>
-    <col min="15" max="15" width="15.5727272727273" customWidth="1"/>
-    <col min="16" max="16" width="14.4272727272727" customWidth="1"/>
-    <col min="17" max="17" width="39.4272727272727" customWidth="1"/>
-    <col min="18" max="18" width="11.7181818181818" customWidth="1"/>
-    <col min="19" max="19" width="11.8545454545455" customWidth="1"/>
-    <col min="20" max="20" width="6.42727272727273" customWidth="1"/>
-    <col min="21" max="22" width="6.57272727272727" customWidth="1"/>
-    <col min="23" max="23" width="37.1454545454545" customWidth="1"/>
-    <col min="24" max="25" width="8" customWidth="1"/>
-    <col min="26" max="26" width="7.71818181818182" customWidth="1"/>
-    <col min="27" max="27" width="6.28181818181818" customWidth="1"/>
-    <col min="28" max="28" width="9.28181818181818" customWidth="1"/>
-    <col min="29" max="29" width="9.71818181818182" customWidth="1"/>
-    <col min="30" max="30" width="12.8545454545455" customWidth="1"/>
-    <col min="31" max="31" width="16.1454545454545" customWidth="1"/>
-    <col min="32" max="32" width="15.4272727272727" customWidth="1"/>
-    <col min="33" max="33" width="24.5727272727273" customWidth="1"/>
-    <col min="34" max="34" width="8.57272727272727" customWidth="1"/>
-    <col min="35" max="35" width="14.7181818181818" customWidth="1"/>
-    <col min="36" max="36" width="18.5727272727273" customWidth="1"/>
-    <col min="37" max="37" width="14.1454545454545" customWidth="1"/>
-    <col min="38" max="38" width="14.7181818181818" customWidth="1"/>
-    <col min="39" max="39" width="17.4272727272727" customWidth="1"/>
-    <col min="40" max="40" width="22" customWidth="1"/>
-    <col min="41" max="41" width="17.5727272727273" customWidth="1"/>
-    <col min="42" max="42" width="25.2818181818182" customWidth="1"/>
-    <col min="43" max="43" width="13" customWidth="1"/>
-    <col min="44" max="44" width="23.7181818181818" customWidth="1"/>
-    <col min="45" max="45" width="10" customWidth="1"/>
-    <col min="46" max="46" width="13" customWidth="1"/>
-    <col min="47" max="47" width="15.5727272727273" customWidth="1"/>
-    <col min="48" max="48" width="21.1454545454545" customWidth="1"/>
-    <col min="49" max="49" width="11.5727272727273" customWidth="1"/>
-    <col min="50" max="50" width="16.7181818181818" customWidth="1"/>
-    <col min="51" max="51" width="14" customWidth="1"/>
-    <col min="52" max="52" width="19.4272727272727" customWidth="1"/>
-    <col min="53" max="53" width="18.8545454545455" customWidth="1"/>
-    <col min="54" max="54" width="23.2818181818182" customWidth="1"/>
-    <col min="55" max="55" width="15.5727272727273" customWidth="1"/>
-    <col min="56" max="56" width="14.2818181818182" customWidth="1"/>
-    <col min="57" max="57" width="17" customWidth="1"/>
-    <col min="58" max="58" width="16.2818181818182" customWidth="1"/>
-    <col min="59" max="59" width="13.5727272727273" customWidth="1"/>
-    <col min="60" max="61" width="12.7181818181818" customWidth="1"/>
-    <col min="62" max="62" width="21.8545454545455" customWidth="1"/>
-    <col min="63" max="63" width="30.5727272727273" customWidth="1"/>
-    <col min="64" max="64" width="10" customWidth="1"/>
-    <col min="65" max="65" width="42.5727272727273" customWidth="1"/>
-    <col min="66" max="66" width="38.1454545454545" customWidth="1"/>
-    <col min="67" max="67" width="19.4272727272727" customWidth="1"/>
-    <col min="68" max="68" width="35.4272727272727" customWidth="1"/>
-    <col min="69" max="69" width="9.57272727272727" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="5.14285714285714"/>
+    <col min="2" max="3" customWidth="true" width="22.0"/>
+    <col min="4" max="4" customWidth="true" width="79.4285714285714"/>
+    <col min="5" max="5" customWidth="true" width="11.5714285714286"/>
+    <col min="6" max="6" customWidth="true" width="5.14285714285714"/>
+    <col min="7" max="7" customWidth="true" width="11.0"/>
+    <col min="8" max="8" customWidth="true" width="12.7142857142857"/>
+    <col min="9" max="9" customWidth="true" width="5.85714285714286"/>
+    <col min="10" max="10" customWidth="true" width="6.0"/>
+    <col min="11" max="11" customWidth="true" width="5.85714285714286"/>
+    <col min="12" max="12" customWidth="true" width="14.2857142857143"/>
+    <col min="13" max="13" customWidth="true" width="9.42857142857143"/>
+    <col min="14" max="14" customWidth="true" width="14.4285714285714"/>
+    <col min="15" max="15" customWidth="true" width="15.5714285714286"/>
+    <col min="16" max="16" customWidth="true" width="14.4285714285714"/>
+    <col min="17" max="17" customWidth="true" width="39.4285714285714"/>
+    <col min="18" max="18" customWidth="true" width="11.7142857142857"/>
+    <col min="19" max="19" customWidth="true" width="11.8571428571429"/>
+    <col min="20" max="20" customWidth="true" width="6.42857142857143"/>
+    <col min="21" max="22" customWidth="true" width="6.57142857142857"/>
+    <col min="23" max="23" customWidth="true" width="37.1428571428571"/>
+    <col min="24" max="25" customWidth="true" width="8.0"/>
+    <col min="26" max="26" customWidth="true" width="7.71428571428571"/>
+    <col min="27" max="27" customWidth="true" width="6.28571428571429"/>
+    <col min="28" max="28" customWidth="true" width="9.28571428571429"/>
+    <col min="29" max="29" customWidth="true" width="9.71428571428571"/>
+    <col min="30" max="30" customWidth="true" width="12.8571428571429"/>
+    <col min="31" max="31" customWidth="true" width="16.1428571428571"/>
+    <col min="32" max="32" customWidth="true" width="15.4285714285714"/>
+    <col min="33" max="33" customWidth="true" width="24.5714285714286"/>
+    <col min="34" max="34" customWidth="true" width="8.57142857142857"/>
+    <col min="35" max="35" customWidth="true" width="14.7142857142857"/>
+    <col min="36" max="36" customWidth="true" width="18.5714285714286"/>
+    <col min="37" max="37" customWidth="true" width="14.1428571428571"/>
+    <col min="38" max="38" customWidth="true" width="14.7142857142857"/>
+    <col min="39" max="39" customWidth="true" width="17.4285714285714"/>
+    <col min="40" max="40" customWidth="true" width="22.0"/>
+    <col min="41" max="41" customWidth="true" width="17.5714285714286"/>
+    <col min="42" max="42" customWidth="true" width="25.2857142857143"/>
+    <col min="43" max="43" customWidth="true" width="13.0"/>
+    <col min="44" max="44" customWidth="true" width="23.7142857142857"/>
+    <col min="45" max="45" customWidth="true" width="10.0"/>
+    <col min="46" max="46" customWidth="true" width="13.0"/>
+    <col min="47" max="47" customWidth="true" width="15.5714285714286"/>
+    <col min="48" max="48" customWidth="true" width="21.1428571428571"/>
+    <col min="49" max="49" customWidth="true" width="11.5714285714286"/>
+    <col min="50" max="50" customWidth="true" width="16.7142857142857"/>
+    <col min="51" max="51" customWidth="true" width="14.0"/>
+    <col min="52" max="52" customWidth="true" width="19.4285714285714"/>
+    <col min="53" max="53" customWidth="true" width="18.8571428571429"/>
+    <col min="54" max="54" customWidth="true" width="23.2857142857143"/>
+    <col min="55" max="55" customWidth="true" width="15.5714285714286"/>
+    <col min="56" max="56" customWidth="true" width="14.2857142857143"/>
+    <col min="57" max="57" customWidth="true" width="17.0"/>
+    <col min="58" max="58" customWidth="true" width="16.2857142857143"/>
+    <col min="59" max="59" customWidth="true" width="13.5714285714286"/>
+    <col min="60" max="61" customWidth="true" width="12.7142857142857"/>
+    <col min="62" max="62" customWidth="true" width="21.8571428571429"/>
+    <col min="63" max="63" customWidth="true" width="30.5714285714286"/>
+    <col min="64" max="64" customWidth="true" width="10.0"/>
+    <col min="65" max="65" customWidth="true" width="42.5714285714286"/>
+    <col min="66" max="66" customWidth="true" width="38.1428571428571"/>
+    <col min="67" max="67" customWidth="true" width="19.4285714285714"/>
+    <col min="68" max="68" customWidth="true" width="35.4285714285714"/>
+    <col min="69" max="69" customWidth="true" width="9.57142857142857"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -17941,7 +17956,7 @@
       <c r="BP2" s="32"/>
       <c r="BQ2" s="32"/>
     </row>
-    <row r="3" ht="15.25" spans="1:69">
+    <row r="3" ht="15.75" spans="1:69">
       <c r="A3" s="33" t="s">
         <v>9</v>
       </c>
@@ -18150,7 +18165,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.25" spans="1:69">
+    <row r="4" ht="15.75" spans="1:69">
       <c r="A4" s="31">
         <v>1</v>
       </c>
@@ -18221,7 +18236,7 @@
         <v>88363222</v>
       </c>
       <c r="U4" s="17">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="V4" s="17">
         <f>IF(OR($C$2=1,$C$2=4),ROUND((((S4*U4)/100)/2),2),0)</f>
@@ -18233,7 +18248,7 @@
       </c>
       <c r="X4" s="17">
         <f>IF($C$2=2,ROUND(((S4*U4)/100),2),0)</f>
-        <v>0</v>
+        <v>68.46</v>
       </c>
       <c r="Y4" s="17">
         <f>IF($C$2=4,ROUND((((S4*U4)/100)/2),2),0)</f>
@@ -18248,11 +18263,11 @@
       </c>
       <c r="AB4" s="17">
         <f>V4+W4+X4+Y4+AA4</f>
-        <v>15.2128</v>
+        <v>83.6728</v>
       </c>
       <c r="AC4" s="17">
         <f>IF($V2=1,S4+AB4,S4)</f>
-        <v>395.5328</v>
+        <v>463.9928</v>
       </c>
       <c r="AD4" s="17">
         <v>120</v>
@@ -18419,18 +18434,18 @@
       </c>
       <c r="X5" s="42">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>68.46</v>
       </c>
       <c r="Y5" s="44"/>
       <c r="Z5" s="44"/>
       <c r="AA5" s="44"/>
       <c r="AB5" s="42">
         <f t="shared" ref="AB5:AE5" si="1">SUM(AB4:AB4)</f>
-        <v>15.2128</v>
+        <v>83.6728</v>
       </c>
       <c r="AC5" s="42">
         <f t="shared" si="1"/>
-        <v>395.5328</v>
+        <v>463.9928</v>
       </c>
       <c r="AD5" s="42">
         <f t="shared" si="1"/>
@@ -18507,73 +18522,73 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ5"/>
-  <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="8.7047619047619" defaultRowHeight="15" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" width="5.14545454545455" customWidth="1"/>
-    <col min="2" max="3" width="25" customWidth="1"/>
-    <col min="4" max="4" width="79.4272727272727" customWidth="1"/>
-    <col min="5" max="5" width="11.5727272727273" customWidth="1"/>
-    <col min="6" max="6" width="5.14545454545455" customWidth="1"/>
-    <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="12.7181818181818" customWidth="1"/>
-    <col min="9" max="9" width="5.85454545454545" customWidth="1"/>
-    <col min="10" max="10" width="6" customWidth="1"/>
-    <col min="11" max="11" width="5.85454545454545" customWidth="1"/>
-    <col min="12" max="12" width="14.2818181818182" customWidth="1"/>
-    <col min="13" max="13" width="9.42727272727273" customWidth="1"/>
-    <col min="14" max="14" width="14.4272727272727" customWidth="1"/>
-    <col min="15" max="15" width="15.5727272727273" customWidth="1"/>
-    <col min="16" max="16" width="14.4272727272727" customWidth="1"/>
-    <col min="17" max="17" width="39.4272727272727" customWidth="1"/>
-    <col min="18" max="18" width="11.7181818181818" customWidth="1"/>
-    <col min="19" max="19" width="11.8545454545455" customWidth="1"/>
-    <col min="20" max="20" width="6.42727272727273" customWidth="1"/>
-    <col min="21" max="22" width="6.57272727272727" customWidth="1"/>
-    <col min="23" max="23" width="37.1454545454545" customWidth="1"/>
-    <col min="24" max="25" width="8" customWidth="1"/>
-    <col min="26" max="26" width="7.71818181818182" customWidth="1"/>
-    <col min="27" max="27" width="6.28181818181818" customWidth="1"/>
-    <col min="28" max="28" width="9.28181818181818" customWidth="1"/>
-    <col min="29" max="29" width="9.71818181818182" customWidth="1"/>
-    <col min="30" max="30" width="12.8545454545455" customWidth="1"/>
-    <col min="31" max="31" width="16.1454545454545" customWidth="1"/>
-    <col min="32" max="32" width="15.4272727272727" customWidth="1"/>
-    <col min="33" max="33" width="24.5727272727273" customWidth="1"/>
-    <col min="34" max="34" width="8.57272727272727" customWidth="1"/>
-    <col min="35" max="35" width="14.7181818181818" customWidth="1"/>
-    <col min="36" max="36" width="18.5727272727273" customWidth="1"/>
-    <col min="37" max="37" width="14.1454545454545" customWidth="1"/>
-    <col min="38" max="38" width="14.7181818181818" customWidth="1"/>
-    <col min="39" max="39" width="17.4272727272727" customWidth="1"/>
-    <col min="40" max="40" width="22" customWidth="1"/>
-    <col min="41" max="41" width="17.5727272727273" customWidth="1"/>
-    <col min="42" max="42" width="25.2818181818182" customWidth="1"/>
-    <col min="43" max="43" width="13" customWidth="1"/>
-    <col min="44" max="44" width="23.7181818181818" customWidth="1"/>
-    <col min="45" max="45" width="10" customWidth="1"/>
-    <col min="46" max="46" width="13" customWidth="1"/>
-    <col min="47" max="47" width="15.5727272727273" customWidth="1"/>
-    <col min="48" max="48" width="21.1454545454545" customWidth="1"/>
-    <col min="49" max="49" width="11.5727272727273" customWidth="1"/>
-    <col min="50" max="50" width="16.7181818181818" customWidth="1"/>
-    <col min="51" max="51" width="14" customWidth="1"/>
-    <col min="52" max="52" width="19.4272727272727" customWidth="1"/>
-    <col min="53" max="53" width="18.8545454545455" customWidth="1"/>
-    <col min="54" max="54" width="23.2818181818182" customWidth="1"/>
-    <col min="55" max="55" width="15.5727272727273" customWidth="1"/>
-    <col min="56" max="56" width="14.2818181818182" customWidth="1"/>
-    <col min="57" max="57" width="17" customWidth="1"/>
-    <col min="58" max="58" width="16.2818181818182" customWidth="1"/>
-    <col min="59" max="59" width="13.5727272727273" customWidth="1"/>
-    <col min="60" max="61" width="12.7181818181818" customWidth="1"/>
-    <col min="62" max="62" width="21.8545454545455" customWidth="1"/>
-    <col min="63" max="63" width="30.5727272727273" customWidth="1"/>
-    <col min="64" max="64" width="10" customWidth="1"/>
-    <col min="65" max="65" width="42.5727272727273" customWidth="1"/>
-    <col min="66" max="66" width="38.1454545454545" customWidth="1"/>
-    <col min="67" max="67" width="19.4272727272727" customWidth="1"/>
-    <col min="68" max="68" width="35.4272727272727" customWidth="1"/>
-    <col min="69" max="69" width="9.57272727272727" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="5.14285714285714"/>
+    <col min="2" max="3" customWidth="true" width="25.0"/>
+    <col min="4" max="4" customWidth="true" width="79.4285714285714"/>
+    <col min="5" max="5" customWidth="true" width="11.5714285714286"/>
+    <col min="6" max="6" customWidth="true" width="5.14285714285714"/>
+    <col min="7" max="7" customWidth="true" width="11.0"/>
+    <col min="8" max="8" customWidth="true" width="12.7142857142857"/>
+    <col min="9" max="9" customWidth="true" width="5.85714285714286"/>
+    <col min="10" max="10" customWidth="true" width="6.0"/>
+    <col min="11" max="11" customWidth="true" width="5.85714285714286"/>
+    <col min="12" max="12" customWidth="true" width="14.2857142857143"/>
+    <col min="13" max="13" customWidth="true" width="9.42857142857143"/>
+    <col min="14" max="14" customWidth="true" width="14.4285714285714"/>
+    <col min="15" max="15" customWidth="true" width="15.5714285714286"/>
+    <col min="16" max="16" customWidth="true" width="14.4285714285714"/>
+    <col min="17" max="17" customWidth="true" width="39.4285714285714"/>
+    <col min="18" max="18" customWidth="true" width="11.7142857142857"/>
+    <col min="19" max="19" customWidth="true" width="11.8571428571429"/>
+    <col min="20" max="20" customWidth="true" width="6.42857142857143"/>
+    <col min="21" max="22" customWidth="true" width="6.57142857142857"/>
+    <col min="23" max="23" customWidth="true" width="37.1428571428571"/>
+    <col min="24" max="25" customWidth="true" width="8.0"/>
+    <col min="26" max="26" customWidth="true" width="7.71428571428571"/>
+    <col min="27" max="27" customWidth="true" width="6.28571428571429"/>
+    <col min="28" max="28" customWidth="true" width="9.28571428571429"/>
+    <col min="29" max="29" customWidth="true" width="9.71428571428571"/>
+    <col min="30" max="30" customWidth="true" width="12.8571428571429"/>
+    <col min="31" max="31" customWidth="true" width="16.1428571428571"/>
+    <col min="32" max="32" customWidth="true" width="15.4285714285714"/>
+    <col min="33" max="33" customWidth="true" width="24.5714285714286"/>
+    <col min="34" max="34" customWidth="true" width="8.57142857142857"/>
+    <col min="35" max="35" customWidth="true" width="14.7142857142857"/>
+    <col min="36" max="36" customWidth="true" width="18.5714285714286"/>
+    <col min="37" max="37" customWidth="true" width="14.1428571428571"/>
+    <col min="38" max="38" customWidth="true" width="14.7142857142857"/>
+    <col min="39" max="39" customWidth="true" width="17.4285714285714"/>
+    <col min="40" max="40" customWidth="true" width="22.0"/>
+    <col min="41" max="41" customWidth="true" width="17.5714285714286"/>
+    <col min="42" max="42" customWidth="true" width="25.2857142857143"/>
+    <col min="43" max="43" customWidth="true" width="13.0"/>
+    <col min="44" max="44" customWidth="true" width="23.7142857142857"/>
+    <col min="45" max="45" customWidth="true" width="10.0"/>
+    <col min="46" max="46" customWidth="true" width="13.0"/>
+    <col min="47" max="47" customWidth="true" width="15.5714285714286"/>
+    <col min="48" max="48" customWidth="true" width="21.1428571428571"/>
+    <col min="49" max="49" customWidth="true" width="11.5714285714286"/>
+    <col min="50" max="50" customWidth="true" width="16.7142857142857"/>
+    <col min="51" max="51" customWidth="true" width="14.0"/>
+    <col min="52" max="52" customWidth="true" width="19.4285714285714"/>
+    <col min="53" max="53" customWidth="true" width="18.8571428571429"/>
+    <col min="54" max="54" customWidth="true" width="23.2857142857143"/>
+    <col min="55" max="55" customWidth="true" width="15.5714285714286"/>
+    <col min="56" max="56" customWidth="true" width="14.2857142857143"/>
+    <col min="57" max="57" customWidth="true" width="17.0"/>
+    <col min="58" max="58" customWidth="true" width="16.2857142857143"/>
+    <col min="59" max="59" customWidth="true" width="13.5714285714286"/>
+    <col min="60" max="61" customWidth="true" width="12.7142857142857"/>
+    <col min="62" max="62" customWidth="true" width="21.8571428571429"/>
+    <col min="63" max="63" customWidth="true" width="30.5714285714286"/>
+    <col min="64" max="64" customWidth="true" width="10.0"/>
+    <col min="65" max="65" customWidth="true" width="42.5714285714286"/>
+    <col min="66" max="66" customWidth="true" width="38.1428571428571"/>
+    <col min="67" max="67" customWidth="true" width="19.4285714285714"/>
+    <col min="68" max="68" customWidth="true" width="35.4285714285714"/>
+    <col min="69" max="69" customWidth="true" width="9.57142857142857"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -18744,7 +18759,7 @@
       <c r="BP2" s="32"/>
       <c r="BQ2" s="32"/>
     </row>
-    <row r="3" ht="15.25" spans="1:69">
+    <row r="3" ht="15.75" spans="1:69">
       <c r="A3" s="33" t="s">
         <v>9</v>
       </c>
@@ -18953,7 +18968,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.25" spans="1:69">
+    <row r="4" ht="15.75" spans="1:69">
       <c r="A4" s="31">
         <v>1</v>
       </c>
@@ -19024,7 +19039,7 @@
         <v>88363222</v>
       </c>
       <c r="U4" s="17">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="V4" s="17">
         <f>IF(OR($C$2=1,$C$2=4),ROUND((((S4*U4)/100)/2),2),0)</f>
@@ -19036,7 +19051,7 @@
       </c>
       <c r="X4" s="17">
         <f>IF($C$2=2,ROUND(((S4*U4)/100),2),0)</f>
-        <v>0</v>
+        <v>67.77</v>
       </c>
       <c r="Y4" s="17">
         <f>IF($C$2=4,ROUND((((S4*U4)/100)/2),2),0)</f>
@@ -19051,11 +19066,11 @@
       </c>
       <c r="AB4" s="17">
         <f>V4+W4+X4+Y4+AA4</f>
-        <v>15.0592</v>
+        <v>82.8292</v>
       </c>
       <c r="AC4" s="17">
         <f>IF($V2=1,S4+AB4,S4)</f>
-        <v>391.5392</v>
+        <v>459.3092</v>
       </c>
       <c r="AD4" s="17">
         <v>120</v>
@@ -19222,18 +19237,18 @@
       </c>
       <c r="X5" s="42">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>67.77</v>
       </c>
       <c r="Y5" s="44"/>
       <c r="Z5" s="44"/>
       <c r="AA5" s="44"/>
       <c r="AB5" s="42">
         <f t="shared" ref="AB5:AE5" si="1">SUM(AB4:AB4)</f>
-        <v>15.0592</v>
+        <v>82.8292</v>
       </c>
       <c r="AC5" s="42">
         <f t="shared" si="1"/>
-        <v>391.5392</v>
+        <v>459.3092</v>
       </c>
       <c r="AD5" s="42">
         <f t="shared" si="1"/>
@@ -19310,73 +19325,73 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ5"/>
-  <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="8.7047619047619" defaultRowHeight="15" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" width="5.14545454545455" customWidth="1"/>
-    <col min="2" max="3" width="25" customWidth="1"/>
-    <col min="4" max="4" width="79.4272727272727" customWidth="1"/>
-    <col min="5" max="5" width="11.5727272727273" customWidth="1"/>
-    <col min="6" max="6" width="5.14545454545455" customWidth="1"/>
-    <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="12.7181818181818" customWidth="1"/>
-    <col min="9" max="9" width="5.85454545454545" customWidth="1"/>
-    <col min="10" max="10" width="6" customWidth="1"/>
-    <col min="11" max="11" width="5.85454545454545" customWidth="1"/>
-    <col min="12" max="12" width="14.2818181818182" customWidth="1"/>
-    <col min="13" max="13" width="9.42727272727273" customWidth="1"/>
-    <col min="14" max="14" width="14.4272727272727" customWidth="1"/>
-    <col min="15" max="15" width="15.5727272727273" customWidth="1"/>
-    <col min="16" max="16" width="14.4272727272727" customWidth="1"/>
-    <col min="17" max="17" width="39.4272727272727" customWidth="1"/>
-    <col min="18" max="18" width="11.7181818181818" customWidth="1"/>
-    <col min="19" max="19" width="11.8545454545455" customWidth="1"/>
-    <col min="20" max="20" width="6.42727272727273" customWidth="1"/>
-    <col min="21" max="22" width="6.57272727272727" customWidth="1"/>
-    <col min="23" max="23" width="37.1454545454545" customWidth="1"/>
-    <col min="24" max="25" width="8" customWidth="1"/>
-    <col min="26" max="26" width="7.71818181818182" customWidth="1"/>
-    <col min="27" max="27" width="6.28181818181818" customWidth="1"/>
-    <col min="28" max="28" width="9.28181818181818" customWidth="1"/>
-    <col min="29" max="29" width="9.71818181818182" customWidth="1"/>
-    <col min="30" max="30" width="12.8545454545455" customWidth="1"/>
-    <col min="31" max="31" width="16.1454545454545" customWidth="1"/>
-    <col min="32" max="32" width="15.4272727272727" customWidth="1"/>
-    <col min="33" max="33" width="24.5727272727273" customWidth="1"/>
-    <col min="34" max="34" width="8.57272727272727" customWidth="1"/>
-    <col min="35" max="35" width="14.7181818181818" customWidth="1"/>
-    <col min="36" max="36" width="18.5727272727273" customWidth="1"/>
-    <col min="37" max="37" width="14.1454545454545" customWidth="1"/>
-    <col min="38" max="38" width="14.7181818181818" customWidth="1"/>
-    <col min="39" max="39" width="17.4272727272727" customWidth="1"/>
-    <col min="40" max="40" width="22" customWidth="1"/>
-    <col min="41" max="41" width="17.5727272727273" customWidth="1"/>
-    <col min="42" max="42" width="25.2818181818182" customWidth="1"/>
-    <col min="43" max="43" width="13" customWidth="1"/>
-    <col min="44" max="44" width="23.7181818181818" customWidth="1"/>
-    <col min="45" max="45" width="10" customWidth="1"/>
-    <col min="46" max="46" width="13" customWidth="1"/>
-    <col min="47" max="47" width="15.5727272727273" customWidth="1"/>
-    <col min="48" max="48" width="21.1454545454545" customWidth="1"/>
-    <col min="49" max="49" width="11.5727272727273" customWidth="1"/>
-    <col min="50" max="50" width="16.7181818181818" customWidth="1"/>
-    <col min="51" max="51" width="14" customWidth="1"/>
-    <col min="52" max="52" width="19.4272727272727" customWidth="1"/>
-    <col min="53" max="53" width="18.8545454545455" customWidth="1"/>
-    <col min="54" max="54" width="23.2818181818182" customWidth="1"/>
-    <col min="55" max="55" width="15.5727272727273" customWidth="1"/>
-    <col min="56" max="56" width="14.2818181818182" customWidth="1"/>
-    <col min="57" max="57" width="17" customWidth="1"/>
-    <col min="58" max="58" width="16.2818181818182" customWidth="1"/>
-    <col min="59" max="59" width="13.5727272727273" customWidth="1"/>
-    <col min="60" max="61" width="12.7181818181818" customWidth="1"/>
-    <col min="62" max="62" width="21.8545454545455" customWidth="1"/>
-    <col min="63" max="63" width="30.5727272727273" customWidth="1"/>
-    <col min="64" max="64" width="10" customWidth="1"/>
-    <col min="65" max="65" width="42.5727272727273" customWidth="1"/>
-    <col min="66" max="66" width="38.1454545454545" customWidth="1"/>
-    <col min="67" max="67" width="19.4272727272727" customWidth="1"/>
-    <col min="68" max="68" width="35.4272727272727" customWidth="1"/>
-    <col min="69" max="69" width="9.57272727272727" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="5.14285714285714"/>
+    <col min="2" max="3" customWidth="true" width="25.0"/>
+    <col min="4" max="4" customWidth="true" width="79.4285714285714"/>
+    <col min="5" max="5" customWidth="true" width="11.5714285714286"/>
+    <col min="6" max="6" customWidth="true" width="5.14285714285714"/>
+    <col min="7" max="7" customWidth="true" width="11.0"/>
+    <col min="8" max="8" customWidth="true" width="12.7142857142857"/>
+    <col min="9" max="9" customWidth="true" width="5.85714285714286"/>
+    <col min="10" max="10" customWidth="true" width="6.0"/>
+    <col min="11" max="11" customWidth="true" width="5.85714285714286"/>
+    <col min="12" max="12" customWidth="true" width="14.2857142857143"/>
+    <col min="13" max="13" customWidth="true" width="9.42857142857143"/>
+    <col min="14" max="14" customWidth="true" width="14.4285714285714"/>
+    <col min="15" max="15" customWidth="true" width="15.5714285714286"/>
+    <col min="16" max="16" customWidth="true" width="14.4285714285714"/>
+    <col min="17" max="17" customWidth="true" width="39.4285714285714"/>
+    <col min="18" max="18" customWidth="true" width="11.7142857142857"/>
+    <col min="19" max="19" customWidth="true" width="11.8571428571429"/>
+    <col min="20" max="20" customWidth="true" width="6.42857142857143"/>
+    <col min="21" max="22" customWidth="true" width="6.57142857142857"/>
+    <col min="23" max="23" customWidth="true" width="37.1428571428571"/>
+    <col min="24" max="25" customWidth="true" width="8.0"/>
+    <col min="26" max="26" customWidth="true" width="7.71428571428571"/>
+    <col min="27" max="27" customWidth="true" width="6.28571428571429"/>
+    <col min="28" max="28" customWidth="true" width="9.28571428571429"/>
+    <col min="29" max="29" customWidth="true" width="9.71428571428571"/>
+    <col min="30" max="30" customWidth="true" width="12.8571428571429"/>
+    <col min="31" max="31" customWidth="true" width="16.1428571428571"/>
+    <col min="32" max="32" customWidth="true" width="15.4285714285714"/>
+    <col min="33" max="33" customWidth="true" width="24.5714285714286"/>
+    <col min="34" max="34" customWidth="true" width="8.57142857142857"/>
+    <col min="35" max="35" customWidth="true" width="14.7142857142857"/>
+    <col min="36" max="36" customWidth="true" width="18.5714285714286"/>
+    <col min="37" max="37" customWidth="true" width="14.1428571428571"/>
+    <col min="38" max="38" customWidth="true" width="14.7142857142857"/>
+    <col min="39" max="39" customWidth="true" width="17.4285714285714"/>
+    <col min="40" max="40" customWidth="true" width="22.0"/>
+    <col min="41" max="41" customWidth="true" width="17.5714285714286"/>
+    <col min="42" max="42" customWidth="true" width="25.2857142857143"/>
+    <col min="43" max="43" customWidth="true" width="13.0"/>
+    <col min="44" max="44" customWidth="true" width="23.7142857142857"/>
+    <col min="45" max="45" customWidth="true" width="10.0"/>
+    <col min="46" max="46" customWidth="true" width="13.0"/>
+    <col min="47" max="47" customWidth="true" width="15.5714285714286"/>
+    <col min="48" max="48" customWidth="true" width="21.1428571428571"/>
+    <col min="49" max="49" customWidth="true" width="11.5714285714286"/>
+    <col min="50" max="50" customWidth="true" width="16.7142857142857"/>
+    <col min="51" max="51" customWidth="true" width="14.0"/>
+    <col min="52" max="52" customWidth="true" width="19.4285714285714"/>
+    <col min="53" max="53" customWidth="true" width="18.8571428571429"/>
+    <col min="54" max="54" customWidth="true" width="23.2857142857143"/>
+    <col min="55" max="55" customWidth="true" width="15.5714285714286"/>
+    <col min="56" max="56" customWidth="true" width="14.2857142857143"/>
+    <col min="57" max="57" customWidth="true" width="17.0"/>
+    <col min="58" max="58" customWidth="true" width="16.2857142857143"/>
+    <col min="59" max="59" customWidth="true" width="13.5714285714286"/>
+    <col min="60" max="61" customWidth="true" width="12.7142857142857"/>
+    <col min="62" max="62" customWidth="true" width="21.8571428571429"/>
+    <col min="63" max="63" customWidth="true" width="30.5714285714286"/>
+    <col min="64" max="64" customWidth="true" width="10.0"/>
+    <col min="65" max="65" customWidth="true" width="42.5714285714286"/>
+    <col min="66" max="66" customWidth="true" width="38.1428571428571"/>
+    <col min="67" max="67" customWidth="true" width="19.4285714285714"/>
+    <col min="68" max="68" customWidth="true" width="35.4285714285714"/>
+    <col min="69" max="69" customWidth="true" width="9.57142857142857"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -19547,7 +19562,7 @@
       <c r="BP2" s="32"/>
       <c r="BQ2" s="32"/>
     </row>
-    <row r="3" ht="15.25" spans="1:69">
+    <row r="3" ht="15.75" spans="1:69">
       <c r="A3" s="33" t="s">
         <v>9</v>
       </c>
@@ -19756,7 +19771,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.25" spans="1:69">
+    <row r="4" ht="15.75" spans="1:69">
       <c r="A4" s="31">
         <v>1</v>
       </c>
@@ -19827,7 +19842,7 @@
         <v>88363222</v>
       </c>
       <c r="U4" s="17">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="V4" s="17">
         <f>IF(OR($C$2=1,$C$2=4),ROUND((((S4*U4)/100)/2),2),0)</f>
@@ -19839,7 +19854,7 @@
       </c>
       <c r="X4" s="17">
         <f>IF($C$2=2,ROUND(((S4*U4)/100),2),0)</f>
-        <v>0</v>
+        <v>67.77</v>
       </c>
       <c r="Y4" s="17">
         <f>IF($C$2=4,ROUND((((S4*U4)/100)/2),2),0)</f>
@@ -19854,11 +19869,11 @@
       </c>
       <c r="AB4" s="17">
         <f>V4+W4+X4+Y4+AA4</f>
-        <v>15.0592</v>
+        <v>82.8292</v>
       </c>
       <c r="AC4" s="17">
         <f>IF($V2=1,S4+AB4,S4)</f>
-        <v>391.5392</v>
+        <v>459.3092</v>
       </c>
       <c r="AD4" s="17">
         <v>120</v>
@@ -20025,18 +20040,18 @@
       </c>
       <c r="X5" s="42">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>67.77</v>
       </c>
       <c r="Y5" s="44"/>
       <c r="Z5" s="44"/>
       <c r="AA5" s="44"/>
       <c r="AB5" s="42">
         <f t="shared" ref="AB5:AE5" si="1">SUM(AB4:AB4)</f>
-        <v>15.0592</v>
+        <v>82.8292</v>
       </c>
       <c r="AC5" s="42">
         <f t="shared" si="1"/>
-        <v>391.5392</v>
+        <v>459.3092</v>
       </c>
       <c r="AD5" s="42">
         <f t="shared" si="1"/>
@@ -20113,73 +20128,73 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ5"/>
-  <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="8.7047619047619" defaultRowHeight="15" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" width="5.14545454545455" customWidth="1"/>
-    <col min="2" max="3" width="25.2818181818182" customWidth="1"/>
-    <col min="4" max="4" width="79.4272727272727" customWidth="1"/>
-    <col min="5" max="5" width="11.5727272727273" customWidth="1"/>
-    <col min="6" max="6" width="5.14545454545455" customWidth="1"/>
-    <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="12.7181818181818" customWidth="1"/>
-    <col min="9" max="9" width="5.85454545454545" customWidth="1"/>
-    <col min="10" max="10" width="6" customWidth="1"/>
-    <col min="11" max="11" width="5.85454545454545" customWidth="1"/>
-    <col min="12" max="12" width="14.2818181818182" customWidth="1"/>
-    <col min="13" max="13" width="9.42727272727273" customWidth="1"/>
-    <col min="14" max="14" width="14.4272727272727" customWidth="1"/>
-    <col min="15" max="15" width="15.5727272727273" customWidth="1"/>
-    <col min="16" max="16" width="14.4272727272727" customWidth="1"/>
-    <col min="17" max="17" width="39.4272727272727" customWidth="1"/>
-    <col min="18" max="18" width="11.7181818181818" customWidth="1"/>
-    <col min="19" max="19" width="11.8545454545455" customWidth="1"/>
-    <col min="20" max="20" width="6.42727272727273" customWidth="1"/>
-    <col min="21" max="22" width="6.57272727272727" customWidth="1"/>
-    <col min="23" max="23" width="37.1454545454545" customWidth="1"/>
-    <col min="24" max="25" width="8" customWidth="1"/>
-    <col min="26" max="26" width="7.71818181818182" customWidth="1"/>
-    <col min="27" max="27" width="6.28181818181818" customWidth="1"/>
-    <col min="28" max="28" width="9.28181818181818" customWidth="1"/>
-    <col min="29" max="29" width="9.71818181818182" customWidth="1"/>
-    <col min="30" max="30" width="12.8545454545455" customWidth="1"/>
-    <col min="31" max="31" width="16.1454545454545" customWidth="1"/>
-    <col min="32" max="32" width="15.4272727272727" customWidth="1"/>
-    <col min="33" max="33" width="24.5727272727273" customWidth="1"/>
-    <col min="34" max="34" width="8.57272727272727" customWidth="1"/>
-    <col min="35" max="35" width="14.7181818181818" customWidth="1"/>
-    <col min="36" max="36" width="18.5727272727273" customWidth="1"/>
-    <col min="37" max="37" width="14.1454545454545" customWidth="1"/>
-    <col min="38" max="38" width="14.7181818181818" customWidth="1"/>
-    <col min="39" max="39" width="17.4272727272727" customWidth="1"/>
-    <col min="40" max="40" width="22" customWidth="1"/>
-    <col min="41" max="41" width="17.5727272727273" customWidth="1"/>
-    <col min="42" max="42" width="25.2818181818182" customWidth="1"/>
-    <col min="43" max="43" width="13" customWidth="1"/>
-    <col min="44" max="44" width="23.7181818181818" customWidth="1"/>
-    <col min="45" max="45" width="10" customWidth="1"/>
-    <col min="46" max="46" width="13" customWidth="1"/>
-    <col min="47" max="47" width="15.5727272727273" customWidth="1"/>
-    <col min="48" max="48" width="21.1454545454545" customWidth="1"/>
-    <col min="49" max="49" width="11.5727272727273" customWidth="1"/>
-    <col min="50" max="50" width="16.7181818181818" customWidth="1"/>
-    <col min="51" max="51" width="14" customWidth="1"/>
-    <col min="52" max="52" width="19.4272727272727" customWidth="1"/>
-    <col min="53" max="53" width="18.8545454545455" customWidth="1"/>
-    <col min="54" max="54" width="23.2818181818182" customWidth="1"/>
-    <col min="55" max="55" width="15.5727272727273" customWidth="1"/>
-    <col min="56" max="56" width="14.2818181818182" customWidth="1"/>
-    <col min="57" max="57" width="17" customWidth="1"/>
-    <col min="58" max="58" width="16.2818181818182" customWidth="1"/>
-    <col min="59" max="59" width="13.5727272727273" customWidth="1"/>
-    <col min="60" max="61" width="12.7181818181818" customWidth="1"/>
-    <col min="62" max="62" width="21.8545454545455" customWidth="1"/>
-    <col min="63" max="63" width="30.5727272727273" customWidth="1"/>
-    <col min="64" max="64" width="10" customWidth="1"/>
-    <col min="65" max="65" width="42.5727272727273" customWidth="1"/>
-    <col min="66" max="66" width="38.1454545454545" customWidth="1"/>
-    <col min="67" max="67" width="19.4272727272727" customWidth="1"/>
-    <col min="68" max="68" width="35.4272727272727" customWidth="1"/>
-    <col min="69" max="69" width="9.57272727272727" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="5.14285714285714"/>
+    <col min="2" max="3" customWidth="true" width="25.2857142857143"/>
+    <col min="4" max="4" customWidth="true" width="79.4285714285714"/>
+    <col min="5" max="5" customWidth="true" width="11.5714285714286"/>
+    <col min="6" max="6" customWidth="true" width="5.14285714285714"/>
+    <col min="7" max="7" customWidth="true" width="11.0"/>
+    <col min="8" max="8" customWidth="true" width="12.7142857142857"/>
+    <col min="9" max="9" customWidth="true" width="5.85714285714286"/>
+    <col min="10" max="10" customWidth="true" width="6.0"/>
+    <col min="11" max="11" customWidth="true" width="5.85714285714286"/>
+    <col min="12" max="12" customWidth="true" width="14.2857142857143"/>
+    <col min="13" max="13" customWidth="true" width="9.42857142857143"/>
+    <col min="14" max="14" customWidth="true" width="14.4285714285714"/>
+    <col min="15" max="15" customWidth="true" width="15.5714285714286"/>
+    <col min="16" max="16" customWidth="true" width="14.4285714285714"/>
+    <col min="17" max="17" customWidth="true" width="39.4285714285714"/>
+    <col min="18" max="18" customWidth="true" width="11.7142857142857"/>
+    <col min="19" max="19" customWidth="true" width="11.8571428571429"/>
+    <col min="20" max="20" customWidth="true" width="6.42857142857143"/>
+    <col min="21" max="22" customWidth="true" width="6.57142857142857"/>
+    <col min="23" max="23" customWidth="true" width="37.1428571428571"/>
+    <col min="24" max="25" customWidth="true" width="8.0"/>
+    <col min="26" max="26" customWidth="true" width="7.71428571428571"/>
+    <col min="27" max="27" customWidth="true" width="6.28571428571429"/>
+    <col min="28" max="28" customWidth="true" width="9.28571428571429"/>
+    <col min="29" max="29" customWidth="true" width="9.71428571428571"/>
+    <col min="30" max="30" customWidth="true" width="12.8571428571429"/>
+    <col min="31" max="31" customWidth="true" width="16.1428571428571"/>
+    <col min="32" max="32" customWidth="true" width="15.4285714285714"/>
+    <col min="33" max="33" customWidth="true" width="24.5714285714286"/>
+    <col min="34" max="34" customWidth="true" width="8.57142857142857"/>
+    <col min="35" max="35" customWidth="true" width="14.7142857142857"/>
+    <col min="36" max="36" customWidth="true" width="18.5714285714286"/>
+    <col min="37" max="37" customWidth="true" width="14.1428571428571"/>
+    <col min="38" max="38" customWidth="true" width="14.7142857142857"/>
+    <col min="39" max="39" customWidth="true" width="17.4285714285714"/>
+    <col min="40" max="40" customWidth="true" width="22.0"/>
+    <col min="41" max="41" customWidth="true" width="17.5714285714286"/>
+    <col min="42" max="42" customWidth="true" width="25.2857142857143"/>
+    <col min="43" max="43" customWidth="true" width="13.0"/>
+    <col min="44" max="44" customWidth="true" width="23.7142857142857"/>
+    <col min="45" max="45" customWidth="true" width="10.0"/>
+    <col min="46" max="46" customWidth="true" width="13.0"/>
+    <col min="47" max="47" customWidth="true" width="15.5714285714286"/>
+    <col min="48" max="48" customWidth="true" width="21.1428571428571"/>
+    <col min="49" max="49" customWidth="true" width="11.5714285714286"/>
+    <col min="50" max="50" customWidth="true" width="16.7142857142857"/>
+    <col min="51" max="51" customWidth="true" width="14.0"/>
+    <col min="52" max="52" customWidth="true" width="19.4285714285714"/>
+    <col min="53" max="53" customWidth="true" width="18.8571428571429"/>
+    <col min="54" max="54" customWidth="true" width="23.2857142857143"/>
+    <col min="55" max="55" customWidth="true" width="15.5714285714286"/>
+    <col min="56" max="56" customWidth="true" width="14.2857142857143"/>
+    <col min="57" max="57" customWidth="true" width="17.0"/>
+    <col min="58" max="58" customWidth="true" width="16.2857142857143"/>
+    <col min="59" max="59" customWidth="true" width="13.5714285714286"/>
+    <col min="60" max="61" customWidth="true" width="12.7142857142857"/>
+    <col min="62" max="62" customWidth="true" width="21.8571428571429"/>
+    <col min="63" max="63" customWidth="true" width="30.5714285714286"/>
+    <col min="64" max="64" customWidth="true" width="10.0"/>
+    <col min="65" max="65" customWidth="true" width="42.5714285714286"/>
+    <col min="66" max="66" customWidth="true" width="38.1428571428571"/>
+    <col min="67" max="67" customWidth="true" width="19.4285714285714"/>
+    <col min="68" max="68" customWidth="true" width="35.4285714285714"/>
+    <col min="69" max="69" customWidth="true" width="9.57142857142857"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -20350,7 +20365,7 @@
       <c r="BP2" s="32"/>
       <c r="BQ2" s="32"/>
     </row>
-    <row r="3" ht="15.25" spans="1:69">
+    <row r="3" ht="15.75" spans="1:69">
       <c r="A3" s="33" t="s">
         <v>9</v>
       </c>
@@ -20559,7 +20574,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.25" spans="1:69">
+    <row r="4" ht="15.75" spans="1:69">
       <c r="A4" s="31">
         <v>1</v>
       </c>
@@ -20630,7 +20645,7 @@
         <v>88363222</v>
       </c>
       <c r="U4" s="17">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="V4" s="17">
         <f>IF(OR($C$2=1,$C$2=4),ROUND((((S4*U4)/100)/2),2),0)</f>
@@ -20642,7 +20657,7 @@
       </c>
       <c r="X4" s="17">
         <f>IF($C$2=2,ROUND(((S4*U4)/100),2),0)</f>
-        <v>0</v>
+        <v>68.46</v>
       </c>
       <c r="Y4" s="17">
         <f>IF($C$2=4,ROUND((((S4*U4)/100)/2),2),0)</f>
@@ -20657,11 +20672,11 @@
       </c>
       <c r="AB4" s="17">
         <f>V4+W4+X4+Y4+AA4</f>
-        <v>15.2128</v>
+        <v>83.6728</v>
       </c>
       <c r="AC4" s="17">
         <f>IF($V2=1,S4+AB4,S4)</f>
-        <v>395.5328</v>
+        <v>463.9928</v>
       </c>
       <c r="AD4" s="17">
         <v>120</v>
@@ -20828,7 +20843,7 @@
       </c>
       <c r="X5" s="42">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>68.46</v>
       </c>
       <c r="Y5" s="42">
         <f t="shared" si="0"/>
@@ -20844,11 +20859,11 @@
       </c>
       <c r="AB5" s="42">
         <f t="shared" si="0"/>
-        <v>15.2128</v>
+        <v>83.6728</v>
       </c>
       <c r="AC5" s="42">
         <f t="shared" si="0"/>
-        <v>395.5328</v>
+        <v>463.9928</v>
       </c>
       <c r="AD5" s="42">
         <f t="shared" si="0"/>
@@ -20928,73 +20943,73 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ5"/>
-  <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="8.7047619047619" defaultRowHeight="15" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" width="5.14545454545455" customWidth="1"/>
-    <col min="2" max="3" width="25.2818181818182" customWidth="1"/>
-    <col min="4" max="4" width="79.4272727272727" customWidth="1"/>
-    <col min="5" max="5" width="11.5727272727273" customWidth="1"/>
-    <col min="6" max="6" width="5.14545454545455" customWidth="1"/>
-    <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="12.7181818181818" customWidth="1"/>
-    <col min="9" max="9" width="5.85454545454545" customWidth="1"/>
-    <col min="10" max="10" width="6" customWidth="1"/>
-    <col min="11" max="11" width="5.85454545454545" customWidth="1"/>
-    <col min="12" max="12" width="14.2818181818182" customWidth="1"/>
-    <col min="13" max="13" width="9.42727272727273" customWidth="1"/>
-    <col min="14" max="14" width="14.4272727272727" customWidth="1"/>
-    <col min="15" max="15" width="15.5727272727273" customWidth="1"/>
-    <col min="16" max="16" width="14.4272727272727" customWidth="1"/>
-    <col min="17" max="17" width="39.4272727272727" customWidth="1"/>
-    <col min="18" max="18" width="11.7181818181818" customWidth="1"/>
-    <col min="19" max="19" width="11.8545454545455" customWidth="1"/>
-    <col min="20" max="20" width="6.42727272727273" customWidth="1"/>
-    <col min="21" max="22" width="6.57272727272727" customWidth="1"/>
-    <col min="23" max="23" width="37.1454545454545" customWidth="1"/>
-    <col min="24" max="25" width="8" customWidth="1"/>
-    <col min="26" max="26" width="7.71818181818182" customWidth="1"/>
-    <col min="27" max="27" width="6.28181818181818" customWidth="1"/>
-    <col min="28" max="28" width="9.28181818181818" customWidth="1"/>
-    <col min="29" max="29" width="9.71818181818182" customWidth="1"/>
-    <col min="30" max="30" width="12.8545454545455" customWidth="1"/>
-    <col min="31" max="31" width="16.1454545454545" customWidth="1"/>
-    <col min="32" max="32" width="15.4272727272727" customWidth="1"/>
-    <col min="33" max="33" width="24.5727272727273" customWidth="1"/>
-    <col min="34" max="34" width="8.57272727272727" customWidth="1"/>
-    <col min="35" max="35" width="14.7181818181818" customWidth="1"/>
-    <col min="36" max="36" width="18.5727272727273" customWidth="1"/>
-    <col min="37" max="37" width="14.1454545454545" customWidth="1"/>
-    <col min="38" max="38" width="14.7181818181818" customWidth="1"/>
-    <col min="39" max="39" width="17.4272727272727" customWidth="1"/>
-    <col min="40" max="40" width="22" customWidth="1"/>
-    <col min="41" max="41" width="17.5727272727273" customWidth="1"/>
-    <col min="42" max="42" width="25.2818181818182" customWidth="1"/>
-    <col min="43" max="43" width="13" customWidth="1"/>
-    <col min="44" max="44" width="23.7181818181818" customWidth="1"/>
-    <col min="45" max="45" width="10" customWidth="1"/>
-    <col min="46" max="46" width="13" customWidth="1"/>
-    <col min="47" max="47" width="15.5727272727273" customWidth="1"/>
-    <col min="48" max="48" width="21.1454545454545" customWidth="1"/>
-    <col min="49" max="49" width="11.5727272727273" customWidth="1"/>
-    <col min="50" max="50" width="16.7181818181818" customWidth="1"/>
-    <col min="51" max="51" width="14" customWidth="1"/>
-    <col min="52" max="52" width="19.4272727272727" customWidth="1"/>
-    <col min="53" max="53" width="18.8545454545455" customWidth="1"/>
-    <col min="54" max="54" width="23.2818181818182" customWidth="1"/>
-    <col min="55" max="55" width="15.5727272727273" customWidth="1"/>
-    <col min="56" max="56" width="14.2818181818182" customWidth="1"/>
-    <col min="57" max="57" width="17" customWidth="1"/>
-    <col min="58" max="58" width="16.2818181818182" customWidth="1"/>
-    <col min="59" max="59" width="13.5727272727273" customWidth="1"/>
-    <col min="60" max="61" width="12.7181818181818" customWidth="1"/>
-    <col min="62" max="62" width="21.8545454545455" customWidth="1"/>
-    <col min="63" max="63" width="30.5727272727273" customWidth="1"/>
-    <col min="64" max="64" width="10" customWidth="1"/>
-    <col min="65" max="65" width="42.5727272727273" customWidth="1"/>
-    <col min="66" max="66" width="38.1454545454545" customWidth="1"/>
-    <col min="67" max="67" width="19.4272727272727" customWidth="1"/>
-    <col min="68" max="68" width="35.4272727272727" customWidth="1"/>
-    <col min="69" max="69" width="9.57272727272727" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="5.14285714285714"/>
+    <col min="2" max="3" customWidth="true" width="25.2857142857143"/>
+    <col min="4" max="4" customWidth="true" width="79.4285714285714"/>
+    <col min="5" max="5" customWidth="true" width="11.5714285714286"/>
+    <col min="6" max="6" customWidth="true" width="5.14285714285714"/>
+    <col min="7" max="7" customWidth="true" width="11.0"/>
+    <col min="8" max="8" customWidth="true" width="12.7142857142857"/>
+    <col min="9" max="9" customWidth="true" width="5.85714285714286"/>
+    <col min="10" max="10" customWidth="true" width="6.0"/>
+    <col min="11" max="11" customWidth="true" width="5.85714285714286"/>
+    <col min="12" max="12" customWidth="true" width="14.2857142857143"/>
+    <col min="13" max="13" customWidth="true" width="9.42857142857143"/>
+    <col min="14" max="14" customWidth="true" width="14.4285714285714"/>
+    <col min="15" max="15" customWidth="true" width="15.5714285714286"/>
+    <col min="16" max="16" customWidth="true" width="14.4285714285714"/>
+    <col min="17" max="17" customWidth="true" width="39.4285714285714"/>
+    <col min="18" max="18" customWidth="true" width="11.7142857142857"/>
+    <col min="19" max="19" customWidth="true" width="11.8571428571429"/>
+    <col min="20" max="20" customWidth="true" width="6.42857142857143"/>
+    <col min="21" max="22" customWidth="true" width="6.57142857142857"/>
+    <col min="23" max="23" customWidth="true" width="37.1428571428571"/>
+    <col min="24" max="25" customWidth="true" width="8.0"/>
+    <col min="26" max="26" customWidth="true" width="7.71428571428571"/>
+    <col min="27" max="27" customWidth="true" width="6.28571428571429"/>
+    <col min="28" max="28" customWidth="true" width="9.28571428571429"/>
+    <col min="29" max="29" customWidth="true" width="9.71428571428571"/>
+    <col min="30" max="30" customWidth="true" width="12.8571428571429"/>
+    <col min="31" max="31" customWidth="true" width="16.1428571428571"/>
+    <col min="32" max="32" customWidth="true" width="15.4285714285714"/>
+    <col min="33" max="33" customWidth="true" width="24.5714285714286"/>
+    <col min="34" max="34" customWidth="true" width="8.57142857142857"/>
+    <col min="35" max="35" customWidth="true" width="14.7142857142857"/>
+    <col min="36" max="36" customWidth="true" width="18.5714285714286"/>
+    <col min="37" max="37" customWidth="true" width="14.1428571428571"/>
+    <col min="38" max="38" customWidth="true" width="14.7142857142857"/>
+    <col min="39" max="39" customWidth="true" width="17.4285714285714"/>
+    <col min="40" max="40" customWidth="true" width="22.0"/>
+    <col min="41" max="41" customWidth="true" width="17.5714285714286"/>
+    <col min="42" max="42" customWidth="true" width="25.2857142857143"/>
+    <col min="43" max="43" customWidth="true" width="13.0"/>
+    <col min="44" max="44" customWidth="true" width="23.7142857142857"/>
+    <col min="45" max="45" customWidth="true" width="10.0"/>
+    <col min="46" max="46" customWidth="true" width="13.0"/>
+    <col min="47" max="47" customWidth="true" width="15.5714285714286"/>
+    <col min="48" max="48" customWidth="true" width="21.1428571428571"/>
+    <col min="49" max="49" customWidth="true" width="11.5714285714286"/>
+    <col min="50" max="50" customWidth="true" width="16.7142857142857"/>
+    <col min="51" max="51" customWidth="true" width="14.0"/>
+    <col min="52" max="52" customWidth="true" width="19.4285714285714"/>
+    <col min="53" max="53" customWidth="true" width="18.8571428571429"/>
+    <col min="54" max="54" customWidth="true" width="23.2857142857143"/>
+    <col min="55" max="55" customWidth="true" width="15.5714285714286"/>
+    <col min="56" max="56" customWidth="true" width="14.2857142857143"/>
+    <col min="57" max="57" customWidth="true" width="17.0"/>
+    <col min="58" max="58" customWidth="true" width="16.2857142857143"/>
+    <col min="59" max="59" customWidth="true" width="13.5714285714286"/>
+    <col min="60" max="61" customWidth="true" width="12.7142857142857"/>
+    <col min="62" max="62" customWidth="true" width="21.8571428571429"/>
+    <col min="63" max="63" customWidth="true" width="30.5714285714286"/>
+    <col min="64" max="64" customWidth="true" width="10.0"/>
+    <col min="65" max="65" customWidth="true" width="42.5714285714286"/>
+    <col min="66" max="66" customWidth="true" width="38.1428571428571"/>
+    <col min="67" max="67" customWidth="true" width="19.4285714285714"/>
+    <col min="68" max="68" customWidth="true" width="35.4285714285714"/>
+    <col min="69" max="69" customWidth="true" width="9.57142857142857"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -21165,7 +21180,7 @@
       <c r="BP2" s="32"/>
       <c r="BQ2" s="32"/>
     </row>
-    <row r="3" ht="15.25" spans="1:69">
+    <row r="3" ht="15.75" spans="1:69">
       <c r="A3" s="33" t="s">
         <v>9</v>
       </c>
@@ -21374,7 +21389,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.25" spans="1:69">
+    <row r="4" spans="1:69">
       <c r="A4" s="31">
         <v>1</v>
       </c>
@@ -21445,7 +21460,7 @@
         <v>88363222</v>
       </c>
       <c r="U4" s="17">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="V4" s="17">
         <f>IF(OR($C$2=1,$C$2=4),ROUND((((S4*U4)/100)/2),2),0)</f>
@@ -21457,7 +21472,7 @@
       </c>
       <c r="X4" s="17">
         <f>IF($C$2=2,ROUND(((S4*U4)/100),2),0)</f>
-        <v>0</v>
+        <v>68.46</v>
       </c>
       <c r="Y4" s="17">
         <f>IF($C$2=4,ROUND((((S4*U4)/100)/2),2),0)</f>
@@ -21472,11 +21487,11 @@
       </c>
       <c r="AB4" s="17">
         <f>V4+W4+X4+Y4+AA4</f>
-        <v>15.2128</v>
+        <v>83.6728</v>
       </c>
       <c r="AC4" s="17">
         <f>IF($V2=1,S4+AB4,S4)</f>
-        <v>395.5328</v>
+        <v>463.9928</v>
       </c>
       <c r="AD4" s="17">
         <v>120</v>
@@ -21643,18 +21658,18 @@
       </c>
       <c r="X5" s="42">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>68.46</v>
       </c>
       <c r="Y5" s="44"/>
       <c r="Z5" s="44"/>
       <c r="AA5" s="44"/>
       <c r="AB5" s="42">
         <f t="shared" ref="AB5:AE5" si="1">SUM(AB4:AB4)</f>
-        <v>15.2128</v>
+        <v>83.6728</v>
       </c>
       <c r="AC5" s="42">
         <f t="shared" si="1"/>
-        <v>395.5328</v>
+        <v>463.9928</v>
       </c>
       <c r="AD5" s="42">
         <f t="shared" si="1"/>
@@ -21731,73 +21746,73 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ5"/>
-  <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="8.7047619047619" defaultRowHeight="15" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" width="5.14545454545455" customWidth="1"/>
-    <col min="2" max="3" width="25.5727272727273" customWidth="1"/>
-    <col min="4" max="4" width="79.4272727272727" customWidth="1"/>
-    <col min="5" max="5" width="11.5727272727273" customWidth="1"/>
-    <col min="6" max="6" width="5.14545454545455" customWidth="1"/>
-    <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="12.7181818181818" customWidth="1"/>
-    <col min="9" max="9" width="5.85454545454545" customWidth="1"/>
-    <col min="10" max="10" width="6" customWidth="1"/>
-    <col min="11" max="11" width="5.85454545454545" customWidth="1"/>
-    <col min="12" max="12" width="14.2818181818182" customWidth="1"/>
-    <col min="13" max="13" width="9.42727272727273" customWidth="1"/>
-    <col min="14" max="14" width="14.4272727272727" customWidth="1"/>
-    <col min="15" max="15" width="15.5727272727273" customWidth="1"/>
-    <col min="16" max="16" width="14.4272727272727" customWidth="1"/>
-    <col min="17" max="17" width="39.4272727272727" customWidth="1"/>
-    <col min="18" max="18" width="11.7181818181818" customWidth="1"/>
-    <col min="19" max="19" width="11.8545454545455" customWidth="1"/>
-    <col min="20" max="20" width="6.42727272727273" customWidth="1"/>
-    <col min="21" max="22" width="6.57272727272727" customWidth="1"/>
-    <col min="23" max="23" width="37.1454545454545" customWidth="1"/>
-    <col min="24" max="25" width="8" customWidth="1"/>
-    <col min="26" max="26" width="7.71818181818182" customWidth="1"/>
-    <col min="27" max="27" width="6.28181818181818" customWidth="1"/>
-    <col min="28" max="28" width="9.28181818181818" customWidth="1"/>
-    <col min="29" max="29" width="9.71818181818182" customWidth="1"/>
-    <col min="30" max="30" width="12.8545454545455" customWidth="1"/>
-    <col min="31" max="31" width="16.1454545454545" customWidth="1"/>
-    <col min="32" max="32" width="15.4272727272727" customWidth="1"/>
-    <col min="33" max="33" width="24.5727272727273" customWidth="1"/>
-    <col min="34" max="34" width="8.57272727272727" customWidth="1"/>
-    <col min="35" max="35" width="14.7181818181818" customWidth="1"/>
-    <col min="36" max="36" width="18.5727272727273" customWidth="1"/>
-    <col min="37" max="37" width="14.1454545454545" customWidth="1"/>
-    <col min="38" max="38" width="14.7181818181818" customWidth="1"/>
-    <col min="39" max="39" width="17.4272727272727" customWidth="1"/>
-    <col min="40" max="40" width="22" customWidth="1"/>
-    <col min="41" max="41" width="17.5727272727273" customWidth="1"/>
-    <col min="42" max="42" width="25.2818181818182" customWidth="1"/>
-    <col min="43" max="43" width="13" customWidth="1"/>
-    <col min="44" max="44" width="23.7181818181818" customWidth="1"/>
-    <col min="45" max="45" width="10" customWidth="1"/>
-    <col min="46" max="46" width="13" customWidth="1"/>
-    <col min="47" max="47" width="15.5727272727273" customWidth="1"/>
-    <col min="48" max="48" width="21.1454545454545" customWidth="1"/>
-    <col min="49" max="49" width="11.5727272727273" customWidth="1"/>
-    <col min="50" max="50" width="16.7181818181818" customWidth="1"/>
-    <col min="51" max="51" width="14" customWidth="1"/>
-    <col min="52" max="52" width="19.4272727272727" customWidth="1"/>
-    <col min="53" max="53" width="18.8545454545455" customWidth="1"/>
-    <col min="54" max="54" width="23.2818181818182" customWidth="1"/>
-    <col min="55" max="55" width="15.5727272727273" customWidth="1"/>
-    <col min="56" max="56" width="14.2818181818182" customWidth="1"/>
-    <col min="57" max="57" width="17" customWidth="1"/>
-    <col min="58" max="58" width="16.2818181818182" customWidth="1"/>
-    <col min="59" max="59" width="13.5727272727273" customWidth="1"/>
-    <col min="60" max="61" width="12.7181818181818" customWidth="1"/>
-    <col min="62" max="62" width="21.8545454545455" customWidth="1"/>
-    <col min="63" max="63" width="30.5727272727273" customWidth="1"/>
-    <col min="64" max="64" width="10" customWidth="1"/>
-    <col min="65" max="65" width="42.5727272727273" customWidth="1"/>
-    <col min="66" max="66" width="38.1454545454545" customWidth="1"/>
-    <col min="67" max="67" width="19.4272727272727" customWidth="1"/>
-    <col min="68" max="68" width="35.4272727272727" customWidth="1"/>
-    <col min="69" max="69" width="9.57272727272727" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="5.14285714285714"/>
+    <col min="2" max="3" customWidth="true" width="25.5714285714286"/>
+    <col min="4" max="4" customWidth="true" width="79.4285714285714"/>
+    <col min="5" max="5" customWidth="true" width="11.5714285714286"/>
+    <col min="6" max="6" customWidth="true" width="5.14285714285714"/>
+    <col min="7" max="7" customWidth="true" width="11.0"/>
+    <col min="8" max="8" customWidth="true" width="12.7142857142857"/>
+    <col min="9" max="9" customWidth="true" width="5.85714285714286"/>
+    <col min="10" max="10" customWidth="true" width="6.0"/>
+    <col min="11" max="11" customWidth="true" width="5.85714285714286"/>
+    <col min="12" max="12" customWidth="true" width="14.2857142857143"/>
+    <col min="13" max="13" customWidth="true" width="9.42857142857143"/>
+    <col min="14" max="14" customWidth="true" width="14.4285714285714"/>
+    <col min="15" max="15" customWidth="true" width="15.5714285714286"/>
+    <col min="16" max="16" customWidth="true" width="14.4285714285714"/>
+    <col min="17" max="17" customWidth="true" width="39.4285714285714"/>
+    <col min="18" max="18" customWidth="true" width="11.7142857142857"/>
+    <col min="19" max="19" customWidth="true" width="11.8571428571429"/>
+    <col min="20" max="20" customWidth="true" width="6.42857142857143"/>
+    <col min="21" max="22" customWidth="true" width="6.57142857142857"/>
+    <col min="23" max="23" customWidth="true" width="37.1428571428571"/>
+    <col min="24" max="25" customWidth="true" width="8.0"/>
+    <col min="26" max="26" customWidth="true" width="7.71428571428571"/>
+    <col min="27" max="27" customWidth="true" width="6.28571428571429"/>
+    <col min="28" max="28" customWidth="true" width="9.28571428571429"/>
+    <col min="29" max="29" customWidth="true" width="9.71428571428571"/>
+    <col min="30" max="30" customWidth="true" width="12.8571428571429"/>
+    <col min="31" max="31" customWidth="true" width="16.1428571428571"/>
+    <col min="32" max="32" customWidth="true" width="15.4285714285714"/>
+    <col min="33" max="33" customWidth="true" width="24.5714285714286"/>
+    <col min="34" max="34" customWidth="true" width="8.57142857142857"/>
+    <col min="35" max="35" customWidth="true" width="14.7142857142857"/>
+    <col min="36" max="36" customWidth="true" width="18.5714285714286"/>
+    <col min="37" max="37" customWidth="true" width="14.1428571428571"/>
+    <col min="38" max="38" customWidth="true" width="14.7142857142857"/>
+    <col min="39" max="39" customWidth="true" width="17.4285714285714"/>
+    <col min="40" max="40" customWidth="true" width="22.0"/>
+    <col min="41" max="41" customWidth="true" width="17.5714285714286"/>
+    <col min="42" max="42" customWidth="true" width="25.2857142857143"/>
+    <col min="43" max="43" customWidth="true" width="13.0"/>
+    <col min="44" max="44" customWidth="true" width="23.7142857142857"/>
+    <col min="45" max="45" customWidth="true" width="10.0"/>
+    <col min="46" max="46" customWidth="true" width="13.0"/>
+    <col min="47" max="47" customWidth="true" width="15.5714285714286"/>
+    <col min="48" max="48" customWidth="true" width="21.1428571428571"/>
+    <col min="49" max="49" customWidth="true" width="11.5714285714286"/>
+    <col min="50" max="50" customWidth="true" width="16.7142857142857"/>
+    <col min="51" max="51" customWidth="true" width="14.0"/>
+    <col min="52" max="52" customWidth="true" width="19.4285714285714"/>
+    <col min="53" max="53" customWidth="true" width="18.8571428571429"/>
+    <col min="54" max="54" customWidth="true" width="23.2857142857143"/>
+    <col min="55" max="55" customWidth="true" width="15.5714285714286"/>
+    <col min="56" max="56" customWidth="true" width="14.2857142857143"/>
+    <col min="57" max="57" customWidth="true" width="17.0"/>
+    <col min="58" max="58" customWidth="true" width="16.2857142857143"/>
+    <col min="59" max="59" customWidth="true" width="13.5714285714286"/>
+    <col min="60" max="61" customWidth="true" width="12.7142857142857"/>
+    <col min="62" max="62" customWidth="true" width="21.8571428571429"/>
+    <col min="63" max="63" customWidth="true" width="30.5714285714286"/>
+    <col min="64" max="64" customWidth="true" width="10.0"/>
+    <col min="65" max="65" customWidth="true" width="42.5714285714286"/>
+    <col min="66" max="66" customWidth="true" width="38.1428571428571"/>
+    <col min="67" max="67" customWidth="true" width="19.4285714285714"/>
+    <col min="68" max="68" customWidth="true" width="35.4285714285714"/>
+    <col min="69" max="69" customWidth="true" width="9.57142857142857"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -21968,7 +21983,7 @@
       <c r="BP2" s="32"/>
       <c r="BQ2" s="32"/>
     </row>
-    <row r="3" ht="15.25" spans="1:69">
+    <row r="3" ht="15.75" spans="1:69">
       <c r="A3" s="33" t="s">
         <v>9</v>
       </c>
@@ -22177,7 +22192,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.25" spans="1:69">
+    <row r="4" ht="15.75" spans="1:69">
       <c r="A4" s="31">
         <v>1</v>
       </c>
@@ -22248,7 +22263,7 @@
         <v>88363222</v>
       </c>
       <c r="U4" s="17">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="V4" s="17">
         <f>IF(OR($C$2=1,$C$2=4),ROUND((((S4*U4)/100)/2),2),0)</f>
@@ -22260,7 +22275,7 @@
       </c>
       <c r="X4" s="17">
         <f>IF($C$2=2,ROUND(((S4*U4)/100),2),0)</f>
-        <v>0</v>
+        <v>68.46</v>
       </c>
       <c r="Y4" s="17">
         <f>IF($C$2=4,ROUND((((S4*U4)/100)/2),2),0)</f>
@@ -22275,11 +22290,11 @@
       </c>
       <c r="AB4" s="17">
         <f>V4+W4+X4+Y4+AA4</f>
-        <v>15.2128</v>
+        <v>83.6728</v>
       </c>
       <c r="AC4" s="17">
         <f>IF($V2=1,S4+AB4,S4)</f>
-        <v>395.5328</v>
+        <v>463.9928</v>
       </c>
       <c r="AD4" s="17">
         <v>120</v>
@@ -22446,18 +22461,18 @@
       </c>
       <c r="X5" s="42">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>68.46</v>
       </c>
       <c r="Y5" s="44"/>
       <c r="Z5" s="44"/>
       <c r="AA5" s="44"/>
       <c r="AB5" s="42">
         <f t="shared" ref="AB5:AE5" si="1">SUM(AB4:AB4)</f>
-        <v>15.2128</v>
+        <v>83.6728</v>
       </c>
       <c r="AC5" s="42">
         <f t="shared" si="1"/>
-        <v>395.5328</v>
+        <v>463.9928</v>
       </c>
       <c r="AD5" s="42">
         <f t="shared" si="1"/>
@@ -22534,73 +22549,73 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:BQ5"/>
-  <sheetFormatPr defaultColWidth="8.70909090909091" defaultRowHeight="14.5" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="8.7047619047619" defaultRowHeight="15" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" width="5.14545454545455" customWidth="1"/>
-    <col min="2" max="3" width="28.2818181818182" customWidth="1"/>
-    <col min="4" max="4" width="79.4272727272727" customWidth="1"/>
-    <col min="5" max="5" width="11.5727272727273" customWidth="1"/>
-    <col min="6" max="6" width="5.14545454545455" customWidth="1"/>
-    <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="12.7181818181818" customWidth="1"/>
-    <col min="9" max="9" width="5.85454545454545" customWidth="1"/>
-    <col min="10" max="10" width="6" customWidth="1"/>
-    <col min="11" max="11" width="5.85454545454545" customWidth="1"/>
-    <col min="12" max="12" width="14.2818181818182" customWidth="1"/>
-    <col min="13" max="13" width="9.42727272727273" customWidth="1"/>
-    <col min="14" max="14" width="14.4272727272727" customWidth="1"/>
-    <col min="15" max="15" width="15.5727272727273" customWidth="1"/>
-    <col min="16" max="16" width="14.4272727272727" customWidth="1"/>
-    <col min="17" max="17" width="39.4272727272727" customWidth="1"/>
-    <col min="18" max="18" width="11.7181818181818" customWidth="1"/>
-    <col min="19" max="19" width="11.8545454545455" customWidth="1"/>
-    <col min="20" max="20" width="6.42727272727273" customWidth="1"/>
-    <col min="21" max="22" width="6.57272727272727" customWidth="1"/>
-    <col min="23" max="23" width="37.1454545454545" customWidth="1"/>
-    <col min="24" max="25" width="8" customWidth="1"/>
-    <col min="26" max="26" width="7.71818181818182" customWidth="1"/>
-    <col min="27" max="27" width="6.28181818181818" customWidth="1"/>
-    <col min="28" max="28" width="9.28181818181818" customWidth="1"/>
-    <col min="29" max="29" width="9.71818181818182" customWidth="1"/>
-    <col min="30" max="30" width="12.8545454545455" customWidth="1"/>
-    <col min="31" max="31" width="16.1454545454545" customWidth="1"/>
-    <col min="32" max="32" width="15.4272727272727" customWidth="1"/>
-    <col min="33" max="33" width="24.5727272727273" customWidth="1"/>
-    <col min="34" max="34" width="8.57272727272727" customWidth="1"/>
-    <col min="35" max="35" width="14.7181818181818" customWidth="1"/>
-    <col min="36" max="36" width="18.5727272727273" customWidth="1"/>
-    <col min="37" max="37" width="14.1454545454545" customWidth="1"/>
-    <col min="38" max="38" width="14.7181818181818" customWidth="1"/>
-    <col min="39" max="39" width="17.4272727272727" customWidth="1"/>
-    <col min="40" max="40" width="22" customWidth="1"/>
-    <col min="41" max="41" width="17.5727272727273" customWidth="1"/>
-    <col min="42" max="42" width="25.2818181818182" customWidth="1"/>
-    <col min="43" max="43" width="13" customWidth="1"/>
-    <col min="44" max="44" width="23.7181818181818" customWidth="1"/>
-    <col min="45" max="45" width="10" customWidth="1"/>
-    <col min="46" max="46" width="13" customWidth="1"/>
-    <col min="47" max="47" width="15.5727272727273" customWidth="1"/>
-    <col min="48" max="48" width="21.1454545454545" customWidth="1"/>
-    <col min="49" max="49" width="11.5727272727273" customWidth="1"/>
-    <col min="50" max="50" width="16.7181818181818" customWidth="1"/>
-    <col min="51" max="51" width="14" customWidth="1"/>
-    <col min="52" max="52" width="19.4272727272727" customWidth="1"/>
-    <col min="53" max="53" width="18.8545454545455" customWidth="1"/>
-    <col min="54" max="54" width="23.2818181818182" customWidth="1"/>
-    <col min="55" max="55" width="15.5727272727273" customWidth="1"/>
-    <col min="56" max="56" width="14.2818181818182" customWidth="1"/>
-    <col min="57" max="57" width="17" customWidth="1"/>
-    <col min="58" max="58" width="16.2818181818182" customWidth="1"/>
-    <col min="59" max="59" width="13.5727272727273" customWidth="1"/>
-    <col min="60" max="61" width="12.7181818181818" customWidth="1"/>
-    <col min="62" max="62" width="21.8545454545455" customWidth="1"/>
-    <col min="63" max="63" width="30.5727272727273" customWidth="1"/>
-    <col min="64" max="64" width="10" customWidth="1"/>
-    <col min="65" max="65" width="42.5727272727273" customWidth="1"/>
-    <col min="66" max="66" width="38.1454545454545" customWidth="1"/>
-    <col min="67" max="67" width="19.4272727272727" customWidth="1"/>
-    <col min="68" max="68" width="35.4272727272727" customWidth="1"/>
-    <col min="69" max="69" width="9.57272727272727" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="5.14285714285714"/>
+    <col min="2" max="3" customWidth="true" width="28.2857142857143"/>
+    <col min="4" max="4" customWidth="true" width="79.4285714285714"/>
+    <col min="5" max="5" customWidth="true" width="11.5714285714286"/>
+    <col min="6" max="6" customWidth="true" width="5.14285714285714"/>
+    <col min="7" max="7" customWidth="true" width="11.0"/>
+    <col min="8" max="8" customWidth="true" width="12.7142857142857"/>
+    <col min="9" max="9" customWidth="true" width="5.85714285714286"/>
+    <col min="10" max="10" customWidth="true" width="6.0"/>
+    <col min="11" max="11" customWidth="true" width="5.85714285714286"/>
+    <col min="12" max="12" customWidth="true" width="14.2857142857143"/>
+    <col min="13" max="13" customWidth="true" width="9.42857142857143"/>
+    <col min="14" max="14" customWidth="true" width="14.4285714285714"/>
+    <col min="15" max="15" customWidth="true" width="15.5714285714286"/>
+    <col min="16" max="16" customWidth="true" width="14.4285714285714"/>
+    <col min="17" max="17" customWidth="true" width="39.4285714285714"/>
+    <col min="18" max="18" customWidth="true" width="11.7142857142857"/>
+    <col min="19" max="19" customWidth="true" width="11.8571428571429"/>
+    <col min="20" max="20" customWidth="true" width="6.42857142857143"/>
+    <col min="21" max="22" customWidth="true" width="6.57142857142857"/>
+    <col min="23" max="23" customWidth="true" width="37.1428571428571"/>
+    <col min="24" max="25" customWidth="true" width="8.0"/>
+    <col min="26" max="26" customWidth="true" width="7.71428571428571"/>
+    <col min="27" max="27" customWidth="true" width="6.28571428571429"/>
+    <col min="28" max="28" customWidth="true" width="9.28571428571429"/>
+    <col min="29" max="29" customWidth="true" width="9.71428571428571"/>
+    <col min="30" max="30" customWidth="true" width="12.8571428571429"/>
+    <col min="31" max="31" customWidth="true" width="16.1428571428571"/>
+    <col min="32" max="32" customWidth="true" width="15.4285714285714"/>
+    <col min="33" max="33" customWidth="true" width="24.5714285714286"/>
+    <col min="34" max="34" customWidth="true" width="8.57142857142857"/>
+    <col min="35" max="35" customWidth="true" width="14.7142857142857"/>
+    <col min="36" max="36" customWidth="true" width="18.5714285714286"/>
+    <col min="37" max="37" customWidth="true" width="14.1428571428571"/>
+    <col min="38" max="38" customWidth="true" width="14.7142857142857"/>
+    <col min="39" max="39" customWidth="true" width="17.4285714285714"/>
+    <col min="40" max="40" customWidth="true" width="22.0"/>
+    <col min="41" max="41" customWidth="true" width="17.5714285714286"/>
+    <col min="42" max="42" customWidth="true" width="25.2857142857143"/>
+    <col min="43" max="43" customWidth="true" width="13.0"/>
+    <col min="44" max="44" customWidth="true" width="23.7142857142857"/>
+    <col min="45" max="45" customWidth="true" width="10.0"/>
+    <col min="46" max="46" customWidth="true" width="13.0"/>
+    <col min="47" max="47" customWidth="true" width="15.5714285714286"/>
+    <col min="48" max="48" customWidth="true" width="21.1428571428571"/>
+    <col min="49" max="49" customWidth="true" width="11.5714285714286"/>
+    <col min="50" max="50" customWidth="true" width="16.7142857142857"/>
+    <col min="51" max="51" customWidth="true" width="14.0"/>
+    <col min="52" max="52" customWidth="true" width="19.4285714285714"/>
+    <col min="53" max="53" customWidth="true" width="18.8571428571429"/>
+    <col min="54" max="54" customWidth="true" width="23.2857142857143"/>
+    <col min="55" max="55" customWidth="true" width="15.5714285714286"/>
+    <col min="56" max="56" customWidth="true" width="14.2857142857143"/>
+    <col min="57" max="57" customWidth="true" width="17.0"/>
+    <col min="58" max="58" customWidth="true" width="16.2857142857143"/>
+    <col min="59" max="59" customWidth="true" width="13.5714285714286"/>
+    <col min="60" max="61" customWidth="true" width="12.7142857142857"/>
+    <col min="62" max="62" customWidth="true" width="21.8571428571429"/>
+    <col min="63" max="63" customWidth="true" width="30.5714285714286"/>
+    <col min="64" max="64" customWidth="true" width="10.0"/>
+    <col min="65" max="65" customWidth="true" width="42.5714285714286"/>
+    <col min="66" max="66" customWidth="true" width="38.1428571428571"/>
+    <col min="67" max="67" customWidth="true" width="19.4285714285714"/>
+    <col min="68" max="68" customWidth="true" width="35.4285714285714"/>
+    <col min="69" max="69" customWidth="true" width="9.57142857142857"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:69">
@@ -22771,7 +22786,7 @@
       <c r="BP2" s="32"/>
       <c r="BQ2" s="32"/>
     </row>
-    <row r="3" ht="15.25" spans="1:69">
+    <row r="3" ht="15.75" spans="1:69">
       <c r="A3" s="33" t="s">
         <v>9</v>
       </c>
@@ -22980,7 +22995,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" ht="15.25" spans="1:69">
+    <row r="4" ht="15.75" spans="1:69">
       <c r="A4" s="31">
         <v>1</v>
       </c>
@@ -23051,7 +23066,7 @@
         <v>88363222</v>
       </c>
       <c r="U4" s="17">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="V4" s="17">
         <f>IF(OR($C$2=1,$C$2=4),ROUND((((S4*U4)/100)/2),2),0)</f>
@@ -23063,7 +23078,7 @@
       </c>
       <c r="X4" s="17">
         <f>IF($C$2=2,ROUND(((S4*U4)/100),2),0)</f>
-        <v>0</v>
+        <v>67.77</v>
       </c>
       <c r="Y4" s="17">
         <f>IF($C$2=4,ROUND((((S4*U4)/100)/2),2),0)</f>
@@ -23078,11 +23093,11 @@
       </c>
       <c r="AB4" s="17">
         <f>V4+W4+X4+Y4+AA4</f>
-        <v>15.0592</v>
+        <v>82.8292</v>
       </c>
       <c r="AC4" s="17">
         <f>IF($V2=1,S4+AB4,S4)</f>
-        <v>391.5392</v>
+        <v>459.3092</v>
       </c>
       <c r="AD4" s="17">
         <v>120</v>
@@ -23249,18 +23264,18 @@
       </c>
       <c r="X5" s="42">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>67.77</v>
       </c>
       <c r="Y5" s="44"/>
       <c r="Z5" s="44"/>
       <c r="AA5" s="44"/>
       <c r="AB5" s="42">
         <f t="shared" ref="AB5:AE5" si="1">SUM(AB4:AB4)</f>
-        <v>15.0592</v>
+        <v>82.8292</v>
       </c>
       <c r="AC5" s="42">
         <f t="shared" si="1"/>
-        <v>391.5392</v>
+        <v>459.3092</v>
       </c>
       <c r="AD5" s="42">
         <f t="shared" si="1"/>
